--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Rd3966e316d314f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Rd8b19a3e329f4630"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,13 +155,13 @@
     <xdr:ext cx="19050000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="f5b6ec1f-e092-4e41-9372-aaa1100ebf4c"/>
+        <xdr:cNvPr id="1" name="dfa4d9af-c8c6-4be9-a947-5792b243477e"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R26e989f7367342c8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0efe5866820b4a75"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1225,9 +1225,9 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R14a049cdb6fd487b"/>
+  <x:drawing ns1:id="R5342fe0e312544f7"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R79ccfdaf7b824d3b"/>
+    <x:tablePart ns1:id="R6a49ab1f8c724309"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Rd8b19a3e329f4630"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R20747da7feaf4bab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,13 +155,13 @@
     <xdr:ext cx="19050000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="dfa4d9af-c8c6-4be9-a947-5792b243477e"/>
+        <xdr:cNvPr id="1" name="2fddf357-8ca6-4d83-9b2f-4438712ed752"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0efe5866820b4a75"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R713a710065d7498d"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1225,9 +1225,9 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R5342fe0e312544f7"/>
+  <x:drawing ns1:id="R200d63594e6240fb"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R6a49ab1f8c724309"/>
+    <x:tablePart ns1:id="R0c5bff48e48f455f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R20747da7feaf4bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R6834d36f50b54332"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -155,13 +155,13 @@
     <xdr:ext cx="19050000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="2fddf357-8ca6-4d83-9b2f-4438712ed752"/>
+        <xdr:cNvPr id="1" name="e7596c26-f2ef-4094-8095-fb5019c1f948"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R713a710065d7498d"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc8fbd875c8494be6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -417,7 +417,7 @@
     <x:row r="2" ht="30" customHeight="1"/>
     <x:row r="3" ht="33" customHeight="1"/>
     <x:row r="4" ht="9" customHeight="1"/>
-    <x:row r="5" ht="42" customHeight="1">
+    <x:row r="5" hidden="0">
       <x:c r="A5" s="5" t="str">
         <x:v>Menu Location</x:v>
       </x:c>
@@ -467,7 +467,7 @@
         <x:v>Rapid Setup Order</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="60" customHeight="1">
+    <x:row r="6" hidden="0">
       <x:c r="A6" s="12" t="str">
         <x:v>Direct control; not normally changed through Q</x:v>
       </x:c>
@@ -517,7 +517,7 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" hidden="0">
       <x:c r="A7" s="12" t="str">
         <x:v>Shooting menu &gt; Metering mode</x:v>
       </x:c>
@@ -567,7 +567,7 @@
         <x:v>100</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="60" customHeight="1">
+    <x:row r="8" hidden="0">
       <x:c r="A8" s="12" t="str">
         <x:v>Direct control; Q is mode-dependent</x:v>
       </x:c>
@@ -617,7 +617,7 @@
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="44" customHeight="1">
+    <x:row r="9" hidden="0">
       <x:c r="A9" s="12" t="str">
         <x:v>Shooting 6 &gt; Shutter mode</x:v>
       </x:c>
@@ -667,7 +667,7 @@
         <x:v>210</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="60" customHeight="1">
+    <x:row r="10" hidden="0">
       <x:c r="A10" s="12" t="str">
         <x:v>Direct control; Q is mode-dependent</x:v>
       </x:c>
@@ -717,7 +717,7 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="60" customHeight="1">
+    <x:row r="11" hidden="0">
       <x:c r="A11" s="12" t="str">
         <x:v>Shooting menu &gt; ISO speed settings</x:v>
       </x:c>
@@ -767,7 +767,7 @@
         <x:v>110</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="60" customHeight="1">
+    <x:row r="12" hidden="0">
       <x:c r="A12" s="12" t="str">
         <x:v>Direct control; Q is the alternative</x:v>
       </x:c>
@@ -817,7 +817,7 @@
         <x:v>120</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="44" customHeight="1">
+    <x:row r="13" hidden="0">
       <x:c r="A13" s="12" t="str">
         <x:v>AF1 &gt; AF operation</x:v>
       </x:c>
@@ -867,7 +867,7 @@
         <x:v>130</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="60" customHeight="1">
+    <x:row r="14" hidden="0">
       <x:c r="A14" s="12" t="str">
         <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
       </x:c>
@@ -917,7 +917,7 @@
         <x:v>140</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="44" customHeight="1">
+    <x:row r="15" hidden="0">
       <x:c r="A15" s="12" t="str">
         <x:v>AF1 &gt; Subject to detect</x:v>
       </x:c>
@@ -967,7 +967,7 @@
         <x:v>220</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="76" customHeight="1">
+    <x:row r="16" hidden="0">
       <x:c r="A16" s="12" t="str">
         <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
       </x:c>
@@ -1017,7 +1017,7 @@
         <x:v>150</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="44" customHeight="1">
+    <x:row r="17" hidden="0">
       <x:c r="A17" s="12" t="str">
         <x:v>Shooting menu &gt; Drive mode</x:v>
       </x:c>
@@ -1067,7 +1067,7 @@
         <x:v>160</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="84" customHeight="1">
+    <x:row r="18" hidden="0">
       <x:c r="A18" s="12" t="str">
         <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
       </x:c>
@@ -1117,7 +1117,7 @@
         <x:v>230</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="84" customHeight="1">
+    <x:row r="19" hidden="0">
       <x:c r="A19" s="12" t="str">
         <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
       </x:c>
@@ -1167,7 +1167,7 @@
         <x:v>40</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="44" customHeight="1">
+    <x:row r="20" hidden="0">
       <x:c r="A20" s="12" t="str">
         <x:v>Shooting 5 &gt; Focus bracketing</x:v>
       </x:c>
@@ -1225,9 +1225,9 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R200d63594e6240fb"/>
+  <x:drawing ns1:id="R953e461ae7d64fab"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R0c5bff48e48f455f"/>
+    <x:tablePart ns1:id="R3a8fd80b2a62415f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R6834d36f50b54332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R5df6c82b87f445b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R44e8aba10eeb4d08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +17,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -36,8 +37,38 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="1"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -54,6 +85,21 @@
         <x:fgColor rgb="FFB7791F"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE8F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F5F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -61,7 +107,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -117,11 +163,212 @@
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="19">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:i/>
@@ -139,6 +386,36 @@
         <x:color rgb="FF9AA4AE"/>
       </x:font>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
@@ -152,16 +429,16 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="19050000" cy="1200150"/>
+    <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="e7596c26-f2ef-4094-8095-fb5019c1f948"/>
+        <xdr:cNvPr id="1" name="fcb4f8a7-5021-4b9e-833b-74f422a50bab"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc8fbd875c8494be6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd54e2ae9fe4b4533"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -176,25 +453,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A5:P20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:P20"/>
-  <x:tableColumns count="16">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:S21"/>
+  <x:tableColumns count="19">
     <x:tableColumn id="1" name="Menu Location"/>
     <x:tableColumn id="2" name="Best or Quick Access"/>
     <x:tableColumn id="3" name="Setting"/>
-    <x:tableColumn id="4" name="Default Settings"/>
-    <x:tableColumn id="5" name="Birds in Flight"/>
-    <x:tableColumn id="6" name="Birds Perched"/>
-    <x:tableColumn id="7" name="Fireworks"/>
-    <x:tableColumn id="8" name="Landscape"/>
-    <x:tableColumn id="9" name="Macro"/>
-    <x:tableColumn id="10" name="People"/>
-    <x:tableColumn id="11" name="Sports"/>
-    <x:tableColumn id="12" name="Travel"/>
-    <x:tableColumn id="13" name="Waterdrops"/>
-    <x:tableColumn id="14" name="Wildlife"/>
-    <x:tableColumn id="15" name="Card Order"/>
-    <x:tableColumn id="16" name="Rapid Setup Order"/>
+    <x:tableColumn id="4" name="C1 Wildlife"/>
+    <x:tableColumn id="5" name="C2 Birds in Flight"/>
+    <x:tableColumn id="6" name="C3 Landscape"/>
+    <x:tableColumn id="7" name="Default Settings"/>
+    <x:tableColumn id="8" name="Birds in Flight"/>
+    <x:tableColumn id="9" name="Birds Perched"/>
+    <x:tableColumn id="10" name="Fireworks"/>
+    <x:tableColumn id="11" name="Landscape"/>
+    <x:tableColumn id="12" name="Macro"/>
+    <x:tableColumn id="13" name="People"/>
+    <x:tableColumn id="14" name="Sports"/>
+    <x:tableColumn id="15" name="Travel"/>
+    <x:tableColumn id="16" name="Waterdrops"/>
+    <x:tableColumn id="17" name="Wildlife"/>
+    <x:tableColumn id="18" name="Card Order"/>
+    <x:tableColumn id="19" name="Rapid Setup Order"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A2:D17"/>
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="Setting"/>
+    <x:tableColumn id="2" name="C1 Wildlife"/>
+    <x:tableColumn id="3" name="C2 Birds in Flight"/>
+    <x:tableColumn id="4" name="C3 Landscape"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -395,6 +688,20 @@
 <x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="20" max="20" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="21" max="21" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="22" max="22" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="23" max="23" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="24" max="24" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="25" max="25" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="26" max="26" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="27" max="27" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="28" max="28" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="29" max="29" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="30" max="30" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="31" max="31" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="32" max="32" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="33" max="33" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="1" max="1" width="12.5600004196167" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.890000343322754" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.890000343322754" hidden="0" customWidth="1"/>
@@ -409,825 +716,2578 @@
     <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="31.5" customHeight="1"/>
-    <x:row r="2" ht="30" customHeight="1"/>
-    <x:row r="3" ht="33" customHeight="1"/>
-    <x:row r="4" ht="9" customHeight="1"/>
-    <x:row r="5" hidden="0">
-      <x:c r="A5" s="5" t="str">
+    <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="T1" s="38"/>
+      <x:c r="U1" s="38"/>
+      <x:c r="V1" s="38"/>
+      <x:c r="W1" s="38"/>
+      <x:c r="X1" s="38"/>
+      <x:c r="Y1" s="38"/>
+      <x:c r="Z1" s="38"/>
+      <x:c r="AA1" s="38"/>
+      <x:c r="AB1" s="38"/>
+      <x:c r="AC1" s="38"/>
+      <x:c r="AD1" s="38"/>
+      <x:c r="AE1" s="38"/>
+      <x:c r="AF1" s="38"/>
+      <x:c r="AG1" s="38"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="T2" s="38"/>
+      <x:c r="U2" s="38"/>
+      <x:c r="V2" s="38"/>
+      <x:c r="W2" s="38"/>
+      <x:c r="X2" s="38"/>
+      <x:c r="Y2" s="38"/>
+      <x:c r="Z2" s="38"/>
+      <x:c r="AA2" s="38"/>
+      <x:c r="AB2" s="38"/>
+      <x:c r="AC2" s="38"/>
+      <x:c r="AD2" s="38"/>
+      <x:c r="AE2" s="38"/>
+      <x:c r="AF2" s="38"/>
+      <x:c r="AG2" s="38"/>
+    </x:row>
+    <x:row r="3" ht="33" customHeight="1">
+      <x:c r="T3" s="38"/>
+      <x:c r="U3" s="38"/>
+      <x:c r="V3" s="38"/>
+      <x:c r="W3" s="38"/>
+      <x:c r="X3" s="38"/>
+      <x:c r="Y3" s="38"/>
+      <x:c r="Z3" s="38"/>
+      <x:c r="AA3" s="38"/>
+      <x:c r="AB3" s="38"/>
+      <x:c r="AC3" s="38"/>
+      <x:c r="AD3" s="38"/>
+      <x:c r="AE3" s="38"/>
+      <x:c r="AF3" s="38"/>
+      <x:c r="AG3" s="38"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="24" t="str">
+        <x:v>Compare to:</x:v>
+      </x:c>
+      <x:c r="D4" s="28" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
+      <x:c r="E4" s="28" t="str">
+        <x:v>C2 Birds in Flight</x:v>
+      </x:c>
+      <x:c r="F4" s="28" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="G4" s="28" t="str">
+        <x:v>Default Settings</x:v>
+      </x:c>
+      <x:c r="H4" s="28" t="str">
+        <x:v>Birds in Flight</x:v>
+      </x:c>
+      <x:c r="I4" s="28" t="str">
+        <x:v>Birds Perched</x:v>
+      </x:c>
+      <x:c r="J4" s="28" t="str">
+        <x:v>Fireworks</x:v>
+      </x:c>
+      <x:c r="K4" s="28" t="str">
+        <x:v>Landscape</x:v>
+      </x:c>
+      <x:c r="L4" s="28" t="str">
+        <x:v>Macro</x:v>
+      </x:c>
+      <x:c r="M4" s="28" t="str">
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="N4" s="28" t="str">
+        <x:v>Sports</x:v>
+      </x:c>
+      <x:c r="O4" s="28" t="str">
+        <x:v>Travel</x:v>
+      </x:c>
+      <x:c r="P4" s="28" t="str">
+        <x:v>Waterdrops</x:v>
+      </x:c>
+      <x:c r="Q4" s="28" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="T4" s="38"/>
+      <x:c r="U4" s="38"/>
+      <x:c r="V4" s="38"/>
+      <x:c r="W4" s="38"/>
+      <x:c r="X4" s="38"/>
+      <x:c r="Y4" s="38"/>
+      <x:c r="Z4" s="38"/>
+      <x:c r="AA4" s="38"/>
+      <x:c r="AB4" s="38"/>
+      <x:c r="AC4" s="38"/>
+      <x:c r="AD4" s="38"/>
+      <x:c r="AE4" s="38"/>
+      <x:c r="AF4" s="38"/>
+      <x:c r="AG4" s="38"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="33" t="str">
+        <x:v>Card starts from:</x:v>
+      </x:c>
+      <x:c r="D5" s="37" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
+      <x:c r="E5" s="37" t="str">
+        <x:v>C2 Birds in Flight</x:v>
+      </x:c>
+      <x:c r="F5" s="37" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="G5" s="37" t="str">
+        <x:v>Camera defaults</x:v>
+      </x:c>
+      <x:c r="H5" s="37" t="str">
+        <x:v>C2 Birds in Flight</x:v>
+      </x:c>
+      <x:c r="I5" s="37" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
+      <x:c r="J5" s="37" t="str">
+        <x:v>C3 Landscape + SWITCH</x:v>
+      </x:c>
+      <x:c r="K5" s="37" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="L5" s="37" t="str">
+        <x:v>C3 Landscape + SWITCH</x:v>
+      </x:c>
+      <x:c r="M5" s="37" t="str">
+        <x:v>C1 Wildlife + SWITCH</x:v>
+      </x:c>
+      <x:c r="N5" s="37" t="str">
+        <x:v>C2 Birds in Flight + SWITCH</x:v>
+      </x:c>
+      <x:c r="O5" s="37" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="P5" s="37" t="str">
+        <x:v>C3 Landscape + SWITCH</x:v>
+      </x:c>
+      <x:c r="Q5" s="37" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
+      <x:c r="T5" s="38"/>
+      <x:c r="U5" s="38"/>
+      <x:c r="V5" s="38"/>
+      <x:c r="W5" s="38"/>
+      <x:c r="X5" s="38"/>
+      <x:c r="Y5" s="38"/>
+      <x:c r="Z5" s="38"/>
+      <x:c r="AA5" s="38"/>
+      <x:c r="AB5" s="38"/>
+      <x:c r="AC5" s="38"/>
+      <x:c r="AD5" s="38"/>
+      <x:c r="AE5" s="38"/>
+      <x:c r="AF5" s="38"/>
+      <x:c r="AG5" s="38"/>
+    </x:row>
+    <x:row r="6" hidden="0">
+      <x:c r="A6" s="5" t="str">
         <x:v>Menu Location</x:v>
       </x:c>
-      <x:c r="B5" s="6" t="str">
+      <x:c r="B6" s="6" t="str">
         <x:v>Best or Quick Access</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C6" s="7" t="str">
         <x:v>Setting</x:v>
       </x:c>
-      <x:c r="D5" s="6" t="str">
+      <x:c r="D6" s="6" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>C2 Birds in Flight</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
         <x:v>Default Settings</x:v>
       </x:c>
-      <x:c r="E5" s="6" t="str">
+      <x:c r="H6" s="6" t="str">
         <x:v>Birds in Flight</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="str">
+      <x:c r="I6" s="6" t="str">
         <x:v>Birds Perched</x:v>
       </x:c>
-      <x:c r="G5" s="6" t="str">
+      <x:c r="J6" s="6" t="str">
         <x:v>Fireworks</x:v>
       </x:c>
-      <x:c r="H5" s="6" t="str">
+      <x:c r="K6" s="6" t="str">
         <x:v>Landscape</x:v>
       </x:c>
-      <x:c r="I5" s="8" t="str">
+      <x:c r="L6" s="8" t="str">
         <x:v>Macro</x:v>
       </x:c>
-      <x:c r="J5" s="6" t="str">
+      <x:c r="M6" s="6" t="str">
         <x:v>People</x:v>
       </x:c>
-      <x:c r="K5" s="8" t="str">
+      <x:c r="N6" s="8" t="str">
         <x:v>Sports</x:v>
       </x:c>
-      <x:c r="L5" s="8" t="str">
+      <x:c r="O6" s="8" t="str">
         <x:v>Travel</x:v>
       </x:c>
-      <x:c r="M5" s="8" t="str">
+      <x:c r="P6" s="8" t="str">
         <x:v>Waterdrops</x:v>
       </x:c>
-      <x:c r="N5" s="6" t="str">
+      <x:c r="Q6" s="6" t="str">
         <x:v>Wildlife</x:v>
       </x:c>
-      <x:c r="O5" s="6" t="str">
+      <x:c r="R6" s="6" t="str">
         <x:v>Card Order</x:v>
       </x:c>
-      <x:c r="P5" s="6" t="str">
+      <x:c r="S6" s="6" t="str">
         <x:v>Rapid Setup Order</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" hidden="0">
-      <x:c r="A6" s="12" t="str">
-        <x:v>Direct control; not normally changed through Q</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>MODE button + Main Dial</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="str">
-        <x:v>Mode</x:v>
-      </x:c>
-      <x:c r="D6" s="17" t="str">
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="str">
-        <x:v>Tv</x:v>
-      </x:c>
-      <x:c r="F6" s="17" t="str">
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="G6" s="17" t="str">
-        <x:v>Manual</x:v>
-      </x:c>
-      <x:c r="H6" s="17" t="str">
-        <x:v>Av</x:v>
-      </x:c>
-      <x:c r="I6" s="17" t="str">
-        <x:v>Av</x:v>
-      </x:c>
-      <x:c r="J6" s="17" t="str">
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="K6" s="17" t="str">
-        <x:v>Tv</x:v>
-      </x:c>
-      <x:c r="L6" s="17" t="str">
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="M6" s="17" t="str">
-        <x:v>Manual</x:v>
-      </x:c>
-      <x:c r="N6" s="17" t="str">
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="O6" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P6" s="20" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="T6" s="38"/>
+      <x:c r="U6" s="38"/>
+      <x:c r="V6" s="38"/>
+      <x:c r="W6" s="38"/>
+      <x:c r="X6" s="38"/>
+      <x:c r="Y6" s="38"/>
+      <x:c r="Z6" s="38"/>
+      <x:c r="AA6" s="38"/>
+      <x:c r="AB6" s="38"/>
+      <x:c r="AC6" s="38"/>
+      <x:c r="AD6" s="38"/>
+      <x:c r="AE6" s="38"/>
+      <x:c r="AF6" s="38"/>
+      <x:c r="AG6" s="38"/>
     </x:row>
     <x:row r="7" hidden="0">
       <x:c r="A7" s="12" t="str">
-        <x:v>Shooting menu &gt; Metering mode</x:v>
+        <x:v>Direct control; not normally changed through Q</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>MODE button + Main Dial</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Metering</x:v>
+        <x:v>Mode</x:v>
       </x:c>
       <x:c r="D7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Fv</x:v>
       </x:c>
       <x:c r="E7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Tv</x:v>
       </x:c>
       <x:c r="F7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Av</x:v>
       </x:c>
       <x:c r="G7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Fv</x:v>
       </x:c>
       <x:c r="H7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Tv</x:v>
       </x:c>
       <x:c r="I7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Fv</x:v>
       </x:c>
       <x:c r="J7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Manual</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Av</x:v>
       </x:c>
       <x:c r="L7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Av</x:v>
       </x:c>
       <x:c r="M7" s="17" t="str">
-        <x:v>Evaluative</x:v>
+        <x:v>Fv</x:v>
       </x:c>
       <x:c r="N7" s="17" t="str">
-        <x:v>Evaluative</x:v>
-      </x:c>
-      <x:c r="O7" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P7" s="20" t="n">
-        <x:v>100</x:v>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="P7" s="17" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="Q7" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="R7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S7" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T7" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D7,IF($D$4="C2 Birds in Flight",E7,IF($D$4="C3 Landscape",F7,IF($D$4="Default Settings",G7,IF($D$4="Birds in Flight",H7,IF($D$4="Birds Perched",I7,IF($D$4="Fireworks",J7,IF($D$4="Landscape",K7,IF($D$4="Macro",L7,IF($D$4="People",M7,IF($D$4="Sports",N7,IF($D$4="Travel",O7,IF($D$4="Waterdrops",P7,IF($D$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="U7" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D7,IF($E$4="C2 Birds in Flight",E7,IF($E$4="C3 Landscape",F7,IF($E$4="Default Settings",G7,IF($E$4="Birds in Flight",H7,IF($E$4="Birds Perched",I7,IF($E$4="Fireworks",J7,IF($E$4="Landscape",K7,IF($E$4="Macro",L7,IF($E$4="People",M7,IF($E$4="Sports",N7,IF($E$4="Travel",O7,IF($E$4="Waterdrops",P7,IF($E$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="V7" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D7,IF($F$4="C2 Birds in Flight",E7,IF($F$4="C3 Landscape",F7,IF($F$4="Default Settings",G7,IF($F$4="Birds in Flight",H7,IF($F$4="Birds Perched",I7,IF($F$4="Fireworks",J7,IF($F$4="Landscape",K7,IF($F$4="Macro",L7,IF($F$4="People",M7,IF($F$4="Sports",N7,IF($F$4="Travel",O7,IF($F$4="Waterdrops",P7,IF($F$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="W7" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D7,IF($G$4="C2 Birds in Flight",E7,IF($G$4="C3 Landscape",F7,IF($G$4="Default Settings",G7,IF($G$4="Birds in Flight",H7,IF($G$4="Birds Perched",I7,IF($G$4="Fireworks",J7,IF($G$4="Landscape",K7,IF($G$4="Macro",L7,IF($G$4="People",M7,IF($G$4="Sports",N7,IF($G$4="Travel",O7,IF($G$4="Waterdrops",P7,IF($G$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="X7" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D7,IF($H$4="C2 Birds in Flight",E7,IF($H$4="C3 Landscape",F7,IF($H$4="Default Settings",G7,IF($H$4="Birds in Flight",H7,IF($H$4="Birds Perched",I7,IF($H$4="Fireworks",J7,IF($H$4="Landscape",K7,IF($H$4="Macro",L7,IF($H$4="People",M7,IF($H$4="Sports",N7,IF($H$4="Travel",O7,IF($H$4="Waterdrops",P7,IF($H$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="Y7" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D7,IF($I$4="C2 Birds in Flight",E7,IF($I$4="C3 Landscape",F7,IF($I$4="Default Settings",G7,IF($I$4="Birds in Flight",H7,IF($I$4="Birds Perched",I7,IF($I$4="Fireworks",J7,IF($I$4="Landscape",K7,IF($I$4="Macro",L7,IF($I$4="People",M7,IF($I$4="Sports",N7,IF($I$4="Travel",O7,IF($I$4="Waterdrops",P7,IF($I$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="Z7" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D7,IF($J$4="C2 Birds in Flight",E7,IF($J$4="C3 Landscape",F7,IF($J$4="Default Settings",G7,IF($J$4="Birds in Flight",H7,IF($J$4="Birds Perched",I7,IF($J$4="Fireworks",J7,IF($J$4="Landscape",K7,IF($J$4="Macro",L7,IF($J$4="People",M7,IF($J$4="Sports",N7,IF($J$4="Travel",O7,IF($J$4="Waterdrops",P7,IF($J$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AA7" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D7,IF($K$4="C2 Birds in Flight",E7,IF($K$4="C3 Landscape",F7,IF($K$4="Default Settings",G7,IF($K$4="Birds in Flight",H7,IF($K$4="Birds Perched",I7,IF($K$4="Fireworks",J7,IF($K$4="Landscape",K7,IF($K$4="Macro",L7,IF($K$4="People",M7,IF($K$4="Sports",N7,IF($K$4="Travel",O7,IF($K$4="Waterdrops",P7,IF($K$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="AB7" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D7,IF($L$4="C2 Birds in Flight",E7,IF($L$4="C3 Landscape",F7,IF($L$4="Default Settings",G7,IF($L$4="Birds in Flight",H7,IF($L$4="Birds Perched",I7,IF($L$4="Fireworks",J7,IF($L$4="Landscape",K7,IF($L$4="Macro",L7,IF($L$4="People",M7,IF($L$4="Sports",N7,IF($L$4="Travel",O7,IF($L$4="Waterdrops",P7,IF($L$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="AC7" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D7,IF($M$4="C2 Birds in Flight",E7,IF($M$4="C3 Landscape",F7,IF($M$4="Default Settings",G7,IF($M$4="Birds in Flight",H7,IF($M$4="Birds Perched",I7,IF($M$4="Fireworks",J7,IF($M$4="Landscape",K7,IF($M$4="Macro",L7,IF($M$4="People",M7,IF($M$4="Sports",N7,IF($M$4="Travel",O7,IF($M$4="Waterdrops",P7,IF($M$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="AD7" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D7,IF($N$4="C2 Birds in Flight",E7,IF($N$4="C3 Landscape",F7,IF($N$4="Default Settings",G7,IF($N$4="Birds in Flight",H7,IF($N$4="Birds Perched",I7,IF($N$4="Fireworks",J7,IF($N$4="Landscape",K7,IF($N$4="Macro",L7,IF($N$4="People",M7,IF($N$4="Sports",N7,IF($N$4="Travel",O7,IF($N$4="Waterdrops",P7,IF($N$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="AE7" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D7,IF($O$4="C2 Birds in Flight",E7,IF($O$4="C3 Landscape",F7,IF($O$4="Default Settings",G7,IF($O$4="Birds in Flight",H7,IF($O$4="Birds Perched",I7,IF($O$4="Fireworks",J7,IF($O$4="Landscape",K7,IF($O$4="Macro",L7,IF($O$4="People",M7,IF($O$4="Sports",N7,IF($O$4="Travel",O7,IF($O$4="Waterdrops",P7,IF($O$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="AF7" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D7,IF($P$4="C2 Birds in Flight",E7,IF($P$4="C3 Landscape",F7,IF($P$4="Default Settings",G7,IF($P$4="Birds in Flight",H7,IF($P$4="Birds Perched",I7,IF($P$4="Fireworks",J7,IF($P$4="Landscape",K7,IF($P$4="Macro",L7,IF($P$4="People",M7,IF($P$4="Sports",N7,IF($P$4="Travel",O7,IF($P$4="Waterdrops",P7,IF($P$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AG7" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D7,IF($Q$4="C2 Birds in Flight",E7,IF($Q$4="C3 Landscape",F7,IF($Q$4="Default Settings",G7,IF($Q$4="Birds in Flight",H7,IF($Q$4="Birds Perched",I7,IF($Q$4="Fireworks",J7,IF($Q$4="Landscape",K7,IF($Q$4="Macro",L7,IF($Q$4="People",M7,IF($Q$4="Sports",N7,IF($Q$4="Travel",O7,IF($Q$4="Waterdrops",P7,IF($Q$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
       </x:c>
     </x:row>
     <x:row r="8" hidden="0">
       <x:c r="A8" s="12" t="str">
-        <x:v>Direct control; Q is mode-dependent</x:v>
+        <x:v>Shooting menu &gt; Metering mode</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Main Dial / Fv exposure dials</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Shutter</x:v>
+        <x:v>Metering</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="E8" s="17" t="str">
-        <x:v>1/2000–1/4000</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="F8" s="17" t="str">
-        <x:v>1/500–1/1000</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="G8" s="17" t="str">
-        <x:v>2–6 s (start at 4 s)</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="H8" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="I8" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="J8" s="17" t="str">
-        <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="K8" s="17" t="str">
-        <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="L8" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="M8" s="17" t="str">
-        <x:v>1/200</x:v>
+        <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="N8" s="17" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="O8" s="20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P8" s="20" t="n">
-        <x:v>20</x:v>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="O8" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="P8" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="Q8" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="R8" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S8" s="20" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="T8" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D8,IF($D$4="C2 Birds in Flight",E8,IF($D$4="C3 Landscape",F8,IF($D$4="Default Settings",G8,IF($D$4="Birds in Flight",H8,IF($D$4="Birds Perched",I8,IF($D$4="Fireworks",J8,IF($D$4="Landscape",K8,IF($D$4="Macro",L8,IF($D$4="People",M8,IF($D$4="Sports",N8,IF($D$4="Travel",O8,IF($D$4="Waterdrops",P8,IF($D$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="U8" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D8,IF($E$4="C2 Birds in Flight",E8,IF($E$4="C3 Landscape",F8,IF($E$4="Default Settings",G8,IF($E$4="Birds in Flight",H8,IF($E$4="Birds Perched",I8,IF($E$4="Fireworks",J8,IF($E$4="Landscape",K8,IF($E$4="Macro",L8,IF($E$4="People",M8,IF($E$4="Sports",N8,IF($E$4="Travel",O8,IF($E$4="Waterdrops",P8,IF($E$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="V8" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D8,IF($F$4="C2 Birds in Flight",E8,IF($F$4="C3 Landscape",F8,IF($F$4="Default Settings",G8,IF($F$4="Birds in Flight",H8,IF($F$4="Birds Perched",I8,IF($F$4="Fireworks",J8,IF($F$4="Landscape",K8,IF($F$4="Macro",L8,IF($F$4="People",M8,IF($F$4="Sports",N8,IF($F$4="Travel",O8,IF($F$4="Waterdrops",P8,IF($F$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="W8" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D8,IF($G$4="C2 Birds in Flight",E8,IF($G$4="C3 Landscape",F8,IF($G$4="Default Settings",G8,IF($G$4="Birds in Flight",H8,IF($G$4="Birds Perched",I8,IF($G$4="Fireworks",J8,IF($G$4="Landscape",K8,IF($G$4="Macro",L8,IF($G$4="People",M8,IF($G$4="Sports",N8,IF($G$4="Travel",O8,IF($G$4="Waterdrops",P8,IF($G$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="X8" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D8,IF($H$4="C2 Birds in Flight",E8,IF($H$4="C3 Landscape",F8,IF($H$4="Default Settings",G8,IF($H$4="Birds in Flight",H8,IF($H$4="Birds Perched",I8,IF($H$4="Fireworks",J8,IF($H$4="Landscape",K8,IF($H$4="Macro",L8,IF($H$4="People",M8,IF($H$4="Sports",N8,IF($H$4="Travel",O8,IF($H$4="Waterdrops",P8,IF($H$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="Y8" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D8,IF($I$4="C2 Birds in Flight",E8,IF($I$4="C3 Landscape",F8,IF($I$4="Default Settings",G8,IF($I$4="Birds in Flight",H8,IF($I$4="Birds Perched",I8,IF($I$4="Fireworks",J8,IF($I$4="Landscape",K8,IF($I$4="Macro",L8,IF($I$4="People",M8,IF($I$4="Sports",N8,IF($I$4="Travel",O8,IF($I$4="Waterdrops",P8,IF($I$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="Z8" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D8,IF($J$4="C2 Birds in Flight",E8,IF($J$4="C3 Landscape",F8,IF($J$4="Default Settings",G8,IF($J$4="Birds in Flight",H8,IF($J$4="Birds Perched",I8,IF($J$4="Fireworks",J8,IF($J$4="Landscape",K8,IF($J$4="Macro",L8,IF($J$4="People",M8,IF($J$4="Sports",N8,IF($J$4="Travel",O8,IF($J$4="Waterdrops",P8,IF($J$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AA8" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D8,IF($K$4="C2 Birds in Flight",E8,IF($K$4="C3 Landscape",F8,IF($K$4="Default Settings",G8,IF($K$4="Birds in Flight",H8,IF($K$4="Birds Perched",I8,IF($K$4="Fireworks",J8,IF($K$4="Landscape",K8,IF($K$4="Macro",L8,IF($K$4="People",M8,IF($K$4="Sports",N8,IF($K$4="Travel",O8,IF($K$4="Waterdrops",P8,IF($K$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AB8" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D8,IF($L$4="C2 Birds in Flight",E8,IF($L$4="C3 Landscape",F8,IF($L$4="Default Settings",G8,IF($L$4="Birds in Flight",H8,IF($L$4="Birds Perched",I8,IF($L$4="Fireworks",J8,IF($L$4="Landscape",K8,IF($L$4="Macro",L8,IF($L$4="People",M8,IF($L$4="Sports",N8,IF($L$4="Travel",O8,IF($L$4="Waterdrops",P8,IF($L$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AC8" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D8,IF($M$4="C2 Birds in Flight",E8,IF($M$4="C3 Landscape",F8,IF($M$4="Default Settings",G8,IF($M$4="Birds in Flight",H8,IF($M$4="Birds Perched",I8,IF($M$4="Fireworks",J8,IF($M$4="Landscape",K8,IF($M$4="Macro",L8,IF($M$4="People",M8,IF($M$4="Sports",N8,IF($M$4="Travel",O8,IF($M$4="Waterdrops",P8,IF($M$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AD8" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D8,IF($N$4="C2 Birds in Flight",E8,IF($N$4="C3 Landscape",F8,IF($N$4="Default Settings",G8,IF($N$4="Birds in Flight",H8,IF($N$4="Birds Perched",I8,IF($N$4="Fireworks",J8,IF($N$4="Landscape",K8,IF($N$4="Macro",L8,IF($N$4="People",M8,IF($N$4="Sports",N8,IF($N$4="Travel",O8,IF($N$4="Waterdrops",P8,IF($N$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AE8" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D8,IF($O$4="C2 Birds in Flight",E8,IF($O$4="C3 Landscape",F8,IF($O$4="Default Settings",G8,IF($O$4="Birds in Flight",H8,IF($O$4="Birds Perched",I8,IF($O$4="Fireworks",J8,IF($O$4="Landscape",K8,IF($O$4="Macro",L8,IF($O$4="People",M8,IF($O$4="Sports",N8,IF($O$4="Travel",O8,IF($O$4="Waterdrops",P8,IF($O$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AF8" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D8,IF($P$4="C2 Birds in Flight",E8,IF($P$4="C3 Landscape",F8,IF($P$4="Default Settings",G8,IF($P$4="Birds in Flight",H8,IF($P$4="Birds Perched",I8,IF($P$4="Fireworks",J8,IF($P$4="Landscape",K8,IF($P$4="Macro",L8,IF($P$4="People",M8,IF($P$4="Sports",N8,IF($P$4="Travel",O8,IF($P$4="Waterdrops",P8,IF($P$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AG8" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D8,IF($Q$4="C2 Birds in Flight",E8,IF($Q$4="C3 Landscape",F8,IF($Q$4="Default Settings",G8,IF($Q$4="Birds in Flight",H8,IF($Q$4="Birds Perched",I8,IF($Q$4="Fireworks",J8,IF($Q$4="Landscape",K8,IF($Q$4="Macro",L8,IF($Q$4="People",M8,IF($Q$4="Sports",N8,IF($Q$4="Travel",O8,IF($Q$4="Waterdrops",P8,IF($Q$4="Wildlife",Q8,""))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
       </x:c>
     </x:row>
     <x:row r="9" hidden="0">
       <x:c r="A9" s="12" t="str">
-        <x:v>Shooting 6 &gt; Shutter mode</x:v>
+        <x:v>Direct control; Q is mode-dependent</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FLASH*/MM-LONG*</x:v>
+        <x:v>Main Dial / Fv exposure dials</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Shutter Type</x:v>
+        <x:v>Shutter</x:v>
       </x:c>
       <x:c r="D9" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="E9" s="17" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>1/2500 sec.</x:v>
       </x:c>
       <x:c r="F9" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="G9" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="H9" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>1/2000–1/4000</x:v>
       </x:c>
       <x:c r="I9" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>1/500–1/1000</x:v>
       </x:c>
       <x:c r="J9" s="17" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>2–6 s (start at 4 s)</x:v>
       </x:c>
       <x:c r="K9" s="17" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="L9" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="M9" s="17" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
       </x:c>
       <x:c r="N9" s="17" t="str">
-        <x:v>EFCS</x:v>
-      </x:c>
-      <x:c r="O9" s="20" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="P9" s="20" t="n">
-        <x:v>210</x:v>
+        <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
+      </x:c>
+      <x:c r="O9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P9" s="17" t="str">
+        <x:v>1/200</x:v>
+      </x:c>
+      <x:c r="Q9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R9" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S9" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="T9" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D9,IF($D$4="C2 Birds in Flight",E9,IF($D$4="C3 Landscape",F9,IF($D$4="Default Settings",G9,IF($D$4="Birds in Flight",H9,IF($D$4="Birds Perched",I9,IF($D$4="Fireworks",J9,IF($D$4="Landscape",K9,IF($D$4="Macro",L9,IF($D$4="People",M9,IF($D$4="Sports",N9,IF($D$4="Travel",O9,IF($D$4="Waterdrops",P9,IF($D$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="U9" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D9,IF($E$4="C2 Birds in Flight",E9,IF($E$4="C3 Landscape",F9,IF($E$4="Default Settings",G9,IF($E$4="Birds in Flight",H9,IF($E$4="Birds Perched",I9,IF($E$4="Fireworks",J9,IF($E$4="Landscape",K9,IF($E$4="Macro",L9,IF($E$4="People",M9,IF($E$4="Sports",N9,IF($E$4="Travel",O9,IF($E$4="Waterdrops",P9,IF($E$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/2500 sec.</x:v>
+      </x:c>
+      <x:c r="V9" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D9,IF($F$4="C2 Birds in Flight",E9,IF($F$4="C3 Landscape",F9,IF($F$4="Default Settings",G9,IF($F$4="Birds in Flight",H9,IF($F$4="Birds Perched",I9,IF($F$4="Fireworks",J9,IF($F$4="Landscape",K9,IF($F$4="Macro",L9,IF($F$4="People",M9,IF($F$4="Sports",N9,IF($F$4="Travel",O9,IF($F$4="Waterdrops",P9,IF($F$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="W9" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D9,IF($G$4="C2 Birds in Flight",E9,IF($G$4="C3 Landscape",F9,IF($G$4="Default Settings",G9,IF($G$4="Birds in Flight",H9,IF($G$4="Birds Perched",I9,IF($G$4="Fireworks",J9,IF($G$4="Landscape",K9,IF($G$4="Macro",L9,IF($G$4="People",M9,IF($G$4="Sports",N9,IF($G$4="Travel",O9,IF($G$4="Waterdrops",P9,IF($G$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X9" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D9,IF($H$4="C2 Birds in Flight",E9,IF($H$4="C3 Landscape",F9,IF($H$4="Default Settings",G9,IF($H$4="Birds in Flight",H9,IF($H$4="Birds Perched",I9,IF($H$4="Fireworks",J9,IF($H$4="Landscape",K9,IF($H$4="Macro",L9,IF($H$4="People",M9,IF($H$4="Sports",N9,IF($H$4="Travel",O9,IF($H$4="Waterdrops",P9,IF($H$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/2000–1/4000</x:v>
+      </x:c>
+      <x:c r="Y9" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D9,IF($I$4="C2 Birds in Flight",E9,IF($I$4="C3 Landscape",F9,IF($I$4="Default Settings",G9,IF($I$4="Birds in Flight",H9,IF($I$4="Birds Perched",I9,IF($I$4="Fireworks",J9,IF($I$4="Landscape",K9,IF($I$4="Macro",L9,IF($I$4="People",M9,IF($I$4="Sports",N9,IF($I$4="Travel",O9,IF($I$4="Waterdrops",P9,IF($I$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/500–1/1000</x:v>
+      </x:c>
+      <x:c r="Z9" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D9,IF($J$4="C2 Birds in Flight",E9,IF($J$4="C3 Landscape",F9,IF($J$4="Default Settings",G9,IF($J$4="Birds in Flight",H9,IF($J$4="Birds Perched",I9,IF($J$4="Fireworks",J9,IF($J$4="Landscape",K9,IF($J$4="Macro",L9,IF($J$4="People",M9,IF($J$4="Sports",N9,IF($J$4="Travel",O9,IF($J$4="Waterdrops",P9,IF($J$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>2–6 s (start at 4 s)</x:v>
+      </x:c>
+      <x:c r="AA9" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D9,IF($K$4="C2 Birds in Flight",E9,IF($K$4="C3 Landscape",F9,IF($K$4="Default Settings",G9,IF($K$4="Birds in Flight",H9,IF($K$4="Birds Perched",I9,IF($K$4="Fireworks",J9,IF($K$4="Landscape",K9,IF($K$4="Macro",L9,IF($K$4="People",M9,IF($K$4="Sports",N9,IF($K$4="Travel",O9,IF($K$4="Waterdrops",P9,IF($K$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AB9" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D9,IF($L$4="C2 Birds in Flight",E9,IF($L$4="C3 Landscape",F9,IF($L$4="Default Settings",G9,IF($L$4="Birds in Flight",H9,IF($L$4="Birds Perched",I9,IF($L$4="Fireworks",J9,IF($L$4="Landscape",K9,IF($L$4="Macro",L9,IF($L$4="People",M9,IF($L$4="Sports",N9,IF($L$4="Travel",O9,IF($L$4="Waterdrops",P9,IF($L$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AC9" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D9,IF($M$4="C2 Birds in Flight",E9,IF($M$4="C3 Landscape",F9,IF($M$4="Default Settings",G9,IF($M$4="Birds in Flight",H9,IF($M$4="Birds Perched",I9,IF($M$4="Fireworks",J9,IF($M$4="Landscape",K9,IF($M$4="Macro",L9,IF($M$4="People",M9,IF($M$4="Sports",N9,IF($M$4="Travel",O9,IF($M$4="Waterdrops",P9,IF($M$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
+      </x:c>
+      <x:c r="AD9" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D9,IF($N$4="C2 Birds in Flight",E9,IF($N$4="C3 Landscape",F9,IF($N$4="Default Settings",G9,IF($N$4="Birds in Flight",H9,IF($N$4="Birds Perched",I9,IF($N$4="Fireworks",J9,IF($N$4="Landscape",K9,IF($N$4="Macro",L9,IF($N$4="People",M9,IF($N$4="Sports",N9,IF($N$4="Travel",O9,IF($N$4="Waterdrops",P9,IF($N$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
+      </x:c>
+      <x:c r="AE9" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D9,IF($O$4="C2 Birds in Flight",E9,IF($O$4="C3 Landscape",F9,IF($O$4="Default Settings",G9,IF($O$4="Birds in Flight",H9,IF($O$4="Birds Perched",I9,IF($O$4="Fireworks",J9,IF($O$4="Landscape",K9,IF($O$4="Macro",L9,IF($O$4="People",M9,IF($O$4="Sports",N9,IF($O$4="Travel",O9,IF($O$4="Waterdrops",P9,IF($O$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF9" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D9,IF($P$4="C2 Birds in Flight",E9,IF($P$4="C3 Landscape",F9,IF($P$4="Default Settings",G9,IF($P$4="Birds in Flight",H9,IF($P$4="Birds Perched",I9,IF($P$4="Fireworks",J9,IF($P$4="Landscape",K9,IF($P$4="Macro",L9,IF($P$4="People",M9,IF($P$4="Sports",N9,IF($P$4="Travel",O9,IF($P$4="Waterdrops",P9,IF($P$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/200</x:v>
+      </x:c>
+      <x:c r="AG9" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D9,IF($Q$4="C2 Birds in Flight",E9,IF($Q$4="C3 Landscape",F9,IF($Q$4="Default Settings",G9,IF($Q$4="Birds in Flight",H9,IF($Q$4="Birds Perched",I9,IF($Q$4="Fireworks",J9,IF($Q$4="Landscape",K9,IF($Q$4="Macro",L9,IF($Q$4="People",M9,IF($Q$4="Sports",N9,IF($Q$4="Travel",O9,IF($Q$4="Waterdrops",P9,IF($Q$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="10" hidden="0">
       <x:c r="A10" s="12" t="str">
-        <x:v>Direct control; Q is mode-dependent</x:v>
+        <x:v>Shooting 6 &gt; Shutter mode</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>Main Dial / Fv exposure dials</x:v>
+        <x:v>MM-SWITCH; MM-FLASH*/MM-LONG*</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>Aperture</x:v>
+        <x:v>Shutter Type</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="E10" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="F10" s="17" t="str">
-        <x:v>f/8</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="G10" s="17" t="str">
-        <x:v>f/8–f/11</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="H10" s="17" t="str">
-        <x:v>f/8–f/11; bracket before f/16</x:v>
+        <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="I10" s="17" t="str">
-        <x:v>f/8</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="J10" s="17" t="str">
-        <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="K10" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="L10" s="17" t="str">
-        <x:v>—</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="M10" s="17" t="str">
-        <x:v>f/8–f/11</x:v>
+        <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="N10" s="17" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="O10" s="20" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P10" s="20" t="n">
-        <x:v>30</x:v>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="P10" s="17" t="str">
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="Q10" s="17" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="R10" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S10" s="20" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="T10" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D10,IF($D$4="C2 Birds in Flight",E10,IF($D$4="C3 Landscape",F10,IF($D$4="Default Settings",G10,IF($D$4="Birds in Flight",H10,IF($D$4="Birds Perched",I10,IF($D$4="Fireworks",J10,IF($D$4="Landscape",K10,IF($D$4="Macro",L10,IF($D$4="People",M10,IF($D$4="Sports",N10,IF($D$4="Travel",O10,IF($D$4="Waterdrops",P10,IF($D$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="U10" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D10,IF($E$4="C2 Birds in Flight",E10,IF($E$4="C3 Landscape",F10,IF($E$4="Default Settings",G10,IF($E$4="Birds in Flight",H10,IF($E$4="Birds Perched",I10,IF($E$4="Fireworks",J10,IF($E$4="Landscape",K10,IF($E$4="Macro",L10,IF($E$4="People",M10,IF($E$4="Sports",N10,IF($E$4="Travel",O10,IF($E$4="Waterdrops",P10,IF($E$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="V10" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D10,IF($F$4="C2 Birds in Flight",E10,IF($F$4="C3 Landscape",F10,IF($F$4="Default Settings",G10,IF($F$4="Birds in Flight",H10,IF($F$4="Birds Perched",I10,IF($F$4="Fireworks",J10,IF($F$4="Landscape",K10,IF($F$4="Macro",L10,IF($F$4="People",M10,IF($F$4="Sports",N10,IF($F$4="Travel",O10,IF($F$4="Waterdrops",P10,IF($F$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="W10" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D10,IF($G$4="C2 Birds in Flight",E10,IF($G$4="C3 Landscape",F10,IF($G$4="Default Settings",G10,IF($G$4="Birds in Flight",H10,IF($G$4="Birds Perched",I10,IF($G$4="Fireworks",J10,IF($G$4="Landscape",K10,IF($G$4="Macro",L10,IF($G$4="People",M10,IF($G$4="Sports",N10,IF($G$4="Travel",O10,IF($G$4="Waterdrops",P10,IF($G$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="X10" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D10,IF($H$4="C2 Birds in Flight",E10,IF($H$4="C3 Landscape",F10,IF($H$4="Default Settings",G10,IF($H$4="Birds in Flight",H10,IF($H$4="Birds Perched",I10,IF($H$4="Fireworks",J10,IF($H$4="Landscape",K10,IF($H$4="Macro",L10,IF($H$4="People",M10,IF($H$4="Sports",N10,IF($H$4="Travel",O10,IF($H$4="Waterdrops",P10,IF($H$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="Y10" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D10,IF($I$4="C2 Birds in Flight",E10,IF($I$4="C3 Landscape",F10,IF($I$4="Default Settings",G10,IF($I$4="Birds in Flight",H10,IF($I$4="Birds Perched",I10,IF($I$4="Fireworks",J10,IF($I$4="Landscape",K10,IF($I$4="Macro",L10,IF($I$4="People",M10,IF($I$4="Sports",N10,IF($I$4="Travel",O10,IF($I$4="Waterdrops",P10,IF($I$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="Z10" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D10,IF($J$4="C2 Birds in Flight",E10,IF($J$4="C3 Landscape",F10,IF($J$4="Default Settings",G10,IF($J$4="Birds in Flight",H10,IF($J$4="Birds Perched",I10,IF($J$4="Fireworks",J10,IF($J$4="Landscape",K10,IF($J$4="Macro",L10,IF($J$4="People",M10,IF($J$4="Sports",N10,IF($J$4="Travel",O10,IF($J$4="Waterdrops",P10,IF($J$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="AA10" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D10,IF($K$4="C2 Birds in Flight",E10,IF($K$4="C3 Landscape",F10,IF($K$4="Default Settings",G10,IF($K$4="Birds in Flight",H10,IF($K$4="Birds Perched",I10,IF($K$4="Fireworks",J10,IF($K$4="Landscape",K10,IF($K$4="Macro",L10,IF($K$4="People",M10,IF($K$4="Sports",N10,IF($K$4="Travel",O10,IF($K$4="Waterdrops",P10,IF($K$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="AB10" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D10,IF($L$4="C2 Birds in Flight",E10,IF($L$4="C3 Landscape",F10,IF($L$4="Default Settings",G10,IF($L$4="Birds in Flight",H10,IF($L$4="Birds Perched",I10,IF($L$4="Fireworks",J10,IF($L$4="Landscape",K10,IF($L$4="Macro",L10,IF($L$4="People",M10,IF($L$4="Sports",N10,IF($L$4="Travel",O10,IF($L$4="Waterdrops",P10,IF($L$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="AC10" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D10,IF($M$4="C2 Birds in Flight",E10,IF($M$4="C3 Landscape",F10,IF($M$4="Default Settings",G10,IF($M$4="Birds in Flight",H10,IF($M$4="Birds Perched",I10,IF($M$4="Fireworks",J10,IF($M$4="Landscape",K10,IF($M$4="Macro",L10,IF($M$4="People",M10,IF($M$4="Sports",N10,IF($M$4="Travel",O10,IF($M$4="Waterdrops",P10,IF($M$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="AD10" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D10,IF($N$4="C2 Birds in Flight",E10,IF($N$4="C3 Landscape",F10,IF($N$4="Default Settings",G10,IF($N$4="Birds in Flight",H10,IF($N$4="Birds Perched",I10,IF($N$4="Fireworks",J10,IF($N$4="Landscape",K10,IF($N$4="Macro",L10,IF($N$4="People",M10,IF($N$4="Sports",N10,IF($N$4="Travel",O10,IF($N$4="Waterdrops",P10,IF($N$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="AE10" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D10,IF($O$4="C2 Birds in Flight",E10,IF($O$4="C3 Landscape",F10,IF($O$4="Default Settings",G10,IF($O$4="Birds in Flight",H10,IF($O$4="Birds Perched",I10,IF($O$4="Fireworks",J10,IF($O$4="Landscape",K10,IF($O$4="Macro",L10,IF($O$4="People",M10,IF($O$4="Sports",N10,IF($O$4="Travel",O10,IF($O$4="Waterdrops",P10,IF($O$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="AF10" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D10,IF($P$4="C2 Birds in Flight",E10,IF($P$4="C3 Landscape",F10,IF($P$4="Default Settings",G10,IF($P$4="Birds in Flight",H10,IF($P$4="Birds Perched",I10,IF($P$4="Fireworks",J10,IF($P$4="Landscape",K10,IF($P$4="Macro",L10,IF($P$4="People",M10,IF($P$4="Sports",N10,IF($P$4="Travel",O10,IF($P$4="Waterdrops",P10,IF($P$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="AG10" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D10,IF($Q$4="C2 Birds in Flight",E10,IF($Q$4="C3 Landscape",F10,IF($Q$4="Default Settings",G10,IF($Q$4="Birds in Flight",H10,IF($Q$4="Birds Perched",I10,IF($Q$4="Fireworks",J10,IF($Q$4="Landscape",K10,IF($Q$4="Macro",L10,IF($Q$4="People",M10,IF($Q$4="Sports",N10,IF($Q$4="Travel",O10,IF($Q$4="Waterdrops",P10,IF($Q$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
       </x:c>
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11" s="12" t="str">
-        <x:v>Shooting menu &gt; ISO speed settings</x:v>
+        <x:v>Direct control; Q is mode-dependent</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>Main Dial / Fv exposure dials</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>ISO</x:v>
+        <x:v>Aperture</x:v>
       </x:c>
       <x:c r="D11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="E11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="F11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>f/9</x:v>
       </x:c>
       <x:c r="G11" s="17" t="str">
-        <x:v>100</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="H11" s="17" t="str">
-        <x:v>100</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="I11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>f/8</x:v>
       </x:c>
       <x:c r="J11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>f/8–f/11</x:v>
       </x:c>
       <x:c r="K11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>f/8–f/11; bracket before f/16</x:v>
       </x:c>
       <x:c r="L11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>f/8</x:v>
       </x:c>
       <x:c r="M11" s="17" t="str">
-        <x:v>100</x:v>
+        <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
       </x:c>
       <x:c r="N11" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="O11" s="20" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="P11" s="20" t="n">
-        <x:v>110</x:v>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P11" s="17" t="str">
+        <x:v>f/8–f/11</x:v>
+      </x:c>
+      <x:c r="Q11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R11" s="20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S11" s="20" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="T11" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D11,IF($D$4="C2 Birds in Flight",E11,IF($D$4="C3 Landscape",F11,IF($D$4="Default Settings",G11,IF($D$4="Birds in Flight",H11,IF($D$4="Birds Perched",I11,IF($D$4="Fireworks",J11,IF($D$4="Landscape",K11,IF($D$4="Macro",L11,IF($D$4="People",M11,IF($D$4="Sports",N11,IF($D$4="Travel",O11,IF($D$4="Waterdrops",P11,IF($D$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="U11" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D11,IF($E$4="C2 Birds in Flight",E11,IF($E$4="C3 Landscape",F11,IF($E$4="Default Settings",G11,IF($E$4="Birds in Flight",H11,IF($E$4="Birds Perched",I11,IF($E$4="Fireworks",J11,IF($E$4="Landscape",K11,IF($E$4="Macro",L11,IF($E$4="People",M11,IF($E$4="Sports",N11,IF($E$4="Travel",O11,IF($E$4="Waterdrops",P11,IF($E$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="V11" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D11,IF($F$4="C2 Birds in Flight",E11,IF($F$4="C3 Landscape",F11,IF($F$4="Default Settings",G11,IF($F$4="Birds in Flight",H11,IF($F$4="Birds Perched",I11,IF($F$4="Fireworks",J11,IF($F$4="Landscape",K11,IF($F$4="Macro",L11,IF($F$4="People",M11,IF($F$4="Sports",N11,IF($F$4="Travel",O11,IF($F$4="Waterdrops",P11,IF($F$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/9</x:v>
+      </x:c>
+      <x:c r="W11" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D11,IF($G$4="C2 Birds in Flight",E11,IF($G$4="C3 Landscape",F11,IF($G$4="Default Settings",G11,IF($G$4="Birds in Flight",H11,IF($G$4="Birds Perched",I11,IF($G$4="Fireworks",J11,IF($G$4="Landscape",K11,IF($G$4="Macro",L11,IF($G$4="People",M11,IF($G$4="Sports",N11,IF($G$4="Travel",O11,IF($G$4="Waterdrops",P11,IF($G$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X11" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D11,IF($H$4="C2 Birds in Flight",E11,IF($H$4="C3 Landscape",F11,IF($H$4="Default Settings",G11,IF($H$4="Birds in Flight",H11,IF($H$4="Birds Perched",I11,IF($H$4="Fireworks",J11,IF($H$4="Landscape",K11,IF($H$4="Macro",L11,IF($H$4="People",M11,IF($H$4="Sports",N11,IF($H$4="Travel",O11,IF($H$4="Waterdrops",P11,IF($H$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Y11" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D11,IF($I$4="C2 Birds in Flight",E11,IF($I$4="C3 Landscape",F11,IF($I$4="Default Settings",G11,IF($I$4="Birds in Flight",H11,IF($I$4="Birds Perched",I11,IF($I$4="Fireworks",J11,IF($I$4="Landscape",K11,IF($I$4="Macro",L11,IF($I$4="People",M11,IF($I$4="Sports",N11,IF($I$4="Travel",O11,IF($I$4="Waterdrops",P11,IF($I$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8</x:v>
+      </x:c>
+      <x:c r="Z11" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D11,IF($J$4="C2 Birds in Flight",E11,IF($J$4="C3 Landscape",F11,IF($J$4="Default Settings",G11,IF($J$4="Birds in Flight",H11,IF($J$4="Birds Perched",I11,IF($J$4="Fireworks",J11,IF($J$4="Landscape",K11,IF($J$4="Macro",L11,IF($J$4="People",M11,IF($J$4="Sports",N11,IF($J$4="Travel",O11,IF($J$4="Waterdrops",P11,IF($J$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8–f/11</x:v>
+      </x:c>
+      <x:c r="AA11" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D11,IF($K$4="C2 Birds in Flight",E11,IF($K$4="C3 Landscape",F11,IF($K$4="Default Settings",G11,IF($K$4="Birds in Flight",H11,IF($K$4="Birds Perched",I11,IF($K$4="Fireworks",J11,IF($K$4="Landscape",K11,IF($K$4="Macro",L11,IF($K$4="People",M11,IF($K$4="Sports",N11,IF($K$4="Travel",O11,IF($K$4="Waterdrops",P11,IF($K$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8–f/11; bracket before f/16</x:v>
+      </x:c>
+      <x:c r="AB11" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D11,IF($L$4="C2 Birds in Flight",E11,IF($L$4="C3 Landscape",F11,IF($L$4="Default Settings",G11,IF($L$4="Birds in Flight",H11,IF($L$4="Birds Perched",I11,IF($L$4="Fireworks",J11,IF($L$4="Landscape",K11,IF($L$4="Macro",L11,IF($L$4="People",M11,IF($L$4="Sports",N11,IF($L$4="Travel",O11,IF($L$4="Waterdrops",P11,IF($L$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8</x:v>
+      </x:c>
+      <x:c r="AC11" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D11,IF($M$4="C2 Birds in Flight",E11,IF($M$4="C3 Landscape",F11,IF($M$4="Default Settings",G11,IF($M$4="Birds in Flight",H11,IF($M$4="Birds Perched",I11,IF($M$4="Fireworks",J11,IF($M$4="Landscape",K11,IF($M$4="Macro",L11,IF($M$4="People",M11,IF($M$4="Sports",N11,IF($M$4="Travel",O11,IF($M$4="Waterdrops",P11,IF($M$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
+      </x:c>
+      <x:c r="AD11" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D11,IF($N$4="C2 Birds in Flight",E11,IF($N$4="C3 Landscape",F11,IF($N$4="Default Settings",G11,IF($N$4="Birds in Flight",H11,IF($N$4="Birds Perched",I11,IF($N$4="Fireworks",J11,IF($N$4="Landscape",K11,IF($N$4="Macro",L11,IF($N$4="People",M11,IF($N$4="Sports",N11,IF($N$4="Travel",O11,IF($N$4="Waterdrops",P11,IF($N$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AE11" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D11,IF($O$4="C2 Birds in Flight",E11,IF($O$4="C3 Landscape",F11,IF($O$4="Default Settings",G11,IF($O$4="Birds in Flight",H11,IF($O$4="Birds Perched",I11,IF($O$4="Fireworks",J11,IF($O$4="Landscape",K11,IF($O$4="Macro",L11,IF($O$4="People",M11,IF($O$4="Sports",N11,IF($O$4="Travel",O11,IF($O$4="Waterdrops",P11,IF($O$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF11" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D11,IF($P$4="C2 Birds in Flight",E11,IF($P$4="C3 Landscape",F11,IF($P$4="Default Settings",G11,IF($P$4="Birds in Flight",H11,IF($P$4="Birds Perched",I11,IF($P$4="Fireworks",J11,IF($P$4="Landscape",K11,IF($P$4="Macro",L11,IF($P$4="People",M11,IF($P$4="Sports",N11,IF($P$4="Travel",O11,IF($P$4="Waterdrops",P11,IF($P$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8–f/11</x:v>
+      </x:c>
+      <x:c r="AG11" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D11,IF($Q$4="C2 Birds in Flight",E11,IF($Q$4="C3 Landscape",F11,IF($Q$4="Default Settings",G11,IF($Q$4="Birds in Flight",H11,IF($Q$4="Birds Perched",I11,IF($Q$4="Fireworks",J11,IF($Q$4="Landscape",K11,IF($Q$4="Macro",L11,IF($Q$4="People",M11,IF($Q$4="Sports",N11,IF($Q$4="Travel",O11,IF($Q$4="Waterdrops",P11,IF($Q$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
       </x:c>
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="12" t="str">
-        <x:v>Direct control; Q is the alternative</x:v>
+        <x:v>Shooting menu &gt; ISO speed settings</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>Rear dial / Fv exposure dials</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>Exposure Comp</x:v>
+        <x:v>ISO</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>0</x:v>
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="E12" s="17" t="str">
-        <x:v>Adjust for background</x:v>
-      </x:c>
-      <x:c r="F12" s="17" t="str">
-        <x:v>0 to +1/3</x:v>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G12" s="17" t="str">
-        <x:v>0</x:v>
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="H12" s="17" t="str">
-        <x:v>0</x:v>
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="I12" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="17" t="str">
-        <x:v>0</x:v>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="J12" s="17" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K12" s="17" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L12" s="17" t="str">
-        <x:v>0</x:v>
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="M12" s="17" t="str">
-        <x:v>0</x:v>
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="N12" s="17" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O12" s="20" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="P12" s="20" t="n">
-        <x:v>120</x:v>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="O12" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="P12" s="17" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="Q12" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="R12" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S12" s="20" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="T12" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D12,IF($D$4="C2 Birds in Flight",E12,IF($D$4="C3 Landscape",F12,IF($D$4="Default Settings",G12,IF($D$4="Birds in Flight",H12,IF($D$4="Birds Perched",I12,IF($D$4="Fireworks",J12,IF($D$4="Landscape",K12,IF($D$4="Macro",L12,IF($D$4="People",M12,IF($D$4="Sports",N12,IF($D$4="Travel",O12,IF($D$4="Waterdrops",P12,IF($D$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="U12" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D12,IF($E$4="C2 Birds in Flight",E12,IF($E$4="C3 Landscape",F12,IF($E$4="Default Settings",G12,IF($E$4="Birds in Flight",H12,IF($E$4="Birds Perched",I12,IF($E$4="Fireworks",J12,IF($E$4="Landscape",K12,IF($E$4="Macro",L12,IF($E$4="People",M12,IF($E$4="Sports",N12,IF($E$4="Travel",O12,IF($E$4="Waterdrops",P12,IF($E$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="V12" s="38" t="n">
+        <x:f>IF($F$4="C1 Wildlife",D12,IF($F$4="C2 Birds in Flight",E12,IF($F$4="C3 Landscape",F12,IF($F$4="Default Settings",G12,IF($F$4="Birds in Flight",H12,IF($F$4="Birds Perched",I12,IF($F$4="Fireworks",J12,IF($F$4="Landscape",K12,IF($F$4="Macro",L12,IF($F$4="People",M12,IF($F$4="Sports",N12,IF($F$4="Travel",O12,IF($F$4="Waterdrops",P12,IF($F$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="W12" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D12,IF($G$4="C2 Birds in Flight",E12,IF($G$4="C3 Landscape",F12,IF($G$4="Default Settings",G12,IF($G$4="Birds in Flight",H12,IF($G$4="Birds Perched",I12,IF($G$4="Fireworks",J12,IF($G$4="Landscape",K12,IF($G$4="Macro",L12,IF($G$4="People",M12,IF($G$4="Sports",N12,IF($G$4="Travel",O12,IF($G$4="Waterdrops",P12,IF($G$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="X12" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D12,IF($H$4="C2 Birds in Flight",E12,IF($H$4="C3 Landscape",F12,IF($H$4="Default Settings",G12,IF($H$4="Birds in Flight",H12,IF($H$4="Birds Perched",I12,IF($H$4="Fireworks",J12,IF($H$4="Landscape",K12,IF($H$4="Macro",L12,IF($H$4="People",M12,IF($H$4="Sports",N12,IF($H$4="Travel",O12,IF($H$4="Waterdrops",P12,IF($H$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="Y12" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D12,IF($I$4="C2 Birds in Flight",E12,IF($I$4="C3 Landscape",F12,IF($I$4="Default Settings",G12,IF($I$4="Birds in Flight",H12,IF($I$4="Birds Perched",I12,IF($I$4="Fireworks",J12,IF($I$4="Landscape",K12,IF($I$4="Macro",L12,IF($I$4="People",M12,IF($I$4="Sports",N12,IF($I$4="Travel",O12,IF($I$4="Waterdrops",P12,IF($I$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="Z12" s="38" t="n">
+        <x:f>IF($J$4="C1 Wildlife",D12,IF($J$4="C2 Birds in Flight",E12,IF($J$4="C3 Landscape",F12,IF($J$4="Default Settings",G12,IF($J$4="Birds in Flight",H12,IF($J$4="Birds Perched",I12,IF($J$4="Fireworks",J12,IF($J$4="Landscape",K12,IF($J$4="Macro",L12,IF($J$4="People",M12,IF($J$4="Sports",N12,IF($J$4="Travel",O12,IF($J$4="Waterdrops",P12,IF($J$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AA12" s="38" t="n">
+        <x:f>IF($K$4="C1 Wildlife",D12,IF($K$4="C2 Birds in Flight",E12,IF($K$4="C3 Landscape",F12,IF($K$4="Default Settings",G12,IF($K$4="Birds in Flight",H12,IF($K$4="Birds Perched",I12,IF($K$4="Fireworks",J12,IF($K$4="Landscape",K12,IF($K$4="Macro",L12,IF($K$4="People",M12,IF($K$4="Sports",N12,IF($K$4="Travel",O12,IF($K$4="Waterdrops",P12,IF($K$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AB12" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D12,IF($L$4="C2 Birds in Flight",E12,IF($L$4="C3 Landscape",F12,IF($L$4="Default Settings",G12,IF($L$4="Birds in Flight",H12,IF($L$4="Birds Perched",I12,IF($L$4="Fireworks",J12,IF($L$4="Landscape",K12,IF($L$4="Macro",L12,IF($L$4="People",M12,IF($L$4="Sports",N12,IF($L$4="Travel",O12,IF($L$4="Waterdrops",P12,IF($L$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AC12" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D12,IF($M$4="C2 Birds in Flight",E12,IF($M$4="C3 Landscape",F12,IF($M$4="Default Settings",G12,IF($M$4="Birds in Flight",H12,IF($M$4="Birds Perched",I12,IF($M$4="Fireworks",J12,IF($M$4="Landscape",K12,IF($M$4="Macro",L12,IF($M$4="People",M12,IF($M$4="Sports",N12,IF($M$4="Travel",O12,IF($M$4="Waterdrops",P12,IF($M$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AD12" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D12,IF($N$4="C2 Birds in Flight",E12,IF($N$4="C3 Landscape",F12,IF($N$4="Default Settings",G12,IF($N$4="Birds in Flight",H12,IF($N$4="Birds Perched",I12,IF($N$4="Fireworks",J12,IF($N$4="Landscape",K12,IF($N$4="Macro",L12,IF($N$4="People",M12,IF($N$4="Sports",N12,IF($N$4="Travel",O12,IF($N$4="Waterdrops",P12,IF($N$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AE12" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D12,IF($O$4="C2 Birds in Flight",E12,IF($O$4="C3 Landscape",F12,IF($O$4="Default Settings",G12,IF($O$4="Birds in Flight",H12,IF($O$4="Birds Perched",I12,IF($O$4="Fireworks",J12,IF($O$4="Landscape",K12,IF($O$4="Macro",L12,IF($O$4="People",M12,IF($O$4="Sports",N12,IF($O$4="Travel",O12,IF($O$4="Waterdrops",P12,IF($O$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AF12" s="38" t="n">
+        <x:f>IF($P$4="C1 Wildlife",D12,IF($P$4="C2 Birds in Flight",E12,IF($P$4="C3 Landscape",F12,IF($P$4="Default Settings",G12,IF($P$4="Birds in Flight",H12,IF($P$4="Birds Perched",I12,IF($P$4="Fireworks",J12,IF($P$4="Landscape",K12,IF($P$4="Macro",L12,IF($P$4="People",M12,IF($P$4="Sports",N12,IF($P$4="Travel",O12,IF($P$4="Waterdrops",P12,IF($P$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AG12" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D12,IF($Q$4="C2 Birds in Flight",E12,IF($Q$4="C3 Landscape",F12,IF($Q$4="Default Settings",G12,IF($Q$4="Birds in Flight",H12,IF($Q$4="Birds Perched",I12,IF($Q$4="Fireworks",J12,IF($Q$4="Landscape",K12,IF($Q$4="Macro",L12,IF($Q$4="People",M12,IF($Q$4="Sports",N12,IF($Q$4="Travel",O12,IF($Q$4="Waterdrops",P12,IF($Q$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
       </x:c>
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="12" t="str">
-        <x:v>AF1 &gt; AF operation</x:v>
+        <x:v>Direct control; Q is the alternative</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>Rear dial / Fv exposure dials</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>AF Operation</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="str">
-        <x:v>Servo AF</x:v>
+        <x:v>Exposure Comp</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E13" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="F13" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="str">
-        <x:v>Manual Focus</x:v>
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
+        <x:v>Adjust for background</x:v>
       </x:c>
       <x:c r="I13" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="K13" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="L13" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="str">
-        <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="N13" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="O13" s="20" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="P13" s="20" t="n">
-        <x:v>130</x:v>
+        <x:v>0 to +1/3</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S13" s="20" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="T13" s="38" t="n">
+        <x:f>IF($D$4="C1 Wildlife",D13,IF($D$4="C2 Birds in Flight",E13,IF($D$4="C3 Landscape",F13,IF($D$4="Default Settings",G13,IF($D$4="Birds in Flight",H13,IF($D$4="Birds Perched",I13,IF($D$4="Fireworks",J13,IF($D$4="Landscape",K13,IF($D$4="Macro",L13,IF($D$4="People",M13,IF($D$4="Sports",N13,IF($D$4="Travel",O13,IF($D$4="Waterdrops",P13,IF($D$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D13,IF($E$4="C2 Birds in Flight",E13,IF($E$4="C3 Landscape",F13,IF($E$4="Default Settings",G13,IF($E$4="Birds in Flight",H13,IF($E$4="Birds Perched",I13,IF($E$4="Fireworks",J13,IF($E$4="Landscape",K13,IF($E$4="Macro",L13,IF($E$4="People",M13,IF($E$4="Sports",N13,IF($E$4="Travel",O13,IF($E$4="Waterdrops",P13,IF($E$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="V13" s="38" t="n">
+        <x:f>IF($F$4="C1 Wildlife",D13,IF($F$4="C2 Birds in Flight",E13,IF($F$4="C3 Landscape",F13,IF($F$4="Default Settings",G13,IF($F$4="Birds in Flight",H13,IF($F$4="Birds Perched",I13,IF($F$4="Fireworks",J13,IF($F$4="Landscape",K13,IF($F$4="Macro",L13,IF($F$4="People",M13,IF($F$4="Sports",N13,IF($F$4="Travel",O13,IF($F$4="Waterdrops",P13,IF($F$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W13" s="38" t="n">
+        <x:f>IF($G$4="C1 Wildlife",D13,IF($G$4="C2 Birds in Flight",E13,IF($G$4="C3 Landscape",F13,IF($G$4="Default Settings",G13,IF($G$4="Birds in Flight",H13,IF($G$4="Birds Perched",I13,IF($G$4="Fireworks",J13,IF($G$4="Landscape",K13,IF($G$4="Macro",L13,IF($G$4="People",M13,IF($G$4="Sports",N13,IF($G$4="Travel",O13,IF($G$4="Waterdrops",P13,IF($G$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X13" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D13,IF($H$4="C2 Birds in Flight",E13,IF($H$4="C3 Landscape",F13,IF($H$4="Default Settings",G13,IF($H$4="Birds in Flight",H13,IF($H$4="Birds Perched",I13,IF($H$4="Fireworks",J13,IF($H$4="Landscape",K13,IF($H$4="Macro",L13,IF($H$4="People",M13,IF($H$4="Sports",N13,IF($H$4="Travel",O13,IF($H$4="Waterdrops",P13,IF($H$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>Adjust for background</x:v>
+      </x:c>
+      <x:c r="Y13" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D13,IF($I$4="C2 Birds in Flight",E13,IF($I$4="C3 Landscape",F13,IF($I$4="Default Settings",G13,IF($I$4="Birds in Flight",H13,IF($I$4="Birds Perched",I13,IF($I$4="Fireworks",J13,IF($I$4="Landscape",K13,IF($I$4="Macro",L13,IF($I$4="People",M13,IF($I$4="Sports",N13,IF($I$4="Travel",O13,IF($I$4="Waterdrops",P13,IF($I$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0 to +1/3</x:v>
+      </x:c>
+      <x:c r="Z13" s="38" t="n">
+        <x:f>IF($J$4="C1 Wildlife",D13,IF($J$4="C2 Birds in Flight",E13,IF($J$4="C3 Landscape",F13,IF($J$4="Default Settings",G13,IF($J$4="Birds in Flight",H13,IF($J$4="Birds Perched",I13,IF($J$4="Fireworks",J13,IF($J$4="Landscape",K13,IF($J$4="Macro",L13,IF($J$4="People",M13,IF($J$4="Sports",N13,IF($J$4="Travel",O13,IF($J$4="Waterdrops",P13,IF($J$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA13" s="38" t="n">
+        <x:f>IF($K$4="C1 Wildlife",D13,IF($K$4="C2 Birds in Flight",E13,IF($K$4="C3 Landscape",F13,IF($K$4="Default Settings",G13,IF($K$4="Birds in Flight",H13,IF($K$4="Birds Perched",I13,IF($K$4="Fireworks",J13,IF($K$4="Landscape",K13,IF($K$4="Macro",L13,IF($K$4="People",M13,IF($K$4="Sports",N13,IF($K$4="Travel",O13,IF($K$4="Waterdrops",P13,IF($K$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB13" s="38" t="n">
+        <x:f>IF($L$4="C1 Wildlife",D13,IF($L$4="C2 Birds in Flight",E13,IF($L$4="C3 Landscape",F13,IF($L$4="Default Settings",G13,IF($L$4="Birds in Flight",H13,IF($L$4="Birds Perched",I13,IF($L$4="Fireworks",J13,IF($L$4="Landscape",K13,IF($L$4="Macro",L13,IF($L$4="People",M13,IF($L$4="Sports",N13,IF($L$4="Travel",O13,IF($L$4="Waterdrops",P13,IF($L$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC13" s="38" t="n">
+        <x:f>IF($M$4="C1 Wildlife",D13,IF($M$4="C2 Birds in Flight",E13,IF($M$4="C3 Landscape",F13,IF($M$4="Default Settings",G13,IF($M$4="Birds in Flight",H13,IF($M$4="Birds Perched",I13,IF($M$4="Fireworks",J13,IF($M$4="Landscape",K13,IF($M$4="Macro",L13,IF($M$4="People",M13,IF($M$4="Sports",N13,IF($M$4="Travel",O13,IF($M$4="Waterdrops",P13,IF($M$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD13" s="38" t="n">
+        <x:f>IF($N$4="C1 Wildlife",D13,IF($N$4="C2 Birds in Flight",E13,IF($N$4="C3 Landscape",F13,IF($N$4="Default Settings",G13,IF($N$4="Birds in Flight",H13,IF($N$4="Birds Perched",I13,IF($N$4="Fireworks",J13,IF($N$4="Landscape",K13,IF($N$4="Macro",L13,IF($N$4="People",M13,IF($N$4="Sports",N13,IF($N$4="Travel",O13,IF($N$4="Waterdrops",P13,IF($N$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE13" s="38" t="n">
+        <x:f>IF($O$4="C1 Wildlife",D13,IF($O$4="C2 Birds in Flight",E13,IF($O$4="C3 Landscape",F13,IF($O$4="Default Settings",G13,IF($O$4="Birds in Flight",H13,IF($O$4="Birds Perched",I13,IF($O$4="Fireworks",J13,IF($O$4="Landscape",K13,IF($O$4="Macro",L13,IF($O$4="People",M13,IF($O$4="Sports",N13,IF($O$4="Travel",O13,IF($O$4="Waterdrops",P13,IF($O$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF13" s="38" t="n">
+        <x:f>IF($P$4="C1 Wildlife",D13,IF($P$4="C2 Birds in Flight",E13,IF($P$4="C3 Landscape",F13,IF($P$4="Default Settings",G13,IF($P$4="Birds in Flight",H13,IF($P$4="Birds Perched",I13,IF($P$4="Fireworks",J13,IF($P$4="Landscape",K13,IF($P$4="Macro",L13,IF($P$4="People",M13,IF($P$4="Sports",N13,IF($P$4="Travel",O13,IF($P$4="Waterdrops",P13,IF($P$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG13" s="38" t="n">
+        <x:f>IF($Q$4="C1 Wildlife",D13,IF($Q$4="C2 Birds in Flight",E13,IF($Q$4="C3 Landscape",F13,IF($Q$4="Default Settings",G13,IF($Q$4="Birds in Flight",H13,IF($Q$4="Birds Perched",I13,IF($Q$4="Fireworks",J13,IF($Q$4="Landscape",K13,IF($Q$4="Macro",L13,IF($Q$4="People",M13,IF($Q$4="Sports",N13,IF($Q$4="Travel",O13,IF($Q$4="Waterdrops",P13,IF($Q$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="12" t="str">
-        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
+        <x:v>AF1 &gt; AF operation</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>AF Point Selection button + Main Dial</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>AF Operation</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="E14" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="F14" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="G14" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="I14" s="17" t="str">
-        <x:v>Spot AF</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="J14" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Manual Focus</x:v>
       </x:c>
       <x:c r="K14" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="L14" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="M14" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="N14" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="O14" s="20" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="P14" s="20" t="n">
-        <x:v>140</x:v>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="P14" s="17" t="str">
+        <x:v>Manual Focus</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="R14" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S14" s="20" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="T14" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D14,IF($D$4="C2 Birds in Flight",E14,IF($D$4="C3 Landscape",F14,IF($D$4="Default Settings",G14,IF($D$4="Birds in Flight",H14,IF($D$4="Birds Perched",I14,IF($D$4="Fireworks",J14,IF($D$4="Landscape",K14,IF($D$4="Macro",L14,IF($D$4="People",M14,IF($D$4="Sports",N14,IF($D$4="Travel",O14,IF($D$4="Waterdrops",P14,IF($D$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="U14" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D14,IF($E$4="C2 Birds in Flight",E14,IF($E$4="C3 Landscape",F14,IF($E$4="Default Settings",G14,IF($E$4="Birds in Flight",H14,IF($E$4="Birds Perched",I14,IF($E$4="Fireworks",J14,IF($E$4="Landscape",K14,IF($E$4="Macro",L14,IF($E$4="People",M14,IF($E$4="Sports",N14,IF($E$4="Travel",O14,IF($E$4="Waterdrops",P14,IF($E$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="V14" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D14,IF($F$4="C2 Birds in Flight",E14,IF($F$4="C3 Landscape",F14,IF($F$4="Default Settings",G14,IF($F$4="Birds in Flight",H14,IF($F$4="Birds Perched",I14,IF($F$4="Fireworks",J14,IF($F$4="Landscape",K14,IF($F$4="Macro",L14,IF($F$4="People",M14,IF($F$4="Sports",N14,IF($F$4="Travel",O14,IF($F$4="Waterdrops",P14,IF($F$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="W14" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D14,IF($G$4="C2 Birds in Flight",E14,IF($G$4="C3 Landscape",F14,IF($G$4="Default Settings",G14,IF($G$4="Birds in Flight",H14,IF($G$4="Birds Perched",I14,IF($G$4="Fireworks",J14,IF($G$4="Landscape",K14,IF($G$4="Macro",L14,IF($G$4="People",M14,IF($G$4="Sports",N14,IF($G$4="Travel",O14,IF($G$4="Waterdrops",P14,IF($G$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="X14" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D14,IF($H$4="C2 Birds in Flight",E14,IF($H$4="C3 Landscape",F14,IF($H$4="Default Settings",G14,IF($H$4="Birds in Flight",H14,IF($H$4="Birds Perched",I14,IF($H$4="Fireworks",J14,IF($H$4="Landscape",K14,IF($H$4="Macro",L14,IF($H$4="People",M14,IF($H$4="Sports",N14,IF($H$4="Travel",O14,IF($H$4="Waterdrops",P14,IF($H$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Y14" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D14,IF($I$4="C2 Birds in Flight",E14,IF($I$4="C3 Landscape",F14,IF($I$4="Default Settings",G14,IF($I$4="Birds in Flight",H14,IF($I$4="Birds Perched",I14,IF($I$4="Fireworks",J14,IF($I$4="Landscape",K14,IF($I$4="Macro",L14,IF($I$4="People",M14,IF($I$4="Sports",N14,IF($I$4="Travel",O14,IF($I$4="Waterdrops",P14,IF($I$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Z14" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D14,IF($J$4="C2 Birds in Flight",E14,IF($J$4="C3 Landscape",F14,IF($J$4="Default Settings",G14,IF($J$4="Birds in Flight",H14,IF($J$4="Birds Perched",I14,IF($J$4="Fireworks",J14,IF($J$4="Landscape",K14,IF($J$4="Macro",L14,IF($J$4="People",M14,IF($J$4="Sports",N14,IF($J$4="Travel",O14,IF($J$4="Waterdrops",P14,IF($J$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Manual Focus</x:v>
+      </x:c>
+      <x:c r="AA14" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D14,IF($K$4="C2 Birds in Flight",E14,IF($K$4="C3 Landscape",F14,IF($K$4="Default Settings",G14,IF($K$4="Birds in Flight",H14,IF($K$4="Birds Perched",I14,IF($K$4="Fireworks",J14,IF($K$4="Landscape",K14,IF($K$4="Macro",L14,IF($K$4="People",M14,IF($K$4="Sports",N14,IF($K$4="Travel",O14,IF($K$4="Waterdrops",P14,IF($K$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="AB14" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D14,IF($L$4="C2 Birds in Flight",E14,IF($L$4="C3 Landscape",F14,IF($L$4="Default Settings",G14,IF($L$4="Birds in Flight",H14,IF($L$4="Birds Perched",I14,IF($L$4="Fireworks",J14,IF($L$4="Landscape",K14,IF($L$4="Macro",L14,IF($L$4="People",M14,IF($L$4="Sports",N14,IF($L$4="Travel",O14,IF($L$4="Waterdrops",P14,IF($L$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="AC14" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D14,IF($M$4="C2 Birds in Flight",E14,IF($M$4="C3 Landscape",F14,IF($M$4="Default Settings",G14,IF($M$4="Birds in Flight",H14,IF($M$4="Birds Perched",I14,IF($M$4="Fireworks",J14,IF($M$4="Landscape",K14,IF($M$4="Macro",L14,IF($M$4="People",M14,IF($M$4="Sports",N14,IF($M$4="Travel",O14,IF($M$4="Waterdrops",P14,IF($M$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="AD14" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D14,IF($N$4="C2 Birds in Flight",E14,IF($N$4="C3 Landscape",F14,IF($N$4="Default Settings",G14,IF($N$4="Birds in Flight",H14,IF($N$4="Birds Perched",I14,IF($N$4="Fireworks",J14,IF($N$4="Landscape",K14,IF($N$4="Macro",L14,IF($N$4="People",M14,IF($N$4="Sports",N14,IF($N$4="Travel",O14,IF($N$4="Waterdrops",P14,IF($N$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="AE14" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D14,IF($O$4="C2 Birds in Flight",E14,IF($O$4="C3 Landscape",F14,IF($O$4="Default Settings",G14,IF($O$4="Birds in Flight",H14,IF($O$4="Birds Perched",I14,IF($O$4="Fireworks",J14,IF($O$4="Landscape",K14,IF($O$4="Macro",L14,IF($O$4="People",M14,IF($O$4="Sports",N14,IF($O$4="Travel",O14,IF($O$4="Waterdrops",P14,IF($O$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="AF14" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D14,IF($P$4="C2 Birds in Flight",E14,IF($P$4="C3 Landscape",F14,IF($P$4="Default Settings",G14,IF($P$4="Birds in Flight",H14,IF($P$4="Birds Perched",I14,IF($P$4="Fireworks",J14,IF($P$4="Landscape",K14,IF($P$4="Macro",L14,IF($P$4="People",M14,IF($P$4="Sports",N14,IF($P$4="Travel",O14,IF($P$4="Waterdrops",P14,IF($P$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Manual Focus</x:v>
+      </x:c>
+      <x:c r="AG14" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D14,IF($Q$4="C2 Birds in Flight",E14,IF($Q$4="C3 Landscape",F14,IF($Q$4="Default Settings",G14,IF($Q$4="Birds in Flight",H14,IF($Q$4="Birds Perched",I14,IF($Q$4="Fireworks",J14,IF($Q$4="Landscape",K14,IF($Q$4="Macro",L14,IF($Q$4="People",M14,IF($Q$4="Sports",N14,IF($Q$4="Travel",O14,IF($Q$4="Waterdrops",P14,IF($Q$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
       </x:c>
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="12" t="str">
-        <x:v>AF1 &gt; Subject to detect</x:v>
+        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>MM-SWITCH</x:v>
+        <x:v>AF Point Selection button + Main Dial</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="E15" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="F15" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="G15" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="H15" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="H15" s="17" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="I15" s="17" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="str">
-        <x:v>People</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="L15" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="M15" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="P15" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="N15" s="17" t="str">
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="O15" s="20" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P15" s="20" t="n">
-        <x:v>220</x:v>
+      <x:c r="Q15" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="R15" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="S15" s="20" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="T15" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Birds in Flight",H15,IF($D$4="Birds Perched",I15,IF($D$4="Fireworks",J15,IF($D$4="Landscape",K15,IF($D$4="Macro",L15,IF($D$4="People",M15,IF($D$4="Sports",N15,IF($D$4="Travel",O15,IF($D$4="Waterdrops",P15,IF($D$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="U15" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Birds in Flight",H15,IF($E$4="Birds Perched",I15,IF($E$4="Fireworks",J15,IF($E$4="Landscape",K15,IF($E$4="Macro",L15,IF($E$4="People",M15,IF($E$4="Sports",N15,IF($E$4="Travel",O15,IF($E$4="Waterdrops",P15,IF($E$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="V15" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Birds in Flight",H15,IF($F$4="Birds Perched",I15,IF($F$4="Fireworks",J15,IF($F$4="Landscape",K15,IF($F$4="Macro",L15,IF($F$4="People",M15,IF($F$4="Sports",N15,IF($F$4="Travel",O15,IF($F$4="Waterdrops",P15,IF($F$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="W15" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Birds in Flight",H15,IF($G$4="Birds Perched",I15,IF($G$4="Fireworks",J15,IF($G$4="Landscape",K15,IF($G$4="Macro",L15,IF($G$4="People",M15,IF($G$4="Sports",N15,IF($G$4="Travel",O15,IF($G$4="Waterdrops",P15,IF($G$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="X15" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Birds in Flight",H15,IF($H$4="Birds Perched",I15,IF($H$4="Fireworks",J15,IF($H$4="Landscape",K15,IF($H$4="Macro",L15,IF($H$4="People",M15,IF($H$4="Sports",N15,IF($H$4="Travel",O15,IF($H$4="Waterdrops",P15,IF($H$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="Y15" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Birds in Flight",H15,IF($I$4="Birds Perched",I15,IF($I$4="Fireworks",J15,IF($I$4="Landscape",K15,IF($I$4="Macro",L15,IF($I$4="People",M15,IF($I$4="Sports",N15,IF($I$4="Travel",O15,IF($I$4="Waterdrops",P15,IF($I$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="Z15" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Birds in Flight",H15,IF($J$4="Birds Perched",I15,IF($J$4="Fireworks",J15,IF($J$4="Landscape",K15,IF($J$4="Macro",L15,IF($J$4="People",M15,IF($J$4="Sports",N15,IF($J$4="Travel",O15,IF($J$4="Waterdrops",P15,IF($J$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA15" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Birds in Flight",H15,IF($K$4="Birds Perched",I15,IF($K$4="Fireworks",J15,IF($K$4="Landscape",K15,IF($K$4="Macro",L15,IF($K$4="People",M15,IF($K$4="Sports",N15,IF($K$4="Travel",O15,IF($K$4="Waterdrops",P15,IF($K$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="AB15" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Birds in Flight",H15,IF($L$4="Birds Perched",I15,IF($L$4="Fireworks",J15,IF($L$4="Landscape",K15,IF($L$4="Macro",L15,IF($L$4="People",M15,IF($L$4="Sports",N15,IF($L$4="Travel",O15,IF($L$4="Waterdrops",P15,IF($L$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Spot AF</x:v>
+      </x:c>
+      <x:c r="AC15" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Birds in Flight",H15,IF($M$4="Birds Perched",I15,IF($M$4="Fireworks",J15,IF($M$4="Landscape",K15,IF($M$4="Macro",L15,IF($M$4="People",M15,IF($M$4="Sports",N15,IF($M$4="Travel",O15,IF($M$4="Waterdrops",P15,IF($M$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="AD15" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Birds in Flight",H15,IF($N$4="Birds Perched",I15,IF($N$4="Fireworks",J15,IF($N$4="Landscape",K15,IF($N$4="Macro",L15,IF($N$4="People",M15,IF($N$4="Sports",N15,IF($N$4="Travel",O15,IF($N$4="Waterdrops",P15,IF($N$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="AE15" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Birds in Flight",H15,IF($O$4="Birds Perched",I15,IF($O$4="Fireworks",J15,IF($O$4="Landscape",K15,IF($O$4="Macro",L15,IF($O$4="People",M15,IF($O$4="Sports",N15,IF($O$4="Travel",O15,IF($O$4="Waterdrops",P15,IF($O$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="AF15" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Birds in Flight",H15,IF($P$4="Birds Perched",I15,IF($P$4="Fireworks",J15,IF($P$4="Landscape",K15,IF($P$4="Macro",L15,IF($P$4="People",M15,IF($P$4="Sports",N15,IF($P$4="Travel",O15,IF($P$4="Waterdrops",P15,IF($P$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AG15" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Birds in Flight",H15,IF($Q$4="Birds Perched",I15,IF($Q$4="Fireworks",J15,IF($Q$4="Landscape",K15,IF($Q$4="Macro",L15,IF($Q$4="People",M15,IF($Q$4="Sports",N15,IF($Q$4="Travel",O15,IF($Q$4="Waterdrops",P15,IF($Q$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="12" t="str">
-        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
+        <x:v>AF1 &gt; Subject to detect</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>SET button</x:v>
+        <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="E16" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="F16" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="H16" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="I16" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="J16" s="17" t="str">
-        <x:v>Enable</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="L16" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="M16" s="17" t="str">
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="str">
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="N16" s="17" t="str">
-        <x:v>Enable</x:v>
-      </x:c>
-      <x:c r="O16" s="20" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="P16" s="20" t="n">
-        <x:v>150</x:v>
+      <x:c r="Q16" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="R16" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S16" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="T16" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Birds in Flight",H16,IF($D$4="Birds Perched",I16,IF($D$4="Fireworks",J16,IF($D$4="Landscape",K16,IF($D$4="Macro",L16,IF($D$4="People",M16,IF($D$4="Sports",N16,IF($D$4="Travel",O16,IF($D$4="Waterdrops",P16,IF($D$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="U16" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Birds in Flight",H16,IF($E$4="Birds Perched",I16,IF($E$4="Fireworks",J16,IF($E$4="Landscape",K16,IF($E$4="Macro",L16,IF($E$4="People",M16,IF($E$4="Sports",N16,IF($E$4="Travel",O16,IF($E$4="Waterdrops",P16,IF($E$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="V16" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Birds in Flight",H16,IF($F$4="Birds Perched",I16,IF($F$4="Fireworks",J16,IF($F$4="Landscape",K16,IF($F$4="Macro",L16,IF($F$4="People",M16,IF($F$4="Sports",N16,IF($F$4="Travel",O16,IF($F$4="Waterdrops",P16,IF($F$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W16" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Birds in Flight",H16,IF($G$4="Birds Perched",I16,IF($G$4="Fireworks",J16,IF($G$4="Landscape",K16,IF($G$4="Macro",L16,IF($G$4="People",M16,IF($G$4="Sports",N16,IF($G$4="Travel",O16,IF($G$4="Waterdrops",P16,IF($G$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="X16" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Birds in Flight",H16,IF($H$4="Birds Perched",I16,IF($H$4="Fireworks",J16,IF($H$4="Landscape",K16,IF($H$4="Macro",L16,IF($H$4="People",M16,IF($H$4="Sports",N16,IF($H$4="Travel",O16,IF($H$4="Waterdrops",P16,IF($H$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="Y16" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Birds in Flight",H16,IF($I$4="Birds Perched",I16,IF($I$4="Fireworks",J16,IF($I$4="Landscape",K16,IF($I$4="Macro",L16,IF($I$4="People",M16,IF($I$4="Sports",N16,IF($I$4="Travel",O16,IF($I$4="Waterdrops",P16,IF($I$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="Z16" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Birds in Flight",H16,IF($J$4="Birds Perched",I16,IF($J$4="Fireworks",J16,IF($J$4="Landscape",K16,IF($J$4="Macro",L16,IF($J$4="People",M16,IF($J$4="Sports",N16,IF($J$4="Travel",O16,IF($J$4="Waterdrops",P16,IF($J$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA16" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Birds in Flight",H16,IF($K$4="Birds Perched",I16,IF($K$4="Fireworks",J16,IF($K$4="Landscape",K16,IF($K$4="Macro",L16,IF($K$4="People",M16,IF($K$4="Sports",N16,IF($K$4="Travel",O16,IF($K$4="Waterdrops",P16,IF($K$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AB16" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Birds in Flight",H16,IF($L$4="Birds Perched",I16,IF($L$4="Fireworks",J16,IF($L$4="Landscape",K16,IF($L$4="Macro",L16,IF($L$4="People",M16,IF($L$4="Sports",N16,IF($L$4="Travel",O16,IF($L$4="Waterdrops",P16,IF($L$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AC16" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Birds in Flight",H16,IF($M$4="Birds Perched",I16,IF($M$4="Fireworks",J16,IF($M$4="Landscape",K16,IF($M$4="Macro",L16,IF($M$4="People",M16,IF($M$4="Sports",N16,IF($M$4="Travel",O16,IF($M$4="Waterdrops",P16,IF($M$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="AD16" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Birds in Flight",H16,IF($N$4="Birds Perched",I16,IF($N$4="Fireworks",J16,IF($N$4="Landscape",K16,IF($N$4="Macro",L16,IF($N$4="People",M16,IF($N$4="Sports",N16,IF($N$4="Travel",O16,IF($N$4="Waterdrops",P16,IF($N$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="AE16" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Birds in Flight",H16,IF($O$4="Birds Perched",I16,IF($O$4="Fireworks",J16,IF($O$4="Landscape",K16,IF($O$4="Macro",L16,IF($O$4="People",M16,IF($O$4="Sports",N16,IF($O$4="Travel",O16,IF($O$4="Waterdrops",P16,IF($O$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AF16" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Birds in Flight",H16,IF($P$4="Birds Perched",I16,IF($P$4="Fireworks",J16,IF($P$4="Landscape",K16,IF($P$4="Macro",L16,IF($P$4="People",M16,IF($P$4="Sports",N16,IF($P$4="Travel",O16,IF($P$4="Waterdrops",P16,IF($P$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AG16" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Birds in Flight",H16,IF($Q$4="Birds Perched",I16,IF($Q$4="Fireworks",J16,IF($Q$4="Landscape",K16,IF($Q$4="Macro",L16,IF($Q$4="People",M16,IF($Q$4="Sports",N16,IF($Q$4="Travel",O16,IF($Q$4="Waterdrops",P16,IF($Q$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="12" t="str">
-        <x:v>Shooting menu &gt; Drive mode</x:v>
+        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>SET button</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="F17" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="L17" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="M17" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
-      </x:c>
-      <x:c r="O17" s="20" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="P17" s="20" t="n">
-        <x:v>160</x:v>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="O17" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P17" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q17" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="R17" s="20" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="S17" s="20" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="T17" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Birds in Flight",H17,IF($D$4="Birds Perched",I17,IF($D$4="Fireworks",J17,IF($D$4="Landscape",K17,IF($D$4="Macro",L17,IF($D$4="People",M17,IF($D$4="Sports",N17,IF($D$4="Travel",O17,IF($D$4="Waterdrops",P17,IF($D$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="U17" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Birds in Flight",H17,IF($E$4="Birds Perched",I17,IF($E$4="Fireworks",J17,IF($E$4="Landscape",K17,IF($E$4="Macro",L17,IF($E$4="People",M17,IF($E$4="Sports",N17,IF($E$4="Travel",O17,IF($E$4="Waterdrops",P17,IF($E$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="V17" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Birds in Flight",H17,IF($F$4="Birds Perched",I17,IF($F$4="Fireworks",J17,IF($F$4="Landscape",K17,IF($F$4="Macro",L17,IF($F$4="People",M17,IF($F$4="Sports",N17,IF($F$4="Travel",O17,IF($F$4="Waterdrops",P17,IF($F$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W17" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Birds in Flight",H17,IF($G$4="Birds Perched",I17,IF($G$4="Fireworks",J17,IF($G$4="Landscape",K17,IF($G$4="Macro",L17,IF($G$4="People",M17,IF($G$4="Sports",N17,IF($G$4="Travel",O17,IF($G$4="Waterdrops",P17,IF($G$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="X17" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Birds in Flight",H17,IF($H$4="Birds Perched",I17,IF($H$4="Fireworks",J17,IF($H$4="Landscape",K17,IF($H$4="Macro",L17,IF($H$4="People",M17,IF($H$4="Sports",N17,IF($H$4="Travel",O17,IF($H$4="Waterdrops",P17,IF($H$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="Y17" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Birds in Flight",H17,IF($I$4="Birds Perched",I17,IF($I$4="Fireworks",J17,IF($I$4="Landscape",K17,IF($I$4="Macro",L17,IF($I$4="People",M17,IF($I$4="Sports",N17,IF($I$4="Travel",O17,IF($I$4="Waterdrops",P17,IF($I$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="Z17" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Birds in Flight",H17,IF($J$4="Birds Perched",I17,IF($J$4="Fireworks",J17,IF($J$4="Landscape",K17,IF($J$4="Macro",L17,IF($J$4="People",M17,IF($J$4="Sports",N17,IF($J$4="Travel",O17,IF($J$4="Waterdrops",P17,IF($J$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA17" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Birds in Flight",H17,IF($K$4="Birds Perched",I17,IF($K$4="Fireworks",J17,IF($K$4="Landscape",K17,IF($K$4="Macro",L17,IF($K$4="People",M17,IF($K$4="Sports",N17,IF($K$4="Travel",O17,IF($K$4="Waterdrops",P17,IF($K$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB17" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Birds in Flight",H17,IF($L$4="Birds Perched",I17,IF($L$4="Fireworks",J17,IF($L$4="Landscape",K17,IF($L$4="Macro",L17,IF($L$4="People",M17,IF($L$4="Sports",N17,IF($L$4="Travel",O17,IF($L$4="Waterdrops",P17,IF($L$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AC17" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Birds in Flight",H17,IF($M$4="Birds Perched",I17,IF($M$4="Fireworks",J17,IF($M$4="Landscape",K17,IF($M$4="Macro",L17,IF($M$4="People",M17,IF($M$4="Sports",N17,IF($M$4="Travel",O17,IF($M$4="Waterdrops",P17,IF($M$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="AD17" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Birds in Flight",H17,IF($N$4="Birds Perched",I17,IF($N$4="Fireworks",J17,IF($N$4="Landscape",K17,IF($N$4="Macro",L17,IF($N$4="People",M17,IF($N$4="Sports",N17,IF($N$4="Travel",O17,IF($N$4="Waterdrops",P17,IF($N$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="AE17" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Birds in Flight",H17,IF($O$4="Birds Perched",I17,IF($O$4="Fireworks",J17,IF($O$4="Landscape",K17,IF($O$4="Macro",L17,IF($O$4="People",M17,IF($O$4="Sports",N17,IF($O$4="Travel",O17,IF($O$4="Waterdrops",P17,IF($O$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AF17" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Birds in Flight",H17,IF($P$4="Birds Perched",I17,IF($P$4="Fireworks",J17,IF($P$4="Landscape",K17,IF($P$4="Macro",L17,IF($P$4="People",M17,IF($P$4="Sports",N17,IF($P$4="Travel",O17,IF($P$4="Waterdrops",P17,IF($P$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AG17" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Birds in Flight",H17,IF($Q$4="Birds Perched",I17,IF($Q$4="Fireworks",J17,IF($Q$4="Landscape",K17,IF($Q$4="Macro",L17,IF($Q$4="People",M17,IF($Q$4="Sports",N17,IF($Q$4="Travel",O17,IF($Q$4="Waterdrops",P17,IF($Q$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
+        <x:v>Shooting menu &gt; Drive mode</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Drive</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="E18" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="F18" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="G18" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="H18" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="I18" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="L18" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="M18" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Low Speed Continuous</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str">
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="O18" s="20" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="P18" s="20" t="n">
-        <x:v>230</x:v>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="O18" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="P18" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="Q18" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="R18" s="20" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="S18" s="20" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="T18" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Birds in Flight",H18,IF($D$4="Birds Perched",I18,IF($D$4="Fireworks",J18,IF($D$4="Landscape",K18,IF($D$4="Macro",L18,IF($D$4="People",M18,IF($D$4="Sports",N18,IF($D$4="Travel",O18,IF($D$4="Waterdrops",P18,IF($D$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="U18" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Birds in Flight",H18,IF($E$4="Birds Perched",I18,IF($E$4="Fireworks",J18,IF($E$4="Landscape",K18,IF($E$4="Macro",L18,IF($E$4="People",M18,IF($E$4="Sports",N18,IF($E$4="Travel",O18,IF($E$4="Waterdrops",P18,IF($E$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="V18" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Birds in Flight",H18,IF($F$4="Birds Perched",I18,IF($F$4="Fireworks",J18,IF($F$4="Landscape",K18,IF($F$4="Macro",L18,IF($F$4="People",M18,IF($F$4="Sports",N18,IF($F$4="Travel",O18,IF($F$4="Waterdrops",P18,IF($F$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="W18" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Birds in Flight",H18,IF($G$4="Birds Perched",I18,IF($G$4="Fireworks",J18,IF($G$4="Landscape",K18,IF($G$4="Macro",L18,IF($G$4="People",M18,IF($G$4="Sports",N18,IF($G$4="Travel",O18,IF($G$4="Waterdrops",P18,IF($G$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="X18" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Birds in Flight",H18,IF($H$4="Birds Perched",I18,IF($H$4="Fireworks",J18,IF($H$4="Landscape",K18,IF($H$4="Macro",L18,IF($H$4="People",M18,IF($H$4="Sports",N18,IF($H$4="Travel",O18,IF($H$4="Waterdrops",P18,IF($H$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="Y18" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Birds in Flight",H18,IF($I$4="Birds Perched",I18,IF($I$4="Fireworks",J18,IF($I$4="Landscape",K18,IF($I$4="Macro",L18,IF($I$4="People",M18,IF($I$4="Sports",N18,IF($I$4="Travel",O18,IF($I$4="Waterdrops",P18,IF($I$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="Z18" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Birds in Flight",H18,IF($J$4="Birds Perched",I18,IF($J$4="Fireworks",J18,IF($J$4="Landscape",K18,IF($J$4="Macro",L18,IF($J$4="People",M18,IF($J$4="Sports",N18,IF($J$4="Travel",O18,IF($J$4="Waterdrops",P18,IF($J$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AA18" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Birds in Flight",H18,IF($K$4="Birds Perched",I18,IF($K$4="Fireworks",J18,IF($K$4="Landscape",K18,IF($K$4="Macro",L18,IF($K$4="People",M18,IF($K$4="Sports",N18,IF($K$4="Travel",O18,IF($K$4="Waterdrops",P18,IF($K$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AB18" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Birds in Flight",H18,IF($L$4="Birds Perched",I18,IF($L$4="Fireworks",J18,IF($L$4="Landscape",K18,IF($L$4="Macro",L18,IF($L$4="People",M18,IF($L$4="Sports",N18,IF($L$4="Travel",O18,IF($L$4="Waterdrops",P18,IF($L$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AC18" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Birds in Flight",H18,IF($M$4="Birds Perched",I18,IF($M$4="Fireworks",J18,IF($M$4="Landscape",K18,IF($M$4="Macro",L18,IF($M$4="People",M18,IF($M$4="Sports",N18,IF($M$4="Travel",O18,IF($M$4="Waterdrops",P18,IF($M$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Low Speed Continuous</x:v>
+      </x:c>
+      <x:c r="AD18" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Birds in Flight",H18,IF($N$4="Birds Perched",I18,IF($N$4="Fireworks",J18,IF($N$4="Landscape",K18,IF($N$4="Macro",L18,IF($N$4="People",M18,IF($N$4="Sports",N18,IF($N$4="Travel",O18,IF($N$4="Waterdrops",P18,IF($N$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="AE18" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Birds in Flight",H18,IF($O$4="Birds Perched",I18,IF($O$4="Fireworks",J18,IF($O$4="Landscape",K18,IF($O$4="Macro",L18,IF($O$4="People",M18,IF($O$4="Sports",N18,IF($O$4="Travel",O18,IF($O$4="Waterdrops",P18,IF($O$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AF18" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Birds in Flight",H18,IF($P$4="Birds Perched",I18,IF($P$4="Fireworks",J18,IF($P$4="Landscape",K18,IF($P$4="Macro",L18,IF($P$4="People",M18,IF($P$4="Sports",N18,IF($P$4="Travel",O18,IF($P$4="Waterdrops",P18,IF($P$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AG18" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Birds in Flight",H18,IF($Q$4="Birds Perched",I18,IF($Q$4="Fireworks",J18,IF($Q$4="Landscape",K18,IF($Q$4="Macro",L18,IF($Q$4="People",M18,IF($Q$4="Sports",N18,IF($Q$4="Travel",O18,IF($Q$4="Waterdrops",P18,IF($Q$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>Lens IS switch; camera IS menu when available</x:v>
+        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Image Stabilization</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="E19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="F19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="G19" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="L19" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="M19" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="O19" s="20" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P19" s="20" t="n">
-        <x:v>40</x:v>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="O19" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="P19" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q19" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="R19" s="20" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S19" s="20" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="T19" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Birds in Flight",H19,IF($D$4="Birds Perched",I19,IF($D$4="Fireworks",J19,IF($D$4="Landscape",K19,IF($D$4="Macro",L19,IF($D$4="People",M19,IF($D$4="Sports",N19,IF($D$4="Travel",O19,IF($D$4="Waterdrops",P19,IF($D$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U19" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Birds in Flight",H19,IF($E$4="Birds Perched",I19,IF($E$4="Fireworks",J19,IF($E$4="Landscape",K19,IF($E$4="Macro",L19,IF($E$4="People",M19,IF($E$4="Sports",N19,IF($E$4="Travel",O19,IF($E$4="Waterdrops",P19,IF($E$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="V19" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Birds in Flight",H19,IF($F$4="Birds Perched",I19,IF($F$4="Fireworks",J19,IF($F$4="Landscape",K19,IF($F$4="Macro",L19,IF($F$4="People",M19,IF($F$4="Sports",N19,IF($F$4="Travel",O19,IF($F$4="Waterdrops",P19,IF($F$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="W19" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Birds in Flight",H19,IF($G$4="Birds Perched",I19,IF($G$4="Fireworks",J19,IF($G$4="Landscape",K19,IF($G$4="Macro",L19,IF($G$4="People",M19,IF($G$4="Sports",N19,IF($G$4="Travel",O19,IF($G$4="Waterdrops",P19,IF($G$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="X19" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Birds in Flight",H19,IF($H$4="Birds Perched",I19,IF($H$4="Fireworks",J19,IF($H$4="Landscape",K19,IF($H$4="Macro",L19,IF($H$4="People",M19,IF($H$4="Sports",N19,IF($H$4="Travel",O19,IF($H$4="Waterdrops",P19,IF($H$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="Y19" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Birds in Flight",H19,IF($I$4="Birds Perched",I19,IF($I$4="Fireworks",J19,IF($I$4="Landscape",K19,IF($I$4="Macro",L19,IF($I$4="People",M19,IF($I$4="Sports",N19,IF($I$4="Travel",O19,IF($I$4="Waterdrops",P19,IF($I$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Z19" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Birds in Flight",H19,IF($J$4="Birds Perched",I19,IF($J$4="Fireworks",J19,IF($J$4="Landscape",K19,IF($J$4="Macro",L19,IF($J$4="People",M19,IF($J$4="Sports",N19,IF($J$4="Travel",O19,IF($J$4="Waterdrops",P19,IF($J$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA19" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Birds in Flight",H19,IF($K$4="Birds Perched",I19,IF($K$4="Fireworks",J19,IF($K$4="Landscape",K19,IF($K$4="Macro",L19,IF($K$4="People",M19,IF($K$4="Sports",N19,IF($K$4="Travel",O19,IF($K$4="Waterdrops",P19,IF($K$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AB19" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Birds in Flight",H19,IF($L$4="Birds Perched",I19,IF($L$4="Fireworks",J19,IF($L$4="Landscape",K19,IF($L$4="Macro",L19,IF($L$4="People",M19,IF($L$4="Sports",N19,IF($L$4="Travel",O19,IF($L$4="Waterdrops",P19,IF($L$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AC19" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Birds in Flight",H19,IF($M$4="Birds Perched",I19,IF($M$4="Fireworks",J19,IF($M$4="Landscape",K19,IF($M$4="Macro",L19,IF($M$4="People",M19,IF($M$4="Sports",N19,IF($M$4="Travel",O19,IF($M$4="Waterdrops",P19,IF($M$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AD19" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Birds in Flight",H19,IF($N$4="Birds Perched",I19,IF($N$4="Fireworks",J19,IF($N$4="Landscape",K19,IF($N$4="Macro",L19,IF($N$4="People",M19,IF($N$4="Sports",N19,IF($N$4="Travel",O19,IF($N$4="Waterdrops",P19,IF($N$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="AE19" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Birds in Flight",H19,IF($O$4="Birds Perched",I19,IF($O$4="Fireworks",J19,IF($O$4="Landscape",K19,IF($O$4="Macro",L19,IF($O$4="People",M19,IF($O$4="Sports",N19,IF($O$4="Travel",O19,IF($O$4="Waterdrops",P19,IF($O$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AF19" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Birds in Flight",H19,IF($P$4="Birds Perched",I19,IF($P$4="Fireworks",J19,IF($P$4="Landscape",K19,IF($P$4="Macro",L19,IF($P$4="People",M19,IF($P$4="Sports",N19,IF($P$4="Travel",O19,IF($P$4="Waterdrops",P19,IF($P$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG19" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Birds in Flight",H19,IF($Q$4="Birds Perched",I19,IF($Q$4="Fireworks",J19,IF($Q$4="Landscape",K19,IF($Q$4="Macro",L19,IF($Q$4="People",M19,IF($Q$4="Sports",N19,IF($Q$4="Travel",O19,IF($Q$4="Waterdrops",P19,IF($Q$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="12" t="str">
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>Lens IS switch; camera IS menu when available</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="str">
+        <x:v>IBIS / Lens IS</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="H20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="J20" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="L20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="N20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="O20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="P20" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="Q20" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="R20" s="20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S20" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="T20" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Birds in Flight",H20,IF($D$4="Birds Perched",I20,IF($D$4="Fireworks",J20,IF($D$4="Landscape",K20,IF($D$4="Macro",L20,IF($D$4="People",M20,IF($D$4="Sports",N20,IF($D$4="Travel",O20,IF($D$4="Waterdrops",P20,IF($D$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U20" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Birds in Flight",H20,IF($E$4="Birds Perched",I20,IF($E$4="Fireworks",J20,IF($E$4="Landscape",K20,IF($E$4="Macro",L20,IF($E$4="People",M20,IF($E$4="Sports",N20,IF($E$4="Travel",O20,IF($E$4="Waterdrops",P20,IF($E$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V20" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Birds in Flight",H20,IF($F$4="Birds Perched",I20,IF($F$4="Fireworks",J20,IF($F$4="Landscape",K20,IF($F$4="Macro",L20,IF($F$4="People",M20,IF($F$4="Sports",N20,IF($F$4="Travel",O20,IF($F$4="Waterdrops",P20,IF($F$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="W20" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Birds in Flight",H20,IF($G$4="Birds Perched",I20,IF($G$4="Fireworks",J20,IF($G$4="Landscape",K20,IF($G$4="Macro",L20,IF($G$4="People",M20,IF($G$4="Sports",N20,IF($G$4="Travel",O20,IF($G$4="Waterdrops",P20,IF($G$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="X20" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Birds in Flight",H20,IF($H$4="Birds Perched",I20,IF($H$4="Fireworks",J20,IF($H$4="Landscape",K20,IF($H$4="Macro",L20,IF($H$4="People",M20,IF($H$4="Sports",N20,IF($H$4="Travel",O20,IF($H$4="Waterdrops",P20,IF($H$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Y20" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Birds in Flight",H20,IF($I$4="Birds Perched",I20,IF($I$4="Fireworks",J20,IF($I$4="Landscape",K20,IF($I$4="Macro",L20,IF($I$4="People",M20,IF($I$4="Sports",N20,IF($I$4="Travel",O20,IF($I$4="Waterdrops",P20,IF($I$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Z20" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Birds in Flight",H20,IF($J$4="Birds Perched",I20,IF($J$4="Fireworks",J20,IF($J$4="Landscape",K20,IF($J$4="Macro",L20,IF($J$4="People",M20,IF($J$4="Sports",N20,IF($J$4="Travel",O20,IF($J$4="Waterdrops",P20,IF($J$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="AA20" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Birds in Flight",H20,IF($K$4="Birds Perched",I20,IF($K$4="Fireworks",J20,IF($K$4="Landscape",K20,IF($K$4="Macro",L20,IF($K$4="People",M20,IF($K$4="Sports",N20,IF($K$4="Travel",O20,IF($K$4="Waterdrops",P20,IF($K$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AB20" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Birds in Flight",H20,IF($L$4="Birds Perched",I20,IF($L$4="Fireworks",J20,IF($L$4="Landscape",K20,IF($L$4="Macro",L20,IF($L$4="People",M20,IF($L$4="Sports",N20,IF($L$4="Travel",O20,IF($L$4="Waterdrops",P20,IF($L$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AC20" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Birds in Flight",H20,IF($M$4="Birds Perched",I20,IF($M$4="Fireworks",J20,IF($M$4="Landscape",K20,IF($M$4="Macro",L20,IF($M$4="People",M20,IF($M$4="Sports",N20,IF($M$4="Travel",O20,IF($M$4="Waterdrops",P20,IF($M$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AD20" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Birds in Flight",H20,IF($N$4="Birds Perched",I20,IF($N$4="Fireworks",J20,IF($N$4="Landscape",K20,IF($N$4="Macro",L20,IF($N$4="People",M20,IF($N$4="Sports",N20,IF($N$4="Travel",O20,IF($N$4="Waterdrops",P20,IF($N$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AE20" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Birds in Flight",H20,IF($O$4="Birds Perched",I20,IF($O$4="Fireworks",J20,IF($O$4="Landscape",K20,IF($O$4="Macro",L20,IF($O$4="People",M20,IF($O$4="Sports",N20,IF($O$4="Travel",O20,IF($O$4="Waterdrops",P20,IF($O$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AF20" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Birds in Flight",H20,IF($P$4="Birds Perched",I20,IF($P$4="Fireworks",J20,IF($P$4="Landscape",K20,IF($P$4="Macro",L20,IF($P$4="People",M20,IF($P$4="Sports",N20,IF($P$4="Travel",O20,IF($P$4="Waterdrops",P20,IF($P$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="AG20" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Birds in Flight",H20,IF($Q$4="Birds Perched",I20,IF($Q$4="Fireworks",J20,IF($Q$4="Landscape",K20,IF($Q$4="Macro",L20,IF($Q$4="People",M20,IF($Q$4="Sports",N20,IF($Q$4="Travel",O20,IF($Q$4="Waterdrops",P20,IF($Q$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" hidden="0">
+      <x:c r="A21" s="12" t="str">
         <x:v>Shooting 5 &gt; Focus bracketing</x:v>
       </x:c>
-      <x:c r="B20" s="14" t="str">
+      <x:c r="B21" s="14" t="str">
         <x:v>MM-SWITCH; MM-FOCUS*</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="C21" s="15" t="str">
         <x:v>Focus Bracketing</x:v>
       </x:c>
-      <x:c r="D20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="E20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="F20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="H20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="I20" s="17" t="str">
+      <x:c r="D21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="H21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="J21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="J20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="K20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="L20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="M20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="N20" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="O20" s="20" t="n">
+      <x:c r="M21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="N21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="O21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R21" s="20" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="P20" s="20" t="n">
+      <x:c r="S21" s="20" t="n">
         <x:v>240</x:v>
       </x:c>
+      <x:c r="T21" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Birds in Flight",H21,IF($D$4="Birds Perched",I21,IF($D$4="Fireworks",J21,IF($D$4="Landscape",K21,IF($D$4="Macro",L21,IF($D$4="People",M21,IF($D$4="Sports",N21,IF($D$4="Travel",O21,IF($D$4="Waterdrops",P21,IF($D$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U21" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Birds in Flight",H21,IF($E$4="Birds Perched",I21,IF($E$4="Fireworks",J21,IF($E$4="Landscape",K21,IF($E$4="Macro",L21,IF($E$4="People",M21,IF($E$4="Sports",N21,IF($E$4="Travel",O21,IF($E$4="Waterdrops",P21,IF($E$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V21" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Birds in Flight",H21,IF($F$4="Birds Perched",I21,IF($F$4="Fireworks",J21,IF($F$4="Landscape",K21,IF($F$4="Macro",L21,IF($F$4="People",M21,IF($F$4="Sports",N21,IF($F$4="Travel",O21,IF($F$4="Waterdrops",P21,IF($F$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W21" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Birds in Flight",H21,IF($G$4="Birds Perched",I21,IF($G$4="Fireworks",J21,IF($G$4="Landscape",K21,IF($G$4="Macro",L21,IF($G$4="People",M21,IF($G$4="Sports",N21,IF($G$4="Travel",O21,IF($G$4="Waterdrops",P21,IF($G$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X21" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Birds in Flight",H21,IF($H$4="Birds Perched",I21,IF($H$4="Fireworks",J21,IF($H$4="Landscape",K21,IF($H$4="Macro",L21,IF($H$4="People",M21,IF($H$4="Sports",N21,IF($H$4="Travel",O21,IF($H$4="Waterdrops",P21,IF($H$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Y21" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Birds in Flight",H21,IF($I$4="Birds Perched",I21,IF($I$4="Fireworks",J21,IF($I$4="Landscape",K21,IF($I$4="Macro",L21,IF($I$4="People",M21,IF($I$4="Sports",N21,IF($I$4="Travel",O21,IF($I$4="Waterdrops",P21,IF($I$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z21" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Birds in Flight",H21,IF($J$4="Birds Perched",I21,IF($J$4="Fireworks",J21,IF($J$4="Landscape",K21,IF($J$4="Macro",L21,IF($J$4="People",M21,IF($J$4="Sports",N21,IF($J$4="Travel",O21,IF($J$4="Waterdrops",P21,IF($J$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AA21" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Birds in Flight",H21,IF($K$4="Birds Perched",I21,IF($K$4="Fireworks",J21,IF($K$4="Landscape",K21,IF($K$4="Macro",L21,IF($K$4="People",M21,IF($K$4="Sports",N21,IF($K$4="Travel",O21,IF($K$4="Waterdrops",P21,IF($K$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB21" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Birds in Flight",H21,IF($L$4="Birds Perched",I21,IF($L$4="Fireworks",J21,IF($L$4="Landscape",K21,IF($L$4="Macro",L21,IF($L$4="People",M21,IF($L$4="Sports",N21,IF($L$4="Travel",O21,IF($L$4="Waterdrops",P21,IF($L$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="AC21" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Birds in Flight",H21,IF($M$4="Birds Perched",I21,IF($M$4="Fireworks",J21,IF($M$4="Landscape",K21,IF($M$4="Macro",L21,IF($M$4="People",M21,IF($M$4="Sports",N21,IF($M$4="Travel",O21,IF($M$4="Waterdrops",P21,IF($M$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD21" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Birds in Flight",H21,IF($N$4="Birds Perched",I21,IF($N$4="Fireworks",J21,IF($N$4="Landscape",K21,IF($N$4="Macro",L21,IF($N$4="People",M21,IF($N$4="Sports",N21,IF($N$4="Travel",O21,IF($N$4="Waterdrops",P21,IF($N$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AE21" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Birds in Flight",H21,IF($O$4="Birds Perched",I21,IF($O$4="Fireworks",J21,IF($O$4="Landscape",K21,IF($O$4="Macro",L21,IF($O$4="People",M21,IF($O$4="Sports",N21,IF($O$4="Travel",O21,IF($O$4="Waterdrops",P21,IF($O$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AF21" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Birds in Flight",H21,IF($P$4="Birds Perched",I21,IF($P$4="Fireworks",J21,IF($P$4="Landscape",K21,IF($P$4="Macro",L21,IF($P$4="People",M21,IF($P$4="Sports",N21,IF($P$4="Travel",O21,IF($P$4="Waterdrops",P21,IF($P$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AG21" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Birds in Flight",H21,IF($Q$4="Birds Perched",I21,IF($Q$4="Fireworks",J21,IF($Q$4="Landscape",K21,IF($Q$4="Macro",L21,IF($Q$4="People",M21,IF($Q$4="Sports",N21,IF($Q$4="Travel",O21,IF($Q$4="Waterdrops",P21,IF($Q$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D6:N20">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Not Used"/>
-    <x:cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <x:conditionalFormatting sqref="D7:D21">
+    <x:cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+      <x:formula>$T7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="E7:E21">
+    <x:cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
+      <x:formula>$U7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F7:F21">
+    <x:cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
+      <x:formula>$V7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="G7:G21">
+    <x:cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
+      <x:formula>$W7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="H7:H21">
+    <x:cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
+      <x:formula>$X7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="I7:I21">
+    <x:cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
+      <x:formula>$Y7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="J7:J21">
+    <x:cfRule type="cellIs" dxfId="6" priority="7" operator="notEqual">
+      <x:formula>$Z7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="K7:K21">
+    <x:cfRule type="cellIs" dxfId="7" priority="8" operator="notEqual">
+      <x:formula>$AA7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="L7:L21">
+    <x:cfRule type="cellIs" dxfId="8" priority="9" operator="notEqual">
+      <x:formula>$AB7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="M7:M21">
+    <x:cfRule type="cellIs" dxfId="9" priority="10" operator="notEqual">
+      <x:formula>$AC7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="N7:N21">
+    <x:cfRule type="cellIs" dxfId="10" priority="11" operator="notEqual">
+      <x:formula>$AD7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="O7:O21">
+    <x:cfRule type="cellIs" dxfId="11" priority="12" operator="notEqual">
+      <x:formula>$AE7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="P7:P21">
+    <x:cfRule type="cellIs" dxfId="12" priority="13" operator="notEqual">
+      <x:formula>$AF7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="Q7:Q21">
+    <x:cfRule type="cellIs" dxfId="13" priority="14" operator="notEqual">
+      <x:formula>$AG7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D7:Q21">
+    <x:cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Not Used"/>
+    <x:cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <x:formula>"—"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:dataValidations count="14">
+    <x:dataValidation type="list" sqref="D4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="P4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="Q4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R953e461ae7d64fab"/>
+  <x:drawing ns1:id="R5e44913e262a4c25"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R3a8fd80b2a62415f"/>
+    <x:tablePart ns1:id="Rfe2e93c97412475f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="6" max="6" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="7" max="7" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="8" max="8" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="9" max="9" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="10" max="10" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="11" max="11" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="12" max="12" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="13" max="13" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="14" max="14" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="15" max="15" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="16" max="16" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="17" max="17" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="18" max="18" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="19" max="19" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="20" max="20" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="21" max="21" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="22" max="22" width="0.2199999988079071" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="43" t="str">
+        <x:v>Approved registration targets pending physical verification. Ordinary copy/paste back to the matching C1–C3 column restores both the target values and compatible comparison highlighting.</x:v>
+      </x:c>
+      <x:c r="B1" s="43"/>
+      <x:c r="C1" s="43"/>
+      <x:c r="D1" s="43"/>
+      <x:c r="T1" s="38"/>
+      <x:c r="U1" s="38"/>
+      <x:c r="V1" s="38"/>
+    </x:row>
+    <x:row r="2" hidden="0">
+      <x:c r="A2" s="6" t="str">
+        <x:v>Setting</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>C1 Wildlife</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>C2 Birds in Flight</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="T2" s="38"/>
+      <x:c r="U2" s="38"/>
+      <x:c r="V2" s="38"/>
+    </x:row>
+    <x:row r="3" hidden="0">
+      <x:c r="A3" s="15" t="str">
+        <x:v>Mode</x:v>
+      </x:c>
+      <x:c r="B3" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="C3" s="17" t="str">
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="D3" s="17" t="str">
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="T3" s="38" t="str">
+        <x:f>B3</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="U3" s="38" t="str">
+        <x:f>C3</x:f>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="V3" s="38" t="str">
+        <x:f>D3</x:f>
+        <x:v>Av</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" hidden="0">
+      <x:c r="A4" s="15" t="str">
+        <x:v>Metering</x:v>
+      </x:c>
+      <x:c r="B4" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="C4" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="T4" s="38" t="str">
+        <x:f>B4</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="U4" s="38" t="str">
+        <x:f>C4</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="V4" s="38" t="str">
+        <x:f>D4</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" hidden="0">
+      <x:c r="A5" s="15" t="str">
+        <x:v>Shutter</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="str">
+        <x:v>1/2500 sec.</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="T5" s="38" t="str">
+        <x:f>B5</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="U5" s="38" t="str">
+        <x:f>C5</x:f>
+        <x:v>1/2500 sec.</x:v>
+      </x:c>
+      <x:c r="V5" s="38" t="str">
+        <x:f>D5</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" hidden="0">
+      <x:c r="A6" s="15" t="str">
+        <x:v>Shutter Type</x:v>
+      </x:c>
+      <x:c r="B6" s="17" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="C6" s="17" t="str">
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="D6" s="17" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="T6" s="38" t="str">
+        <x:f>B6</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="U6" s="38" t="str">
+        <x:f>C6</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="V6" s="38" t="str">
+        <x:f>D6</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" hidden="0">
+      <x:c r="A7" s="15" t="str">
+        <x:v>Aperture</x:v>
+      </x:c>
+      <x:c r="B7" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="C7" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="D7" s="17" t="str">
+        <x:v>f/9</x:v>
+      </x:c>
+      <x:c r="T7" s="38" t="str">
+        <x:f>B7</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="U7" s="38" t="str">
+        <x:f>C7</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="V7" s="38" t="str">
+        <x:f>D7</x:f>
+        <x:v>f/9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" hidden="0">
+      <x:c r="A8" s="15" t="str">
+        <x:v>ISO</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="C8" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="D8" s="17" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="T8" s="38" t="str">
+        <x:f>B8</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="U8" s="38" t="str">
+        <x:f>C8</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="V8" s="38" t="n">
+        <x:f>D8</x:f>
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" hidden="0">
+      <x:c r="A9" s="15" t="str">
+        <x:v>Exposure Comp</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="D9" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T9" s="38" t="n">
+        <x:f>B9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" s="38" t="str">
+        <x:f>C9</x:f>
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="V9" s="38" t="n">
+        <x:f>D9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" hidden="0">
+      <x:c r="A10" s="15" t="str">
+        <x:v>AF Operation</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="str">
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="T10" s="38" t="str">
+        <x:f>B10</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="U10" s="38" t="str">
+        <x:f>C10</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="V10" s="38" t="str">
+        <x:f>D10</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" hidden="0">
+      <x:c r="A11" s="15" t="str">
+        <x:v>AF Method</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="str">
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="T11" s="38" t="str">
+        <x:f>B11</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="U11" s="38" t="str">
+        <x:f>C11</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="V11" s="38" t="str">
+        <x:f>D11</x:f>
+        <x:v>1-Point AF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" hidden="0">
+      <x:c r="A12" s="15" t="str">
+        <x:v>Subject Detection</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="D12" s="17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="T12" s="38" t="str">
+        <x:f>B12</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="U12" s="38" t="str">
+        <x:f>C12</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="V12" s="38" t="str">
+        <x:f>D12</x:f>
+        <x:v>None</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" hidden="0">
+      <x:c r="A13" s="15" t="str">
+        <x:v>Eye Detection</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="T13" s="38" t="str">
+        <x:f>B13</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="U13" s="38" t="str">
+        <x:f>C13</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="V13" s="38" t="str">
+        <x:f>D13</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" hidden="0">
+      <x:c r="A14" s="15" t="str">
+        <x:v>Drive</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="T14" s="38" t="str">
+        <x:f>B14</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="U14" s="38" t="str">
+        <x:f>C14</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="V14" s="38" t="str">
+        <x:f>D14</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" hidden="0">
+      <x:c r="A15" s="15" t="str">
+        <x:v>Image Stabilization</x:v>
+      </x:c>
+      <x:c r="B15" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="T15" s="38" t="str">
+        <x:f>B15</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U15" s="38" t="str">
+        <x:f>C15</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="V15" s="38" t="str">
+        <x:f>D15</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" hidden="0">
+      <x:c r="A16" s="15" t="str">
+        <x:v>IBIS / Lens IS</x:v>
+      </x:c>
+      <x:c r="B16" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="T16" s="38" t="str">
+        <x:f>B16</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U16" s="38" t="str">
+        <x:f>C16</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V16" s="38" t="str">
+        <x:f>D16</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" hidden="0">
+      <x:c r="A17" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="B17" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="D17" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="T17" s="38" t="str">
+        <x:f>B17</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U17" s="38" t="str">
+        <x:f>C17</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V17" s="38" t="str">
+        <x:f>D17</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="B3:B17">
+    <x:cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
+      <x:formula>$T3</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="C3:C17">
+    <x:cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
+      <x:formula>$U3</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D3:D17">
+    <x:cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
+      <x:formula>$V3</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart ns1:id="R4d2ccdd858164261"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R5df6c82b87f445b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R44e8aba10eeb4d08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R3fdcf251db024281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R02723b7cd57d4c8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="fcb4f8a7-5021-4b9e-833b-74f422a50bab"/>
+        <xdr:cNvPr id="1" name="b60ca0eb-0b7a-4823-87e2-9dbc97009bd9"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd54e2ae9fe4b4533"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf80b1f0f983941cc"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -453,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:S21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:S22"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="Menu Location"/>
     <x:tableColumn id="2" name="Best or Quick Access"/>
@@ -481,8 +481,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A2:D17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A2:D18"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Setting"/>
     <x:tableColumn id="2" name="C1 Wildlife"/>
@@ -849,10 +849,10 @@
         <x:v>Camera defaults</x:v>
       </x:c>
       <x:c r="H5" s="37" t="str">
-        <x:v>C2 Birds in Flight</x:v>
+        <x:v>C2 Birds in Flight + AF Case</x:v>
       </x:c>
       <x:c r="I5" s="37" t="str">
-        <x:v>C1 Wildlife</x:v>
+        <x:v>C1 Wildlife + AF Case</x:v>
       </x:c>
       <x:c r="J5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
@@ -864,10 +864,10 @@
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="M5" s="37" t="str">
-        <x:v>C1 Wildlife + SWITCH</x:v>
+        <x:v>C1 Wildlife + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="N5" s="37" t="str">
-        <x:v>C2 Birds in Flight + SWITCH</x:v>
+        <x:v>C2 Birds in Flight + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="O5" s="37" t="str">
         <x:v>C3 Landscape</x:v>
@@ -876,7 +876,7 @@
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="Q5" s="37" t="str">
-        <x:v>C1 Wildlife</x:v>
+        <x:v>C1 Wildlife + AF Case</x:v>
       </x:c>
       <x:c r="T5" s="38"/>
       <x:c r="U5" s="38"/>
@@ -1888,85 +1888,85 @@
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="12" t="str">
-        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Servo AF; AF3 &gt; Servo AF characteristics</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>AF Point Selection button + Main Dial</x:v>
+        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="E15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="F15" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="I15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="J15" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K15" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L15" s="17" t="str">
-        <x:v>Spot AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="N15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="O15" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="P15" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="R15" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="S15" s="20" t="n">
-        <x:v>140</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="T15" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Birds in Flight",H15,IF($D$4="Birds Perched",I15,IF($D$4="Fireworks",J15,IF($D$4="Landscape",K15,IF($D$4="Macro",L15,IF($D$4="People",M15,IF($D$4="Sports",N15,IF($D$4="Travel",O15,IF($D$4="Waterdrops",P15,IF($D$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="U15" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Birds in Flight",H15,IF($E$4="Birds Perched",I15,IF($E$4="Fireworks",J15,IF($E$4="Landscape",K15,IF($E$4="Macro",L15,IF($E$4="People",M15,IF($E$4="Sports",N15,IF($E$4="Travel",O15,IF($E$4="Waterdrops",P15,IF($E$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="V15" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Birds in Flight",H15,IF($F$4="Birds Perched",I15,IF($F$4="Fireworks",J15,IF($F$4="Landscape",K15,IF($F$4="Macro",L15,IF($F$4="People",M15,IF($F$4="Sports",N15,IF($F$4="Travel",O15,IF($F$4="Waterdrops",P15,IF($F$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W15" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Birds in Flight",H15,IF($G$4="Birds Perched",I15,IF($G$4="Fireworks",J15,IF($G$4="Landscape",K15,IF($G$4="Macro",L15,IF($G$4="People",M15,IF($G$4="Sports",N15,IF($G$4="Travel",O15,IF($G$4="Waterdrops",P15,IF($G$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="X15" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Birds in Flight",H15,IF($H$4="Birds Perched",I15,IF($H$4="Fireworks",J15,IF($H$4="Landscape",K15,IF($H$4="Macro",L15,IF($H$4="People",M15,IF($H$4="Sports",N15,IF($H$4="Travel",O15,IF($H$4="Waterdrops",P15,IF($H$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="Y15" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Birds in Flight",H15,IF($I$4="Birds Perched",I15,IF($I$4="Fireworks",J15,IF($I$4="Landscape",K15,IF($I$4="Macro",L15,IF($I$4="People",M15,IF($I$4="Sports",N15,IF($I$4="Travel",O15,IF($I$4="Waterdrops",P15,IF($I$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="Z15" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Birds in Flight",H15,IF($J$4="Birds Perched",I15,IF($J$4="Fireworks",J15,IF($J$4="Landscape",K15,IF($J$4="Macro",L15,IF($J$4="People",M15,IF($J$4="Sports",N15,IF($J$4="Travel",O15,IF($J$4="Waterdrops",P15,IF($J$4="Wildlife",Q15,""))))))))))))))</x:f>
@@ -1974,23 +1974,23 @@
       </x:c>
       <x:c r="AA15" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Birds in Flight",H15,IF($K$4="Birds Perched",I15,IF($K$4="Fireworks",J15,IF($K$4="Landscape",K15,IF($K$4="Macro",L15,IF($K$4="People",M15,IF($K$4="Sports",N15,IF($K$4="Travel",O15,IF($K$4="Waterdrops",P15,IF($K$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB15" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Birds in Flight",H15,IF($L$4="Birds Perched",I15,IF($L$4="Fireworks",J15,IF($L$4="Landscape",K15,IF($L$4="Macro",L15,IF($L$4="People",M15,IF($L$4="Sports",N15,IF($L$4="Travel",O15,IF($L$4="Waterdrops",P15,IF($L$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Spot AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC15" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Birds in Flight",H15,IF($M$4="Birds Perched",I15,IF($M$4="Fireworks",J15,IF($M$4="Landscape",K15,IF($M$4="Macro",L15,IF($M$4="People",M15,IF($M$4="Sports",N15,IF($M$4="Travel",O15,IF($M$4="Waterdrops",P15,IF($M$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="AD15" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Birds in Flight",H15,IF($N$4="Birds Perched",I15,IF($N$4="Fireworks",J15,IF($N$4="Landscape",K15,IF($N$4="Macro",L15,IF($N$4="People",M15,IF($N$4="Sports",N15,IF($N$4="Travel",O15,IF($N$4="Waterdrops",P15,IF($N$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="AE15" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Birds in Flight",H15,IF($O$4="Birds Perched",I15,IF($O$4="Fireworks",J15,IF($O$4="Landscape",K15,IF($O$4="Macro",L15,IF($O$4="People",M15,IF($O$4="Sports",N15,IF($O$4="Travel",O15,IF($O$4="Waterdrops",P15,IF($O$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="AF15" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Birds in Flight",H15,IF($P$4="Birds Perched",I15,IF($P$4="Fireworks",J15,IF($P$4="Landscape",K15,IF($P$4="Macro",L15,IF($P$4="People",M15,IF($P$4="Sports",N15,IF($P$4="Travel",O15,IF($P$4="Waterdrops",P15,IF($P$4="Wildlife",Q15,""))))))))))))))</x:f>
@@ -1998,90 +1998,90 @@
       </x:c>
       <x:c r="AG15" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Birds in Flight",H15,IF($Q$4="Birds Perched",I15,IF($Q$4="Fireworks",J15,IF($Q$4="Landscape",K15,IF($Q$4="Macro",L15,IF($Q$4="People",M15,IF($Q$4="Sports",N15,IF($Q$4="Travel",O15,IF($Q$4="Waterdrops",P15,IF($Q$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="12" t="str">
-        <x:v>AF1 &gt; Subject to detect</x:v>
+        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>MM-SWITCH</x:v>
+        <x:v>AF Point Selection button + Main Dial</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="E16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="F16" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="H16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="I16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="J16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="L16" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="M16" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="N16" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="O16" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="P16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="R16" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="S16" s="20" t="n">
-        <x:v>220</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="T16" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Birds in Flight",H16,IF($D$4="Birds Perched",I16,IF($D$4="Fireworks",J16,IF($D$4="Landscape",K16,IF($D$4="Macro",L16,IF($D$4="People",M16,IF($D$4="Sports",N16,IF($D$4="Travel",O16,IF($D$4="Waterdrops",P16,IF($D$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="U16" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Birds in Flight",H16,IF($E$4="Birds Perched",I16,IF($E$4="Fireworks",J16,IF($E$4="Landscape",K16,IF($E$4="Macro",L16,IF($E$4="People",M16,IF($E$4="Sports",N16,IF($E$4="Travel",O16,IF($E$4="Waterdrops",P16,IF($E$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="V16" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Birds in Flight",H16,IF($F$4="Birds Perched",I16,IF($F$4="Fireworks",J16,IF($F$4="Landscape",K16,IF($F$4="Macro",L16,IF($F$4="People",M16,IF($F$4="Sports",N16,IF($F$4="Travel",O16,IF($F$4="Waterdrops",P16,IF($F$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="W16" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Birds in Flight",H16,IF($G$4="Birds Perched",I16,IF($G$4="Fireworks",J16,IF($G$4="Landscape",K16,IF($G$4="Macro",L16,IF($G$4="People",M16,IF($G$4="Sports",N16,IF($G$4="Travel",O16,IF($G$4="Waterdrops",P16,IF($G$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="X16" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Birds in Flight",H16,IF($H$4="Birds Perched",I16,IF($H$4="Fireworks",J16,IF($H$4="Landscape",K16,IF($H$4="Macro",L16,IF($H$4="People",M16,IF($H$4="Sports",N16,IF($H$4="Travel",O16,IF($H$4="Waterdrops",P16,IF($H$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Y16" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Birds in Flight",H16,IF($I$4="Birds Perched",I16,IF($I$4="Fireworks",J16,IF($I$4="Landscape",K16,IF($I$4="Macro",L16,IF($I$4="People",M16,IF($I$4="Sports",N16,IF($I$4="Travel",O16,IF($I$4="Waterdrops",P16,IF($I$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Z16" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Birds in Flight",H16,IF($J$4="Birds Perched",I16,IF($J$4="Fireworks",J16,IF($J$4="Landscape",K16,IF($J$4="Macro",L16,IF($J$4="People",M16,IF($J$4="Sports",N16,IF($J$4="Travel",O16,IF($J$4="Waterdrops",P16,IF($J$4="Wildlife",Q16,""))))))))))))))</x:f>
@@ -2089,23 +2089,23 @@
       </x:c>
       <x:c r="AA16" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Birds in Flight",H16,IF($K$4="Birds Perched",I16,IF($K$4="Fireworks",J16,IF($K$4="Landscape",K16,IF($K$4="Macro",L16,IF($K$4="People",M16,IF($K$4="Sports",N16,IF($K$4="Travel",O16,IF($K$4="Waterdrops",P16,IF($K$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="AB16" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Birds in Flight",H16,IF($L$4="Birds Perched",I16,IF($L$4="Fireworks",J16,IF($L$4="Landscape",K16,IF($L$4="Macro",L16,IF($L$4="People",M16,IF($L$4="Sports",N16,IF($L$4="Travel",O16,IF($L$4="Waterdrops",P16,IF($L$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="AC16" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Birds in Flight",H16,IF($M$4="Birds Perched",I16,IF($M$4="Fireworks",J16,IF($M$4="Landscape",K16,IF($M$4="Macro",L16,IF($M$4="People",M16,IF($M$4="Sports",N16,IF($M$4="Travel",O16,IF($M$4="Waterdrops",P16,IF($M$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="AD16" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Birds in Flight",H16,IF($N$4="Birds Perched",I16,IF($N$4="Fireworks",J16,IF($N$4="Landscape",K16,IF($N$4="Macro",L16,IF($N$4="People",M16,IF($N$4="Sports",N16,IF($N$4="Travel",O16,IF($N$4="Waterdrops",P16,IF($N$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="AE16" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Birds in Flight",H16,IF($O$4="Birds Perched",I16,IF($O$4="Fireworks",J16,IF($O$4="Landscape",K16,IF($O$4="Macro",L16,IF($O$4="People",M16,IF($O$4="Sports",N16,IF($O$4="Travel",O16,IF($O$4="Waterdrops",P16,IF($O$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="AF16" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Birds in Flight",H16,IF($P$4="Birds Perched",I16,IF($P$4="Fireworks",J16,IF($P$4="Landscape",K16,IF($P$4="Macro",L16,IF($P$4="People",M16,IF($P$4="Sports",N16,IF($P$4="Travel",O16,IF($P$4="Waterdrops",P16,IF($P$4="Wildlife",Q16,""))))))))))))))</x:f>
@@ -2113,90 +2113,90 @@
       </x:c>
       <x:c r="AG16" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Birds in Flight",H16,IF($Q$4="Birds Perched",I16,IF($Q$4="Fireworks",J16,IF($Q$4="Landscape",K16,IF($Q$4="Macro",L16,IF($Q$4="People",M16,IF($Q$4="Sports",N16,IF($Q$4="Travel",O16,IF($Q$4="Waterdrops",P16,IF($Q$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="12" t="str">
-        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
+        <x:v>AF1 &gt; Subject to detect</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>SET button</x:v>
+        <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="F17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="L17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="M17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="O17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="P17" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="R17" s="20" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="S17" s="20" t="n">
-        <x:v>150</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="T17" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Birds in Flight",H17,IF($D$4="Birds Perched",I17,IF($D$4="Fireworks",J17,IF($D$4="Landscape",K17,IF($D$4="Macro",L17,IF($D$4="People",M17,IF($D$4="Sports",N17,IF($D$4="Travel",O17,IF($D$4="Waterdrops",P17,IF($D$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="U17" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Birds in Flight",H17,IF($E$4="Birds Perched",I17,IF($E$4="Fireworks",J17,IF($E$4="Landscape",K17,IF($E$4="Macro",L17,IF($E$4="People",M17,IF($E$4="Sports",N17,IF($E$4="Travel",O17,IF($E$4="Waterdrops",P17,IF($E$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Birds in Flight",H17,IF($F$4="Birds Perched",I17,IF($F$4="Fireworks",J17,IF($F$4="Landscape",K17,IF($F$4="Macro",L17,IF($F$4="People",M17,IF($F$4="Sports",N17,IF($F$4="Travel",O17,IF($F$4="Waterdrops",P17,IF($F$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="W17" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Birds in Flight",H17,IF($G$4="Birds Perched",I17,IF($G$4="Fireworks",J17,IF($G$4="Landscape",K17,IF($G$4="Macro",L17,IF($G$4="People",M17,IF($G$4="Sports",N17,IF($G$4="Travel",O17,IF($G$4="Waterdrops",P17,IF($G$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="X17" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Birds in Flight",H17,IF($H$4="Birds Perched",I17,IF($H$4="Fireworks",J17,IF($H$4="Landscape",K17,IF($H$4="Macro",L17,IF($H$4="People",M17,IF($H$4="Sports",N17,IF($H$4="Travel",O17,IF($H$4="Waterdrops",P17,IF($H$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Y17" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Birds in Flight",H17,IF($I$4="Birds Perched",I17,IF($I$4="Fireworks",J17,IF($I$4="Landscape",K17,IF($I$4="Macro",L17,IF($I$4="People",M17,IF($I$4="Sports",N17,IF($I$4="Travel",O17,IF($I$4="Waterdrops",P17,IF($I$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Z17" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Birds in Flight",H17,IF($J$4="Birds Perched",I17,IF($J$4="Fireworks",J17,IF($J$4="Landscape",K17,IF($J$4="Macro",L17,IF($J$4="People",M17,IF($J$4="Sports",N17,IF($J$4="Travel",O17,IF($J$4="Waterdrops",P17,IF($J$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2204,23 +2204,23 @@
       </x:c>
       <x:c r="AA17" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Birds in Flight",H17,IF($K$4="Birds Perched",I17,IF($K$4="Fireworks",J17,IF($K$4="Landscape",K17,IF($K$4="Macro",L17,IF($K$4="People",M17,IF($K$4="Sports",N17,IF($K$4="Travel",O17,IF($K$4="Waterdrops",P17,IF($K$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AB17" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Birds in Flight",H17,IF($L$4="Birds Perched",I17,IF($L$4="Fireworks",J17,IF($L$4="Landscape",K17,IF($L$4="Macro",L17,IF($L$4="People",M17,IF($L$4="Sports",N17,IF($L$4="Travel",O17,IF($L$4="Waterdrops",P17,IF($L$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AC17" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Birds in Flight",H17,IF($M$4="Birds Perched",I17,IF($M$4="Fireworks",J17,IF($M$4="Landscape",K17,IF($M$4="Macro",L17,IF($M$4="People",M17,IF($M$4="Sports",N17,IF($M$4="Travel",O17,IF($M$4="Waterdrops",P17,IF($M$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="AD17" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Birds in Flight",H17,IF($N$4="Birds Perched",I17,IF($N$4="Fireworks",J17,IF($N$4="Landscape",K17,IF($N$4="Macro",L17,IF($N$4="People",M17,IF($N$4="Sports",N17,IF($N$4="Travel",O17,IF($N$4="Waterdrops",P17,IF($N$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="AE17" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Birds in Flight",H17,IF($O$4="Birds Perched",I17,IF($O$4="Fireworks",J17,IF($O$4="Landscape",K17,IF($O$4="Macro",L17,IF($O$4="People",M17,IF($O$4="Sports",N17,IF($O$4="Travel",O17,IF($O$4="Waterdrops",P17,IF($O$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AF17" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Birds in Flight",H17,IF($P$4="Birds Perched",I17,IF($P$4="Fireworks",J17,IF($P$4="Landscape",K17,IF($P$4="Macro",L17,IF($P$4="People",M17,IF($P$4="Sports",N17,IF($P$4="Travel",O17,IF($P$4="Waterdrops",P17,IF($P$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2228,541 +2228,656 @@
       </x:c>
       <x:c r="AG17" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Birds in Flight",H17,IF($Q$4="Birds Perched",I17,IF($Q$4="Fireworks",J17,IF($Q$4="Landscape",K17,IF($Q$4="Macro",L17,IF($Q$4="People",M17,IF($Q$4="Sports",N17,IF($Q$4="Travel",O17,IF($Q$4="Waterdrops",P17,IF($Q$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="12" t="str">
-        <x:v>Shooting menu &gt; Drive mode</x:v>
+        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>SET button</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="E18" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="F18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="G18" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="H18" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="I18" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="L18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="M18" s="17" t="str">
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="O18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="P18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q18" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="R18" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="S18" s="20" t="n">
-        <x:v>160</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="T18" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Birds in Flight",H18,IF($D$4="Birds Perched",I18,IF($D$4="Fireworks",J18,IF($D$4="Landscape",K18,IF($D$4="Macro",L18,IF($D$4="People",M18,IF($D$4="Sports",N18,IF($D$4="Travel",O18,IF($D$4="Waterdrops",P18,IF($D$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="U18" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Birds in Flight",H18,IF($E$4="Birds Perched",I18,IF($E$4="Fireworks",J18,IF($E$4="Landscape",K18,IF($E$4="Macro",L18,IF($E$4="People",M18,IF($E$4="Sports",N18,IF($E$4="Travel",O18,IF($E$4="Waterdrops",P18,IF($E$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V18" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Birds in Flight",H18,IF($F$4="Birds Perched",I18,IF($F$4="Fireworks",J18,IF($F$4="Landscape",K18,IF($F$4="Macro",L18,IF($F$4="People",M18,IF($F$4="Sports",N18,IF($F$4="Travel",O18,IF($F$4="Waterdrops",P18,IF($F$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="W18" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Birds in Flight",H18,IF($G$4="Birds Perched",I18,IF($G$4="Fireworks",J18,IF($G$4="Landscape",K18,IF($G$4="Macro",L18,IF($G$4="People",M18,IF($G$4="Sports",N18,IF($G$4="Travel",O18,IF($G$4="Waterdrops",P18,IF($G$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="X18" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Birds in Flight",H18,IF($H$4="Birds Perched",I18,IF($H$4="Fireworks",J18,IF($H$4="Landscape",K18,IF($H$4="Macro",L18,IF($H$4="People",M18,IF($H$4="Sports",N18,IF($H$4="Travel",O18,IF($H$4="Waterdrops",P18,IF($H$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Y18" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Birds in Flight",H18,IF($I$4="Birds Perched",I18,IF($I$4="Fireworks",J18,IF($I$4="Landscape",K18,IF($I$4="Macro",L18,IF($I$4="People",M18,IF($I$4="Sports",N18,IF($I$4="Travel",O18,IF($I$4="Waterdrops",P18,IF($I$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Z18" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Birds in Flight",H18,IF($J$4="Birds Perched",I18,IF($J$4="Fireworks",J18,IF($J$4="Landscape",K18,IF($J$4="Macro",L18,IF($J$4="People",M18,IF($J$4="Sports",N18,IF($J$4="Travel",O18,IF($J$4="Waterdrops",P18,IF($J$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AA18" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Birds in Flight",H18,IF($K$4="Birds Perched",I18,IF($K$4="Fireworks",J18,IF($K$4="Landscape",K18,IF($K$4="Macro",L18,IF($K$4="People",M18,IF($K$4="Sports",N18,IF($K$4="Travel",O18,IF($K$4="Waterdrops",P18,IF($K$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AB18" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Birds in Flight",H18,IF($L$4="Birds Perched",I18,IF($L$4="Fireworks",J18,IF($L$4="Landscape",K18,IF($L$4="Macro",L18,IF($L$4="People",M18,IF($L$4="Sports",N18,IF($L$4="Travel",O18,IF($L$4="Waterdrops",P18,IF($L$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AC18" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Birds in Flight",H18,IF($M$4="Birds Perched",I18,IF($M$4="Fireworks",J18,IF($M$4="Landscape",K18,IF($M$4="Macro",L18,IF($M$4="People",M18,IF($M$4="Sports",N18,IF($M$4="Travel",O18,IF($M$4="Waterdrops",P18,IF($M$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AD18" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Birds in Flight",H18,IF($N$4="Birds Perched",I18,IF($N$4="Fireworks",J18,IF($N$4="Landscape",K18,IF($N$4="Macro",L18,IF($N$4="People",M18,IF($N$4="Sports",N18,IF($N$4="Travel",O18,IF($N$4="Waterdrops",P18,IF($N$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AE18" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Birds in Flight",H18,IF($O$4="Birds Perched",I18,IF($O$4="Fireworks",J18,IF($O$4="Landscape",K18,IF($O$4="Macro",L18,IF($O$4="People",M18,IF($O$4="Sports",N18,IF($O$4="Travel",O18,IF($O$4="Waterdrops",P18,IF($O$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AF18" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Birds in Flight",H18,IF($P$4="Birds Perched",I18,IF($P$4="Fireworks",J18,IF($P$4="Landscape",K18,IF($P$4="Macro",L18,IF($P$4="People",M18,IF($P$4="Sports",N18,IF($P$4="Travel",O18,IF($P$4="Waterdrops",P18,IF($P$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG18" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Birds in Flight",H18,IF($Q$4="Birds Perched",I18,IF($Q$4="Fireworks",J18,IF($Q$4="Landscape",K18,IF($Q$4="Macro",L18,IF($Q$4="People",M18,IF($Q$4="Sports",N18,IF($Q$4="Travel",O18,IF($Q$4="Waterdrops",P18,IF($Q$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
+        <x:v>Shooting menu &gt; Drive mode</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Drive</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="E19" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="F19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="G19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="L19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="M19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Low Speed Continuous</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="O19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="P19" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="Q19" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="R19" s="20" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="S19" s="20" t="n">
-        <x:v>230</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="T19" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Birds in Flight",H19,IF($D$4="Birds Perched",I19,IF($D$4="Fireworks",J19,IF($D$4="Landscape",K19,IF($D$4="Macro",L19,IF($D$4="People",M19,IF($D$4="Sports",N19,IF($D$4="Travel",O19,IF($D$4="Waterdrops",P19,IF($D$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="U19" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Birds in Flight",H19,IF($E$4="Birds Perched",I19,IF($E$4="Fireworks",J19,IF($E$4="Landscape",K19,IF($E$4="Macro",L19,IF($E$4="People",M19,IF($E$4="Sports",N19,IF($E$4="Travel",O19,IF($E$4="Waterdrops",P19,IF($E$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="V19" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Birds in Flight",H19,IF($F$4="Birds Perched",I19,IF($F$4="Fireworks",J19,IF($F$4="Landscape",K19,IF($F$4="Macro",L19,IF($F$4="People",M19,IF($F$4="Sports",N19,IF($F$4="Travel",O19,IF($F$4="Waterdrops",P19,IF($F$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="W19" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Birds in Flight",H19,IF($G$4="Birds Perched",I19,IF($G$4="Fireworks",J19,IF($G$4="Landscape",K19,IF($G$4="Macro",L19,IF($G$4="People",M19,IF($G$4="Sports",N19,IF($G$4="Travel",O19,IF($G$4="Waterdrops",P19,IF($G$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="X19" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Birds in Flight",H19,IF($H$4="Birds Perched",I19,IF($H$4="Fireworks",J19,IF($H$4="Landscape",K19,IF($H$4="Macro",L19,IF($H$4="People",M19,IF($H$4="Sports",N19,IF($H$4="Travel",O19,IF($H$4="Waterdrops",P19,IF($H$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="Y19" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Birds in Flight",H19,IF($I$4="Birds Perched",I19,IF($I$4="Fireworks",J19,IF($I$4="Landscape",K19,IF($I$4="Macro",L19,IF($I$4="People",M19,IF($I$4="Sports",N19,IF($I$4="Travel",O19,IF($I$4="Waterdrops",P19,IF($I$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="Z19" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Birds in Flight",H19,IF($J$4="Birds Perched",I19,IF($J$4="Fireworks",J19,IF($J$4="Landscape",K19,IF($J$4="Macro",L19,IF($J$4="People",M19,IF($J$4="Sports",N19,IF($J$4="Travel",O19,IF($J$4="Waterdrops",P19,IF($J$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Off</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AA19" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Birds in Flight",H19,IF($K$4="Birds Perched",I19,IF($K$4="Fireworks",J19,IF($K$4="Landscape",K19,IF($K$4="Macro",L19,IF($K$4="People",M19,IF($K$4="Sports",N19,IF($K$4="Travel",O19,IF($K$4="Waterdrops",P19,IF($K$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AB19" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Birds in Flight",H19,IF($L$4="Birds Perched",I19,IF($L$4="Fireworks",J19,IF($L$4="Landscape",K19,IF($L$4="Macro",L19,IF($L$4="People",M19,IF($L$4="Sports",N19,IF($L$4="Travel",O19,IF($L$4="Waterdrops",P19,IF($L$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AC19" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Birds in Flight",H19,IF($M$4="Birds Perched",I19,IF($M$4="Fireworks",J19,IF($M$4="Landscape",K19,IF($M$4="Macro",L19,IF($M$4="People",M19,IF($M$4="Sports",N19,IF($M$4="Travel",O19,IF($M$4="Waterdrops",P19,IF($M$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Low Speed Continuous</x:v>
       </x:c>
       <x:c r="AD19" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Birds in Flight",H19,IF($N$4="Birds Perched",I19,IF($N$4="Fireworks",J19,IF($N$4="Landscape",K19,IF($N$4="Macro",L19,IF($N$4="People",M19,IF($N$4="Sports",N19,IF($N$4="Travel",O19,IF($N$4="Waterdrops",P19,IF($N$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="AE19" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Birds in Flight",H19,IF($O$4="Birds Perched",I19,IF($O$4="Fireworks",J19,IF($O$4="Landscape",K19,IF($O$4="Macro",L19,IF($O$4="People",M19,IF($O$4="Sports",N19,IF($O$4="Travel",O19,IF($O$4="Waterdrops",P19,IF($O$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AF19" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Birds in Flight",H19,IF($P$4="Birds Perched",I19,IF($P$4="Fireworks",J19,IF($P$4="Landscape",K19,IF($P$4="Macro",L19,IF($P$4="People",M19,IF($P$4="Sports",N19,IF($P$4="Travel",O19,IF($P$4="Waterdrops",P19,IF($P$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Off</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AG19" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Birds in Flight",H19,IF($Q$4="Birds Perched",I19,IF($Q$4="Fireworks",J19,IF($Q$4="Landscape",K19,IF($Q$4="Macro",L19,IF($Q$4="People",M19,IF($Q$4="Sports",N19,IF($Q$4="Travel",O19,IF($Q$4="Waterdrops",P19,IF($Q$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>Lens IS switch; camera IS menu when available</x:v>
+        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Image Stabilization</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="E20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="F20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="G20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="L20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="M20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="N20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="O20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="P20" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="Q20" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="R20" s="20" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="S20" s="20" t="n">
-        <x:v>40</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="T20" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Birds in Flight",H20,IF($D$4="Birds Perched",I20,IF($D$4="Fireworks",J20,IF($D$4="Landscape",K20,IF($D$4="Macro",L20,IF($D$4="People",M20,IF($D$4="Sports",N20,IF($D$4="Travel",O20,IF($D$4="Waterdrops",P20,IF($D$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="U20" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Birds in Flight",H20,IF($E$4="Birds Perched",I20,IF($E$4="Fireworks",J20,IF($E$4="Landscape",K20,IF($E$4="Macro",L20,IF($E$4="People",M20,IF($E$4="Sports",N20,IF($E$4="Travel",O20,IF($E$4="Waterdrops",P20,IF($E$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="V20" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Birds in Flight",H20,IF($F$4="Birds Perched",I20,IF($F$4="Fireworks",J20,IF($F$4="Landscape",K20,IF($F$4="Macro",L20,IF($F$4="People",M20,IF($F$4="Sports",N20,IF($F$4="Travel",O20,IF($F$4="Waterdrops",P20,IF($F$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="W20" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Birds in Flight",H20,IF($G$4="Birds Perched",I20,IF($G$4="Fireworks",J20,IF($G$4="Landscape",K20,IF($G$4="Macro",L20,IF($G$4="People",M20,IF($G$4="Sports",N20,IF($G$4="Travel",O20,IF($G$4="Waterdrops",P20,IF($G$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="X20" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Birds in Flight",H20,IF($H$4="Birds Perched",I20,IF($H$4="Fireworks",J20,IF($H$4="Landscape",K20,IF($H$4="Macro",L20,IF($H$4="People",M20,IF($H$4="Sports",N20,IF($H$4="Travel",O20,IF($H$4="Waterdrops",P20,IF($H$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="Y20" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Birds in Flight",H20,IF($I$4="Birds Perched",I20,IF($I$4="Fireworks",J20,IF($I$4="Landscape",K20,IF($I$4="Macro",L20,IF($I$4="People",M20,IF($I$4="Sports",N20,IF($I$4="Travel",O20,IF($I$4="Waterdrops",P20,IF($I$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="Z20" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Birds in Flight",H20,IF($J$4="Birds Perched",I20,IF($J$4="Fireworks",J20,IF($J$4="Landscape",K20,IF($J$4="Macro",L20,IF($J$4="People",M20,IF($J$4="Sports",N20,IF($J$4="Travel",O20,IF($J$4="Waterdrops",P20,IF($J$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="AA20" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Birds in Flight",H20,IF($K$4="Birds Perched",I20,IF($K$4="Fireworks",J20,IF($K$4="Landscape",K20,IF($K$4="Macro",L20,IF($K$4="People",M20,IF($K$4="Sports",N20,IF($K$4="Travel",O20,IF($K$4="Waterdrops",P20,IF($K$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="AB20" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Birds in Flight",H20,IF($L$4="Birds Perched",I20,IF($L$4="Fireworks",J20,IF($L$4="Landscape",K20,IF($L$4="Macro",L20,IF($L$4="People",M20,IF($L$4="Sports",N20,IF($L$4="Travel",O20,IF($L$4="Waterdrops",P20,IF($L$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="AC20" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Birds in Flight",H20,IF($M$4="Birds Perched",I20,IF($M$4="Fireworks",J20,IF($M$4="Landscape",K20,IF($M$4="Macro",L20,IF($M$4="People",M20,IF($M$4="Sports",N20,IF($M$4="Travel",O20,IF($M$4="Waterdrops",P20,IF($M$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="AD20" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Birds in Flight",H20,IF($N$4="Birds Perched",I20,IF($N$4="Fireworks",J20,IF($N$4="Landscape",K20,IF($N$4="Macro",L20,IF($N$4="People",M20,IF($N$4="Sports",N20,IF($N$4="Travel",O20,IF($N$4="Waterdrops",P20,IF($N$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="AE20" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Birds in Flight",H20,IF($O$4="Birds Perched",I20,IF($O$4="Fireworks",J20,IF($O$4="Landscape",K20,IF($O$4="Macro",L20,IF($O$4="People",M20,IF($O$4="Sports",N20,IF($O$4="Travel",O20,IF($O$4="Waterdrops",P20,IF($O$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="AF20" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Birds in Flight",H20,IF($P$4="Birds Perched",I20,IF($P$4="Fireworks",J20,IF($P$4="Landscape",K20,IF($P$4="Macro",L20,IF($P$4="People",M20,IF($P$4="Sports",N20,IF($P$4="Travel",O20,IF($P$4="Waterdrops",P20,IF($P$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
+        <x:v>Off</x:v>
       </x:c>
       <x:c r="AG20" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Birds in Flight",H20,IF($Q$4="Birds Perched",I20,IF($Q$4="Fireworks",J20,IF($Q$4="Landscape",K20,IF($Q$4="Macro",L20,IF($Q$4="People",M20,IF($Q$4="Sports",N20,IF($Q$4="Travel",O20,IF($Q$4="Waterdrops",P20,IF($Q$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="12" t="str">
-        <x:v>Shooting 5 &gt; Focus bracketing</x:v>
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*</x:v>
+        <x:v>Lens IS switch; camera IS menu when available</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>IBIS / Lens IS</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="E21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="F21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="G21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Off / Off</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="L21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="M21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="N21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="O21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="P21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Off / Off</x:v>
       </x:c>
       <x:c r="Q21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="R21" s="20" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="S21" s="20" t="n">
-        <x:v>240</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="T21" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Birds in Flight",H21,IF($D$4="Birds Perched",I21,IF($D$4="Fireworks",J21,IF($D$4="Landscape",K21,IF($D$4="Macro",L21,IF($D$4="People",M21,IF($D$4="Sports",N21,IF($D$4="Travel",O21,IF($D$4="Waterdrops",P21,IF($D$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="U21" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Birds in Flight",H21,IF($E$4="Birds Perched",I21,IF($E$4="Fireworks",J21,IF($E$4="Landscape",K21,IF($E$4="Macro",L21,IF($E$4="People",M21,IF($E$4="Sports",N21,IF($E$4="Travel",O21,IF($E$4="Waterdrops",P21,IF($E$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="V21" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Birds in Flight",H21,IF($F$4="Birds Perched",I21,IF($F$4="Fireworks",J21,IF($F$4="Landscape",K21,IF($F$4="Macro",L21,IF($F$4="People",M21,IF($F$4="Sports",N21,IF($F$4="Travel",O21,IF($F$4="Waterdrops",P21,IF($F$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="W21" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Birds in Flight",H21,IF($G$4="Birds Perched",I21,IF($G$4="Fireworks",J21,IF($G$4="Landscape",K21,IF($G$4="Macro",L21,IF($G$4="People",M21,IF($G$4="Sports",N21,IF($G$4="Travel",O21,IF($G$4="Waterdrops",P21,IF($G$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="X21" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Birds in Flight",H21,IF($H$4="Birds Perched",I21,IF($H$4="Fireworks",J21,IF($H$4="Landscape",K21,IF($H$4="Macro",L21,IF($H$4="People",M21,IF($H$4="Sports",N21,IF($H$4="Travel",O21,IF($H$4="Waterdrops",P21,IF($H$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="Y21" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Birds in Flight",H21,IF($I$4="Birds Perched",I21,IF($I$4="Fireworks",J21,IF($I$4="Landscape",K21,IF($I$4="Macro",L21,IF($I$4="People",M21,IF($I$4="Sports",N21,IF($I$4="Travel",O21,IF($I$4="Waterdrops",P21,IF($I$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="Z21" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Birds in Flight",H21,IF($J$4="Birds Perched",I21,IF($J$4="Fireworks",J21,IF($J$4="Landscape",K21,IF($J$4="Macro",L21,IF($J$4="People",M21,IF($J$4="Sports",N21,IF($J$4="Travel",O21,IF($J$4="Waterdrops",P21,IF($J$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Off / Off</x:v>
       </x:c>
       <x:c r="AA21" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Birds in Flight",H21,IF($K$4="Birds Perched",I21,IF($K$4="Fireworks",J21,IF($K$4="Landscape",K21,IF($K$4="Macro",L21,IF($K$4="People",M21,IF($K$4="Sports",N21,IF($K$4="Travel",O21,IF($K$4="Waterdrops",P21,IF($K$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="AB21" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Birds in Flight",H21,IF($L$4="Birds Perched",I21,IF($L$4="Fireworks",J21,IF($L$4="Landscape",K21,IF($L$4="Macro",L21,IF($L$4="People",M21,IF($L$4="Sports",N21,IF($L$4="Travel",O21,IF($L$4="Waterdrops",P21,IF($L$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="AC21" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Birds in Flight",H21,IF($M$4="Birds Perched",I21,IF($M$4="Fireworks",J21,IF($M$4="Landscape",K21,IF($M$4="Macro",L21,IF($M$4="People",M21,IF($M$4="Sports",N21,IF($M$4="Travel",O21,IF($M$4="Waterdrops",P21,IF($M$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="AD21" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Birds in Flight",H21,IF($N$4="Birds Perched",I21,IF($N$4="Fireworks",J21,IF($N$4="Landscape",K21,IF($N$4="Macro",L21,IF($N$4="People",M21,IF($N$4="Sports",N21,IF($N$4="Travel",O21,IF($N$4="Waterdrops",P21,IF($N$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="AE21" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Birds in Flight",H21,IF($O$4="Birds Perched",I21,IF($O$4="Fireworks",J21,IF($O$4="Landscape",K21,IF($O$4="Macro",L21,IF($O$4="People",M21,IF($O$4="Sports",N21,IF($O$4="Travel",O21,IF($O$4="Waterdrops",P21,IF($O$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="AF21" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Birds in Flight",H21,IF($P$4="Birds Perched",I21,IF($P$4="Fireworks",J21,IF($P$4="Landscape",K21,IF($P$4="Macro",L21,IF($P$4="People",M21,IF($P$4="Sports",N21,IF($P$4="Travel",O21,IF($P$4="Waterdrops",P21,IF($P$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Off / Off</x:v>
       </x:c>
       <x:c r="AG21" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Birds in Flight",H21,IF($Q$4="Birds Perched",I21,IF($Q$4="Fireworks",J21,IF($Q$4="Landscape",K21,IF($Q$4="Macro",L21,IF($Q$4="People",M21,IF($Q$4="Sports",N21,IF($Q$4="Travel",O21,IF($Q$4="Waterdrops",P21,IF($Q$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" hidden="0">
+      <x:c r="A22" s="12" t="str">
+        <x:v>Shooting 5 &gt; Focus bracketing</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>MM-SWITCH; MM-FOCUS*</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="H22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L22" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="N22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="O22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R22" s="20" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="S22" s="20" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="T22" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Birds in Flight",H22,IF($D$4="Birds Perched",I22,IF($D$4="Fireworks",J22,IF($D$4="Landscape",K22,IF($D$4="Macro",L22,IF($D$4="People",M22,IF($D$4="Sports",N22,IF($D$4="Travel",O22,IF($D$4="Waterdrops",P22,IF($D$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U22" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Birds in Flight",H22,IF($E$4="Birds Perched",I22,IF($E$4="Fireworks",J22,IF($E$4="Landscape",K22,IF($E$4="Macro",L22,IF($E$4="People",M22,IF($E$4="Sports",N22,IF($E$4="Travel",O22,IF($E$4="Waterdrops",P22,IF($E$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V22" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Birds in Flight",H22,IF($F$4="Birds Perched",I22,IF($F$4="Fireworks",J22,IF($F$4="Landscape",K22,IF($F$4="Macro",L22,IF($F$4="People",M22,IF($F$4="Sports",N22,IF($F$4="Travel",O22,IF($F$4="Waterdrops",P22,IF($F$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W22" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Birds in Flight",H22,IF($G$4="Birds Perched",I22,IF($G$4="Fireworks",J22,IF($G$4="Landscape",K22,IF($G$4="Macro",L22,IF($G$4="People",M22,IF($G$4="Sports",N22,IF($G$4="Travel",O22,IF($G$4="Waterdrops",P22,IF($G$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X22" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Birds in Flight",H22,IF($H$4="Birds Perched",I22,IF($H$4="Fireworks",J22,IF($H$4="Landscape",K22,IF($H$4="Macro",L22,IF($H$4="People",M22,IF($H$4="Sports",N22,IF($H$4="Travel",O22,IF($H$4="Waterdrops",P22,IF($H$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Y22" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Birds in Flight",H22,IF($I$4="Birds Perched",I22,IF($I$4="Fireworks",J22,IF($I$4="Landscape",K22,IF($I$4="Macro",L22,IF($I$4="People",M22,IF($I$4="Sports",N22,IF($I$4="Travel",O22,IF($I$4="Waterdrops",P22,IF($I$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z22" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Birds in Flight",H22,IF($J$4="Birds Perched",I22,IF($J$4="Fireworks",J22,IF($J$4="Landscape",K22,IF($J$4="Macro",L22,IF($J$4="People",M22,IF($J$4="Sports",N22,IF($J$4="Travel",O22,IF($J$4="Waterdrops",P22,IF($J$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AA22" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Birds in Flight",H22,IF($K$4="Birds Perched",I22,IF($K$4="Fireworks",J22,IF($K$4="Landscape",K22,IF($K$4="Macro",L22,IF($K$4="People",M22,IF($K$4="Sports",N22,IF($K$4="Travel",O22,IF($K$4="Waterdrops",P22,IF($K$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB22" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Birds in Flight",H22,IF($L$4="Birds Perched",I22,IF($L$4="Fireworks",J22,IF($L$4="Landscape",K22,IF($L$4="Macro",L22,IF($L$4="People",M22,IF($L$4="Sports",N22,IF($L$4="Travel",O22,IF($L$4="Waterdrops",P22,IF($L$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="AC22" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Birds in Flight",H22,IF($M$4="Birds Perched",I22,IF($M$4="Fireworks",J22,IF($M$4="Landscape",K22,IF($M$4="Macro",L22,IF($M$4="People",M22,IF($M$4="Sports",N22,IF($M$4="Travel",O22,IF($M$4="Waterdrops",P22,IF($M$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD22" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Birds in Flight",H22,IF($N$4="Birds Perched",I22,IF($N$4="Fireworks",J22,IF($N$4="Landscape",K22,IF($N$4="Macro",L22,IF($N$4="People",M22,IF($N$4="Sports",N22,IF($N$4="Travel",O22,IF($N$4="Waterdrops",P22,IF($N$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AE22" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Birds in Flight",H22,IF($O$4="Birds Perched",I22,IF($O$4="Fireworks",J22,IF($O$4="Landscape",K22,IF($O$4="Macro",L22,IF($O$4="People",M22,IF($O$4="Sports",N22,IF($O$4="Travel",O22,IF($O$4="Waterdrops",P22,IF($O$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AF22" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Birds in Flight",H22,IF($P$4="Birds Perched",I22,IF($P$4="Fireworks",J22,IF($P$4="Landscape",K22,IF($P$4="Macro",L22,IF($P$4="People",M22,IF($P$4="Sports",N22,IF($P$4="Travel",O22,IF($P$4="Waterdrops",P22,IF($P$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AG22" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Birds in Flight",H22,IF($Q$4="Birds Perched",I22,IF($Q$4="Fireworks",J22,IF($Q$4="Landscape",K22,IF($Q$4="Macro",L22,IF($Q$4="People",M22,IF($Q$4="Sports",N22,IF($Q$4="Travel",O22,IF($Q$4="Waterdrops",P22,IF($Q$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D7:D21">
+  <x:conditionalFormatting sqref="D7:D22">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <x:formula>$T7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E7:E21">
+  <x:conditionalFormatting sqref="E7:E22">
     <x:cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
       <x:formula>$U7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F7:F21">
+  <x:conditionalFormatting sqref="F7:F22">
     <x:cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
       <x:formula>$V7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G7:G21">
+  <x:conditionalFormatting sqref="G7:G22">
     <x:cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
       <x:formula>$W7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="H7:H21">
+  <x:conditionalFormatting sqref="H7:H22">
     <x:cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
       <x:formula>$X7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I7:I21">
+  <x:conditionalFormatting sqref="I7:I22">
     <x:cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
       <x:formula>$Y7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J7:J21">
+  <x:conditionalFormatting sqref="J7:J22">
     <x:cfRule type="cellIs" dxfId="6" priority="7" operator="notEqual">
       <x:formula>$Z7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K7:K21">
+  <x:conditionalFormatting sqref="K7:K22">
     <x:cfRule type="cellIs" dxfId="7" priority="8" operator="notEqual">
       <x:formula>$AA7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="L7:L21">
+  <x:conditionalFormatting sqref="L7:L22">
     <x:cfRule type="cellIs" dxfId="8" priority="9" operator="notEqual">
       <x:formula>$AB7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M7:M21">
+  <x:conditionalFormatting sqref="M7:M22">
     <x:cfRule type="cellIs" dxfId="9" priority="10" operator="notEqual">
       <x:formula>$AC7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N7:N21">
+  <x:conditionalFormatting sqref="N7:N22">
     <x:cfRule type="cellIs" dxfId="10" priority="11" operator="notEqual">
       <x:formula>$AD7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O7:O21">
+  <x:conditionalFormatting sqref="O7:O22">
     <x:cfRule type="cellIs" dxfId="11" priority="12" operator="notEqual">
       <x:formula>$AE7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="P7:P21">
+  <x:conditionalFormatting sqref="P7:P22">
     <x:cfRule type="cellIs" dxfId="12" priority="13" operator="notEqual">
       <x:formula>$AF7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Q7:Q21">
+  <x:conditionalFormatting sqref="Q7:Q22">
     <x:cfRule type="cellIs" dxfId="13" priority="14" operator="notEqual">
       <x:formula>$AG7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:Q21">
+  <x:conditionalFormatting sqref="D7:Q22">
     <x:cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Not Used"/>
     <x:cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <x:formula>"—"</x:formula>
@@ -2813,9 +2928,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R5e44913e262a4c25"/>
+  <x:drawing ns1:id="R79e7159db9ca4871"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rfe2e93c97412475f"/>
+    <x:tablePart ns1:id="R89c601264feb4c92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3086,183 +3201,209 @@
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11" s="15" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="B11" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="D11" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="T11" s="38" t="str">
         <x:f>B11</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="U11" s="38" t="str">
         <x:f>C11</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="V11" s="38" t="str">
         <x:f>D11</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="B12" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="C12" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="T12" s="38" t="str">
         <x:f>B12</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="U12" s="38" t="str">
         <x:f>C12</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="V12" s="38" t="str">
         <x:f>D12</x:f>
-        <x:v>None</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="T13" s="38" t="str">
         <x:f>B13</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="U13" s="38" t="str">
         <x:f>C13</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="V13" s="38" t="str">
         <x:f>D13</x:f>
-        <x:v>Disable</x:v>
+        <x:v>None</x:v>
       </x:c>
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="T14" s="38" t="str">
         <x:f>B14</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="U14" s="38" t="str">
         <x:f>C14</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V14" s="38" t="str">
         <x:f>D14</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Disable</x:v>
       </x:c>
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Drive</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="C15" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="T15" s="38" t="str">
         <x:f>B15</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="U15" s="38" t="str">
         <x:f>C15</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="V15" s="38" t="str">
         <x:f>D15</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Image Stabilization</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="C16" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="T16" s="38" t="str">
         <x:f>B16</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="U16" s="38" t="str">
         <x:f>C16</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 3</x:v>
       </x:c>
       <x:c r="V16" s="38" t="str">
         <x:f>D16</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Mode 1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="15" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>IBIS / Lens IS</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="T17" s="38" t="str">
         <x:f>B17</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="U17" s="38" t="str">
         <x:f>C17</x:f>
-        <x:v>Disable</x:v>
+        <x:v>On / On</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
         <x:f>D17</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" hidden="0">
+      <x:c r="A18" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="T18" s="38" t="str">
+        <x:f>B18</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U18" s="38" t="str">
+        <x:f>C18</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V18" s="38" t="str">
+        <x:f>D18</x:f>
         <x:v>Disable</x:v>
       </x:c>
     </x:row>
@@ -3270,24 +3411,24 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="B3:B17">
+  <x:conditionalFormatting sqref="B3:B18">
     <x:cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
       <x:formula>$T3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C3:C17">
+  <x:conditionalFormatting sqref="C3:C18">
     <x:cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
       <x:formula>$U3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D3:D17">
+  <x:conditionalFormatting sqref="D3:D18">
     <x:cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
       <x:formula>$V3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R4d2ccdd858164261"/>
+    <x:tablePart ns1:id="Rd35bcf722d10420f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R3fdcf251db024281"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R02723b7cd57d4c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R91b3e431b9e444b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R6d041c6ad3c0481b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="b60ca0eb-0b7a-4823-87e2-9dbc97009bd9"/>
+        <xdr:cNvPr id="1" name="646283c4-0ec3-4e01-8dc0-89e33c3f8925"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf80b1f0f983941cc"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc056bdc970214e17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -453,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:S22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:S26"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="Menu Location"/>
     <x:tableColumn id="2" name="Best or Quick Access"/>
@@ -481,8 +481,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A2:D18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A2:D22"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Setting"/>
     <x:tableColumn id="2" name="C1 Wildlife"/>
@@ -846,7 +846,7 @@
         <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="G5" s="37" t="str">
-        <x:v>Camera defaults</x:v>
+        <x:v>Camera Defaults + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="H5" s="37" t="str">
         <x:v>C2 Birds in Flight + AF Case</x:v>
@@ -1587,8 +1587,8 @@
       <x:c r="O12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="P12" s="17" t="n">
-        <x:v>100</x:v>
+      <x:c r="P12" s="17" t="str">
+        <x:v>100-400</x:v>
       </x:c>
       <x:c r="Q12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
@@ -1647,9 +1647,9 @@
         <x:f>IF($O$4="C1 Wildlife",D12,IF($O$4="C2 Birds in Flight",E12,IF($O$4="C3 Landscape",F12,IF($O$4="Default Settings",G12,IF($O$4="Birds in Flight",H12,IF($O$4="Birds Perched",I12,IF($O$4="Fireworks",J12,IF($O$4="Landscape",K12,IF($O$4="Macro",L12,IF($O$4="People",M12,IF($O$4="Sports",N12,IF($O$4="Travel",O12,IF($O$4="Waterdrops",P12,IF($O$4="Wildlife",Q12,""))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="AF12" s="38" t="n">
+      <x:c r="AF12" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D12,IF($P$4="C2 Birds in Flight",E12,IF($P$4="C3 Landscape",F12,IF($P$4="Default Settings",G12,IF($P$4="Birds in Flight",H12,IF($P$4="Birds Perched",I12,IF($P$4="Fireworks",J12,IF($P$4="Landscape",K12,IF($P$4="Macro",L12,IF($P$4="People",M12,IF($P$4="Sports",N12,IF($P$4="Travel",O12,IF($P$4="Waterdrops",P12,IF($P$4="Wildlife",Q12,""))))))))))))))</x:f>
-        <x:v>100</x:v>
+        <x:v>100-400</x:v>
       </x:c>
       <x:c r="AG12" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D12,IF($Q$4="C2 Birds in Flight",E12,IF($Q$4="C3 Landscape",F12,IF($Q$4="Default Settings",G12,IF($Q$4="Birds in Flight",H12,IF($Q$4="Birds Perched",I12,IF($Q$4="Fireworks",J12,IF($Q$4="Landscape",K12,IF($Q$4="Macro",L12,IF($Q$4="People",M12,IF($Q$4="Sports",N12,IF($Q$4="Travel",O12,IF($Q$4="Waterdrops",P12,IF($Q$4="Wildlife",Q12,""))))))))))))))</x:f>
@@ -1897,7 +1897,7 @@
         <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="E15" s="17" t="str">
         <x:v>Case 4</x:v>
@@ -1912,7 +1912,7 @@
         <x:v>Case 4</x:v>
       </x:c>
       <x:c r="I15" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="J15" s="17" t="str">
         <x:v>Not Used</x:v>
@@ -1927,7 +1927,7 @@
         <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="N15" s="17" t="str">
-        <x:v>Case 4</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="O15" s="17" t="str">
         <x:v>Case A (Auto)</x:v>
@@ -1936,7 +1936,7 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q15" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="R15" s="20" t="n">
         <x:v>9</x:v>
@@ -1946,7 +1946,7 @@
       </x:c>
       <x:c r="T15" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Birds in Flight",H15,IF($D$4="Birds Perched",I15,IF($D$4="Fireworks",J15,IF($D$4="Landscape",K15,IF($D$4="Macro",L15,IF($D$4="People",M15,IF($D$4="Sports",N15,IF($D$4="Travel",O15,IF($D$4="Waterdrops",P15,IF($D$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="U15" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Birds in Flight",H15,IF($E$4="Birds Perched",I15,IF($E$4="Fireworks",J15,IF($E$4="Landscape",K15,IF($E$4="Macro",L15,IF($E$4="People",M15,IF($E$4="Sports",N15,IF($E$4="Travel",O15,IF($E$4="Waterdrops",P15,IF($E$4="Wildlife",Q15,""))))))))))))))</x:f>
@@ -1966,7 +1966,7 @@
       </x:c>
       <x:c r="Y15" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Birds in Flight",H15,IF($I$4="Birds Perched",I15,IF($I$4="Fireworks",J15,IF($I$4="Landscape",K15,IF($I$4="Macro",L15,IF($I$4="People",M15,IF($I$4="Sports",N15,IF($I$4="Travel",O15,IF($I$4="Waterdrops",P15,IF($I$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="Z15" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Birds in Flight",H15,IF($J$4="Birds Perched",I15,IF($J$4="Fireworks",J15,IF($J$4="Landscape",K15,IF($J$4="Macro",L15,IF($J$4="People",M15,IF($J$4="Sports",N15,IF($J$4="Travel",O15,IF($J$4="Waterdrops",P15,IF($J$4="Wildlife",Q15,""))))))))))))))</x:f>
@@ -1986,7 +1986,7 @@
       </x:c>
       <x:c r="AD15" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Birds in Flight",H15,IF($N$4="Birds Perched",I15,IF($N$4="Fireworks",J15,IF($N$4="Landscape",K15,IF($N$4="Macro",L15,IF($N$4="People",M15,IF($N$4="Sports",N15,IF($N$4="Travel",O15,IF($N$4="Waterdrops",P15,IF($N$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 4</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="AE15" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Birds in Flight",H15,IF($O$4="Birds Perched",I15,IF($O$4="Fireworks",J15,IF($O$4="Landscape",K15,IF($O$4="Macro",L15,IF($O$4="People",M15,IF($O$4="Sports",N15,IF($O$4="Travel",O15,IF($O$4="Waterdrops",P15,IF($O$4="Wildlife",Q15,""))))))))))))))</x:f>
@@ -1998,90 +1998,90 @@
       </x:c>
       <x:c r="AG15" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Birds in Flight",H15,IF($Q$4="Birds Perched",I15,IF($Q$4="Fireworks",J15,IF($Q$4="Landscape",K15,IF($Q$4="Macro",L15,IF($Q$4="People",M15,IF($Q$4="Sports",N15,IF($Q$4="Travel",O15,IF($Q$4="Waterdrops",P15,IF($Q$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="12" t="str">
-        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Tracking Sensitivity; AF3 &gt; Servo AF characteristics</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>AF Point Selection button + Main Dial</x:v>
+        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>AF Method</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Tracking Sensitivity</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="H16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="I16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="J16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L16" s="17" t="str">
-        <x:v>Spot AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="N16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="O16" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="P16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="Q16" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+      <x:c r="Q16" s="17" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="R16" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="S16" s="20" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="T16" s="38" t="str">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="T16" s="38" t="n">
         <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Birds in Flight",H16,IF($D$4="Birds Perched",I16,IF($D$4="Fireworks",J16,IF($D$4="Landscape",K16,IF($D$4="Macro",L16,IF($D$4="People",M16,IF($D$4="Sports",N16,IF($D$4="Travel",O16,IF($D$4="Waterdrops",P16,IF($D$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="U16" s="38" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="U16" s="38" t="n">
         <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Birds in Flight",H16,IF($E$4="Birds Perched",I16,IF($E$4="Fireworks",J16,IF($E$4="Landscape",K16,IF($E$4="Macro",L16,IF($E$4="People",M16,IF($E$4="Sports",N16,IF($E$4="Travel",O16,IF($E$4="Waterdrops",P16,IF($E$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V16" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Birds in Flight",H16,IF($F$4="Birds Perched",I16,IF($F$4="Fireworks",J16,IF($F$4="Landscape",K16,IF($F$4="Macro",L16,IF($F$4="People",M16,IF($F$4="Sports",N16,IF($F$4="Travel",O16,IF($F$4="Waterdrops",P16,IF($F$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W16" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Birds in Flight",H16,IF($G$4="Birds Perched",I16,IF($G$4="Fireworks",J16,IF($G$4="Landscape",K16,IF($G$4="Macro",L16,IF($G$4="People",M16,IF($G$4="Sports",N16,IF($G$4="Travel",O16,IF($G$4="Waterdrops",P16,IF($G$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="X16" s="38" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X16" s="38" t="n">
         <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Birds in Flight",H16,IF($H$4="Birds Perched",I16,IF($H$4="Fireworks",J16,IF($H$4="Landscape",K16,IF($H$4="Macro",L16,IF($H$4="People",M16,IF($H$4="Sports",N16,IF($H$4="Travel",O16,IF($H$4="Waterdrops",P16,IF($H$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="Y16" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y16" s="38" t="n">
         <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Birds in Flight",H16,IF($I$4="Birds Perched",I16,IF($I$4="Fireworks",J16,IF($I$4="Landscape",K16,IF($I$4="Macro",L16,IF($I$4="People",M16,IF($I$4="Sports",N16,IF($I$4="Travel",O16,IF($I$4="Waterdrops",P16,IF($I$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="Z16" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Birds in Flight",H16,IF($J$4="Birds Perched",I16,IF($J$4="Fireworks",J16,IF($J$4="Landscape",K16,IF($J$4="Macro",L16,IF($J$4="People",M16,IF($J$4="Sports",N16,IF($J$4="Travel",O16,IF($J$4="Waterdrops",P16,IF($J$4="Wildlife",Q16,""))))))))))))))</x:f>
@@ -2089,114 +2089,114 @@
       </x:c>
       <x:c r="AA16" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Birds in Flight",H16,IF($K$4="Birds Perched",I16,IF($K$4="Fireworks",J16,IF($K$4="Landscape",K16,IF($K$4="Macro",L16,IF($K$4="People",M16,IF($K$4="Sports",N16,IF($K$4="Travel",O16,IF($K$4="Waterdrops",P16,IF($K$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB16" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Birds in Flight",H16,IF($L$4="Birds Perched",I16,IF($L$4="Fireworks",J16,IF($L$4="Landscape",K16,IF($L$4="Macro",L16,IF($L$4="People",M16,IF($L$4="Sports",N16,IF($L$4="Travel",O16,IF($L$4="Waterdrops",P16,IF($L$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Spot AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC16" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Birds in Flight",H16,IF($M$4="Birds Perched",I16,IF($M$4="Fireworks",J16,IF($M$4="Landscape",K16,IF($M$4="Macro",L16,IF($M$4="People",M16,IF($M$4="Sports",N16,IF($M$4="Travel",O16,IF($M$4="Waterdrops",P16,IF($M$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="AD16" s="38" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AD16" s="38" t="n">
         <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Birds in Flight",H16,IF($N$4="Birds Perched",I16,IF($N$4="Fireworks",J16,IF($N$4="Landscape",K16,IF($N$4="Macro",L16,IF($N$4="People",M16,IF($N$4="Sports",N16,IF($N$4="Travel",O16,IF($N$4="Waterdrops",P16,IF($N$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="AE16" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Birds in Flight",H16,IF($O$4="Birds Perched",I16,IF($O$4="Fireworks",J16,IF($O$4="Landscape",K16,IF($O$4="Macro",L16,IF($O$4="People",M16,IF($O$4="Sports",N16,IF($O$4="Travel",O16,IF($O$4="Waterdrops",P16,IF($O$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="AF16" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Birds in Flight",H16,IF($P$4="Birds Perched",I16,IF($P$4="Fireworks",J16,IF($P$4="Landscape",K16,IF($P$4="Macro",L16,IF($P$4="People",M16,IF($P$4="Sports",N16,IF($P$4="Travel",O16,IF($P$4="Waterdrops",P16,IF($P$4="Wildlife",Q16,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="AG16" s="38" t="str">
+      <x:c r="AG16" s="38" t="n">
         <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Birds in Flight",H16,IF($Q$4="Birds Perched",I16,IF($Q$4="Fireworks",J16,IF($Q$4="Landscape",K16,IF($Q$4="Macro",L16,IF($Q$4="People",M16,IF($Q$4="Sports",N16,IF($Q$4="Travel",O16,IF($Q$4="Waterdrops",P16,IF($Q$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>-1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="12" t="str">
-        <x:v>AF1 &gt; Subject to detect</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Accel./Decel. tracking; AF3 &gt; Servo AF characteristics</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>MM-SWITCH</x:v>
+        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="F17" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L17" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M17" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="O17" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="P17" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q17" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="R17" s="20" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="S17" s="20" t="n">
-        <x:v>220</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="T17" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Birds in Flight",H17,IF($D$4="Birds Perched",I17,IF($D$4="Fireworks",J17,IF($D$4="Landscape",K17,IF($D$4="Macro",L17,IF($D$4="People",M17,IF($D$4="Sports",N17,IF($D$4="Travel",O17,IF($D$4="Waterdrops",P17,IF($D$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="U17" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Birds in Flight",H17,IF($E$4="Birds Perched",I17,IF($E$4="Fireworks",J17,IF($E$4="Landscape",K17,IF($E$4="Macro",L17,IF($E$4="People",M17,IF($E$4="Sports",N17,IF($E$4="Travel",O17,IF($E$4="Waterdrops",P17,IF($E$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Birds in Flight",H17,IF($F$4="Birds Perched",I17,IF($F$4="Fireworks",J17,IF($F$4="Landscape",K17,IF($F$4="Macro",L17,IF($F$4="People",M17,IF($F$4="Sports",N17,IF($F$4="Travel",O17,IF($F$4="Waterdrops",P17,IF($F$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W17" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Birds in Flight",H17,IF($G$4="Birds Perched",I17,IF($G$4="Fireworks",J17,IF($G$4="Landscape",K17,IF($G$4="Macro",L17,IF($G$4="People",M17,IF($G$4="Sports",N17,IF($G$4="Travel",O17,IF($G$4="Waterdrops",P17,IF($G$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="X17" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Birds in Flight",H17,IF($H$4="Birds Perched",I17,IF($H$4="Fireworks",J17,IF($H$4="Landscape",K17,IF($H$4="Macro",L17,IF($H$4="People",M17,IF($H$4="Sports",N17,IF($H$4="Travel",O17,IF($H$4="Waterdrops",P17,IF($H$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="Y17" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Birds in Flight",H17,IF($I$4="Birds Perched",I17,IF($I$4="Fireworks",J17,IF($I$4="Landscape",K17,IF($I$4="Macro",L17,IF($I$4="People",M17,IF($I$4="Sports",N17,IF($I$4="Travel",O17,IF($I$4="Waterdrops",P17,IF($I$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="Z17" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Birds in Flight",H17,IF($J$4="Birds Perched",I17,IF($J$4="Fireworks",J17,IF($J$4="Landscape",K17,IF($J$4="Macro",L17,IF($J$4="People",M17,IF($J$4="Sports",N17,IF($J$4="Travel",O17,IF($J$4="Waterdrops",P17,IF($J$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2204,23 +2204,23 @@
       </x:c>
       <x:c r="AA17" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Birds in Flight",H17,IF($K$4="Birds Perched",I17,IF($K$4="Fireworks",J17,IF($K$4="Landscape",K17,IF($K$4="Macro",L17,IF($K$4="People",M17,IF($K$4="Sports",N17,IF($K$4="Travel",O17,IF($K$4="Waterdrops",P17,IF($K$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB17" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Birds in Flight",H17,IF($L$4="Birds Perched",I17,IF($L$4="Fireworks",J17,IF($L$4="Landscape",K17,IF($L$4="Macro",L17,IF($L$4="People",M17,IF($L$4="Sports",N17,IF($L$4="Travel",O17,IF($L$4="Waterdrops",P17,IF($L$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC17" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Birds in Flight",H17,IF($M$4="Birds Perched",I17,IF($M$4="Fireworks",J17,IF($M$4="Landscape",K17,IF($M$4="Macro",L17,IF($M$4="People",M17,IF($M$4="Sports",N17,IF($M$4="Travel",O17,IF($M$4="Waterdrops",P17,IF($M$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="AD17" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Birds in Flight",H17,IF($N$4="Birds Perched",I17,IF($N$4="Fireworks",J17,IF($N$4="Landscape",K17,IF($N$4="Macro",L17,IF($N$4="People",M17,IF($N$4="Sports",N17,IF($N$4="Travel",O17,IF($N$4="Waterdrops",P17,IF($N$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="AE17" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Birds in Flight",H17,IF($O$4="Birds Perched",I17,IF($O$4="Fireworks",J17,IF($O$4="Landscape",K17,IF($O$4="Macro",L17,IF($O$4="People",M17,IF($O$4="Sports",N17,IF($O$4="Travel",O17,IF($O$4="Waterdrops",P17,IF($O$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="AF17" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Birds in Flight",H17,IF($P$4="Birds Perched",I17,IF($P$4="Fireworks",J17,IF($P$4="Landscape",K17,IF($P$4="Macro",L17,IF($P$4="People",M17,IF($P$4="Sports",N17,IF($P$4="Travel",O17,IF($P$4="Waterdrops",P17,IF($P$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2228,90 +2228,90 @@
       </x:c>
       <x:c r="AG17" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Birds in Flight",H17,IF($Q$4="Birds Perched",I17,IF($Q$4="Fireworks",J17,IF($Q$4="Landscape",K17,IF($Q$4="Macro",L17,IF($Q$4="People",M17,IF($Q$4="Sports",N17,IF($Q$4="Travel",O17,IF($Q$4="Waterdrops",P17,IF($Q$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="12" t="str">
-        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Switching tracked subjects; AF4 &gt; Switching tracked subjects</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>SET button</x:v>
+        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="E18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="F18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="H18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="I18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="O18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="P18" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q18" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="R18" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="S18" s="20" t="n">
-        <x:v>150</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="T18" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Birds in Flight",H18,IF($D$4="Birds Perched",I18,IF($D$4="Fireworks",J18,IF($D$4="Landscape",K18,IF($D$4="Macro",L18,IF($D$4="People",M18,IF($D$4="Sports",N18,IF($D$4="Travel",O18,IF($D$4="Waterdrops",P18,IF($D$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="U18" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Birds in Flight",H18,IF($E$4="Birds Perched",I18,IF($E$4="Fireworks",J18,IF($E$4="Landscape",K18,IF($E$4="Macro",L18,IF($E$4="People",M18,IF($E$4="Sports",N18,IF($E$4="Travel",O18,IF($E$4="Waterdrops",P18,IF($E$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="V18" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Birds in Flight",H18,IF($F$4="Birds Perched",I18,IF($F$4="Fireworks",J18,IF($F$4="Landscape",K18,IF($F$4="Macro",L18,IF($F$4="People",M18,IF($F$4="Sports",N18,IF($F$4="Travel",O18,IF($F$4="Waterdrops",P18,IF($F$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W18" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Birds in Flight",H18,IF($G$4="Birds Perched",I18,IF($G$4="Fireworks",J18,IF($G$4="Landscape",K18,IF($G$4="Macro",L18,IF($G$4="People",M18,IF($G$4="Sports",N18,IF($G$4="Travel",O18,IF($G$4="Waterdrops",P18,IF($G$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="X18" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Birds in Flight",H18,IF($H$4="Birds Perched",I18,IF($H$4="Fireworks",J18,IF($H$4="Landscape",K18,IF($H$4="Macro",L18,IF($H$4="People",M18,IF($H$4="Sports",N18,IF($H$4="Travel",O18,IF($H$4="Waterdrops",P18,IF($H$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="Y18" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Birds in Flight",H18,IF($I$4="Birds Perched",I18,IF($I$4="Fireworks",J18,IF($I$4="Landscape",K18,IF($I$4="Macro",L18,IF($I$4="People",M18,IF($I$4="Sports",N18,IF($I$4="Travel",O18,IF($I$4="Waterdrops",P18,IF($I$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="Z18" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Birds in Flight",H18,IF($J$4="Birds Perched",I18,IF($J$4="Fireworks",J18,IF($J$4="Landscape",K18,IF($J$4="Macro",L18,IF($J$4="People",M18,IF($J$4="Sports",N18,IF($J$4="Travel",O18,IF($J$4="Waterdrops",P18,IF($J$4="Wildlife",Q18,""))))))))))))))</x:f>
@@ -2319,23 +2319,23 @@
       </x:c>
       <x:c r="AA18" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Birds in Flight",H18,IF($K$4="Birds Perched",I18,IF($K$4="Fireworks",J18,IF($K$4="Landscape",K18,IF($K$4="Macro",L18,IF($K$4="People",M18,IF($K$4="Sports",N18,IF($K$4="Travel",O18,IF($K$4="Waterdrops",P18,IF($K$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB18" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Birds in Flight",H18,IF($L$4="Birds Perched",I18,IF($L$4="Fireworks",J18,IF($L$4="Landscape",K18,IF($L$4="Macro",L18,IF($L$4="People",M18,IF($L$4="Sports",N18,IF($L$4="Travel",O18,IF($L$4="Waterdrops",P18,IF($L$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC18" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Birds in Flight",H18,IF($M$4="Birds Perched",I18,IF($M$4="Fireworks",J18,IF($M$4="Landscape",K18,IF($M$4="Macro",L18,IF($M$4="People",M18,IF($M$4="Sports",N18,IF($M$4="Travel",O18,IF($M$4="Waterdrops",P18,IF($M$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="AD18" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Birds in Flight",H18,IF($N$4="Birds Perched",I18,IF($N$4="Fireworks",J18,IF($N$4="Landscape",K18,IF($N$4="Macro",L18,IF($N$4="People",M18,IF($N$4="Sports",N18,IF($N$4="Travel",O18,IF($N$4="Waterdrops",P18,IF($N$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="AE18" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Birds in Flight",H18,IF($O$4="Birds Perched",I18,IF($O$4="Fireworks",J18,IF($O$4="Landscape",K18,IF($O$4="Macro",L18,IF($O$4="People",M18,IF($O$4="Sports",N18,IF($O$4="Travel",O18,IF($O$4="Waterdrops",P18,IF($O$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AF18" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Birds in Flight",H18,IF($P$4="Birds Perched",I18,IF($P$4="Fireworks",J18,IF($P$4="Landscape",K18,IF($P$4="Macro",L18,IF($P$4="People",M18,IF($P$4="Sports",N18,IF($P$4="Travel",O18,IF($P$4="Waterdrops",P18,IF($P$4="Wildlife",Q18,""))))))))))))))</x:f>
@@ -2343,541 +2343,1001 @@
       </x:c>
       <x:c r="AG18" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Birds in Flight",H18,IF($Q$4="Birds Perched",I18,IF($Q$4="Fireworks",J18,IF($Q$4="Landscape",K18,IF($Q$4="Macro",L18,IF($Q$4="People",M18,IF($Q$4="Sports",N18,IF($Q$4="Travel",O18,IF($Q$4="Waterdrops",P18,IF($Q$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="12" t="str">
-        <x:v>Shooting menu &gt; Drive mode</x:v>
+        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>AF Point Selection button + Main Dial</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="E19" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="F19" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="G19" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="L19" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="M19" s="17" t="str">
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="O19" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="P19" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q19" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="R19" s="20" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="S19" s="20" t="n">
-        <x:v>160</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="T19" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Birds in Flight",H19,IF($D$4="Birds Perched",I19,IF($D$4="Fireworks",J19,IF($D$4="Landscape",K19,IF($D$4="Macro",L19,IF($D$4="People",M19,IF($D$4="Sports",N19,IF($D$4="Travel",O19,IF($D$4="Waterdrops",P19,IF($D$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="U19" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Birds in Flight",H19,IF($E$4="Birds Perched",I19,IF($E$4="Fireworks",J19,IF($E$4="Landscape",K19,IF($E$4="Macro",L19,IF($E$4="People",M19,IF($E$4="Sports",N19,IF($E$4="Travel",O19,IF($E$4="Waterdrops",P19,IF($E$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="V19" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Birds in Flight",H19,IF($F$4="Birds Perched",I19,IF($F$4="Fireworks",J19,IF($F$4="Landscape",K19,IF($F$4="Macro",L19,IF($F$4="People",M19,IF($F$4="Sports",N19,IF($F$4="Travel",O19,IF($F$4="Waterdrops",P19,IF($F$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="W19" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Birds in Flight",H19,IF($G$4="Birds Perched",I19,IF($G$4="Fireworks",J19,IF($G$4="Landscape",K19,IF($G$4="Macro",L19,IF($G$4="People",M19,IF($G$4="Sports",N19,IF($G$4="Travel",O19,IF($G$4="Waterdrops",P19,IF($G$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="X19" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Birds in Flight",H19,IF($H$4="Birds Perched",I19,IF($H$4="Fireworks",J19,IF($H$4="Landscape",K19,IF($H$4="Macro",L19,IF($H$4="People",M19,IF($H$4="Sports",N19,IF($H$4="Travel",O19,IF($H$4="Waterdrops",P19,IF($H$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Y19" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Birds in Flight",H19,IF($I$4="Birds Perched",I19,IF($I$4="Fireworks",J19,IF($I$4="Landscape",K19,IF($I$4="Macro",L19,IF($I$4="People",M19,IF($I$4="Sports",N19,IF($I$4="Travel",O19,IF($I$4="Waterdrops",P19,IF($I$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Z19" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Birds in Flight",H19,IF($J$4="Birds Perched",I19,IF($J$4="Fireworks",J19,IF($J$4="Landscape",K19,IF($J$4="Macro",L19,IF($J$4="People",M19,IF($J$4="Sports",N19,IF($J$4="Travel",O19,IF($J$4="Waterdrops",P19,IF($J$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AA19" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Birds in Flight",H19,IF($K$4="Birds Perched",I19,IF($K$4="Fireworks",J19,IF($K$4="Landscape",K19,IF($K$4="Macro",L19,IF($K$4="People",M19,IF($K$4="Sports",N19,IF($K$4="Travel",O19,IF($K$4="Waterdrops",P19,IF($K$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="AB19" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Birds in Flight",H19,IF($L$4="Birds Perched",I19,IF($L$4="Fireworks",J19,IF($L$4="Landscape",K19,IF($L$4="Macro",L19,IF($L$4="People",M19,IF($L$4="Sports",N19,IF($L$4="Travel",O19,IF($L$4="Waterdrops",P19,IF($L$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="AC19" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Birds in Flight",H19,IF($M$4="Birds Perched",I19,IF($M$4="Fireworks",J19,IF($M$4="Landscape",K19,IF($M$4="Macro",L19,IF($M$4="People",M19,IF($M$4="Sports",N19,IF($M$4="Travel",O19,IF($M$4="Waterdrops",P19,IF($M$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="AD19" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Birds in Flight",H19,IF($N$4="Birds Perched",I19,IF($N$4="Fireworks",J19,IF($N$4="Landscape",K19,IF($N$4="Macro",L19,IF($N$4="People",M19,IF($N$4="Sports",N19,IF($N$4="Travel",O19,IF($N$4="Waterdrops",P19,IF($N$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="AE19" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Birds in Flight",H19,IF($O$4="Birds Perched",I19,IF($O$4="Fireworks",J19,IF($O$4="Landscape",K19,IF($O$4="Macro",L19,IF($O$4="People",M19,IF($O$4="Sports",N19,IF($O$4="Travel",O19,IF($O$4="Waterdrops",P19,IF($O$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="AF19" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Birds in Flight",H19,IF($P$4="Birds Perched",I19,IF($P$4="Fireworks",J19,IF($P$4="Landscape",K19,IF($P$4="Macro",L19,IF($P$4="People",M19,IF($P$4="Sports",N19,IF($P$4="Travel",O19,IF($P$4="Waterdrops",P19,IF($P$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG19" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Birds in Flight",H19,IF($Q$4="Birds Perched",I19,IF($Q$4="Fireworks",J19,IF($Q$4="Landscape",K19,IF($Q$4="Macro",L19,IF($Q$4="People",M19,IF($Q$4="Sports",N19,IF($Q$4="Travel",O19,IF($Q$4="Waterdrops",P19,IF($Q$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
+        <x:v>AF1 &gt; Subject to detect</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
+        <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="E20" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="F20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="L20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="M20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="N20" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="O20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="P20" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="R20" s="20" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="S20" s="20" t="n">
-        <x:v>230</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="T20" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Birds in Flight",H20,IF($D$4="Birds Perched",I20,IF($D$4="Fireworks",J20,IF($D$4="Landscape",K20,IF($D$4="Macro",L20,IF($D$4="People",M20,IF($D$4="Sports",N20,IF($D$4="Travel",O20,IF($D$4="Waterdrops",P20,IF($D$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="U20" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Birds in Flight",H20,IF($E$4="Birds Perched",I20,IF($E$4="Fireworks",J20,IF($E$4="Landscape",K20,IF($E$4="Macro",L20,IF($E$4="People",M20,IF($E$4="Sports",N20,IF($E$4="Travel",O20,IF($E$4="Waterdrops",P20,IF($E$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="V20" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Birds in Flight",H20,IF($F$4="Birds Perched",I20,IF($F$4="Fireworks",J20,IF($F$4="Landscape",K20,IF($F$4="Macro",L20,IF($F$4="People",M20,IF($F$4="Sports",N20,IF($F$4="Travel",O20,IF($F$4="Waterdrops",P20,IF($F$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="W20" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Birds in Flight",H20,IF($G$4="Birds Perched",I20,IF($G$4="Fireworks",J20,IF($G$4="Landscape",K20,IF($G$4="Macro",L20,IF($G$4="People",M20,IF($G$4="Sports",N20,IF($G$4="Travel",O20,IF($G$4="Waterdrops",P20,IF($G$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="X20" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Birds in Flight",H20,IF($H$4="Birds Perched",I20,IF($H$4="Fireworks",J20,IF($H$4="Landscape",K20,IF($H$4="Macro",L20,IF($H$4="People",M20,IF($H$4="Sports",N20,IF($H$4="Travel",O20,IF($H$4="Waterdrops",P20,IF($H$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Y20" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Birds in Flight",H20,IF($I$4="Birds Perched",I20,IF($I$4="Fireworks",J20,IF($I$4="Landscape",K20,IF($I$4="Macro",L20,IF($I$4="People",M20,IF($I$4="Sports",N20,IF($I$4="Travel",O20,IF($I$4="Waterdrops",P20,IF($I$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Z20" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Birds in Flight",H20,IF($J$4="Birds Perched",I20,IF($J$4="Fireworks",J20,IF($J$4="Landscape",K20,IF($J$4="Macro",L20,IF($J$4="People",M20,IF($J$4="Sports",N20,IF($J$4="Travel",O20,IF($J$4="Waterdrops",P20,IF($J$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AA20" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Birds in Flight",H20,IF($K$4="Birds Perched",I20,IF($K$4="Fireworks",J20,IF($K$4="Landscape",K20,IF($K$4="Macro",L20,IF($K$4="People",M20,IF($K$4="Sports",N20,IF($K$4="Travel",O20,IF($K$4="Waterdrops",P20,IF($K$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AB20" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Birds in Flight",H20,IF($L$4="Birds Perched",I20,IF($L$4="Fireworks",J20,IF($L$4="Landscape",K20,IF($L$4="Macro",L20,IF($L$4="People",M20,IF($L$4="Sports",N20,IF($L$4="Travel",O20,IF($L$4="Waterdrops",P20,IF($L$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AC20" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Birds in Flight",H20,IF($M$4="Birds Perched",I20,IF($M$4="Fireworks",J20,IF($M$4="Landscape",K20,IF($M$4="Macro",L20,IF($M$4="People",M20,IF($M$4="Sports",N20,IF($M$4="Travel",O20,IF($M$4="Waterdrops",P20,IF($M$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="AD20" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Birds in Flight",H20,IF($N$4="Birds Perched",I20,IF($N$4="Fireworks",J20,IF($N$4="Landscape",K20,IF($N$4="Macro",L20,IF($N$4="People",M20,IF($N$4="Sports",N20,IF($N$4="Travel",O20,IF($N$4="Waterdrops",P20,IF($N$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="AE20" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Birds in Flight",H20,IF($O$4="Birds Perched",I20,IF($O$4="Fireworks",J20,IF($O$4="Landscape",K20,IF($O$4="Macro",L20,IF($O$4="People",M20,IF($O$4="Sports",N20,IF($O$4="Travel",O20,IF($O$4="Waterdrops",P20,IF($O$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AF20" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Birds in Flight",H20,IF($P$4="Birds Perched",I20,IF($P$4="Fireworks",J20,IF($P$4="Landscape",K20,IF($P$4="Macro",L20,IF($P$4="People",M20,IF($P$4="Sports",N20,IF($P$4="Travel",O20,IF($P$4="Waterdrops",P20,IF($P$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG20" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Birds in Flight",H20,IF($Q$4="Birds Perched",I20,IF($Q$4="Fireworks",J20,IF($Q$4="Landscape",K20,IF($Q$4="Macro",L20,IF($Q$4="People",M20,IF($Q$4="Sports",N20,IF($Q$4="Travel",O20,IF($Q$4="Waterdrops",P20,IF($Q$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>Lens IS switch; camera IS menu when available</x:v>
+        <x:v>SET button</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="E21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="F21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="G21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="L21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="M21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="N21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="O21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="P21" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="R21" s="20" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="S21" s="20" t="n">
-        <x:v>40</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="T21" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Birds in Flight",H21,IF($D$4="Birds Perched",I21,IF($D$4="Fireworks",J21,IF($D$4="Landscape",K21,IF($D$4="Macro",L21,IF($D$4="People",M21,IF($D$4="Sports",N21,IF($D$4="Travel",O21,IF($D$4="Waterdrops",P21,IF($D$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="U21" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Birds in Flight",H21,IF($E$4="Birds Perched",I21,IF($E$4="Fireworks",J21,IF($E$4="Landscape",K21,IF($E$4="Macro",L21,IF($E$4="People",M21,IF($E$4="Sports",N21,IF($E$4="Travel",O21,IF($E$4="Waterdrops",P21,IF($E$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V21" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Birds in Flight",H21,IF($F$4="Birds Perched",I21,IF($F$4="Fireworks",J21,IF($F$4="Landscape",K21,IF($F$4="Macro",L21,IF($F$4="People",M21,IF($F$4="Sports",N21,IF($F$4="Travel",O21,IF($F$4="Waterdrops",P21,IF($F$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="W21" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Birds in Flight",H21,IF($G$4="Birds Perched",I21,IF($G$4="Fireworks",J21,IF($G$4="Landscape",K21,IF($G$4="Macro",L21,IF($G$4="People",M21,IF($G$4="Sports",N21,IF($G$4="Travel",O21,IF($G$4="Waterdrops",P21,IF($G$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="X21" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Birds in Flight",H21,IF($H$4="Birds Perched",I21,IF($H$4="Fireworks",J21,IF($H$4="Landscape",K21,IF($H$4="Macro",L21,IF($H$4="People",M21,IF($H$4="Sports",N21,IF($H$4="Travel",O21,IF($H$4="Waterdrops",P21,IF($H$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Y21" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Birds in Flight",H21,IF($I$4="Birds Perched",I21,IF($I$4="Fireworks",J21,IF($I$4="Landscape",K21,IF($I$4="Macro",L21,IF($I$4="People",M21,IF($I$4="Sports",N21,IF($I$4="Travel",O21,IF($I$4="Waterdrops",P21,IF($I$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Z21" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Birds in Flight",H21,IF($J$4="Birds Perched",I21,IF($J$4="Fireworks",J21,IF($J$4="Landscape",K21,IF($J$4="Macro",L21,IF($J$4="People",M21,IF($J$4="Sports",N21,IF($J$4="Travel",O21,IF($J$4="Waterdrops",P21,IF($J$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AA21" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Birds in Flight",H21,IF($K$4="Birds Perched",I21,IF($K$4="Fireworks",J21,IF($K$4="Landscape",K21,IF($K$4="Macro",L21,IF($K$4="People",M21,IF($K$4="Sports",N21,IF($K$4="Travel",O21,IF($K$4="Waterdrops",P21,IF($K$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AB21" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Birds in Flight",H21,IF($L$4="Birds Perched",I21,IF($L$4="Fireworks",J21,IF($L$4="Landscape",K21,IF($L$4="Macro",L21,IF($L$4="People",M21,IF($L$4="Sports",N21,IF($L$4="Travel",O21,IF($L$4="Waterdrops",P21,IF($L$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AC21" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Birds in Flight",H21,IF($M$4="Birds Perched",I21,IF($M$4="Fireworks",J21,IF($M$4="Landscape",K21,IF($M$4="Macro",L21,IF($M$4="People",M21,IF($M$4="Sports",N21,IF($M$4="Travel",O21,IF($M$4="Waterdrops",P21,IF($M$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AD21" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Birds in Flight",H21,IF($N$4="Birds Perched",I21,IF($N$4="Fireworks",J21,IF($N$4="Landscape",K21,IF($N$4="Macro",L21,IF($N$4="People",M21,IF($N$4="Sports",N21,IF($N$4="Travel",O21,IF($N$4="Waterdrops",P21,IF($N$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AE21" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Birds in Flight",H21,IF($O$4="Birds Perched",I21,IF($O$4="Fireworks",J21,IF($O$4="Landscape",K21,IF($O$4="Macro",L21,IF($O$4="People",M21,IF($O$4="Sports",N21,IF($O$4="Travel",O21,IF($O$4="Waterdrops",P21,IF($O$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AF21" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Birds in Flight",H21,IF($P$4="Birds Perched",I21,IF($P$4="Fireworks",J21,IF($P$4="Landscape",K21,IF($P$4="Macro",L21,IF($P$4="People",M21,IF($P$4="Sports",N21,IF($P$4="Travel",O21,IF($P$4="Waterdrops",P21,IF($P$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG21" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Birds in Flight",H21,IF($Q$4="Birds Perched",I21,IF($Q$4="Fireworks",J21,IF($Q$4="Landscape",K21,IF($Q$4="Macro",L21,IF($Q$4="People",M21,IF($Q$4="Sports",N21,IF($Q$4="Travel",O21,IF($Q$4="Waterdrops",P21,IF($Q$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="22" hidden="0">
       <x:c r="A22" s="12" t="str">
-        <x:v>Shooting 5 &gt; Focus bracketing</x:v>
+        <x:v>Shooting menu &gt; Drive mode</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C22" s="15" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>Drive</x:v>
       </x:c>
       <x:c r="D22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="E22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="F22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="G22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="H22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="I22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="J22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="L22" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="M22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Low Speed Continuous</x:v>
       </x:c>
       <x:c r="N22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="O22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="P22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="Q22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="R22" s="20" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="S22" s="20" t="n">
-        <x:v>240</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="T22" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Birds in Flight",H22,IF($D$4="Birds Perched",I22,IF($D$4="Fireworks",J22,IF($D$4="Landscape",K22,IF($D$4="Macro",L22,IF($D$4="People",M22,IF($D$4="Sports",N22,IF($D$4="Travel",O22,IF($D$4="Waterdrops",P22,IF($D$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="U22" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Birds in Flight",H22,IF($E$4="Birds Perched",I22,IF($E$4="Fireworks",J22,IF($E$4="Landscape",K22,IF($E$4="Macro",L22,IF($E$4="People",M22,IF($E$4="Sports",N22,IF($E$4="Travel",O22,IF($E$4="Waterdrops",P22,IF($E$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="V22" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Birds in Flight",H22,IF($F$4="Birds Perched",I22,IF($F$4="Fireworks",J22,IF($F$4="Landscape",K22,IF($F$4="Macro",L22,IF($F$4="People",M22,IF($F$4="Sports",N22,IF($F$4="Travel",O22,IF($F$4="Waterdrops",P22,IF($F$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="W22" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Birds in Flight",H22,IF($G$4="Birds Perched",I22,IF($G$4="Fireworks",J22,IF($G$4="Landscape",K22,IF($G$4="Macro",L22,IF($G$4="People",M22,IF($G$4="Sports",N22,IF($G$4="Travel",O22,IF($G$4="Waterdrops",P22,IF($G$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="X22" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Birds in Flight",H22,IF($H$4="Birds Perched",I22,IF($H$4="Fireworks",J22,IF($H$4="Landscape",K22,IF($H$4="Macro",L22,IF($H$4="People",M22,IF($H$4="Sports",N22,IF($H$4="Travel",O22,IF($H$4="Waterdrops",P22,IF($H$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="Y22" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Birds in Flight",H22,IF($I$4="Birds Perched",I22,IF($I$4="Fireworks",J22,IF($I$4="Landscape",K22,IF($I$4="Macro",L22,IF($I$4="People",M22,IF($I$4="Sports",N22,IF($I$4="Travel",O22,IF($I$4="Waterdrops",P22,IF($I$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="Z22" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Birds in Flight",H22,IF($J$4="Birds Perched",I22,IF($J$4="Fireworks",J22,IF($J$4="Landscape",K22,IF($J$4="Macro",L22,IF($J$4="People",M22,IF($J$4="Sports",N22,IF($J$4="Travel",O22,IF($J$4="Waterdrops",P22,IF($J$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AA22" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Birds in Flight",H22,IF($K$4="Birds Perched",I22,IF($K$4="Fireworks",J22,IF($K$4="Landscape",K22,IF($K$4="Macro",L22,IF($K$4="People",M22,IF($K$4="Sports",N22,IF($K$4="Travel",O22,IF($K$4="Waterdrops",P22,IF($K$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AB22" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Birds in Flight",H22,IF($L$4="Birds Perched",I22,IF($L$4="Fireworks",J22,IF($L$4="Landscape",K22,IF($L$4="Macro",L22,IF($L$4="People",M22,IF($L$4="Sports",N22,IF($L$4="Travel",O22,IF($L$4="Waterdrops",P22,IF($L$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AC22" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Birds in Flight",H22,IF($M$4="Birds Perched",I22,IF($M$4="Fireworks",J22,IF($M$4="Landscape",K22,IF($M$4="Macro",L22,IF($M$4="People",M22,IF($M$4="Sports",N22,IF($M$4="Travel",O22,IF($M$4="Waterdrops",P22,IF($M$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Low Speed Continuous</x:v>
       </x:c>
       <x:c r="AD22" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Birds in Flight",H22,IF($N$4="Birds Perched",I22,IF($N$4="Fireworks",J22,IF($N$4="Landscape",K22,IF($N$4="Macro",L22,IF($N$4="People",M22,IF($N$4="Sports",N22,IF($N$4="Travel",O22,IF($N$4="Waterdrops",P22,IF($N$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="AE22" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Birds in Flight",H22,IF($O$4="Birds Perched",I22,IF($O$4="Fireworks",J22,IF($O$4="Landscape",K22,IF($O$4="Macro",L22,IF($O$4="People",M22,IF($O$4="Sports",N22,IF($O$4="Travel",O22,IF($O$4="Waterdrops",P22,IF($O$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AF22" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Birds in Flight",H22,IF($P$4="Birds Perched",I22,IF($P$4="Fireworks",J22,IF($P$4="Landscape",K22,IF($P$4="Macro",L22,IF($P$4="People",M22,IF($P$4="Sports",N22,IF($P$4="Travel",O22,IF($P$4="Waterdrops",P22,IF($P$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="AG22" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Birds in Flight",H22,IF($Q$4="Birds Perched",I22,IF($Q$4="Fireworks",J22,IF($Q$4="Landscape",K22,IF($Q$4="Macro",L22,IF($Q$4="People",M22,IF($Q$4="Sports",N22,IF($Q$4="Travel",O22,IF($Q$4="Waterdrops",P22,IF($Q$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" hidden="0">
+      <x:c r="A23" s="12" t="str">
+        <x:v>Shooting 7 &gt; High speed display</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>Set once; C1-C3 registered profile</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="str">
+        <x:v>High Speed Display</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="H23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="I23" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="N23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="O23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="P23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q23" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="R23" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="S23" s="20" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="T23" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D23,IF($D$4="C2 Birds in Flight",E23,IF($D$4="C3 Landscape",F23,IF($D$4="Default Settings",G23,IF($D$4="Birds in Flight",H23,IF($D$4="Birds Perched",I23,IF($D$4="Fireworks",J23,IF($D$4="Landscape",K23,IF($D$4="Macro",L23,IF($D$4="People",M23,IF($D$4="Sports",N23,IF($D$4="Travel",O23,IF($D$4="Waterdrops",P23,IF($D$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="U23" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D23,IF($E$4="C2 Birds in Flight",E23,IF($E$4="C3 Landscape",F23,IF($E$4="Default Settings",G23,IF($E$4="Birds in Flight",H23,IF($E$4="Birds Perched",I23,IF($E$4="Fireworks",J23,IF($E$4="Landscape",K23,IF($E$4="Macro",L23,IF($E$4="People",M23,IF($E$4="Sports",N23,IF($E$4="Travel",O23,IF($E$4="Waterdrops",P23,IF($E$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="V23" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D23,IF($F$4="C2 Birds in Flight",E23,IF($F$4="C3 Landscape",F23,IF($F$4="Default Settings",G23,IF($F$4="Birds in Flight",H23,IF($F$4="Birds Perched",I23,IF($F$4="Fireworks",J23,IF($F$4="Landscape",K23,IF($F$4="Macro",L23,IF($F$4="People",M23,IF($F$4="Sports",N23,IF($F$4="Travel",O23,IF($F$4="Waterdrops",P23,IF($F$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W23" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D23,IF($G$4="C2 Birds in Flight",E23,IF($G$4="C3 Landscape",F23,IF($G$4="Default Settings",G23,IF($G$4="Birds in Flight",H23,IF($G$4="Birds Perched",I23,IF($G$4="Fireworks",J23,IF($G$4="Landscape",K23,IF($G$4="Macro",L23,IF($G$4="People",M23,IF($G$4="Sports",N23,IF($G$4="Travel",O23,IF($G$4="Waterdrops",P23,IF($G$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="X23" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D23,IF($H$4="C2 Birds in Flight",E23,IF($H$4="C3 Landscape",F23,IF($H$4="Default Settings",G23,IF($H$4="Birds in Flight",H23,IF($H$4="Birds Perched",I23,IF($H$4="Fireworks",J23,IF($H$4="Landscape",K23,IF($H$4="Macro",L23,IF($H$4="People",M23,IF($H$4="Sports",N23,IF($H$4="Travel",O23,IF($H$4="Waterdrops",P23,IF($H$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Y23" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D23,IF($I$4="C2 Birds in Flight",E23,IF($I$4="C3 Landscape",F23,IF($I$4="Default Settings",G23,IF($I$4="Birds in Flight",H23,IF($I$4="Birds Perched",I23,IF($I$4="Fireworks",J23,IF($I$4="Landscape",K23,IF($I$4="Macro",L23,IF($I$4="People",M23,IF($I$4="Sports",N23,IF($I$4="Travel",O23,IF($I$4="Waterdrops",P23,IF($I$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="Z23" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D23,IF($J$4="C2 Birds in Flight",E23,IF($J$4="C3 Landscape",F23,IF($J$4="Default Settings",G23,IF($J$4="Birds in Flight",H23,IF($J$4="Birds Perched",I23,IF($J$4="Fireworks",J23,IF($J$4="Landscape",K23,IF($J$4="Macro",L23,IF($J$4="People",M23,IF($J$4="Sports",N23,IF($J$4="Travel",O23,IF($J$4="Waterdrops",P23,IF($J$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA23" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D23,IF($K$4="C2 Birds in Flight",E23,IF($K$4="C3 Landscape",F23,IF($K$4="Default Settings",G23,IF($K$4="Birds in Flight",H23,IF($K$4="Birds Perched",I23,IF($K$4="Fireworks",J23,IF($K$4="Landscape",K23,IF($K$4="Macro",L23,IF($K$4="People",M23,IF($K$4="Sports",N23,IF($K$4="Travel",O23,IF($K$4="Waterdrops",P23,IF($K$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AB23" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D23,IF($L$4="C2 Birds in Flight",E23,IF($L$4="C3 Landscape",F23,IF($L$4="Default Settings",G23,IF($L$4="Birds in Flight",H23,IF($L$4="Birds Perched",I23,IF($L$4="Fireworks",J23,IF($L$4="Landscape",K23,IF($L$4="Macro",L23,IF($L$4="People",M23,IF($L$4="Sports",N23,IF($L$4="Travel",O23,IF($L$4="Waterdrops",P23,IF($L$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC23" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D23,IF($M$4="C2 Birds in Flight",E23,IF($M$4="C3 Landscape",F23,IF($M$4="Default Settings",G23,IF($M$4="Birds in Flight",H23,IF($M$4="Birds Perched",I23,IF($M$4="Fireworks",J23,IF($M$4="Landscape",K23,IF($M$4="Macro",L23,IF($M$4="People",M23,IF($M$4="Sports",N23,IF($M$4="Travel",O23,IF($M$4="Waterdrops",P23,IF($M$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AD23" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D23,IF($N$4="C2 Birds in Flight",E23,IF($N$4="C3 Landscape",F23,IF($N$4="Default Settings",G23,IF($N$4="Birds in Flight",H23,IF($N$4="Birds Perched",I23,IF($N$4="Fireworks",J23,IF($N$4="Landscape",K23,IF($N$4="Macro",L23,IF($N$4="People",M23,IF($N$4="Sports",N23,IF($N$4="Travel",O23,IF($N$4="Waterdrops",P23,IF($N$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AE23" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D23,IF($O$4="C2 Birds in Flight",E23,IF($O$4="C3 Landscape",F23,IF($O$4="Default Settings",G23,IF($O$4="Birds in Flight",H23,IF($O$4="Birds Perched",I23,IF($O$4="Fireworks",J23,IF($O$4="Landscape",K23,IF($O$4="Macro",L23,IF($O$4="People",M23,IF($O$4="Sports",N23,IF($O$4="Travel",O23,IF($O$4="Waterdrops",P23,IF($O$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AF23" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D23,IF($P$4="C2 Birds in Flight",E23,IF($P$4="C3 Landscape",F23,IF($P$4="Default Settings",G23,IF($P$4="Birds in Flight",H23,IF($P$4="Birds Perched",I23,IF($P$4="Fireworks",J23,IF($P$4="Landscape",K23,IF($P$4="Macro",L23,IF($P$4="People",M23,IF($P$4="Sports",N23,IF($P$4="Travel",O23,IF($P$4="Waterdrops",P23,IF($P$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AG23" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D23,IF($Q$4="C2 Birds in Flight",E23,IF($Q$4="C3 Landscape",F23,IF($Q$4="Default Settings",G23,IF($Q$4="Birds in Flight",H23,IF($Q$4="Birds Perched",I23,IF($Q$4="Fireworks",J23,IF($Q$4="Landscape",K23,IF($Q$4="Macro",L23,IF($Q$4="People",M23,IF($Q$4="Sports",N23,IF($Q$4="Travel",O23,IF($Q$4="Waterdrops",P23,IF($Q$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" hidden="0">
+      <x:c r="A24" s="12" t="str">
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="str">
+        <x:v>Image Stabilization</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="H24" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="L24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="N24" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="O24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="P24" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="R24" s="20" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="S24" s="20" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="T24" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D24,IF($D$4="C2 Birds in Flight",E24,IF($D$4="C3 Landscape",F24,IF($D$4="Default Settings",G24,IF($D$4="Birds in Flight",H24,IF($D$4="Birds Perched",I24,IF($D$4="Fireworks",J24,IF($D$4="Landscape",K24,IF($D$4="Macro",L24,IF($D$4="People",M24,IF($D$4="Sports",N24,IF($D$4="Travel",O24,IF($D$4="Waterdrops",P24,IF($D$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U24" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D24,IF($E$4="C2 Birds in Flight",E24,IF($E$4="C3 Landscape",F24,IF($E$4="Default Settings",G24,IF($E$4="Birds in Flight",H24,IF($E$4="Birds Perched",I24,IF($E$4="Fireworks",J24,IF($E$4="Landscape",K24,IF($E$4="Macro",L24,IF($E$4="People",M24,IF($E$4="Sports",N24,IF($E$4="Travel",O24,IF($E$4="Waterdrops",P24,IF($E$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="V24" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D24,IF($F$4="C2 Birds in Flight",E24,IF($F$4="C3 Landscape",F24,IF($F$4="Default Settings",G24,IF($F$4="Birds in Flight",H24,IF($F$4="Birds Perched",I24,IF($F$4="Fireworks",J24,IF($F$4="Landscape",K24,IF($F$4="Macro",L24,IF($F$4="People",M24,IF($F$4="Sports",N24,IF($F$4="Travel",O24,IF($F$4="Waterdrops",P24,IF($F$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="W24" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D24,IF($G$4="C2 Birds in Flight",E24,IF($G$4="C3 Landscape",F24,IF($G$4="Default Settings",G24,IF($G$4="Birds in Flight",H24,IF($G$4="Birds Perched",I24,IF($G$4="Fireworks",J24,IF($G$4="Landscape",K24,IF($G$4="Macro",L24,IF($G$4="People",M24,IF($G$4="Sports",N24,IF($G$4="Travel",O24,IF($G$4="Waterdrops",P24,IF($G$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="X24" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D24,IF($H$4="C2 Birds in Flight",E24,IF($H$4="C3 Landscape",F24,IF($H$4="Default Settings",G24,IF($H$4="Birds in Flight",H24,IF($H$4="Birds Perched",I24,IF($H$4="Fireworks",J24,IF($H$4="Landscape",K24,IF($H$4="Macro",L24,IF($H$4="People",M24,IF($H$4="Sports",N24,IF($H$4="Travel",O24,IF($H$4="Waterdrops",P24,IF($H$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="Y24" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D24,IF($I$4="C2 Birds in Flight",E24,IF($I$4="C3 Landscape",F24,IF($I$4="Default Settings",G24,IF($I$4="Birds in Flight",H24,IF($I$4="Birds Perched",I24,IF($I$4="Fireworks",J24,IF($I$4="Landscape",K24,IF($I$4="Macro",L24,IF($I$4="People",M24,IF($I$4="Sports",N24,IF($I$4="Travel",O24,IF($I$4="Waterdrops",P24,IF($I$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Z24" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D24,IF($J$4="C2 Birds in Flight",E24,IF($J$4="C3 Landscape",F24,IF($J$4="Default Settings",G24,IF($J$4="Birds in Flight",H24,IF($J$4="Birds Perched",I24,IF($J$4="Fireworks",J24,IF($J$4="Landscape",K24,IF($J$4="Macro",L24,IF($J$4="People",M24,IF($J$4="Sports",N24,IF($J$4="Travel",O24,IF($J$4="Waterdrops",P24,IF($J$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA24" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D24,IF($K$4="C2 Birds in Flight",E24,IF($K$4="C3 Landscape",F24,IF($K$4="Default Settings",G24,IF($K$4="Birds in Flight",H24,IF($K$4="Birds Perched",I24,IF($K$4="Fireworks",J24,IF($K$4="Landscape",K24,IF($K$4="Macro",L24,IF($K$4="People",M24,IF($K$4="Sports",N24,IF($K$4="Travel",O24,IF($K$4="Waterdrops",P24,IF($K$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AB24" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D24,IF($L$4="C2 Birds in Flight",E24,IF($L$4="C3 Landscape",F24,IF($L$4="Default Settings",G24,IF($L$4="Birds in Flight",H24,IF($L$4="Birds Perched",I24,IF($L$4="Fireworks",J24,IF($L$4="Landscape",K24,IF($L$4="Macro",L24,IF($L$4="People",M24,IF($L$4="Sports",N24,IF($L$4="Travel",O24,IF($L$4="Waterdrops",P24,IF($L$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AC24" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D24,IF($M$4="C2 Birds in Flight",E24,IF($M$4="C3 Landscape",F24,IF($M$4="Default Settings",G24,IF($M$4="Birds in Flight",H24,IF($M$4="Birds Perched",I24,IF($M$4="Fireworks",J24,IF($M$4="Landscape",K24,IF($M$4="Macro",L24,IF($M$4="People",M24,IF($M$4="Sports",N24,IF($M$4="Travel",O24,IF($M$4="Waterdrops",P24,IF($M$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AD24" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D24,IF($N$4="C2 Birds in Flight",E24,IF($N$4="C3 Landscape",F24,IF($N$4="Default Settings",G24,IF($N$4="Birds in Flight",H24,IF($N$4="Birds Perched",I24,IF($N$4="Fireworks",J24,IF($N$4="Landscape",K24,IF($N$4="Macro",L24,IF($N$4="People",M24,IF($N$4="Sports",N24,IF($N$4="Travel",O24,IF($N$4="Waterdrops",P24,IF($N$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="AE24" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D24,IF($O$4="C2 Birds in Flight",E24,IF($O$4="C3 Landscape",F24,IF($O$4="Default Settings",G24,IF($O$4="Birds in Flight",H24,IF($O$4="Birds Perched",I24,IF($O$4="Fireworks",J24,IF($O$4="Landscape",K24,IF($O$4="Macro",L24,IF($O$4="People",M24,IF($O$4="Sports",N24,IF($O$4="Travel",O24,IF($O$4="Waterdrops",P24,IF($O$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AF24" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D24,IF($P$4="C2 Birds in Flight",E24,IF($P$4="C3 Landscape",F24,IF($P$4="Default Settings",G24,IF($P$4="Birds in Flight",H24,IF($P$4="Birds Perched",I24,IF($P$4="Fireworks",J24,IF($P$4="Landscape",K24,IF($P$4="Macro",L24,IF($P$4="People",M24,IF($P$4="Sports",N24,IF($P$4="Travel",O24,IF($P$4="Waterdrops",P24,IF($P$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG24" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D24,IF($Q$4="C2 Birds in Flight",E24,IF($Q$4="C3 Landscape",F24,IF($Q$4="Default Settings",G24,IF($Q$4="Birds in Flight",H24,IF($Q$4="Birds Perched",I24,IF($Q$4="Fireworks",J24,IF($Q$4="Landscape",K24,IF($Q$4="Macro",L24,IF($Q$4="People",M24,IF($Q$4="Sports",N24,IF($Q$4="Travel",O24,IF($Q$4="Waterdrops",P24,IF($Q$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" hidden="0">
+      <x:c r="A25" s="12" t="str">
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>Lens IS switch; camera IS menu when available</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="str">
+        <x:v>IBIS / Lens IS</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="H25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="I25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="J25" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="L25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="M25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="N25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="O25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="P25" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="Q25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="R25" s="20" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="S25" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="T25" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D25,IF($D$4="C2 Birds in Flight",E25,IF($D$4="C3 Landscape",F25,IF($D$4="Default Settings",G25,IF($D$4="Birds in Flight",H25,IF($D$4="Birds Perched",I25,IF($D$4="Fireworks",J25,IF($D$4="Landscape",K25,IF($D$4="Macro",L25,IF($D$4="People",M25,IF($D$4="Sports",N25,IF($D$4="Travel",O25,IF($D$4="Waterdrops",P25,IF($D$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U25" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D25,IF($E$4="C2 Birds in Flight",E25,IF($E$4="C3 Landscape",F25,IF($E$4="Default Settings",G25,IF($E$4="Birds in Flight",H25,IF($E$4="Birds Perched",I25,IF($E$4="Fireworks",J25,IF($E$4="Landscape",K25,IF($E$4="Macro",L25,IF($E$4="People",M25,IF($E$4="Sports",N25,IF($E$4="Travel",O25,IF($E$4="Waterdrops",P25,IF($E$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V25" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D25,IF($F$4="C2 Birds in Flight",E25,IF($F$4="C3 Landscape",F25,IF($F$4="Default Settings",G25,IF($F$4="Birds in Flight",H25,IF($F$4="Birds Perched",I25,IF($F$4="Fireworks",J25,IF($F$4="Landscape",K25,IF($F$4="Macro",L25,IF($F$4="People",M25,IF($F$4="Sports",N25,IF($F$4="Travel",O25,IF($F$4="Waterdrops",P25,IF($F$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="W25" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D25,IF($G$4="C2 Birds in Flight",E25,IF($G$4="C3 Landscape",F25,IF($G$4="Default Settings",G25,IF($G$4="Birds in Flight",H25,IF($G$4="Birds Perched",I25,IF($G$4="Fireworks",J25,IF($G$4="Landscape",K25,IF($G$4="Macro",L25,IF($G$4="People",M25,IF($G$4="Sports",N25,IF($G$4="Travel",O25,IF($G$4="Waterdrops",P25,IF($G$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="X25" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D25,IF($H$4="C2 Birds in Flight",E25,IF($H$4="C3 Landscape",F25,IF($H$4="Default Settings",G25,IF($H$4="Birds in Flight",H25,IF($H$4="Birds Perched",I25,IF($H$4="Fireworks",J25,IF($H$4="Landscape",K25,IF($H$4="Macro",L25,IF($H$4="People",M25,IF($H$4="Sports",N25,IF($H$4="Travel",O25,IF($H$4="Waterdrops",P25,IF($H$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Y25" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D25,IF($I$4="C2 Birds in Flight",E25,IF($I$4="C3 Landscape",F25,IF($I$4="Default Settings",G25,IF($I$4="Birds in Flight",H25,IF($I$4="Birds Perched",I25,IF($I$4="Fireworks",J25,IF($I$4="Landscape",K25,IF($I$4="Macro",L25,IF($I$4="People",M25,IF($I$4="Sports",N25,IF($I$4="Travel",O25,IF($I$4="Waterdrops",P25,IF($I$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Z25" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D25,IF($J$4="C2 Birds in Flight",E25,IF($J$4="C3 Landscape",F25,IF($J$4="Default Settings",G25,IF($J$4="Birds in Flight",H25,IF($J$4="Birds Perched",I25,IF($J$4="Fireworks",J25,IF($J$4="Landscape",K25,IF($J$4="Macro",L25,IF($J$4="People",M25,IF($J$4="Sports",N25,IF($J$4="Travel",O25,IF($J$4="Waterdrops",P25,IF($J$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="AA25" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D25,IF($K$4="C2 Birds in Flight",E25,IF($K$4="C3 Landscape",F25,IF($K$4="Default Settings",G25,IF($K$4="Birds in Flight",H25,IF($K$4="Birds Perched",I25,IF($K$4="Fireworks",J25,IF($K$4="Landscape",K25,IF($K$4="Macro",L25,IF($K$4="People",M25,IF($K$4="Sports",N25,IF($K$4="Travel",O25,IF($K$4="Waterdrops",P25,IF($K$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AB25" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D25,IF($L$4="C2 Birds in Flight",E25,IF($L$4="C3 Landscape",F25,IF($L$4="Default Settings",G25,IF($L$4="Birds in Flight",H25,IF($L$4="Birds Perched",I25,IF($L$4="Fireworks",J25,IF($L$4="Landscape",K25,IF($L$4="Macro",L25,IF($L$4="People",M25,IF($L$4="Sports",N25,IF($L$4="Travel",O25,IF($L$4="Waterdrops",P25,IF($L$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AC25" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D25,IF($M$4="C2 Birds in Flight",E25,IF($M$4="C3 Landscape",F25,IF($M$4="Default Settings",G25,IF($M$4="Birds in Flight",H25,IF($M$4="Birds Perched",I25,IF($M$4="Fireworks",J25,IF($M$4="Landscape",K25,IF($M$4="Macro",L25,IF($M$4="People",M25,IF($M$4="Sports",N25,IF($M$4="Travel",O25,IF($M$4="Waterdrops",P25,IF($M$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AD25" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D25,IF($N$4="C2 Birds in Flight",E25,IF($N$4="C3 Landscape",F25,IF($N$4="Default Settings",G25,IF($N$4="Birds in Flight",H25,IF($N$4="Birds Perched",I25,IF($N$4="Fireworks",J25,IF($N$4="Landscape",K25,IF($N$4="Macro",L25,IF($N$4="People",M25,IF($N$4="Sports",N25,IF($N$4="Travel",O25,IF($N$4="Waterdrops",P25,IF($N$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AE25" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D25,IF($O$4="C2 Birds in Flight",E25,IF($O$4="C3 Landscape",F25,IF($O$4="Default Settings",G25,IF($O$4="Birds in Flight",H25,IF($O$4="Birds Perched",I25,IF($O$4="Fireworks",J25,IF($O$4="Landscape",K25,IF($O$4="Macro",L25,IF($O$4="People",M25,IF($O$4="Sports",N25,IF($O$4="Travel",O25,IF($O$4="Waterdrops",P25,IF($O$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AF25" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D25,IF($P$4="C2 Birds in Flight",E25,IF($P$4="C3 Landscape",F25,IF($P$4="Default Settings",G25,IF($P$4="Birds in Flight",H25,IF($P$4="Birds Perched",I25,IF($P$4="Fireworks",J25,IF($P$4="Landscape",K25,IF($P$4="Macro",L25,IF($P$4="People",M25,IF($P$4="Sports",N25,IF($P$4="Travel",O25,IF($P$4="Waterdrops",P25,IF($P$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="AG25" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D25,IF($Q$4="C2 Birds in Flight",E25,IF($Q$4="C3 Landscape",F25,IF($Q$4="Default Settings",G25,IF($Q$4="Birds in Flight",H25,IF($Q$4="Birds Perched",I25,IF($Q$4="Fireworks",J25,IF($Q$4="Landscape",K25,IF($Q$4="Macro",L25,IF($Q$4="People",M25,IF($Q$4="Sports",N25,IF($Q$4="Travel",O25,IF($Q$4="Waterdrops",P25,IF($Q$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" hidden="0">
+      <x:c r="A26" s="12" t="str">
+        <x:v>Shooting 5 &gt; Focus bracketing</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>MM-SWITCH; MM-FOCUS*</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="H26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="I26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L26" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="N26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="O26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R26" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="S26" s="20" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="T26" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D26,IF($D$4="C2 Birds in Flight",E26,IF($D$4="C3 Landscape",F26,IF($D$4="Default Settings",G26,IF($D$4="Birds in Flight",H26,IF($D$4="Birds Perched",I26,IF($D$4="Fireworks",J26,IF($D$4="Landscape",K26,IF($D$4="Macro",L26,IF($D$4="People",M26,IF($D$4="Sports",N26,IF($D$4="Travel",O26,IF($D$4="Waterdrops",P26,IF($D$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U26" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D26,IF($E$4="C2 Birds in Flight",E26,IF($E$4="C3 Landscape",F26,IF($E$4="Default Settings",G26,IF($E$4="Birds in Flight",H26,IF($E$4="Birds Perched",I26,IF($E$4="Fireworks",J26,IF($E$4="Landscape",K26,IF($E$4="Macro",L26,IF($E$4="People",M26,IF($E$4="Sports",N26,IF($E$4="Travel",O26,IF($E$4="Waterdrops",P26,IF($E$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V26" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D26,IF($F$4="C2 Birds in Flight",E26,IF($F$4="C3 Landscape",F26,IF($F$4="Default Settings",G26,IF($F$4="Birds in Flight",H26,IF($F$4="Birds Perched",I26,IF($F$4="Fireworks",J26,IF($F$4="Landscape",K26,IF($F$4="Macro",L26,IF($F$4="People",M26,IF($F$4="Sports",N26,IF($F$4="Travel",O26,IF($F$4="Waterdrops",P26,IF($F$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W26" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D26,IF($G$4="C2 Birds in Flight",E26,IF($G$4="C3 Landscape",F26,IF($G$4="Default Settings",G26,IF($G$4="Birds in Flight",H26,IF($G$4="Birds Perched",I26,IF($G$4="Fireworks",J26,IF($G$4="Landscape",K26,IF($G$4="Macro",L26,IF($G$4="People",M26,IF($G$4="Sports",N26,IF($G$4="Travel",O26,IF($G$4="Waterdrops",P26,IF($G$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X26" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D26,IF($H$4="C2 Birds in Flight",E26,IF($H$4="C3 Landscape",F26,IF($H$4="Default Settings",G26,IF($H$4="Birds in Flight",H26,IF($H$4="Birds Perched",I26,IF($H$4="Fireworks",J26,IF($H$4="Landscape",K26,IF($H$4="Macro",L26,IF($H$4="People",M26,IF($H$4="Sports",N26,IF($H$4="Travel",O26,IF($H$4="Waterdrops",P26,IF($H$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Y26" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D26,IF($I$4="C2 Birds in Flight",E26,IF($I$4="C3 Landscape",F26,IF($I$4="Default Settings",G26,IF($I$4="Birds in Flight",H26,IF($I$4="Birds Perched",I26,IF($I$4="Fireworks",J26,IF($I$4="Landscape",K26,IF($I$4="Macro",L26,IF($I$4="People",M26,IF($I$4="Sports",N26,IF($I$4="Travel",O26,IF($I$4="Waterdrops",P26,IF($I$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z26" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D26,IF($J$4="C2 Birds in Flight",E26,IF($J$4="C3 Landscape",F26,IF($J$4="Default Settings",G26,IF($J$4="Birds in Flight",H26,IF($J$4="Birds Perched",I26,IF($J$4="Fireworks",J26,IF($J$4="Landscape",K26,IF($J$4="Macro",L26,IF($J$4="People",M26,IF($J$4="Sports",N26,IF($J$4="Travel",O26,IF($J$4="Waterdrops",P26,IF($J$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AA26" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D26,IF($K$4="C2 Birds in Flight",E26,IF($K$4="C3 Landscape",F26,IF($K$4="Default Settings",G26,IF($K$4="Birds in Flight",H26,IF($K$4="Birds Perched",I26,IF($K$4="Fireworks",J26,IF($K$4="Landscape",K26,IF($K$4="Macro",L26,IF($K$4="People",M26,IF($K$4="Sports",N26,IF($K$4="Travel",O26,IF($K$4="Waterdrops",P26,IF($K$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB26" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D26,IF($L$4="C2 Birds in Flight",E26,IF($L$4="C3 Landscape",F26,IF($L$4="Default Settings",G26,IF($L$4="Birds in Flight",H26,IF($L$4="Birds Perched",I26,IF($L$4="Fireworks",J26,IF($L$4="Landscape",K26,IF($L$4="Macro",L26,IF($L$4="People",M26,IF($L$4="Sports",N26,IF($L$4="Travel",O26,IF($L$4="Waterdrops",P26,IF($L$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="AC26" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D26,IF($M$4="C2 Birds in Flight",E26,IF($M$4="C3 Landscape",F26,IF($M$4="Default Settings",G26,IF($M$4="Birds in Flight",H26,IF($M$4="Birds Perched",I26,IF($M$4="Fireworks",J26,IF($M$4="Landscape",K26,IF($M$4="Macro",L26,IF($M$4="People",M26,IF($M$4="Sports",N26,IF($M$4="Travel",O26,IF($M$4="Waterdrops",P26,IF($M$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD26" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D26,IF($N$4="C2 Birds in Flight",E26,IF($N$4="C3 Landscape",F26,IF($N$4="Default Settings",G26,IF($N$4="Birds in Flight",H26,IF($N$4="Birds Perched",I26,IF($N$4="Fireworks",J26,IF($N$4="Landscape",K26,IF($N$4="Macro",L26,IF($N$4="People",M26,IF($N$4="Sports",N26,IF($N$4="Travel",O26,IF($N$4="Waterdrops",P26,IF($N$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AE26" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D26,IF($O$4="C2 Birds in Flight",E26,IF($O$4="C3 Landscape",F26,IF($O$4="Default Settings",G26,IF($O$4="Birds in Flight",H26,IF($O$4="Birds Perched",I26,IF($O$4="Fireworks",J26,IF($O$4="Landscape",K26,IF($O$4="Macro",L26,IF($O$4="People",M26,IF($O$4="Sports",N26,IF($O$4="Travel",O26,IF($O$4="Waterdrops",P26,IF($O$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AF26" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D26,IF($P$4="C2 Birds in Flight",E26,IF($P$4="C3 Landscape",F26,IF($P$4="Default Settings",G26,IF($P$4="Birds in Flight",H26,IF($P$4="Birds Perched",I26,IF($P$4="Fireworks",J26,IF($P$4="Landscape",K26,IF($P$4="Macro",L26,IF($P$4="People",M26,IF($P$4="Sports",N26,IF($P$4="Travel",O26,IF($P$4="Waterdrops",P26,IF($P$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AG26" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D26,IF($Q$4="C2 Birds in Flight",E26,IF($Q$4="C3 Landscape",F26,IF($Q$4="Default Settings",G26,IF($Q$4="Birds in Flight",H26,IF($Q$4="Birds Perched",I26,IF($Q$4="Fireworks",J26,IF($Q$4="Landscape",K26,IF($Q$4="Macro",L26,IF($Q$4="People",M26,IF($Q$4="Sports",N26,IF($Q$4="Travel",O26,IF($Q$4="Waterdrops",P26,IF($Q$4="Wildlife",Q26,""))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D7:D22">
+  <x:conditionalFormatting sqref="D7:D26">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <x:formula>$T7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E7:E22">
+  <x:conditionalFormatting sqref="E7:E26">
     <x:cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
       <x:formula>$U7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F7:F22">
+  <x:conditionalFormatting sqref="F7:F26">
     <x:cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
       <x:formula>$V7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G7:G22">
+  <x:conditionalFormatting sqref="G7:G26">
     <x:cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
       <x:formula>$W7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="H7:H22">
+  <x:conditionalFormatting sqref="H7:H26">
     <x:cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
       <x:formula>$X7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I7:I22">
+  <x:conditionalFormatting sqref="I7:I26">
     <x:cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
       <x:formula>$Y7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J7:J22">
+  <x:conditionalFormatting sqref="J7:J26">
     <x:cfRule type="cellIs" dxfId="6" priority="7" operator="notEqual">
       <x:formula>$Z7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K7:K22">
+  <x:conditionalFormatting sqref="K7:K26">
     <x:cfRule type="cellIs" dxfId="7" priority="8" operator="notEqual">
       <x:formula>$AA7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="L7:L22">
+  <x:conditionalFormatting sqref="L7:L26">
     <x:cfRule type="cellIs" dxfId="8" priority="9" operator="notEqual">
       <x:formula>$AB7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M7:M22">
+  <x:conditionalFormatting sqref="M7:M26">
     <x:cfRule type="cellIs" dxfId="9" priority="10" operator="notEqual">
       <x:formula>$AC7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N7:N22">
+  <x:conditionalFormatting sqref="N7:N26">
     <x:cfRule type="cellIs" dxfId="10" priority="11" operator="notEqual">
       <x:formula>$AD7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O7:O22">
+  <x:conditionalFormatting sqref="O7:O26">
     <x:cfRule type="cellIs" dxfId="11" priority="12" operator="notEqual">
       <x:formula>$AE7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="P7:P22">
+  <x:conditionalFormatting sqref="P7:P26">
     <x:cfRule type="cellIs" dxfId="12" priority="13" operator="notEqual">
       <x:formula>$AF7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Q7:Q22">
+  <x:conditionalFormatting sqref="Q7:Q26">
     <x:cfRule type="cellIs" dxfId="13" priority="14" operator="notEqual">
       <x:formula>$AG7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:Q22">
+  <x:conditionalFormatting sqref="D7:Q26">
     <x:cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Not Used"/>
     <x:cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <x:formula>"—"</x:formula>
@@ -2928,9 +3388,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R79e7159db9ca4871"/>
+  <x:drawing ns1:id="Rbe9a3ada33a24cdf"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R89c601264feb4c92"/>
+    <x:tablePart ns1:id="R0f96c99050124d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3204,7 +3664,7 @@
         <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="B11" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
         <x:v>Case 4</x:v>
@@ -3214,7 +3674,7 @@
       </x:c>
       <x:c r="T11" s="38" t="str">
         <x:f>B11</x:f>
-        <x:v>Case A (Auto)</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="U11" s="38" t="str">
         <x:f>C11</x:f>
@@ -3227,183 +3687,287 @@
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="15" t="str">
-        <x:v>AF Method</x:v>
-      </x:c>
-      <x:c r="B12" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Tracking Sensitivity</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>1-Point AF</x:v>
-      </x:c>
-      <x:c r="T12" s="38" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="T12" s="38" t="n">
         <x:f>B12</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="U12" s="38" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="U12" s="38" t="n">
         <x:f>C12</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V12" s="38" t="str">
         <x:f>D12</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="T13" s="38" t="str">
         <x:f>B13</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="U13" s="38" t="str">
         <x:f>C13</x:f>
-        <x:v>Animals</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="V13" s="38" t="str">
         <x:f>D13</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="T14" s="38" t="str">
         <x:f>B14</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="U14" s="38" t="str">
         <x:f>C14</x:f>
-        <x:v>Enable</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="V14" s="38" t="str">
         <x:f>D14</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="C15" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="T15" s="38" t="str">
         <x:f>B15</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="U15" s="38" t="str">
         <x:f>C15</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="V15" s="38" t="str">
         <x:f>D15</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="C16" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="T16" s="38" t="str">
         <x:f>B16</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="U16" s="38" t="str">
         <x:f>C16</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="V16" s="38" t="str">
         <x:f>D16</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>None</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="T17" s="38" t="str">
         <x:f>B17</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="U17" s="38" t="str">
         <x:f>C17</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
         <x:f>D17</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Disable</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="15" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>Drive</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="C18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="T18" s="38" t="str">
         <x:f>B18</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="U18" s="38" t="str">
         <x:f>C18</x:f>
-        <x:v>Disable</x:v>
+        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="V18" s="38" t="str">
         <x:f>D18</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" hidden="0">
+      <x:c r="A19" s="15" t="str">
+        <x:v>High Speed Display</x:v>
+      </x:c>
+      <x:c r="B19" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="D19" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="T19" s="38" t="str">
+        <x:f>B19</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="U19" s="38" t="str">
+        <x:f>C19</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="V19" s="38" t="str">
+        <x:f>D19</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" hidden="0">
+      <x:c r="A20" s="15" t="str">
+        <x:v>Image Stabilization</x:v>
+      </x:c>
+      <x:c r="B20" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="D20" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="T20" s="38" t="str">
+        <x:f>B20</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U20" s="38" t="str">
+        <x:f>C20</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="V20" s="38" t="str">
+        <x:f>D20</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" hidden="0">
+      <x:c r="A21" s="15" t="str">
+        <x:v>IBIS / Lens IS</x:v>
+      </x:c>
+      <x:c r="B21" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="D21" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="T21" s="38" t="str">
+        <x:f>B21</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U21" s="38" t="str">
+        <x:f>C21</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V21" s="38" t="str">
+        <x:f>D21</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" hidden="0">
+      <x:c r="A22" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="B22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="D22" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="T22" s="38" t="str">
+        <x:f>B22</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U22" s="38" t="str">
+        <x:f>C22</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V22" s="38" t="str">
+        <x:f>D22</x:f>
         <x:v>Disable</x:v>
       </x:c>
     </x:row>
@@ -3411,24 +3975,24 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="B3:B18">
+  <x:conditionalFormatting sqref="B3:B22">
     <x:cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
       <x:formula>$T3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C3:C18">
+  <x:conditionalFormatting sqref="C3:C22">
     <x:cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
       <x:formula>$U3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D3:D18">
+  <x:conditionalFormatting sqref="D3:D22">
     <x:cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
       <x:formula>$V3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rd35bcf722d10420f"/>
+    <x:tablePart ns1:id="R81d79827fe37415a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R91b3e431b9e444b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R6d041c6ad3c0481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R824ee18e150241cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R28d78cec9aee4da1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -228,7 +228,17 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="19">
+  <x:dxfs count="20">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF000000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFFC98"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:color rgb="FF000000"/>
@@ -432,13 +442,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="646283c4-0ec3-4e01-8dc0-89e33c3f8925"/>
+        <xdr:cNvPr id="1" name="576ca5da-cf47-4658-9a49-8a2d7b60f4c2"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc056bdc970214e17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1df47e7eae0a4738"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -453,9 +463,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:S26"/>
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:T26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:T26"/>
+  <x:tableColumns count="20">
     <x:tableColumn id="1" name="Menu Location"/>
     <x:tableColumn id="2" name="Best or Quick Access"/>
     <x:tableColumn id="3" name="Setting"/>
@@ -463,18 +473,19 @@
     <x:tableColumn id="5" name="C2 Birds in Flight"/>
     <x:tableColumn id="6" name="C3 Landscape"/>
     <x:tableColumn id="7" name="Default Settings"/>
-    <x:tableColumn id="8" name="Birds in Flight"/>
-    <x:tableColumn id="9" name="Birds Perched"/>
-    <x:tableColumn id="10" name="Fireworks"/>
-    <x:tableColumn id="11" name="Landscape"/>
-    <x:tableColumn id="12" name="Macro"/>
-    <x:tableColumn id="13" name="People"/>
-    <x:tableColumn id="14" name="Sports"/>
-    <x:tableColumn id="15" name="Travel"/>
-    <x:tableColumn id="16" name="Waterdrops"/>
-    <x:tableColumn id="17" name="Wildlife"/>
-    <x:tableColumn id="18" name="Card Order"/>
-    <x:tableColumn id="19" name="Rapid Setup Order"/>
+    <x:tableColumn id="8" name="Androo"/>
+    <x:tableColumn id="9" name="Birds in Flight"/>
+    <x:tableColumn id="10" name="Birds Perched"/>
+    <x:tableColumn id="11" name="Fireworks"/>
+    <x:tableColumn id="12" name="Landscape"/>
+    <x:tableColumn id="13" name="Macro"/>
+    <x:tableColumn id="14" name="People"/>
+    <x:tableColumn id="15" name="Sports"/>
+    <x:tableColumn id="16" name="Travel"/>
+    <x:tableColumn id="17" name="Waterdrops"/>
+    <x:tableColumn id="18" name="Wildlife"/>
+    <x:tableColumn id="19" name="Card Order"/>
+    <x:tableColumn id="20" name="Rapid Setup Order"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -688,7 +699,6 @@
 <x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="20" max="20" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="21" max="21" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="22" max="22" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="23" max="23" width="0.2199999988079071" hidden="1" customWidth="1"/>
@@ -702,6 +712,8 @@
     <x:col min="31" max="31" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="32" max="32" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="33" max="33" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="34" max="34" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="35" max="35" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="1" max="1" width="12.5600004196167" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.890000343322754" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.890000343322754" hidden="0" customWidth="1"/>
@@ -719,12 +731,12 @@
     <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
-      <x:c r="T1" s="38"/>
       <x:c r="U1" s="38"/>
       <x:c r="V1" s="38"/>
       <x:c r="W1" s="38"/>
@@ -738,9 +750,10 @@
       <x:c r="AE1" s="38"/>
       <x:c r="AF1" s="38"/>
       <x:c r="AG1" s="38"/>
+      <x:c r="AH1" s="38"/>
+      <x:c r="AI1" s="38"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="T2" s="38"/>
       <x:c r="U2" s="38"/>
       <x:c r="V2" s="38"/>
       <x:c r="W2" s="38"/>
@@ -754,9 +767,10 @@
       <x:c r="AE2" s="38"/>
       <x:c r="AF2" s="38"/>
       <x:c r="AG2" s="38"/>
+      <x:c r="AH2" s="38"/>
+      <x:c r="AI2" s="38"/>
     </x:row>
     <x:row r="3" ht="33" customHeight="1">
-      <x:c r="T3" s="38"/>
       <x:c r="U3" s="38"/>
       <x:c r="V3" s="38"/>
       <x:c r="W3" s="38"/>
@@ -770,6 +784,8 @@
       <x:c r="AE3" s="38"/>
       <x:c r="AF3" s="38"/>
       <x:c r="AG3" s="38"/>
+      <x:c r="AH3" s="38"/>
+      <x:c r="AI3" s="38"/>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="24" t="str">
@@ -788,36 +804,38 @@
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="H4" s="28" t="str">
+        <x:v>Androo</x:v>
+      </x:c>
+      <x:c r="I4" s="28" t="str">
         <x:v>Birds in Flight</x:v>
       </x:c>
-      <x:c r="I4" s="28" t="str">
+      <x:c r="J4" s="28" t="str">
         <x:v>Birds Perched</x:v>
       </x:c>
-      <x:c r="J4" s="28" t="str">
+      <x:c r="K4" s="28" t="str">
         <x:v>Fireworks</x:v>
       </x:c>
-      <x:c r="K4" s="28" t="str">
+      <x:c r="L4" s="28" t="str">
         <x:v>Landscape</x:v>
       </x:c>
-      <x:c r="L4" s="28" t="str">
+      <x:c r="M4" s="28" t="str">
         <x:v>Macro</x:v>
       </x:c>
-      <x:c r="M4" s="28" t="str">
+      <x:c r="N4" s="28" t="str">
         <x:v>People</x:v>
       </x:c>
-      <x:c r="N4" s="28" t="str">
+      <x:c r="O4" s="28" t="str">
         <x:v>Sports</x:v>
       </x:c>
-      <x:c r="O4" s="28" t="str">
+      <x:c r="P4" s="28" t="str">
         <x:v>Travel</x:v>
       </x:c>
-      <x:c r="P4" s="28" t="str">
+      <x:c r="Q4" s="28" t="str">
         <x:v>Waterdrops</x:v>
       </x:c>
-      <x:c r="Q4" s="28" t="str">
+      <x:c r="R4" s="28" t="str">
         <x:v>Wildlife</x:v>
       </x:c>
-      <x:c r="T4" s="38"/>
       <x:c r="U4" s="38"/>
       <x:c r="V4" s="38"/>
       <x:c r="W4" s="38"/>
@@ -831,6 +849,8 @@
       <x:c r="AE4" s="38"/>
       <x:c r="AF4" s="38"/>
       <x:c r="AG4" s="38"/>
+      <x:c r="AH4" s="38"/>
+      <x:c r="AI4" s="38"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="33" t="str">
@@ -849,36 +869,38 @@
         <x:v>Camera Defaults + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="H5" s="37" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I5" s="37" t="str">
         <x:v>C2 Birds in Flight + AF Case</x:v>
       </x:c>
-      <x:c r="I5" s="37" t="str">
+      <x:c r="J5" s="37" t="str">
         <x:v>C1 Wildlife + AF Case</x:v>
       </x:c>
-      <x:c r="J5" s="37" t="str">
+      <x:c r="K5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
-      <x:c r="K5" s="37" t="str">
+      <x:c r="L5" s="37" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
-      <x:c r="L5" s="37" t="str">
+      <x:c r="M5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
-      <x:c r="M5" s="37" t="str">
+      <x:c r="N5" s="37" t="str">
         <x:v>C1 Wildlife + SWITCH + AF Case</x:v>
       </x:c>
-      <x:c r="N5" s="37" t="str">
+      <x:c r="O5" s="37" t="str">
         <x:v>C2 Birds in Flight + SWITCH + AF Case</x:v>
       </x:c>
-      <x:c r="O5" s="37" t="str">
+      <x:c r="P5" s="37" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
-      <x:c r="P5" s="37" t="str">
+      <x:c r="Q5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
-      <x:c r="Q5" s="37" t="str">
+      <x:c r="R5" s="37" t="str">
         <x:v>C1 Wildlife + AF Case</x:v>
       </x:c>
-      <x:c r="T5" s="38"/>
       <x:c r="U5" s="38"/>
       <x:c r="V5" s="38"/>
       <x:c r="W5" s="38"/>
@@ -892,6 +914,8 @@
       <x:c r="AE5" s="38"/>
       <x:c r="AF5" s="38"/>
       <x:c r="AG5" s="38"/>
+      <x:c r="AH5" s="38"/>
+      <x:c r="AI5" s="38"/>
     </x:row>
     <x:row r="6" hidden="0">
       <x:c r="A6" s="5" t="str">
@@ -916,42 +940,44 @@
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
+        <x:v>Androo</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
         <x:v>Birds in Flight</x:v>
       </x:c>
-      <x:c r="I6" s="6" t="str">
+      <x:c r="J6" s="6" t="str">
         <x:v>Birds Perched</x:v>
       </x:c>
-      <x:c r="J6" s="6" t="str">
+      <x:c r="K6" s="6" t="str">
         <x:v>Fireworks</x:v>
       </x:c>
-      <x:c r="K6" s="6" t="str">
+      <x:c r="L6" s="6" t="str">
         <x:v>Landscape</x:v>
       </x:c>
-      <x:c r="L6" s="8" t="str">
+      <x:c r="M6" s="8" t="str">
         <x:v>Macro</x:v>
       </x:c>
-      <x:c r="M6" s="6" t="str">
+      <x:c r="N6" s="6" t="str">
         <x:v>People</x:v>
       </x:c>
-      <x:c r="N6" s="8" t="str">
+      <x:c r="O6" s="8" t="str">
         <x:v>Sports</x:v>
       </x:c>
-      <x:c r="O6" s="8" t="str">
+      <x:c r="P6" s="8" t="str">
         <x:v>Travel</x:v>
       </x:c>
-      <x:c r="P6" s="8" t="str">
+      <x:c r="Q6" s="8" t="str">
         <x:v>Waterdrops</x:v>
       </x:c>
-      <x:c r="Q6" s="6" t="str">
+      <x:c r="R6" s="6" t="str">
         <x:v>Wildlife</x:v>
       </x:c>
-      <x:c r="R6" s="6" t="str">
+      <x:c r="S6" s="6" t="str">
         <x:v>Card Order</x:v>
       </x:c>
-      <x:c r="S6" s="6" t="str">
+      <x:c r="T6" s="6" t="str">
         <x:v>Rapid Setup Order</x:v>
       </x:c>
-      <x:c r="T6" s="38"/>
       <x:c r="U6" s="38"/>
       <x:c r="V6" s="38"/>
       <x:c r="W6" s="38"/>
@@ -965,6 +991,8 @@
       <x:c r="AE6" s="38"/>
       <x:c r="AF6" s="38"/>
       <x:c r="AG6" s="38"/>
+      <x:c r="AH6" s="38"/>
+      <x:c r="AI6" s="38"/>
     </x:row>
     <x:row r="7" hidden="0">
       <x:c r="A7" s="12" t="str">
@@ -989,95 +1017,102 @@
         <x:v>Fv</x:v>
       </x:c>
       <x:c r="H7" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="str">
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="I7" s="17" t="str">
+      <x:c r="J7" s="17" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="J7" s="17" t="str">
+      <x:c r="K7" s="17" t="str">
         <x:v>Manual</x:v>
-      </x:c>
-      <x:c r="K7" s="17" t="str">
-        <x:v>Av</x:v>
       </x:c>
       <x:c r="L7" s="17" t="str">
         <x:v>Av</x:v>
       </x:c>
       <x:c r="M7" s="17" t="str">
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="N7" s="17" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="N7" s="17" t="str">
+      <x:c r="O7" s="17" t="str">
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="O7" s="17" t="str">
+      <x:c r="P7" s="17" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="P7" s="17" t="str">
+      <x:c r="Q7" s="17" t="str">
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="Q7" s="17" t="str">
+      <x:c r="R7" s="17" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="n">
+      <x:c r="S7" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="n">
+      <x:c r="T7" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="T7" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D7,IF($D$4="C2 Birds in Flight",E7,IF($D$4="C3 Landscape",F7,IF($D$4="Default Settings",G7,IF($D$4="Birds in Flight",H7,IF($D$4="Birds Perched",I7,IF($D$4="Fireworks",J7,IF($D$4="Landscape",K7,IF($D$4="Macro",L7,IF($D$4="People",M7,IF($D$4="Sports",N7,IF($D$4="Travel",O7,IF($D$4="Waterdrops",P7,IF($D$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="U7" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D7,IF($D$4="C2 Birds in Flight",E7,IF($D$4="C3 Landscape",F7,IF($D$4="Default Settings",G7,IF($D$4="Androo",H7,IF($D$4="Birds in Flight",I7,IF($D$4="Birds Perched",J7,IF($D$4="Fireworks",K7,IF($D$4="Landscape",L7,IF($D$4="Macro",M7,IF($D$4="People",N7,IF($D$4="Sports",O7,IF($D$4="Travel",P7,IF($D$4="Waterdrops",Q7,IF($D$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="U7" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D7,IF($E$4="C2 Birds in Flight",E7,IF($E$4="C3 Landscape",F7,IF($E$4="Default Settings",G7,IF($E$4="Birds in Flight",H7,IF($E$4="Birds Perched",I7,IF($E$4="Fireworks",J7,IF($E$4="Landscape",K7,IF($E$4="Macro",L7,IF($E$4="People",M7,IF($E$4="Sports",N7,IF($E$4="Travel",O7,IF($E$4="Waterdrops",P7,IF($E$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="V7" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D7,IF($E$4="C2 Birds in Flight",E7,IF($E$4="C3 Landscape",F7,IF($E$4="Default Settings",G7,IF($E$4="Androo",H7,IF($E$4="Birds in Flight",I7,IF($E$4="Birds Perched",J7,IF($E$4="Fireworks",K7,IF($E$4="Landscape",L7,IF($E$4="Macro",M7,IF($E$4="People",N7,IF($E$4="Sports",O7,IF($E$4="Travel",P7,IF($E$4="Waterdrops",Q7,IF($E$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="V7" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D7,IF($F$4="C2 Birds in Flight",E7,IF($F$4="C3 Landscape",F7,IF($F$4="Default Settings",G7,IF($F$4="Birds in Flight",H7,IF($F$4="Birds Perched",I7,IF($F$4="Fireworks",J7,IF($F$4="Landscape",K7,IF($F$4="Macro",L7,IF($F$4="People",M7,IF($F$4="Sports",N7,IF($F$4="Travel",O7,IF($F$4="Waterdrops",P7,IF($F$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="W7" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D7,IF($F$4="C2 Birds in Flight",E7,IF($F$4="C3 Landscape",F7,IF($F$4="Default Settings",G7,IF($F$4="Androo",H7,IF($F$4="Birds in Flight",I7,IF($F$4="Birds Perched",J7,IF($F$4="Fireworks",K7,IF($F$4="Landscape",L7,IF($F$4="Macro",M7,IF($F$4="People",N7,IF($F$4="Sports",O7,IF($F$4="Travel",P7,IF($F$4="Waterdrops",Q7,IF($F$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="W7" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D7,IF($G$4="C2 Birds in Flight",E7,IF($G$4="C3 Landscape",F7,IF($G$4="Default Settings",G7,IF($G$4="Birds in Flight",H7,IF($G$4="Birds Perched",I7,IF($G$4="Fireworks",J7,IF($G$4="Landscape",K7,IF($G$4="Macro",L7,IF($G$4="People",M7,IF($G$4="Sports",N7,IF($G$4="Travel",O7,IF($G$4="Waterdrops",P7,IF($G$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="X7" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D7,IF($G$4="C2 Birds in Flight",E7,IF($G$4="C3 Landscape",F7,IF($G$4="Default Settings",G7,IF($G$4="Androo",H7,IF($G$4="Birds in Flight",I7,IF($G$4="Birds Perched",J7,IF($G$4="Fireworks",K7,IF($G$4="Landscape",L7,IF($G$4="Macro",M7,IF($G$4="People",N7,IF($G$4="Sports",O7,IF($G$4="Travel",P7,IF($G$4="Waterdrops",Q7,IF($G$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="X7" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D7,IF($H$4="C2 Birds in Flight",E7,IF($H$4="C3 Landscape",F7,IF($H$4="Default Settings",G7,IF($H$4="Birds in Flight",H7,IF($H$4="Birds Perched",I7,IF($H$4="Fireworks",J7,IF($H$4="Landscape",K7,IF($H$4="Macro",L7,IF($H$4="People",M7,IF($H$4="Sports",N7,IF($H$4="Travel",O7,IF($H$4="Waterdrops",P7,IF($H$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="Y7" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D7,IF($H$4="C2 Birds in Flight",E7,IF($H$4="C3 Landscape",F7,IF($H$4="Default Settings",G7,IF($H$4="Androo",H7,IF($H$4="Birds in Flight",I7,IF($H$4="Birds Perched",J7,IF($H$4="Fireworks",K7,IF($H$4="Landscape",L7,IF($H$4="Macro",M7,IF($H$4="People",N7,IF($H$4="Sports",O7,IF($H$4="Travel",P7,IF($H$4="Waterdrops",Q7,IF($H$4="Wildlife",R7,"")))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="Z7" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D7,IF($I$4="C2 Birds in Flight",E7,IF($I$4="C3 Landscape",F7,IF($I$4="Default Settings",G7,IF($I$4="Androo",H7,IF($I$4="Birds in Flight",I7,IF($I$4="Birds Perched",J7,IF($I$4="Fireworks",K7,IF($I$4="Landscape",L7,IF($I$4="Macro",M7,IF($I$4="People",N7,IF($I$4="Sports",O7,IF($I$4="Travel",P7,IF($I$4="Waterdrops",Q7,IF($I$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="Y7" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D7,IF($I$4="C2 Birds in Flight",E7,IF($I$4="C3 Landscape",F7,IF($I$4="Default Settings",G7,IF($I$4="Birds in Flight",H7,IF($I$4="Birds Perched",I7,IF($I$4="Fireworks",J7,IF($I$4="Landscape",K7,IF($I$4="Macro",L7,IF($I$4="People",M7,IF($I$4="Sports",N7,IF($I$4="Travel",O7,IF($I$4="Waterdrops",P7,IF($I$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AA7" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D7,IF($J$4="C2 Birds in Flight",E7,IF($J$4="C3 Landscape",F7,IF($J$4="Default Settings",G7,IF($J$4="Androo",H7,IF($J$4="Birds in Flight",I7,IF($J$4="Birds Perched",J7,IF($J$4="Fireworks",K7,IF($J$4="Landscape",L7,IF($J$4="Macro",M7,IF($J$4="People",N7,IF($J$4="Sports",O7,IF($J$4="Travel",P7,IF($J$4="Waterdrops",Q7,IF($J$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="Z7" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D7,IF($J$4="C2 Birds in Flight",E7,IF($J$4="C3 Landscape",F7,IF($J$4="Default Settings",G7,IF($J$4="Birds in Flight",H7,IF($J$4="Birds Perched",I7,IF($J$4="Fireworks",J7,IF($J$4="Landscape",K7,IF($J$4="Macro",L7,IF($J$4="People",M7,IF($J$4="Sports",N7,IF($J$4="Travel",O7,IF($J$4="Waterdrops",P7,IF($J$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AB7" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D7,IF($K$4="C2 Birds in Flight",E7,IF($K$4="C3 Landscape",F7,IF($K$4="Default Settings",G7,IF($K$4="Androo",H7,IF($K$4="Birds in Flight",I7,IF($K$4="Birds Perched",J7,IF($K$4="Fireworks",K7,IF($K$4="Landscape",L7,IF($K$4="Macro",M7,IF($K$4="People",N7,IF($K$4="Sports",O7,IF($K$4="Travel",P7,IF($K$4="Waterdrops",Q7,IF($K$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="AA7" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D7,IF($K$4="C2 Birds in Flight",E7,IF($K$4="C3 Landscape",F7,IF($K$4="Default Settings",G7,IF($K$4="Birds in Flight",H7,IF($K$4="Birds Perched",I7,IF($K$4="Fireworks",J7,IF($K$4="Landscape",K7,IF($K$4="Macro",L7,IF($K$4="People",M7,IF($K$4="Sports",N7,IF($K$4="Travel",O7,IF($K$4="Waterdrops",P7,IF($K$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AC7" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D7,IF($L$4="C2 Birds in Flight",E7,IF($L$4="C3 Landscape",F7,IF($L$4="Default Settings",G7,IF($L$4="Androo",H7,IF($L$4="Birds in Flight",I7,IF($L$4="Birds Perched",J7,IF($L$4="Fireworks",K7,IF($L$4="Landscape",L7,IF($L$4="Macro",M7,IF($L$4="People",N7,IF($L$4="Sports",O7,IF($L$4="Travel",P7,IF($L$4="Waterdrops",Q7,IF($L$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="AB7" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D7,IF($L$4="C2 Birds in Flight",E7,IF($L$4="C3 Landscape",F7,IF($L$4="Default Settings",G7,IF($L$4="Birds in Flight",H7,IF($L$4="Birds Perched",I7,IF($L$4="Fireworks",J7,IF($L$4="Landscape",K7,IF($L$4="Macro",L7,IF($L$4="People",M7,IF($L$4="Sports",N7,IF($L$4="Travel",O7,IF($L$4="Waterdrops",P7,IF($L$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AD7" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D7,IF($M$4="C2 Birds in Flight",E7,IF($M$4="C3 Landscape",F7,IF($M$4="Default Settings",G7,IF($M$4="Androo",H7,IF($M$4="Birds in Flight",I7,IF($M$4="Birds Perched",J7,IF($M$4="Fireworks",K7,IF($M$4="Landscape",L7,IF($M$4="Macro",M7,IF($M$4="People",N7,IF($M$4="Sports",O7,IF($M$4="Travel",P7,IF($M$4="Waterdrops",Q7,IF($M$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="AC7" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D7,IF($M$4="C2 Birds in Flight",E7,IF($M$4="C3 Landscape",F7,IF($M$4="Default Settings",G7,IF($M$4="Birds in Flight",H7,IF($M$4="Birds Perched",I7,IF($M$4="Fireworks",J7,IF($M$4="Landscape",K7,IF($M$4="Macro",L7,IF($M$4="People",M7,IF($M$4="Sports",N7,IF($M$4="Travel",O7,IF($M$4="Waterdrops",P7,IF($M$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AE7" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D7,IF($N$4="C2 Birds in Flight",E7,IF($N$4="C3 Landscape",F7,IF($N$4="Default Settings",G7,IF($N$4="Androo",H7,IF($N$4="Birds in Flight",I7,IF($N$4="Birds Perched",J7,IF($N$4="Fireworks",K7,IF($N$4="Landscape",L7,IF($N$4="Macro",M7,IF($N$4="People",N7,IF($N$4="Sports",O7,IF($N$4="Travel",P7,IF($N$4="Waterdrops",Q7,IF($N$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="AD7" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D7,IF($N$4="C2 Birds in Flight",E7,IF($N$4="C3 Landscape",F7,IF($N$4="Default Settings",G7,IF($N$4="Birds in Flight",H7,IF($N$4="Birds Perched",I7,IF($N$4="Fireworks",J7,IF($N$4="Landscape",K7,IF($N$4="Macro",L7,IF($N$4="People",M7,IF($N$4="Sports",N7,IF($N$4="Travel",O7,IF($N$4="Waterdrops",P7,IF($N$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AF7" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D7,IF($O$4="C2 Birds in Flight",E7,IF($O$4="C3 Landscape",F7,IF($O$4="Default Settings",G7,IF($O$4="Androo",H7,IF($O$4="Birds in Flight",I7,IF($O$4="Birds Perched",J7,IF($O$4="Fireworks",K7,IF($O$4="Landscape",L7,IF($O$4="Macro",M7,IF($O$4="People",N7,IF($O$4="Sports",O7,IF($O$4="Travel",P7,IF($O$4="Waterdrops",Q7,IF($O$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="AE7" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D7,IF($O$4="C2 Birds in Flight",E7,IF($O$4="C3 Landscape",F7,IF($O$4="Default Settings",G7,IF($O$4="Birds in Flight",H7,IF($O$4="Birds Perched",I7,IF($O$4="Fireworks",J7,IF($O$4="Landscape",K7,IF($O$4="Macro",L7,IF($O$4="People",M7,IF($O$4="Sports",N7,IF($O$4="Travel",O7,IF($O$4="Waterdrops",P7,IF($O$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AG7" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D7,IF($P$4="C2 Birds in Flight",E7,IF($P$4="C3 Landscape",F7,IF($P$4="Default Settings",G7,IF($P$4="Androo",H7,IF($P$4="Birds in Flight",I7,IF($P$4="Birds Perched",J7,IF($P$4="Fireworks",K7,IF($P$4="Landscape",L7,IF($P$4="Macro",M7,IF($P$4="People",N7,IF($P$4="Sports",O7,IF($P$4="Travel",P7,IF($P$4="Waterdrops",Q7,IF($P$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="AF7" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D7,IF($P$4="C2 Birds in Flight",E7,IF($P$4="C3 Landscape",F7,IF($P$4="Default Settings",G7,IF($P$4="Birds in Flight",H7,IF($P$4="Birds Perched",I7,IF($P$4="Fireworks",J7,IF($P$4="Landscape",K7,IF($P$4="Macro",L7,IF($P$4="People",M7,IF($P$4="Sports",N7,IF($P$4="Travel",O7,IF($P$4="Waterdrops",P7,IF($P$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AH7" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D7,IF($Q$4="C2 Birds in Flight",E7,IF($Q$4="C3 Landscape",F7,IF($Q$4="Default Settings",G7,IF($Q$4="Androo",H7,IF($Q$4="Birds in Flight",I7,IF($Q$4="Birds Perched",J7,IF($Q$4="Fireworks",K7,IF($Q$4="Landscape",L7,IF($Q$4="Macro",M7,IF($Q$4="People",N7,IF($Q$4="Sports",O7,IF($Q$4="Travel",P7,IF($Q$4="Waterdrops",Q7,IF($Q$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="AG7" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D7,IF($Q$4="C2 Birds in Flight",E7,IF($Q$4="C3 Landscape",F7,IF($Q$4="Default Settings",G7,IF($Q$4="Birds in Flight",H7,IF($Q$4="Birds Perched",I7,IF($Q$4="Fireworks",J7,IF($Q$4="Landscape",K7,IF($Q$4="Macro",L7,IF($Q$4="People",M7,IF($Q$4="Sports",N7,IF($Q$4="Travel",O7,IF($Q$4="Waterdrops",P7,IF($Q$4="Wildlife",Q7,""))))))))))))))</x:f>
+      <x:c r="AI7" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D7,IF($R$4="C2 Birds in Flight",E7,IF($R$4="C3 Landscape",F7,IF($R$4="Default Settings",G7,IF($R$4="Androo",H7,IF($R$4="Birds in Flight",I7,IF($R$4="Birds Perched",J7,IF($R$4="Fireworks",K7,IF($R$4="Landscape",L7,IF($R$4="Macro",M7,IF($R$4="People",N7,IF($R$4="Sports",O7,IF($R$4="Travel",P7,IF($R$4="Waterdrops",Q7,IF($R$4="Wildlife",R7,"")))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
     </x:row>
@@ -1133,66 +1168,73 @@
       <x:c r="Q8" s="17" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="R8" s="20" t="n">
+      <x:c r="R8" s="17" t="str">
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="S8" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="S8" s="20" t="n">
+      <x:c r="T8" s="20" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="T8" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D8,IF($D$4="C2 Birds in Flight",E8,IF($D$4="C3 Landscape",F8,IF($D$4="Default Settings",G8,IF($D$4="Birds in Flight",H8,IF($D$4="Birds Perched",I8,IF($D$4="Fireworks",J8,IF($D$4="Landscape",K8,IF($D$4="Macro",L8,IF($D$4="People",M8,IF($D$4="Sports",N8,IF($D$4="Travel",O8,IF($D$4="Waterdrops",P8,IF($D$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="U8" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D8,IF($D$4="C2 Birds in Flight",E8,IF($D$4="C3 Landscape",F8,IF($D$4="Default Settings",G8,IF($D$4="Androo",H8,IF($D$4="Birds in Flight",I8,IF($D$4="Birds Perched",J8,IF($D$4="Fireworks",K8,IF($D$4="Landscape",L8,IF($D$4="Macro",M8,IF($D$4="People",N8,IF($D$4="Sports",O8,IF($D$4="Travel",P8,IF($D$4="Waterdrops",Q8,IF($D$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="U8" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D8,IF($E$4="C2 Birds in Flight",E8,IF($E$4="C3 Landscape",F8,IF($E$4="Default Settings",G8,IF($E$4="Birds in Flight",H8,IF($E$4="Birds Perched",I8,IF($E$4="Fireworks",J8,IF($E$4="Landscape",K8,IF($E$4="Macro",L8,IF($E$4="People",M8,IF($E$4="Sports",N8,IF($E$4="Travel",O8,IF($E$4="Waterdrops",P8,IF($E$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="V8" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D8,IF($E$4="C2 Birds in Flight",E8,IF($E$4="C3 Landscape",F8,IF($E$4="Default Settings",G8,IF($E$4="Androo",H8,IF($E$4="Birds in Flight",I8,IF($E$4="Birds Perched",J8,IF($E$4="Fireworks",K8,IF($E$4="Landscape",L8,IF($E$4="Macro",M8,IF($E$4="People",N8,IF($E$4="Sports",O8,IF($E$4="Travel",P8,IF($E$4="Waterdrops",Q8,IF($E$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="V8" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D8,IF($F$4="C2 Birds in Flight",E8,IF($F$4="C3 Landscape",F8,IF($F$4="Default Settings",G8,IF($F$4="Birds in Flight",H8,IF($F$4="Birds Perched",I8,IF($F$4="Fireworks",J8,IF($F$4="Landscape",K8,IF($F$4="Macro",L8,IF($F$4="People",M8,IF($F$4="Sports",N8,IF($F$4="Travel",O8,IF($F$4="Waterdrops",P8,IF($F$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="W8" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D8,IF($F$4="C2 Birds in Flight",E8,IF($F$4="C3 Landscape",F8,IF($F$4="Default Settings",G8,IF($F$4="Androo",H8,IF($F$4="Birds in Flight",I8,IF($F$4="Birds Perched",J8,IF($F$4="Fireworks",K8,IF($F$4="Landscape",L8,IF($F$4="Macro",M8,IF($F$4="People",N8,IF($F$4="Sports",O8,IF($F$4="Travel",P8,IF($F$4="Waterdrops",Q8,IF($F$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="W8" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D8,IF($G$4="C2 Birds in Flight",E8,IF($G$4="C3 Landscape",F8,IF($G$4="Default Settings",G8,IF($G$4="Birds in Flight",H8,IF($G$4="Birds Perched",I8,IF($G$4="Fireworks",J8,IF($G$4="Landscape",K8,IF($G$4="Macro",L8,IF($G$4="People",M8,IF($G$4="Sports",N8,IF($G$4="Travel",O8,IF($G$4="Waterdrops",P8,IF($G$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="X8" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D8,IF($G$4="C2 Birds in Flight",E8,IF($G$4="C3 Landscape",F8,IF($G$4="Default Settings",G8,IF($G$4="Androo",H8,IF($G$4="Birds in Flight",I8,IF($G$4="Birds Perched",J8,IF($G$4="Fireworks",K8,IF($G$4="Landscape",L8,IF($G$4="Macro",M8,IF($G$4="People",N8,IF($G$4="Sports",O8,IF($G$4="Travel",P8,IF($G$4="Waterdrops",Q8,IF($G$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="X8" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D8,IF($H$4="C2 Birds in Flight",E8,IF($H$4="C3 Landscape",F8,IF($H$4="Default Settings",G8,IF($H$4="Birds in Flight",H8,IF($H$4="Birds Perched",I8,IF($H$4="Fireworks",J8,IF($H$4="Landscape",K8,IF($H$4="Macro",L8,IF($H$4="People",M8,IF($H$4="Sports",N8,IF($H$4="Travel",O8,IF($H$4="Waterdrops",P8,IF($H$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="Y8" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D8,IF($H$4="C2 Birds in Flight",E8,IF($H$4="C3 Landscape",F8,IF($H$4="Default Settings",G8,IF($H$4="Androo",H8,IF($H$4="Birds in Flight",I8,IF($H$4="Birds Perched",J8,IF($H$4="Fireworks",K8,IF($H$4="Landscape",L8,IF($H$4="Macro",M8,IF($H$4="People",N8,IF($H$4="Sports",O8,IF($H$4="Travel",P8,IF($H$4="Waterdrops",Q8,IF($H$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="Y8" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D8,IF($I$4="C2 Birds in Flight",E8,IF($I$4="C3 Landscape",F8,IF($I$4="Default Settings",G8,IF($I$4="Birds in Flight",H8,IF($I$4="Birds Perched",I8,IF($I$4="Fireworks",J8,IF($I$4="Landscape",K8,IF($I$4="Macro",L8,IF($I$4="People",M8,IF($I$4="Sports",N8,IF($I$4="Travel",O8,IF($I$4="Waterdrops",P8,IF($I$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="Z8" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D8,IF($I$4="C2 Birds in Flight",E8,IF($I$4="C3 Landscape",F8,IF($I$4="Default Settings",G8,IF($I$4="Androo",H8,IF($I$4="Birds in Flight",I8,IF($I$4="Birds Perched",J8,IF($I$4="Fireworks",K8,IF($I$4="Landscape",L8,IF($I$4="Macro",M8,IF($I$4="People",N8,IF($I$4="Sports",O8,IF($I$4="Travel",P8,IF($I$4="Waterdrops",Q8,IF($I$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="Z8" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D8,IF($J$4="C2 Birds in Flight",E8,IF($J$4="C3 Landscape",F8,IF($J$4="Default Settings",G8,IF($J$4="Birds in Flight",H8,IF($J$4="Birds Perched",I8,IF($J$4="Fireworks",J8,IF($J$4="Landscape",K8,IF($J$4="Macro",L8,IF($J$4="People",M8,IF($J$4="Sports",N8,IF($J$4="Travel",O8,IF($J$4="Waterdrops",P8,IF($J$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AA8" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D8,IF($J$4="C2 Birds in Flight",E8,IF($J$4="C3 Landscape",F8,IF($J$4="Default Settings",G8,IF($J$4="Androo",H8,IF($J$4="Birds in Flight",I8,IF($J$4="Birds Perched",J8,IF($J$4="Fireworks",K8,IF($J$4="Landscape",L8,IF($J$4="Macro",M8,IF($J$4="People",N8,IF($J$4="Sports",O8,IF($J$4="Travel",P8,IF($J$4="Waterdrops",Q8,IF($J$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AA8" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D8,IF($K$4="C2 Birds in Flight",E8,IF($K$4="C3 Landscape",F8,IF($K$4="Default Settings",G8,IF($K$4="Birds in Flight",H8,IF($K$4="Birds Perched",I8,IF($K$4="Fireworks",J8,IF($K$4="Landscape",K8,IF($K$4="Macro",L8,IF($K$4="People",M8,IF($K$4="Sports",N8,IF($K$4="Travel",O8,IF($K$4="Waterdrops",P8,IF($K$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AB8" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D8,IF($K$4="C2 Birds in Flight",E8,IF($K$4="C3 Landscape",F8,IF($K$4="Default Settings",G8,IF($K$4="Androo",H8,IF($K$4="Birds in Flight",I8,IF($K$4="Birds Perched",J8,IF($K$4="Fireworks",K8,IF($K$4="Landscape",L8,IF($K$4="Macro",M8,IF($K$4="People",N8,IF($K$4="Sports",O8,IF($K$4="Travel",P8,IF($K$4="Waterdrops",Q8,IF($K$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AB8" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D8,IF($L$4="C2 Birds in Flight",E8,IF($L$4="C3 Landscape",F8,IF($L$4="Default Settings",G8,IF($L$4="Birds in Flight",H8,IF($L$4="Birds Perched",I8,IF($L$4="Fireworks",J8,IF($L$4="Landscape",K8,IF($L$4="Macro",L8,IF($L$4="People",M8,IF($L$4="Sports",N8,IF($L$4="Travel",O8,IF($L$4="Waterdrops",P8,IF($L$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AC8" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D8,IF($L$4="C2 Birds in Flight",E8,IF($L$4="C3 Landscape",F8,IF($L$4="Default Settings",G8,IF($L$4="Androo",H8,IF($L$4="Birds in Flight",I8,IF($L$4="Birds Perched",J8,IF($L$4="Fireworks",K8,IF($L$4="Landscape",L8,IF($L$4="Macro",M8,IF($L$4="People",N8,IF($L$4="Sports",O8,IF($L$4="Travel",P8,IF($L$4="Waterdrops",Q8,IF($L$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AC8" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D8,IF($M$4="C2 Birds in Flight",E8,IF($M$4="C3 Landscape",F8,IF($M$4="Default Settings",G8,IF($M$4="Birds in Flight",H8,IF($M$4="Birds Perched",I8,IF($M$4="Fireworks",J8,IF($M$4="Landscape",K8,IF($M$4="Macro",L8,IF($M$4="People",M8,IF($M$4="Sports",N8,IF($M$4="Travel",O8,IF($M$4="Waterdrops",P8,IF($M$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AD8" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D8,IF($M$4="C2 Birds in Flight",E8,IF($M$4="C3 Landscape",F8,IF($M$4="Default Settings",G8,IF($M$4="Androo",H8,IF($M$4="Birds in Flight",I8,IF($M$4="Birds Perched",J8,IF($M$4="Fireworks",K8,IF($M$4="Landscape",L8,IF($M$4="Macro",M8,IF($M$4="People",N8,IF($M$4="Sports",O8,IF($M$4="Travel",P8,IF($M$4="Waterdrops",Q8,IF($M$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AD8" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D8,IF($N$4="C2 Birds in Flight",E8,IF($N$4="C3 Landscape",F8,IF($N$4="Default Settings",G8,IF($N$4="Birds in Flight",H8,IF($N$4="Birds Perched",I8,IF($N$4="Fireworks",J8,IF($N$4="Landscape",K8,IF($N$4="Macro",L8,IF($N$4="People",M8,IF($N$4="Sports",N8,IF($N$4="Travel",O8,IF($N$4="Waterdrops",P8,IF($N$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AE8" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D8,IF($N$4="C2 Birds in Flight",E8,IF($N$4="C3 Landscape",F8,IF($N$4="Default Settings",G8,IF($N$4="Androo",H8,IF($N$4="Birds in Flight",I8,IF($N$4="Birds Perched",J8,IF($N$4="Fireworks",K8,IF($N$4="Landscape",L8,IF($N$4="Macro",M8,IF($N$4="People",N8,IF($N$4="Sports",O8,IF($N$4="Travel",P8,IF($N$4="Waterdrops",Q8,IF($N$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AE8" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D8,IF($O$4="C2 Birds in Flight",E8,IF($O$4="C3 Landscape",F8,IF($O$4="Default Settings",G8,IF($O$4="Birds in Flight",H8,IF($O$4="Birds Perched",I8,IF($O$4="Fireworks",J8,IF($O$4="Landscape",K8,IF($O$4="Macro",L8,IF($O$4="People",M8,IF($O$4="Sports",N8,IF($O$4="Travel",O8,IF($O$4="Waterdrops",P8,IF($O$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AF8" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D8,IF($O$4="C2 Birds in Flight",E8,IF($O$4="C3 Landscape",F8,IF($O$4="Default Settings",G8,IF($O$4="Androo",H8,IF($O$4="Birds in Flight",I8,IF($O$4="Birds Perched",J8,IF($O$4="Fireworks",K8,IF($O$4="Landscape",L8,IF($O$4="Macro",M8,IF($O$4="People",N8,IF($O$4="Sports",O8,IF($O$4="Travel",P8,IF($O$4="Waterdrops",Q8,IF($O$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AF8" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D8,IF($P$4="C2 Birds in Flight",E8,IF($P$4="C3 Landscape",F8,IF($P$4="Default Settings",G8,IF($P$4="Birds in Flight",H8,IF($P$4="Birds Perched",I8,IF($P$4="Fireworks",J8,IF($P$4="Landscape",K8,IF($P$4="Macro",L8,IF($P$4="People",M8,IF($P$4="Sports",N8,IF($P$4="Travel",O8,IF($P$4="Waterdrops",P8,IF($P$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AG8" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D8,IF($P$4="C2 Birds in Flight",E8,IF($P$4="C3 Landscape",F8,IF($P$4="Default Settings",G8,IF($P$4="Androo",H8,IF($P$4="Birds in Flight",I8,IF($P$4="Birds Perched",J8,IF($P$4="Fireworks",K8,IF($P$4="Landscape",L8,IF($P$4="Macro",M8,IF($P$4="People",N8,IF($P$4="Sports",O8,IF($P$4="Travel",P8,IF($P$4="Waterdrops",Q8,IF($P$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="AG8" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D8,IF($Q$4="C2 Birds in Flight",E8,IF($Q$4="C3 Landscape",F8,IF($Q$4="Default Settings",G8,IF($Q$4="Birds in Flight",H8,IF($Q$4="Birds Perched",I8,IF($Q$4="Fireworks",J8,IF($Q$4="Landscape",K8,IF($Q$4="Macro",L8,IF($Q$4="People",M8,IF($Q$4="Sports",N8,IF($Q$4="Travel",O8,IF($Q$4="Waterdrops",P8,IF($Q$4="Wildlife",Q8,""))))))))))))))</x:f>
+      <x:c r="AH8" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D8,IF($Q$4="C2 Birds in Flight",E8,IF($Q$4="C3 Landscape",F8,IF($Q$4="Default Settings",G8,IF($Q$4="Androo",H8,IF($Q$4="Birds in Flight",I8,IF($Q$4="Birds Perched",J8,IF($Q$4="Fireworks",K8,IF($Q$4="Landscape",L8,IF($Q$4="Macro",M8,IF($Q$4="People",N8,IF($Q$4="Sports",O8,IF($Q$4="Travel",P8,IF($Q$4="Waterdrops",Q8,IF($Q$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:v>Evaluative</x:v>
+      </x:c>
+      <x:c r="AI8" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D8,IF($R$4="C2 Birds in Flight",E8,IF($R$4="C3 Landscape",F8,IF($R$4="Default Settings",G8,IF($R$4="Androo",H8,IF($R$4="Birds in Flight",I8,IF($R$4="Birds Perched",J8,IF($R$4="Fireworks",K8,IF($R$4="Landscape",L8,IF($R$4="Macro",M8,IF($R$4="People",N8,IF($R$4="Sports",O8,IF($R$4="Travel",P8,IF($R$4="Waterdrops",Q8,IF($R$4="Wildlife",R8,"")))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
     </x:row>
@@ -1219,95 +1261,102 @@
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="H9" s="17" t="str">
+        <x:v>1/200</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
         <x:v>1/2000–1/4000</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="str">
+      <x:c r="J9" s="17" t="str">
         <x:v>1/500–1/1000</x:v>
       </x:c>
-      <x:c r="J9" s="17" t="str">
+      <x:c r="K9" s="17" t="str">
         <x:v>2–6 s (start at 4 s)</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="L9" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="M9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="N9" s="17" t="str">
         <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
       </x:c>
-      <x:c r="N9" s="17" t="str">
+      <x:c r="O9" s="17" t="str">
         <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
       </x:c>
-      <x:c r="O9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="P9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Q9" s="17" t="str">
         <x:v>1/200</x:v>
       </x:c>
-      <x:c r="Q9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="R9" s="20" t="n">
+      <x:c r="R9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="S9" s="20" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="n">
+      <x:c r="T9" s="20" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="T9" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D9,IF($D$4="C2 Birds in Flight",E9,IF($D$4="C3 Landscape",F9,IF($D$4="Default Settings",G9,IF($D$4="Birds in Flight",H9,IF($D$4="Birds Perched",I9,IF($D$4="Fireworks",J9,IF($D$4="Landscape",K9,IF($D$4="Macro",L9,IF($D$4="People",M9,IF($D$4="Sports",N9,IF($D$4="Travel",O9,IF($D$4="Waterdrops",P9,IF($D$4="Wildlife",Q9,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="U9" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D9,IF($E$4="C2 Birds in Flight",E9,IF($E$4="C3 Landscape",F9,IF($E$4="Default Settings",G9,IF($E$4="Birds in Flight",H9,IF($E$4="Birds Perched",I9,IF($E$4="Fireworks",J9,IF($E$4="Landscape",K9,IF($E$4="Macro",L9,IF($E$4="People",M9,IF($E$4="Sports",N9,IF($E$4="Travel",O9,IF($E$4="Waterdrops",P9,IF($E$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:f>IF($D$4="C1 Wildlife",D9,IF($D$4="C2 Birds in Flight",E9,IF($D$4="C3 Landscape",F9,IF($D$4="Default Settings",G9,IF($D$4="Androo",H9,IF($D$4="Birds in Flight",I9,IF($D$4="Birds Perched",J9,IF($D$4="Fireworks",K9,IF($D$4="Landscape",L9,IF($D$4="Macro",M9,IF($D$4="People",N9,IF($D$4="Sports",O9,IF($D$4="Travel",P9,IF($D$4="Waterdrops",Q9,IF($D$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="V9" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D9,IF($E$4="C2 Birds in Flight",E9,IF($E$4="C3 Landscape",F9,IF($E$4="Default Settings",G9,IF($E$4="Androo",H9,IF($E$4="Birds in Flight",I9,IF($E$4="Birds Perched",J9,IF($E$4="Fireworks",K9,IF($E$4="Landscape",L9,IF($E$4="Macro",M9,IF($E$4="People",N9,IF($E$4="Sports",O9,IF($E$4="Travel",P9,IF($E$4="Waterdrops",Q9,IF($E$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>1/2500 sec.</x:v>
       </x:c>
-      <x:c r="V9" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D9,IF($F$4="C2 Birds in Flight",E9,IF($F$4="C3 Landscape",F9,IF($F$4="Default Settings",G9,IF($F$4="Birds in Flight",H9,IF($F$4="Birds Perched",I9,IF($F$4="Fireworks",J9,IF($F$4="Landscape",K9,IF($F$4="Macro",L9,IF($F$4="People",M9,IF($F$4="Sports",N9,IF($F$4="Travel",O9,IF($F$4="Waterdrops",P9,IF($F$4="Wildlife",Q9,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="W9" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D9,IF($G$4="C2 Birds in Flight",E9,IF($G$4="C3 Landscape",F9,IF($G$4="Default Settings",G9,IF($G$4="Birds in Flight",H9,IF($G$4="Birds Perched",I9,IF($G$4="Fireworks",J9,IF($G$4="Landscape",K9,IF($G$4="Macro",L9,IF($G$4="People",M9,IF($G$4="Sports",N9,IF($G$4="Travel",O9,IF($G$4="Waterdrops",P9,IF($G$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D9,IF($F$4="C2 Birds in Flight",E9,IF($F$4="C3 Landscape",F9,IF($F$4="Default Settings",G9,IF($F$4="Androo",H9,IF($F$4="Birds in Flight",I9,IF($F$4="Birds Perched",J9,IF($F$4="Fireworks",K9,IF($F$4="Landscape",L9,IF($F$4="Macro",M9,IF($F$4="People",N9,IF($F$4="Sports",O9,IF($F$4="Travel",P9,IF($F$4="Waterdrops",Q9,IF($F$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="X9" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D9,IF($H$4="C2 Birds in Flight",E9,IF($H$4="C3 Landscape",F9,IF($H$4="Default Settings",G9,IF($H$4="Birds in Flight",H9,IF($H$4="Birds Perched",I9,IF($H$4="Fireworks",J9,IF($H$4="Landscape",K9,IF($H$4="Macro",L9,IF($H$4="People",M9,IF($H$4="Sports",N9,IF($H$4="Travel",O9,IF($H$4="Waterdrops",P9,IF($H$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:f>IF($G$4="C1 Wildlife",D9,IF($G$4="C2 Birds in Flight",E9,IF($G$4="C3 Landscape",F9,IF($G$4="Default Settings",G9,IF($G$4="Androo",H9,IF($G$4="Birds in Flight",I9,IF($G$4="Birds Perched",J9,IF($G$4="Fireworks",K9,IF($G$4="Landscape",L9,IF($G$4="Macro",M9,IF($G$4="People",N9,IF($G$4="Sports",O9,IF($G$4="Travel",P9,IF($G$4="Waterdrops",Q9,IF($G$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Y9" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D9,IF($H$4="C2 Birds in Flight",E9,IF($H$4="C3 Landscape",F9,IF($H$4="Default Settings",G9,IF($H$4="Androo",H9,IF($H$4="Birds in Flight",I9,IF($H$4="Birds Perched",J9,IF($H$4="Fireworks",K9,IF($H$4="Landscape",L9,IF($H$4="Macro",M9,IF($H$4="People",N9,IF($H$4="Sports",O9,IF($H$4="Travel",P9,IF($H$4="Waterdrops",Q9,IF($H$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:v>1/200</x:v>
+      </x:c>
+      <x:c r="Z9" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D9,IF($I$4="C2 Birds in Flight",E9,IF($I$4="C3 Landscape",F9,IF($I$4="Default Settings",G9,IF($I$4="Androo",H9,IF($I$4="Birds in Flight",I9,IF($I$4="Birds Perched",J9,IF($I$4="Fireworks",K9,IF($I$4="Landscape",L9,IF($I$4="Macro",M9,IF($I$4="People",N9,IF($I$4="Sports",O9,IF($I$4="Travel",P9,IF($I$4="Waterdrops",Q9,IF($I$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>1/2000–1/4000</x:v>
       </x:c>
-      <x:c r="Y9" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D9,IF($I$4="C2 Birds in Flight",E9,IF($I$4="C3 Landscape",F9,IF($I$4="Default Settings",G9,IF($I$4="Birds in Flight",H9,IF($I$4="Birds Perched",I9,IF($I$4="Fireworks",J9,IF($I$4="Landscape",K9,IF($I$4="Macro",L9,IF($I$4="People",M9,IF($I$4="Sports",N9,IF($I$4="Travel",O9,IF($I$4="Waterdrops",P9,IF($I$4="Wildlife",Q9,""))))))))))))))</x:f>
+      <x:c r="AA9" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D9,IF($J$4="C2 Birds in Flight",E9,IF($J$4="C3 Landscape",F9,IF($J$4="Default Settings",G9,IF($J$4="Androo",H9,IF($J$4="Birds in Flight",I9,IF($J$4="Birds Perched",J9,IF($J$4="Fireworks",K9,IF($J$4="Landscape",L9,IF($J$4="Macro",M9,IF($J$4="People",N9,IF($J$4="Sports",O9,IF($J$4="Travel",P9,IF($J$4="Waterdrops",Q9,IF($J$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>1/500–1/1000</x:v>
       </x:c>
-      <x:c r="Z9" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D9,IF($J$4="C2 Birds in Flight",E9,IF($J$4="C3 Landscape",F9,IF($J$4="Default Settings",G9,IF($J$4="Birds in Flight",H9,IF($J$4="Birds Perched",I9,IF($J$4="Fireworks",J9,IF($J$4="Landscape",K9,IF($J$4="Macro",L9,IF($J$4="People",M9,IF($J$4="Sports",N9,IF($J$4="Travel",O9,IF($J$4="Waterdrops",P9,IF($J$4="Wildlife",Q9,""))))))))))))))</x:f>
+      <x:c r="AB9" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D9,IF($K$4="C2 Birds in Flight",E9,IF($K$4="C3 Landscape",F9,IF($K$4="Default Settings",G9,IF($K$4="Androo",H9,IF($K$4="Birds in Flight",I9,IF($K$4="Birds Perched",J9,IF($K$4="Fireworks",K9,IF($K$4="Landscape",L9,IF($K$4="Macro",M9,IF($K$4="People",N9,IF($K$4="Sports",O9,IF($K$4="Travel",P9,IF($K$4="Waterdrops",Q9,IF($K$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>2–6 s (start at 4 s)</x:v>
       </x:c>
-      <x:c r="AA9" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D9,IF($K$4="C2 Birds in Flight",E9,IF($K$4="C3 Landscape",F9,IF($K$4="Default Settings",G9,IF($K$4="Birds in Flight",H9,IF($K$4="Birds Perched",I9,IF($K$4="Fireworks",J9,IF($K$4="Landscape",K9,IF($K$4="Macro",L9,IF($K$4="People",M9,IF($K$4="Sports",N9,IF($K$4="Travel",O9,IF($K$4="Waterdrops",P9,IF($K$4="Wildlife",Q9,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AB9" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D9,IF($L$4="C2 Birds in Flight",E9,IF($L$4="C3 Landscape",F9,IF($L$4="Default Settings",G9,IF($L$4="Birds in Flight",H9,IF($L$4="Birds Perched",I9,IF($L$4="Fireworks",J9,IF($L$4="Landscape",K9,IF($L$4="Macro",L9,IF($L$4="People",M9,IF($L$4="Sports",N9,IF($L$4="Travel",O9,IF($L$4="Waterdrops",P9,IF($L$4="Wildlife",Q9,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="AC9" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D9,IF($M$4="C2 Birds in Flight",E9,IF($M$4="C3 Landscape",F9,IF($M$4="Default Settings",G9,IF($M$4="Birds in Flight",H9,IF($M$4="Birds Perched",I9,IF($M$4="Fireworks",J9,IF($M$4="Landscape",K9,IF($M$4="Macro",L9,IF($M$4="People",M9,IF($M$4="Sports",N9,IF($M$4="Travel",O9,IF($M$4="Waterdrops",P9,IF($M$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D9,IF($L$4="C2 Birds in Flight",E9,IF($L$4="C3 Landscape",F9,IF($L$4="Default Settings",G9,IF($L$4="Androo",H9,IF($L$4="Birds in Flight",I9,IF($L$4="Birds Perched",J9,IF($L$4="Fireworks",K9,IF($L$4="Landscape",L9,IF($L$4="Macro",M9,IF($L$4="People",N9,IF($L$4="Sports",O9,IF($L$4="Travel",P9,IF($L$4="Waterdrops",Q9,IF($L$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AD9" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D9,IF($M$4="C2 Birds in Flight",E9,IF($M$4="C3 Landscape",F9,IF($M$4="Default Settings",G9,IF($M$4="Androo",H9,IF($M$4="Birds in Flight",I9,IF($M$4="Birds Perched",J9,IF($M$4="Fireworks",K9,IF($M$4="Landscape",L9,IF($M$4="Macro",M9,IF($M$4="People",N9,IF($M$4="Sports",O9,IF($M$4="Travel",P9,IF($M$4="Waterdrops",Q9,IF($M$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AE9" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D9,IF($N$4="C2 Birds in Flight",E9,IF($N$4="C3 Landscape",F9,IF($N$4="Default Settings",G9,IF($N$4="Androo",H9,IF($N$4="Birds in Flight",I9,IF($N$4="Birds Perched",J9,IF($N$4="Fireworks",K9,IF($N$4="Landscape",L9,IF($N$4="Macro",M9,IF($N$4="People",N9,IF($N$4="Sports",O9,IF($N$4="Travel",P9,IF($N$4="Waterdrops",Q9,IF($N$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
       </x:c>
-      <x:c r="AD9" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D9,IF($N$4="C2 Birds in Flight",E9,IF($N$4="C3 Landscape",F9,IF($N$4="Default Settings",G9,IF($N$4="Birds in Flight",H9,IF($N$4="Birds Perched",I9,IF($N$4="Fireworks",J9,IF($N$4="Landscape",K9,IF($N$4="Macro",L9,IF($N$4="People",M9,IF($N$4="Sports",N9,IF($N$4="Travel",O9,IF($N$4="Waterdrops",P9,IF($N$4="Wildlife",Q9,""))))))))))))))</x:f>
+      <x:c r="AF9" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D9,IF($O$4="C2 Birds in Flight",E9,IF($O$4="C3 Landscape",F9,IF($O$4="Default Settings",G9,IF($O$4="Androo",H9,IF($O$4="Birds in Flight",I9,IF($O$4="Birds Perched",J9,IF($O$4="Fireworks",K9,IF($O$4="Landscape",L9,IF($O$4="Macro",M9,IF($O$4="People",N9,IF($O$4="Sports",O9,IF($O$4="Travel",P9,IF($O$4="Waterdrops",Q9,IF($O$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
       </x:c>
-      <x:c r="AE9" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D9,IF($O$4="C2 Birds in Flight",E9,IF($O$4="C3 Landscape",F9,IF($O$4="Default Settings",G9,IF($O$4="Birds in Flight",H9,IF($O$4="Birds Perched",I9,IF($O$4="Fireworks",J9,IF($O$4="Landscape",K9,IF($O$4="Macro",L9,IF($O$4="People",M9,IF($O$4="Sports",N9,IF($O$4="Travel",O9,IF($O$4="Waterdrops",P9,IF($O$4="Wildlife",Q9,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AF9" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D9,IF($P$4="C2 Birds in Flight",E9,IF($P$4="C3 Landscape",F9,IF($P$4="Default Settings",G9,IF($P$4="Birds in Flight",H9,IF($P$4="Birds Perched",I9,IF($P$4="Fireworks",J9,IF($P$4="Landscape",K9,IF($P$4="Macro",L9,IF($P$4="People",M9,IF($P$4="Sports",N9,IF($P$4="Travel",O9,IF($P$4="Waterdrops",P9,IF($P$4="Wildlife",Q9,""))))))))))))))</x:f>
+      <x:c r="AG9" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D9,IF($P$4="C2 Birds in Flight",E9,IF($P$4="C3 Landscape",F9,IF($P$4="Default Settings",G9,IF($P$4="Androo",H9,IF($P$4="Birds in Flight",I9,IF($P$4="Birds Perched",J9,IF($P$4="Fireworks",K9,IF($P$4="Landscape",L9,IF($P$4="Macro",M9,IF($P$4="People",N9,IF($P$4="Sports",O9,IF($P$4="Travel",P9,IF($P$4="Waterdrops",Q9,IF($P$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AH9" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D9,IF($Q$4="C2 Birds in Flight",E9,IF($Q$4="C3 Landscape",F9,IF($Q$4="Default Settings",G9,IF($Q$4="Androo",H9,IF($Q$4="Birds in Flight",I9,IF($Q$4="Birds Perched",J9,IF($Q$4="Fireworks",K9,IF($Q$4="Landscape",L9,IF($Q$4="Macro",M9,IF($Q$4="People",N9,IF($Q$4="Sports",O9,IF($Q$4="Travel",P9,IF($Q$4="Waterdrops",Q9,IF($Q$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>1/200</x:v>
       </x:c>
-      <x:c r="AG9" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D9,IF($Q$4="C2 Birds in Flight",E9,IF($Q$4="C3 Landscape",F9,IF($Q$4="Default Settings",G9,IF($Q$4="Birds in Flight",H9,IF($Q$4="Birds Perched",I9,IF($Q$4="Fireworks",J9,IF($Q$4="Landscape",K9,IF($Q$4="Macro",L9,IF($Q$4="People",M9,IF($Q$4="Sports",N9,IF($Q$4="Travel",O9,IF($Q$4="Waterdrops",P9,IF($Q$4="Wildlife",Q9,""))))))))))))))</x:f>
+      <x:c r="AI9" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D9,IF($R$4="C2 Birds in Flight",E9,IF($R$4="C3 Landscape",F9,IF($R$4="Default Settings",G9,IF($R$4="Androo",H9,IF($R$4="Birds in Flight",I9,IF($R$4="Birds Perched",J9,IF($R$4="Fireworks",K9,IF($R$4="Landscape",L9,IF($R$4="Macro",M9,IF($R$4="People",N9,IF($R$4="Sports",O9,IF($R$4="Travel",P9,IF($R$4="Waterdrops",Q9,IF($R$4="Wildlife",R9,"")))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
@@ -1337,7 +1386,7 @@
         <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="I10" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="J10" s="17" t="str">
         <x:v>EFCS</x:v>
@@ -1349,80 +1398,87 @@
         <x:v>EFCS</x:v>
       </x:c>
       <x:c r="M10" s="17" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="N10" s="17" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="O10" s="17" t="str">
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="P10" s="17" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="P10" s="17" t="str">
+      <x:c r="Q10" s="17" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="Q10" s="17" t="str">
+      <x:c r="R10" s="17" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="R10" s="20" t="n">
+      <x:c r="S10" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="S10" s="20" t="n">
+      <x:c r="T10" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="T10" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D10,IF($D$4="C2 Birds in Flight",E10,IF($D$4="C3 Landscape",F10,IF($D$4="Default Settings",G10,IF($D$4="Birds in Flight",H10,IF($D$4="Birds Perched",I10,IF($D$4="Fireworks",J10,IF($D$4="Landscape",K10,IF($D$4="Macro",L10,IF($D$4="People",M10,IF($D$4="Sports",N10,IF($D$4="Travel",O10,IF($D$4="Waterdrops",P10,IF($D$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="U10" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D10,IF($D$4="C2 Birds in Flight",E10,IF($D$4="C3 Landscape",F10,IF($D$4="Default Settings",G10,IF($D$4="Androo",H10,IF($D$4="Birds in Flight",I10,IF($D$4="Birds Perched",J10,IF($D$4="Fireworks",K10,IF($D$4="Landscape",L10,IF($D$4="Macro",M10,IF($D$4="People",N10,IF($D$4="Sports",O10,IF($D$4="Travel",P10,IF($D$4="Waterdrops",Q10,IF($D$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="U10" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D10,IF($E$4="C2 Birds in Flight",E10,IF($E$4="C3 Landscape",F10,IF($E$4="Default Settings",G10,IF($E$4="Birds in Flight",H10,IF($E$4="Birds Perched",I10,IF($E$4="Fireworks",J10,IF($E$4="Landscape",K10,IF($E$4="Macro",L10,IF($E$4="People",M10,IF($E$4="Sports",N10,IF($E$4="Travel",O10,IF($E$4="Waterdrops",P10,IF($E$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="V10" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D10,IF($E$4="C2 Birds in Flight",E10,IF($E$4="C3 Landscape",F10,IF($E$4="Default Settings",G10,IF($E$4="Androo",H10,IF($E$4="Birds in Flight",I10,IF($E$4="Birds Perched",J10,IF($E$4="Fireworks",K10,IF($E$4="Landscape",L10,IF($E$4="Macro",M10,IF($E$4="People",N10,IF($E$4="Sports",O10,IF($E$4="Travel",P10,IF($E$4="Waterdrops",Q10,IF($E$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="V10" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D10,IF($F$4="C2 Birds in Flight",E10,IF($F$4="C3 Landscape",F10,IF($F$4="Default Settings",G10,IF($F$4="Birds in Flight",H10,IF($F$4="Birds Perched",I10,IF($F$4="Fireworks",J10,IF($F$4="Landscape",K10,IF($F$4="Macro",L10,IF($F$4="People",M10,IF($F$4="Sports",N10,IF($F$4="Travel",O10,IF($F$4="Waterdrops",P10,IF($F$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="W10" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D10,IF($F$4="C2 Birds in Flight",E10,IF($F$4="C3 Landscape",F10,IF($F$4="Default Settings",G10,IF($F$4="Androo",H10,IF($F$4="Birds in Flight",I10,IF($F$4="Birds Perched",J10,IF($F$4="Fireworks",K10,IF($F$4="Landscape",L10,IF($F$4="Macro",M10,IF($F$4="People",N10,IF($F$4="Sports",O10,IF($F$4="Travel",P10,IF($F$4="Waterdrops",Q10,IF($F$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="W10" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D10,IF($G$4="C2 Birds in Flight",E10,IF($G$4="C3 Landscape",F10,IF($G$4="Default Settings",G10,IF($G$4="Birds in Flight",H10,IF($G$4="Birds Perched",I10,IF($G$4="Fireworks",J10,IF($G$4="Landscape",K10,IF($G$4="Macro",L10,IF($G$4="People",M10,IF($G$4="Sports",N10,IF($G$4="Travel",O10,IF($G$4="Waterdrops",P10,IF($G$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="X10" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D10,IF($G$4="C2 Birds in Flight",E10,IF($G$4="C3 Landscape",F10,IF($G$4="Default Settings",G10,IF($G$4="Androo",H10,IF($G$4="Birds in Flight",I10,IF($G$4="Birds Perched",J10,IF($G$4="Fireworks",K10,IF($G$4="Landscape",L10,IF($G$4="Macro",M10,IF($G$4="People",N10,IF($G$4="Sports",O10,IF($G$4="Travel",P10,IF($G$4="Waterdrops",Q10,IF($G$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="X10" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D10,IF($H$4="C2 Birds in Flight",E10,IF($H$4="C3 Landscape",F10,IF($H$4="Default Settings",G10,IF($H$4="Birds in Flight",H10,IF($H$4="Birds Perched",I10,IF($H$4="Fireworks",J10,IF($H$4="Landscape",K10,IF($H$4="Macro",L10,IF($H$4="People",M10,IF($H$4="Sports",N10,IF($H$4="Travel",O10,IF($H$4="Waterdrops",P10,IF($H$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="Y10" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D10,IF($H$4="C2 Birds in Flight",E10,IF($H$4="C3 Landscape",F10,IF($H$4="Default Settings",G10,IF($H$4="Androo",H10,IF($H$4="Birds in Flight",I10,IF($H$4="Birds Perched",J10,IF($H$4="Fireworks",K10,IF($H$4="Landscape",L10,IF($H$4="Macro",M10,IF($H$4="People",N10,IF($H$4="Sports",O10,IF($H$4="Travel",P10,IF($H$4="Waterdrops",Q10,IF($H$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="Y10" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D10,IF($I$4="C2 Birds in Flight",E10,IF($I$4="C3 Landscape",F10,IF($I$4="Default Settings",G10,IF($I$4="Birds in Flight",H10,IF($I$4="Birds Perched",I10,IF($I$4="Fireworks",J10,IF($I$4="Landscape",K10,IF($I$4="Macro",L10,IF($I$4="People",M10,IF($I$4="Sports",N10,IF($I$4="Travel",O10,IF($I$4="Waterdrops",P10,IF($I$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="Z10" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D10,IF($I$4="C2 Birds in Flight",E10,IF($I$4="C3 Landscape",F10,IF($I$4="Default Settings",G10,IF($I$4="Androo",H10,IF($I$4="Birds in Flight",I10,IF($I$4="Birds Perched",J10,IF($I$4="Fireworks",K10,IF($I$4="Landscape",L10,IF($I$4="Macro",M10,IF($I$4="People",N10,IF($I$4="Sports",O10,IF($I$4="Travel",P10,IF($I$4="Waterdrops",Q10,IF($I$4="Wildlife",R10,"")))))))))))))))</x:f>
+        <x:v>Mechanical</x:v>
+      </x:c>
+      <x:c r="AA10" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D10,IF($J$4="C2 Birds in Flight",E10,IF($J$4="C3 Landscape",F10,IF($J$4="Default Settings",G10,IF($J$4="Androo",H10,IF($J$4="Birds in Flight",I10,IF($J$4="Birds Perched",J10,IF($J$4="Fireworks",K10,IF($J$4="Landscape",L10,IF($J$4="Macro",M10,IF($J$4="People",N10,IF($J$4="Sports",O10,IF($J$4="Travel",P10,IF($J$4="Waterdrops",Q10,IF($J$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="Z10" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D10,IF($J$4="C2 Birds in Flight",E10,IF($J$4="C3 Landscape",F10,IF($J$4="Default Settings",G10,IF($J$4="Birds in Flight",H10,IF($J$4="Birds Perched",I10,IF($J$4="Fireworks",J10,IF($J$4="Landscape",K10,IF($J$4="Macro",L10,IF($J$4="People",M10,IF($J$4="Sports",N10,IF($J$4="Travel",O10,IF($J$4="Waterdrops",P10,IF($J$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AB10" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D10,IF($K$4="C2 Birds in Flight",E10,IF($K$4="C3 Landscape",F10,IF($K$4="Default Settings",G10,IF($K$4="Androo",H10,IF($K$4="Birds in Flight",I10,IF($K$4="Birds Perched",J10,IF($K$4="Fireworks",K10,IF($K$4="Landscape",L10,IF($K$4="Macro",M10,IF($K$4="People",N10,IF($K$4="Sports",O10,IF($K$4="Travel",P10,IF($K$4="Waterdrops",Q10,IF($K$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="AA10" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D10,IF($K$4="C2 Birds in Flight",E10,IF($K$4="C3 Landscape",F10,IF($K$4="Default Settings",G10,IF($K$4="Birds in Flight",H10,IF($K$4="Birds Perched",I10,IF($K$4="Fireworks",J10,IF($K$4="Landscape",K10,IF($K$4="Macro",L10,IF($K$4="People",M10,IF($K$4="Sports",N10,IF($K$4="Travel",O10,IF($K$4="Waterdrops",P10,IF($K$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AC10" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D10,IF($L$4="C2 Birds in Flight",E10,IF($L$4="C3 Landscape",F10,IF($L$4="Default Settings",G10,IF($L$4="Androo",H10,IF($L$4="Birds in Flight",I10,IF($L$4="Birds Perched",J10,IF($L$4="Fireworks",K10,IF($L$4="Landscape",L10,IF($L$4="Macro",M10,IF($L$4="People",N10,IF($L$4="Sports",O10,IF($L$4="Travel",P10,IF($L$4="Waterdrops",Q10,IF($L$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="AB10" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D10,IF($L$4="C2 Birds in Flight",E10,IF($L$4="C3 Landscape",F10,IF($L$4="Default Settings",G10,IF($L$4="Birds in Flight",H10,IF($L$4="Birds Perched",I10,IF($L$4="Fireworks",J10,IF($L$4="Landscape",K10,IF($L$4="Macro",L10,IF($L$4="People",M10,IF($L$4="Sports",N10,IF($L$4="Travel",O10,IF($L$4="Waterdrops",P10,IF($L$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AD10" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D10,IF($M$4="C2 Birds in Flight",E10,IF($M$4="C3 Landscape",F10,IF($M$4="Default Settings",G10,IF($M$4="Androo",H10,IF($M$4="Birds in Flight",I10,IF($M$4="Birds Perched",J10,IF($M$4="Fireworks",K10,IF($M$4="Landscape",L10,IF($M$4="Macro",M10,IF($M$4="People",N10,IF($M$4="Sports",O10,IF($M$4="Travel",P10,IF($M$4="Waterdrops",Q10,IF($M$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="AC10" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D10,IF($M$4="C2 Birds in Flight",E10,IF($M$4="C3 Landscape",F10,IF($M$4="Default Settings",G10,IF($M$4="Birds in Flight",H10,IF($M$4="Birds Perched",I10,IF($M$4="Fireworks",J10,IF($M$4="Landscape",K10,IF($M$4="Macro",L10,IF($M$4="People",M10,IF($M$4="Sports",N10,IF($M$4="Travel",O10,IF($M$4="Waterdrops",P10,IF($M$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AE10" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D10,IF($N$4="C2 Birds in Flight",E10,IF($N$4="C3 Landscape",F10,IF($N$4="Default Settings",G10,IF($N$4="Androo",H10,IF($N$4="Birds in Flight",I10,IF($N$4="Birds Perched",J10,IF($N$4="Fireworks",K10,IF($N$4="Landscape",L10,IF($N$4="Macro",M10,IF($N$4="People",N10,IF($N$4="Sports",O10,IF($N$4="Travel",P10,IF($N$4="Waterdrops",Q10,IF($N$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="AD10" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D10,IF($N$4="C2 Birds in Flight",E10,IF($N$4="C3 Landscape",F10,IF($N$4="Default Settings",G10,IF($N$4="Birds in Flight",H10,IF($N$4="Birds Perched",I10,IF($N$4="Fireworks",J10,IF($N$4="Landscape",K10,IF($N$4="Macro",L10,IF($N$4="People",M10,IF($N$4="Sports",N10,IF($N$4="Travel",O10,IF($N$4="Waterdrops",P10,IF($N$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AF10" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D10,IF($O$4="C2 Birds in Flight",E10,IF($O$4="C3 Landscape",F10,IF($O$4="Default Settings",G10,IF($O$4="Androo",H10,IF($O$4="Birds in Flight",I10,IF($O$4="Birds Perched",J10,IF($O$4="Fireworks",K10,IF($O$4="Landscape",L10,IF($O$4="Macro",M10,IF($O$4="People",N10,IF($O$4="Sports",O10,IF($O$4="Travel",P10,IF($O$4="Waterdrops",Q10,IF($O$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="AE10" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D10,IF($O$4="C2 Birds in Flight",E10,IF($O$4="C3 Landscape",F10,IF($O$4="Default Settings",G10,IF($O$4="Birds in Flight",H10,IF($O$4="Birds Perched",I10,IF($O$4="Fireworks",J10,IF($O$4="Landscape",K10,IF($O$4="Macro",L10,IF($O$4="People",M10,IF($O$4="Sports",N10,IF($O$4="Travel",O10,IF($O$4="Waterdrops",P10,IF($O$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AG10" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D10,IF($P$4="C2 Birds in Flight",E10,IF($P$4="C3 Landscape",F10,IF($P$4="Default Settings",G10,IF($P$4="Androo",H10,IF($P$4="Birds in Flight",I10,IF($P$4="Birds Perched",J10,IF($P$4="Fireworks",K10,IF($P$4="Landscape",L10,IF($P$4="Macro",M10,IF($P$4="People",N10,IF($P$4="Sports",O10,IF($P$4="Travel",P10,IF($P$4="Waterdrops",Q10,IF($P$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="AF10" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D10,IF($P$4="C2 Birds in Flight",E10,IF($P$4="C3 Landscape",F10,IF($P$4="Default Settings",G10,IF($P$4="Birds in Flight",H10,IF($P$4="Birds Perched",I10,IF($P$4="Fireworks",J10,IF($P$4="Landscape",K10,IF($P$4="Macro",L10,IF($P$4="People",M10,IF($P$4="Sports",N10,IF($P$4="Travel",O10,IF($P$4="Waterdrops",P10,IF($P$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AH10" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D10,IF($Q$4="C2 Birds in Flight",E10,IF($Q$4="C3 Landscape",F10,IF($Q$4="Default Settings",G10,IF($Q$4="Androo",H10,IF($Q$4="Birds in Flight",I10,IF($Q$4="Birds Perched",J10,IF($Q$4="Fireworks",K10,IF($Q$4="Landscape",L10,IF($Q$4="Macro",M10,IF($Q$4="People",N10,IF($Q$4="Sports",O10,IF($Q$4="Travel",P10,IF($Q$4="Waterdrops",Q10,IF($Q$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="AG10" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D10,IF($Q$4="C2 Birds in Flight",E10,IF($Q$4="C3 Landscape",F10,IF($Q$4="Default Settings",G10,IF($Q$4="Birds in Flight",H10,IF($Q$4="Birds Perched",I10,IF($Q$4="Fireworks",J10,IF($Q$4="Landscape",K10,IF($Q$4="Macro",L10,IF($Q$4="People",M10,IF($Q$4="Sports",N10,IF($Q$4="Travel",O10,IF($Q$4="Waterdrops",P10,IF($Q$4="Wildlife",Q10,""))))))))))))))</x:f>
+      <x:c r="AI10" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D10,IF($R$4="C2 Birds in Flight",E10,IF($R$4="C3 Landscape",F10,IF($R$4="Default Settings",G10,IF($R$4="Androo",H10,IF($R$4="Birds in Flight",I10,IF($R$4="Birds Perched",J10,IF($R$4="Fireworks",K10,IF($R$4="Landscape",L10,IF($R$4="Macro",M10,IF($R$4="People",N10,IF($R$4="Sports",O10,IF($R$4="Travel",P10,IF($R$4="Waterdrops",Q10,IF($R$4="Wildlife",R10,"")))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
     </x:row>
@@ -1448,96 +1504,103 @@
       <x:c r="G11" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="H11" s="17" t="str">
-        <x:v>Auto</x:v>
+      <x:c r="H11" s="17" t="n">
+        <x:v>5.89</x:v>
       </x:c>
       <x:c r="I11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="str">
         <x:v>f/8</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="str">
+      <x:c r="K11" s="17" t="str">
         <x:v>f/8–f/11</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="str">
+      <x:c r="L11" s="17" t="str">
         <x:v>f/8–f/11; bracket before f/16</x:v>
       </x:c>
-      <x:c r="L11" s="17" t="str">
+      <x:c r="M11" s="17" t="str">
         <x:v>f/8</x:v>
       </x:c>
-      <x:c r="M11" s="17" t="str">
+      <x:c r="N11" s="17" t="str">
         <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
       </x:c>
-      <x:c r="N11" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="O11" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="P11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Q11" s="17" t="str">
         <x:v>f/8–f/11</x:v>
       </x:c>
-      <x:c r="Q11" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="R11" s="20" t="n">
+      <x:c r="R11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="S11" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="n">
+      <x:c r="T11" s="20" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="T11" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D11,IF($D$4="C2 Birds in Flight",E11,IF($D$4="C3 Landscape",F11,IF($D$4="Default Settings",G11,IF($D$4="Birds in Flight",H11,IF($D$4="Birds Perched",I11,IF($D$4="Fireworks",J11,IF($D$4="Landscape",K11,IF($D$4="Macro",L11,IF($D$4="People",M11,IF($D$4="Sports",N11,IF($D$4="Travel",O11,IF($D$4="Waterdrops",P11,IF($D$4="Wildlife",Q11,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="U11" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D11,IF($E$4="C2 Birds in Flight",E11,IF($E$4="C3 Landscape",F11,IF($E$4="Default Settings",G11,IF($E$4="Birds in Flight",H11,IF($E$4="Birds Perched",I11,IF($E$4="Fireworks",J11,IF($E$4="Landscape",K11,IF($E$4="Macro",L11,IF($E$4="People",M11,IF($E$4="Sports",N11,IF($E$4="Travel",O11,IF($E$4="Waterdrops",P11,IF($E$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:f>IF($D$4="C1 Wildlife",D11,IF($D$4="C2 Birds in Flight",E11,IF($D$4="C3 Landscape",F11,IF($D$4="Default Settings",G11,IF($D$4="Androo",H11,IF($D$4="Birds in Flight",I11,IF($D$4="Birds Perched",J11,IF($D$4="Fireworks",K11,IF($D$4="Landscape",L11,IF($D$4="Macro",M11,IF($D$4="People",N11,IF($D$4="Sports",O11,IF($D$4="Travel",P11,IF($D$4="Waterdrops",Q11,IF($D$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="V11" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D11,IF($F$4="C2 Birds in Flight",E11,IF($F$4="C3 Landscape",F11,IF($F$4="Default Settings",G11,IF($F$4="Birds in Flight",H11,IF($F$4="Birds Perched",I11,IF($F$4="Fireworks",J11,IF($F$4="Landscape",K11,IF($F$4="Macro",L11,IF($F$4="People",M11,IF($F$4="Sports",N11,IF($F$4="Travel",O11,IF($F$4="Waterdrops",P11,IF($F$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D11,IF($E$4="C2 Birds in Flight",E11,IF($E$4="C3 Landscape",F11,IF($E$4="Default Settings",G11,IF($E$4="Androo",H11,IF($E$4="Birds in Flight",I11,IF($E$4="Birds Perched",J11,IF($E$4="Fireworks",K11,IF($E$4="Landscape",L11,IF($E$4="Macro",M11,IF($E$4="People",N11,IF($E$4="Sports",O11,IF($E$4="Travel",P11,IF($E$4="Waterdrops",Q11,IF($E$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="W11" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D11,IF($F$4="C2 Birds in Flight",E11,IF($F$4="C3 Landscape",F11,IF($F$4="Default Settings",G11,IF($F$4="Androo",H11,IF($F$4="Birds in Flight",I11,IF($F$4="Birds Perched",J11,IF($F$4="Fireworks",K11,IF($F$4="Landscape",L11,IF($F$4="Macro",M11,IF($F$4="People",N11,IF($F$4="Sports",O11,IF($F$4="Travel",P11,IF($F$4="Waterdrops",Q11,IF($F$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/9</x:v>
       </x:c>
-      <x:c r="W11" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D11,IF($G$4="C2 Birds in Flight",E11,IF($G$4="C3 Landscape",F11,IF($G$4="Default Settings",G11,IF($G$4="Birds in Flight",H11,IF($G$4="Birds Perched",I11,IF($G$4="Fireworks",J11,IF($G$4="Landscape",K11,IF($G$4="Macro",L11,IF($G$4="People",M11,IF($G$4="Sports",N11,IF($G$4="Travel",O11,IF($G$4="Waterdrops",P11,IF($G$4="Wildlife",Q11,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="X11" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D11,IF($H$4="C2 Birds in Flight",E11,IF($H$4="C3 Landscape",F11,IF($H$4="Default Settings",G11,IF($H$4="Birds in Flight",H11,IF($H$4="Birds Perched",I11,IF($H$4="Fireworks",J11,IF($H$4="Landscape",K11,IF($H$4="Macro",L11,IF($H$4="People",M11,IF($H$4="Sports",N11,IF($H$4="Travel",O11,IF($H$4="Waterdrops",P11,IF($H$4="Wildlife",Q11,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Y11" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D11,IF($I$4="C2 Birds in Flight",E11,IF($I$4="C3 Landscape",F11,IF($I$4="Default Settings",G11,IF($I$4="Birds in Flight",H11,IF($I$4="Birds Perched",I11,IF($I$4="Fireworks",J11,IF($I$4="Landscape",K11,IF($I$4="Macro",L11,IF($I$4="People",M11,IF($I$4="Sports",N11,IF($I$4="Travel",O11,IF($I$4="Waterdrops",P11,IF($I$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:f>IF($G$4="C1 Wildlife",D11,IF($G$4="C2 Birds in Flight",E11,IF($G$4="C3 Landscape",F11,IF($G$4="Default Settings",G11,IF($G$4="Androo",H11,IF($G$4="Birds in Flight",I11,IF($G$4="Birds Perched",J11,IF($G$4="Fireworks",K11,IF($G$4="Landscape",L11,IF($G$4="Macro",M11,IF($G$4="People",N11,IF($G$4="Sports",O11,IF($G$4="Travel",P11,IF($G$4="Waterdrops",Q11,IF($G$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Y11" s="38" t="n">
+        <x:f>IF($H$4="C1 Wildlife",D11,IF($H$4="C2 Birds in Flight",E11,IF($H$4="C3 Landscape",F11,IF($H$4="Default Settings",G11,IF($H$4="Androo",H11,IF($H$4="Birds in Flight",I11,IF($H$4="Birds Perched",J11,IF($H$4="Fireworks",K11,IF($H$4="Landscape",L11,IF($H$4="Macro",M11,IF($H$4="People",N11,IF($H$4="Sports",O11,IF($H$4="Travel",P11,IF($H$4="Waterdrops",Q11,IF($H$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:v>5.89</x:v>
+      </x:c>
+      <x:c r="Z11" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D11,IF($I$4="C2 Birds in Flight",E11,IF($I$4="C3 Landscape",F11,IF($I$4="Default Settings",G11,IF($I$4="Androo",H11,IF($I$4="Birds in Flight",I11,IF($I$4="Birds Perched",J11,IF($I$4="Fireworks",K11,IF($I$4="Landscape",L11,IF($I$4="Macro",M11,IF($I$4="People",N11,IF($I$4="Sports",O11,IF($I$4="Travel",P11,IF($I$4="Waterdrops",Q11,IF($I$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AA11" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D11,IF($J$4="C2 Birds in Flight",E11,IF($J$4="C3 Landscape",F11,IF($J$4="Default Settings",G11,IF($J$4="Androo",H11,IF($J$4="Birds in Flight",I11,IF($J$4="Birds Perched",J11,IF($J$4="Fireworks",K11,IF($J$4="Landscape",L11,IF($J$4="Macro",M11,IF($J$4="People",N11,IF($J$4="Sports",O11,IF($J$4="Travel",P11,IF($J$4="Waterdrops",Q11,IF($J$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/8</x:v>
       </x:c>
-      <x:c r="Z11" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D11,IF($J$4="C2 Birds in Flight",E11,IF($J$4="C3 Landscape",F11,IF($J$4="Default Settings",G11,IF($J$4="Birds in Flight",H11,IF($J$4="Birds Perched",I11,IF($J$4="Fireworks",J11,IF($J$4="Landscape",K11,IF($J$4="Macro",L11,IF($J$4="People",M11,IF($J$4="Sports",N11,IF($J$4="Travel",O11,IF($J$4="Waterdrops",P11,IF($J$4="Wildlife",Q11,""))))))))))))))</x:f>
+      <x:c r="AB11" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D11,IF($K$4="C2 Birds in Flight",E11,IF($K$4="C3 Landscape",F11,IF($K$4="Default Settings",G11,IF($K$4="Androo",H11,IF($K$4="Birds in Flight",I11,IF($K$4="Birds Perched",J11,IF($K$4="Fireworks",K11,IF($K$4="Landscape",L11,IF($K$4="Macro",M11,IF($K$4="People",N11,IF($K$4="Sports",O11,IF($K$4="Travel",P11,IF($K$4="Waterdrops",Q11,IF($K$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/8–f/11</x:v>
       </x:c>
-      <x:c r="AA11" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D11,IF($K$4="C2 Birds in Flight",E11,IF($K$4="C3 Landscape",F11,IF($K$4="Default Settings",G11,IF($K$4="Birds in Flight",H11,IF($K$4="Birds Perched",I11,IF($K$4="Fireworks",J11,IF($K$4="Landscape",K11,IF($K$4="Macro",L11,IF($K$4="People",M11,IF($K$4="Sports",N11,IF($K$4="Travel",O11,IF($K$4="Waterdrops",P11,IF($K$4="Wildlife",Q11,""))))))))))))))</x:f>
+      <x:c r="AC11" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D11,IF($L$4="C2 Birds in Flight",E11,IF($L$4="C3 Landscape",F11,IF($L$4="Default Settings",G11,IF($L$4="Androo",H11,IF($L$4="Birds in Flight",I11,IF($L$4="Birds Perched",J11,IF($L$4="Fireworks",K11,IF($L$4="Landscape",L11,IF($L$4="Macro",M11,IF($L$4="People",N11,IF($L$4="Sports",O11,IF($L$4="Travel",P11,IF($L$4="Waterdrops",Q11,IF($L$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/8–f/11; bracket before f/16</x:v>
       </x:c>
-      <x:c r="AB11" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D11,IF($L$4="C2 Birds in Flight",E11,IF($L$4="C3 Landscape",F11,IF($L$4="Default Settings",G11,IF($L$4="Birds in Flight",H11,IF($L$4="Birds Perched",I11,IF($L$4="Fireworks",J11,IF($L$4="Landscape",K11,IF($L$4="Macro",L11,IF($L$4="People",M11,IF($L$4="Sports",N11,IF($L$4="Travel",O11,IF($L$4="Waterdrops",P11,IF($L$4="Wildlife",Q11,""))))))))))))))</x:f>
+      <x:c r="AD11" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D11,IF($M$4="C2 Birds in Flight",E11,IF($M$4="C3 Landscape",F11,IF($M$4="Default Settings",G11,IF($M$4="Androo",H11,IF($M$4="Birds in Flight",I11,IF($M$4="Birds Perched",J11,IF($M$4="Fireworks",K11,IF($M$4="Landscape",L11,IF($M$4="Macro",M11,IF($M$4="People",N11,IF($M$4="Sports",O11,IF($M$4="Travel",P11,IF($M$4="Waterdrops",Q11,IF($M$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/8</x:v>
       </x:c>
-      <x:c r="AC11" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D11,IF($M$4="C2 Birds in Flight",E11,IF($M$4="C3 Landscape",F11,IF($M$4="Default Settings",G11,IF($M$4="Birds in Flight",H11,IF($M$4="Birds Perched",I11,IF($M$4="Fireworks",J11,IF($M$4="Landscape",K11,IF($M$4="Macro",L11,IF($M$4="People",M11,IF($M$4="Sports",N11,IF($M$4="Travel",O11,IF($M$4="Waterdrops",P11,IF($M$4="Wildlife",Q11,""))))))))))))))</x:f>
+      <x:c r="AE11" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D11,IF($N$4="C2 Birds in Flight",E11,IF($N$4="C3 Landscape",F11,IF($N$4="Default Settings",G11,IF($N$4="Androo",H11,IF($N$4="Birds in Flight",I11,IF($N$4="Birds Perched",J11,IF($N$4="Fireworks",K11,IF($N$4="Landscape",L11,IF($N$4="Macro",M11,IF($N$4="People",N11,IF($N$4="Sports",O11,IF($N$4="Travel",P11,IF($N$4="Waterdrops",Q11,IF($N$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
       </x:c>
-      <x:c r="AD11" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D11,IF($N$4="C2 Birds in Flight",E11,IF($N$4="C3 Landscape",F11,IF($N$4="Default Settings",G11,IF($N$4="Birds in Flight",H11,IF($N$4="Birds Perched",I11,IF($N$4="Fireworks",J11,IF($N$4="Landscape",K11,IF($N$4="Macro",L11,IF($N$4="People",M11,IF($N$4="Sports",N11,IF($N$4="Travel",O11,IF($N$4="Waterdrops",P11,IF($N$4="Wildlife",Q11,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AE11" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D11,IF($O$4="C2 Birds in Flight",E11,IF($O$4="C3 Landscape",F11,IF($O$4="Default Settings",G11,IF($O$4="Birds in Flight",H11,IF($O$4="Birds Perched",I11,IF($O$4="Fireworks",J11,IF($O$4="Landscape",K11,IF($O$4="Macro",L11,IF($O$4="People",M11,IF($O$4="Sports",N11,IF($O$4="Travel",O11,IF($O$4="Waterdrops",P11,IF($O$4="Wildlife",Q11,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="AF11" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D11,IF($P$4="C2 Birds in Flight",E11,IF($P$4="C3 Landscape",F11,IF($P$4="Default Settings",G11,IF($P$4="Birds in Flight",H11,IF($P$4="Birds Perched",I11,IF($P$4="Fireworks",J11,IF($P$4="Landscape",K11,IF($P$4="Macro",L11,IF($P$4="People",M11,IF($P$4="Sports",N11,IF($P$4="Travel",O11,IF($P$4="Waterdrops",P11,IF($P$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D11,IF($O$4="C2 Birds in Flight",E11,IF($O$4="C3 Landscape",F11,IF($O$4="Default Settings",G11,IF($O$4="Androo",H11,IF($O$4="Birds in Flight",I11,IF($O$4="Birds Perched",J11,IF($O$4="Fireworks",K11,IF($O$4="Landscape",L11,IF($O$4="Macro",M11,IF($O$4="People",N11,IF($O$4="Sports",O11,IF($O$4="Travel",P11,IF($O$4="Waterdrops",Q11,IF($O$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AG11" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D11,IF($P$4="C2 Birds in Flight",E11,IF($P$4="C3 Landscape",F11,IF($P$4="Default Settings",G11,IF($P$4="Androo",H11,IF($P$4="Birds in Flight",I11,IF($P$4="Birds Perched",J11,IF($P$4="Fireworks",K11,IF($P$4="Landscape",L11,IF($P$4="Macro",M11,IF($P$4="People",N11,IF($P$4="Sports",O11,IF($P$4="Travel",P11,IF($P$4="Waterdrops",Q11,IF($P$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AH11" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D11,IF($Q$4="C2 Birds in Flight",E11,IF($Q$4="C3 Landscape",F11,IF($Q$4="Default Settings",G11,IF($Q$4="Androo",H11,IF($Q$4="Birds in Flight",I11,IF($Q$4="Birds Perched",J11,IF($Q$4="Fireworks",K11,IF($Q$4="Landscape",L11,IF($Q$4="Macro",M11,IF($Q$4="People",N11,IF($Q$4="Sports",O11,IF($Q$4="Travel",P11,IF($Q$4="Waterdrops",Q11,IF($Q$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>f/8–f/11</x:v>
       </x:c>
-      <x:c r="AG11" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D11,IF($Q$4="C2 Birds in Flight",E11,IF($Q$4="C3 Landscape",F11,IF($Q$4="Default Settings",G11,IF($Q$4="Birds in Flight",H11,IF($Q$4="Birds Perched",I11,IF($Q$4="Fireworks",J11,IF($Q$4="Landscape",K11,IF($Q$4="Macro",L11,IF($Q$4="People",M11,IF($Q$4="Sports",N11,IF($Q$4="Travel",O11,IF($Q$4="Waterdrops",P11,IF($Q$4="Wildlife",Q11,""))))))))))))))</x:f>
+      <x:c r="AI11" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D11,IF($R$4="C2 Birds in Flight",E11,IF($R$4="C3 Landscape",F11,IF($R$4="Default Settings",G11,IF($R$4="Androo",H11,IF($R$4="Birds in Flight",I11,IF($R$4="Birds Perched",J11,IF($R$4="Fireworks",K11,IF($R$4="Landscape",L11,IF($R$4="Macro",M11,IF($R$4="People",N11,IF($R$4="Sports",O11,IF($R$4="Travel",P11,IF($R$4="Waterdrops",Q11,IF($R$4="Wildlife",R11,"")))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
@@ -1564,19 +1627,19 @@
         <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="H12" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+        <x:v>Auto - 3200</x:v>
       </x:c>
       <x:c r="I12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
-        <x:v>100</x:v>
+      <x:c r="J12" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="L12" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+      <x:c r="L12" s="17" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="M12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
@@ -1588,71 +1651,78 @@
         <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="P12" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="Q12" s="17" t="str">
         <x:v>100-400</x:v>
       </x:c>
-      <x:c r="Q12" s="17" t="str">
+      <x:c r="R12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="R12" s="20" t="n">
+      <x:c r="S12" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="S12" s="20" t="n">
+      <x:c r="T12" s="20" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="T12" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D12,IF($D$4="C2 Birds in Flight",E12,IF($D$4="C3 Landscape",F12,IF($D$4="Default Settings",G12,IF($D$4="Birds in Flight",H12,IF($D$4="Birds Perched",I12,IF($D$4="Fireworks",J12,IF($D$4="Landscape",K12,IF($D$4="Macro",L12,IF($D$4="People",M12,IF($D$4="Sports",N12,IF($D$4="Travel",O12,IF($D$4="Waterdrops",P12,IF($D$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="U12" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D12,IF($D$4="C2 Birds in Flight",E12,IF($D$4="C3 Landscape",F12,IF($D$4="Default Settings",G12,IF($D$4="Androo",H12,IF($D$4="Birds in Flight",I12,IF($D$4="Birds Perched",J12,IF($D$4="Fireworks",K12,IF($D$4="Landscape",L12,IF($D$4="Macro",M12,IF($D$4="People",N12,IF($D$4="Sports",O12,IF($D$4="Travel",P12,IF($D$4="Waterdrops",Q12,IF($D$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="U12" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D12,IF($E$4="C2 Birds in Flight",E12,IF($E$4="C3 Landscape",F12,IF($E$4="Default Settings",G12,IF($E$4="Birds in Flight",H12,IF($E$4="Birds Perched",I12,IF($E$4="Fireworks",J12,IF($E$4="Landscape",K12,IF($E$4="Macro",L12,IF($E$4="People",M12,IF($E$4="Sports",N12,IF($E$4="Travel",O12,IF($E$4="Waterdrops",P12,IF($E$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="V12" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D12,IF($E$4="C2 Birds in Flight",E12,IF($E$4="C3 Landscape",F12,IF($E$4="Default Settings",G12,IF($E$4="Androo",H12,IF($E$4="Birds in Flight",I12,IF($E$4="Birds Perched",J12,IF($E$4="Fireworks",K12,IF($E$4="Landscape",L12,IF($E$4="Macro",M12,IF($E$4="People",N12,IF($E$4="Sports",O12,IF($E$4="Travel",P12,IF($E$4="Waterdrops",Q12,IF($E$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="V12" s="38" t="n">
-        <x:f>IF($F$4="C1 Wildlife",D12,IF($F$4="C2 Birds in Flight",E12,IF($F$4="C3 Landscape",F12,IF($F$4="Default Settings",G12,IF($F$4="Birds in Flight",H12,IF($F$4="Birds Perched",I12,IF($F$4="Fireworks",J12,IF($F$4="Landscape",K12,IF($F$4="Macro",L12,IF($F$4="People",M12,IF($F$4="Sports",N12,IF($F$4="Travel",O12,IF($F$4="Waterdrops",P12,IF($F$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="W12" s="38" t="n">
+        <x:f>IF($F$4="C1 Wildlife",D12,IF($F$4="C2 Birds in Flight",E12,IF($F$4="C3 Landscape",F12,IF($F$4="Default Settings",G12,IF($F$4="Androo",H12,IF($F$4="Birds in Flight",I12,IF($F$4="Birds Perched",J12,IF($F$4="Fireworks",K12,IF($F$4="Landscape",L12,IF($F$4="Macro",M12,IF($F$4="People",N12,IF($F$4="Sports",O12,IF($F$4="Travel",P12,IF($F$4="Waterdrops",Q12,IF($F$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="W12" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D12,IF($G$4="C2 Birds in Flight",E12,IF($G$4="C3 Landscape",F12,IF($G$4="Default Settings",G12,IF($G$4="Birds in Flight",H12,IF($G$4="Birds Perched",I12,IF($G$4="Fireworks",J12,IF($G$4="Landscape",K12,IF($G$4="Macro",L12,IF($G$4="People",M12,IF($G$4="Sports",N12,IF($G$4="Travel",O12,IF($G$4="Waterdrops",P12,IF($G$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="X12" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D12,IF($G$4="C2 Birds in Flight",E12,IF($G$4="C3 Landscape",F12,IF($G$4="Default Settings",G12,IF($G$4="Androo",H12,IF($G$4="Birds in Flight",I12,IF($G$4="Birds Perched",J12,IF($G$4="Fireworks",K12,IF($G$4="Landscape",L12,IF($G$4="Macro",M12,IF($G$4="People",N12,IF($G$4="Sports",O12,IF($G$4="Travel",P12,IF($G$4="Waterdrops",Q12,IF($G$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="X12" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D12,IF($H$4="C2 Birds in Flight",E12,IF($H$4="C3 Landscape",F12,IF($H$4="Default Settings",G12,IF($H$4="Birds in Flight",H12,IF($H$4="Birds Perched",I12,IF($H$4="Fireworks",J12,IF($H$4="Landscape",K12,IF($H$4="Macro",L12,IF($H$4="People",M12,IF($H$4="Sports",N12,IF($H$4="Travel",O12,IF($H$4="Waterdrops",P12,IF($H$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="Y12" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D12,IF($H$4="C2 Birds in Flight",E12,IF($H$4="C3 Landscape",F12,IF($H$4="Default Settings",G12,IF($H$4="Androo",H12,IF($H$4="Birds in Flight",I12,IF($H$4="Birds Perched",J12,IF($H$4="Fireworks",K12,IF($H$4="Landscape",L12,IF($H$4="Macro",M12,IF($H$4="People",N12,IF($H$4="Sports",O12,IF($H$4="Travel",P12,IF($H$4="Waterdrops",Q12,IF($H$4="Wildlife",R12,"")))))))))))))))</x:f>
+        <x:v>Auto - 3200</x:v>
+      </x:c>
+      <x:c r="Z12" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D12,IF($I$4="C2 Birds in Flight",E12,IF($I$4="C3 Landscape",F12,IF($I$4="Default Settings",G12,IF($I$4="Androo",H12,IF($I$4="Birds in Flight",I12,IF($I$4="Birds Perched",J12,IF($I$4="Fireworks",K12,IF($I$4="Landscape",L12,IF($I$4="Macro",M12,IF($I$4="People",N12,IF($I$4="Sports",O12,IF($I$4="Travel",P12,IF($I$4="Waterdrops",Q12,IF($I$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="Y12" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D12,IF($I$4="C2 Birds in Flight",E12,IF($I$4="C3 Landscape",F12,IF($I$4="Default Settings",G12,IF($I$4="Birds in Flight",H12,IF($I$4="Birds Perched",I12,IF($I$4="Fireworks",J12,IF($I$4="Landscape",K12,IF($I$4="Macro",L12,IF($I$4="People",M12,IF($I$4="Sports",N12,IF($I$4="Travel",O12,IF($I$4="Waterdrops",P12,IF($I$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AA12" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D12,IF($J$4="C2 Birds in Flight",E12,IF($J$4="C3 Landscape",F12,IF($J$4="Default Settings",G12,IF($J$4="Androo",H12,IF($J$4="Birds in Flight",I12,IF($J$4="Birds Perched",J12,IF($J$4="Fireworks",K12,IF($J$4="Landscape",L12,IF($J$4="Macro",M12,IF($J$4="People",N12,IF($J$4="Sports",O12,IF($J$4="Travel",P12,IF($J$4="Waterdrops",Q12,IF($J$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="Z12" s="38" t="n">
-        <x:f>IF($J$4="C1 Wildlife",D12,IF($J$4="C2 Birds in Flight",E12,IF($J$4="C3 Landscape",F12,IF($J$4="Default Settings",G12,IF($J$4="Birds in Flight",H12,IF($J$4="Birds Perched",I12,IF($J$4="Fireworks",J12,IF($J$4="Landscape",K12,IF($J$4="Macro",L12,IF($J$4="People",M12,IF($J$4="Sports",N12,IF($J$4="Travel",O12,IF($J$4="Waterdrops",P12,IF($J$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AB12" s="38" t="n">
+        <x:f>IF($K$4="C1 Wildlife",D12,IF($K$4="C2 Birds in Flight",E12,IF($K$4="C3 Landscape",F12,IF($K$4="Default Settings",G12,IF($K$4="Androo",H12,IF($K$4="Birds in Flight",I12,IF($K$4="Birds Perched",J12,IF($K$4="Fireworks",K12,IF($K$4="Landscape",L12,IF($K$4="Macro",M12,IF($K$4="People",N12,IF($K$4="Sports",O12,IF($K$4="Travel",P12,IF($K$4="Waterdrops",Q12,IF($K$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="AA12" s="38" t="n">
-        <x:f>IF($K$4="C1 Wildlife",D12,IF($K$4="C2 Birds in Flight",E12,IF($K$4="C3 Landscape",F12,IF($K$4="Default Settings",G12,IF($K$4="Birds in Flight",H12,IF($K$4="Birds Perched",I12,IF($K$4="Fireworks",J12,IF($K$4="Landscape",K12,IF($K$4="Macro",L12,IF($K$4="People",M12,IF($K$4="Sports",N12,IF($K$4="Travel",O12,IF($K$4="Waterdrops",P12,IF($K$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AC12" s="38" t="n">
+        <x:f>IF($L$4="C1 Wildlife",D12,IF($L$4="C2 Birds in Flight",E12,IF($L$4="C3 Landscape",F12,IF($L$4="Default Settings",G12,IF($L$4="Androo",H12,IF($L$4="Birds in Flight",I12,IF($L$4="Birds Perched",J12,IF($L$4="Fireworks",K12,IF($L$4="Landscape",L12,IF($L$4="Macro",M12,IF($L$4="People",N12,IF($L$4="Sports",O12,IF($L$4="Travel",P12,IF($L$4="Waterdrops",Q12,IF($L$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="AB12" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D12,IF($L$4="C2 Birds in Flight",E12,IF($L$4="C3 Landscape",F12,IF($L$4="Default Settings",G12,IF($L$4="Birds in Flight",H12,IF($L$4="Birds Perched",I12,IF($L$4="Fireworks",J12,IF($L$4="Landscape",K12,IF($L$4="Macro",L12,IF($L$4="People",M12,IF($L$4="Sports",N12,IF($L$4="Travel",O12,IF($L$4="Waterdrops",P12,IF($L$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AD12" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D12,IF($M$4="C2 Birds in Flight",E12,IF($M$4="C3 Landscape",F12,IF($M$4="Default Settings",G12,IF($M$4="Androo",H12,IF($M$4="Birds in Flight",I12,IF($M$4="Birds Perched",J12,IF($M$4="Fireworks",K12,IF($M$4="Landscape",L12,IF($M$4="Macro",M12,IF($M$4="People",N12,IF($M$4="Sports",O12,IF($M$4="Travel",P12,IF($M$4="Waterdrops",Q12,IF($M$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="AC12" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D12,IF($M$4="C2 Birds in Flight",E12,IF($M$4="C3 Landscape",F12,IF($M$4="Default Settings",G12,IF($M$4="Birds in Flight",H12,IF($M$4="Birds Perched",I12,IF($M$4="Fireworks",J12,IF($M$4="Landscape",K12,IF($M$4="Macro",L12,IF($M$4="People",M12,IF($M$4="Sports",N12,IF($M$4="Travel",O12,IF($M$4="Waterdrops",P12,IF($M$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AE12" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D12,IF($N$4="C2 Birds in Flight",E12,IF($N$4="C3 Landscape",F12,IF($N$4="Default Settings",G12,IF($N$4="Androo",H12,IF($N$4="Birds in Flight",I12,IF($N$4="Birds Perched",J12,IF($N$4="Fireworks",K12,IF($N$4="Landscape",L12,IF($N$4="Macro",M12,IF($N$4="People",N12,IF($N$4="Sports",O12,IF($N$4="Travel",P12,IF($N$4="Waterdrops",Q12,IF($N$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="AD12" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D12,IF($N$4="C2 Birds in Flight",E12,IF($N$4="C3 Landscape",F12,IF($N$4="Default Settings",G12,IF($N$4="Birds in Flight",H12,IF($N$4="Birds Perched",I12,IF($N$4="Fireworks",J12,IF($N$4="Landscape",K12,IF($N$4="Macro",L12,IF($N$4="People",M12,IF($N$4="Sports",N12,IF($N$4="Travel",O12,IF($N$4="Waterdrops",P12,IF($N$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AF12" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D12,IF($O$4="C2 Birds in Flight",E12,IF($O$4="C3 Landscape",F12,IF($O$4="Default Settings",G12,IF($O$4="Androo",H12,IF($O$4="Birds in Flight",I12,IF($O$4="Birds Perched",J12,IF($O$4="Fireworks",K12,IF($O$4="Landscape",L12,IF($O$4="Macro",M12,IF($O$4="People",N12,IF($O$4="Sports",O12,IF($O$4="Travel",P12,IF($O$4="Waterdrops",Q12,IF($O$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="AE12" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D12,IF($O$4="C2 Birds in Flight",E12,IF($O$4="C3 Landscape",F12,IF($O$4="Default Settings",G12,IF($O$4="Birds in Flight",H12,IF($O$4="Birds Perched",I12,IF($O$4="Fireworks",J12,IF($O$4="Landscape",K12,IF($O$4="Macro",L12,IF($O$4="People",M12,IF($O$4="Sports",N12,IF($O$4="Travel",O12,IF($O$4="Waterdrops",P12,IF($O$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AG12" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D12,IF($P$4="C2 Birds in Flight",E12,IF($P$4="C3 Landscape",F12,IF($P$4="Default Settings",G12,IF($P$4="Androo",H12,IF($P$4="Birds in Flight",I12,IF($P$4="Birds Perched",J12,IF($P$4="Fireworks",K12,IF($P$4="Landscape",L12,IF($P$4="Macro",M12,IF($P$4="People",N12,IF($P$4="Sports",O12,IF($P$4="Travel",P12,IF($P$4="Waterdrops",Q12,IF($P$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="AF12" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D12,IF($P$4="C2 Birds in Flight",E12,IF($P$4="C3 Landscape",F12,IF($P$4="Default Settings",G12,IF($P$4="Birds in Flight",H12,IF($P$4="Birds Perched",I12,IF($P$4="Fireworks",J12,IF($P$4="Landscape",K12,IF($P$4="Macro",L12,IF($P$4="People",M12,IF($P$4="Sports",N12,IF($P$4="Travel",O12,IF($P$4="Waterdrops",P12,IF($P$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AH12" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D12,IF($Q$4="C2 Birds in Flight",E12,IF($Q$4="C3 Landscape",F12,IF($Q$4="Default Settings",G12,IF($Q$4="Androo",H12,IF($Q$4="Birds in Flight",I12,IF($Q$4="Birds Perched",J12,IF($Q$4="Fireworks",K12,IF($Q$4="Landscape",L12,IF($Q$4="Macro",M12,IF($Q$4="People",N12,IF($Q$4="Sports",O12,IF($Q$4="Travel",P12,IF($Q$4="Waterdrops",Q12,IF($Q$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>100-400</x:v>
       </x:c>
-      <x:c r="AG12" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D12,IF($Q$4="C2 Birds in Flight",E12,IF($Q$4="C3 Landscape",F12,IF($Q$4="Default Settings",G12,IF($Q$4="Birds in Flight",H12,IF($Q$4="Birds Perched",I12,IF($Q$4="Fireworks",J12,IF($Q$4="Landscape",K12,IF($Q$4="Macro",L12,IF($Q$4="People",M12,IF($Q$4="Sports",N12,IF($Q$4="Travel",O12,IF($Q$4="Waterdrops",P12,IF($Q$4="Wildlife",Q12,""))))))))))))))</x:f>
+      <x:c r="AI12" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D12,IF($R$4="C2 Birds in Flight",E12,IF($R$4="C3 Landscape",F12,IF($R$4="Default Settings",G12,IF($R$4="Androo",H12,IF($R$4="Birds in Flight",I12,IF($R$4="Birds Perched",J12,IF($R$4="Fireworks",K12,IF($R$4="Landscape",L12,IF($R$4="Macro",M12,IF($R$4="People",N12,IF($R$4="Sports",O12,IF($R$4="Travel",P12,IF($R$4="Waterdrops",Q12,IF($R$4="Wildlife",R12,"")))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
     </x:row>
@@ -1678,14 +1748,14 @@
       <x:c r="G13" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H13" s="17" t="str">
+      <x:c r="H13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
         <x:v>Adjust for background</x:v>
       </x:c>
-      <x:c r="I13" s="17" t="str">
+      <x:c r="J13" s="17" t="str">
         <x:v>0 to +1/3</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="n">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>0</x:v>
@@ -1708,66 +1778,73 @@
       <x:c r="Q13" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="n">
+      <x:c r="R13" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="n">
+      <x:c r="T13" s="20" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="T13" s="38" t="n">
-        <x:f>IF($D$4="C1 Wildlife",D13,IF($D$4="C2 Birds in Flight",E13,IF($D$4="C3 Landscape",F13,IF($D$4="Default Settings",G13,IF($D$4="Birds in Flight",H13,IF($D$4="Birds Perched",I13,IF($D$4="Fireworks",J13,IF($D$4="Landscape",K13,IF($D$4="Macro",L13,IF($D$4="People",M13,IF($D$4="Sports",N13,IF($D$4="Travel",O13,IF($D$4="Waterdrops",P13,IF($D$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="U13" s="38" t="n">
+        <x:f>IF($D$4="C1 Wildlife",D13,IF($D$4="C2 Birds in Flight",E13,IF($D$4="C3 Landscape",F13,IF($D$4="Default Settings",G13,IF($D$4="Androo",H13,IF($D$4="Birds in Flight",I13,IF($D$4="Birds Perched",J13,IF($D$4="Fireworks",K13,IF($D$4="Landscape",L13,IF($D$4="Macro",M13,IF($D$4="People",N13,IF($D$4="Sports",O13,IF($D$4="Travel",P13,IF($D$4="Waterdrops",Q13,IF($D$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U13" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D13,IF($E$4="C2 Birds in Flight",E13,IF($E$4="C3 Landscape",F13,IF($E$4="Default Settings",G13,IF($E$4="Birds in Flight",H13,IF($E$4="Birds Perched",I13,IF($E$4="Fireworks",J13,IF($E$4="Landscape",K13,IF($E$4="Macro",L13,IF($E$4="People",M13,IF($E$4="Sports",N13,IF($E$4="Travel",O13,IF($E$4="Waterdrops",P13,IF($E$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="V13" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D13,IF($E$4="C2 Birds in Flight",E13,IF($E$4="C3 Landscape",F13,IF($E$4="Default Settings",G13,IF($E$4="Androo",H13,IF($E$4="Birds in Flight",I13,IF($E$4="Birds Perched",J13,IF($E$4="Fireworks",K13,IF($E$4="Landscape",L13,IF($E$4="Macro",M13,IF($E$4="People",N13,IF($E$4="Sports",O13,IF($E$4="Travel",P13,IF($E$4="Waterdrops",Q13,IF($E$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0 starting point</x:v>
       </x:c>
-      <x:c r="V13" s="38" t="n">
-        <x:f>IF($F$4="C1 Wildlife",D13,IF($F$4="C2 Birds in Flight",E13,IF($F$4="C3 Landscape",F13,IF($F$4="Default Settings",G13,IF($F$4="Birds in Flight",H13,IF($F$4="Birds Perched",I13,IF($F$4="Fireworks",J13,IF($F$4="Landscape",K13,IF($F$4="Macro",L13,IF($F$4="People",M13,IF($F$4="Sports",N13,IF($F$4="Travel",O13,IF($F$4="Waterdrops",P13,IF($F$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="W13" s="38" t="n">
+        <x:f>IF($F$4="C1 Wildlife",D13,IF($F$4="C2 Birds in Flight",E13,IF($F$4="C3 Landscape",F13,IF($F$4="Default Settings",G13,IF($F$4="Androo",H13,IF($F$4="Birds in Flight",I13,IF($F$4="Birds Perched",J13,IF($F$4="Fireworks",K13,IF($F$4="Landscape",L13,IF($F$4="Macro",M13,IF($F$4="People",N13,IF($F$4="Sports",O13,IF($F$4="Travel",P13,IF($F$4="Waterdrops",Q13,IF($F$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W13" s="38" t="n">
-        <x:f>IF($G$4="C1 Wildlife",D13,IF($G$4="C2 Birds in Flight",E13,IF($G$4="C3 Landscape",F13,IF($G$4="Default Settings",G13,IF($G$4="Birds in Flight",H13,IF($G$4="Birds Perched",I13,IF($G$4="Fireworks",J13,IF($G$4="Landscape",K13,IF($G$4="Macro",L13,IF($G$4="People",M13,IF($G$4="Sports",N13,IF($G$4="Travel",O13,IF($G$4="Waterdrops",P13,IF($G$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="X13" s="38" t="n">
+        <x:f>IF($G$4="C1 Wildlife",D13,IF($G$4="C2 Birds in Flight",E13,IF($G$4="C3 Landscape",F13,IF($G$4="Default Settings",G13,IF($G$4="Androo",H13,IF($G$4="Birds in Flight",I13,IF($G$4="Birds Perched",J13,IF($G$4="Fireworks",K13,IF($G$4="Landscape",L13,IF($G$4="Macro",M13,IF($G$4="People",N13,IF($G$4="Sports",O13,IF($G$4="Travel",P13,IF($G$4="Waterdrops",Q13,IF($G$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X13" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D13,IF($H$4="C2 Birds in Flight",E13,IF($H$4="C3 Landscape",F13,IF($H$4="Default Settings",G13,IF($H$4="Birds in Flight",H13,IF($H$4="Birds Perched",I13,IF($H$4="Fireworks",J13,IF($H$4="Landscape",K13,IF($H$4="Macro",L13,IF($H$4="People",M13,IF($H$4="Sports",N13,IF($H$4="Travel",O13,IF($H$4="Waterdrops",P13,IF($H$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="Y13" s="38" t="n">
+        <x:f>IF($H$4="C1 Wildlife",D13,IF($H$4="C2 Birds in Flight",E13,IF($H$4="C3 Landscape",F13,IF($H$4="Default Settings",G13,IF($H$4="Androo",H13,IF($H$4="Birds in Flight",I13,IF($H$4="Birds Perched",J13,IF($H$4="Fireworks",K13,IF($H$4="Landscape",L13,IF($H$4="Macro",M13,IF($H$4="People",N13,IF($H$4="Sports",O13,IF($H$4="Travel",P13,IF($H$4="Waterdrops",Q13,IF($H$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z13" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D13,IF($I$4="C2 Birds in Flight",E13,IF($I$4="C3 Landscape",F13,IF($I$4="Default Settings",G13,IF($I$4="Androo",H13,IF($I$4="Birds in Flight",I13,IF($I$4="Birds Perched",J13,IF($I$4="Fireworks",K13,IF($I$4="Landscape",L13,IF($I$4="Macro",M13,IF($I$4="People",N13,IF($I$4="Sports",O13,IF($I$4="Travel",P13,IF($I$4="Waterdrops",Q13,IF($I$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>Adjust for background</x:v>
       </x:c>
-      <x:c r="Y13" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D13,IF($I$4="C2 Birds in Flight",E13,IF($I$4="C3 Landscape",F13,IF($I$4="Default Settings",G13,IF($I$4="Birds in Flight",H13,IF($I$4="Birds Perched",I13,IF($I$4="Fireworks",J13,IF($I$4="Landscape",K13,IF($I$4="Macro",L13,IF($I$4="People",M13,IF($I$4="Sports",N13,IF($I$4="Travel",O13,IF($I$4="Waterdrops",P13,IF($I$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AA13" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D13,IF($J$4="C2 Birds in Flight",E13,IF($J$4="C3 Landscape",F13,IF($J$4="Default Settings",G13,IF($J$4="Androo",H13,IF($J$4="Birds in Flight",I13,IF($J$4="Birds Perched",J13,IF($J$4="Fireworks",K13,IF($J$4="Landscape",L13,IF($J$4="Macro",M13,IF($J$4="People",N13,IF($J$4="Sports",O13,IF($J$4="Travel",P13,IF($J$4="Waterdrops",Q13,IF($J$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0 to +1/3</x:v>
       </x:c>
-      <x:c r="Z13" s="38" t="n">
-        <x:f>IF($J$4="C1 Wildlife",D13,IF($J$4="C2 Birds in Flight",E13,IF($J$4="C3 Landscape",F13,IF($J$4="Default Settings",G13,IF($J$4="Birds in Flight",H13,IF($J$4="Birds Perched",I13,IF($J$4="Fireworks",J13,IF($J$4="Landscape",K13,IF($J$4="Macro",L13,IF($J$4="People",M13,IF($J$4="Sports",N13,IF($J$4="Travel",O13,IF($J$4="Waterdrops",P13,IF($J$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AB13" s="38" t="n">
+        <x:f>IF($K$4="C1 Wildlife",D13,IF($K$4="C2 Birds in Flight",E13,IF($K$4="C3 Landscape",F13,IF($K$4="Default Settings",G13,IF($K$4="Androo",H13,IF($K$4="Birds in Flight",I13,IF($K$4="Birds Perched",J13,IF($K$4="Fireworks",K13,IF($K$4="Landscape",L13,IF($K$4="Macro",M13,IF($K$4="People",N13,IF($K$4="Sports",O13,IF($K$4="Travel",P13,IF($K$4="Waterdrops",Q13,IF($K$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA13" s="38" t="n">
-        <x:f>IF($K$4="C1 Wildlife",D13,IF($K$4="C2 Birds in Flight",E13,IF($K$4="C3 Landscape",F13,IF($K$4="Default Settings",G13,IF($K$4="Birds in Flight",H13,IF($K$4="Birds Perched",I13,IF($K$4="Fireworks",J13,IF($K$4="Landscape",K13,IF($K$4="Macro",L13,IF($K$4="People",M13,IF($K$4="Sports",N13,IF($K$4="Travel",O13,IF($K$4="Waterdrops",P13,IF($K$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AC13" s="38" t="n">
+        <x:f>IF($L$4="C1 Wildlife",D13,IF($L$4="C2 Birds in Flight",E13,IF($L$4="C3 Landscape",F13,IF($L$4="Default Settings",G13,IF($L$4="Androo",H13,IF($L$4="Birds in Flight",I13,IF($L$4="Birds Perched",J13,IF($L$4="Fireworks",K13,IF($L$4="Landscape",L13,IF($L$4="Macro",M13,IF($L$4="People",N13,IF($L$4="Sports",O13,IF($L$4="Travel",P13,IF($L$4="Waterdrops",Q13,IF($L$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AB13" s="38" t="n">
-        <x:f>IF($L$4="C1 Wildlife",D13,IF($L$4="C2 Birds in Flight",E13,IF($L$4="C3 Landscape",F13,IF($L$4="Default Settings",G13,IF($L$4="Birds in Flight",H13,IF($L$4="Birds Perched",I13,IF($L$4="Fireworks",J13,IF($L$4="Landscape",K13,IF($L$4="Macro",L13,IF($L$4="People",M13,IF($L$4="Sports",N13,IF($L$4="Travel",O13,IF($L$4="Waterdrops",P13,IF($L$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AD13" s="38" t="n">
+        <x:f>IF($M$4="C1 Wildlife",D13,IF($M$4="C2 Birds in Flight",E13,IF($M$4="C3 Landscape",F13,IF($M$4="Default Settings",G13,IF($M$4="Androo",H13,IF($M$4="Birds in Flight",I13,IF($M$4="Birds Perched",J13,IF($M$4="Fireworks",K13,IF($M$4="Landscape",L13,IF($M$4="Macro",M13,IF($M$4="People",N13,IF($M$4="Sports",O13,IF($M$4="Travel",P13,IF($M$4="Waterdrops",Q13,IF($M$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AC13" s="38" t="n">
-        <x:f>IF($M$4="C1 Wildlife",D13,IF($M$4="C2 Birds in Flight",E13,IF($M$4="C3 Landscape",F13,IF($M$4="Default Settings",G13,IF($M$4="Birds in Flight",H13,IF($M$4="Birds Perched",I13,IF($M$4="Fireworks",J13,IF($M$4="Landscape",K13,IF($M$4="Macro",L13,IF($M$4="People",M13,IF($M$4="Sports",N13,IF($M$4="Travel",O13,IF($M$4="Waterdrops",P13,IF($M$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AE13" s="38" t="n">
+        <x:f>IF($N$4="C1 Wildlife",D13,IF($N$4="C2 Birds in Flight",E13,IF($N$4="C3 Landscape",F13,IF($N$4="Default Settings",G13,IF($N$4="Androo",H13,IF($N$4="Birds in Flight",I13,IF($N$4="Birds Perched",J13,IF($N$4="Fireworks",K13,IF($N$4="Landscape",L13,IF($N$4="Macro",M13,IF($N$4="People",N13,IF($N$4="Sports",O13,IF($N$4="Travel",P13,IF($N$4="Waterdrops",Q13,IF($N$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AD13" s="38" t="n">
-        <x:f>IF($N$4="C1 Wildlife",D13,IF($N$4="C2 Birds in Flight",E13,IF($N$4="C3 Landscape",F13,IF($N$4="Default Settings",G13,IF($N$4="Birds in Flight",H13,IF($N$4="Birds Perched",I13,IF($N$4="Fireworks",J13,IF($N$4="Landscape",K13,IF($N$4="Macro",L13,IF($N$4="People",M13,IF($N$4="Sports",N13,IF($N$4="Travel",O13,IF($N$4="Waterdrops",P13,IF($N$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AF13" s="38" t="n">
+        <x:f>IF($O$4="C1 Wildlife",D13,IF($O$4="C2 Birds in Flight",E13,IF($O$4="C3 Landscape",F13,IF($O$4="Default Settings",G13,IF($O$4="Androo",H13,IF($O$4="Birds in Flight",I13,IF($O$4="Birds Perched",J13,IF($O$4="Fireworks",K13,IF($O$4="Landscape",L13,IF($O$4="Macro",M13,IF($O$4="People",N13,IF($O$4="Sports",O13,IF($O$4="Travel",P13,IF($O$4="Waterdrops",Q13,IF($O$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AE13" s="38" t="n">
-        <x:f>IF($O$4="C1 Wildlife",D13,IF($O$4="C2 Birds in Flight",E13,IF($O$4="C3 Landscape",F13,IF($O$4="Default Settings",G13,IF($O$4="Birds in Flight",H13,IF($O$4="Birds Perched",I13,IF($O$4="Fireworks",J13,IF($O$4="Landscape",K13,IF($O$4="Macro",L13,IF($O$4="People",M13,IF($O$4="Sports",N13,IF($O$4="Travel",O13,IF($O$4="Waterdrops",P13,IF($O$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AG13" s="38" t="n">
+        <x:f>IF($P$4="C1 Wildlife",D13,IF($P$4="C2 Birds in Flight",E13,IF($P$4="C3 Landscape",F13,IF($P$4="Default Settings",G13,IF($P$4="Androo",H13,IF($P$4="Birds in Flight",I13,IF($P$4="Birds Perched",J13,IF($P$4="Fireworks",K13,IF($P$4="Landscape",L13,IF($P$4="Macro",M13,IF($P$4="People",N13,IF($P$4="Sports",O13,IF($P$4="Travel",P13,IF($P$4="Waterdrops",Q13,IF($P$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AF13" s="38" t="n">
-        <x:f>IF($P$4="C1 Wildlife",D13,IF($P$4="C2 Birds in Flight",E13,IF($P$4="C3 Landscape",F13,IF($P$4="Default Settings",G13,IF($P$4="Birds in Flight",H13,IF($P$4="Birds Perched",I13,IF($P$4="Fireworks",J13,IF($P$4="Landscape",K13,IF($P$4="Macro",L13,IF($P$4="People",M13,IF($P$4="Sports",N13,IF($P$4="Travel",O13,IF($P$4="Waterdrops",P13,IF($P$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AH13" s="38" t="n">
+        <x:f>IF($Q$4="C1 Wildlife",D13,IF($Q$4="C2 Birds in Flight",E13,IF($Q$4="C3 Landscape",F13,IF($Q$4="Default Settings",G13,IF($Q$4="Androo",H13,IF($Q$4="Birds in Flight",I13,IF($Q$4="Birds Perched",J13,IF($Q$4="Fireworks",K13,IF($Q$4="Landscape",L13,IF($Q$4="Macro",M13,IF($Q$4="People",N13,IF($Q$4="Sports",O13,IF($Q$4="Travel",P13,IF($Q$4="Waterdrops",Q13,IF($Q$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AG13" s="38" t="n">
-        <x:f>IF($Q$4="C1 Wildlife",D13,IF($Q$4="C2 Birds in Flight",E13,IF($Q$4="C3 Landscape",F13,IF($Q$4="Default Settings",G13,IF($Q$4="Birds in Flight",H13,IF($Q$4="Birds Perched",I13,IF($Q$4="Fireworks",J13,IF($Q$4="Landscape",K13,IF($Q$4="Macro",L13,IF($Q$4="People",M13,IF($Q$4="Sports",N13,IF($Q$4="Travel",O13,IF($Q$4="Waterdrops",P13,IF($Q$4="Wildlife",Q13,""))))))))))))))</x:f>
+      <x:c r="AI13" s="38" t="n">
+        <x:f>IF($R$4="C1 Wildlife",D13,IF($R$4="C2 Birds in Flight",E13,IF($R$4="C3 Landscape",F13,IF($R$4="Default Settings",G13,IF($R$4="Androo",H13,IF($R$4="Birds in Flight",I13,IF($R$4="Birds Perched",J13,IF($R$4="Fireworks",K13,IF($R$4="Landscape",L13,IF($R$4="Macro",M13,IF($R$4="People",N13,IF($R$4="Sports",O13,IF($R$4="Travel",P13,IF($R$4="Waterdrops",Q13,IF($R$4="Wildlife",R13,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1794,22 +1871,22 @@
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>Servo AF</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="I14" s="17" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="J14" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="str">
         <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="L14" s="17" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="M14" s="17" t="str">
-        <x:v>Servo AF</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="N14" s="17" t="str">
         <x:v>Servo AF</x:v>
@@ -1818,71 +1895,78 @@
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="P14" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="str">
         <x:v>Manual Focus</x:v>
       </x:c>
-      <x:c r="Q14" s="17" t="str">
+      <x:c r="R14" s="17" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="R14" s="20" t="n">
+      <x:c r="S14" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="S14" s="20" t="n">
+      <x:c r="T14" s="20" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="T14" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D14,IF($D$4="C2 Birds in Flight",E14,IF($D$4="C3 Landscape",F14,IF($D$4="Default Settings",G14,IF($D$4="Birds in Flight",H14,IF($D$4="Birds Perched",I14,IF($D$4="Fireworks",J14,IF($D$4="Landscape",K14,IF($D$4="Macro",L14,IF($D$4="People",M14,IF($D$4="Sports",N14,IF($D$4="Travel",O14,IF($D$4="Waterdrops",P14,IF($D$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="U14" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D14,IF($D$4="C2 Birds in Flight",E14,IF($D$4="C3 Landscape",F14,IF($D$4="Default Settings",G14,IF($D$4="Androo",H14,IF($D$4="Birds in Flight",I14,IF($D$4="Birds Perched",J14,IF($D$4="Fireworks",K14,IF($D$4="Landscape",L14,IF($D$4="Macro",M14,IF($D$4="People",N14,IF($D$4="Sports",O14,IF($D$4="Travel",P14,IF($D$4="Waterdrops",Q14,IF($D$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="U14" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D14,IF($E$4="C2 Birds in Flight",E14,IF($E$4="C3 Landscape",F14,IF($E$4="Default Settings",G14,IF($E$4="Birds in Flight",H14,IF($E$4="Birds Perched",I14,IF($E$4="Fireworks",J14,IF($E$4="Landscape",K14,IF($E$4="Macro",L14,IF($E$4="People",M14,IF($E$4="Sports",N14,IF($E$4="Travel",O14,IF($E$4="Waterdrops",P14,IF($E$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="V14" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D14,IF($E$4="C2 Birds in Flight",E14,IF($E$4="C3 Landscape",F14,IF($E$4="Default Settings",G14,IF($E$4="Androo",H14,IF($E$4="Birds in Flight",I14,IF($E$4="Birds Perched",J14,IF($E$4="Fireworks",K14,IF($E$4="Landscape",L14,IF($E$4="Macro",M14,IF($E$4="People",N14,IF($E$4="Sports",O14,IF($E$4="Travel",P14,IF($E$4="Waterdrops",Q14,IF($E$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="V14" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D14,IF($F$4="C2 Birds in Flight",E14,IF($F$4="C3 Landscape",F14,IF($F$4="Default Settings",G14,IF($F$4="Birds in Flight",H14,IF($F$4="Birds Perched",I14,IF($F$4="Fireworks",J14,IF($F$4="Landscape",K14,IF($F$4="Macro",L14,IF($F$4="People",M14,IF($F$4="Sports",N14,IF($F$4="Travel",O14,IF($F$4="Waterdrops",P14,IF($F$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="W14" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D14,IF($F$4="C2 Birds in Flight",E14,IF($F$4="C3 Landscape",F14,IF($F$4="Default Settings",G14,IF($F$4="Androo",H14,IF($F$4="Birds in Flight",I14,IF($F$4="Birds Perched",J14,IF($F$4="Fireworks",K14,IF($F$4="Landscape",L14,IF($F$4="Macro",M14,IF($F$4="People",N14,IF($F$4="Sports",O14,IF($F$4="Travel",P14,IF($F$4="Waterdrops",Q14,IF($F$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="W14" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D14,IF($G$4="C2 Birds in Flight",E14,IF($G$4="C3 Landscape",F14,IF($G$4="Default Settings",G14,IF($G$4="Birds in Flight",H14,IF($G$4="Birds Perched",I14,IF($G$4="Fireworks",J14,IF($G$4="Landscape",K14,IF($G$4="Macro",L14,IF($G$4="People",M14,IF($G$4="Sports",N14,IF($G$4="Travel",O14,IF($G$4="Waterdrops",P14,IF($G$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="X14" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D14,IF($G$4="C2 Birds in Flight",E14,IF($G$4="C3 Landscape",F14,IF($G$4="Default Settings",G14,IF($G$4="Androo",H14,IF($G$4="Birds in Flight",I14,IF($G$4="Birds Perched",J14,IF($G$4="Fireworks",K14,IF($G$4="Landscape",L14,IF($G$4="Macro",M14,IF($G$4="People",N14,IF($G$4="Sports",O14,IF($G$4="Travel",P14,IF($G$4="Waterdrops",Q14,IF($G$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="X14" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D14,IF($H$4="C2 Birds in Flight",E14,IF($H$4="C3 Landscape",F14,IF($H$4="Default Settings",G14,IF($H$4="Birds in Flight",H14,IF($H$4="Birds Perched",I14,IF($H$4="Fireworks",J14,IF($H$4="Landscape",K14,IF($H$4="Macro",L14,IF($H$4="People",M14,IF($H$4="Sports",N14,IF($H$4="Travel",O14,IF($H$4="Waterdrops",P14,IF($H$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="Y14" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D14,IF($H$4="C2 Birds in Flight",E14,IF($H$4="C3 Landscape",F14,IF($H$4="Default Settings",G14,IF($H$4="Androo",H14,IF($H$4="Birds in Flight",I14,IF($H$4="Birds Perched",J14,IF($H$4="Fireworks",K14,IF($H$4="Landscape",L14,IF($H$4="Macro",M14,IF($H$4="People",N14,IF($H$4="Sports",O14,IF($H$4="Travel",P14,IF($H$4="Waterdrops",Q14,IF($H$4="Wildlife",R14,"")))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="Z14" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D14,IF($I$4="C2 Birds in Flight",E14,IF($I$4="C3 Landscape",F14,IF($I$4="Default Settings",G14,IF($I$4="Androo",H14,IF($I$4="Birds in Flight",I14,IF($I$4="Birds Perched",J14,IF($I$4="Fireworks",K14,IF($I$4="Landscape",L14,IF($I$4="Macro",M14,IF($I$4="People",N14,IF($I$4="Sports",O14,IF($I$4="Travel",P14,IF($I$4="Waterdrops",Q14,IF($I$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="Y14" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D14,IF($I$4="C2 Birds in Flight",E14,IF($I$4="C3 Landscape",F14,IF($I$4="Default Settings",G14,IF($I$4="Birds in Flight",H14,IF($I$4="Birds Perched",I14,IF($I$4="Fireworks",J14,IF($I$4="Landscape",K14,IF($I$4="Macro",L14,IF($I$4="People",M14,IF($I$4="Sports",N14,IF($I$4="Travel",O14,IF($I$4="Waterdrops",P14,IF($I$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AA14" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D14,IF($J$4="C2 Birds in Flight",E14,IF($J$4="C3 Landscape",F14,IF($J$4="Default Settings",G14,IF($J$4="Androo",H14,IF($J$4="Birds in Flight",I14,IF($J$4="Birds Perched",J14,IF($J$4="Fireworks",K14,IF($J$4="Landscape",L14,IF($J$4="Macro",M14,IF($J$4="People",N14,IF($J$4="Sports",O14,IF($J$4="Travel",P14,IF($J$4="Waterdrops",Q14,IF($J$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="Z14" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D14,IF($J$4="C2 Birds in Flight",E14,IF($J$4="C3 Landscape",F14,IF($J$4="Default Settings",G14,IF($J$4="Birds in Flight",H14,IF($J$4="Birds Perched",I14,IF($J$4="Fireworks",J14,IF($J$4="Landscape",K14,IF($J$4="Macro",L14,IF($J$4="People",M14,IF($J$4="Sports",N14,IF($J$4="Travel",O14,IF($J$4="Waterdrops",P14,IF($J$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AB14" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D14,IF($K$4="C2 Birds in Flight",E14,IF($K$4="C3 Landscape",F14,IF($K$4="Default Settings",G14,IF($K$4="Androo",H14,IF($K$4="Birds in Flight",I14,IF($K$4="Birds Perched",J14,IF($K$4="Fireworks",K14,IF($K$4="Landscape",L14,IF($K$4="Macro",M14,IF($K$4="People",N14,IF($K$4="Sports",O14,IF($K$4="Travel",P14,IF($K$4="Waterdrops",Q14,IF($K$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Manual Focus</x:v>
       </x:c>
-      <x:c r="AA14" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D14,IF($K$4="C2 Birds in Flight",E14,IF($K$4="C3 Landscape",F14,IF($K$4="Default Settings",G14,IF($K$4="Birds in Flight",H14,IF($K$4="Birds Perched",I14,IF($K$4="Fireworks",J14,IF($K$4="Landscape",K14,IF($K$4="Macro",L14,IF($K$4="People",M14,IF($K$4="Sports",N14,IF($K$4="Travel",O14,IF($K$4="Waterdrops",P14,IF($K$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AC14" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D14,IF($L$4="C2 Birds in Flight",E14,IF($L$4="C3 Landscape",F14,IF($L$4="Default Settings",G14,IF($L$4="Androo",H14,IF($L$4="Birds in Flight",I14,IF($L$4="Birds Perched",J14,IF($L$4="Fireworks",K14,IF($L$4="Landscape",L14,IF($L$4="Macro",M14,IF($L$4="People",N14,IF($L$4="Sports",O14,IF($L$4="Travel",P14,IF($L$4="Waterdrops",Q14,IF($L$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="AB14" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D14,IF($L$4="C2 Birds in Flight",E14,IF($L$4="C3 Landscape",F14,IF($L$4="Default Settings",G14,IF($L$4="Birds in Flight",H14,IF($L$4="Birds Perched",I14,IF($L$4="Fireworks",J14,IF($L$4="Landscape",K14,IF($L$4="Macro",L14,IF($L$4="People",M14,IF($L$4="Sports",N14,IF($L$4="Travel",O14,IF($L$4="Waterdrops",P14,IF($L$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AD14" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D14,IF($M$4="C2 Birds in Flight",E14,IF($M$4="C3 Landscape",F14,IF($M$4="Default Settings",G14,IF($M$4="Androo",H14,IF($M$4="Birds in Flight",I14,IF($M$4="Birds Perched",J14,IF($M$4="Fireworks",K14,IF($M$4="Landscape",L14,IF($M$4="Macro",M14,IF($M$4="People",N14,IF($M$4="Sports",O14,IF($M$4="Travel",P14,IF($M$4="Waterdrops",Q14,IF($M$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="AC14" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D14,IF($M$4="C2 Birds in Flight",E14,IF($M$4="C3 Landscape",F14,IF($M$4="Default Settings",G14,IF($M$4="Birds in Flight",H14,IF($M$4="Birds Perched",I14,IF($M$4="Fireworks",J14,IF($M$4="Landscape",K14,IF($M$4="Macro",L14,IF($M$4="People",M14,IF($M$4="Sports",N14,IF($M$4="Travel",O14,IF($M$4="Waterdrops",P14,IF($M$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AE14" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D14,IF($N$4="C2 Birds in Flight",E14,IF($N$4="C3 Landscape",F14,IF($N$4="Default Settings",G14,IF($N$4="Androo",H14,IF($N$4="Birds in Flight",I14,IF($N$4="Birds Perched",J14,IF($N$4="Fireworks",K14,IF($N$4="Landscape",L14,IF($N$4="Macro",M14,IF($N$4="People",N14,IF($N$4="Sports",O14,IF($N$4="Travel",P14,IF($N$4="Waterdrops",Q14,IF($N$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="AD14" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D14,IF($N$4="C2 Birds in Flight",E14,IF($N$4="C3 Landscape",F14,IF($N$4="Default Settings",G14,IF($N$4="Birds in Flight",H14,IF($N$4="Birds Perched",I14,IF($N$4="Fireworks",J14,IF($N$4="Landscape",K14,IF($N$4="Macro",L14,IF($N$4="People",M14,IF($N$4="Sports",N14,IF($N$4="Travel",O14,IF($N$4="Waterdrops",P14,IF($N$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AF14" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D14,IF($O$4="C2 Birds in Flight",E14,IF($O$4="C3 Landscape",F14,IF($O$4="Default Settings",G14,IF($O$4="Androo",H14,IF($O$4="Birds in Flight",I14,IF($O$4="Birds Perched",J14,IF($O$4="Fireworks",K14,IF($O$4="Landscape",L14,IF($O$4="Macro",M14,IF($O$4="People",N14,IF($O$4="Sports",O14,IF($O$4="Travel",P14,IF($O$4="Waterdrops",Q14,IF($O$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="AE14" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D14,IF($O$4="C2 Birds in Flight",E14,IF($O$4="C3 Landscape",F14,IF($O$4="Default Settings",G14,IF($O$4="Birds in Flight",H14,IF($O$4="Birds Perched",I14,IF($O$4="Fireworks",J14,IF($O$4="Landscape",K14,IF($O$4="Macro",L14,IF($O$4="People",M14,IF($O$4="Sports",N14,IF($O$4="Travel",O14,IF($O$4="Waterdrops",P14,IF($O$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AG14" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D14,IF($P$4="C2 Birds in Flight",E14,IF($P$4="C3 Landscape",F14,IF($P$4="Default Settings",G14,IF($P$4="Androo",H14,IF($P$4="Birds in Flight",I14,IF($P$4="Birds Perched",J14,IF($P$4="Fireworks",K14,IF($P$4="Landscape",L14,IF($P$4="Macro",M14,IF($P$4="People",N14,IF($P$4="Sports",O14,IF($P$4="Travel",P14,IF($P$4="Waterdrops",Q14,IF($P$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="AF14" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D14,IF($P$4="C2 Birds in Flight",E14,IF($P$4="C3 Landscape",F14,IF($P$4="Default Settings",G14,IF($P$4="Birds in Flight",H14,IF($P$4="Birds Perched",I14,IF($P$4="Fireworks",J14,IF($P$4="Landscape",K14,IF($P$4="Macro",L14,IF($P$4="People",M14,IF($P$4="Sports",N14,IF($P$4="Travel",O14,IF($P$4="Waterdrops",P14,IF($P$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AH14" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D14,IF($Q$4="C2 Birds in Flight",E14,IF($Q$4="C3 Landscape",F14,IF($Q$4="Default Settings",G14,IF($Q$4="Androo",H14,IF($Q$4="Birds in Flight",I14,IF($Q$4="Birds Perched",J14,IF($Q$4="Fireworks",K14,IF($Q$4="Landscape",L14,IF($Q$4="Macro",M14,IF($Q$4="People",N14,IF($Q$4="Sports",O14,IF($Q$4="Travel",P14,IF($Q$4="Waterdrops",Q14,IF($Q$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Manual Focus</x:v>
       </x:c>
-      <x:c r="AG14" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D14,IF($Q$4="C2 Birds in Flight",E14,IF($Q$4="C3 Landscape",F14,IF($Q$4="Default Settings",G14,IF($Q$4="Birds in Flight",H14,IF($Q$4="Birds Perched",I14,IF($Q$4="Fireworks",J14,IF($Q$4="Landscape",K14,IF($Q$4="Macro",L14,IF($Q$4="People",M14,IF($Q$4="Sports",N14,IF($Q$4="Travel",O14,IF($Q$4="Waterdrops",P14,IF($Q$4="Wildlife",Q14,""))))))))))))))</x:f>
+      <x:c r="AI14" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D14,IF($R$4="C2 Birds in Flight",E14,IF($R$4="C3 Landscape",F14,IF($R$4="Default Settings",G14,IF($R$4="Androo",H14,IF($R$4="Birds in Flight",I14,IF($R$4="Birds Perched",J14,IF($R$4="Fireworks",K14,IF($R$4="Landscape",L14,IF($R$4="Macro",M14,IF($R$4="People",N14,IF($R$4="Sports",O14,IF($R$4="Travel",P14,IF($R$4="Waterdrops",Q14,IF($R$4="Wildlife",R14,"")))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
     </x:row>
@@ -1909,14 +1993,14 @@
         <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
         <x:v>Case 4</x:v>
       </x:c>
-      <x:c r="I15" s="17" t="str">
+      <x:c r="J15" s="17" t="str">
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="J15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
@@ -1924,80 +2008,87 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="str">
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="N15" s="17" t="str">
+      <x:c r="O15" s="17" t="str">
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="O15" s="17" t="str">
+      <x:c r="P15" s="17" t="str">
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="P15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="Q15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R15" s="17" t="str">
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="n">
+      <x:c r="S15" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="n">
+      <x:c r="T15" s="20" t="n">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="T15" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Birds in Flight",H15,IF($D$4="Birds Perched",I15,IF($D$4="Fireworks",J15,IF($D$4="Landscape",K15,IF($D$4="Macro",L15,IF($D$4="People",M15,IF($D$4="Sports",N15,IF($D$4="Travel",O15,IF($D$4="Waterdrops",P15,IF($D$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="U15" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Androo",H15,IF($D$4="Birds in Flight",I15,IF($D$4="Birds Perched",J15,IF($D$4="Fireworks",K15,IF($D$4="Landscape",L15,IF($D$4="Macro",M15,IF($D$4="People",N15,IF($D$4="Sports",O15,IF($D$4="Travel",P15,IF($D$4="Waterdrops",Q15,IF($D$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="U15" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Birds in Flight",H15,IF($E$4="Birds Perched",I15,IF($E$4="Fireworks",J15,IF($E$4="Landscape",K15,IF($E$4="Macro",L15,IF($E$4="People",M15,IF($E$4="Sports",N15,IF($E$4="Travel",O15,IF($E$4="Waterdrops",P15,IF($E$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="V15" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Androo",H15,IF($E$4="Birds in Flight",I15,IF($E$4="Birds Perched",J15,IF($E$4="Fireworks",K15,IF($E$4="Landscape",L15,IF($E$4="Macro",M15,IF($E$4="People",N15,IF($E$4="Sports",O15,IF($E$4="Travel",P15,IF($E$4="Waterdrops",Q15,IF($E$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case 4</x:v>
       </x:c>
-      <x:c r="V15" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Birds in Flight",H15,IF($F$4="Birds Perched",I15,IF($F$4="Fireworks",J15,IF($F$4="Landscape",K15,IF($F$4="Macro",L15,IF($F$4="People",M15,IF($F$4="Sports",N15,IF($F$4="Travel",O15,IF($F$4="Waterdrops",P15,IF($F$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="W15" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Birds in Flight",H15,IF($G$4="Birds Perched",I15,IF($G$4="Fireworks",J15,IF($G$4="Landscape",K15,IF($G$4="Macro",L15,IF($G$4="People",M15,IF($G$4="Sports",N15,IF($G$4="Travel",O15,IF($G$4="Waterdrops",P15,IF($G$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Androo",H15,IF($F$4="Birds in Flight",I15,IF($F$4="Birds Perched",J15,IF($F$4="Fireworks",K15,IF($F$4="Landscape",L15,IF($F$4="Macro",M15,IF($F$4="People",N15,IF($F$4="Sports",O15,IF($F$4="Travel",P15,IF($F$4="Waterdrops",Q15,IF($F$4="Wildlife",R15,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="X15" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Androo",H15,IF($G$4="Birds in Flight",I15,IF($G$4="Birds Perched",J15,IF($G$4="Fireworks",K15,IF($G$4="Landscape",L15,IF($G$4="Macro",M15,IF($G$4="People",N15,IF($G$4="Sports",O15,IF($G$4="Travel",P15,IF($G$4="Waterdrops",Q15,IF($G$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="X15" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Birds in Flight",H15,IF($H$4="Birds Perched",I15,IF($H$4="Fireworks",J15,IF($H$4="Landscape",K15,IF($H$4="Macro",L15,IF($H$4="People",M15,IF($H$4="Sports",N15,IF($H$4="Travel",O15,IF($H$4="Waterdrops",P15,IF($H$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="Y15" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Androo",H15,IF($H$4="Birds in Flight",I15,IF($H$4="Birds Perched",J15,IF($H$4="Fireworks",K15,IF($H$4="Landscape",L15,IF($H$4="Macro",M15,IF($H$4="People",N15,IF($H$4="Sports",O15,IF($H$4="Travel",P15,IF($H$4="Waterdrops",Q15,IF($H$4="Wildlife",R15,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Z15" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Androo",H15,IF($I$4="Birds in Flight",I15,IF($I$4="Birds Perched",J15,IF($I$4="Fireworks",K15,IF($I$4="Landscape",L15,IF($I$4="Macro",M15,IF($I$4="People",N15,IF($I$4="Sports",O15,IF($I$4="Travel",P15,IF($I$4="Waterdrops",Q15,IF($I$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case 4</x:v>
       </x:c>
-      <x:c r="Y15" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Birds in Flight",H15,IF($I$4="Birds Perched",I15,IF($I$4="Fireworks",J15,IF($I$4="Landscape",K15,IF($I$4="Macro",L15,IF($I$4="People",M15,IF($I$4="Sports",N15,IF($I$4="Travel",O15,IF($I$4="Waterdrops",P15,IF($I$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="AA15" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Androo",H15,IF($J$4="Birds in Flight",I15,IF($J$4="Birds Perched",J15,IF($J$4="Fireworks",K15,IF($J$4="Landscape",L15,IF($J$4="Macro",M15,IF($J$4="People",N15,IF($J$4="Sports",O15,IF($J$4="Travel",P15,IF($J$4="Waterdrops",Q15,IF($J$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="Z15" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Birds in Flight",H15,IF($J$4="Birds Perched",I15,IF($J$4="Fireworks",J15,IF($J$4="Landscape",K15,IF($J$4="Macro",L15,IF($J$4="People",M15,IF($J$4="Sports",N15,IF($J$4="Travel",O15,IF($J$4="Waterdrops",P15,IF($J$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA15" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Birds in Flight",H15,IF($K$4="Birds Perched",I15,IF($K$4="Fireworks",J15,IF($K$4="Landscape",K15,IF($K$4="Macro",L15,IF($K$4="People",M15,IF($K$4="Sports",N15,IF($K$4="Travel",O15,IF($K$4="Waterdrops",P15,IF($K$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AB15" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Birds in Flight",H15,IF($L$4="Birds Perched",I15,IF($L$4="Fireworks",J15,IF($L$4="Landscape",K15,IF($L$4="Macro",L15,IF($L$4="People",M15,IF($L$4="Sports",N15,IF($L$4="Travel",O15,IF($L$4="Waterdrops",P15,IF($L$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Androo",H15,IF($K$4="Birds in Flight",I15,IF($K$4="Birds Perched",J15,IF($K$4="Fireworks",K15,IF($K$4="Landscape",L15,IF($K$4="Macro",M15,IF($K$4="People",N15,IF($K$4="Sports",O15,IF($K$4="Travel",P15,IF($K$4="Waterdrops",Q15,IF($K$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC15" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Birds in Flight",H15,IF($M$4="Birds Perched",I15,IF($M$4="Fireworks",J15,IF($M$4="Landscape",K15,IF($M$4="Macro",L15,IF($M$4="People",M15,IF($M$4="Sports",N15,IF($M$4="Travel",O15,IF($M$4="Waterdrops",P15,IF($M$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Androo",H15,IF($L$4="Birds in Flight",I15,IF($L$4="Birds Perched",J15,IF($L$4="Fireworks",K15,IF($L$4="Landscape",L15,IF($L$4="Macro",M15,IF($L$4="People",N15,IF($L$4="Sports",O15,IF($L$4="Travel",P15,IF($L$4="Waterdrops",Q15,IF($L$4="Wildlife",R15,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AD15" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Androo",H15,IF($M$4="Birds in Flight",I15,IF($M$4="Birds Perched",J15,IF($M$4="Fireworks",K15,IF($M$4="Landscape",L15,IF($M$4="Macro",M15,IF($M$4="People",N15,IF($M$4="Sports",O15,IF($M$4="Travel",P15,IF($M$4="Waterdrops",Q15,IF($M$4="Wildlife",R15,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AE15" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Androo",H15,IF($N$4="Birds in Flight",I15,IF($N$4="Birds Perched",J15,IF($N$4="Fireworks",K15,IF($N$4="Landscape",L15,IF($N$4="Macro",M15,IF($N$4="People",N15,IF($N$4="Sports",O15,IF($N$4="Travel",P15,IF($N$4="Waterdrops",Q15,IF($N$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="AD15" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Birds in Flight",H15,IF($N$4="Birds Perched",I15,IF($N$4="Fireworks",J15,IF($N$4="Landscape",K15,IF($N$4="Macro",L15,IF($N$4="People",M15,IF($N$4="Sports",N15,IF($N$4="Travel",O15,IF($N$4="Waterdrops",P15,IF($N$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="AF15" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Androo",H15,IF($O$4="Birds in Flight",I15,IF($O$4="Birds Perched",J15,IF($O$4="Fireworks",K15,IF($O$4="Landscape",L15,IF($O$4="Macro",M15,IF($O$4="People",N15,IF($O$4="Sports",O15,IF($O$4="Travel",P15,IF($O$4="Waterdrops",Q15,IF($O$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="AE15" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Birds in Flight",H15,IF($O$4="Birds Perched",I15,IF($O$4="Fireworks",J15,IF($O$4="Landscape",K15,IF($O$4="Macro",L15,IF($O$4="People",M15,IF($O$4="Sports",N15,IF($O$4="Travel",O15,IF($O$4="Waterdrops",P15,IF($O$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="AG15" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Androo",H15,IF($P$4="Birds in Flight",I15,IF($P$4="Birds Perched",J15,IF($P$4="Fireworks",K15,IF($P$4="Landscape",L15,IF($P$4="Macro",M15,IF($P$4="People",N15,IF($P$4="Sports",O15,IF($P$4="Travel",P15,IF($P$4="Waterdrops",Q15,IF($P$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="AF15" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Birds in Flight",H15,IF($P$4="Birds Perched",I15,IF($P$4="Fireworks",J15,IF($P$4="Landscape",K15,IF($P$4="Macro",L15,IF($P$4="People",M15,IF($P$4="Sports",N15,IF($P$4="Travel",O15,IF($P$4="Waterdrops",P15,IF($P$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AG15" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Birds in Flight",H15,IF($Q$4="Birds Perched",I15,IF($Q$4="Fireworks",J15,IF($Q$4="Landscape",K15,IF($Q$4="Macro",L15,IF($Q$4="People",M15,IF($Q$4="Sports",N15,IF($Q$4="Travel",O15,IF($Q$4="Waterdrops",P15,IF($Q$4="Wildlife",Q15,""))))))))))))))</x:f>
+      <x:c r="AH15" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Androo",H15,IF($Q$4="Birds in Flight",I15,IF($Q$4="Birds Perched",J15,IF($Q$4="Fireworks",K15,IF($Q$4="Landscape",L15,IF($Q$4="Macro",M15,IF($Q$4="People",N15,IF($Q$4="Sports",O15,IF($Q$4="Travel",P15,IF($Q$4="Waterdrops",Q15,IF($Q$4="Wildlife",R15,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI15" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D15,IF($R$4="C2 Birds in Flight",E15,IF($R$4="C3 Landscape",F15,IF($R$4="Default Settings",G15,IF($R$4="Androo",H15,IF($R$4="Birds in Flight",I15,IF($R$4="Birds Perched",J15,IF($R$4="Fireworks",K15,IF($R$4="Landscape",L15,IF($R$4="Macro",M15,IF($R$4="People",N15,IF($R$4="Sports",O15,IF($R$4="Travel",P15,IF($R$4="Waterdrops",Q15,IF($R$4="Wildlife",R15,"")))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
     </x:row>
@@ -2023,15 +2114,15 @@
       <x:c r="G16" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="H16" s="17" t="n">
+      <x:c r="H16" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="17" t="n">
+      <x:c r="J16" s="17" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="J16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
@@ -2039,80 +2130,87 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M16" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="N16" s="17" t="n">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="O16" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="P16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Q16" s="17" t="n">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Q16" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R16" s="17" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="R16" s="20" t="n">
+      <x:c r="S16" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="S16" s="20" t="n">
+      <x:c r="T16" s="20" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="T16" s="38" t="n">
-        <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Birds in Flight",H16,IF($D$4="Birds Perched",I16,IF($D$4="Fireworks",J16,IF($D$4="Landscape",K16,IF($D$4="Macro",L16,IF($D$4="People",M16,IF($D$4="Sports",N16,IF($D$4="Travel",O16,IF($D$4="Waterdrops",P16,IF($D$4="Wildlife",Q16,""))))))))))))))</x:f>
+      <x:c r="U16" s="38" t="n">
+        <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Androo",H16,IF($D$4="Birds in Flight",I16,IF($D$4="Birds Perched",J16,IF($D$4="Fireworks",K16,IF($D$4="Landscape",L16,IF($D$4="Macro",M16,IF($D$4="People",N16,IF($D$4="Sports",O16,IF($D$4="Travel",P16,IF($D$4="Waterdrops",Q16,IF($D$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="U16" s="38" t="n">
-        <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Birds in Flight",H16,IF($E$4="Birds Perched",I16,IF($E$4="Fireworks",J16,IF($E$4="Landscape",K16,IF($E$4="Macro",L16,IF($E$4="People",M16,IF($E$4="Sports",N16,IF($E$4="Travel",O16,IF($E$4="Waterdrops",P16,IF($E$4="Wildlife",Q16,""))))))))))))))</x:f>
+      <x:c r="V16" s="38" t="n">
+        <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Androo",H16,IF($E$4="Birds in Flight",I16,IF($E$4="Birds Perched",J16,IF($E$4="Fireworks",K16,IF($E$4="Landscape",L16,IF($E$4="Macro",M16,IF($E$4="People",N16,IF($E$4="Sports",O16,IF($E$4="Travel",P16,IF($E$4="Waterdrops",Q16,IF($E$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V16" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Birds in Flight",H16,IF($F$4="Birds Perched",I16,IF($F$4="Fireworks",J16,IF($F$4="Landscape",K16,IF($F$4="Macro",L16,IF($F$4="People",M16,IF($F$4="Sports",N16,IF($F$4="Travel",O16,IF($F$4="Waterdrops",P16,IF($F$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="W16" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Birds in Flight",H16,IF($G$4="Birds Perched",I16,IF($G$4="Fireworks",J16,IF($G$4="Landscape",K16,IF($G$4="Macro",L16,IF($G$4="People",M16,IF($G$4="Sports",N16,IF($G$4="Travel",O16,IF($G$4="Waterdrops",P16,IF($G$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="X16" s="38" t="n">
-        <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Birds in Flight",H16,IF($H$4="Birds Perched",I16,IF($H$4="Fireworks",J16,IF($H$4="Landscape",K16,IF($H$4="Macro",L16,IF($H$4="People",M16,IF($H$4="Sports",N16,IF($H$4="Travel",O16,IF($H$4="Waterdrops",P16,IF($H$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Androo",H16,IF($F$4="Birds in Flight",I16,IF($F$4="Birds Perched",J16,IF($F$4="Fireworks",K16,IF($F$4="Landscape",L16,IF($F$4="Macro",M16,IF($F$4="People",N16,IF($F$4="Sports",O16,IF($F$4="Travel",P16,IF($F$4="Waterdrops",Q16,IF($F$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="X16" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Androo",H16,IF($G$4="Birds in Flight",I16,IF($G$4="Birds Perched",J16,IF($G$4="Fireworks",K16,IF($G$4="Landscape",L16,IF($G$4="Macro",M16,IF($G$4="People",N16,IF($G$4="Sports",O16,IF($G$4="Travel",P16,IF($G$4="Waterdrops",Q16,IF($G$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Y16" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Androo",H16,IF($H$4="Birds in Flight",I16,IF($H$4="Birds Perched",J16,IF($H$4="Fireworks",K16,IF($H$4="Landscape",L16,IF($H$4="Macro",M16,IF($H$4="People",N16,IF($H$4="Sports",O16,IF($H$4="Travel",P16,IF($H$4="Waterdrops",Q16,IF($H$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Z16" s="38" t="n">
+        <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Androo",H16,IF($I$4="Birds in Flight",I16,IF($I$4="Birds Perched",J16,IF($I$4="Fireworks",K16,IF($I$4="Landscape",L16,IF($I$4="Macro",M16,IF($I$4="People",N16,IF($I$4="Sports",O16,IF($I$4="Travel",P16,IF($I$4="Waterdrops",Q16,IF($I$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y16" s="38" t="n">
-        <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Birds in Flight",H16,IF($I$4="Birds Perched",I16,IF($I$4="Fireworks",J16,IF($I$4="Landscape",K16,IF($I$4="Macro",L16,IF($I$4="People",M16,IF($I$4="Sports",N16,IF($I$4="Travel",O16,IF($I$4="Waterdrops",P16,IF($I$4="Wildlife",Q16,""))))))))))))))</x:f>
+      <x:c r="AA16" s="38" t="n">
+        <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Androo",H16,IF($J$4="Birds in Flight",I16,IF($J$4="Birds Perched",J16,IF($J$4="Fireworks",K16,IF($J$4="Landscape",L16,IF($J$4="Macro",M16,IF($J$4="People",N16,IF($J$4="Sports",O16,IF($J$4="Travel",P16,IF($J$4="Waterdrops",Q16,IF($J$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="Z16" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Birds in Flight",H16,IF($J$4="Birds Perched",I16,IF($J$4="Fireworks",J16,IF($J$4="Landscape",K16,IF($J$4="Macro",L16,IF($J$4="People",M16,IF($J$4="Sports",N16,IF($J$4="Travel",O16,IF($J$4="Waterdrops",P16,IF($J$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA16" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Birds in Flight",H16,IF($K$4="Birds Perched",I16,IF($K$4="Fireworks",J16,IF($K$4="Landscape",K16,IF($K$4="Macro",L16,IF($K$4="People",M16,IF($K$4="Sports",N16,IF($K$4="Travel",O16,IF($K$4="Waterdrops",P16,IF($K$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AB16" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Birds in Flight",H16,IF($L$4="Birds Perched",I16,IF($L$4="Fireworks",J16,IF($L$4="Landscape",K16,IF($L$4="Macro",L16,IF($L$4="People",M16,IF($L$4="Sports",N16,IF($L$4="Travel",O16,IF($L$4="Waterdrops",P16,IF($L$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Androo",H16,IF($K$4="Birds in Flight",I16,IF($K$4="Birds Perched",J16,IF($K$4="Fireworks",K16,IF($K$4="Landscape",L16,IF($K$4="Macro",M16,IF($K$4="People",N16,IF($K$4="Sports",O16,IF($K$4="Travel",P16,IF($K$4="Waterdrops",Q16,IF($K$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC16" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Birds in Flight",H16,IF($M$4="Birds Perched",I16,IF($M$4="Fireworks",J16,IF($M$4="Landscape",K16,IF($M$4="Macro",L16,IF($M$4="People",M16,IF($M$4="Sports",N16,IF($M$4="Travel",O16,IF($M$4="Waterdrops",P16,IF($M$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AD16" s="38" t="n">
-        <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Birds in Flight",H16,IF($N$4="Birds Perched",I16,IF($N$4="Fireworks",J16,IF($N$4="Landscape",K16,IF($N$4="Macro",L16,IF($N$4="People",M16,IF($N$4="Sports",N16,IF($N$4="Travel",O16,IF($N$4="Waterdrops",P16,IF($N$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Androo",H16,IF($L$4="Birds in Flight",I16,IF($L$4="Birds Perched",J16,IF($L$4="Fireworks",K16,IF($L$4="Landscape",L16,IF($L$4="Macro",M16,IF($L$4="People",N16,IF($L$4="Sports",O16,IF($L$4="Travel",P16,IF($L$4="Waterdrops",Q16,IF($L$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AD16" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Androo",H16,IF($M$4="Birds in Flight",I16,IF($M$4="Birds Perched",J16,IF($M$4="Fireworks",K16,IF($M$4="Landscape",L16,IF($M$4="Macro",M16,IF($M$4="People",N16,IF($M$4="Sports",O16,IF($M$4="Travel",P16,IF($M$4="Waterdrops",Q16,IF($M$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AE16" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Androo",H16,IF($N$4="Birds in Flight",I16,IF($N$4="Birds Perched",J16,IF($N$4="Fireworks",K16,IF($N$4="Landscape",L16,IF($N$4="Macro",M16,IF($N$4="People",N16,IF($N$4="Sports",O16,IF($N$4="Travel",P16,IF($N$4="Waterdrops",Q16,IF($N$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF16" s="38" t="n">
+        <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Androo",H16,IF($O$4="Birds in Flight",I16,IF($O$4="Birds Perched",J16,IF($O$4="Fireworks",K16,IF($O$4="Landscape",L16,IF($O$4="Macro",M16,IF($O$4="People",N16,IF($O$4="Sports",O16,IF($O$4="Travel",P16,IF($O$4="Waterdrops",Q16,IF($O$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="AE16" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Birds in Flight",H16,IF($O$4="Birds Perched",I16,IF($O$4="Fireworks",J16,IF($O$4="Landscape",K16,IF($O$4="Macro",L16,IF($O$4="People",M16,IF($O$4="Sports",N16,IF($O$4="Travel",O16,IF($O$4="Waterdrops",P16,IF($O$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AF16" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Birds in Flight",H16,IF($P$4="Birds Perched",I16,IF($P$4="Fireworks",J16,IF($P$4="Landscape",K16,IF($P$4="Macro",L16,IF($P$4="People",M16,IF($P$4="Sports",N16,IF($P$4="Travel",O16,IF($P$4="Waterdrops",P16,IF($P$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AG16" s="38" t="n">
-        <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Birds in Flight",H16,IF($Q$4="Birds Perched",I16,IF($Q$4="Fireworks",J16,IF($Q$4="Landscape",K16,IF($Q$4="Macro",L16,IF($Q$4="People",M16,IF($Q$4="Sports",N16,IF($Q$4="Travel",O16,IF($Q$4="Waterdrops",P16,IF($Q$4="Wildlife",Q16,""))))))))))))))</x:f>
+      <x:c r="AG16" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Androo",H16,IF($P$4="Birds in Flight",I16,IF($P$4="Birds Perched",J16,IF($P$4="Fireworks",K16,IF($P$4="Landscape",L16,IF($P$4="Macro",M16,IF($P$4="People",N16,IF($P$4="Sports",O16,IF($P$4="Travel",P16,IF($P$4="Waterdrops",Q16,IF($P$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AH16" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Androo",H16,IF($Q$4="Birds in Flight",I16,IF($Q$4="Birds Perched",J16,IF($Q$4="Fireworks",K16,IF($Q$4="Landscape",L16,IF($Q$4="Macro",M16,IF($Q$4="People",N16,IF($Q$4="Sports",O16,IF($Q$4="Travel",P16,IF($Q$4="Waterdrops",Q16,IF($Q$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI16" s="38" t="n">
+        <x:f>IF($R$4="C1 Wildlife",D16,IF($R$4="C2 Birds in Flight",E16,IF($R$4="C3 Landscape",F16,IF($R$4="Default Settings",G16,IF($R$4="Androo",H16,IF($R$4="Birds in Flight",I16,IF($R$4="Birds Perched",J16,IF($R$4="Fireworks",K16,IF($R$4="Landscape",L16,IF($R$4="Macro",M16,IF($R$4="People",N16,IF($R$4="Sports",O16,IF($R$4="Travel",P16,IF($R$4="Waterdrops",Q16,IF($R$4="Wildlife",R16,"")))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
     </x:row>
@@ -2139,13 +2237,13 @@
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
         <x:v>+1</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="K17" s="17" t="str">
         <x:v>Not Used</x:v>
@@ -2154,80 +2252,87 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M17" s="17" t="str">
-        <x:v>Auto</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="O17" s="17" t="str">
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="O17" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="P17" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="Q17" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R17" s="17" t="str">
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="R17" s="20" t="n">
+      <x:c r="S17" s="20" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="n">
+      <x:c r="T17" s="20" t="n">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="T17" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Birds in Flight",H17,IF($D$4="Birds Perched",I17,IF($D$4="Fireworks",J17,IF($D$4="Landscape",K17,IF($D$4="Macro",L17,IF($D$4="People",M17,IF($D$4="Sports",N17,IF($D$4="Travel",O17,IF($D$4="Waterdrops",P17,IF($D$4="Wildlife",Q17,""))))))))))))))</x:f>
+      <x:c r="U17" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Androo",H17,IF($D$4="Birds in Flight",I17,IF($D$4="Birds Perched",J17,IF($D$4="Fireworks",K17,IF($D$4="Landscape",L17,IF($D$4="Macro",M17,IF($D$4="People",N17,IF($D$4="Sports",O17,IF($D$4="Travel",P17,IF($D$4="Waterdrops",Q17,IF($D$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="U17" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Birds in Flight",H17,IF($E$4="Birds Perched",I17,IF($E$4="Fireworks",J17,IF($E$4="Landscape",K17,IF($E$4="Macro",L17,IF($E$4="People",M17,IF($E$4="Sports",N17,IF($E$4="Travel",O17,IF($E$4="Waterdrops",P17,IF($E$4="Wildlife",Q17,""))))))))))))))</x:f>
+      <x:c r="V17" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Androo",H17,IF($E$4="Birds in Flight",I17,IF($E$4="Birds Perched",J17,IF($E$4="Fireworks",K17,IF($E$4="Landscape",L17,IF($E$4="Macro",M17,IF($E$4="People",N17,IF($E$4="Sports",O17,IF($E$4="Travel",P17,IF($E$4="Waterdrops",Q17,IF($E$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="V17" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Birds in Flight",H17,IF($F$4="Birds Perched",I17,IF($F$4="Fireworks",J17,IF($F$4="Landscape",K17,IF($F$4="Macro",L17,IF($F$4="People",M17,IF($F$4="Sports",N17,IF($F$4="Travel",O17,IF($F$4="Waterdrops",P17,IF($F$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="W17" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Birds in Flight",H17,IF($G$4="Birds Perched",I17,IF($G$4="Fireworks",J17,IF($G$4="Landscape",K17,IF($G$4="Macro",L17,IF($G$4="People",M17,IF($G$4="Sports",N17,IF($G$4="Travel",O17,IF($G$4="Waterdrops",P17,IF($G$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
+        <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Androo",H17,IF($F$4="Birds in Flight",I17,IF($F$4="Birds Perched",J17,IF($F$4="Fireworks",K17,IF($F$4="Landscape",L17,IF($F$4="Macro",M17,IF($F$4="People",N17,IF($F$4="Sports",O17,IF($F$4="Travel",P17,IF($F$4="Waterdrops",Q17,IF($F$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="X17" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Birds in Flight",H17,IF($H$4="Birds Perched",I17,IF($H$4="Fireworks",J17,IF($H$4="Landscape",K17,IF($H$4="Macro",L17,IF($H$4="People",M17,IF($H$4="Sports",N17,IF($H$4="Travel",O17,IF($H$4="Waterdrops",P17,IF($H$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Androo",H17,IF($G$4="Birds in Flight",I17,IF($G$4="Birds Perched",J17,IF($G$4="Fireworks",K17,IF($G$4="Landscape",L17,IF($G$4="Macro",M17,IF($G$4="People",N17,IF($G$4="Sports",O17,IF($G$4="Travel",P17,IF($G$4="Waterdrops",Q17,IF($G$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Y17" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Androo",H17,IF($H$4="Birds in Flight",I17,IF($H$4="Birds Perched",J17,IF($H$4="Fireworks",K17,IF($H$4="Landscape",L17,IF($H$4="Macro",M17,IF($H$4="People",N17,IF($H$4="Sports",O17,IF($H$4="Travel",P17,IF($H$4="Waterdrops",Q17,IF($H$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Z17" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Androo",H17,IF($I$4="Birds in Flight",I17,IF($I$4="Birds Perched",J17,IF($I$4="Fireworks",K17,IF($I$4="Landscape",L17,IF($I$4="Macro",M17,IF($I$4="People",N17,IF($I$4="Sports",O17,IF($I$4="Travel",P17,IF($I$4="Waterdrops",Q17,IF($I$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="Y17" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Birds in Flight",H17,IF($I$4="Birds Perched",I17,IF($I$4="Fireworks",J17,IF($I$4="Landscape",K17,IF($I$4="Macro",L17,IF($I$4="People",M17,IF($I$4="Sports",N17,IF($I$4="Travel",O17,IF($I$4="Waterdrops",P17,IF($I$4="Wildlife",Q17,""))))))))))))))</x:f>
+      <x:c r="AA17" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Androo",H17,IF($J$4="Birds in Flight",I17,IF($J$4="Birds Perched",J17,IF($J$4="Fireworks",K17,IF($J$4="Landscape",L17,IF($J$4="Macro",M17,IF($J$4="People",N17,IF($J$4="Sports",O17,IF($J$4="Travel",P17,IF($J$4="Waterdrops",Q17,IF($J$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="Z17" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Birds in Flight",H17,IF($J$4="Birds Perched",I17,IF($J$4="Fireworks",J17,IF($J$4="Landscape",K17,IF($J$4="Macro",L17,IF($J$4="People",M17,IF($J$4="Sports",N17,IF($J$4="Travel",O17,IF($J$4="Waterdrops",P17,IF($J$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA17" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Birds in Flight",H17,IF($K$4="Birds Perched",I17,IF($K$4="Fireworks",J17,IF($K$4="Landscape",K17,IF($K$4="Macro",L17,IF($K$4="People",M17,IF($K$4="Sports",N17,IF($K$4="Travel",O17,IF($K$4="Waterdrops",P17,IF($K$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AB17" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Birds in Flight",H17,IF($L$4="Birds Perched",I17,IF($L$4="Fireworks",J17,IF($L$4="Landscape",K17,IF($L$4="Macro",L17,IF($L$4="People",M17,IF($L$4="Sports",N17,IF($L$4="Travel",O17,IF($L$4="Waterdrops",P17,IF($L$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Androo",H17,IF($K$4="Birds in Flight",I17,IF($K$4="Birds Perched",J17,IF($K$4="Fireworks",K17,IF($K$4="Landscape",L17,IF($K$4="Macro",M17,IF($K$4="People",N17,IF($K$4="Sports",O17,IF($K$4="Travel",P17,IF($K$4="Waterdrops",Q17,IF($K$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC17" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Birds in Flight",H17,IF($M$4="Birds Perched",I17,IF($M$4="Fireworks",J17,IF($M$4="Landscape",K17,IF($M$4="Macro",L17,IF($M$4="People",M17,IF($M$4="Sports",N17,IF($M$4="Travel",O17,IF($M$4="Waterdrops",P17,IF($M$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
+        <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Androo",H17,IF($L$4="Birds in Flight",I17,IF($L$4="Birds Perched",J17,IF($L$4="Fireworks",K17,IF($L$4="Landscape",L17,IF($L$4="Macro",M17,IF($L$4="People",N17,IF($L$4="Sports",O17,IF($L$4="Travel",P17,IF($L$4="Waterdrops",Q17,IF($L$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AD17" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Birds in Flight",H17,IF($N$4="Birds Perched",I17,IF($N$4="Fireworks",J17,IF($N$4="Landscape",K17,IF($N$4="Macro",L17,IF($N$4="People",M17,IF($N$4="Sports",N17,IF($N$4="Travel",O17,IF($N$4="Waterdrops",P17,IF($N$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Androo",H17,IF($M$4="Birds in Flight",I17,IF($M$4="Birds Perched",J17,IF($M$4="Fireworks",K17,IF($M$4="Landscape",L17,IF($M$4="Macro",M17,IF($M$4="People",N17,IF($M$4="Sports",O17,IF($M$4="Travel",P17,IF($M$4="Waterdrops",Q17,IF($M$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AE17" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Androo",H17,IF($N$4="Birds in Flight",I17,IF($N$4="Birds Perched",J17,IF($N$4="Fireworks",K17,IF($N$4="Landscape",L17,IF($N$4="Macro",M17,IF($N$4="People",N17,IF($N$4="Sports",O17,IF($N$4="Travel",P17,IF($N$4="Waterdrops",Q17,IF($N$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF17" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Androo",H17,IF($O$4="Birds in Flight",I17,IF($O$4="Birds Perched",J17,IF($O$4="Fireworks",K17,IF($O$4="Landscape",L17,IF($O$4="Macro",M17,IF($O$4="People",N17,IF($O$4="Sports",O17,IF($O$4="Travel",P17,IF($O$4="Waterdrops",Q17,IF($O$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="AE17" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Birds in Flight",H17,IF($O$4="Birds Perched",I17,IF($O$4="Fireworks",J17,IF($O$4="Landscape",K17,IF($O$4="Macro",L17,IF($O$4="People",M17,IF($O$4="Sports",N17,IF($O$4="Travel",O17,IF($O$4="Waterdrops",P17,IF($O$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AF17" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Birds in Flight",H17,IF($P$4="Birds Perched",I17,IF($P$4="Fireworks",J17,IF($P$4="Landscape",K17,IF($P$4="Macro",L17,IF($P$4="People",M17,IF($P$4="Sports",N17,IF($P$4="Travel",O17,IF($P$4="Waterdrops",P17,IF($P$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AG17" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Birds in Flight",H17,IF($Q$4="Birds Perched",I17,IF($Q$4="Fireworks",J17,IF($Q$4="Landscape",K17,IF($Q$4="Macro",L17,IF($Q$4="People",M17,IF($Q$4="Sports",N17,IF($Q$4="Travel",O17,IF($Q$4="Waterdrops",P17,IF($Q$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Androo",H17,IF($P$4="Birds in Flight",I17,IF($P$4="Birds Perched",J17,IF($P$4="Fireworks",K17,IF($P$4="Landscape",L17,IF($P$4="Macro",M17,IF($P$4="People",N17,IF($P$4="Sports",O17,IF($P$4="Travel",P17,IF($P$4="Waterdrops",Q17,IF($P$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AH17" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Androo",H17,IF($Q$4="Birds in Flight",I17,IF($Q$4="Birds Perched",J17,IF($Q$4="Fireworks",K17,IF($Q$4="Landscape",L17,IF($Q$4="Macro",M17,IF($Q$4="People",N17,IF($Q$4="Sports",O17,IF($Q$4="Travel",P17,IF($Q$4="Waterdrops",Q17,IF($Q$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI17" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D17,IF($R$4="C2 Birds in Flight",E17,IF($R$4="C3 Landscape",F17,IF($R$4="Default Settings",G17,IF($R$4="Androo",H17,IF($R$4="Birds in Flight",I17,IF($R$4="Birds Perched",J17,IF($R$4="Fireworks",K17,IF($R$4="Landscape",L17,IF($R$4="Macro",M17,IF($R$4="People",N17,IF($R$4="Sports",O17,IF($R$4="Travel",P17,IF($R$4="Waterdrops",Q17,IF($R$4="Wildlife",R17,"")))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
     </x:row>
@@ -2260,7 +2365,7 @@
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="K18" s="17" t="str">
         <x:v>Not Used</x:v>
@@ -2269,80 +2374,87 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M18" s="17" t="str">
-        <x:v>On subject</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str">
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="O18" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="P18" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q18" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R18" s="17" t="str">
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="R18" s="20" t="n">
+      <x:c r="S18" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="S18" s="20" t="n">
+      <x:c r="T18" s="20" t="n">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="T18" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Birds in Flight",H18,IF($D$4="Birds Perched",I18,IF($D$4="Fireworks",J18,IF($D$4="Landscape",K18,IF($D$4="Macro",L18,IF($D$4="People",M18,IF($D$4="Sports",N18,IF($D$4="Travel",O18,IF($D$4="Waterdrops",P18,IF($D$4="Wildlife",Q18,""))))))))))))))</x:f>
+      <x:c r="U18" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Androo",H18,IF($D$4="Birds in Flight",I18,IF($D$4="Birds Perched",J18,IF($D$4="Fireworks",K18,IF($D$4="Landscape",L18,IF($D$4="Macro",M18,IF($D$4="People",N18,IF($D$4="Sports",O18,IF($D$4="Travel",P18,IF($D$4="Waterdrops",Q18,IF($D$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="U18" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Birds in Flight",H18,IF($E$4="Birds Perched",I18,IF($E$4="Fireworks",J18,IF($E$4="Landscape",K18,IF($E$4="Macro",L18,IF($E$4="People",M18,IF($E$4="Sports",N18,IF($E$4="Travel",O18,IF($E$4="Waterdrops",P18,IF($E$4="Wildlife",Q18,""))))))))))))))</x:f>
+      <x:c r="V18" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Androo",H18,IF($E$4="Birds in Flight",I18,IF($E$4="Birds Perched",J18,IF($E$4="Fireworks",K18,IF($E$4="Landscape",L18,IF($E$4="Macro",M18,IF($E$4="People",N18,IF($E$4="Sports",O18,IF($E$4="Travel",P18,IF($E$4="Waterdrops",Q18,IF($E$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="V18" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Birds in Flight",H18,IF($F$4="Birds Perched",I18,IF($F$4="Fireworks",J18,IF($F$4="Landscape",K18,IF($F$4="Macro",L18,IF($F$4="People",M18,IF($F$4="Sports",N18,IF($F$4="Travel",O18,IF($F$4="Waterdrops",P18,IF($F$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="W18" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Birds in Flight",H18,IF($G$4="Birds Perched",I18,IF($G$4="Fireworks",J18,IF($G$4="Landscape",K18,IF($G$4="Macro",L18,IF($G$4="People",M18,IF($G$4="Sports",N18,IF($G$4="Travel",O18,IF($G$4="Waterdrops",P18,IF($G$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Androo",H18,IF($F$4="Birds in Flight",I18,IF($F$4="Birds Perched",J18,IF($F$4="Fireworks",K18,IF($F$4="Landscape",L18,IF($F$4="Macro",M18,IF($F$4="People",N18,IF($F$4="Sports",O18,IF($F$4="Travel",P18,IF($F$4="Waterdrops",Q18,IF($F$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="X18" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Androo",H18,IF($G$4="Birds in Flight",I18,IF($G$4="Birds Perched",J18,IF($G$4="Fireworks",K18,IF($G$4="Landscape",L18,IF($G$4="Macro",M18,IF($G$4="People",N18,IF($G$4="Sports",O18,IF($G$4="Travel",P18,IF($G$4="Waterdrops",Q18,IF($G$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="X18" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Birds in Flight",H18,IF($H$4="Birds Perched",I18,IF($H$4="Fireworks",J18,IF($H$4="Landscape",K18,IF($H$4="Macro",L18,IF($H$4="People",M18,IF($H$4="Sports",N18,IF($H$4="Travel",O18,IF($H$4="Waterdrops",P18,IF($H$4="Wildlife",Q18,""))))))))))))))</x:f>
+      <x:c r="Y18" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Androo",H18,IF($H$4="Birds in Flight",I18,IF($H$4="Birds Perched",J18,IF($H$4="Fireworks",K18,IF($H$4="Landscape",L18,IF($H$4="Macro",M18,IF($H$4="People",N18,IF($H$4="Sports",O18,IF($H$4="Travel",P18,IF($H$4="Waterdrops",Q18,IF($H$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="Y18" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Birds in Flight",H18,IF($I$4="Birds Perched",I18,IF($I$4="Fireworks",J18,IF($I$4="Landscape",K18,IF($I$4="Macro",L18,IF($I$4="People",M18,IF($I$4="Sports",N18,IF($I$4="Travel",O18,IF($I$4="Waterdrops",P18,IF($I$4="Wildlife",Q18,""))))))))))))))</x:f>
+      <x:c r="Z18" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Androo",H18,IF($I$4="Birds in Flight",I18,IF($I$4="Birds Perched",J18,IF($I$4="Fireworks",K18,IF($I$4="Landscape",L18,IF($I$4="Macro",M18,IF($I$4="People",N18,IF($I$4="Sports",O18,IF($I$4="Travel",P18,IF($I$4="Waterdrops",Q18,IF($I$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="Z18" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Birds in Flight",H18,IF($J$4="Birds Perched",I18,IF($J$4="Fireworks",J18,IF($J$4="Landscape",K18,IF($J$4="Macro",L18,IF($J$4="People",M18,IF($J$4="Sports",N18,IF($J$4="Travel",O18,IF($J$4="Waterdrops",P18,IF($J$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AA18" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Birds in Flight",H18,IF($K$4="Birds Perched",I18,IF($K$4="Fireworks",J18,IF($K$4="Landscape",K18,IF($K$4="Macro",L18,IF($K$4="People",M18,IF($K$4="Sports",N18,IF($K$4="Travel",O18,IF($K$4="Waterdrops",P18,IF($K$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Androo",H18,IF($J$4="Birds in Flight",I18,IF($J$4="Birds Perched",J18,IF($J$4="Fireworks",K18,IF($J$4="Landscape",L18,IF($J$4="Macro",M18,IF($J$4="People",N18,IF($J$4="Sports",O18,IF($J$4="Travel",P18,IF($J$4="Waterdrops",Q18,IF($J$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="AB18" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Birds in Flight",H18,IF($L$4="Birds Perched",I18,IF($L$4="Fireworks",J18,IF($L$4="Landscape",K18,IF($L$4="Macro",L18,IF($L$4="People",M18,IF($L$4="Sports",N18,IF($L$4="Travel",O18,IF($L$4="Waterdrops",P18,IF($L$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Androo",H18,IF($K$4="Birds in Flight",I18,IF($K$4="Birds Perched",J18,IF($K$4="Fireworks",K18,IF($K$4="Landscape",L18,IF($K$4="Macro",M18,IF($K$4="People",N18,IF($K$4="Sports",O18,IF($K$4="Travel",P18,IF($K$4="Waterdrops",Q18,IF($K$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC18" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Birds in Flight",H18,IF($M$4="Birds Perched",I18,IF($M$4="Fireworks",J18,IF($M$4="Landscape",K18,IF($M$4="Macro",L18,IF($M$4="People",M18,IF($M$4="Sports",N18,IF($M$4="Travel",O18,IF($M$4="Waterdrops",P18,IF($M$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Androo",H18,IF($L$4="Birds in Flight",I18,IF($L$4="Birds Perched",J18,IF($L$4="Fireworks",K18,IF($L$4="Landscape",L18,IF($L$4="Macro",M18,IF($L$4="People",N18,IF($L$4="Sports",O18,IF($L$4="Travel",P18,IF($L$4="Waterdrops",Q18,IF($L$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AD18" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Androo",H18,IF($M$4="Birds in Flight",I18,IF($M$4="Birds Perched",J18,IF($M$4="Fireworks",K18,IF($M$4="Landscape",L18,IF($M$4="Macro",M18,IF($M$4="People",N18,IF($M$4="Sports",O18,IF($M$4="Travel",P18,IF($M$4="Waterdrops",Q18,IF($M$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AE18" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Androo",H18,IF($N$4="Birds in Flight",I18,IF($N$4="Birds Perched",J18,IF($N$4="Fireworks",K18,IF($N$4="Landscape",L18,IF($N$4="Macro",M18,IF($N$4="People",N18,IF($N$4="Sports",O18,IF($N$4="Travel",P18,IF($N$4="Waterdrops",Q18,IF($N$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="AD18" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Birds in Flight",H18,IF($N$4="Birds Perched",I18,IF($N$4="Fireworks",J18,IF($N$4="Landscape",K18,IF($N$4="Macro",L18,IF($N$4="People",M18,IF($N$4="Sports",N18,IF($N$4="Travel",O18,IF($N$4="Waterdrops",P18,IF($N$4="Wildlife",Q18,""))))))))))))))</x:f>
+      <x:c r="AF18" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Androo",H18,IF($O$4="Birds in Flight",I18,IF($O$4="Birds Perched",J18,IF($O$4="Fireworks",K18,IF($O$4="Landscape",L18,IF($O$4="Macro",M18,IF($O$4="People",N18,IF($O$4="Sports",O18,IF($O$4="Travel",P18,IF($O$4="Waterdrops",Q18,IF($O$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="AE18" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Birds in Flight",H18,IF($O$4="Birds Perched",I18,IF($O$4="Fireworks",J18,IF($O$4="Landscape",K18,IF($O$4="Macro",L18,IF($O$4="People",M18,IF($O$4="Sports",N18,IF($O$4="Travel",O18,IF($O$4="Waterdrops",P18,IF($O$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AF18" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Birds in Flight",H18,IF($P$4="Birds Perched",I18,IF($P$4="Fireworks",J18,IF($P$4="Landscape",K18,IF($P$4="Macro",L18,IF($P$4="People",M18,IF($P$4="Sports",N18,IF($P$4="Travel",O18,IF($P$4="Waterdrops",P18,IF($P$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AG18" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Birds in Flight",H18,IF($Q$4="Birds Perched",I18,IF($Q$4="Fireworks",J18,IF($Q$4="Landscape",K18,IF($Q$4="Macro",L18,IF($Q$4="People",M18,IF($Q$4="Sports",N18,IF($Q$4="Travel",O18,IF($Q$4="Waterdrops",P18,IF($Q$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Androo",H18,IF($P$4="Birds in Flight",I18,IF($P$4="Birds Perched",J18,IF($P$4="Fireworks",K18,IF($P$4="Landscape",L18,IF($P$4="Macro",M18,IF($P$4="People",N18,IF($P$4="Sports",O18,IF($P$4="Travel",P18,IF($P$4="Waterdrops",Q18,IF($P$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AH18" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Androo",H18,IF($Q$4="Birds in Flight",I18,IF($Q$4="Birds Perched",J18,IF($Q$4="Fireworks",K18,IF($Q$4="Landscape",L18,IF($Q$4="Macro",M18,IF($Q$4="People",N18,IF($Q$4="Sports",O18,IF($Q$4="Travel",P18,IF($Q$4="Waterdrops",Q18,IF($Q$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI18" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D18,IF($R$4="C2 Birds in Flight",E18,IF($R$4="C3 Landscape",F18,IF($R$4="Default Settings",G18,IF($R$4="Androo",H18,IF($R$4="Birds in Flight",I18,IF($R$4="Birds Perched",J18,IF($R$4="Fireworks",K18,IF($R$4="Landscape",L18,IF($R$4="Macro",M18,IF($R$4="People",N18,IF($R$4="Sports",O18,IF($R$4="Travel",P18,IF($R$4="Waterdrops",Q18,IF($R$4="Wildlife",R18,"")))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
     </x:row>
@@ -2375,89 +2487,96 @@
         <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L19" s="17" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="L19" s="17" t="str">
+      <x:c r="M19" s="17" t="str">
         <x:v>Spot AF</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="O19" s="17" t="str">
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="P19" s="17" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="P19" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="Q19" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R19" s="17" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="R19" s="20" t="n">
+      <x:c r="S19" s="20" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="S19" s="20" t="n">
+      <x:c r="T19" s="20" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="T19" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Birds in Flight",H19,IF($D$4="Birds Perched",I19,IF($D$4="Fireworks",J19,IF($D$4="Landscape",K19,IF($D$4="Macro",L19,IF($D$4="People",M19,IF($D$4="Sports",N19,IF($D$4="Travel",O19,IF($D$4="Waterdrops",P19,IF($D$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="U19" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Androo",H19,IF($D$4="Birds in Flight",I19,IF($D$4="Birds Perched",J19,IF($D$4="Fireworks",K19,IF($D$4="Landscape",L19,IF($D$4="Macro",M19,IF($D$4="People",N19,IF($D$4="Sports",O19,IF($D$4="Travel",P19,IF($D$4="Waterdrops",Q19,IF($D$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="U19" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Birds in Flight",H19,IF($E$4="Birds Perched",I19,IF($E$4="Fireworks",J19,IF($E$4="Landscape",K19,IF($E$4="Macro",L19,IF($E$4="People",M19,IF($E$4="Sports",N19,IF($E$4="Travel",O19,IF($E$4="Waterdrops",P19,IF($E$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="V19" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Androo",H19,IF($E$4="Birds in Flight",I19,IF($E$4="Birds Perched",J19,IF($E$4="Fireworks",K19,IF($E$4="Landscape",L19,IF($E$4="Macro",M19,IF($E$4="People",N19,IF($E$4="Sports",O19,IF($E$4="Travel",P19,IF($E$4="Waterdrops",Q19,IF($E$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="V19" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Birds in Flight",H19,IF($F$4="Birds Perched",I19,IF($F$4="Fireworks",J19,IF($F$4="Landscape",K19,IF($F$4="Macro",L19,IF($F$4="People",M19,IF($F$4="Sports",N19,IF($F$4="Travel",O19,IF($F$4="Waterdrops",P19,IF($F$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="W19" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Androo",H19,IF($F$4="Birds in Flight",I19,IF($F$4="Birds Perched",J19,IF($F$4="Fireworks",K19,IF($F$4="Landscape",L19,IF($F$4="Macro",M19,IF($F$4="People",N19,IF($F$4="Sports",O19,IF($F$4="Travel",P19,IF($F$4="Waterdrops",Q19,IF($F$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="W19" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Birds in Flight",H19,IF($G$4="Birds Perched",I19,IF($G$4="Fireworks",J19,IF($G$4="Landscape",K19,IF($G$4="Macro",L19,IF($G$4="People",M19,IF($G$4="Sports",N19,IF($G$4="Travel",O19,IF($G$4="Waterdrops",P19,IF($G$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="X19" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Androo",H19,IF($G$4="Birds in Flight",I19,IF($G$4="Birds Perched",J19,IF($G$4="Fireworks",K19,IF($G$4="Landscape",L19,IF($G$4="Macro",M19,IF($G$4="People",N19,IF($G$4="Sports",O19,IF($G$4="Travel",P19,IF($G$4="Waterdrops",Q19,IF($G$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="X19" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Birds in Flight",H19,IF($H$4="Birds Perched",I19,IF($H$4="Fireworks",J19,IF($H$4="Landscape",K19,IF($H$4="Macro",L19,IF($H$4="People",M19,IF($H$4="Sports",N19,IF($H$4="Travel",O19,IF($H$4="Waterdrops",P19,IF($H$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="Y19" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Androo",H19,IF($H$4="Birds in Flight",I19,IF($H$4="Birds Perched",J19,IF($H$4="Fireworks",K19,IF($H$4="Landscape",L19,IF($H$4="Macro",M19,IF($H$4="People",N19,IF($H$4="Sports",O19,IF($H$4="Travel",P19,IF($H$4="Waterdrops",Q19,IF($H$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="Y19" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Birds in Flight",H19,IF($I$4="Birds Perched",I19,IF($I$4="Fireworks",J19,IF($I$4="Landscape",K19,IF($I$4="Macro",L19,IF($I$4="People",M19,IF($I$4="Sports",N19,IF($I$4="Travel",O19,IF($I$4="Waterdrops",P19,IF($I$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="Z19" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Androo",H19,IF($I$4="Birds in Flight",I19,IF($I$4="Birds Perched",J19,IF($I$4="Fireworks",K19,IF($I$4="Landscape",L19,IF($I$4="Macro",M19,IF($I$4="People",N19,IF($I$4="Sports",O19,IF($I$4="Travel",P19,IF($I$4="Waterdrops",Q19,IF($I$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="Z19" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Birds in Flight",H19,IF($J$4="Birds Perched",I19,IF($J$4="Fireworks",J19,IF($J$4="Landscape",K19,IF($J$4="Macro",L19,IF($J$4="People",M19,IF($J$4="Sports",N19,IF($J$4="Travel",O19,IF($J$4="Waterdrops",P19,IF($J$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AA19" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Birds in Flight",H19,IF($K$4="Birds Perched",I19,IF($K$4="Fireworks",J19,IF($K$4="Landscape",K19,IF($K$4="Macro",L19,IF($K$4="People",M19,IF($K$4="Sports",N19,IF($K$4="Travel",O19,IF($K$4="Waterdrops",P19,IF($K$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Androo",H19,IF($J$4="Birds in Flight",I19,IF($J$4="Birds Perched",J19,IF($J$4="Fireworks",K19,IF($J$4="Landscape",L19,IF($J$4="Macro",M19,IF($J$4="People",N19,IF($J$4="Sports",O19,IF($J$4="Travel",P19,IF($J$4="Waterdrops",Q19,IF($J$4="Wildlife",R19,"")))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="AB19" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Androo",H19,IF($K$4="Birds in Flight",I19,IF($K$4="Birds Perched",J19,IF($K$4="Fireworks",K19,IF($K$4="Landscape",L19,IF($K$4="Macro",M19,IF($K$4="People",N19,IF($K$4="Sports",O19,IF($K$4="Travel",P19,IF($K$4="Waterdrops",Q19,IF($K$4="Wildlife",R19,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC19" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Androo",H19,IF($L$4="Birds in Flight",I19,IF($L$4="Birds Perched",J19,IF($L$4="Fireworks",K19,IF($L$4="Landscape",L19,IF($L$4="Macro",M19,IF($L$4="People",N19,IF($L$4="Sports",O19,IF($L$4="Travel",P19,IF($L$4="Waterdrops",Q19,IF($L$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="AB19" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Birds in Flight",H19,IF($L$4="Birds Perched",I19,IF($L$4="Fireworks",J19,IF($L$4="Landscape",K19,IF($L$4="Macro",L19,IF($L$4="People",M19,IF($L$4="Sports",N19,IF($L$4="Travel",O19,IF($L$4="Waterdrops",P19,IF($L$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="AD19" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Androo",H19,IF($M$4="Birds in Flight",I19,IF($M$4="Birds Perched",J19,IF($M$4="Fireworks",K19,IF($M$4="Landscape",L19,IF($M$4="Macro",M19,IF($M$4="People",N19,IF($M$4="Sports",O19,IF($M$4="Travel",P19,IF($M$4="Waterdrops",Q19,IF($M$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Spot AF</x:v>
       </x:c>
-      <x:c r="AC19" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Birds in Flight",H19,IF($M$4="Birds Perched",I19,IF($M$4="Fireworks",J19,IF($M$4="Landscape",K19,IF($M$4="Macro",L19,IF($M$4="People",M19,IF($M$4="Sports",N19,IF($M$4="Travel",O19,IF($M$4="Waterdrops",P19,IF($M$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="AE19" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Androo",H19,IF($N$4="Birds in Flight",I19,IF($N$4="Birds Perched",J19,IF($N$4="Fireworks",K19,IF($N$4="Landscape",L19,IF($N$4="Macro",M19,IF($N$4="People",N19,IF($N$4="Sports",O19,IF($N$4="Travel",P19,IF($N$4="Waterdrops",Q19,IF($N$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="AD19" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Birds in Flight",H19,IF($N$4="Birds Perched",I19,IF($N$4="Fireworks",J19,IF($N$4="Landscape",K19,IF($N$4="Macro",L19,IF($N$4="People",M19,IF($N$4="Sports",N19,IF($N$4="Travel",O19,IF($N$4="Waterdrops",P19,IF($N$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="AF19" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Androo",H19,IF($O$4="Birds in Flight",I19,IF($O$4="Birds Perched",J19,IF($O$4="Fireworks",K19,IF($O$4="Landscape",L19,IF($O$4="Macro",M19,IF($O$4="People",N19,IF($O$4="Sports",O19,IF($O$4="Travel",P19,IF($O$4="Waterdrops",Q19,IF($O$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="AE19" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Birds in Flight",H19,IF($O$4="Birds Perched",I19,IF($O$4="Fireworks",J19,IF($O$4="Landscape",K19,IF($O$4="Macro",L19,IF($O$4="People",M19,IF($O$4="Sports",N19,IF($O$4="Travel",O19,IF($O$4="Waterdrops",P19,IF($O$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="AG19" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Androo",H19,IF($P$4="Birds in Flight",I19,IF($P$4="Birds Perched",J19,IF($P$4="Fireworks",K19,IF($P$4="Landscape",L19,IF($P$4="Macro",M19,IF($P$4="People",N19,IF($P$4="Sports",O19,IF($P$4="Travel",P19,IF($P$4="Waterdrops",Q19,IF($P$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="AF19" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Birds in Flight",H19,IF($P$4="Birds Perched",I19,IF($P$4="Fireworks",J19,IF($P$4="Landscape",K19,IF($P$4="Macro",L19,IF($P$4="People",M19,IF($P$4="Sports",N19,IF($P$4="Travel",O19,IF($P$4="Waterdrops",P19,IF($P$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AG19" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Birds in Flight",H19,IF($Q$4="Birds Perched",I19,IF($Q$4="Fireworks",J19,IF($Q$4="Landscape",K19,IF($Q$4="Macro",L19,IF($Q$4="People",M19,IF($Q$4="Sports",N19,IF($Q$4="Travel",O19,IF($Q$4="Waterdrops",P19,IF($Q$4="Wildlife",Q19,""))))))))))))))</x:f>
+      <x:c r="AH19" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Androo",H19,IF($Q$4="Birds in Flight",I19,IF($Q$4="Birds Perched",J19,IF($Q$4="Fireworks",K19,IF($Q$4="Landscape",L19,IF($Q$4="Macro",M19,IF($Q$4="People",N19,IF($Q$4="Sports",O19,IF($Q$4="Travel",P19,IF($Q$4="Waterdrops",Q19,IF($Q$4="Wildlife",R19,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI19" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D19,IF($R$4="C2 Birds in Flight",E19,IF($R$4="C3 Landscape",F19,IF($R$4="Default Settings",G19,IF($R$4="Androo",H19,IF($R$4="Birds in Flight",I19,IF($R$4="Birds Perched",J19,IF($R$4="Fireworks",K19,IF($R$4="Landscape",L19,IF($R$4="Macro",M19,IF($R$4="People",N19,IF($R$4="Sports",O19,IF($R$4="Travel",P19,IF($R$4="Waterdrops",Q19,IF($R$4="Wildlife",R19,"")))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
@@ -2484,95 +2603,102 @@
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Vehicles</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L20" s="17" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="M20" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="N20" s="17" t="str">
         <x:v>People</x:v>
       </x:c>
       <x:c r="O20" s="17" t="str">
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="P20" s="17" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="P20" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="Q20" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R20" s="17" t="str">
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="R20" s="20" t="n">
+      <x:c r="S20" s="20" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="S20" s="20" t="n">
+      <x:c r="T20" s="20" t="n">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="T20" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Birds in Flight",H20,IF($D$4="Birds Perched",I20,IF($D$4="Fireworks",J20,IF($D$4="Landscape",K20,IF($D$4="Macro",L20,IF($D$4="People",M20,IF($D$4="Sports",N20,IF($D$4="Travel",O20,IF($D$4="Waterdrops",P20,IF($D$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="U20" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Androo",H20,IF($D$4="Birds in Flight",I20,IF($D$4="Birds Perched",J20,IF($D$4="Fireworks",K20,IF($D$4="Landscape",L20,IF($D$4="Macro",M20,IF($D$4="People",N20,IF($D$4="Sports",O20,IF($D$4="Travel",P20,IF($D$4="Waterdrops",Q20,IF($D$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="U20" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Birds in Flight",H20,IF($E$4="Birds Perched",I20,IF($E$4="Fireworks",J20,IF($E$4="Landscape",K20,IF($E$4="Macro",L20,IF($E$4="People",M20,IF($E$4="Sports",N20,IF($E$4="Travel",O20,IF($E$4="Waterdrops",P20,IF($E$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="V20" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Androo",H20,IF($E$4="Birds in Flight",I20,IF($E$4="Birds Perched",J20,IF($E$4="Fireworks",K20,IF($E$4="Landscape",L20,IF($E$4="Macro",M20,IF($E$4="People",N20,IF($E$4="Sports",O20,IF($E$4="Travel",P20,IF($E$4="Waterdrops",Q20,IF($E$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="V20" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Birds in Flight",H20,IF($F$4="Birds Perched",I20,IF($F$4="Fireworks",J20,IF($F$4="Landscape",K20,IF($F$4="Macro",L20,IF($F$4="People",M20,IF($F$4="Sports",N20,IF($F$4="Travel",O20,IF($F$4="Waterdrops",P20,IF($F$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="W20" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Androo",H20,IF($F$4="Birds in Flight",I20,IF($F$4="Birds Perched",J20,IF($F$4="Fireworks",K20,IF($F$4="Landscape",L20,IF($F$4="Macro",M20,IF($F$4="People",N20,IF($F$4="Sports",O20,IF($F$4="Travel",P20,IF($F$4="Waterdrops",Q20,IF($F$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="W20" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Birds in Flight",H20,IF($G$4="Birds Perched",I20,IF($G$4="Fireworks",J20,IF($G$4="Landscape",K20,IF($G$4="Macro",L20,IF($G$4="People",M20,IF($G$4="Sports",N20,IF($G$4="Travel",O20,IF($G$4="Waterdrops",P20,IF($G$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="X20" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Androo",H20,IF($G$4="Birds in Flight",I20,IF($G$4="Birds Perched",J20,IF($G$4="Fireworks",K20,IF($G$4="Landscape",L20,IF($G$4="Macro",M20,IF($G$4="People",N20,IF($G$4="Sports",O20,IF($G$4="Travel",P20,IF($G$4="Waterdrops",Q20,IF($G$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="X20" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Birds in Flight",H20,IF($H$4="Birds Perched",I20,IF($H$4="Fireworks",J20,IF($H$4="Landscape",K20,IF($H$4="Macro",L20,IF($H$4="People",M20,IF($H$4="Sports",N20,IF($H$4="Travel",O20,IF($H$4="Waterdrops",P20,IF($H$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="Y20" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Androo",H20,IF($H$4="Birds in Flight",I20,IF($H$4="Birds Perched",J20,IF($H$4="Fireworks",K20,IF($H$4="Landscape",L20,IF($H$4="Macro",M20,IF($H$4="People",N20,IF($H$4="Sports",O20,IF($H$4="Travel",P20,IF($H$4="Waterdrops",Q20,IF($H$4="Wildlife",R20,"")))))))))))))))</x:f>
+        <x:v>Vehicles</x:v>
+      </x:c>
+      <x:c r="Z20" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Androo",H20,IF($I$4="Birds in Flight",I20,IF($I$4="Birds Perched",J20,IF($I$4="Fireworks",K20,IF($I$4="Landscape",L20,IF($I$4="Macro",M20,IF($I$4="People",N20,IF($I$4="Sports",O20,IF($I$4="Travel",P20,IF($I$4="Waterdrops",Q20,IF($I$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="Y20" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Birds in Flight",H20,IF($I$4="Birds Perched",I20,IF($I$4="Fireworks",J20,IF($I$4="Landscape",K20,IF($I$4="Macro",L20,IF($I$4="People",M20,IF($I$4="Sports",N20,IF($I$4="Travel",O20,IF($I$4="Waterdrops",P20,IF($I$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AA20" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Androo",H20,IF($J$4="Birds in Flight",I20,IF($J$4="Birds Perched",J20,IF($J$4="Fireworks",K20,IF($J$4="Landscape",L20,IF($J$4="Macro",M20,IF($J$4="People",N20,IF($J$4="Sports",O20,IF($J$4="Travel",P20,IF($J$4="Waterdrops",Q20,IF($J$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="Z20" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Birds in Flight",H20,IF($J$4="Birds Perched",I20,IF($J$4="Fireworks",J20,IF($J$4="Landscape",K20,IF($J$4="Macro",L20,IF($J$4="People",M20,IF($J$4="Sports",N20,IF($J$4="Travel",O20,IF($J$4="Waterdrops",P20,IF($J$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA20" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Birds in Flight",H20,IF($K$4="Birds Perched",I20,IF($K$4="Fireworks",J20,IF($K$4="Landscape",K20,IF($K$4="Macro",L20,IF($K$4="People",M20,IF($K$4="Sports",N20,IF($K$4="Travel",O20,IF($K$4="Waterdrops",P20,IF($K$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AB20" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Androo",H20,IF($K$4="Birds in Flight",I20,IF($K$4="Birds Perched",J20,IF($K$4="Fireworks",K20,IF($K$4="Landscape",L20,IF($K$4="Macro",M20,IF($K$4="People",N20,IF($K$4="Sports",O20,IF($K$4="Travel",P20,IF($K$4="Waterdrops",Q20,IF($K$4="Wildlife",R20,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC20" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Androo",H20,IF($L$4="Birds in Flight",I20,IF($L$4="Birds Perched",J20,IF($L$4="Fireworks",K20,IF($L$4="Landscape",L20,IF($L$4="Macro",M20,IF($L$4="People",N20,IF($L$4="Sports",O20,IF($L$4="Travel",P20,IF($L$4="Waterdrops",Q20,IF($L$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="AB20" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Birds in Flight",H20,IF($L$4="Birds Perched",I20,IF($L$4="Fireworks",J20,IF($L$4="Landscape",K20,IF($L$4="Macro",L20,IF($L$4="People",M20,IF($L$4="Sports",N20,IF($L$4="Travel",O20,IF($L$4="Waterdrops",P20,IF($L$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AD20" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Androo",H20,IF($M$4="Birds in Flight",I20,IF($M$4="Birds Perched",J20,IF($M$4="Fireworks",K20,IF($M$4="Landscape",L20,IF($M$4="Macro",M20,IF($M$4="People",N20,IF($M$4="Sports",O20,IF($M$4="Travel",P20,IF($M$4="Waterdrops",Q20,IF($M$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="AC20" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Birds in Flight",H20,IF($M$4="Birds Perched",I20,IF($M$4="Fireworks",J20,IF($M$4="Landscape",K20,IF($M$4="Macro",L20,IF($M$4="People",M20,IF($M$4="Sports",N20,IF($M$4="Travel",O20,IF($M$4="Waterdrops",P20,IF($M$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AE20" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Androo",H20,IF($N$4="Birds in Flight",I20,IF($N$4="Birds Perched",J20,IF($N$4="Fireworks",K20,IF($N$4="Landscape",L20,IF($N$4="Macro",M20,IF($N$4="People",N20,IF($N$4="Sports",O20,IF($N$4="Travel",P20,IF($N$4="Waterdrops",Q20,IF($N$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>People</x:v>
       </x:c>
-      <x:c r="AD20" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Birds in Flight",H20,IF($N$4="Birds Perched",I20,IF($N$4="Fireworks",J20,IF($N$4="Landscape",K20,IF($N$4="Macro",L20,IF($N$4="People",M20,IF($N$4="Sports",N20,IF($N$4="Travel",O20,IF($N$4="Waterdrops",P20,IF($N$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AF20" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Androo",H20,IF($O$4="Birds in Flight",I20,IF($O$4="Birds Perched",J20,IF($O$4="Fireworks",K20,IF($O$4="Landscape",L20,IF($O$4="Macro",M20,IF($O$4="People",N20,IF($O$4="Sports",O20,IF($O$4="Travel",P20,IF($O$4="Waterdrops",Q20,IF($O$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>People</x:v>
       </x:c>
-      <x:c r="AE20" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Birds in Flight",H20,IF($O$4="Birds Perched",I20,IF($O$4="Fireworks",J20,IF($O$4="Landscape",K20,IF($O$4="Macro",L20,IF($O$4="People",M20,IF($O$4="Sports",N20,IF($O$4="Travel",O20,IF($O$4="Waterdrops",P20,IF($O$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AG20" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Androo",H20,IF($P$4="Birds in Flight",I20,IF($P$4="Birds Perched",J20,IF($P$4="Fireworks",K20,IF($P$4="Landscape",L20,IF($P$4="Macro",M20,IF($P$4="People",N20,IF($P$4="Sports",O20,IF($P$4="Travel",P20,IF($P$4="Waterdrops",Q20,IF($P$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="AF20" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Birds in Flight",H20,IF($P$4="Birds Perched",I20,IF($P$4="Fireworks",J20,IF($P$4="Landscape",K20,IF($P$4="Macro",L20,IF($P$4="People",M20,IF($P$4="Sports",N20,IF($P$4="Travel",O20,IF($P$4="Waterdrops",P20,IF($P$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AG20" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Birds in Flight",H20,IF($Q$4="Birds Perched",I20,IF($Q$4="Fireworks",J20,IF($Q$4="Landscape",K20,IF($Q$4="Macro",L20,IF($Q$4="People",M20,IF($Q$4="Sports",N20,IF($Q$4="Travel",O20,IF($Q$4="Waterdrops",P20,IF($Q$4="Wildlife",Q20,""))))))))))))))</x:f>
+      <x:c r="AH20" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Androo",H20,IF($Q$4="Birds in Flight",I20,IF($Q$4="Birds Perched",J20,IF($Q$4="Fireworks",K20,IF($Q$4="Landscape",L20,IF($Q$4="Macro",M20,IF($Q$4="People",N20,IF($Q$4="Sports",O20,IF($Q$4="Travel",P20,IF($Q$4="Waterdrops",Q20,IF($Q$4="Wildlife",R20,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI20" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D20,IF($R$4="C2 Birds in Flight",E20,IF($R$4="C3 Landscape",F20,IF($R$4="Default Settings",G20,IF($R$4="Androo",H20,IF($R$4="Birds in Flight",I20,IF($R$4="Birds Perched",J20,IF($R$4="Fireworks",K20,IF($R$4="Landscape",L20,IF($R$4="Macro",M20,IF($R$4="People",N20,IF($R$4="Sports",O20,IF($R$4="Travel",P20,IF($R$4="Waterdrops",Q20,IF($R$4="Wildlife",R20,"")))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
     </x:row>
@@ -2599,95 +2725,102 @@
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L21" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="M21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="N21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="O21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="P21" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="Q21" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="R21" s="20" t="n">
+      <x:c r="S21" s="20" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="S21" s="20" t="n">
+      <x:c r="T21" s="20" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="T21" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Birds in Flight",H21,IF($D$4="Birds Perched",I21,IF($D$4="Fireworks",J21,IF($D$4="Landscape",K21,IF($D$4="Macro",L21,IF($D$4="People",M21,IF($D$4="Sports",N21,IF($D$4="Travel",O21,IF($D$4="Waterdrops",P21,IF($D$4="Wildlife",Q21,""))))))))))))))</x:f>
+      <x:c r="U21" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Androo",H21,IF($D$4="Birds in Flight",I21,IF($D$4="Birds Perched",J21,IF($D$4="Fireworks",K21,IF($D$4="Landscape",L21,IF($D$4="Macro",M21,IF($D$4="People",N21,IF($D$4="Sports",O21,IF($D$4="Travel",P21,IF($D$4="Waterdrops",Q21,IF($D$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="U21" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Birds in Flight",H21,IF($E$4="Birds Perched",I21,IF($E$4="Fireworks",J21,IF($E$4="Landscape",K21,IF($E$4="Macro",L21,IF($E$4="People",M21,IF($E$4="Sports",N21,IF($E$4="Travel",O21,IF($E$4="Waterdrops",P21,IF($E$4="Wildlife",Q21,""))))))))))))))</x:f>
+      <x:c r="V21" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Androo",H21,IF($E$4="Birds in Flight",I21,IF($E$4="Birds Perched",J21,IF($E$4="Fireworks",K21,IF($E$4="Landscape",L21,IF($E$4="Macro",M21,IF($E$4="People",N21,IF($E$4="Sports",O21,IF($E$4="Travel",P21,IF($E$4="Waterdrops",Q21,IF($E$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="V21" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Birds in Flight",H21,IF($F$4="Birds Perched",I21,IF($F$4="Fireworks",J21,IF($F$4="Landscape",K21,IF($F$4="Macro",L21,IF($F$4="People",M21,IF($F$4="Sports",N21,IF($F$4="Travel",O21,IF($F$4="Waterdrops",P21,IF($F$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="W21" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Birds in Flight",H21,IF($G$4="Birds Perched",I21,IF($G$4="Fireworks",J21,IF($G$4="Landscape",K21,IF($G$4="Macro",L21,IF($G$4="People",M21,IF($G$4="Sports",N21,IF($G$4="Travel",O21,IF($G$4="Waterdrops",P21,IF($G$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Androo",H21,IF($F$4="Birds in Flight",I21,IF($F$4="Birds Perched",J21,IF($F$4="Fireworks",K21,IF($F$4="Landscape",L21,IF($F$4="Macro",M21,IF($F$4="People",N21,IF($F$4="Sports",O21,IF($F$4="Travel",P21,IF($F$4="Waterdrops",Q21,IF($F$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X21" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Androo",H21,IF($G$4="Birds in Flight",I21,IF($G$4="Birds Perched",J21,IF($G$4="Fireworks",K21,IF($G$4="Landscape",L21,IF($G$4="Macro",M21,IF($G$4="People",N21,IF($G$4="Sports",O21,IF($G$4="Travel",P21,IF($G$4="Waterdrops",Q21,IF($G$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="X21" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Birds in Flight",H21,IF($H$4="Birds Perched",I21,IF($H$4="Fireworks",J21,IF($H$4="Landscape",K21,IF($H$4="Macro",L21,IF($H$4="People",M21,IF($H$4="Sports",N21,IF($H$4="Travel",O21,IF($H$4="Waterdrops",P21,IF($H$4="Wildlife",Q21,""))))))))))))))</x:f>
+      <x:c r="Y21" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Androo",H21,IF($H$4="Birds in Flight",I21,IF($H$4="Birds Perched",J21,IF($H$4="Fireworks",K21,IF($H$4="Landscape",L21,IF($H$4="Macro",M21,IF($H$4="People",N21,IF($H$4="Sports",O21,IF($H$4="Travel",P21,IF($H$4="Waterdrops",Q21,IF($H$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z21" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Androo",H21,IF($I$4="Birds in Flight",I21,IF($I$4="Birds Perched",J21,IF($I$4="Fireworks",K21,IF($I$4="Landscape",L21,IF($I$4="Macro",M21,IF($I$4="People",N21,IF($I$4="Sports",O21,IF($I$4="Travel",P21,IF($I$4="Waterdrops",Q21,IF($I$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="Y21" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Birds in Flight",H21,IF($I$4="Birds Perched",I21,IF($I$4="Fireworks",J21,IF($I$4="Landscape",K21,IF($I$4="Macro",L21,IF($I$4="People",M21,IF($I$4="Sports",N21,IF($I$4="Travel",O21,IF($I$4="Waterdrops",P21,IF($I$4="Wildlife",Q21,""))))))))))))))</x:f>
+      <x:c r="AA21" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Androo",H21,IF($J$4="Birds in Flight",I21,IF($J$4="Birds Perched",J21,IF($J$4="Fireworks",K21,IF($J$4="Landscape",L21,IF($J$4="Macro",M21,IF($J$4="People",N21,IF($J$4="Sports",O21,IF($J$4="Travel",P21,IF($J$4="Waterdrops",Q21,IF($J$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="Z21" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Birds in Flight",H21,IF($J$4="Birds Perched",I21,IF($J$4="Fireworks",J21,IF($J$4="Landscape",K21,IF($J$4="Macro",L21,IF($J$4="People",M21,IF($J$4="Sports",N21,IF($J$4="Travel",O21,IF($J$4="Waterdrops",P21,IF($J$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA21" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Birds in Flight",H21,IF($K$4="Birds Perched",I21,IF($K$4="Fireworks",J21,IF($K$4="Landscape",K21,IF($K$4="Macro",L21,IF($K$4="People",M21,IF($K$4="Sports",N21,IF($K$4="Travel",O21,IF($K$4="Waterdrops",P21,IF($K$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="AB21" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Birds in Flight",H21,IF($L$4="Birds Perched",I21,IF($L$4="Fireworks",J21,IF($L$4="Landscape",K21,IF($L$4="Macro",L21,IF($L$4="People",M21,IF($L$4="Sports",N21,IF($L$4="Travel",O21,IF($L$4="Waterdrops",P21,IF($L$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Androo",H21,IF($K$4="Birds in Flight",I21,IF($K$4="Birds Perched",J21,IF($K$4="Fireworks",K21,IF($K$4="Landscape",L21,IF($K$4="Macro",M21,IF($K$4="People",N21,IF($K$4="Sports",O21,IF($K$4="Travel",P21,IF($K$4="Waterdrops",Q21,IF($K$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC21" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Birds in Flight",H21,IF($M$4="Birds Perched",I21,IF($M$4="Fireworks",J21,IF($M$4="Landscape",K21,IF($M$4="Macro",L21,IF($M$4="People",M21,IF($M$4="Sports",N21,IF($M$4="Travel",O21,IF($M$4="Waterdrops",P21,IF($M$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Androo",H21,IF($L$4="Birds in Flight",I21,IF($L$4="Birds Perched",J21,IF($L$4="Fireworks",K21,IF($L$4="Landscape",L21,IF($L$4="Macro",M21,IF($L$4="People",N21,IF($L$4="Sports",O21,IF($L$4="Travel",P21,IF($L$4="Waterdrops",Q21,IF($L$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD21" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Androo",H21,IF($M$4="Birds in Flight",I21,IF($M$4="Birds Perched",J21,IF($M$4="Fireworks",K21,IF($M$4="Landscape",L21,IF($M$4="Macro",M21,IF($M$4="People",N21,IF($M$4="Sports",O21,IF($M$4="Travel",P21,IF($M$4="Waterdrops",Q21,IF($M$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AE21" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Androo",H21,IF($N$4="Birds in Flight",I21,IF($N$4="Birds Perched",J21,IF($N$4="Fireworks",K21,IF($N$4="Landscape",L21,IF($N$4="Macro",M21,IF($N$4="People",N21,IF($N$4="Sports",O21,IF($N$4="Travel",P21,IF($N$4="Waterdrops",Q21,IF($N$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="AD21" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Birds in Flight",H21,IF($N$4="Birds Perched",I21,IF($N$4="Fireworks",J21,IF($N$4="Landscape",K21,IF($N$4="Macro",L21,IF($N$4="People",M21,IF($N$4="Sports",N21,IF($N$4="Travel",O21,IF($N$4="Waterdrops",P21,IF($N$4="Wildlife",Q21,""))))))))))))))</x:f>
+      <x:c r="AF21" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Androo",H21,IF($O$4="Birds in Flight",I21,IF($O$4="Birds Perched",J21,IF($O$4="Fireworks",K21,IF($O$4="Landscape",L21,IF($O$4="Macro",M21,IF($O$4="People",N21,IF($O$4="Sports",O21,IF($O$4="Travel",P21,IF($O$4="Waterdrops",Q21,IF($O$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="AE21" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Birds in Flight",H21,IF($O$4="Birds Perched",I21,IF($O$4="Fireworks",J21,IF($O$4="Landscape",K21,IF($O$4="Macro",L21,IF($O$4="People",M21,IF($O$4="Sports",N21,IF($O$4="Travel",O21,IF($O$4="Waterdrops",P21,IF($O$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AF21" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Birds in Flight",H21,IF($P$4="Birds Perched",I21,IF($P$4="Fireworks",J21,IF($P$4="Landscape",K21,IF($P$4="Macro",L21,IF($P$4="People",M21,IF($P$4="Sports",N21,IF($P$4="Travel",O21,IF($P$4="Waterdrops",P21,IF($P$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AG21" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Birds in Flight",H21,IF($Q$4="Birds Perched",I21,IF($Q$4="Fireworks",J21,IF($Q$4="Landscape",K21,IF($Q$4="Macro",L21,IF($Q$4="People",M21,IF($Q$4="Sports",N21,IF($Q$4="Travel",O21,IF($Q$4="Waterdrops",P21,IF($Q$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Androo",H21,IF($P$4="Birds in Flight",I21,IF($P$4="Birds Perched",J21,IF($P$4="Fireworks",K21,IF($P$4="Landscape",L21,IF($P$4="Macro",M21,IF($P$4="People",N21,IF($P$4="Sports",O21,IF($P$4="Travel",P21,IF($P$4="Waterdrops",Q21,IF($P$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AH21" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Androo",H21,IF($Q$4="Birds in Flight",I21,IF($Q$4="Birds Perched",J21,IF($Q$4="Fireworks",K21,IF($Q$4="Landscape",L21,IF($Q$4="Macro",M21,IF($Q$4="People",N21,IF($Q$4="Sports",O21,IF($Q$4="Travel",P21,IF($Q$4="Waterdrops",Q21,IF($Q$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI21" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D21,IF($R$4="C2 Birds in Flight",E21,IF($R$4="C3 Landscape",F21,IF($R$4="Default Settings",G21,IF($R$4="Androo",H21,IF($R$4="Birds in Flight",I21,IF($R$4="Birds Perched",J21,IF($R$4="Fireworks",K21,IF($R$4="Landscape",L21,IF($R$4="Macro",M21,IF($R$4="People",N21,IF($R$4="Sports",O21,IF($R$4="Travel",P21,IF($R$4="Waterdrops",Q21,IF($R$4="Wildlife",R21,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
@@ -2714,13 +2847,13 @@
         <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="H22" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="I22" s="17" t="str">
+      <x:c r="J22" s="17" t="str">
         <x:v>High Speed Continuous</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="str">
-        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
         <x:v>Single Shot</x:v>
@@ -2729,80 +2862,87 @@
         <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="M22" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="N22" s="17" t="str">
         <x:v>Low Speed Continuous</x:v>
       </x:c>
-      <x:c r="N22" s="17" t="str">
+      <x:c r="O22" s="17" t="str">
         <x:v>High Speed Continuous+</x:v>
-      </x:c>
-      <x:c r="O22" s="17" t="str">
-        <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="P22" s="17" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="Q22" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="R22" s="17" t="str">
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="R22" s="20" t="n">
+      <x:c r="S22" s="20" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="S22" s="20" t="n">
+      <x:c r="T22" s="20" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="T22" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Birds in Flight",H22,IF($D$4="Birds Perched",I22,IF($D$4="Fireworks",J22,IF($D$4="Landscape",K22,IF($D$4="Macro",L22,IF($D$4="People",M22,IF($D$4="Sports",N22,IF($D$4="Travel",O22,IF($D$4="Waterdrops",P22,IF($D$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="U22" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Androo",H22,IF($D$4="Birds in Flight",I22,IF($D$4="Birds Perched",J22,IF($D$4="Fireworks",K22,IF($D$4="Landscape",L22,IF($D$4="Macro",M22,IF($D$4="People",N22,IF($D$4="Sports",O22,IF($D$4="Travel",P22,IF($D$4="Waterdrops",Q22,IF($D$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="U22" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Birds in Flight",H22,IF($E$4="Birds Perched",I22,IF($E$4="Fireworks",J22,IF($E$4="Landscape",K22,IF($E$4="Macro",L22,IF($E$4="People",M22,IF($E$4="Sports",N22,IF($E$4="Travel",O22,IF($E$4="Waterdrops",P22,IF($E$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="V22" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Androo",H22,IF($E$4="Birds in Flight",I22,IF($E$4="Birds Perched",J22,IF($E$4="Fireworks",K22,IF($E$4="Landscape",L22,IF($E$4="Macro",M22,IF($E$4="People",N22,IF($E$4="Sports",O22,IF($E$4="Travel",P22,IF($E$4="Waterdrops",Q22,IF($E$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="V22" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Birds in Flight",H22,IF($F$4="Birds Perched",I22,IF($F$4="Fireworks",J22,IF($F$4="Landscape",K22,IF($F$4="Macro",L22,IF($F$4="People",M22,IF($F$4="Sports",N22,IF($F$4="Travel",O22,IF($F$4="Waterdrops",P22,IF($F$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="W22" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Androo",H22,IF($F$4="Birds in Flight",I22,IF($F$4="Birds Perched",J22,IF($F$4="Fireworks",K22,IF($F$4="Landscape",L22,IF($F$4="Macro",M22,IF($F$4="People",N22,IF($F$4="Sports",O22,IF($F$4="Travel",P22,IF($F$4="Waterdrops",Q22,IF($F$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="W22" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Birds in Flight",H22,IF($G$4="Birds Perched",I22,IF($G$4="Fireworks",J22,IF($G$4="Landscape",K22,IF($G$4="Macro",L22,IF($G$4="People",M22,IF($G$4="Sports",N22,IF($G$4="Travel",O22,IF($G$4="Waterdrops",P22,IF($G$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="X22" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Androo",H22,IF($G$4="Birds in Flight",I22,IF($G$4="Birds Perched",J22,IF($G$4="Fireworks",K22,IF($G$4="Landscape",L22,IF($G$4="Macro",M22,IF($G$4="People",N22,IF($G$4="Sports",O22,IF($G$4="Travel",P22,IF($G$4="Waterdrops",Q22,IF($G$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="X22" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Birds in Flight",H22,IF($H$4="Birds Perched",I22,IF($H$4="Fireworks",J22,IF($H$4="Landscape",K22,IF($H$4="Macro",L22,IF($H$4="People",M22,IF($H$4="Sports",N22,IF($H$4="Travel",O22,IF($H$4="Waterdrops",P22,IF($H$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="Y22" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Androo",H22,IF($H$4="Birds in Flight",I22,IF($H$4="Birds Perched",J22,IF($H$4="Fireworks",K22,IF($H$4="Landscape",L22,IF($H$4="Macro",M22,IF($H$4="People",N22,IF($H$4="Sports",O22,IF($H$4="Travel",P22,IF($H$4="Waterdrops",Q22,IF($H$4="Wildlife",R22,"")))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="Z22" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Androo",H22,IF($I$4="Birds in Flight",I22,IF($I$4="Birds Perched",J22,IF($I$4="Fireworks",K22,IF($I$4="Landscape",L22,IF($I$4="Macro",M22,IF($I$4="People",N22,IF($I$4="Sports",O22,IF($I$4="Travel",P22,IF($I$4="Waterdrops",Q22,IF($I$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="Y22" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Birds in Flight",H22,IF($I$4="Birds Perched",I22,IF($I$4="Fireworks",J22,IF($I$4="Landscape",K22,IF($I$4="Macro",L22,IF($I$4="People",M22,IF($I$4="Sports",N22,IF($I$4="Travel",O22,IF($I$4="Waterdrops",P22,IF($I$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AA22" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Androo",H22,IF($J$4="Birds in Flight",I22,IF($J$4="Birds Perched",J22,IF($J$4="Fireworks",K22,IF($J$4="Landscape",L22,IF($J$4="Macro",M22,IF($J$4="People",N22,IF($J$4="Sports",O22,IF($J$4="Travel",P22,IF($J$4="Waterdrops",Q22,IF($J$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="Z22" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Birds in Flight",H22,IF($J$4="Birds Perched",I22,IF($J$4="Fireworks",J22,IF($J$4="Landscape",K22,IF($J$4="Macro",L22,IF($J$4="People",M22,IF($J$4="Sports",N22,IF($J$4="Travel",O22,IF($J$4="Waterdrops",P22,IF($J$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AB22" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Androo",H22,IF($K$4="Birds in Flight",I22,IF($K$4="Birds Perched",J22,IF($K$4="Fireworks",K22,IF($K$4="Landscape",L22,IF($K$4="Macro",M22,IF($K$4="People",N22,IF($K$4="Sports",O22,IF($K$4="Travel",P22,IF($K$4="Waterdrops",Q22,IF($K$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="AA22" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Birds in Flight",H22,IF($K$4="Birds Perched",I22,IF($K$4="Fireworks",J22,IF($K$4="Landscape",K22,IF($K$4="Macro",L22,IF($K$4="People",M22,IF($K$4="Sports",N22,IF($K$4="Travel",O22,IF($K$4="Waterdrops",P22,IF($K$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AC22" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Androo",H22,IF($L$4="Birds in Flight",I22,IF($L$4="Birds Perched",J22,IF($L$4="Fireworks",K22,IF($L$4="Landscape",L22,IF($L$4="Macro",M22,IF($L$4="People",N22,IF($L$4="Sports",O22,IF($L$4="Travel",P22,IF($L$4="Waterdrops",Q22,IF($L$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="AB22" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Birds in Flight",H22,IF($L$4="Birds Perched",I22,IF($L$4="Fireworks",J22,IF($L$4="Landscape",K22,IF($L$4="Macro",L22,IF($L$4="People",M22,IF($L$4="Sports",N22,IF($L$4="Travel",O22,IF($L$4="Waterdrops",P22,IF($L$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AD22" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Androo",H22,IF($M$4="Birds in Flight",I22,IF($M$4="Birds Perched",J22,IF($M$4="Fireworks",K22,IF($M$4="Landscape",L22,IF($M$4="Macro",M22,IF($M$4="People",N22,IF($M$4="Sports",O22,IF($M$4="Travel",P22,IF($M$4="Waterdrops",Q22,IF($M$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="AC22" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Birds in Flight",H22,IF($M$4="Birds Perched",I22,IF($M$4="Fireworks",J22,IF($M$4="Landscape",K22,IF($M$4="Macro",L22,IF($M$4="People",M22,IF($M$4="Sports",N22,IF($M$4="Travel",O22,IF($M$4="Waterdrops",P22,IF($M$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AE22" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Androo",H22,IF($N$4="Birds in Flight",I22,IF($N$4="Birds Perched",J22,IF($N$4="Fireworks",K22,IF($N$4="Landscape",L22,IF($N$4="Macro",M22,IF($N$4="People",N22,IF($N$4="Sports",O22,IF($N$4="Travel",P22,IF($N$4="Waterdrops",Q22,IF($N$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Low Speed Continuous</x:v>
       </x:c>
-      <x:c r="AD22" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Birds in Flight",H22,IF($N$4="Birds Perched",I22,IF($N$4="Fireworks",J22,IF($N$4="Landscape",K22,IF($N$4="Macro",L22,IF($N$4="People",M22,IF($N$4="Sports",N22,IF($N$4="Travel",O22,IF($N$4="Waterdrops",P22,IF($N$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AF22" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Androo",H22,IF($O$4="Birds in Flight",I22,IF($O$4="Birds Perched",J22,IF($O$4="Fireworks",K22,IF($O$4="Landscape",L22,IF($O$4="Macro",M22,IF($O$4="People",N22,IF($O$4="Sports",O22,IF($O$4="Travel",P22,IF($O$4="Waterdrops",Q22,IF($O$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="AE22" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Birds in Flight",H22,IF($O$4="Birds Perched",I22,IF($O$4="Fireworks",J22,IF($O$4="Landscape",K22,IF($O$4="Macro",L22,IF($O$4="People",M22,IF($O$4="Sports",N22,IF($O$4="Travel",O22,IF($O$4="Waterdrops",P22,IF($O$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AG22" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Androo",H22,IF($P$4="Birds in Flight",I22,IF($P$4="Birds Perched",J22,IF($P$4="Fireworks",K22,IF($P$4="Landscape",L22,IF($P$4="Macro",M22,IF($P$4="People",N22,IF($P$4="Sports",O22,IF($P$4="Travel",P22,IF($P$4="Waterdrops",Q22,IF($P$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="AF22" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Birds in Flight",H22,IF($P$4="Birds Perched",I22,IF($P$4="Fireworks",J22,IF($P$4="Landscape",K22,IF($P$4="Macro",L22,IF($P$4="People",M22,IF($P$4="Sports",N22,IF($P$4="Travel",O22,IF($P$4="Waterdrops",P22,IF($P$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AH22" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Androo",H22,IF($Q$4="Birds in Flight",I22,IF($Q$4="Birds Perched",J22,IF($Q$4="Fireworks",K22,IF($Q$4="Landscape",L22,IF($Q$4="Macro",M22,IF($Q$4="People",N22,IF($Q$4="Sports",O22,IF($Q$4="Travel",P22,IF($Q$4="Waterdrops",Q22,IF($Q$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="AG22" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Birds in Flight",H22,IF($Q$4="Birds Perched",I22,IF($Q$4="Fireworks",J22,IF($Q$4="Landscape",K22,IF($Q$4="Macro",L22,IF($Q$4="People",M22,IF($Q$4="Sports",N22,IF($Q$4="Travel",O22,IF($Q$4="Waterdrops",P22,IF($Q$4="Wildlife",Q22,""))))))))))))))</x:f>
+      <x:c r="AI22" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D22,IF($R$4="C2 Birds in Flight",E22,IF($R$4="C3 Landscape",F22,IF($R$4="Default Settings",G22,IF($R$4="Androo",H22,IF($R$4="Birds in Flight",I22,IF($R$4="Birds Perched",J22,IF($R$4="Fireworks",K22,IF($R$4="Landscape",L22,IF($R$4="Macro",M22,IF($R$4="People",N22,IF($R$4="Sports",O22,IF($R$4="Travel",P22,IF($R$4="Waterdrops",Q22,IF($R$4="Wildlife",R22,"")))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
     </x:row>
@@ -2832,11 +2972,11 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="J23" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="J23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="K23" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
@@ -2856,68 +2996,75 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="R23" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="R23" s="20" t="n">
+      <x:c r="S23" s="20" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="S23" s="20" t="n">
+      <x:c r="T23" s="20" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="T23" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D23,IF($D$4="C2 Birds in Flight",E23,IF($D$4="C3 Landscape",F23,IF($D$4="Default Settings",G23,IF($D$4="Birds in Flight",H23,IF($D$4="Birds Perched",I23,IF($D$4="Fireworks",J23,IF($D$4="Landscape",K23,IF($D$4="Macro",L23,IF($D$4="People",M23,IF($D$4="Sports",N23,IF($D$4="Travel",O23,IF($D$4="Waterdrops",P23,IF($D$4="Wildlife",Q23,""))))))))))))))</x:f>
+      <x:c r="U23" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D23,IF($D$4="C2 Birds in Flight",E23,IF($D$4="C3 Landscape",F23,IF($D$4="Default Settings",G23,IF($D$4="Androo",H23,IF($D$4="Birds in Flight",I23,IF($D$4="Birds Perched",J23,IF($D$4="Fireworks",K23,IF($D$4="Landscape",L23,IF($D$4="Macro",M23,IF($D$4="People",N23,IF($D$4="Sports",O23,IF($D$4="Travel",P23,IF($D$4="Waterdrops",Q23,IF($D$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="U23" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D23,IF($E$4="C2 Birds in Flight",E23,IF($E$4="C3 Landscape",F23,IF($E$4="Default Settings",G23,IF($E$4="Birds in Flight",H23,IF($E$4="Birds Perched",I23,IF($E$4="Fireworks",J23,IF($E$4="Landscape",K23,IF($E$4="Macro",L23,IF($E$4="People",M23,IF($E$4="Sports",N23,IF($E$4="Travel",O23,IF($E$4="Waterdrops",P23,IF($E$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="V23" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D23,IF($F$4="C2 Birds in Flight",E23,IF($F$4="C3 Landscape",F23,IF($F$4="Default Settings",G23,IF($F$4="Birds in Flight",H23,IF($F$4="Birds Perched",I23,IF($F$4="Fireworks",J23,IF($F$4="Landscape",K23,IF($F$4="Macro",L23,IF($F$4="People",M23,IF($F$4="Sports",N23,IF($F$4="Travel",O23,IF($F$4="Waterdrops",P23,IF($F$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D23,IF($E$4="C2 Birds in Flight",E23,IF($E$4="C3 Landscape",F23,IF($E$4="Default Settings",G23,IF($E$4="Androo",H23,IF($E$4="Birds in Flight",I23,IF($E$4="Birds Perched",J23,IF($E$4="Fireworks",K23,IF($E$4="Landscape",L23,IF($E$4="Macro",M23,IF($E$4="People",N23,IF($E$4="Sports",O23,IF($E$4="Travel",P23,IF($E$4="Waterdrops",Q23,IF($E$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W23" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D23,IF($G$4="C2 Birds in Flight",E23,IF($G$4="C3 Landscape",F23,IF($G$4="Default Settings",G23,IF($G$4="Birds in Flight",H23,IF($G$4="Birds Perched",I23,IF($G$4="Fireworks",J23,IF($G$4="Landscape",K23,IF($G$4="Macro",L23,IF($G$4="People",M23,IF($G$4="Sports",N23,IF($G$4="Travel",O23,IF($G$4="Waterdrops",P23,IF($G$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D23,IF($F$4="C2 Birds in Flight",E23,IF($F$4="C3 Landscape",F23,IF($F$4="Default Settings",G23,IF($F$4="Androo",H23,IF($F$4="Birds in Flight",I23,IF($F$4="Birds Perched",J23,IF($F$4="Fireworks",K23,IF($F$4="Landscape",L23,IF($F$4="Macro",M23,IF($F$4="People",N23,IF($F$4="Sports",O23,IF($F$4="Travel",P23,IF($F$4="Waterdrops",Q23,IF($F$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="X23" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D23,IF($G$4="C2 Birds in Flight",E23,IF($G$4="C3 Landscape",F23,IF($G$4="Default Settings",G23,IF($G$4="Androo",H23,IF($G$4="Birds in Flight",I23,IF($G$4="Birds Perched",J23,IF($G$4="Fireworks",K23,IF($G$4="Landscape",L23,IF($G$4="Macro",M23,IF($G$4="People",N23,IF($G$4="Sports",O23,IF($G$4="Travel",P23,IF($G$4="Waterdrops",Q23,IF($G$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="X23" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D23,IF($H$4="C2 Birds in Flight",E23,IF($H$4="C3 Landscape",F23,IF($H$4="Default Settings",G23,IF($H$4="Birds in Flight",H23,IF($H$4="Birds Perched",I23,IF($H$4="Fireworks",J23,IF($H$4="Landscape",K23,IF($H$4="Macro",L23,IF($H$4="People",M23,IF($H$4="Sports",N23,IF($H$4="Travel",O23,IF($H$4="Waterdrops",P23,IF($H$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="Y23" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D23,IF($I$4="C2 Birds in Flight",E23,IF($I$4="C3 Landscape",F23,IF($I$4="Default Settings",G23,IF($I$4="Birds in Flight",H23,IF($I$4="Birds Perched",I23,IF($I$4="Fireworks",J23,IF($I$4="Landscape",K23,IF($I$4="Macro",L23,IF($I$4="People",M23,IF($I$4="Sports",N23,IF($I$4="Travel",O23,IF($I$4="Waterdrops",P23,IF($I$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($H$4="C1 Wildlife",D23,IF($H$4="C2 Birds in Flight",E23,IF($H$4="C3 Landscape",F23,IF($H$4="Default Settings",G23,IF($H$4="Androo",H23,IF($H$4="Birds in Flight",I23,IF($H$4="Birds Perched",J23,IF($H$4="Fireworks",K23,IF($H$4="Landscape",L23,IF($H$4="Macro",M23,IF($H$4="People",N23,IF($H$4="Sports",O23,IF($H$4="Travel",P23,IF($H$4="Waterdrops",Q23,IF($H$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Z23" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D23,IF($I$4="C2 Birds in Flight",E23,IF($I$4="C3 Landscape",F23,IF($I$4="Default Settings",G23,IF($I$4="Androo",H23,IF($I$4="Birds in Flight",I23,IF($I$4="Birds Perched",J23,IF($I$4="Fireworks",K23,IF($I$4="Landscape",L23,IF($I$4="Macro",M23,IF($I$4="People",N23,IF($I$4="Sports",O23,IF($I$4="Travel",P23,IF($I$4="Waterdrops",Q23,IF($I$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA23" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D23,IF($J$4="C2 Birds in Flight",E23,IF($J$4="C3 Landscape",F23,IF($J$4="Default Settings",G23,IF($J$4="Androo",H23,IF($J$4="Birds in Flight",I23,IF($J$4="Birds Perched",J23,IF($J$4="Fireworks",K23,IF($J$4="Landscape",L23,IF($J$4="Macro",M23,IF($J$4="People",N23,IF($J$4="Sports",O23,IF($J$4="Travel",P23,IF($J$4="Waterdrops",Q23,IF($J$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="Z23" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D23,IF($J$4="C2 Birds in Flight",E23,IF($J$4="C3 Landscape",F23,IF($J$4="Default Settings",G23,IF($J$4="Birds in Flight",H23,IF($J$4="Birds Perched",I23,IF($J$4="Fireworks",J23,IF($J$4="Landscape",K23,IF($J$4="Macro",L23,IF($J$4="People",M23,IF($J$4="Sports",N23,IF($J$4="Travel",O23,IF($J$4="Waterdrops",P23,IF($J$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA23" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D23,IF($K$4="C2 Birds in Flight",E23,IF($K$4="C3 Landscape",F23,IF($K$4="Default Settings",G23,IF($K$4="Birds in Flight",H23,IF($K$4="Birds Perched",I23,IF($K$4="Fireworks",J23,IF($K$4="Landscape",K23,IF($K$4="Macro",L23,IF($K$4="People",M23,IF($K$4="Sports",N23,IF($K$4="Travel",O23,IF($K$4="Waterdrops",P23,IF($K$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AB23" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D23,IF($L$4="C2 Birds in Flight",E23,IF($L$4="C3 Landscape",F23,IF($L$4="Default Settings",G23,IF($L$4="Birds in Flight",H23,IF($L$4="Birds Perched",I23,IF($L$4="Fireworks",J23,IF($L$4="Landscape",K23,IF($L$4="Macro",L23,IF($L$4="People",M23,IF($L$4="Sports",N23,IF($L$4="Travel",O23,IF($L$4="Waterdrops",P23,IF($L$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D23,IF($K$4="C2 Birds in Flight",E23,IF($K$4="C3 Landscape",F23,IF($K$4="Default Settings",G23,IF($K$4="Androo",H23,IF($K$4="Birds in Flight",I23,IF($K$4="Birds Perched",J23,IF($K$4="Fireworks",K23,IF($K$4="Landscape",L23,IF($K$4="Macro",M23,IF($K$4="People",N23,IF($K$4="Sports",O23,IF($K$4="Travel",P23,IF($K$4="Waterdrops",Q23,IF($K$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC23" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D23,IF($M$4="C2 Birds in Flight",E23,IF($M$4="C3 Landscape",F23,IF($M$4="Default Settings",G23,IF($M$4="Birds in Flight",H23,IF($M$4="Birds Perched",I23,IF($M$4="Fireworks",J23,IF($M$4="Landscape",K23,IF($M$4="Macro",L23,IF($M$4="People",M23,IF($M$4="Sports",N23,IF($M$4="Travel",O23,IF($M$4="Waterdrops",P23,IF($M$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D23,IF($L$4="C2 Birds in Flight",E23,IF($L$4="C3 Landscape",F23,IF($L$4="Default Settings",G23,IF($L$4="Androo",H23,IF($L$4="Birds in Flight",I23,IF($L$4="Birds Perched",J23,IF($L$4="Fireworks",K23,IF($L$4="Landscape",L23,IF($L$4="Macro",M23,IF($L$4="People",N23,IF($L$4="Sports",O23,IF($L$4="Travel",P23,IF($L$4="Waterdrops",Q23,IF($L$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AD23" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D23,IF($N$4="C2 Birds in Flight",E23,IF($N$4="C3 Landscape",F23,IF($N$4="Default Settings",G23,IF($N$4="Birds in Flight",H23,IF($N$4="Birds Perched",I23,IF($N$4="Fireworks",J23,IF($N$4="Landscape",K23,IF($N$4="Macro",L23,IF($N$4="People",M23,IF($N$4="Sports",N23,IF($N$4="Travel",O23,IF($N$4="Waterdrops",P23,IF($N$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($M$4="C1 Wildlife",D23,IF($M$4="C2 Birds in Flight",E23,IF($M$4="C3 Landscape",F23,IF($M$4="Default Settings",G23,IF($M$4="Androo",H23,IF($M$4="Birds in Flight",I23,IF($M$4="Birds Perched",J23,IF($M$4="Fireworks",K23,IF($M$4="Landscape",L23,IF($M$4="Macro",M23,IF($M$4="People",N23,IF($M$4="Sports",O23,IF($M$4="Travel",P23,IF($M$4="Waterdrops",Q23,IF($M$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AE23" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D23,IF($O$4="C2 Birds in Flight",E23,IF($O$4="C3 Landscape",F23,IF($O$4="Default Settings",G23,IF($O$4="Birds in Flight",H23,IF($O$4="Birds Perched",I23,IF($O$4="Fireworks",J23,IF($O$4="Landscape",K23,IF($O$4="Macro",L23,IF($O$4="People",M23,IF($O$4="Sports",N23,IF($O$4="Travel",O23,IF($O$4="Waterdrops",P23,IF($O$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($N$4="C1 Wildlife",D23,IF($N$4="C2 Birds in Flight",E23,IF($N$4="C3 Landscape",F23,IF($N$4="Default Settings",G23,IF($N$4="Androo",H23,IF($N$4="Birds in Flight",I23,IF($N$4="Birds Perched",J23,IF($N$4="Fireworks",K23,IF($N$4="Landscape",L23,IF($N$4="Macro",M23,IF($N$4="People",N23,IF($N$4="Sports",O23,IF($N$4="Travel",P23,IF($N$4="Waterdrops",Q23,IF($N$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AF23" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D23,IF($P$4="C2 Birds in Flight",E23,IF($P$4="C3 Landscape",F23,IF($P$4="Default Settings",G23,IF($P$4="Birds in Flight",H23,IF($P$4="Birds Perched",I23,IF($P$4="Fireworks",J23,IF($P$4="Landscape",K23,IF($P$4="Macro",L23,IF($P$4="People",M23,IF($P$4="Sports",N23,IF($P$4="Travel",O23,IF($P$4="Waterdrops",P23,IF($P$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D23,IF($O$4="C2 Birds in Flight",E23,IF($O$4="C3 Landscape",F23,IF($O$4="Default Settings",G23,IF($O$4="Androo",H23,IF($O$4="Birds in Flight",I23,IF($O$4="Birds Perched",J23,IF($O$4="Fireworks",K23,IF($O$4="Landscape",L23,IF($O$4="Macro",M23,IF($O$4="People",N23,IF($O$4="Sports",O23,IF($O$4="Travel",P23,IF($O$4="Waterdrops",Q23,IF($O$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG23" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D23,IF($Q$4="C2 Birds in Flight",E23,IF($Q$4="C3 Landscape",F23,IF($Q$4="Default Settings",G23,IF($Q$4="Birds in Flight",H23,IF($Q$4="Birds Perched",I23,IF($Q$4="Fireworks",J23,IF($Q$4="Landscape",K23,IF($Q$4="Macro",L23,IF($Q$4="People",M23,IF($Q$4="Sports",N23,IF($Q$4="Travel",O23,IF($Q$4="Waterdrops",P23,IF($Q$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D23,IF($P$4="C2 Birds in Flight",E23,IF($P$4="C3 Landscape",F23,IF($P$4="Default Settings",G23,IF($P$4="Androo",H23,IF($P$4="Birds in Flight",I23,IF($P$4="Birds Perched",J23,IF($P$4="Fireworks",K23,IF($P$4="Landscape",L23,IF($P$4="Macro",M23,IF($P$4="People",N23,IF($P$4="Sports",O23,IF($P$4="Travel",P23,IF($P$4="Waterdrops",Q23,IF($P$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AH23" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D23,IF($Q$4="C2 Birds in Flight",E23,IF($Q$4="C3 Landscape",F23,IF($Q$4="Default Settings",G23,IF($Q$4="Androo",H23,IF($Q$4="Birds in Flight",I23,IF($Q$4="Birds Perched",J23,IF($Q$4="Fireworks",K23,IF($Q$4="Landscape",L23,IF($Q$4="Macro",M23,IF($Q$4="People",N23,IF($Q$4="Sports",O23,IF($Q$4="Travel",P23,IF($Q$4="Waterdrops",Q23,IF($Q$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AI23" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D23,IF($R$4="C2 Birds in Flight",E23,IF($R$4="C3 Landscape",F23,IF($R$4="Default Settings",G23,IF($R$4="Androo",H23,IF($R$4="Birds in Flight",I23,IF($R$4="Birds Perched",J23,IF($R$4="Fireworks",K23,IF($R$4="Landscape",L23,IF($R$4="Macro",M23,IF($R$4="People",N23,IF($R$4="Sports",O23,IF($R$4="Travel",P23,IF($R$4="Waterdrops",Q23,IF($R$4="Wildlife",R23,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
@@ -2944,16 +3091,16 @@
         <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="H24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="I24" s="17" t="str">
+      <x:c r="J24" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="J24" s="17" t="str">
+      <x:c r="K24" s="17" t="str">
         <x:v>Off</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="str">
-        <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="L24" s="17" t="str">
         <x:v>Mode 1</x:v>
@@ -2962,77 +3109,84 @@
         <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="N24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="O24" s="17" t="str">
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="O24" s="17" t="str">
+      <x:c r="P24" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="P24" s="17" t="str">
+      <x:c r="Q24" s="17" t="str">
         <x:v>Off</x:v>
       </x:c>
-      <x:c r="Q24" s="17" t="str">
+      <x:c r="R24" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="R24" s="20" t="n">
+      <x:c r="S24" s="20" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="S24" s="20" t="n">
+      <x:c r="T24" s="20" t="n">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="T24" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D24,IF($D$4="C2 Birds in Flight",E24,IF($D$4="C3 Landscape",F24,IF($D$4="Default Settings",G24,IF($D$4="Birds in Flight",H24,IF($D$4="Birds Perched",I24,IF($D$4="Fireworks",J24,IF($D$4="Landscape",K24,IF($D$4="Macro",L24,IF($D$4="People",M24,IF($D$4="Sports",N24,IF($D$4="Travel",O24,IF($D$4="Waterdrops",P24,IF($D$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="U24" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D24,IF($D$4="C2 Birds in Flight",E24,IF($D$4="C3 Landscape",F24,IF($D$4="Default Settings",G24,IF($D$4="Androo",H24,IF($D$4="Birds in Flight",I24,IF($D$4="Birds Perched",J24,IF($D$4="Fireworks",K24,IF($D$4="Landscape",L24,IF($D$4="Macro",M24,IF($D$4="People",N24,IF($D$4="Sports",O24,IF($D$4="Travel",P24,IF($D$4="Waterdrops",Q24,IF($D$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="U24" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D24,IF($E$4="C2 Birds in Flight",E24,IF($E$4="C3 Landscape",F24,IF($E$4="Default Settings",G24,IF($E$4="Birds in Flight",H24,IF($E$4="Birds Perched",I24,IF($E$4="Fireworks",J24,IF($E$4="Landscape",K24,IF($E$4="Macro",L24,IF($E$4="People",M24,IF($E$4="Sports",N24,IF($E$4="Travel",O24,IF($E$4="Waterdrops",P24,IF($E$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="V24" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D24,IF($E$4="C2 Birds in Flight",E24,IF($E$4="C3 Landscape",F24,IF($E$4="Default Settings",G24,IF($E$4="Androo",H24,IF($E$4="Birds in Flight",I24,IF($E$4="Birds Perched",J24,IF($E$4="Fireworks",K24,IF($E$4="Landscape",L24,IF($E$4="Macro",M24,IF($E$4="People",N24,IF($E$4="Sports",O24,IF($E$4="Travel",P24,IF($E$4="Waterdrops",Q24,IF($E$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="V24" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D24,IF($F$4="C2 Birds in Flight",E24,IF($F$4="C3 Landscape",F24,IF($F$4="Default Settings",G24,IF($F$4="Birds in Flight",H24,IF($F$4="Birds Perched",I24,IF($F$4="Fireworks",J24,IF($F$4="Landscape",K24,IF($F$4="Macro",L24,IF($F$4="People",M24,IF($F$4="Sports",N24,IF($F$4="Travel",O24,IF($F$4="Waterdrops",P24,IF($F$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="W24" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D24,IF($F$4="C2 Birds in Flight",E24,IF($F$4="C3 Landscape",F24,IF($F$4="Default Settings",G24,IF($F$4="Androo",H24,IF($F$4="Birds in Flight",I24,IF($F$4="Birds Perched",J24,IF($F$4="Fireworks",K24,IF($F$4="Landscape",L24,IF($F$4="Macro",M24,IF($F$4="People",N24,IF($F$4="Sports",O24,IF($F$4="Travel",P24,IF($F$4="Waterdrops",Q24,IF($F$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="W24" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D24,IF($G$4="C2 Birds in Flight",E24,IF($G$4="C3 Landscape",F24,IF($G$4="Default Settings",G24,IF($G$4="Birds in Flight",H24,IF($G$4="Birds Perched",I24,IF($G$4="Fireworks",J24,IF($G$4="Landscape",K24,IF($G$4="Macro",L24,IF($G$4="People",M24,IF($G$4="Sports",N24,IF($G$4="Travel",O24,IF($G$4="Waterdrops",P24,IF($G$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="X24" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D24,IF($G$4="C2 Birds in Flight",E24,IF($G$4="C3 Landscape",F24,IF($G$4="Default Settings",G24,IF($G$4="Androo",H24,IF($G$4="Birds in Flight",I24,IF($G$4="Birds Perched",J24,IF($G$4="Fireworks",K24,IF($G$4="Landscape",L24,IF($G$4="Macro",M24,IF($G$4="People",N24,IF($G$4="Sports",O24,IF($G$4="Travel",P24,IF($G$4="Waterdrops",Q24,IF($G$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="X24" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D24,IF($H$4="C2 Birds in Flight",E24,IF($H$4="C3 Landscape",F24,IF($H$4="Default Settings",G24,IF($H$4="Birds in Flight",H24,IF($H$4="Birds Perched",I24,IF($H$4="Fireworks",J24,IF($H$4="Landscape",K24,IF($H$4="Macro",L24,IF($H$4="People",M24,IF($H$4="Sports",N24,IF($H$4="Travel",O24,IF($H$4="Waterdrops",P24,IF($H$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="Y24" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D24,IF($H$4="C2 Birds in Flight",E24,IF($H$4="C3 Landscape",F24,IF($H$4="Default Settings",G24,IF($H$4="Androo",H24,IF($H$4="Birds in Flight",I24,IF($H$4="Birds Perched",J24,IF($H$4="Fireworks",K24,IF($H$4="Landscape",L24,IF($H$4="Macro",M24,IF($H$4="People",N24,IF($H$4="Sports",O24,IF($H$4="Travel",P24,IF($H$4="Waterdrops",Q24,IF($H$4="Wildlife",R24,"")))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Z24" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D24,IF($I$4="C2 Birds in Flight",E24,IF($I$4="C3 Landscape",F24,IF($I$4="Default Settings",G24,IF($I$4="Androo",H24,IF($I$4="Birds in Flight",I24,IF($I$4="Birds Perched",J24,IF($I$4="Fireworks",K24,IF($I$4="Landscape",L24,IF($I$4="Macro",M24,IF($I$4="People",N24,IF($I$4="Sports",O24,IF($I$4="Travel",P24,IF($I$4="Waterdrops",Q24,IF($I$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="Y24" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D24,IF($I$4="C2 Birds in Flight",E24,IF($I$4="C3 Landscape",F24,IF($I$4="Default Settings",G24,IF($I$4="Birds in Flight",H24,IF($I$4="Birds Perched",I24,IF($I$4="Fireworks",J24,IF($I$4="Landscape",K24,IF($I$4="Macro",L24,IF($I$4="People",M24,IF($I$4="Sports",N24,IF($I$4="Travel",O24,IF($I$4="Waterdrops",P24,IF($I$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AA24" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D24,IF($J$4="C2 Birds in Flight",E24,IF($J$4="C3 Landscape",F24,IF($J$4="Default Settings",G24,IF($J$4="Androo",H24,IF($J$4="Birds in Flight",I24,IF($J$4="Birds Perched",J24,IF($J$4="Fireworks",K24,IF($J$4="Landscape",L24,IF($J$4="Macro",M24,IF($J$4="People",N24,IF($J$4="Sports",O24,IF($J$4="Travel",P24,IF($J$4="Waterdrops",Q24,IF($J$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="Z24" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D24,IF($J$4="C2 Birds in Flight",E24,IF($J$4="C3 Landscape",F24,IF($J$4="Default Settings",G24,IF($J$4="Birds in Flight",H24,IF($J$4="Birds Perched",I24,IF($J$4="Fireworks",J24,IF($J$4="Landscape",K24,IF($J$4="Macro",L24,IF($J$4="People",M24,IF($J$4="Sports",N24,IF($J$4="Travel",O24,IF($J$4="Waterdrops",P24,IF($J$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AB24" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D24,IF($K$4="C2 Birds in Flight",E24,IF($K$4="C3 Landscape",F24,IF($K$4="Default Settings",G24,IF($K$4="Androo",H24,IF($K$4="Birds in Flight",I24,IF($K$4="Birds Perched",J24,IF($K$4="Fireworks",K24,IF($K$4="Landscape",L24,IF($K$4="Macro",M24,IF($K$4="People",N24,IF($K$4="Sports",O24,IF($K$4="Travel",P24,IF($K$4="Waterdrops",Q24,IF($K$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Off</x:v>
       </x:c>
-      <x:c r="AA24" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D24,IF($K$4="C2 Birds in Flight",E24,IF($K$4="C3 Landscape",F24,IF($K$4="Default Settings",G24,IF($K$4="Birds in Flight",H24,IF($K$4="Birds Perched",I24,IF($K$4="Fireworks",J24,IF($K$4="Landscape",K24,IF($K$4="Macro",L24,IF($K$4="People",M24,IF($K$4="Sports",N24,IF($K$4="Travel",O24,IF($K$4="Waterdrops",P24,IF($K$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AC24" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D24,IF($L$4="C2 Birds in Flight",E24,IF($L$4="C3 Landscape",F24,IF($L$4="Default Settings",G24,IF($L$4="Androo",H24,IF($L$4="Birds in Flight",I24,IF($L$4="Birds Perched",J24,IF($L$4="Fireworks",K24,IF($L$4="Landscape",L24,IF($L$4="Macro",M24,IF($L$4="People",N24,IF($L$4="Sports",O24,IF($L$4="Travel",P24,IF($L$4="Waterdrops",Q24,IF($L$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="AB24" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D24,IF($L$4="C2 Birds in Flight",E24,IF($L$4="C3 Landscape",F24,IF($L$4="Default Settings",G24,IF($L$4="Birds in Flight",H24,IF($L$4="Birds Perched",I24,IF($L$4="Fireworks",J24,IF($L$4="Landscape",K24,IF($L$4="Macro",L24,IF($L$4="People",M24,IF($L$4="Sports",N24,IF($L$4="Travel",O24,IF($L$4="Waterdrops",P24,IF($L$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AD24" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D24,IF($M$4="C2 Birds in Flight",E24,IF($M$4="C3 Landscape",F24,IF($M$4="Default Settings",G24,IF($M$4="Androo",H24,IF($M$4="Birds in Flight",I24,IF($M$4="Birds Perched",J24,IF($M$4="Fireworks",K24,IF($M$4="Landscape",L24,IF($M$4="Macro",M24,IF($M$4="People",N24,IF($M$4="Sports",O24,IF($M$4="Travel",P24,IF($M$4="Waterdrops",Q24,IF($M$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="AC24" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D24,IF($M$4="C2 Birds in Flight",E24,IF($M$4="C3 Landscape",F24,IF($M$4="Default Settings",G24,IF($M$4="Birds in Flight",H24,IF($M$4="Birds Perched",I24,IF($M$4="Fireworks",J24,IF($M$4="Landscape",K24,IF($M$4="Macro",L24,IF($M$4="People",M24,IF($M$4="Sports",N24,IF($M$4="Travel",O24,IF($M$4="Waterdrops",P24,IF($M$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AE24" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D24,IF($N$4="C2 Birds in Flight",E24,IF($N$4="C3 Landscape",F24,IF($N$4="Default Settings",G24,IF($N$4="Androo",H24,IF($N$4="Birds in Flight",I24,IF($N$4="Birds Perched",J24,IF($N$4="Fireworks",K24,IF($N$4="Landscape",L24,IF($N$4="Macro",M24,IF($N$4="People",N24,IF($N$4="Sports",O24,IF($N$4="Travel",P24,IF($N$4="Waterdrops",Q24,IF($N$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="AD24" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D24,IF($N$4="C2 Birds in Flight",E24,IF($N$4="C3 Landscape",F24,IF($N$4="Default Settings",G24,IF($N$4="Birds in Flight",H24,IF($N$4="Birds Perched",I24,IF($N$4="Fireworks",J24,IF($N$4="Landscape",K24,IF($N$4="Macro",L24,IF($N$4="People",M24,IF($N$4="Sports",N24,IF($N$4="Travel",O24,IF($N$4="Waterdrops",P24,IF($N$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AF24" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D24,IF($O$4="C2 Birds in Flight",E24,IF($O$4="C3 Landscape",F24,IF($O$4="Default Settings",G24,IF($O$4="Androo",H24,IF($O$4="Birds in Flight",I24,IF($O$4="Birds Perched",J24,IF($O$4="Fireworks",K24,IF($O$4="Landscape",L24,IF($O$4="Macro",M24,IF($O$4="People",N24,IF($O$4="Sports",O24,IF($O$4="Travel",P24,IF($O$4="Waterdrops",Q24,IF($O$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="AE24" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D24,IF($O$4="C2 Birds in Flight",E24,IF($O$4="C3 Landscape",F24,IF($O$4="Default Settings",G24,IF($O$4="Birds in Flight",H24,IF($O$4="Birds Perched",I24,IF($O$4="Fireworks",J24,IF($O$4="Landscape",K24,IF($O$4="Macro",L24,IF($O$4="People",M24,IF($O$4="Sports",N24,IF($O$4="Travel",O24,IF($O$4="Waterdrops",P24,IF($O$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AG24" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D24,IF($P$4="C2 Birds in Flight",E24,IF($P$4="C3 Landscape",F24,IF($P$4="Default Settings",G24,IF($P$4="Androo",H24,IF($P$4="Birds in Flight",I24,IF($P$4="Birds Perched",J24,IF($P$4="Fireworks",K24,IF($P$4="Landscape",L24,IF($P$4="Macro",M24,IF($P$4="People",N24,IF($P$4="Sports",O24,IF($P$4="Travel",P24,IF($P$4="Waterdrops",Q24,IF($P$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="AF24" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D24,IF($P$4="C2 Birds in Flight",E24,IF($P$4="C3 Landscape",F24,IF($P$4="Default Settings",G24,IF($P$4="Birds in Flight",H24,IF($P$4="Birds Perched",I24,IF($P$4="Fireworks",J24,IF($P$4="Landscape",K24,IF($P$4="Macro",L24,IF($P$4="People",M24,IF($P$4="Sports",N24,IF($P$4="Travel",O24,IF($P$4="Waterdrops",P24,IF($P$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AH24" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D24,IF($Q$4="C2 Birds in Flight",E24,IF($Q$4="C3 Landscape",F24,IF($Q$4="Default Settings",G24,IF($Q$4="Androo",H24,IF($Q$4="Birds in Flight",I24,IF($Q$4="Birds Perched",J24,IF($Q$4="Fireworks",K24,IF($Q$4="Landscape",L24,IF($Q$4="Macro",M24,IF($Q$4="People",N24,IF($Q$4="Sports",O24,IF($Q$4="Travel",P24,IF($Q$4="Waterdrops",Q24,IF($Q$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Off</x:v>
       </x:c>
-      <x:c r="AG24" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D24,IF($Q$4="C2 Birds in Flight",E24,IF($Q$4="C3 Landscape",F24,IF($Q$4="Default Settings",G24,IF($Q$4="Birds in Flight",H24,IF($Q$4="Birds Perched",I24,IF($Q$4="Fireworks",J24,IF($Q$4="Landscape",K24,IF($Q$4="Macro",L24,IF($Q$4="People",M24,IF($Q$4="Sports",N24,IF($Q$4="Travel",O24,IF($Q$4="Waterdrops",P24,IF($Q$4="Wildlife",Q24,""))))))))))))))</x:f>
+      <x:c r="AI24" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D24,IF($R$4="C2 Birds in Flight",E24,IF($R$4="C3 Landscape",F24,IF($R$4="Default Settings",G24,IF($R$4="Androo",H24,IF($R$4="Birds in Flight",I24,IF($R$4="Birds Perched",J24,IF($R$4="Fireworks",K24,IF($R$4="Landscape",L24,IF($R$4="Macro",M24,IF($R$4="People",N24,IF($R$4="Sports",O24,IF($R$4="Travel",P24,IF($R$4="Waterdrops",Q24,IF($R$4="Wildlife",R24,"")))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
     </x:row>
@@ -3065,10 +3219,10 @@
         <x:v>On / On</x:v>
       </x:c>
       <x:c r="J25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="str">
         <x:v>Off / Off</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="str">
-        <x:v>On / On</x:v>
       </x:c>
       <x:c r="L25" s="17" t="str">
         <x:v>On / On</x:v>
@@ -3083,71 +3237,78 @@
         <x:v>On / On</x:v>
       </x:c>
       <x:c r="P25" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Q25" s="17" t="str">
         <x:v>Off / Off</x:v>
       </x:c>
-      <x:c r="Q25" s="17" t="str">
+      <x:c r="R25" s="17" t="str">
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="R25" s="20" t="n">
+      <x:c r="S25" s="20" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="S25" s="20" t="n">
+      <x:c r="T25" s="20" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="T25" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D25,IF($D$4="C2 Birds in Flight",E25,IF($D$4="C3 Landscape",F25,IF($D$4="Default Settings",G25,IF($D$4="Birds in Flight",H25,IF($D$4="Birds Perched",I25,IF($D$4="Fireworks",J25,IF($D$4="Landscape",K25,IF($D$4="Macro",L25,IF($D$4="People",M25,IF($D$4="Sports",N25,IF($D$4="Travel",O25,IF($D$4="Waterdrops",P25,IF($D$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="U25" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D25,IF($D$4="C2 Birds in Flight",E25,IF($D$4="C3 Landscape",F25,IF($D$4="Default Settings",G25,IF($D$4="Androo",H25,IF($D$4="Birds in Flight",I25,IF($D$4="Birds Perched",J25,IF($D$4="Fireworks",K25,IF($D$4="Landscape",L25,IF($D$4="Macro",M25,IF($D$4="People",N25,IF($D$4="Sports",O25,IF($D$4="Travel",P25,IF($D$4="Waterdrops",Q25,IF($D$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="U25" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D25,IF($E$4="C2 Birds in Flight",E25,IF($E$4="C3 Landscape",F25,IF($E$4="Default Settings",G25,IF($E$4="Birds in Flight",H25,IF($E$4="Birds Perched",I25,IF($E$4="Fireworks",J25,IF($E$4="Landscape",K25,IF($E$4="Macro",L25,IF($E$4="People",M25,IF($E$4="Sports",N25,IF($E$4="Travel",O25,IF($E$4="Waterdrops",P25,IF($E$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="V25" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D25,IF($E$4="C2 Birds in Flight",E25,IF($E$4="C3 Landscape",F25,IF($E$4="Default Settings",G25,IF($E$4="Androo",H25,IF($E$4="Birds in Flight",I25,IF($E$4="Birds Perched",J25,IF($E$4="Fireworks",K25,IF($E$4="Landscape",L25,IF($E$4="Macro",M25,IF($E$4="People",N25,IF($E$4="Sports",O25,IF($E$4="Travel",P25,IF($E$4="Waterdrops",Q25,IF($E$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="V25" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D25,IF($F$4="C2 Birds in Flight",E25,IF($F$4="C3 Landscape",F25,IF($F$4="Default Settings",G25,IF($F$4="Birds in Flight",H25,IF($F$4="Birds Perched",I25,IF($F$4="Fireworks",J25,IF($F$4="Landscape",K25,IF($F$4="Macro",L25,IF($F$4="People",M25,IF($F$4="Sports",N25,IF($F$4="Travel",O25,IF($F$4="Waterdrops",P25,IF($F$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="W25" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D25,IF($F$4="C2 Birds in Flight",E25,IF($F$4="C3 Landscape",F25,IF($F$4="Default Settings",G25,IF($F$4="Androo",H25,IF($F$4="Birds in Flight",I25,IF($F$4="Birds Perched",J25,IF($F$4="Fireworks",K25,IF($F$4="Landscape",L25,IF($F$4="Macro",M25,IF($F$4="People",N25,IF($F$4="Sports",O25,IF($F$4="Travel",P25,IF($F$4="Waterdrops",Q25,IF($F$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="W25" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D25,IF($G$4="C2 Birds in Flight",E25,IF($G$4="C3 Landscape",F25,IF($G$4="Default Settings",G25,IF($G$4="Birds in Flight",H25,IF($G$4="Birds Perched",I25,IF($G$4="Fireworks",J25,IF($G$4="Landscape",K25,IF($G$4="Macro",L25,IF($G$4="People",M25,IF($G$4="Sports",N25,IF($G$4="Travel",O25,IF($G$4="Waterdrops",P25,IF($G$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="X25" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D25,IF($G$4="C2 Birds in Flight",E25,IF($G$4="C3 Landscape",F25,IF($G$4="Default Settings",G25,IF($G$4="Androo",H25,IF($G$4="Birds in Flight",I25,IF($G$4="Birds Perched",J25,IF($G$4="Fireworks",K25,IF($G$4="Landscape",L25,IF($G$4="Macro",M25,IF($G$4="People",N25,IF($G$4="Sports",O25,IF($G$4="Travel",P25,IF($G$4="Waterdrops",Q25,IF($G$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="X25" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D25,IF($H$4="C2 Birds in Flight",E25,IF($H$4="C3 Landscape",F25,IF($H$4="Default Settings",G25,IF($H$4="Birds in Flight",H25,IF($H$4="Birds Perched",I25,IF($H$4="Fireworks",J25,IF($H$4="Landscape",K25,IF($H$4="Macro",L25,IF($H$4="People",M25,IF($H$4="Sports",N25,IF($H$4="Travel",O25,IF($H$4="Waterdrops",P25,IF($H$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="Y25" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D25,IF($H$4="C2 Birds in Flight",E25,IF($H$4="C3 Landscape",F25,IF($H$4="Default Settings",G25,IF($H$4="Androo",H25,IF($H$4="Birds in Flight",I25,IF($H$4="Birds Perched",J25,IF($H$4="Fireworks",K25,IF($H$4="Landscape",L25,IF($H$4="Macro",M25,IF($H$4="People",N25,IF($H$4="Sports",O25,IF($H$4="Travel",P25,IF($H$4="Waterdrops",Q25,IF($H$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="Y25" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D25,IF($I$4="C2 Birds in Flight",E25,IF($I$4="C3 Landscape",F25,IF($I$4="Default Settings",G25,IF($I$4="Birds in Flight",H25,IF($I$4="Birds Perched",I25,IF($I$4="Fireworks",J25,IF($I$4="Landscape",K25,IF($I$4="Macro",L25,IF($I$4="People",M25,IF($I$4="Sports",N25,IF($I$4="Travel",O25,IF($I$4="Waterdrops",P25,IF($I$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="Z25" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D25,IF($I$4="C2 Birds in Flight",E25,IF($I$4="C3 Landscape",F25,IF($I$4="Default Settings",G25,IF($I$4="Androo",H25,IF($I$4="Birds in Flight",I25,IF($I$4="Birds Perched",J25,IF($I$4="Fireworks",K25,IF($I$4="Landscape",L25,IF($I$4="Macro",M25,IF($I$4="People",N25,IF($I$4="Sports",O25,IF($I$4="Travel",P25,IF($I$4="Waterdrops",Q25,IF($I$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="Z25" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D25,IF($J$4="C2 Birds in Flight",E25,IF($J$4="C3 Landscape",F25,IF($J$4="Default Settings",G25,IF($J$4="Birds in Flight",H25,IF($J$4="Birds Perched",I25,IF($J$4="Fireworks",J25,IF($J$4="Landscape",K25,IF($J$4="Macro",L25,IF($J$4="People",M25,IF($J$4="Sports",N25,IF($J$4="Travel",O25,IF($J$4="Waterdrops",P25,IF($J$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AA25" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D25,IF($J$4="C2 Birds in Flight",E25,IF($J$4="C3 Landscape",F25,IF($J$4="Default Settings",G25,IF($J$4="Androo",H25,IF($J$4="Birds in Flight",I25,IF($J$4="Birds Perched",J25,IF($J$4="Fireworks",K25,IF($J$4="Landscape",L25,IF($J$4="Macro",M25,IF($J$4="People",N25,IF($J$4="Sports",O25,IF($J$4="Travel",P25,IF($J$4="Waterdrops",Q25,IF($J$4="Wildlife",R25,"")))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AB25" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D25,IF($K$4="C2 Birds in Flight",E25,IF($K$4="C3 Landscape",F25,IF($K$4="Default Settings",G25,IF($K$4="Androo",H25,IF($K$4="Birds in Flight",I25,IF($K$4="Birds Perched",J25,IF($K$4="Fireworks",K25,IF($K$4="Landscape",L25,IF($K$4="Macro",M25,IF($K$4="People",N25,IF($K$4="Sports",O25,IF($K$4="Travel",P25,IF($K$4="Waterdrops",Q25,IF($K$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>Off / Off</x:v>
       </x:c>
-      <x:c r="AA25" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D25,IF($K$4="C2 Birds in Flight",E25,IF($K$4="C3 Landscape",F25,IF($K$4="Default Settings",G25,IF($K$4="Birds in Flight",H25,IF($K$4="Birds Perched",I25,IF($K$4="Fireworks",J25,IF($K$4="Landscape",K25,IF($K$4="Macro",L25,IF($K$4="People",M25,IF($K$4="Sports",N25,IF($K$4="Travel",O25,IF($K$4="Waterdrops",P25,IF($K$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AC25" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D25,IF($L$4="C2 Birds in Flight",E25,IF($L$4="C3 Landscape",F25,IF($L$4="Default Settings",G25,IF($L$4="Androo",H25,IF($L$4="Birds in Flight",I25,IF($L$4="Birds Perched",J25,IF($L$4="Fireworks",K25,IF($L$4="Landscape",L25,IF($L$4="Macro",M25,IF($L$4="People",N25,IF($L$4="Sports",O25,IF($L$4="Travel",P25,IF($L$4="Waterdrops",Q25,IF($L$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="AB25" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D25,IF($L$4="C2 Birds in Flight",E25,IF($L$4="C3 Landscape",F25,IF($L$4="Default Settings",G25,IF($L$4="Birds in Flight",H25,IF($L$4="Birds Perched",I25,IF($L$4="Fireworks",J25,IF($L$4="Landscape",K25,IF($L$4="Macro",L25,IF($L$4="People",M25,IF($L$4="Sports",N25,IF($L$4="Travel",O25,IF($L$4="Waterdrops",P25,IF($L$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AD25" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D25,IF($M$4="C2 Birds in Flight",E25,IF($M$4="C3 Landscape",F25,IF($M$4="Default Settings",G25,IF($M$4="Androo",H25,IF($M$4="Birds in Flight",I25,IF($M$4="Birds Perched",J25,IF($M$4="Fireworks",K25,IF($M$4="Landscape",L25,IF($M$4="Macro",M25,IF($M$4="People",N25,IF($M$4="Sports",O25,IF($M$4="Travel",P25,IF($M$4="Waterdrops",Q25,IF($M$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="AC25" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D25,IF($M$4="C2 Birds in Flight",E25,IF($M$4="C3 Landscape",F25,IF($M$4="Default Settings",G25,IF($M$4="Birds in Flight",H25,IF($M$4="Birds Perched",I25,IF($M$4="Fireworks",J25,IF($M$4="Landscape",K25,IF($M$4="Macro",L25,IF($M$4="People",M25,IF($M$4="Sports",N25,IF($M$4="Travel",O25,IF($M$4="Waterdrops",P25,IF($M$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AE25" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D25,IF($N$4="C2 Birds in Flight",E25,IF($N$4="C3 Landscape",F25,IF($N$4="Default Settings",G25,IF($N$4="Androo",H25,IF($N$4="Birds in Flight",I25,IF($N$4="Birds Perched",J25,IF($N$4="Fireworks",K25,IF($N$4="Landscape",L25,IF($N$4="Macro",M25,IF($N$4="People",N25,IF($N$4="Sports",O25,IF($N$4="Travel",P25,IF($N$4="Waterdrops",Q25,IF($N$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="AD25" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D25,IF($N$4="C2 Birds in Flight",E25,IF($N$4="C3 Landscape",F25,IF($N$4="Default Settings",G25,IF($N$4="Birds in Flight",H25,IF($N$4="Birds Perched",I25,IF($N$4="Fireworks",J25,IF($N$4="Landscape",K25,IF($N$4="Macro",L25,IF($N$4="People",M25,IF($N$4="Sports",N25,IF($N$4="Travel",O25,IF($N$4="Waterdrops",P25,IF($N$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AF25" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D25,IF($O$4="C2 Birds in Flight",E25,IF($O$4="C3 Landscape",F25,IF($O$4="Default Settings",G25,IF($O$4="Androo",H25,IF($O$4="Birds in Flight",I25,IF($O$4="Birds Perched",J25,IF($O$4="Fireworks",K25,IF($O$4="Landscape",L25,IF($O$4="Macro",M25,IF($O$4="People",N25,IF($O$4="Sports",O25,IF($O$4="Travel",P25,IF($O$4="Waterdrops",Q25,IF($O$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="AE25" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D25,IF($O$4="C2 Birds in Flight",E25,IF($O$4="C3 Landscape",F25,IF($O$4="Default Settings",G25,IF($O$4="Birds in Flight",H25,IF($O$4="Birds Perched",I25,IF($O$4="Fireworks",J25,IF($O$4="Landscape",K25,IF($O$4="Macro",L25,IF($O$4="People",M25,IF($O$4="Sports",N25,IF($O$4="Travel",O25,IF($O$4="Waterdrops",P25,IF($O$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AG25" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D25,IF($P$4="C2 Birds in Flight",E25,IF($P$4="C3 Landscape",F25,IF($P$4="Default Settings",G25,IF($P$4="Androo",H25,IF($P$4="Birds in Flight",I25,IF($P$4="Birds Perched",J25,IF($P$4="Fireworks",K25,IF($P$4="Landscape",L25,IF($P$4="Macro",M25,IF($P$4="People",N25,IF($P$4="Sports",O25,IF($P$4="Travel",P25,IF($P$4="Waterdrops",Q25,IF($P$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="AF25" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D25,IF($P$4="C2 Birds in Flight",E25,IF($P$4="C3 Landscape",F25,IF($P$4="Default Settings",G25,IF($P$4="Birds in Flight",H25,IF($P$4="Birds Perched",I25,IF($P$4="Fireworks",J25,IF($P$4="Landscape",K25,IF($P$4="Macro",L25,IF($P$4="People",M25,IF($P$4="Sports",N25,IF($P$4="Travel",O25,IF($P$4="Waterdrops",P25,IF($P$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AH25" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D25,IF($Q$4="C2 Birds in Flight",E25,IF($Q$4="C3 Landscape",F25,IF($Q$4="Default Settings",G25,IF($Q$4="Androo",H25,IF($Q$4="Birds in Flight",I25,IF($Q$4="Birds Perched",J25,IF($Q$4="Fireworks",K25,IF($Q$4="Landscape",L25,IF($Q$4="Macro",M25,IF($Q$4="People",N25,IF($Q$4="Sports",O25,IF($Q$4="Travel",P25,IF($Q$4="Waterdrops",Q25,IF($Q$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>Off / Off</x:v>
       </x:c>
-      <x:c r="AG25" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D25,IF($Q$4="C2 Birds in Flight",E25,IF($Q$4="C3 Landscape",F25,IF($Q$4="Default Settings",G25,IF($Q$4="Birds in Flight",H25,IF($Q$4="Birds Perched",I25,IF($Q$4="Fireworks",J25,IF($Q$4="Landscape",K25,IF($Q$4="Macro",L25,IF($Q$4="People",M25,IF($Q$4="Sports",N25,IF($Q$4="Travel",O25,IF($Q$4="Waterdrops",P25,IF($Q$4="Wildlife",Q25,""))))))))))))))</x:f>
+      <x:c r="AI25" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D25,IF($R$4="C2 Birds in Flight",E25,IF($R$4="C3 Landscape",F25,IF($R$4="Default Settings",G25,IF($R$4="Androo",H25,IF($R$4="Birds in Flight",I25,IF($R$4="Birds Perched",J25,IF($R$4="Fireworks",K25,IF($R$4="Landscape",L25,IF($R$4="Macro",M25,IF($R$4="People",N25,IF($R$4="Sports",O25,IF($R$4="Travel",P25,IF($R$4="Waterdrops",Q25,IF($R$4="Wildlife",R25,"")))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
     </x:row>
@@ -3186,11 +3347,11 @@
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="L26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="M26" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="M26" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="N26" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
@@ -3203,194 +3364,209 @@
       <x:c r="Q26" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="R26" s="20" t="n">
+      <x:c r="R26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="S26" s="20" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="S26" s="20" t="n">
+      <x:c r="T26" s="20" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="T26" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D26,IF($D$4="C2 Birds in Flight",E26,IF($D$4="C3 Landscape",F26,IF($D$4="Default Settings",G26,IF($D$4="Birds in Flight",H26,IF($D$4="Birds Perched",I26,IF($D$4="Fireworks",J26,IF($D$4="Landscape",K26,IF($D$4="Macro",L26,IF($D$4="People",M26,IF($D$4="Sports",N26,IF($D$4="Travel",O26,IF($D$4="Waterdrops",P26,IF($D$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="U26" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D26,IF($E$4="C2 Birds in Flight",E26,IF($E$4="C3 Landscape",F26,IF($E$4="Default Settings",G26,IF($E$4="Birds in Flight",H26,IF($E$4="Birds Perched",I26,IF($E$4="Fireworks",J26,IF($E$4="Landscape",K26,IF($E$4="Macro",L26,IF($E$4="People",M26,IF($E$4="Sports",N26,IF($E$4="Travel",O26,IF($E$4="Waterdrops",P26,IF($E$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($D$4="C1 Wildlife",D26,IF($D$4="C2 Birds in Flight",E26,IF($D$4="C3 Landscape",F26,IF($D$4="Default Settings",G26,IF($D$4="Androo",H26,IF($D$4="Birds in Flight",I26,IF($D$4="Birds Perched",J26,IF($D$4="Fireworks",K26,IF($D$4="Landscape",L26,IF($D$4="Macro",M26,IF($D$4="People",N26,IF($D$4="Sports",O26,IF($D$4="Travel",P26,IF($D$4="Waterdrops",Q26,IF($D$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="V26" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D26,IF($F$4="C2 Birds in Flight",E26,IF($F$4="C3 Landscape",F26,IF($F$4="Default Settings",G26,IF($F$4="Birds in Flight",H26,IF($F$4="Birds Perched",I26,IF($F$4="Fireworks",J26,IF($F$4="Landscape",K26,IF($F$4="Macro",L26,IF($F$4="People",M26,IF($F$4="Sports",N26,IF($F$4="Travel",O26,IF($F$4="Waterdrops",P26,IF($F$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D26,IF($E$4="C2 Birds in Flight",E26,IF($E$4="C3 Landscape",F26,IF($E$4="Default Settings",G26,IF($E$4="Androo",H26,IF($E$4="Birds in Flight",I26,IF($E$4="Birds Perched",J26,IF($E$4="Fireworks",K26,IF($E$4="Landscape",L26,IF($E$4="Macro",M26,IF($E$4="People",N26,IF($E$4="Sports",O26,IF($E$4="Travel",P26,IF($E$4="Waterdrops",Q26,IF($E$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="W26" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D26,IF($G$4="C2 Birds in Flight",E26,IF($G$4="C3 Landscape",F26,IF($G$4="Default Settings",G26,IF($G$4="Birds in Flight",H26,IF($G$4="Birds Perched",I26,IF($G$4="Fireworks",J26,IF($G$4="Landscape",K26,IF($G$4="Macro",L26,IF($G$4="People",M26,IF($G$4="Sports",N26,IF($G$4="Travel",O26,IF($G$4="Waterdrops",P26,IF($G$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D26,IF($F$4="C2 Birds in Flight",E26,IF($F$4="C3 Landscape",F26,IF($F$4="Default Settings",G26,IF($F$4="Androo",H26,IF($F$4="Birds in Flight",I26,IF($F$4="Birds Perched",J26,IF($F$4="Fireworks",K26,IF($F$4="Landscape",L26,IF($F$4="Macro",M26,IF($F$4="People",N26,IF($F$4="Sports",O26,IF($F$4="Travel",P26,IF($F$4="Waterdrops",Q26,IF($F$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="X26" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D26,IF($H$4="C2 Birds in Flight",E26,IF($H$4="C3 Landscape",F26,IF($H$4="Default Settings",G26,IF($H$4="Birds in Flight",H26,IF($H$4="Birds Perched",I26,IF($H$4="Fireworks",J26,IF($H$4="Landscape",K26,IF($H$4="Macro",L26,IF($H$4="People",M26,IF($H$4="Sports",N26,IF($H$4="Travel",O26,IF($H$4="Waterdrops",P26,IF($H$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($G$4="C1 Wildlife",D26,IF($G$4="C2 Birds in Flight",E26,IF($G$4="C3 Landscape",F26,IF($G$4="Default Settings",G26,IF($G$4="Androo",H26,IF($G$4="Birds in Flight",I26,IF($G$4="Birds Perched",J26,IF($G$4="Fireworks",K26,IF($G$4="Landscape",L26,IF($G$4="Macro",M26,IF($G$4="People",N26,IF($G$4="Sports",O26,IF($G$4="Travel",P26,IF($G$4="Waterdrops",Q26,IF($G$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="Y26" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D26,IF($I$4="C2 Birds in Flight",E26,IF($I$4="C3 Landscape",F26,IF($I$4="Default Settings",G26,IF($I$4="Birds in Flight",H26,IF($I$4="Birds Perched",I26,IF($I$4="Fireworks",J26,IF($I$4="Landscape",K26,IF($I$4="Macro",L26,IF($I$4="People",M26,IF($I$4="Sports",N26,IF($I$4="Travel",O26,IF($I$4="Waterdrops",P26,IF($I$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($H$4="C1 Wildlife",D26,IF($H$4="C2 Birds in Flight",E26,IF($H$4="C3 Landscape",F26,IF($H$4="Default Settings",G26,IF($H$4="Androo",H26,IF($H$4="Birds in Flight",I26,IF($H$4="Birds Perched",J26,IF($H$4="Fireworks",K26,IF($H$4="Landscape",L26,IF($H$4="Macro",M26,IF($H$4="People",N26,IF($H$4="Sports",O26,IF($H$4="Travel",P26,IF($H$4="Waterdrops",Q26,IF($H$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="Z26" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D26,IF($J$4="C2 Birds in Flight",E26,IF($J$4="C3 Landscape",F26,IF($J$4="Default Settings",G26,IF($J$4="Birds in Flight",H26,IF($J$4="Birds Perched",I26,IF($J$4="Fireworks",J26,IF($J$4="Landscape",K26,IF($J$4="Macro",L26,IF($J$4="People",M26,IF($J$4="Sports",N26,IF($J$4="Travel",O26,IF($J$4="Waterdrops",P26,IF($J$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($I$4="C1 Wildlife",D26,IF($I$4="C2 Birds in Flight",E26,IF($I$4="C3 Landscape",F26,IF($I$4="Default Settings",G26,IF($I$4="Androo",H26,IF($I$4="Birds in Flight",I26,IF($I$4="Birds Perched",J26,IF($I$4="Fireworks",K26,IF($I$4="Landscape",L26,IF($I$4="Macro",M26,IF($I$4="People",N26,IF($I$4="Sports",O26,IF($I$4="Travel",P26,IF($I$4="Waterdrops",Q26,IF($I$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AA26" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D26,IF($K$4="C2 Birds in Flight",E26,IF($K$4="C3 Landscape",F26,IF($K$4="Default Settings",G26,IF($K$4="Birds in Flight",H26,IF($K$4="Birds Perched",I26,IF($K$4="Fireworks",J26,IF($K$4="Landscape",K26,IF($K$4="Macro",L26,IF($K$4="People",M26,IF($K$4="Sports",N26,IF($K$4="Travel",O26,IF($K$4="Waterdrops",P26,IF($K$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D26,IF($J$4="C2 Birds in Flight",E26,IF($J$4="C3 Landscape",F26,IF($J$4="Default Settings",G26,IF($J$4="Androo",H26,IF($J$4="Birds in Flight",I26,IF($J$4="Birds Perched",J26,IF($J$4="Fireworks",K26,IF($J$4="Landscape",L26,IF($J$4="Macro",M26,IF($J$4="People",N26,IF($J$4="Sports",O26,IF($J$4="Travel",P26,IF($J$4="Waterdrops",Q26,IF($J$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AB26" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D26,IF($L$4="C2 Birds in Flight",E26,IF($L$4="C3 Landscape",F26,IF($L$4="Default Settings",G26,IF($L$4="Birds in Flight",H26,IF($L$4="Birds Perched",I26,IF($L$4="Fireworks",J26,IF($L$4="Landscape",K26,IF($L$4="Macro",L26,IF($L$4="People",M26,IF($L$4="Sports",N26,IF($L$4="Travel",O26,IF($L$4="Waterdrops",P26,IF($L$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D26,IF($K$4="C2 Birds in Flight",E26,IF($K$4="C3 Landscape",F26,IF($K$4="Default Settings",G26,IF($K$4="Androo",H26,IF($K$4="Birds in Flight",I26,IF($K$4="Birds Perched",J26,IF($K$4="Fireworks",K26,IF($K$4="Landscape",L26,IF($K$4="Macro",M26,IF($K$4="People",N26,IF($K$4="Sports",O26,IF($K$4="Travel",P26,IF($K$4="Waterdrops",Q26,IF($K$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AC26" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D26,IF($L$4="C2 Birds in Flight",E26,IF($L$4="C3 Landscape",F26,IF($L$4="Default Settings",G26,IF($L$4="Androo",H26,IF($L$4="Birds in Flight",I26,IF($L$4="Birds Perched",J26,IF($L$4="Fireworks",K26,IF($L$4="Landscape",L26,IF($L$4="Macro",M26,IF($L$4="People",N26,IF($L$4="Sports",O26,IF($L$4="Travel",P26,IF($L$4="Waterdrops",Q26,IF($L$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD26" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D26,IF($M$4="C2 Birds in Flight",E26,IF($M$4="C3 Landscape",F26,IF($M$4="Default Settings",G26,IF($M$4="Androo",H26,IF($M$4="Birds in Flight",I26,IF($M$4="Birds Perched",J26,IF($M$4="Fireworks",K26,IF($M$4="Landscape",L26,IF($M$4="Macro",M26,IF($M$4="People",N26,IF($M$4="Sports",O26,IF($M$4="Travel",P26,IF($M$4="Waterdrops",Q26,IF($M$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="AC26" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D26,IF($M$4="C2 Birds in Flight",E26,IF($M$4="C3 Landscape",F26,IF($M$4="Default Settings",G26,IF($M$4="Birds in Flight",H26,IF($M$4="Birds Perched",I26,IF($M$4="Fireworks",J26,IF($M$4="Landscape",K26,IF($M$4="Macro",L26,IF($M$4="People",M26,IF($M$4="Sports",N26,IF($M$4="Travel",O26,IF($M$4="Waterdrops",P26,IF($M$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AD26" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D26,IF($N$4="C2 Birds in Flight",E26,IF($N$4="C3 Landscape",F26,IF($N$4="Default Settings",G26,IF($N$4="Birds in Flight",H26,IF($N$4="Birds Perched",I26,IF($N$4="Fireworks",J26,IF($N$4="Landscape",K26,IF($N$4="Macro",L26,IF($N$4="People",M26,IF($N$4="Sports",N26,IF($N$4="Travel",O26,IF($N$4="Waterdrops",P26,IF($N$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="AE26" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D26,IF($O$4="C2 Birds in Flight",E26,IF($O$4="C3 Landscape",F26,IF($O$4="Default Settings",G26,IF($O$4="Birds in Flight",H26,IF($O$4="Birds Perched",I26,IF($O$4="Fireworks",J26,IF($O$4="Landscape",K26,IF($O$4="Macro",L26,IF($O$4="People",M26,IF($O$4="Sports",N26,IF($O$4="Travel",O26,IF($O$4="Waterdrops",P26,IF($O$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($N$4="C1 Wildlife",D26,IF($N$4="C2 Birds in Flight",E26,IF($N$4="C3 Landscape",F26,IF($N$4="Default Settings",G26,IF($N$4="Androo",H26,IF($N$4="Birds in Flight",I26,IF($N$4="Birds Perched",J26,IF($N$4="Fireworks",K26,IF($N$4="Landscape",L26,IF($N$4="Macro",M26,IF($N$4="People",N26,IF($N$4="Sports",O26,IF($N$4="Travel",P26,IF($N$4="Waterdrops",Q26,IF($N$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AF26" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D26,IF($P$4="C2 Birds in Flight",E26,IF($P$4="C3 Landscape",F26,IF($P$4="Default Settings",G26,IF($P$4="Birds in Flight",H26,IF($P$4="Birds Perched",I26,IF($P$4="Fireworks",J26,IF($P$4="Landscape",K26,IF($P$4="Macro",L26,IF($P$4="People",M26,IF($P$4="Sports",N26,IF($P$4="Travel",O26,IF($P$4="Waterdrops",P26,IF($P$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D26,IF($O$4="C2 Birds in Flight",E26,IF($O$4="C3 Landscape",F26,IF($O$4="Default Settings",G26,IF($O$4="Androo",H26,IF($O$4="Birds in Flight",I26,IF($O$4="Birds Perched",J26,IF($O$4="Fireworks",K26,IF($O$4="Landscape",L26,IF($O$4="Macro",M26,IF($O$4="People",N26,IF($O$4="Sports",O26,IF($O$4="Travel",P26,IF($O$4="Waterdrops",Q26,IF($O$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AG26" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D26,IF($Q$4="C2 Birds in Flight",E26,IF($Q$4="C3 Landscape",F26,IF($Q$4="Default Settings",G26,IF($Q$4="Birds in Flight",H26,IF($Q$4="Birds Perched",I26,IF($Q$4="Fireworks",J26,IF($Q$4="Landscape",K26,IF($Q$4="Macro",L26,IF($Q$4="People",M26,IF($Q$4="Sports",N26,IF($Q$4="Travel",O26,IF($Q$4="Waterdrops",P26,IF($Q$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D26,IF($P$4="C2 Birds in Flight",E26,IF($P$4="C3 Landscape",F26,IF($P$4="Default Settings",G26,IF($P$4="Androo",H26,IF($P$4="Birds in Flight",I26,IF($P$4="Birds Perched",J26,IF($P$4="Fireworks",K26,IF($P$4="Landscape",L26,IF($P$4="Macro",M26,IF($P$4="People",N26,IF($P$4="Sports",O26,IF($P$4="Travel",P26,IF($P$4="Waterdrops",Q26,IF($P$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AH26" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D26,IF($Q$4="C2 Birds in Flight",E26,IF($Q$4="C3 Landscape",F26,IF($Q$4="Default Settings",G26,IF($Q$4="Androo",H26,IF($Q$4="Birds in Flight",I26,IF($Q$4="Birds Perched",J26,IF($Q$4="Fireworks",K26,IF($Q$4="Landscape",L26,IF($Q$4="Macro",M26,IF($Q$4="People",N26,IF($Q$4="Sports",O26,IF($Q$4="Travel",P26,IF($Q$4="Waterdrops",Q26,IF($Q$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AI26" s="38" t="str">
+        <x:f>IF($R$4="C1 Wildlife",D26,IF($R$4="C2 Birds in Flight",E26,IF($R$4="C3 Landscape",F26,IF($R$4="Default Settings",G26,IF($R$4="Androo",H26,IF($R$4="Birds in Flight",I26,IF($R$4="Birds Perched",J26,IF($R$4="Fireworks",K26,IF($R$4="Landscape",L26,IF($R$4="Macro",M26,IF($R$4="People",N26,IF($R$4="Sports",O26,IF($R$4="Travel",P26,IF($R$4="Waterdrops",Q26,IF($R$4="Wildlife",R26,"")))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D26">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
-      <x:formula>$T7</x:formula>
+      <x:formula>$U7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E7:E26">
     <x:cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
-      <x:formula>$U7</x:formula>
+      <x:formula>$V7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F7:F26">
     <x:cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
-      <x:formula>$V7</x:formula>
+      <x:formula>$W7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="G7:G26">
     <x:cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
-      <x:formula>$W7</x:formula>
+      <x:formula>$X7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="H7:H26">
     <x:cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
-      <x:formula>$X7</x:formula>
+      <x:formula>$Y7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="I7:I26">
     <x:cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
-      <x:formula>$Y7</x:formula>
+      <x:formula>$Z7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="J7:J26">
     <x:cfRule type="cellIs" dxfId="6" priority="7" operator="notEqual">
-      <x:formula>$Z7</x:formula>
+      <x:formula>$AA7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="K7:K26">
     <x:cfRule type="cellIs" dxfId="7" priority="8" operator="notEqual">
-      <x:formula>$AA7</x:formula>
+      <x:formula>$AB7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="L7:L26">
     <x:cfRule type="cellIs" dxfId="8" priority="9" operator="notEqual">
-      <x:formula>$AB7</x:formula>
+      <x:formula>$AC7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="M7:M26">
     <x:cfRule type="cellIs" dxfId="9" priority="10" operator="notEqual">
-      <x:formula>$AC7</x:formula>
+      <x:formula>$AD7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="N7:N26">
     <x:cfRule type="cellIs" dxfId="10" priority="11" operator="notEqual">
-      <x:formula>$AD7</x:formula>
+      <x:formula>$AE7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="O7:O26">
     <x:cfRule type="cellIs" dxfId="11" priority="12" operator="notEqual">
-      <x:formula>$AE7</x:formula>
+      <x:formula>$AF7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="P7:P26">
     <x:cfRule type="cellIs" dxfId="12" priority="13" operator="notEqual">
-      <x:formula>$AF7</x:formula>
+      <x:formula>$AG7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="Q7:Q26">
     <x:cfRule type="cellIs" dxfId="13" priority="14" operator="notEqual">
-      <x:formula>$AG7</x:formula>
+      <x:formula>$AH7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:Q26">
-    <x:cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Not Used"/>
-    <x:cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+  <x:conditionalFormatting sqref="R7:R26">
+    <x:cfRule type="cellIs" dxfId="14" priority="15" operator="notEqual">
+      <x:formula>$AI7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="D7:R26">
+    <x:cfRule type="containsText" dxfId="15" priority="16" operator="containsText" text="Not Used"/>
+    <x:cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <x:formula>"—"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="14">
+  <x:dataValidations count="15">
     <x:dataValidation type="list" sqref="D4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="H4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="I4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="K4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="L4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="M4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="N4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="O4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="P4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="Q4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="R4">
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rbe9a3ada33a24cdf"/>
+  <x:drawing ns1:id="R067a38a0f2224c49"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R0f96c99050124d18"/>
+    <x:tablePart ns1:id="Rf27bc0303c6045ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3421,6 +3597,7 @@
     <x:col min="20" max="20" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="21" max="21" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="22" max="22" width="0.2199999988079071" hidden="1" customWidth="1"/>
+    <x:col min="23" max="23" width="0.2199999988079071" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -3430,9 +3607,9 @@
       <x:c r="B1" s="43"/>
       <x:c r="C1" s="43"/>
       <x:c r="D1" s="43"/>
-      <x:c r="T1" s="38"/>
       <x:c r="U1" s="38"/>
       <x:c r="V1" s="38"/>
+      <x:c r="W1" s="38"/>
     </x:row>
     <x:row r="2" hidden="0">
       <x:c r="A2" s="6" t="str">
@@ -3447,9 +3624,9 @@
       <x:c r="D2" s="6" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
-      <x:c r="T2" s="38"/>
       <x:c r="U2" s="38"/>
       <x:c r="V2" s="38"/>
+      <x:c r="W2" s="38"/>
     </x:row>
     <x:row r="3" hidden="0">
       <x:c r="A3" s="15" t="str">
@@ -3464,15 +3641,15 @@
       <x:c r="D3" s="17" t="str">
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="T3" s="38" t="str">
+      <x:c r="U3" s="38" t="str">
         <x:f>B3</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="U3" s="38" t="str">
+      <x:c r="V3" s="38" t="str">
         <x:f>C3</x:f>
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="V3" s="38" t="str">
+      <x:c r="W3" s="38" t="str">
         <x:f>D3</x:f>
         <x:v>Av</x:v>
       </x:c>
@@ -3490,15 +3667,15 @@
       <x:c r="D4" s="17" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="T4" s="38" t="str">
+      <x:c r="U4" s="38" t="str">
         <x:f>B4</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="U4" s="38" t="str">
+      <x:c r="V4" s="38" t="str">
         <x:f>C4</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="V4" s="38" t="str">
+      <x:c r="W4" s="38" t="str">
         <x:f>D4</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
@@ -3516,15 +3693,15 @@
       <x:c r="D5" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="T5" s="38" t="str">
+      <x:c r="U5" s="38" t="str">
         <x:f>B5</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="U5" s="38" t="str">
+      <x:c r="V5" s="38" t="str">
         <x:f>C5</x:f>
         <x:v>1/2500 sec.</x:v>
       </x:c>
-      <x:c r="V5" s="38" t="str">
+      <x:c r="W5" s="38" t="str">
         <x:f>D5</x:f>
         <x:v>Auto</x:v>
       </x:c>
@@ -3542,15 +3719,15 @@
       <x:c r="D6" s="17" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="T6" s="38" t="str">
+      <x:c r="U6" s="38" t="str">
         <x:f>B6</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="U6" s="38" t="str">
+      <x:c r="V6" s="38" t="str">
         <x:f>C6</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="V6" s="38" t="str">
+      <x:c r="W6" s="38" t="str">
         <x:f>D6</x:f>
         <x:v>EFCS</x:v>
       </x:c>
@@ -3568,15 +3745,15 @@
       <x:c r="D7" s="17" t="str">
         <x:v>f/9</x:v>
       </x:c>
-      <x:c r="T7" s="38" t="str">
+      <x:c r="U7" s="38" t="str">
         <x:f>B7</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="U7" s="38" t="str">
+      <x:c r="V7" s="38" t="str">
         <x:f>C7</x:f>
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="V7" s="38" t="str">
+      <x:c r="W7" s="38" t="str">
         <x:f>D7</x:f>
         <x:v>f/9</x:v>
       </x:c>
@@ -3594,15 +3771,15 @@
       <x:c r="D8" s="17" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="T8" s="38" t="str">
+      <x:c r="U8" s="38" t="str">
         <x:f>B8</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="U8" s="38" t="str">
+      <x:c r="V8" s="38" t="str">
         <x:f>C8</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="V8" s="38" t="n">
+      <x:c r="W8" s="38" t="n">
         <x:f>D8</x:f>
         <x:v>100</x:v>
       </x:c>
@@ -3620,15 +3797,15 @@
       <x:c r="D9" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="T9" s="38" t="n">
+      <x:c r="U9" s="38" t="n">
         <x:f>B9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U9" s="38" t="str">
+      <x:c r="V9" s="38" t="str">
         <x:f>C9</x:f>
         <x:v>0 starting point</x:v>
       </x:c>
-      <x:c r="V9" s="38" t="n">
+      <x:c r="W9" s="38" t="n">
         <x:f>D9</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3646,15 +3823,15 @@
       <x:c r="D10" s="17" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="T10" s="38" t="str">
+      <x:c r="U10" s="38" t="str">
         <x:f>B10</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="U10" s="38" t="str">
+      <x:c r="V10" s="38" t="str">
         <x:f>C10</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="V10" s="38" t="str">
+      <x:c r="W10" s="38" t="str">
         <x:f>D10</x:f>
         <x:v>One-Shot AF</x:v>
       </x:c>
@@ -3672,15 +3849,15 @@
       <x:c r="D11" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="T11" s="38" t="str">
+      <x:c r="U11" s="38" t="str">
         <x:f>B11</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="U11" s="38" t="str">
+      <x:c r="V11" s="38" t="str">
         <x:f>C11</x:f>
         <x:v>Case 4</x:v>
       </x:c>
-      <x:c r="V11" s="38" t="str">
+      <x:c r="W11" s="38" t="str">
         <x:f>D11</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3698,15 +3875,15 @@
       <x:c r="D12" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="T12" s="38" t="n">
+      <x:c r="U12" s="38" t="n">
         <x:f>B12</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="U12" s="38" t="n">
+      <x:c r="V12" s="38" t="n">
         <x:f>C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V12" s="38" t="str">
+      <x:c r="W12" s="38" t="str">
         <x:f>D12</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3724,15 +3901,15 @@
       <x:c r="D13" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="T13" s="38" t="str">
+      <x:c r="U13" s="38" t="str">
         <x:f>B13</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="U13" s="38" t="str">
+      <x:c r="V13" s="38" t="str">
         <x:f>C13</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="V13" s="38" t="str">
+      <x:c r="W13" s="38" t="str">
         <x:f>D13</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3750,15 +3927,15 @@
       <x:c r="D14" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="T14" s="38" t="str">
+      <x:c r="U14" s="38" t="str">
         <x:f>B14</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="U14" s="38" t="str">
+      <x:c r="V14" s="38" t="str">
         <x:f>C14</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="V14" s="38" t="str">
+      <x:c r="W14" s="38" t="str">
         <x:f>D14</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3776,15 +3953,15 @@
       <x:c r="D15" s="17" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="T15" s="38" t="str">
+      <x:c r="U15" s="38" t="str">
         <x:f>B15</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="U15" s="38" t="str">
+      <x:c r="V15" s="38" t="str">
         <x:f>C15</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="V15" s="38" t="str">
+      <x:c r="W15" s="38" t="str">
         <x:f>D15</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
@@ -3802,15 +3979,15 @@
       <x:c r="D16" s="17" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="T16" s="38" t="str">
+      <x:c r="U16" s="38" t="str">
         <x:f>B16</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="U16" s="38" t="str">
+      <x:c r="V16" s="38" t="str">
         <x:f>C16</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="V16" s="38" t="str">
+      <x:c r="W16" s="38" t="str">
         <x:f>D16</x:f>
         <x:v>None</x:v>
       </x:c>
@@ -3828,15 +4005,15 @@
       <x:c r="D17" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="T17" s="38" t="str">
+      <x:c r="U17" s="38" t="str">
         <x:f>B17</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="U17" s="38" t="str">
+      <x:c r="V17" s="38" t="str">
         <x:f>C17</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="V17" s="38" t="str">
+      <x:c r="W17" s="38" t="str">
         <x:f>D17</x:f>
         <x:v>Disable</x:v>
       </x:c>
@@ -3854,15 +4031,15 @@
       <x:c r="D18" s="17" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="T18" s="38" t="str">
+      <x:c r="U18" s="38" t="str">
         <x:f>B18</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="U18" s="38" t="str">
+      <x:c r="V18" s="38" t="str">
         <x:f>C18</x:f>
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="V18" s="38" t="str">
+      <x:c r="W18" s="38" t="str">
         <x:f>D18</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
@@ -3880,15 +4057,15 @@
       <x:c r="D19" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="T19" s="38" t="str">
+      <x:c r="U19" s="38" t="str">
         <x:f>B19</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="U19" s="38" t="str">
+      <x:c r="V19" s="38" t="str">
         <x:f>C19</x:f>
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="V19" s="38" t="str">
+      <x:c r="W19" s="38" t="str">
         <x:f>D19</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3906,15 +4083,15 @@
       <x:c r="D20" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="T20" s="38" t="str">
+      <x:c r="U20" s="38" t="str">
         <x:f>B20</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="U20" s="38" t="str">
+      <x:c r="V20" s="38" t="str">
         <x:f>C20</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="V20" s="38" t="str">
+      <x:c r="W20" s="38" t="str">
         <x:f>D20</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
@@ -3932,15 +4109,15 @@
       <x:c r="D21" s="17" t="str">
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="T21" s="38" t="str">
+      <x:c r="U21" s="38" t="str">
         <x:f>B21</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="U21" s="38" t="str">
+      <x:c r="V21" s="38" t="str">
         <x:f>C21</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="V21" s="38" t="str">
+      <x:c r="W21" s="38" t="str">
         <x:f>D21</x:f>
         <x:v>On / On</x:v>
       </x:c>
@@ -3958,15 +4135,15 @@
       <x:c r="D22" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="T22" s="38" t="str">
+      <x:c r="U22" s="38" t="str">
         <x:f>B22</x:f>
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="U22" s="38" t="str">
+      <x:c r="V22" s="38" t="str">
         <x:f>C22</x:f>
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="V22" s="38" t="str">
+      <x:c r="W22" s="38" t="str">
         <x:f>D22</x:f>
         <x:v>Disable</x:v>
       </x:c>
@@ -3976,23 +4153,23 @@
     <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B3:B22">
-    <x:cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
-      <x:formula>$T3</x:formula>
+    <x:cfRule type="cellIs" dxfId="17" priority="1" operator="notEqual">
+      <x:formula>$U3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="C3:C22">
-    <x:cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
-      <x:formula>$U3</x:formula>
+    <x:cfRule type="cellIs" dxfId="18" priority="2" operator="notEqual">
+      <x:formula>$V3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="D3:D22">
-    <x:cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
-      <x:formula>$V3</x:formula>
+    <x:cfRule type="cellIs" dxfId="19" priority="3" operator="notEqual">
+      <x:formula>$W3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R81d79827fe37415a"/>
+    <x:tablePart ns1:id="Rbf3d86e136ad4681"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R824ee18e150241cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R28d78cec9aee4da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R2afe67f6ee2840ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R14fd38c3c264479f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -442,13 +442,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="576ca5da-cf47-4658-9a49-8a2d7b60f4c2"/>
+        <xdr:cNvPr id="1" name="054b8a2c-517e-4233-a27b-2ea6128ec031"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1df47e7eae0a4738"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6443544de43e4be6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3564,9 +3564,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R067a38a0f2224c49"/>
+  <x:drawing ns1:id="R88e47254ab084a2f"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rf27bc0303c6045ae"/>
+    <x:tablePart ns1:id="Rd5a22c5ba6be4cab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4169,7 +4169,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rbf3d86e136ad4681"/>
+    <x:tablePart ns1:id="R17fa0bab26a34961"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R2afe67f6ee2840ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R14fd38c3c264479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R012c929af9a24e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="Rb8d9112ab9d44261"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -442,13 +442,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="054b8a2c-517e-4233-a27b-2ea6128ec031"/>
+        <xdr:cNvPr id="1" name="66be9fb7-2aef-4427-8833-e1af377ef603"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6443544de43e4be6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5b9fb84365864e3f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -869,19 +869,19 @@
         <x:v>Camera Defaults + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="H5" s="37" t="str">
-        <x:v>—</x:v>
+        <x:v>No Cx + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="I5" s="37" t="str">
-        <x:v>C2 Birds in Flight + AF Case</x:v>
+        <x:v>C2 Birds in Flight + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="J5" s="37" t="str">
-        <x:v>C1 Wildlife + AF Case</x:v>
+        <x:v>C1 Wildlife + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="K5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="L5" s="37" t="str">
-        <x:v>C3 Landscape</x:v>
+        <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="M5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
@@ -893,13 +893,13 @@
         <x:v>C2 Birds in Flight + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="P5" s="37" t="str">
-        <x:v>C3 Landscape</x:v>
+        <x:v>C3 Landscape + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="Q5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="R5" s="37" t="str">
-        <x:v>C1 Wildlife + AF Case</x:v>
+        <x:v>C1 Wildlife + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="U5" s="38"/>
       <x:c r="V5" s="38"/>
@@ -3564,9 +3564,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R88e47254ab084a2f"/>
+  <x:drawing ns1:id="R927c036383c9451f"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rd5a22c5ba6be4cab"/>
+    <x:tablePart ns1:id="R9fa21415ad914f34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4169,7 +4169,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R17fa0bab26a34961"/>
+    <x:tablePart ns1:id="R0fb18e4be6514425"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R012c929af9a24e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="Rb8d9112ab9d44261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R91b3e431b9e444b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R6d041c6ad3c0481b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -228,17 +228,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="20">
-    <x:dxf>
-      <x:font>
-        <x:color rgb="FF000000"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFFC98"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
+  <x:dxfs count="19">
     <x:dxf>
       <x:font>
         <x:color rgb="FF000000"/>
@@ -442,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="66be9fb7-2aef-4427-8833-e1af377ef603"/>
+        <xdr:cNvPr id="1" name="646283c4-0ec3-4e01-8dc0-89e33c3f8925"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5b9fb84365864e3f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc056bdc970214e17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -463,9 +453,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:T26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:T26"/>
-  <x:tableColumns count="20">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:S26"/>
+  <x:tableColumns count="19">
     <x:tableColumn id="1" name="Menu Location"/>
     <x:tableColumn id="2" name="Best or Quick Access"/>
     <x:tableColumn id="3" name="Setting"/>
@@ -473,19 +463,18 @@
     <x:tableColumn id="5" name="C2 Birds in Flight"/>
     <x:tableColumn id="6" name="C3 Landscape"/>
     <x:tableColumn id="7" name="Default Settings"/>
-    <x:tableColumn id="8" name="Androo"/>
-    <x:tableColumn id="9" name="Birds in Flight"/>
-    <x:tableColumn id="10" name="Birds Perched"/>
-    <x:tableColumn id="11" name="Fireworks"/>
-    <x:tableColumn id="12" name="Landscape"/>
-    <x:tableColumn id="13" name="Macro"/>
-    <x:tableColumn id="14" name="People"/>
-    <x:tableColumn id="15" name="Sports"/>
-    <x:tableColumn id="16" name="Travel"/>
-    <x:tableColumn id="17" name="Waterdrops"/>
-    <x:tableColumn id="18" name="Wildlife"/>
-    <x:tableColumn id="19" name="Card Order"/>
-    <x:tableColumn id="20" name="Rapid Setup Order"/>
+    <x:tableColumn id="8" name="Birds in Flight"/>
+    <x:tableColumn id="9" name="Birds Perched"/>
+    <x:tableColumn id="10" name="Fireworks"/>
+    <x:tableColumn id="11" name="Landscape"/>
+    <x:tableColumn id="12" name="Macro"/>
+    <x:tableColumn id="13" name="People"/>
+    <x:tableColumn id="14" name="Sports"/>
+    <x:tableColumn id="15" name="Travel"/>
+    <x:tableColumn id="16" name="Waterdrops"/>
+    <x:tableColumn id="17" name="Wildlife"/>
+    <x:tableColumn id="18" name="Card Order"/>
+    <x:tableColumn id="19" name="Rapid Setup Order"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -699,6 +688,7 @@
 <x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="20" max="20" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="21" max="21" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="22" max="22" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="23" max="23" width="0.2199999988079071" hidden="1" customWidth="1"/>
@@ -712,8 +702,6 @@
     <x:col min="31" max="31" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="32" max="32" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="33" max="33" width="0.2199999988079071" hidden="1" customWidth="1"/>
-    <x:col min="34" max="34" width="0.2199999988079071" hidden="1" customWidth="1"/>
-    <x:col min="35" max="35" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="1" max="1" width="12.5600004196167" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.890000343322754" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.890000343322754" hidden="0" customWidth="1"/>
@@ -731,12 +719,12 @@
     <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="12" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="T1" s="38"/>
       <x:c r="U1" s="38"/>
       <x:c r="V1" s="38"/>
       <x:c r="W1" s="38"/>
@@ -750,10 +738,9 @@
       <x:c r="AE1" s="38"/>
       <x:c r="AF1" s="38"/>
       <x:c r="AG1" s="38"/>
-      <x:c r="AH1" s="38"/>
-      <x:c r="AI1" s="38"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
+      <x:c r="T2" s="38"/>
       <x:c r="U2" s="38"/>
       <x:c r="V2" s="38"/>
       <x:c r="W2" s="38"/>
@@ -767,10 +754,9 @@
       <x:c r="AE2" s="38"/>
       <x:c r="AF2" s="38"/>
       <x:c r="AG2" s="38"/>
-      <x:c r="AH2" s="38"/>
-      <x:c r="AI2" s="38"/>
     </x:row>
     <x:row r="3" ht="33" customHeight="1">
+      <x:c r="T3" s="38"/>
       <x:c r="U3" s="38"/>
       <x:c r="V3" s="38"/>
       <x:c r="W3" s="38"/>
@@ -784,8 +770,6 @@
       <x:c r="AE3" s="38"/>
       <x:c r="AF3" s="38"/>
       <x:c r="AG3" s="38"/>
-      <x:c r="AH3" s="38"/>
-      <x:c r="AI3" s="38"/>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="24" t="str">
@@ -804,38 +788,36 @@
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="H4" s="28" t="str">
-        <x:v>Androo</x:v>
+        <x:v>Birds in Flight</x:v>
       </x:c>
       <x:c r="I4" s="28" t="str">
-        <x:v>Birds in Flight</x:v>
+        <x:v>Birds Perched</x:v>
       </x:c>
       <x:c r="J4" s="28" t="str">
-        <x:v>Birds Perched</x:v>
+        <x:v>Fireworks</x:v>
       </x:c>
       <x:c r="K4" s="28" t="str">
-        <x:v>Fireworks</x:v>
+        <x:v>Landscape</x:v>
       </x:c>
       <x:c r="L4" s="28" t="str">
-        <x:v>Landscape</x:v>
+        <x:v>Macro</x:v>
       </x:c>
       <x:c r="M4" s="28" t="str">
-        <x:v>Macro</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="N4" s="28" t="str">
-        <x:v>People</x:v>
+        <x:v>Sports</x:v>
       </x:c>
       <x:c r="O4" s="28" t="str">
-        <x:v>Sports</x:v>
+        <x:v>Travel</x:v>
       </x:c>
       <x:c r="P4" s="28" t="str">
-        <x:v>Travel</x:v>
+        <x:v>Waterdrops</x:v>
       </x:c>
       <x:c r="Q4" s="28" t="str">
-        <x:v>Waterdrops</x:v>
-      </x:c>
-      <x:c r="R4" s="28" t="str">
         <x:v>Wildlife</x:v>
       </x:c>
+      <x:c r="T4" s="38"/>
       <x:c r="U4" s="38"/>
       <x:c r="V4" s="38"/>
       <x:c r="W4" s="38"/>
@@ -849,8 +831,6 @@
       <x:c r="AE4" s="38"/>
       <x:c r="AF4" s="38"/>
       <x:c r="AG4" s="38"/>
-      <x:c r="AH4" s="38"/>
-      <x:c r="AI4" s="38"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="33" t="str">
@@ -869,38 +849,36 @@
         <x:v>Camera Defaults + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="H5" s="37" t="str">
-        <x:v>No Cx + AF Case + SWITCH</x:v>
+        <x:v>C2 Birds in Flight + AF Case</x:v>
       </x:c>
       <x:c r="I5" s="37" t="str">
-        <x:v>C2 Birds in Flight + AF Case + SWITCH</x:v>
+        <x:v>C1 Wildlife + AF Case</x:v>
       </x:c>
       <x:c r="J5" s="37" t="str">
-        <x:v>C1 Wildlife + AF Case + SWITCH</x:v>
+        <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="K5" s="37" t="str">
-        <x:v>C3 Landscape + SWITCH</x:v>
+        <x:v>C3 Landscape</x:v>
       </x:c>
       <x:c r="L5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="M5" s="37" t="str">
+        <x:v>C1 Wildlife + SWITCH + AF Case</x:v>
+      </x:c>
+      <x:c r="N5" s="37" t="str">
+        <x:v>C2 Birds in Flight + SWITCH + AF Case</x:v>
+      </x:c>
+      <x:c r="O5" s="37" t="str">
+        <x:v>C3 Landscape</x:v>
+      </x:c>
+      <x:c r="P5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
-      <x:c r="N5" s="37" t="str">
-        <x:v>C1 Wildlife + SWITCH + AF Case</x:v>
-      </x:c>
-      <x:c r="O5" s="37" t="str">
-        <x:v>C2 Birds in Flight + SWITCH + AF Case</x:v>
-      </x:c>
-      <x:c r="P5" s="37" t="str">
-        <x:v>C3 Landscape + AF Case + SWITCH</x:v>
-      </x:c>
       <x:c r="Q5" s="37" t="str">
-        <x:v>C3 Landscape + SWITCH</x:v>
-      </x:c>
-      <x:c r="R5" s="37" t="str">
-        <x:v>C1 Wildlife + AF Case + SWITCH</x:v>
-      </x:c>
+        <x:v>C1 Wildlife + AF Case</x:v>
+      </x:c>
+      <x:c r="T5" s="38"/>
       <x:c r="U5" s="38"/>
       <x:c r="V5" s="38"/>
       <x:c r="W5" s="38"/>
@@ -914,8 +892,6 @@
       <x:c r="AE5" s="38"/>
       <x:c r="AF5" s="38"/>
       <x:c r="AG5" s="38"/>
-      <x:c r="AH5" s="38"/>
-      <x:c r="AI5" s="38"/>
     </x:row>
     <x:row r="6" hidden="0">
       <x:c r="A6" s="5" t="str">
@@ -940,44 +916,42 @@
         <x:v>Default Settings</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
-        <x:v>Androo</x:v>
+        <x:v>Birds in Flight</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str">
-        <x:v>Birds in Flight</x:v>
+        <x:v>Birds Perched</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
-        <x:v>Birds Perched</x:v>
+        <x:v>Fireworks</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str">
-        <x:v>Fireworks</x:v>
-      </x:c>
-      <x:c r="L6" s="6" t="str">
         <x:v>Landscape</x:v>
       </x:c>
-      <x:c r="M6" s="8" t="str">
+      <x:c r="L6" s="8" t="str">
         <x:v>Macro</x:v>
       </x:c>
-      <x:c r="N6" s="6" t="str">
+      <x:c r="M6" s="6" t="str">
         <x:v>People</x:v>
       </x:c>
+      <x:c r="N6" s="8" t="str">
+        <x:v>Sports</x:v>
+      </x:c>
       <x:c r="O6" s="8" t="str">
-        <x:v>Sports</x:v>
+        <x:v>Travel</x:v>
       </x:c>
       <x:c r="P6" s="8" t="str">
-        <x:v>Travel</x:v>
-      </x:c>
-      <x:c r="Q6" s="8" t="str">
         <x:v>Waterdrops</x:v>
       </x:c>
+      <x:c r="Q6" s="6" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
       <x:c r="R6" s="6" t="str">
-        <x:v>Wildlife</x:v>
+        <x:v>Card Order</x:v>
       </x:c>
       <x:c r="S6" s="6" t="str">
-        <x:v>Card Order</x:v>
-      </x:c>
-      <x:c r="T6" s="6" t="str">
         <x:v>Rapid Setup Order</x:v>
       </x:c>
+      <x:c r="T6" s="38"/>
       <x:c r="U6" s="38"/>
       <x:c r="V6" s="38"/>
       <x:c r="W6" s="38"/>
@@ -991,8 +965,6 @@
       <x:c r="AE6" s="38"/>
       <x:c r="AF6" s="38"/>
       <x:c r="AG6" s="38"/>
-      <x:c r="AH6" s="38"/>
-      <x:c r="AI6" s="38"/>
     </x:row>
     <x:row r="7" hidden="0">
       <x:c r="A7" s="12" t="str">
@@ -1017,102 +989,95 @@
         <x:v>Fv</x:v>
       </x:c>
       <x:c r="H7" s="17" t="str">
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="str">
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="I7" s="17" t="str">
-        <x:v>Tv</x:v>
-      </x:c>
       <x:c r="J7" s="17" t="str">
-        <x:v>Fv</x:v>
+        <x:v>Manual</x:v>
       </x:c>
       <x:c r="K7" s="17" t="str">
-        <x:v>Manual</x:v>
+        <x:v>Av</x:v>
       </x:c>
       <x:c r="L7" s="17" t="str">
         <x:v>Av</x:v>
       </x:c>
       <x:c r="M7" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="N7" s="17" t="str">
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="P7" s="17" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="Q7" s="17" t="str">
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="R7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S7" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="T7" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D7,IF($D$4="C2 Birds in Flight",E7,IF($D$4="C3 Landscape",F7,IF($D$4="Default Settings",G7,IF($D$4="Birds in Flight",H7,IF($D$4="Birds Perched",I7,IF($D$4="Fireworks",J7,IF($D$4="Landscape",K7,IF($D$4="Macro",L7,IF($D$4="People",M7,IF($D$4="Sports",N7,IF($D$4="Travel",O7,IF($D$4="Waterdrops",P7,IF($D$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Fv</x:v>
+      </x:c>
+      <x:c r="U7" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D7,IF($E$4="C2 Birds in Flight",E7,IF($E$4="C3 Landscape",F7,IF($E$4="Default Settings",G7,IF($E$4="Birds in Flight",H7,IF($E$4="Birds Perched",I7,IF($E$4="Fireworks",J7,IF($E$4="Landscape",K7,IF($E$4="Macro",L7,IF($E$4="People",M7,IF($E$4="Sports",N7,IF($E$4="Travel",O7,IF($E$4="Waterdrops",P7,IF($E$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="V7" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D7,IF($F$4="C2 Birds in Flight",E7,IF($F$4="C3 Landscape",F7,IF($F$4="Default Settings",G7,IF($F$4="Birds in Flight",H7,IF($F$4="Birds Perched",I7,IF($F$4="Fireworks",J7,IF($F$4="Landscape",K7,IF($F$4="Macro",L7,IF($F$4="People",M7,IF($F$4="Sports",N7,IF($F$4="Travel",O7,IF($F$4="Waterdrops",P7,IF($F$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="N7" s="17" t="str">
+      <x:c r="W7" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D7,IF($G$4="C2 Birds in Flight",E7,IF($G$4="C3 Landscape",F7,IF($G$4="Default Settings",G7,IF($G$4="Birds in Flight",H7,IF($G$4="Birds Perched",I7,IF($G$4="Fireworks",J7,IF($G$4="Landscape",K7,IF($G$4="Macro",L7,IF($G$4="People",M7,IF($G$4="Sports",N7,IF($G$4="Travel",O7,IF($G$4="Waterdrops",P7,IF($G$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="O7" s="17" t="str">
+      <x:c r="X7" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D7,IF($H$4="C2 Birds in Flight",E7,IF($H$4="C3 Landscape",F7,IF($H$4="Default Settings",G7,IF($H$4="Birds in Flight",H7,IF($H$4="Birds Perched",I7,IF($H$4="Fireworks",J7,IF($H$4="Landscape",K7,IF($H$4="Macro",L7,IF($H$4="People",M7,IF($H$4="Sports",N7,IF($H$4="Travel",O7,IF($H$4="Waterdrops",P7,IF($H$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="P7" s="17" t="str">
+      <x:c r="Y7" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D7,IF($I$4="C2 Birds in Flight",E7,IF($I$4="C3 Landscape",F7,IF($I$4="Default Settings",G7,IF($I$4="Birds in Flight",H7,IF($I$4="Birds Perched",I7,IF($I$4="Fireworks",J7,IF($I$4="Landscape",K7,IF($I$4="Macro",L7,IF($I$4="People",M7,IF($I$4="Sports",N7,IF($I$4="Travel",O7,IF($I$4="Waterdrops",P7,IF($I$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="Q7" s="17" t="str">
+      <x:c r="Z7" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D7,IF($J$4="C2 Birds in Flight",E7,IF($J$4="C3 Landscape",F7,IF($J$4="Default Settings",G7,IF($J$4="Birds in Flight",H7,IF($J$4="Birds Perched",I7,IF($J$4="Fireworks",J7,IF($J$4="Landscape",K7,IF($J$4="Macro",L7,IF($J$4="People",M7,IF($J$4="Sports",N7,IF($J$4="Travel",O7,IF($J$4="Waterdrops",P7,IF($J$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="R7" s="17" t="str">
+      <x:c r="AA7" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D7,IF($K$4="C2 Birds in Flight",E7,IF($K$4="C3 Landscape",F7,IF($K$4="Default Settings",G7,IF($K$4="Birds in Flight",H7,IF($K$4="Birds Perched",I7,IF($K$4="Fireworks",J7,IF($K$4="Landscape",K7,IF($K$4="Macro",L7,IF($K$4="People",M7,IF($K$4="Sports",N7,IF($K$4="Travel",O7,IF($K$4="Waterdrops",P7,IF($K$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="AB7" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D7,IF($L$4="C2 Birds in Flight",E7,IF($L$4="C3 Landscape",F7,IF($L$4="Default Settings",G7,IF($L$4="Birds in Flight",H7,IF($L$4="Birds Perched",I7,IF($L$4="Fireworks",J7,IF($L$4="Landscape",K7,IF($L$4="Macro",L7,IF($L$4="People",M7,IF($L$4="Sports",N7,IF($L$4="Travel",O7,IF($L$4="Waterdrops",P7,IF($L$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Av</x:v>
+      </x:c>
+      <x:c r="AC7" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D7,IF($M$4="C2 Birds in Flight",E7,IF($M$4="C3 Landscape",F7,IF($M$4="Default Settings",G7,IF($M$4="Birds in Flight",H7,IF($M$4="Birds Perched",I7,IF($M$4="Fireworks",J7,IF($M$4="Landscape",K7,IF($M$4="Macro",L7,IF($M$4="People",M7,IF($M$4="Sports",N7,IF($M$4="Travel",O7,IF($M$4="Waterdrops",P7,IF($M$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T7" s="20" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="U7" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D7,IF($D$4="C2 Birds in Flight",E7,IF($D$4="C3 Landscape",F7,IF($D$4="Default Settings",G7,IF($D$4="Androo",H7,IF($D$4="Birds in Flight",I7,IF($D$4="Birds Perched",J7,IF($D$4="Fireworks",K7,IF($D$4="Landscape",L7,IF($D$4="Macro",M7,IF($D$4="People",N7,IF($D$4="Sports",O7,IF($D$4="Travel",P7,IF($D$4="Waterdrops",Q7,IF($D$4="Wildlife",R7,"")))))))))))))))</x:f>
+      <x:c r="AD7" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D7,IF($N$4="C2 Birds in Flight",E7,IF($N$4="C3 Landscape",F7,IF($N$4="Default Settings",G7,IF($N$4="Birds in Flight",H7,IF($N$4="Birds Perched",I7,IF($N$4="Fireworks",J7,IF($N$4="Landscape",K7,IF($N$4="Macro",L7,IF($N$4="People",M7,IF($N$4="Sports",N7,IF($N$4="Travel",O7,IF($N$4="Waterdrops",P7,IF($N$4="Wildlife",Q7,""))))))))))))))</x:f>
+        <x:v>Tv</x:v>
+      </x:c>
+      <x:c r="AE7" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D7,IF($O$4="C2 Birds in Flight",E7,IF($O$4="C3 Landscape",F7,IF($O$4="Default Settings",G7,IF($O$4="Birds in Flight",H7,IF($O$4="Birds Perched",I7,IF($O$4="Fireworks",J7,IF($O$4="Landscape",K7,IF($O$4="Macro",L7,IF($O$4="People",M7,IF($O$4="Sports",N7,IF($O$4="Travel",O7,IF($O$4="Waterdrops",P7,IF($O$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="V7" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D7,IF($E$4="C2 Birds in Flight",E7,IF($E$4="C3 Landscape",F7,IF($E$4="Default Settings",G7,IF($E$4="Androo",H7,IF($E$4="Birds in Flight",I7,IF($E$4="Birds Perched",J7,IF($E$4="Fireworks",K7,IF($E$4="Landscape",L7,IF($E$4="Macro",M7,IF($E$4="People",N7,IF($E$4="Sports",O7,IF($E$4="Travel",P7,IF($E$4="Waterdrops",Q7,IF($E$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Tv</x:v>
-      </x:c>
-      <x:c r="W7" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D7,IF($F$4="C2 Birds in Flight",E7,IF($F$4="C3 Landscape",F7,IF($F$4="Default Settings",G7,IF($F$4="Androo",H7,IF($F$4="Birds in Flight",I7,IF($F$4="Birds Perched",J7,IF($F$4="Fireworks",K7,IF($F$4="Landscape",L7,IF($F$4="Macro",M7,IF($F$4="People",N7,IF($F$4="Sports",O7,IF($F$4="Travel",P7,IF($F$4="Waterdrops",Q7,IF($F$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Av</x:v>
-      </x:c>
-      <x:c r="X7" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D7,IF($G$4="C2 Birds in Flight",E7,IF($G$4="C3 Landscape",F7,IF($G$4="Default Settings",G7,IF($G$4="Androo",H7,IF($G$4="Birds in Flight",I7,IF($G$4="Birds Perched",J7,IF($G$4="Fireworks",K7,IF($G$4="Landscape",L7,IF($G$4="Macro",M7,IF($G$4="People",N7,IF($G$4="Sports",O7,IF($G$4="Travel",P7,IF($G$4="Waterdrops",Q7,IF($G$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="Y7" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D7,IF($H$4="C2 Birds in Flight",E7,IF($H$4="C3 Landscape",F7,IF($H$4="Default Settings",G7,IF($H$4="Androo",H7,IF($H$4="Birds in Flight",I7,IF($H$4="Birds Perched",J7,IF($H$4="Fireworks",K7,IF($H$4="Landscape",L7,IF($H$4="Macro",M7,IF($H$4="People",N7,IF($H$4="Sports",O7,IF($H$4="Travel",P7,IF($H$4="Waterdrops",Q7,IF($H$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="Z7" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D7,IF($I$4="C2 Birds in Flight",E7,IF($I$4="C3 Landscape",F7,IF($I$4="Default Settings",G7,IF($I$4="Androo",H7,IF($I$4="Birds in Flight",I7,IF($I$4="Birds Perched",J7,IF($I$4="Fireworks",K7,IF($I$4="Landscape",L7,IF($I$4="Macro",M7,IF($I$4="People",N7,IF($I$4="Sports",O7,IF($I$4="Travel",P7,IF($I$4="Waterdrops",Q7,IF($I$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Tv</x:v>
-      </x:c>
-      <x:c r="AA7" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D7,IF($J$4="C2 Birds in Flight",E7,IF($J$4="C3 Landscape",F7,IF($J$4="Default Settings",G7,IF($J$4="Androo",H7,IF($J$4="Birds in Flight",I7,IF($J$4="Birds Perched",J7,IF($J$4="Fireworks",K7,IF($J$4="Landscape",L7,IF($J$4="Macro",M7,IF($J$4="People",N7,IF($J$4="Sports",O7,IF($J$4="Travel",P7,IF($J$4="Waterdrops",Q7,IF($J$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="AB7" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D7,IF($K$4="C2 Birds in Flight",E7,IF($K$4="C3 Landscape",F7,IF($K$4="Default Settings",G7,IF($K$4="Androo",H7,IF($K$4="Birds in Flight",I7,IF($K$4="Birds Perched",J7,IF($K$4="Fireworks",K7,IF($K$4="Landscape",L7,IF($K$4="Macro",M7,IF($K$4="People",N7,IF($K$4="Sports",O7,IF($K$4="Travel",P7,IF($K$4="Waterdrops",Q7,IF($K$4="Wildlife",R7,"")))))))))))))))</x:f>
+      <x:c r="AF7" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D7,IF($P$4="C2 Birds in Flight",E7,IF($P$4="C3 Landscape",F7,IF($P$4="Default Settings",G7,IF($P$4="Birds in Flight",H7,IF($P$4="Birds Perched",I7,IF($P$4="Fireworks",J7,IF($P$4="Landscape",K7,IF($P$4="Macro",L7,IF($P$4="People",M7,IF($P$4="Sports",N7,IF($P$4="Travel",O7,IF($P$4="Waterdrops",P7,IF($P$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="AC7" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D7,IF($L$4="C2 Birds in Flight",E7,IF($L$4="C3 Landscape",F7,IF($L$4="Default Settings",G7,IF($L$4="Androo",H7,IF($L$4="Birds in Flight",I7,IF($L$4="Birds Perched",J7,IF($L$4="Fireworks",K7,IF($L$4="Landscape",L7,IF($L$4="Macro",M7,IF($L$4="People",N7,IF($L$4="Sports",O7,IF($L$4="Travel",P7,IF($L$4="Waterdrops",Q7,IF($L$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Av</x:v>
-      </x:c>
-      <x:c r="AD7" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D7,IF($M$4="C2 Birds in Flight",E7,IF($M$4="C3 Landscape",F7,IF($M$4="Default Settings",G7,IF($M$4="Androo",H7,IF($M$4="Birds in Flight",I7,IF($M$4="Birds Perched",J7,IF($M$4="Fireworks",K7,IF($M$4="Landscape",L7,IF($M$4="Macro",M7,IF($M$4="People",N7,IF($M$4="Sports",O7,IF($M$4="Travel",P7,IF($M$4="Waterdrops",Q7,IF($M$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Av</x:v>
-      </x:c>
-      <x:c r="AE7" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D7,IF($N$4="C2 Birds in Flight",E7,IF($N$4="C3 Landscape",F7,IF($N$4="Default Settings",G7,IF($N$4="Androo",H7,IF($N$4="Birds in Flight",I7,IF($N$4="Birds Perched",J7,IF($N$4="Fireworks",K7,IF($N$4="Landscape",L7,IF($N$4="Macro",M7,IF($N$4="People",N7,IF($N$4="Sports",O7,IF($N$4="Travel",P7,IF($N$4="Waterdrops",Q7,IF($N$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="AF7" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D7,IF($O$4="C2 Birds in Flight",E7,IF($O$4="C3 Landscape",F7,IF($O$4="Default Settings",G7,IF($O$4="Androo",H7,IF($O$4="Birds in Flight",I7,IF($O$4="Birds Perched",J7,IF($O$4="Fireworks",K7,IF($O$4="Landscape",L7,IF($O$4="Macro",M7,IF($O$4="People",N7,IF($O$4="Sports",O7,IF($O$4="Travel",P7,IF($O$4="Waterdrops",Q7,IF($O$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Tv</x:v>
-      </x:c>
       <x:c r="AG7" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D7,IF($P$4="C2 Birds in Flight",E7,IF($P$4="C3 Landscape",F7,IF($P$4="Default Settings",G7,IF($P$4="Androo",H7,IF($P$4="Birds in Flight",I7,IF($P$4="Birds Perched",J7,IF($P$4="Fireworks",K7,IF($P$4="Landscape",L7,IF($P$4="Macro",M7,IF($P$4="People",N7,IF($P$4="Sports",O7,IF($P$4="Travel",P7,IF($P$4="Waterdrops",Q7,IF($P$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Fv</x:v>
-      </x:c>
-      <x:c r="AH7" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D7,IF($Q$4="C2 Birds in Flight",E7,IF($Q$4="C3 Landscape",F7,IF($Q$4="Default Settings",G7,IF($Q$4="Androo",H7,IF($Q$4="Birds in Flight",I7,IF($Q$4="Birds Perched",J7,IF($Q$4="Fireworks",K7,IF($Q$4="Landscape",L7,IF($Q$4="Macro",M7,IF($Q$4="People",N7,IF($Q$4="Sports",O7,IF($Q$4="Travel",P7,IF($Q$4="Waterdrops",Q7,IF($Q$4="Wildlife",R7,"")))))))))))))))</x:f>
-        <x:v>Manual</x:v>
-      </x:c>
-      <x:c r="AI7" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D7,IF($R$4="C2 Birds in Flight",E7,IF($R$4="C3 Landscape",F7,IF($R$4="Default Settings",G7,IF($R$4="Androo",H7,IF($R$4="Birds in Flight",I7,IF($R$4="Birds Perched",J7,IF($R$4="Fireworks",K7,IF($R$4="Landscape",L7,IF($R$4="Macro",M7,IF($R$4="People",N7,IF($R$4="Sports",O7,IF($R$4="Travel",P7,IF($R$4="Waterdrops",Q7,IF($R$4="Wildlife",R7,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D7,IF($Q$4="C2 Birds in Flight",E7,IF($Q$4="C3 Landscape",F7,IF($Q$4="Default Settings",G7,IF($Q$4="Birds in Flight",H7,IF($Q$4="Birds Perched",I7,IF($Q$4="Fireworks",J7,IF($Q$4="Landscape",K7,IF($Q$4="Macro",L7,IF($Q$4="People",M7,IF($Q$4="Sports",N7,IF($Q$4="Travel",O7,IF($Q$4="Waterdrops",P7,IF($Q$4="Wildlife",Q7,""))))))))))))))</x:f>
         <x:v>Fv</x:v>
       </x:c>
     </x:row>
@@ -1168,73 +1133,66 @@
       <x:c r="Q8" s="17" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="R8" s="17" t="str">
+      <x:c r="R8" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S8" s="20" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="T8" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D8,IF($D$4="C2 Birds in Flight",E8,IF($D$4="C3 Landscape",F8,IF($D$4="Default Settings",G8,IF($D$4="Birds in Flight",H8,IF($D$4="Birds Perched",I8,IF($D$4="Fireworks",J8,IF($D$4="Landscape",K8,IF($D$4="Macro",L8,IF($D$4="People",M8,IF($D$4="Sports",N8,IF($D$4="Travel",O8,IF($D$4="Waterdrops",P8,IF($D$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="S8" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T8" s="20" t="n">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="U8" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D8,IF($D$4="C2 Birds in Flight",E8,IF($D$4="C3 Landscape",F8,IF($D$4="Default Settings",G8,IF($D$4="Androo",H8,IF($D$4="Birds in Flight",I8,IF($D$4="Birds Perched",J8,IF($D$4="Fireworks",K8,IF($D$4="Landscape",L8,IF($D$4="Macro",M8,IF($D$4="People",N8,IF($D$4="Sports",O8,IF($D$4="Travel",P8,IF($D$4="Waterdrops",Q8,IF($D$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D8,IF($E$4="C2 Birds in Flight",E8,IF($E$4="C3 Landscape",F8,IF($E$4="Default Settings",G8,IF($E$4="Birds in Flight",H8,IF($E$4="Birds Perched",I8,IF($E$4="Fireworks",J8,IF($E$4="Landscape",K8,IF($E$4="Macro",L8,IF($E$4="People",M8,IF($E$4="Sports",N8,IF($E$4="Travel",O8,IF($E$4="Waterdrops",P8,IF($E$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="V8" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D8,IF($E$4="C2 Birds in Flight",E8,IF($E$4="C3 Landscape",F8,IF($E$4="Default Settings",G8,IF($E$4="Androo",H8,IF($E$4="Birds in Flight",I8,IF($E$4="Birds Perched",J8,IF($E$4="Fireworks",K8,IF($E$4="Landscape",L8,IF($E$4="Macro",M8,IF($E$4="People",N8,IF($E$4="Sports",O8,IF($E$4="Travel",P8,IF($E$4="Waterdrops",Q8,IF($E$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D8,IF($F$4="C2 Birds in Flight",E8,IF($F$4="C3 Landscape",F8,IF($F$4="Default Settings",G8,IF($F$4="Birds in Flight",H8,IF($F$4="Birds Perched",I8,IF($F$4="Fireworks",J8,IF($F$4="Landscape",K8,IF($F$4="Macro",L8,IF($F$4="People",M8,IF($F$4="Sports",N8,IF($F$4="Travel",O8,IF($F$4="Waterdrops",P8,IF($F$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="W8" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D8,IF($F$4="C2 Birds in Flight",E8,IF($F$4="C3 Landscape",F8,IF($F$4="Default Settings",G8,IF($F$4="Androo",H8,IF($F$4="Birds in Flight",I8,IF($F$4="Birds Perched",J8,IF($F$4="Fireworks",K8,IF($F$4="Landscape",L8,IF($F$4="Macro",M8,IF($F$4="People",N8,IF($F$4="Sports",O8,IF($F$4="Travel",P8,IF($F$4="Waterdrops",Q8,IF($F$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($G$4="C1 Wildlife",D8,IF($G$4="C2 Birds in Flight",E8,IF($G$4="C3 Landscape",F8,IF($G$4="Default Settings",G8,IF($G$4="Birds in Flight",H8,IF($G$4="Birds Perched",I8,IF($G$4="Fireworks",J8,IF($G$4="Landscape",K8,IF($G$4="Macro",L8,IF($G$4="People",M8,IF($G$4="Sports",N8,IF($G$4="Travel",O8,IF($G$4="Waterdrops",P8,IF($G$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="X8" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D8,IF($G$4="C2 Birds in Flight",E8,IF($G$4="C3 Landscape",F8,IF($G$4="Default Settings",G8,IF($G$4="Androo",H8,IF($G$4="Birds in Flight",I8,IF($G$4="Birds Perched",J8,IF($G$4="Fireworks",K8,IF($G$4="Landscape",L8,IF($G$4="Macro",M8,IF($G$4="People",N8,IF($G$4="Sports",O8,IF($G$4="Travel",P8,IF($G$4="Waterdrops",Q8,IF($G$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($H$4="C1 Wildlife",D8,IF($H$4="C2 Birds in Flight",E8,IF($H$4="C3 Landscape",F8,IF($H$4="Default Settings",G8,IF($H$4="Birds in Flight",H8,IF($H$4="Birds Perched",I8,IF($H$4="Fireworks",J8,IF($H$4="Landscape",K8,IF($H$4="Macro",L8,IF($H$4="People",M8,IF($H$4="Sports",N8,IF($H$4="Travel",O8,IF($H$4="Waterdrops",P8,IF($H$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="Y8" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D8,IF($H$4="C2 Birds in Flight",E8,IF($H$4="C3 Landscape",F8,IF($H$4="Default Settings",G8,IF($H$4="Androo",H8,IF($H$4="Birds in Flight",I8,IF($H$4="Birds Perched",J8,IF($H$4="Fireworks",K8,IF($H$4="Landscape",L8,IF($H$4="Macro",M8,IF($H$4="People",N8,IF($H$4="Sports",O8,IF($H$4="Travel",P8,IF($H$4="Waterdrops",Q8,IF($H$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($I$4="C1 Wildlife",D8,IF($I$4="C2 Birds in Flight",E8,IF($I$4="C3 Landscape",F8,IF($I$4="Default Settings",G8,IF($I$4="Birds in Flight",H8,IF($I$4="Birds Perched",I8,IF($I$4="Fireworks",J8,IF($I$4="Landscape",K8,IF($I$4="Macro",L8,IF($I$4="People",M8,IF($I$4="Sports",N8,IF($I$4="Travel",O8,IF($I$4="Waterdrops",P8,IF($I$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="Z8" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D8,IF($I$4="C2 Birds in Flight",E8,IF($I$4="C3 Landscape",F8,IF($I$4="Default Settings",G8,IF($I$4="Androo",H8,IF($I$4="Birds in Flight",I8,IF($I$4="Birds Perched",J8,IF($I$4="Fireworks",K8,IF($I$4="Landscape",L8,IF($I$4="Macro",M8,IF($I$4="People",N8,IF($I$4="Sports",O8,IF($I$4="Travel",P8,IF($I$4="Waterdrops",Q8,IF($I$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D8,IF($J$4="C2 Birds in Flight",E8,IF($J$4="C3 Landscape",F8,IF($J$4="Default Settings",G8,IF($J$4="Birds in Flight",H8,IF($J$4="Birds Perched",I8,IF($J$4="Fireworks",J8,IF($J$4="Landscape",K8,IF($J$4="Macro",L8,IF($J$4="People",M8,IF($J$4="Sports",N8,IF($J$4="Travel",O8,IF($J$4="Waterdrops",P8,IF($J$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AA8" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D8,IF($J$4="C2 Birds in Flight",E8,IF($J$4="C3 Landscape",F8,IF($J$4="Default Settings",G8,IF($J$4="Androo",H8,IF($J$4="Birds in Flight",I8,IF($J$4="Birds Perched",J8,IF($J$4="Fireworks",K8,IF($J$4="Landscape",L8,IF($J$4="Macro",M8,IF($J$4="People",N8,IF($J$4="Sports",O8,IF($J$4="Travel",P8,IF($J$4="Waterdrops",Q8,IF($J$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($K$4="C1 Wildlife",D8,IF($K$4="C2 Birds in Flight",E8,IF($K$4="C3 Landscape",F8,IF($K$4="Default Settings",G8,IF($K$4="Birds in Flight",H8,IF($K$4="Birds Perched",I8,IF($K$4="Fireworks",J8,IF($K$4="Landscape",K8,IF($K$4="Macro",L8,IF($K$4="People",M8,IF($K$4="Sports",N8,IF($K$4="Travel",O8,IF($K$4="Waterdrops",P8,IF($K$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AB8" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D8,IF($K$4="C2 Birds in Flight",E8,IF($K$4="C3 Landscape",F8,IF($K$4="Default Settings",G8,IF($K$4="Androo",H8,IF($K$4="Birds in Flight",I8,IF($K$4="Birds Perched",J8,IF($K$4="Fireworks",K8,IF($K$4="Landscape",L8,IF($K$4="Macro",M8,IF($K$4="People",N8,IF($K$4="Sports",O8,IF($K$4="Travel",P8,IF($K$4="Waterdrops",Q8,IF($K$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D8,IF($L$4="C2 Birds in Flight",E8,IF($L$4="C3 Landscape",F8,IF($L$4="Default Settings",G8,IF($L$4="Birds in Flight",H8,IF($L$4="Birds Perched",I8,IF($L$4="Fireworks",J8,IF($L$4="Landscape",K8,IF($L$4="Macro",L8,IF($L$4="People",M8,IF($L$4="Sports",N8,IF($L$4="Travel",O8,IF($L$4="Waterdrops",P8,IF($L$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AC8" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D8,IF($L$4="C2 Birds in Flight",E8,IF($L$4="C3 Landscape",F8,IF($L$4="Default Settings",G8,IF($L$4="Androo",H8,IF($L$4="Birds in Flight",I8,IF($L$4="Birds Perched",J8,IF($L$4="Fireworks",K8,IF($L$4="Landscape",L8,IF($L$4="Macro",M8,IF($L$4="People",N8,IF($L$4="Sports",O8,IF($L$4="Travel",P8,IF($L$4="Waterdrops",Q8,IF($L$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($M$4="C1 Wildlife",D8,IF($M$4="C2 Birds in Flight",E8,IF($M$4="C3 Landscape",F8,IF($M$4="Default Settings",G8,IF($M$4="Birds in Flight",H8,IF($M$4="Birds Perched",I8,IF($M$4="Fireworks",J8,IF($M$4="Landscape",K8,IF($M$4="Macro",L8,IF($M$4="People",M8,IF($M$4="Sports",N8,IF($M$4="Travel",O8,IF($M$4="Waterdrops",P8,IF($M$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AD8" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D8,IF($M$4="C2 Birds in Flight",E8,IF($M$4="C3 Landscape",F8,IF($M$4="Default Settings",G8,IF($M$4="Androo",H8,IF($M$4="Birds in Flight",I8,IF($M$4="Birds Perched",J8,IF($M$4="Fireworks",K8,IF($M$4="Landscape",L8,IF($M$4="Macro",M8,IF($M$4="People",N8,IF($M$4="Sports",O8,IF($M$4="Travel",P8,IF($M$4="Waterdrops",Q8,IF($M$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($N$4="C1 Wildlife",D8,IF($N$4="C2 Birds in Flight",E8,IF($N$4="C3 Landscape",F8,IF($N$4="Default Settings",G8,IF($N$4="Birds in Flight",H8,IF($N$4="Birds Perched",I8,IF($N$4="Fireworks",J8,IF($N$4="Landscape",K8,IF($N$4="Macro",L8,IF($N$4="People",M8,IF($N$4="Sports",N8,IF($N$4="Travel",O8,IF($N$4="Waterdrops",P8,IF($N$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AE8" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D8,IF($N$4="C2 Birds in Flight",E8,IF($N$4="C3 Landscape",F8,IF($N$4="Default Settings",G8,IF($N$4="Androo",H8,IF($N$4="Birds in Flight",I8,IF($N$4="Birds Perched",J8,IF($N$4="Fireworks",K8,IF($N$4="Landscape",L8,IF($N$4="Macro",M8,IF($N$4="People",N8,IF($N$4="Sports",O8,IF($N$4="Travel",P8,IF($N$4="Waterdrops",Q8,IF($N$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D8,IF($O$4="C2 Birds in Flight",E8,IF($O$4="C3 Landscape",F8,IF($O$4="Default Settings",G8,IF($O$4="Birds in Flight",H8,IF($O$4="Birds Perched",I8,IF($O$4="Fireworks",J8,IF($O$4="Landscape",K8,IF($O$4="Macro",L8,IF($O$4="People",M8,IF($O$4="Sports",N8,IF($O$4="Travel",O8,IF($O$4="Waterdrops",P8,IF($O$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AF8" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D8,IF($O$4="C2 Birds in Flight",E8,IF($O$4="C3 Landscape",F8,IF($O$4="Default Settings",G8,IF($O$4="Androo",H8,IF($O$4="Birds in Flight",I8,IF($O$4="Birds Perched",J8,IF($O$4="Fireworks",K8,IF($O$4="Landscape",L8,IF($O$4="Macro",M8,IF($O$4="People",N8,IF($O$4="Sports",O8,IF($O$4="Travel",P8,IF($O$4="Waterdrops",Q8,IF($O$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D8,IF($P$4="C2 Birds in Flight",E8,IF($P$4="C3 Landscape",F8,IF($P$4="Default Settings",G8,IF($P$4="Birds in Flight",H8,IF($P$4="Birds Perched",I8,IF($P$4="Fireworks",J8,IF($P$4="Landscape",K8,IF($P$4="Macro",L8,IF($P$4="People",M8,IF($P$4="Sports",N8,IF($P$4="Travel",O8,IF($P$4="Waterdrops",P8,IF($P$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
       <x:c r="AG8" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D8,IF($P$4="C2 Birds in Flight",E8,IF($P$4="C3 Landscape",F8,IF($P$4="Default Settings",G8,IF($P$4="Androo",H8,IF($P$4="Birds in Flight",I8,IF($P$4="Birds Perched",J8,IF($P$4="Fireworks",K8,IF($P$4="Landscape",L8,IF($P$4="Macro",M8,IF($P$4="People",N8,IF($P$4="Sports",O8,IF($P$4="Travel",P8,IF($P$4="Waterdrops",Q8,IF($P$4="Wildlife",R8,"")))))))))))))))</x:f>
-        <x:v>Evaluative</x:v>
-      </x:c>
-      <x:c r="AH8" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D8,IF($Q$4="C2 Birds in Flight",E8,IF($Q$4="C3 Landscape",F8,IF($Q$4="Default Settings",G8,IF($Q$4="Androo",H8,IF($Q$4="Birds in Flight",I8,IF($Q$4="Birds Perched",J8,IF($Q$4="Fireworks",K8,IF($Q$4="Landscape",L8,IF($Q$4="Macro",M8,IF($Q$4="People",N8,IF($Q$4="Sports",O8,IF($Q$4="Travel",P8,IF($Q$4="Waterdrops",Q8,IF($Q$4="Wildlife",R8,"")))))))))))))))</x:f>
-        <x:v>Evaluative</x:v>
-      </x:c>
-      <x:c r="AI8" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D8,IF($R$4="C2 Birds in Flight",E8,IF($R$4="C3 Landscape",F8,IF($R$4="Default Settings",G8,IF($R$4="Androo",H8,IF($R$4="Birds in Flight",I8,IF($R$4="Birds Perched",J8,IF($R$4="Fireworks",K8,IF($R$4="Landscape",L8,IF($R$4="Macro",M8,IF($R$4="People",N8,IF($R$4="Sports",O8,IF($R$4="Travel",P8,IF($R$4="Waterdrops",Q8,IF($R$4="Wildlife",R8,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D8,IF($Q$4="C2 Birds in Flight",E8,IF($Q$4="C3 Landscape",F8,IF($Q$4="Default Settings",G8,IF($Q$4="Birds in Flight",H8,IF($Q$4="Birds Perched",I8,IF($Q$4="Fireworks",J8,IF($Q$4="Landscape",K8,IF($Q$4="Macro",L8,IF($Q$4="People",M8,IF($Q$4="Sports",N8,IF($Q$4="Travel",O8,IF($Q$4="Waterdrops",P8,IF($Q$4="Wildlife",Q8,""))))))))))))))</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
     </x:row>
@@ -1261,102 +1219,95 @@
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="H9" s="17" t="str">
+        <x:v>1/2000–1/4000</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
+        <x:v>1/500–1/1000</x:v>
+      </x:c>
+      <x:c r="J9" s="17" t="str">
+        <x:v>2–6 s (start at 4 s)</x:v>
+      </x:c>
+      <x:c r="K9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="L9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="M9" s="17" t="str">
+        <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
+      </x:c>
+      <x:c r="N9" s="17" t="str">
+        <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
+      </x:c>
+      <x:c r="O9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P9" s="17" t="str">
         <x:v>1/200</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="str">
+      <x:c r="Q9" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R9" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S9" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="T9" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D9,IF($D$4="C2 Birds in Flight",E9,IF($D$4="C3 Landscape",F9,IF($D$4="Default Settings",G9,IF($D$4="Birds in Flight",H9,IF($D$4="Birds Perched",I9,IF($D$4="Fireworks",J9,IF($D$4="Landscape",K9,IF($D$4="Macro",L9,IF($D$4="People",M9,IF($D$4="Sports",N9,IF($D$4="Travel",O9,IF($D$4="Waterdrops",P9,IF($D$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="U9" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D9,IF($E$4="C2 Birds in Flight",E9,IF($E$4="C3 Landscape",F9,IF($E$4="Default Settings",G9,IF($E$4="Birds in Flight",H9,IF($E$4="Birds Perched",I9,IF($E$4="Fireworks",J9,IF($E$4="Landscape",K9,IF($E$4="Macro",L9,IF($E$4="People",M9,IF($E$4="Sports",N9,IF($E$4="Travel",O9,IF($E$4="Waterdrops",P9,IF($E$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>1/2500 sec.</x:v>
+      </x:c>
+      <x:c r="V9" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D9,IF($F$4="C2 Birds in Flight",E9,IF($F$4="C3 Landscape",F9,IF($F$4="Default Settings",G9,IF($F$4="Birds in Flight",H9,IF($F$4="Birds Perched",I9,IF($F$4="Fireworks",J9,IF($F$4="Landscape",K9,IF($F$4="Macro",L9,IF($F$4="People",M9,IF($F$4="Sports",N9,IF($F$4="Travel",O9,IF($F$4="Waterdrops",P9,IF($F$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="W9" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D9,IF($G$4="C2 Birds in Flight",E9,IF($G$4="C3 Landscape",F9,IF($G$4="Default Settings",G9,IF($G$4="Birds in Flight",H9,IF($G$4="Birds Perched",I9,IF($G$4="Fireworks",J9,IF($G$4="Landscape",K9,IF($G$4="Macro",L9,IF($G$4="People",M9,IF($G$4="Sports",N9,IF($G$4="Travel",O9,IF($G$4="Waterdrops",P9,IF($G$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X9" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D9,IF($H$4="C2 Birds in Flight",E9,IF($H$4="C3 Landscape",F9,IF($H$4="Default Settings",G9,IF($H$4="Birds in Flight",H9,IF($H$4="Birds Perched",I9,IF($H$4="Fireworks",J9,IF($H$4="Landscape",K9,IF($H$4="Macro",L9,IF($H$4="People",M9,IF($H$4="Sports",N9,IF($H$4="Travel",O9,IF($H$4="Waterdrops",P9,IF($H$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>1/2000–1/4000</x:v>
       </x:c>
-      <x:c r="J9" s="17" t="str">
+      <x:c r="Y9" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D9,IF($I$4="C2 Birds in Flight",E9,IF($I$4="C3 Landscape",F9,IF($I$4="Default Settings",G9,IF($I$4="Birds in Flight",H9,IF($I$4="Birds Perched",I9,IF($I$4="Fireworks",J9,IF($I$4="Landscape",K9,IF($I$4="Macro",L9,IF($I$4="People",M9,IF($I$4="Sports",N9,IF($I$4="Travel",O9,IF($I$4="Waterdrops",P9,IF($I$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>1/500–1/1000</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="str">
+      <x:c r="Z9" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D9,IF($J$4="C2 Birds in Flight",E9,IF($J$4="C3 Landscape",F9,IF($J$4="Default Settings",G9,IF($J$4="Birds in Flight",H9,IF($J$4="Birds Perched",I9,IF($J$4="Fireworks",J9,IF($J$4="Landscape",K9,IF($J$4="Macro",L9,IF($J$4="People",M9,IF($J$4="Sports",N9,IF($J$4="Travel",O9,IF($J$4="Waterdrops",P9,IF($J$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>2–6 s (start at 4 s)</x:v>
       </x:c>
-      <x:c r="L9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="M9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="N9" s="17" t="str">
+      <x:c r="AA9" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D9,IF($K$4="C2 Birds in Flight",E9,IF($K$4="C3 Landscape",F9,IF($K$4="Default Settings",G9,IF($K$4="Birds in Flight",H9,IF($K$4="Birds Perched",I9,IF($K$4="Fireworks",J9,IF($K$4="Landscape",K9,IF($K$4="Macro",L9,IF($K$4="People",M9,IF($K$4="Sports",N9,IF($K$4="Travel",O9,IF($K$4="Waterdrops",P9,IF($K$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AB9" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D9,IF($L$4="C2 Birds in Flight",E9,IF($L$4="C3 Landscape",F9,IF($L$4="Default Settings",G9,IF($L$4="Birds in Flight",H9,IF($L$4="Birds Perched",I9,IF($L$4="Fireworks",J9,IF($L$4="Landscape",K9,IF($L$4="Macro",L9,IF($L$4="People",M9,IF($L$4="Sports",N9,IF($L$4="Travel",O9,IF($L$4="Waterdrops",P9,IF($L$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AC9" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D9,IF($M$4="C2 Birds in Flight",E9,IF($M$4="C3 Landscape",F9,IF($M$4="Default Settings",G9,IF($M$4="Birds in Flight",H9,IF($M$4="Birds Perched",I9,IF($M$4="Fireworks",J9,IF($M$4="Landscape",K9,IF($M$4="Macro",L9,IF($M$4="People",M9,IF($M$4="Sports",N9,IF($M$4="Travel",O9,IF($M$4="Waterdrops",P9,IF($M$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
       </x:c>
-      <x:c r="O9" s="17" t="str">
+      <x:c r="AD9" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D9,IF($N$4="C2 Birds in Flight",E9,IF($N$4="C3 Landscape",F9,IF($N$4="Default Settings",G9,IF($N$4="Birds in Flight",H9,IF($N$4="Birds Perched",I9,IF($N$4="Fireworks",J9,IF($N$4="Landscape",K9,IF($N$4="Macro",L9,IF($N$4="People",M9,IF($N$4="Sports",N9,IF($N$4="Travel",O9,IF($N$4="Waterdrops",P9,IF($N$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
       </x:c>
-      <x:c r="P9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Q9" s="17" t="str">
+      <x:c r="AE9" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D9,IF($O$4="C2 Birds in Flight",E9,IF($O$4="C3 Landscape",F9,IF($O$4="Default Settings",G9,IF($O$4="Birds in Flight",H9,IF($O$4="Birds Perched",I9,IF($O$4="Fireworks",J9,IF($O$4="Landscape",K9,IF($O$4="Macro",L9,IF($O$4="People",M9,IF($O$4="Sports",N9,IF($O$4="Travel",O9,IF($O$4="Waterdrops",P9,IF($O$4="Wildlife",Q9,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF9" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D9,IF($P$4="C2 Birds in Flight",E9,IF($P$4="C3 Landscape",F9,IF($P$4="Default Settings",G9,IF($P$4="Birds in Flight",H9,IF($P$4="Birds Perched",I9,IF($P$4="Fireworks",J9,IF($P$4="Landscape",K9,IF($P$4="Macro",L9,IF($P$4="People",M9,IF($P$4="Sports",N9,IF($P$4="Travel",O9,IF($P$4="Waterdrops",P9,IF($P$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>1/200</x:v>
       </x:c>
-      <x:c r="R9" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="S9" s="20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T9" s="20" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="U9" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D9,IF($D$4="C2 Birds in Flight",E9,IF($D$4="C3 Landscape",F9,IF($D$4="Default Settings",G9,IF($D$4="Androo",H9,IF($D$4="Birds in Flight",I9,IF($D$4="Birds Perched",J9,IF($D$4="Fireworks",K9,IF($D$4="Landscape",L9,IF($D$4="Macro",M9,IF($D$4="People",N9,IF($D$4="Sports",O9,IF($D$4="Travel",P9,IF($D$4="Waterdrops",Q9,IF($D$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="V9" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D9,IF($E$4="C2 Birds in Flight",E9,IF($E$4="C3 Landscape",F9,IF($E$4="Default Settings",G9,IF($E$4="Androo",H9,IF($E$4="Birds in Flight",I9,IF($E$4="Birds Perched",J9,IF($E$4="Fireworks",K9,IF($E$4="Landscape",L9,IF($E$4="Macro",M9,IF($E$4="People",N9,IF($E$4="Sports",O9,IF($E$4="Travel",P9,IF($E$4="Waterdrops",Q9,IF($E$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/2500 sec.</x:v>
-      </x:c>
-      <x:c r="W9" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D9,IF($F$4="C2 Birds in Flight",E9,IF($F$4="C3 Landscape",F9,IF($F$4="Default Settings",G9,IF($F$4="Androo",H9,IF($F$4="Birds in Flight",I9,IF($F$4="Birds Perched",J9,IF($F$4="Fireworks",K9,IF($F$4="Landscape",L9,IF($F$4="Macro",M9,IF($F$4="People",N9,IF($F$4="Sports",O9,IF($F$4="Travel",P9,IF($F$4="Waterdrops",Q9,IF($F$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="X9" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D9,IF($G$4="C2 Birds in Flight",E9,IF($G$4="C3 Landscape",F9,IF($G$4="Default Settings",G9,IF($G$4="Androo",H9,IF($G$4="Birds in Flight",I9,IF($G$4="Birds Perched",J9,IF($G$4="Fireworks",K9,IF($G$4="Landscape",L9,IF($G$4="Macro",M9,IF($G$4="People",N9,IF($G$4="Sports",O9,IF($G$4="Travel",P9,IF($G$4="Waterdrops",Q9,IF($G$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Y9" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D9,IF($H$4="C2 Birds in Flight",E9,IF($H$4="C3 Landscape",F9,IF($H$4="Default Settings",G9,IF($H$4="Androo",H9,IF($H$4="Birds in Flight",I9,IF($H$4="Birds Perched",J9,IF($H$4="Fireworks",K9,IF($H$4="Landscape",L9,IF($H$4="Macro",M9,IF($H$4="People",N9,IF($H$4="Sports",O9,IF($H$4="Travel",P9,IF($H$4="Waterdrops",Q9,IF($H$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/200</x:v>
-      </x:c>
-      <x:c r="Z9" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D9,IF($I$4="C2 Birds in Flight",E9,IF($I$4="C3 Landscape",F9,IF($I$4="Default Settings",G9,IF($I$4="Androo",H9,IF($I$4="Birds in Flight",I9,IF($I$4="Birds Perched",J9,IF($I$4="Fireworks",K9,IF($I$4="Landscape",L9,IF($I$4="Macro",M9,IF($I$4="People",N9,IF($I$4="Sports",O9,IF($I$4="Travel",P9,IF($I$4="Waterdrops",Q9,IF($I$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/2000–1/4000</x:v>
-      </x:c>
-      <x:c r="AA9" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D9,IF($J$4="C2 Birds in Flight",E9,IF($J$4="C3 Landscape",F9,IF($J$4="Default Settings",G9,IF($J$4="Androo",H9,IF($J$4="Birds in Flight",I9,IF($J$4="Birds Perched",J9,IF($J$4="Fireworks",K9,IF($J$4="Landscape",L9,IF($J$4="Macro",M9,IF($J$4="People",N9,IF($J$4="Sports",O9,IF($J$4="Travel",P9,IF($J$4="Waterdrops",Q9,IF($J$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/500–1/1000</x:v>
-      </x:c>
-      <x:c r="AB9" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D9,IF($K$4="C2 Birds in Flight",E9,IF($K$4="C3 Landscape",F9,IF($K$4="Default Settings",G9,IF($K$4="Androo",H9,IF($K$4="Birds in Flight",I9,IF($K$4="Birds Perched",J9,IF($K$4="Fireworks",K9,IF($K$4="Landscape",L9,IF($K$4="Macro",M9,IF($K$4="People",N9,IF($K$4="Sports",O9,IF($K$4="Travel",P9,IF($K$4="Waterdrops",Q9,IF($K$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>2–6 s (start at 4 s)</x:v>
-      </x:c>
-      <x:c r="AC9" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D9,IF($L$4="C2 Birds in Flight",E9,IF($L$4="C3 Landscape",F9,IF($L$4="Default Settings",G9,IF($L$4="Androo",H9,IF($L$4="Birds in Flight",I9,IF($L$4="Birds Perched",J9,IF($L$4="Fireworks",K9,IF($L$4="Landscape",L9,IF($L$4="Macro",M9,IF($L$4="People",N9,IF($L$4="Sports",O9,IF($L$4="Travel",P9,IF($L$4="Waterdrops",Q9,IF($L$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AD9" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D9,IF($M$4="C2 Birds in Flight",E9,IF($M$4="C3 Landscape",F9,IF($M$4="Default Settings",G9,IF($M$4="Androo",H9,IF($M$4="Birds in Flight",I9,IF($M$4="Birds Perched",J9,IF($M$4="Fireworks",K9,IF($M$4="Landscape",L9,IF($M$4="Macro",M9,IF($M$4="People",N9,IF($M$4="Sports",O9,IF($M$4="Travel",P9,IF($M$4="Waterdrops",Q9,IF($M$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AE9" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D9,IF($N$4="C2 Birds in Flight",E9,IF($N$4="C3 Landscape",F9,IF($N$4="Default Settings",G9,IF($N$4="Androo",H9,IF($N$4="Birds in Flight",I9,IF($N$4="Birds Perched",J9,IF($N$4="Fireworks",K9,IF($N$4="Landscape",L9,IF($N$4="Macro",M9,IF($N$4="People",N9,IF($N$4="Sports",O9,IF($N$4="Travel",P9,IF($N$4="Waterdrops",Q9,IF($N$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/200–1/320 portraits; 1/500+ action</x:v>
-      </x:c>
-      <x:c r="AF9" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D9,IF($O$4="C2 Birds in Flight",E9,IF($O$4="C3 Landscape",F9,IF($O$4="Default Settings",G9,IF($O$4="Androo",H9,IF($O$4="Birds in Flight",I9,IF($O$4="Birds Perched",J9,IF($O$4="Fireworks",K9,IF($O$4="Landscape",L9,IF($O$4="Macro",M9,IF($O$4="People",N9,IF($O$4="Sports",O9,IF($O$4="Travel",P9,IF($O$4="Waterdrops",Q9,IF($O$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/1000–1/2000 outdoor; 1/640–1/1000 indoor</x:v>
-      </x:c>
       <x:c r="AG9" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D9,IF($P$4="C2 Birds in Flight",E9,IF($P$4="C3 Landscape",F9,IF($P$4="Default Settings",G9,IF($P$4="Androo",H9,IF($P$4="Birds in Flight",I9,IF($P$4="Birds Perched",J9,IF($P$4="Fireworks",K9,IF($P$4="Landscape",L9,IF($P$4="Macro",M9,IF($P$4="People",N9,IF($P$4="Sports",O9,IF($P$4="Travel",P9,IF($P$4="Waterdrops",Q9,IF($P$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AH9" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D9,IF($Q$4="C2 Birds in Flight",E9,IF($Q$4="C3 Landscape",F9,IF($Q$4="Default Settings",G9,IF($Q$4="Androo",H9,IF($Q$4="Birds in Flight",I9,IF($Q$4="Birds Perched",J9,IF($Q$4="Fireworks",K9,IF($Q$4="Landscape",L9,IF($Q$4="Macro",M9,IF($Q$4="People",N9,IF($Q$4="Sports",O9,IF($Q$4="Travel",P9,IF($Q$4="Waterdrops",Q9,IF($Q$4="Wildlife",R9,"")))))))))))))))</x:f>
-        <x:v>1/200</x:v>
-      </x:c>
-      <x:c r="AI9" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D9,IF($R$4="C2 Birds in Flight",E9,IF($R$4="C3 Landscape",F9,IF($R$4="Default Settings",G9,IF($R$4="Androo",H9,IF($R$4="Birds in Flight",I9,IF($R$4="Birds Perched",J9,IF($R$4="Fireworks",K9,IF($R$4="Landscape",L9,IF($R$4="Macro",M9,IF($R$4="People",N9,IF($R$4="Sports",O9,IF($R$4="Travel",P9,IF($R$4="Waterdrops",Q9,IF($R$4="Wildlife",R9,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D9,IF($Q$4="C2 Birds in Flight",E9,IF($Q$4="C3 Landscape",F9,IF($Q$4="Default Settings",G9,IF($Q$4="Birds in Flight",H9,IF($Q$4="Birds Perched",I9,IF($Q$4="Fireworks",J9,IF($Q$4="Landscape",K9,IF($Q$4="Macro",L9,IF($Q$4="People",M9,IF($Q$4="Sports",N9,IF($Q$4="Travel",O9,IF($Q$4="Waterdrops",P9,IF($Q$4="Wildlife",Q9,""))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
@@ -1386,7 +1337,7 @@
         <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="I10" s="17" t="str">
-        <x:v>Mechanical</x:v>
+        <x:v>EFCS</x:v>
       </x:c>
       <x:c r="J10" s="17" t="str">
         <x:v>EFCS</x:v>
@@ -1398,87 +1349,80 @@
         <x:v>EFCS</x:v>
       </x:c>
       <x:c r="M10" s="17" t="str">
-        <x:v>EFCS</x:v>
+        <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="N10" s="17" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
       <x:c r="O10" s="17" t="str">
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="P10" s="17" t="str">
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="P10" s="17" t="str">
+      <x:c r="Q10" s="17" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="Q10" s="17" t="str">
+      <x:c r="R10" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S10" s="20" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="T10" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D10,IF($D$4="C2 Birds in Flight",E10,IF($D$4="C3 Landscape",F10,IF($D$4="Default Settings",G10,IF($D$4="Birds in Flight",H10,IF($D$4="Birds Perched",I10,IF($D$4="Fireworks",J10,IF($D$4="Landscape",K10,IF($D$4="Macro",L10,IF($D$4="People",M10,IF($D$4="Sports",N10,IF($D$4="Travel",O10,IF($D$4="Waterdrops",P10,IF($D$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="U10" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D10,IF($E$4="C2 Birds in Flight",E10,IF($E$4="C3 Landscape",F10,IF($E$4="Default Settings",G10,IF($E$4="Birds in Flight",H10,IF($E$4="Birds Perched",I10,IF($E$4="Fireworks",J10,IF($E$4="Landscape",K10,IF($E$4="Macro",L10,IF($E$4="People",M10,IF($E$4="Sports",N10,IF($E$4="Travel",O10,IF($E$4="Waterdrops",P10,IF($E$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="R10" s="17" t="str">
+      <x:c r="V10" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D10,IF($F$4="C2 Birds in Flight",E10,IF($F$4="C3 Landscape",F10,IF($F$4="Default Settings",G10,IF($F$4="Birds in Flight",H10,IF($F$4="Birds Perched",I10,IF($F$4="Fireworks",J10,IF($F$4="Landscape",K10,IF($F$4="Macro",L10,IF($F$4="People",M10,IF($F$4="Sports",N10,IF($F$4="Travel",O10,IF($F$4="Waterdrops",P10,IF($F$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="S10" s="20" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="T10" s="20" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="U10" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D10,IF($D$4="C2 Birds in Flight",E10,IF($D$4="C3 Landscape",F10,IF($D$4="Default Settings",G10,IF($D$4="Androo",H10,IF($D$4="Birds in Flight",I10,IF($D$4="Birds Perched",J10,IF($D$4="Fireworks",K10,IF($D$4="Landscape",L10,IF($D$4="Macro",M10,IF($D$4="People",N10,IF($D$4="Sports",O10,IF($D$4="Travel",P10,IF($D$4="Waterdrops",Q10,IF($D$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="W10" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D10,IF($G$4="C2 Birds in Flight",E10,IF($G$4="C3 Landscape",F10,IF($G$4="Default Settings",G10,IF($G$4="Birds in Flight",H10,IF($G$4="Birds Perched",I10,IF($G$4="Fireworks",J10,IF($G$4="Landscape",K10,IF($G$4="Macro",L10,IF($G$4="People",M10,IF($G$4="Sports",N10,IF($G$4="Travel",O10,IF($G$4="Waterdrops",P10,IF($G$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="V10" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D10,IF($E$4="C2 Birds in Flight",E10,IF($E$4="C3 Landscape",F10,IF($E$4="Default Settings",G10,IF($E$4="Androo",H10,IF($E$4="Birds in Flight",I10,IF($E$4="Birds Perched",J10,IF($E$4="Fireworks",K10,IF($E$4="Landscape",L10,IF($E$4="Macro",M10,IF($E$4="People",N10,IF($E$4="Sports",O10,IF($E$4="Travel",P10,IF($E$4="Waterdrops",Q10,IF($E$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="X10" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D10,IF($H$4="C2 Birds in Flight",E10,IF($H$4="C3 Landscape",F10,IF($H$4="Default Settings",G10,IF($H$4="Birds in Flight",H10,IF($H$4="Birds Perched",I10,IF($H$4="Fireworks",J10,IF($H$4="Landscape",K10,IF($H$4="Macro",L10,IF($H$4="People",M10,IF($H$4="Sports",N10,IF($H$4="Travel",O10,IF($H$4="Waterdrops",P10,IF($H$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="W10" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D10,IF($F$4="C2 Birds in Flight",E10,IF($F$4="C3 Landscape",F10,IF($F$4="Default Settings",G10,IF($F$4="Androo",H10,IF($F$4="Birds in Flight",I10,IF($F$4="Birds Perched",J10,IF($F$4="Fireworks",K10,IF($F$4="Landscape",L10,IF($F$4="Macro",M10,IF($F$4="People",N10,IF($F$4="Sports",O10,IF($F$4="Travel",P10,IF($F$4="Waterdrops",Q10,IF($F$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="Y10" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D10,IF($I$4="C2 Birds in Flight",E10,IF($I$4="C3 Landscape",F10,IF($I$4="Default Settings",G10,IF($I$4="Birds in Flight",H10,IF($I$4="Birds Perched",I10,IF($I$4="Fireworks",J10,IF($I$4="Landscape",K10,IF($I$4="Macro",L10,IF($I$4="People",M10,IF($I$4="Sports",N10,IF($I$4="Travel",O10,IF($I$4="Waterdrops",P10,IF($I$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="X10" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D10,IF($G$4="C2 Birds in Flight",E10,IF($G$4="C3 Landscape",F10,IF($G$4="Default Settings",G10,IF($G$4="Androo",H10,IF($G$4="Birds in Flight",I10,IF($G$4="Birds Perched",J10,IF($G$4="Fireworks",K10,IF($G$4="Landscape",L10,IF($G$4="Macro",M10,IF($G$4="People",N10,IF($G$4="Sports",O10,IF($G$4="Travel",P10,IF($G$4="Waterdrops",Q10,IF($G$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="Z10" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D10,IF($J$4="C2 Birds in Flight",E10,IF($J$4="C3 Landscape",F10,IF($J$4="Default Settings",G10,IF($J$4="Birds in Flight",H10,IF($J$4="Birds Perched",I10,IF($J$4="Fireworks",J10,IF($J$4="Landscape",K10,IF($J$4="Macro",L10,IF($J$4="People",M10,IF($J$4="Sports",N10,IF($J$4="Travel",O10,IF($J$4="Waterdrops",P10,IF($J$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="Y10" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D10,IF($H$4="C2 Birds in Flight",E10,IF($H$4="C3 Landscape",F10,IF($H$4="Default Settings",G10,IF($H$4="Androo",H10,IF($H$4="Birds in Flight",I10,IF($H$4="Birds Perched",J10,IF($H$4="Fireworks",K10,IF($H$4="Landscape",L10,IF($H$4="Macro",M10,IF($H$4="People",N10,IF($H$4="Sports",O10,IF($H$4="Travel",P10,IF($H$4="Waterdrops",Q10,IF($H$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="AA10" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D10,IF($K$4="C2 Birds in Flight",E10,IF($K$4="C3 Landscape",F10,IF($K$4="Default Settings",G10,IF($K$4="Birds in Flight",H10,IF($K$4="Birds Perched",I10,IF($K$4="Fireworks",J10,IF($K$4="Landscape",K10,IF($K$4="Macro",L10,IF($K$4="People",M10,IF($K$4="Sports",N10,IF($K$4="Travel",O10,IF($K$4="Waterdrops",P10,IF($K$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="AB10" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D10,IF($L$4="C2 Birds in Flight",E10,IF($L$4="C3 Landscape",F10,IF($L$4="Default Settings",G10,IF($L$4="Birds in Flight",H10,IF($L$4="Birds Perched",I10,IF($L$4="Fireworks",J10,IF($L$4="Landscape",K10,IF($L$4="Macro",L10,IF($L$4="People",M10,IF($L$4="Sports",N10,IF($L$4="Travel",O10,IF($L$4="Waterdrops",P10,IF($L$4="Wildlife",Q10,""))))))))))))))</x:f>
+        <x:v>EFCS</x:v>
+      </x:c>
+      <x:c r="AC10" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D10,IF($M$4="C2 Birds in Flight",E10,IF($M$4="C3 Landscape",F10,IF($M$4="Default Settings",G10,IF($M$4="Birds in Flight",H10,IF($M$4="Birds Perched",I10,IF($M$4="Fireworks",J10,IF($M$4="Landscape",K10,IF($M$4="Macro",L10,IF($M$4="People",M10,IF($M$4="Sports",N10,IF($M$4="Travel",O10,IF($M$4="Waterdrops",P10,IF($M$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="Z10" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D10,IF($I$4="C2 Birds in Flight",E10,IF($I$4="C3 Landscape",F10,IF($I$4="Default Settings",G10,IF($I$4="Androo",H10,IF($I$4="Birds in Flight",I10,IF($I$4="Birds Perched",J10,IF($I$4="Fireworks",K10,IF($I$4="Landscape",L10,IF($I$4="Macro",M10,IF($I$4="People",N10,IF($I$4="Sports",O10,IF($I$4="Travel",P10,IF($I$4="Waterdrops",Q10,IF($I$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="AD10" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D10,IF($N$4="C2 Birds in Flight",E10,IF($N$4="C3 Landscape",F10,IF($N$4="Default Settings",G10,IF($N$4="Birds in Flight",H10,IF($N$4="Birds Perched",I10,IF($N$4="Fireworks",J10,IF($N$4="Landscape",K10,IF($N$4="Macro",L10,IF($N$4="People",M10,IF($N$4="Sports",N10,IF($N$4="Travel",O10,IF($N$4="Waterdrops",P10,IF($N$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="AA10" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D10,IF($J$4="C2 Birds in Flight",E10,IF($J$4="C3 Landscape",F10,IF($J$4="Default Settings",G10,IF($J$4="Androo",H10,IF($J$4="Birds in Flight",I10,IF($J$4="Birds Perched",J10,IF($J$4="Fireworks",K10,IF($J$4="Landscape",L10,IF($J$4="Macro",M10,IF($J$4="People",N10,IF($J$4="Sports",O10,IF($J$4="Travel",P10,IF($J$4="Waterdrops",Q10,IF($J$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="AE10" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D10,IF($O$4="C2 Birds in Flight",E10,IF($O$4="C3 Landscape",F10,IF($O$4="Default Settings",G10,IF($O$4="Birds in Flight",H10,IF($O$4="Birds Perched",I10,IF($O$4="Fireworks",J10,IF($O$4="Landscape",K10,IF($O$4="Macro",L10,IF($O$4="People",M10,IF($O$4="Sports",N10,IF($O$4="Travel",O10,IF($O$4="Waterdrops",P10,IF($O$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="AB10" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D10,IF($K$4="C2 Birds in Flight",E10,IF($K$4="C3 Landscape",F10,IF($K$4="Default Settings",G10,IF($K$4="Androo",H10,IF($K$4="Birds in Flight",I10,IF($K$4="Birds Perched",J10,IF($K$4="Fireworks",K10,IF($K$4="Landscape",L10,IF($K$4="Macro",M10,IF($K$4="People",N10,IF($K$4="Sports",O10,IF($K$4="Travel",P10,IF($K$4="Waterdrops",Q10,IF($K$4="Wildlife",R10,"")))))))))))))))</x:f>
-        <x:v>EFCS</x:v>
-      </x:c>
-      <x:c r="AC10" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D10,IF($L$4="C2 Birds in Flight",E10,IF($L$4="C3 Landscape",F10,IF($L$4="Default Settings",G10,IF($L$4="Androo",H10,IF($L$4="Birds in Flight",I10,IF($L$4="Birds Perched",J10,IF($L$4="Fireworks",K10,IF($L$4="Landscape",L10,IF($L$4="Macro",M10,IF($L$4="People",N10,IF($L$4="Sports",O10,IF($L$4="Travel",P10,IF($L$4="Waterdrops",Q10,IF($L$4="Wildlife",R10,"")))))))))))))))</x:f>
-        <x:v>EFCS</x:v>
-      </x:c>
-      <x:c r="AD10" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D10,IF($M$4="C2 Birds in Flight",E10,IF($M$4="C3 Landscape",F10,IF($M$4="Default Settings",G10,IF($M$4="Androo",H10,IF($M$4="Birds in Flight",I10,IF($M$4="Birds Perched",J10,IF($M$4="Fireworks",K10,IF($M$4="Landscape",L10,IF($M$4="Macro",M10,IF($M$4="People",N10,IF($M$4="Sports",O10,IF($M$4="Travel",P10,IF($M$4="Waterdrops",Q10,IF($M$4="Wildlife",R10,"")))))))))))))))</x:f>
-        <x:v>EFCS</x:v>
-      </x:c>
-      <x:c r="AE10" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D10,IF($N$4="C2 Birds in Flight",E10,IF($N$4="C3 Landscape",F10,IF($N$4="Default Settings",G10,IF($N$4="Androo",H10,IF($N$4="Birds in Flight",I10,IF($N$4="Birds Perched",J10,IF($N$4="Fireworks",K10,IF($N$4="Landscape",L10,IF($N$4="Macro",M10,IF($N$4="People",N10,IF($N$4="Sports",O10,IF($N$4="Travel",P10,IF($N$4="Waterdrops",Q10,IF($N$4="Wildlife",R10,"")))))))))))))))</x:f>
+      <x:c r="AF10" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D10,IF($P$4="C2 Birds in Flight",E10,IF($P$4="C3 Landscape",F10,IF($P$4="Default Settings",G10,IF($P$4="Birds in Flight",H10,IF($P$4="Birds Perched",I10,IF($P$4="Fireworks",J10,IF($P$4="Landscape",K10,IF($P$4="Macro",L10,IF($P$4="People",M10,IF($P$4="Sports",N10,IF($P$4="Travel",O10,IF($P$4="Waterdrops",P10,IF($P$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="AF10" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D10,IF($O$4="C2 Birds in Flight",E10,IF($O$4="C3 Landscape",F10,IF($O$4="Default Settings",G10,IF($O$4="Androo",H10,IF($O$4="Birds in Flight",I10,IF($O$4="Birds Perched",J10,IF($O$4="Fireworks",K10,IF($O$4="Landscape",L10,IF($O$4="Macro",M10,IF($O$4="People",N10,IF($O$4="Sports",O10,IF($O$4="Travel",P10,IF($O$4="Waterdrops",Q10,IF($O$4="Wildlife",R10,"")))))))))))))))</x:f>
-        <x:v>Mechanical</x:v>
-      </x:c>
       <x:c r="AG10" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D10,IF($P$4="C2 Birds in Flight",E10,IF($P$4="C3 Landscape",F10,IF($P$4="Default Settings",G10,IF($P$4="Androo",H10,IF($P$4="Birds in Flight",I10,IF($P$4="Birds Perched",J10,IF($P$4="Fireworks",K10,IF($P$4="Landscape",L10,IF($P$4="Macro",M10,IF($P$4="People",N10,IF($P$4="Sports",O10,IF($P$4="Travel",P10,IF($P$4="Waterdrops",Q10,IF($P$4="Wildlife",R10,"")))))))))))))))</x:f>
-        <x:v>EFCS</x:v>
-      </x:c>
-      <x:c r="AH10" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D10,IF($Q$4="C2 Birds in Flight",E10,IF($Q$4="C3 Landscape",F10,IF($Q$4="Default Settings",G10,IF($Q$4="Androo",H10,IF($Q$4="Birds in Flight",I10,IF($Q$4="Birds Perched",J10,IF($Q$4="Fireworks",K10,IF($Q$4="Landscape",L10,IF($Q$4="Macro",M10,IF($Q$4="People",N10,IF($Q$4="Sports",O10,IF($Q$4="Travel",P10,IF($Q$4="Waterdrops",Q10,IF($Q$4="Wildlife",R10,"")))))))))))))))</x:f>
-        <x:v>Mechanical</x:v>
-      </x:c>
-      <x:c r="AI10" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D10,IF($R$4="C2 Birds in Flight",E10,IF($R$4="C3 Landscape",F10,IF($R$4="Default Settings",G10,IF($R$4="Androo",H10,IF($R$4="Birds in Flight",I10,IF($R$4="Birds Perched",J10,IF($R$4="Fireworks",K10,IF($R$4="Landscape",L10,IF($R$4="Macro",M10,IF($R$4="People",N10,IF($R$4="Sports",O10,IF($R$4="Travel",P10,IF($R$4="Waterdrops",Q10,IF($R$4="Wildlife",R10,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D10,IF($Q$4="C2 Birds in Flight",E10,IF($Q$4="C3 Landscape",F10,IF($Q$4="Default Settings",G10,IF($Q$4="Birds in Flight",H10,IF($Q$4="Birds Perched",I10,IF($Q$4="Fireworks",J10,IF($Q$4="Landscape",K10,IF($Q$4="Macro",L10,IF($Q$4="People",M10,IF($Q$4="Sports",N10,IF($Q$4="Travel",O10,IF($Q$4="Waterdrops",P10,IF($Q$4="Wildlife",Q10,""))))))))))))))</x:f>
         <x:v>EFCS</x:v>
       </x:c>
     </x:row>
@@ -1504,103 +1448,96 @@
       <x:c r="G11" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="H11" s="17" t="n">
-        <x:v>5.89</x:v>
+      <x:c r="H11" s="17" t="str">
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="I11" s="17" t="str">
-        <x:v>Auto</x:v>
+        <x:v>f/8</x:v>
       </x:c>
       <x:c r="J11" s="17" t="str">
+        <x:v>f/8–f/11</x:v>
+      </x:c>
+      <x:c r="K11" s="17" t="str">
+        <x:v>f/8–f/11; bracket before f/16</x:v>
+      </x:c>
+      <x:c r="L11" s="17" t="str">
         <x:v>f/8</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="str">
+      <x:c r="M11" s="17" t="str">
+        <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
+      </x:c>
+      <x:c r="N11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P11" s="17" t="str">
         <x:v>f/8–f/11</x:v>
       </x:c>
-      <x:c r="L11" s="17" t="str">
+      <x:c r="Q11" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="R11" s="20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S11" s="20" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="T11" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D11,IF($D$4="C2 Birds in Flight",E11,IF($D$4="C3 Landscape",F11,IF($D$4="Default Settings",G11,IF($D$4="Birds in Flight",H11,IF($D$4="Birds Perched",I11,IF($D$4="Fireworks",J11,IF($D$4="Landscape",K11,IF($D$4="Macro",L11,IF($D$4="People",M11,IF($D$4="Sports",N11,IF($D$4="Travel",O11,IF($D$4="Waterdrops",P11,IF($D$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="U11" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D11,IF($E$4="C2 Birds in Flight",E11,IF($E$4="C3 Landscape",F11,IF($E$4="Default Settings",G11,IF($E$4="Birds in Flight",H11,IF($E$4="Birds Perched",I11,IF($E$4="Fireworks",J11,IF($E$4="Landscape",K11,IF($E$4="Macro",L11,IF($E$4="People",M11,IF($E$4="Sports",N11,IF($E$4="Travel",O11,IF($E$4="Waterdrops",P11,IF($E$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="V11" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D11,IF($F$4="C2 Birds in Flight",E11,IF($F$4="C3 Landscape",F11,IF($F$4="Default Settings",G11,IF($F$4="Birds in Flight",H11,IF($F$4="Birds Perched",I11,IF($F$4="Fireworks",J11,IF($F$4="Landscape",K11,IF($F$4="Macro",L11,IF($F$4="People",M11,IF($F$4="Sports",N11,IF($F$4="Travel",O11,IF($F$4="Waterdrops",P11,IF($F$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/9</x:v>
+      </x:c>
+      <x:c r="W11" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D11,IF($G$4="C2 Birds in Flight",E11,IF($G$4="C3 Landscape",F11,IF($G$4="Default Settings",G11,IF($G$4="Birds in Flight",H11,IF($G$4="Birds Perched",I11,IF($G$4="Fireworks",J11,IF($G$4="Landscape",K11,IF($G$4="Macro",L11,IF($G$4="People",M11,IF($G$4="Sports",N11,IF($G$4="Travel",O11,IF($G$4="Waterdrops",P11,IF($G$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X11" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D11,IF($H$4="C2 Birds in Flight",E11,IF($H$4="C3 Landscape",F11,IF($H$4="Default Settings",G11,IF($H$4="Birds in Flight",H11,IF($H$4="Birds Perched",I11,IF($H$4="Fireworks",J11,IF($H$4="Landscape",K11,IF($H$4="Macro",L11,IF($H$4="People",M11,IF($H$4="Sports",N11,IF($H$4="Travel",O11,IF($H$4="Waterdrops",P11,IF($H$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="Y11" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D11,IF($I$4="C2 Birds in Flight",E11,IF($I$4="C3 Landscape",F11,IF($I$4="Default Settings",G11,IF($I$4="Birds in Flight",H11,IF($I$4="Birds Perched",I11,IF($I$4="Fireworks",J11,IF($I$4="Landscape",K11,IF($I$4="Macro",L11,IF($I$4="People",M11,IF($I$4="Sports",N11,IF($I$4="Travel",O11,IF($I$4="Waterdrops",P11,IF($I$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8</x:v>
+      </x:c>
+      <x:c r="Z11" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D11,IF($J$4="C2 Birds in Flight",E11,IF($J$4="C3 Landscape",F11,IF($J$4="Default Settings",G11,IF($J$4="Birds in Flight",H11,IF($J$4="Birds Perched",I11,IF($J$4="Fireworks",J11,IF($J$4="Landscape",K11,IF($J$4="Macro",L11,IF($J$4="People",M11,IF($J$4="Sports",N11,IF($J$4="Travel",O11,IF($J$4="Waterdrops",P11,IF($J$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>f/8–f/11</x:v>
+      </x:c>
+      <x:c r="AA11" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D11,IF($K$4="C2 Birds in Flight",E11,IF($K$4="C3 Landscape",F11,IF($K$4="Default Settings",G11,IF($K$4="Birds in Flight",H11,IF($K$4="Birds Perched",I11,IF($K$4="Fireworks",J11,IF($K$4="Landscape",K11,IF($K$4="Macro",L11,IF($K$4="People",M11,IF($K$4="Sports",N11,IF($K$4="Travel",O11,IF($K$4="Waterdrops",P11,IF($K$4="Wildlife",Q11,""))))))))))))))</x:f>
         <x:v>f/8–f/11; bracket before f/16</x:v>
       </x:c>
-      <x:c r="M11" s="17" t="str">
+      <x:c r="AB11" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D11,IF($L$4="C2 Birds in Flight",E11,IF($L$4="C3 Landscape",F11,IF($L$4="Default Settings",G11,IF($L$4="Birds in Flight",H11,IF($L$4="Birds Perched",I11,IF($L$4="Fireworks",J11,IF($L$4="Landscape",K11,IF($L$4="Macro",L11,IF($L$4="People",M11,IF($L$4="Sports",N11,IF($L$4="Travel",O11,IF($L$4="Waterdrops",P11,IF($L$4="Wildlife",Q11,""))))))))))))))</x:f>
         <x:v>f/8</x:v>
       </x:c>
-      <x:c r="N11" s="17" t="str">
+      <x:c r="AC11" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D11,IF($M$4="C2 Birds in Flight",E11,IF($M$4="C3 Landscape",F11,IF($M$4="Default Settings",G11,IF($M$4="Birds in Flight",H11,IF($M$4="Birds Perched",I11,IF($M$4="Fireworks",J11,IF($M$4="Landscape",K11,IF($M$4="Macro",L11,IF($M$4="People",M11,IF($M$4="Sports",N11,IF($M$4="Travel",O11,IF($M$4="Waterdrops",P11,IF($M$4="Wildlife",Q11,""))))))))))))))</x:f>
         <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
       </x:c>
-      <x:c r="O11" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="P11" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Q11" s="17" t="str">
+      <x:c r="AD11" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D11,IF($N$4="C2 Birds in Flight",E11,IF($N$4="C3 Landscape",F11,IF($N$4="Default Settings",G11,IF($N$4="Birds in Flight",H11,IF($N$4="Birds Perched",I11,IF($N$4="Fireworks",J11,IF($N$4="Landscape",K11,IF($N$4="Macro",L11,IF($N$4="People",M11,IF($N$4="Sports",N11,IF($N$4="Travel",O11,IF($N$4="Waterdrops",P11,IF($N$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AE11" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D11,IF($O$4="C2 Birds in Flight",E11,IF($O$4="C3 Landscape",F11,IF($O$4="Default Settings",G11,IF($O$4="Birds in Flight",H11,IF($O$4="Birds Perched",I11,IF($O$4="Fireworks",J11,IF($O$4="Landscape",K11,IF($O$4="Macro",L11,IF($O$4="People",M11,IF($O$4="Sports",N11,IF($O$4="Travel",O11,IF($O$4="Waterdrops",P11,IF($O$4="Wildlife",Q11,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF11" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D11,IF($P$4="C2 Birds in Flight",E11,IF($P$4="C3 Landscape",F11,IF($P$4="Default Settings",G11,IF($P$4="Birds in Flight",H11,IF($P$4="Birds Perched",I11,IF($P$4="Fireworks",J11,IF($P$4="Landscape",K11,IF($P$4="Macro",L11,IF($P$4="People",M11,IF($P$4="Sports",N11,IF($P$4="Travel",O11,IF($P$4="Waterdrops",P11,IF($P$4="Wildlife",Q11,""))))))))))))))</x:f>
         <x:v>f/8–f/11</x:v>
       </x:c>
-      <x:c r="R11" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="S11" s="20" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T11" s="20" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U11" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D11,IF($D$4="C2 Birds in Flight",E11,IF($D$4="C3 Landscape",F11,IF($D$4="Default Settings",G11,IF($D$4="Androo",H11,IF($D$4="Birds in Flight",I11,IF($D$4="Birds Perched",J11,IF($D$4="Fireworks",K11,IF($D$4="Landscape",L11,IF($D$4="Macro",M11,IF($D$4="People",N11,IF($D$4="Sports",O11,IF($D$4="Travel",P11,IF($D$4="Waterdrops",Q11,IF($D$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="V11" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D11,IF($E$4="C2 Birds in Flight",E11,IF($E$4="C3 Landscape",F11,IF($E$4="Default Settings",G11,IF($E$4="Androo",H11,IF($E$4="Birds in Flight",I11,IF($E$4="Birds Perched",J11,IF($E$4="Fireworks",K11,IF($E$4="Landscape",L11,IF($E$4="Macro",M11,IF($E$4="People",N11,IF($E$4="Sports",O11,IF($E$4="Travel",P11,IF($E$4="Waterdrops",Q11,IF($E$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="W11" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D11,IF($F$4="C2 Birds in Flight",E11,IF($F$4="C3 Landscape",F11,IF($F$4="Default Settings",G11,IF($F$4="Androo",H11,IF($F$4="Birds in Flight",I11,IF($F$4="Birds Perched",J11,IF($F$4="Fireworks",K11,IF($F$4="Landscape",L11,IF($F$4="Macro",M11,IF($F$4="People",N11,IF($F$4="Sports",O11,IF($F$4="Travel",P11,IF($F$4="Waterdrops",Q11,IF($F$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/9</x:v>
-      </x:c>
-      <x:c r="X11" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D11,IF($G$4="C2 Birds in Flight",E11,IF($G$4="C3 Landscape",F11,IF($G$4="Default Settings",G11,IF($G$4="Androo",H11,IF($G$4="Birds in Flight",I11,IF($G$4="Birds Perched",J11,IF($G$4="Fireworks",K11,IF($G$4="Landscape",L11,IF($G$4="Macro",M11,IF($G$4="People",N11,IF($G$4="Sports",O11,IF($G$4="Travel",P11,IF($G$4="Waterdrops",Q11,IF($G$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Y11" s="38" t="n">
-        <x:f>IF($H$4="C1 Wildlife",D11,IF($H$4="C2 Birds in Flight",E11,IF($H$4="C3 Landscape",F11,IF($H$4="Default Settings",G11,IF($H$4="Androo",H11,IF($H$4="Birds in Flight",I11,IF($H$4="Birds Perched",J11,IF($H$4="Fireworks",K11,IF($H$4="Landscape",L11,IF($H$4="Macro",M11,IF($H$4="People",N11,IF($H$4="Sports",O11,IF($H$4="Travel",P11,IF($H$4="Waterdrops",Q11,IF($H$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>5.89</x:v>
-      </x:c>
-      <x:c r="Z11" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D11,IF($I$4="C2 Birds in Flight",E11,IF($I$4="C3 Landscape",F11,IF($I$4="Default Settings",G11,IF($I$4="Androo",H11,IF($I$4="Birds in Flight",I11,IF($I$4="Birds Perched",J11,IF($I$4="Fireworks",K11,IF($I$4="Landscape",L11,IF($I$4="Macro",M11,IF($I$4="People",N11,IF($I$4="Sports",O11,IF($I$4="Travel",P11,IF($I$4="Waterdrops",Q11,IF($I$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AA11" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D11,IF($J$4="C2 Birds in Flight",E11,IF($J$4="C3 Landscape",F11,IF($J$4="Default Settings",G11,IF($J$4="Androo",H11,IF($J$4="Birds in Flight",I11,IF($J$4="Birds Perched",J11,IF($J$4="Fireworks",K11,IF($J$4="Landscape",L11,IF($J$4="Macro",M11,IF($J$4="People",N11,IF($J$4="Sports",O11,IF($J$4="Travel",P11,IF($J$4="Waterdrops",Q11,IF($J$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/8</x:v>
-      </x:c>
-      <x:c r="AB11" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D11,IF($K$4="C2 Birds in Flight",E11,IF($K$4="C3 Landscape",F11,IF($K$4="Default Settings",G11,IF($K$4="Androo",H11,IF($K$4="Birds in Flight",I11,IF($K$4="Birds Perched",J11,IF($K$4="Fireworks",K11,IF($K$4="Landscape",L11,IF($K$4="Macro",M11,IF($K$4="People",N11,IF($K$4="Sports",O11,IF($K$4="Travel",P11,IF($K$4="Waterdrops",Q11,IF($K$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/8–f/11</x:v>
-      </x:c>
-      <x:c r="AC11" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D11,IF($L$4="C2 Birds in Flight",E11,IF($L$4="C3 Landscape",F11,IF($L$4="Default Settings",G11,IF($L$4="Androo",H11,IF($L$4="Birds in Flight",I11,IF($L$4="Birds Perched",J11,IF($L$4="Fireworks",K11,IF($L$4="Landscape",L11,IF($L$4="Macro",M11,IF($L$4="People",N11,IF($L$4="Sports",O11,IF($L$4="Travel",P11,IF($L$4="Waterdrops",Q11,IF($L$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/8–f/11; bracket before f/16</x:v>
-      </x:c>
-      <x:c r="AD11" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D11,IF($M$4="C2 Birds in Flight",E11,IF($M$4="C3 Landscape",F11,IF($M$4="Default Settings",G11,IF($M$4="Androo",H11,IF($M$4="Birds in Flight",I11,IF($M$4="Birds Perched",J11,IF($M$4="Fireworks",K11,IF($M$4="Landscape",L11,IF($M$4="Macro",M11,IF($M$4="People",N11,IF($M$4="Sports",O11,IF($M$4="Travel",P11,IF($M$4="Waterdrops",Q11,IF($M$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/8</x:v>
-      </x:c>
-      <x:c r="AE11" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D11,IF($N$4="C2 Birds in Flight",E11,IF($N$4="C3 Landscape",F11,IF($N$4="Default Settings",G11,IF($N$4="Androo",H11,IF($N$4="Birds in Flight",I11,IF($N$4="Birds Perched",J11,IF($N$4="Fireworks",K11,IF($N$4="Landscape",L11,IF($N$4="Macro",M11,IF($N$4="People",N11,IF($N$4="Sports",O11,IF($N$4="Travel",P11,IF($N$4="Waterdrops",Q11,IF($N$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/1.8–f/4 single; f/4–f/8 groups</x:v>
-      </x:c>
-      <x:c r="AF11" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D11,IF($O$4="C2 Birds in Flight",E11,IF($O$4="C3 Landscape",F11,IF($O$4="Default Settings",G11,IF($O$4="Androo",H11,IF($O$4="Birds in Flight",I11,IF($O$4="Birds Perched",J11,IF($O$4="Fireworks",K11,IF($O$4="Landscape",L11,IF($O$4="Macro",M11,IF($O$4="People",N11,IF($O$4="Sports",O11,IF($O$4="Travel",P11,IF($O$4="Waterdrops",Q11,IF($O$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="AG11" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D11,IF($P$4="C2 Birds in Flight",E11,IF($P$4="C3 Landscape",F11,IF($P$4="Default Settings",G11,IF($P$4="Androo",H11,IF($P$4="Birds in Flight",I11,IF($P$4="Birds Perched",J11,IF($P$4="Fireworks",K11,IF($P$4="Landscape",L11,IF($P$4="Macro",M11,IF($P$4="People",N11,IF($P$4="Sports",O11,IF($P$4="Travel",P11,IF($P$4="Waterdrops",Q11,IF($P$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AH11" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D11,IF($Q$4="C2 Birds in Flight",E11,IF($Q$4="C3 Landscape",F11,IF($Q$4="Default Settings",G11,IF($Q$4="Androo",H11,IF($Q$4="Birds in Flight",I11,IF($Q$4="Birds Perched",J11,IF($Q$4="Fireworks",K11,IF($Q$4="Landscape",L11,IF($Q$4="Macro",M11,IF($Q$4="People",N11,IF($Q$4="Sports",O11,IF($Q$4="Travel",P11,IF($Q$4="Waterdrops",Q11,IF($Q$4="Wildlife",R11,"")))))))))))))))</x:f>
-        <x:v>f/8–f/11</x:v>
-      </x:c>
-      <x:c r="AI11" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D11,IF($R$4="C2 Birds in Flight",E11,IF($R$4="C3 Landscape",F11,IF($R$4="Default Settings",G11,IF($R$4="Androo",H11,IF($R$4="Birds in Flight",I11,IF($R$4="Birds Perched",J11,IF($R$4="Fireworks",K11,IF($R$4="Landscape",L11,IF($R$4="Macro",M11,IF($R$4="People",N11,IF($R$4="Sports",O11,IF($R$4="Travel",P11,IF($R$4="Waterdrops",Q11,IF($R$4="Wildlife",R11,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D11,IF($Q$4="C2 Birds in Flight",E11,IF($Q$4="C3 Landscape",F11,IF($Q$4="Default Settings",G11,IF($Q$4="Birds in Flight",H11,IF($Q$4="Birds Perched",I11,IF($Q$4="Fireworks",J11,IF($Q$4="Landscape",K11,IF($Q$4="Macro",L11,IF($Q$4="People",M11,IF($Q$4="Sports",N11,IF($Q$4="Travel",O11,IF($Q$4="Waterdrops",P11,IF($Q$4="Wildlife",Q11,""))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
     </x:row>
@@ -1627,19 +1564,19 @@
         <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="H12" s="17" t="str">
-        <x:v>Auto - 3200</x:v>
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="I12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
+      <x:c r="J12" s="17" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="L12" s="17" t="n">
-        <x:v>100</x:v>
+      <x:c r="L12" s="17" t="str">
+        <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="M12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
@@ -1651,78 +1588,71 @@
         <x:v>Auto - 12800</x:v>
       </x:c>
       <x:c r="P12" s="17" t="str">
+        <x:v>100-400</x:v>
+      </x:c>
+      <x:c r="Q12" s="17" t="str">
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="Q12" s="17" t="str">
+      <x:c r="R12" s="20" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S12" s="20" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="T12" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D12,IF($D$4="C2 Birds in Flight",E12,IF($D$4="C3 Landscape",F12,IF($D$4="Default Settings",G12,IF($D$4="Birds in Flight",H12,IF($D$4="Birds Perched",I12,IF($D$4="Fireworks",J12,IF($D$4="Landscape",K12,IF($D$4="Macro",L12,IF($D$4="People",M12,IF($D$4="Sports",N12,IF($D$4="Travel",O12,IF($D$4="Waterdrops",P12,IF($D$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="U12" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D12,IF($E$4="C2 Birds in Flight",E12,IF($E$4="C3 Landscape",F12,IF($E$4="Default Settings",G12,IF($E$4="Birds in Flight",H12,IF($E$4="Birds Perched",I12,IF($E$4="Fireworks",J12,IF($E$4="Landscape",K12,IF($E$4="Macro",L12,IF($E$4="People",M12,IF($E$4="Sports",N12,IF($E$4="Travel",O12,IF($E$4="Waterdrops",P12,IF($E$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="V12" s="38" t="n">
+        <x:f>IF($F$4="C1 Wildlife",D12,IF($F$4="C2 Birds in Flight",E12,IF($F$4="C3 Landscape",F12,IF($F$4="Default Settings",G12,IF($F$4="Birds in Flight",H12,IF($F$4="Birds Perched",I12,IF($F$4="Fireworks",J12,IF($F$4="Landscape",K12,IF($F$4="Macro",L12,IF($F$4="People",M12,IF($F$4="Sports",N12,IF($F$4="Travel",O12,IF($F$4="Waterdrops",P12,IF($F$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="W12" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D12,IF($G$4="C2 Birds in Flight",E12,IF($G$4="C3 Landscape",F12,IF($G$4="Default Settings",G12,IF($G$4="Birds in Flight",H12,IF($G$4="Birds Perched",I12,IF($G$4="Fireworks",J12,IF($G$4="Landscape",K12,IF($G$4="Macro",L12,IF($G$4="People",M12,IF($G$4="Sports",N12,IF($G$4="Travel",O12,IF($G$4="Waterdrops",P12,IF($G$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="X12" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D12,IF($H$4="C2 Birds in Flight",E12,IF($H$4="C3 Landscape",F12,IF($H$4="Default Settings",G12,IF($H$4="Birds in Flight",H12,IF($H$4="Birds Perched",I12,IF($H$4="Fireworks",J12,IF($H$4="Landscape",K12,IF($H$4="Macro",L12,IF($H$4="People",M12,IF($H$4="Sports",N12,IF($H$4="Travel",O12,IF($H$4="Waterdrops",P12,IF($H$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="Y12" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D12,IF($I$4="C2 Birds in Flight",E12,IF($I$4="C3 Landscape",F12,IF($I$4="Default Settings",G12,IF($I$4="Birds in Flight",H12,IF($I$4="Birds Perched",I12,IF($I$4="Fireworks",J12,IF($I$4="Landscape",K12,IF($I$4="Macro",L12,IF($I$4="People",M12,IF($I$4="Sports",N12,IF($I$4="Travel",O12,IF($I$4="Waterdrops",P12,IF($I$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="Z12" s="38" t="n">
+        <x:f>IF($J$4="C1 Wildlife",D12,IF($J$4="C2 Birds in Flight",E12,IF($J$4="C3 Landscape",F12,IF($J$4="Default Settings",G12,IF($J$4="Birds in Flight",H12,IF($J$4="Birds Perched",I12,IF($J$4="Fireworks",J12,IF($J$4="Landscape",K12,IF($J$4="Macro",L12,IF($J$4="People",M12,IF($J$4="Sports",N12,IF($J$4="Travel",O12,IF($J$4="Waterdrops",P12,IF($J$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AA12" s="38" t="n">
+        <x:f>IF($K$4="C1 Wildlife",D12,IF($K$4="C2 Birds in Flight",E12,IF($K$4="C3 Landscape",F12,IF($K$4="Default Settings",G12,IF($K$4="Birds in Flight",H12,IF($K$4="Birds Perched",I12,IF($K$4="Fireworks",J12,IF($K$4="Landscape",K12,IF($K$4="Macro",L12,IF($K$4="People",M12,IF($K$4="Sports",N12,IF($K$4="Travel",O12,IF($K$4="Waterdrops",P12,IF($K$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AB12" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D12,IF($L$4="C2 Birds in Flight",E12,IF($L$4="C3 Landscape",F12,IF($L$4="Default Settings",G12,IF($L$4="Birds in Flight",H12,IF($L$4="Birds Perched",I12,IF($L$4="Fireworks",J12,IF($L$4="Landscape",K12,IF($L$4="Macro",L12,IF($L$4="People",M12,IF($L$4="Sports",N12,IF($L$4="Travel",O12,IF($L$4="Waterdrops",P12,IF($L$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AC12" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D12,IF($M$4="C2 Birds in Flight",E12,IF($M$4="C3 Landscape",F12,IF($M$4="Default Settings",G12,IF($M$4="Birds in Flight",H12,IF($M$4="Birds Perched",I12,IF($M$4="Fireworks",J12,IF($M$4="Landscape",K12,IF($M$4="Macro",L12,IF($M$4="People",M12,IF($M$4="Sports",N12,IF($M$4="Travel",O12,IF($M$4="Waterdrops",P12,IF($M$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AD12" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D12,IF($N$4="C2 Birds in Flight",E12,IF($N$4="C3 Landscape",F12,IF($N$4="Default Settings",G12,IF($N$4="Birds in Flight",H12,IF($N$4="Birds Perched",I12,IF($N$4="Fireworks",J12,IF($N$4="Landscape",K12,IF($N$4="Macro",L12,IF($N$4="People",M12,IF($N$4="Sports",N12,IF($N$4="Travel",O12,IF($N$4="Waterdrops",P12,IF($N$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AE12" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D12,IF($O$4="C2 Birds in Flight",E12,IF($O$4="C3 Landscape",F12,IF($O$4="Default Settings",G12,IF($O$4="Birds in Flight",H12,IF($O$4="Birds Perched",I12,IF($O$4="Fireworks",J12,IF($O$4="Landscape",K12,IF($O$4="Macro",L12,IF($O$4="People",M12,IF($O$4="Sports",N12,IF($O$4="Travel",O12,IF($O$4="Waterdrops",P12,IF($O$4="Wildlife",Q12,""))))))))))))))</x:f>
+        <x:v>Auto - 12800</x:v>
+      </x:c>
+      <x:c r="AF12" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D12,IF($P$4="C2 Birds in Flight",E12,IF($P$4="C3 Landscape",F12,IF($P$4="Default Settings",G12,IF($P$4="Birds in Flight",H12,IF($P$4="Birds Perched",I12,IF($P$4="Fireworks",J12,IF($P$4="Landscape",K12,IF($P$4="Macro",L12,IF($P$4="People",M12,IF($P$4="Sports",N12,IF($P$4="Travel",O12,IF($P$4="Waterdrops",P12,IF($P$4="Wildlife",Q12,""))))))))))))))</x:f>
         <x:v>100-400</x:v>
       </x:c>
-      <x:c r="R12" s="17" t="str">
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="S12" s="20" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="T12" s="20" t="n">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="U12" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D12,IF($D$4="C2 Birds in Flight",E12,IF($D$4="C3 Landscape",F12,IF($D$4="Default Settings",G12,IF($D$4="Androo",H12,IF($D$4="Birds in Flight",I12,IF($D$4="Birds Perched",J12,IF($D$4="Fireworks",K12,IF($D$4="Landscape",L12,IF($D$4="Macro",M12,IF($D$4="People",N12,IF($D$4="Sports",O12,IF($D$4="Travel",P12,IF($D$4="Waterdrops",Q12,IF($D$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="V12" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D12,IF($E$4="C2 Birds in Flight",E12,IF($E$4="C3 Landscape",F12,IF($E$4="Default Settings",G12,IF($E$4="Androo",H12,IF($E$4="Birds in Flight",I12,IF($E$4="Birds Perched",J12,IF($E$4="Fireworks",K12,IF($E$4="Landscape",L12,IF($E$4="Macro",M12,IF($E$4="People",N12,IF($E$4="Sports",O12,IF($E$4="Travel",P12,IF($E$4="Waterdrops",Q12,IF($E$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="W12" s="38" t="n">
-        <x:f>IF($F$4="C1 Wildlife",D12,IF($F$4="C2 Birds in Flight",E12,IF($F$4="C3 Landscape",F12,IF($F$4="Default Settings",G12,IF($F$4="Androo",H12,IF($F$4="Birds in Flight",I12,IF($F$4="Birds Perched",J12,IF($F$4="Fireworks",K12,IF($F$4="Landscape",L12,IF($F$4="Macro",M12,IF($F$4="People",N12,IF($F$4="Sports",O12,IF($F$4="Travel",P12,IF($F$4="Waterdrops",Q12,IF($F$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="X12" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D12,IF($G$4="C2 Birds in Flight",E12,IF($G$4="C3 Landscape",F12,IF($G$4="Default Settings",G12,IF($G$4="Androo",H12,IF($G$4="Birds in Flight",I12,IF($G$4="Birds Perched",J12,IF($G$4="Fireworks",K12,IF($G$4="Landscape",L12,IF($G$4="Macro",M12,IF($G$4="People",N12,IF($G$4="Sports",O12,IF($G$4="Travel",P12,IF($G$4="Waterdrops",Q12,IF($G$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="Y12" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D12,IF($H$4="C2 Birds in Flight",E12,IF($H$4="C3 Landscape",F12,IF($H$4="Default Settings",G12,IF($H$4="Androo",H12,IF($H$4="Birds in Flight",I12,IF($H$4="Birds Perched",J12,IF($H$4="Fireworks",K12,IF($H$4="Landscape",L12,IF($H$4="Macro",M12,IF($H$4="People",N12,IF($H$4="Sports",O12,IF($H$4="Travel",P12,IF($H$4="Waterdrops",Q12,IF($H$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 3200</x:v>
-      </x:c>
-      <x:c r="Z12" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D12,IF($I$4="C2 Birds in Flight",E12,IF($I$4="C3 Landscape",F12,IF($I$4="Default Settings",G12,IF($I$4="Androo",H12,IF($I$4="Birds in Flight",I12,IF($I$4="Birds Perched",J12,IF($I$4="Fireworks",K12,IF($I$4="Landscape",L12,IF($I$4="Macro",M12,IF($I$4="People",N12,IF($I$4="Sports",O12,IF($I$4="Travel",P12,IF($I$4="Waterdrops",Q12,IF($I$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="AA12" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D12,IF($J$4="C2 Birds in Flight",E12,IF($J$4="C3 Landscape",F12,IF($J$4="Default Settings",G12,IF($J$4="Androo",H12,IF($J$4="Birds in Flight",I12,IF($J$4="Birds Perched",J12,IF($J$4="Fireworks",K12,IF($J$4="Landscape",L12,IF($J$4="Macro",M12,IF($J$4="People",N12,IF($J$4="Sports",O12,IF($J$4="Travel",P12,IF($J$4="Waterdrops",Q12,IF($J$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="AB12" s="38" t="n">
-        <x:f>IF($K$4="C1 Wildlife",D12,IF($K$4="C2 Birds in Flight",E12,IF($K$4="C3 Landscape",F12,IF($K$4="Default Settings",G12,IF($K$4="Androo",H12,IF($K$4="Birds in Flight",I12,IF($K$4="Birds Perched",J12,IF($K$4="Fireworks",K12,IF($K$4="Landscape",L12,IF($K$4="Macro",M12,IF($K$4="People",N12,IF($K$4="Sports",O12,IF($K$4="Travel",P12,IF($K$4="Waterdrops",Q12,IF($K$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AC12" s="38" t="n">
-        <x:f>IF($L$4="C1 Wildlife",D12,IF($L$4="C2 Birds in Flight",E12,IF($L$4="C3 Landscape",F12,IF($L$4="Default Settings",G12,IF($L$4="Androo",H12,IF($L$4="Birds in Flight",I12,IF($L$4="Birds Perched",J12,IF($L$4="Fireworks",K12,IF($L$4="Landscape",L12,IF($L$4="Macro",M12,IF($L$4="People",N12,IF($L$4="Sports",O12,IF($L$4="Travel",P12,IF($L$4="Waterdrops",Q12,IF($L$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="AD12" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D12,IF($M$4="C2 Birds in Flight",E12,IF($M$4="C3 Landscape",F12,IF($M$4="Default Settings",G12,IF($M$4="Androo",H12,IF($M$4="Birds in Flight",I12,IF($M$4="Birds Perched",J12,IF($M$4="Fireworks",K12,IF($M$4="Landscape",L12,IF($M$4="Macro",M12,IF($M$4="People",N12,IF($M$4="Sports",O12,IF($M$4="Travel",P12,IF($M$4="Waterdrops",Q12,IF($M$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="AE12" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D12,IF($N$4="C2 Birds in Flight",E12,IF($N$4="C3 Landscape",F12,IF($N$4="Default Settings",G12,IF($N$4="Androo",H12,IF($N$4="Birds in Flight",I12,IF($N$4="Birds Perched",J12,IF($N$4="Fireworks",K12,IF($N$4="Landscape",L12,IF($N$4="Macro",M12,IF($N$4="People",N12,IF($N$4="Sports",O12,IF($N$4="Travel",P12,IF($N$4="Waterdrops",Q12,IF($N$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="AF12" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D12,IF($O$4="C2 Birds in Flight",E12,IF($O$4="C3 Landscape",F12,IF($O$4="Default Settings",G12,IF($O$4="Androo",H12,IF($O$4="Birds in Flight",I12,IF($O$4="Birds Perched",J12,IF($O$4="Fireworks",K12,IF($O$4="Landscape",L12,IF($O$4="Macro",M12,IF($O$4="People",N12,IF($O$4="Sports",O12,IF($O$4="Travel",P12,IF($O$4="Waterdrops",Q12,IF($O$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
       <x:c r="AG12" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D12,IF($P$4="C2 Birds in Flight",E12,IF($P$4="C3 Landscape",F12,IF($P$4="Default Settings",G12,IF($P$4="Androo",H12,IF($P$4="Birds in Flight",I12,IF($P$4="Birds Perched",J12,IF($P$4="Fireworks",K12,IF($P$4="Landscape",L12,IF($P$4="Macro",M12,IF($P$4="People",N12,IF($P$4="Sports",O12,IF($P$4="Travel",P12,IF($P$4="Waterdrops",Q12,IF($P$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>Auto - 12800</x:v>
-      </x:c>
-      <x:c r="AH12" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D12,IF($Q$4="C2 Birds in Flight",E12,IF($Q$4="C3 Landscape",F12,IF($Q$4="Default Settings",G12,IF($Q$4="Androo",H12,IF($Q$4="Birds in Flight",I12,IF($Q$4="Birds Perched",J12,IF($Q$4="Fireworks",K12,IF($Q$4="Landscape",L12,IF($Q$4="Macro",M12,IF($Q$4="People",N12,IF($Q$4="Sports",O12,IF($Q$4="Travel",P12,IF($Q$4="Waterdrops",Q12,IF($Q$4="Wildlife",R12,"")))))))))))))))</x:f>
-        <x:v>100-400</x:v>
-      </x:c>
-      <x:c r="AI12" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D12,IF($R$4="C2 Birds in Flight",E12,IF($R$4="C3 Landscape",F12,IF($R$4="Default Settings",G12,IF($R$4="Androo",H12,IF($R$4="Birds in Flight",I12,IF($R$4="Birds Perched",J12,IF($R$4="Fireworks",K12,IF($R$4="Landscape",L12,IF($R$4="Macro",M12,IF($R$4="People",N12,IF($R$4="Sports",O12,IF($R$4="Travel",P12,IF($R$4="Waterdrops",Q12,IF($R$4="Wildlife",R12,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D12,IF($Q$4="C2 Birds in Flight",E12,IF($Q$4="C3 Landscape",F12,IF($Q$4="Default Settings",G12,IF($Q$4="Birds in Flight",H12,IF($Q$4="Birds Perched",I12,IF($Q$4="Fireworks",J12,IF($Q$4="Landscape",K12,IF($Q$4="Macro",L12,IF($Q$4="People",M12,IF($Q$4="Sports",N12,IF($Q$4="Travel",O12,IF($Q$4="Waterdrops",P12,IF($Q$4="Wildlife",Q12,""))))))))))))))</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
     </x:row>
@@ -1748,14 +1678,14 @@
       <x:c r="G13" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H13" s="17" t="n">
+      <x:c r="H13" s="17" t="str">
+        <x:v>Adjust for background</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
+        <x:v>0 to +1/3</x:v>
+      </x:c>
+      <x:c r="J13" s="17" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="17" t="str">
-        <x:v>Adjust for background</x:v>
-      </x:c>
-      <x:c r="J13" s="17" t="str">
-        <x:v>0 to +1/3</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>0</x:v>
@@ -1778,73 +1708,66 @@
       <x:c r="Q13" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R13" s="17" t="n">
+      <x:c r="R13" s="20" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S13" s="20" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="T13" s="38" t="n">
+        <x:f>IF($D$4="C1 Wildlife",D13,IF($D$4="C2 Birds in Flight",E13,IF($D$4="C3 Landscape",F13,IF($D$4="Default Settings",G13,IF($D$4="Birds in Flight",H13,IF($D$4="Birds Perched",I13,IF($D$4="Fireworks",J13,IF($D$4="Landscape",K13,IF($D$4="Macro",L13,IF($D$4="People",M13,IF($D$4="Sports",N13,IF($D$4="Travel",O13,IF($D$4="Waterdrops",P13,IF($D$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T13" s="20" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="U13" s="38" t="n">
-        <x:f>IF($D$4="C1 Wildlife",D13,IF($D$4="C2 Birds in Flight",E13,IF($D$4="C3 Landscape",F13,IF($D$4="Default Settings",G13,IF($D$4="Androo",H13,IF($D$4="Birds in Flight",I13,IF($D$4="Birds Perched",J13,IF($D$4="Fireworks",K13,IF($D$4="Landscape",L13,IF($D$4="Macro",M13,IF($D$4="People",N13,IF($D$4="Sports",O13,IF($D$4="Travel",P13,IF($D$4="Waterdrops",Q13,IF($D$4="Wildlife",R13,"")))))))))))))))</x:f>
+      <x:c r="U13" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D13,IF($E$4="C2 Birds in Flight",E13,IF($E$4="C3 Landscape",F13,IF($E$4="Default Settings",G13,IF($E$4="Birds in Flight",H13,IF($E$4="Birds Perched",I13,IF($E$4="Fireworks",J13,IF($E$4="Landscape",K13,IF($E$4="Macro",L13,IF($E$4="People",M13,IF($E$4="Sports",N13,IF($E$4="Travel",O13,IF($E$4="Waterdrops",P13,IF($E$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="V13" s="38" t="n">
+        <x:f>IF($F$4="C1 Wildlife",D13,IF($F$4="C2 Birds in Flight",E13,IF($F$4="C3 Landscape",F13,IF($F$4="Default Settings",G13,IF($F$4="Birds in Flight",H13,IF($F$4="Birds Perched",I13,IF($F$4="Fireworks",J13,IF($F$4="Landscape",K13,IF($F$4="Macro",L13,IF($F$4="People",M13,IF($F$4="Sports",N13,IF($F$4="Travel",O13,IF($F$4="Waterdrops",P13,IF($F$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V13" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D13,IF($E$4="C2 Birds in Flight",E13,IF($E$4="C3 Landscape",F13,IF($E$4="Default Settings",G13,IF($E$4="Androo",H13,IF($E$4="Birds in Flight",I13,IF($E$4="Birds Perched",J13,IF($E$4="Fireworks",K13,IF($E$4="Landscape",L13,IF($E$4="Macro",M13,IF($E$4="People",N13,IF($E$4="Sports",O13,IF($E$4="Travel",P13,IF($E$4="Waterdrops",Q13,IF($E$4="Wildlife",R13,"")))))))))))))))</x:f>
-        <x:v>0 starting point</x:v>
-      </x:c>
       <x:c r="W13" s="38" t="n">
-        <x:f>IF($F$4="C1 Wildlife",D13,IF($F$4="C2 Birds in Flight",E13,IF($F$4="C3 Landscape",F13,IF($F$4="Default Settings",G13,IF($F$4="Androo",H13,IF($F$4="Birds in Flight",I13,IF($F$4="Birds Perched",J13,IF($F$4="Fireworks",K13,IF($F$4="Landscape",L13,IF($F$4="Macro",M13,IF($F$4="People",N13,IF($F$4="Sports",O13,IF($F$4="Travel",P13,IF($F$4="Waterdrops",Q13,IF($F$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($G$4="C1 Wildlife",D13,IF($G$4="C2 Birds in Flight",E13,IF($G$4="C3 Landscape",F13,IF($G$4="Default Settings",G13,IF($G$4="Birds in Flight",H13,IF($G$4="Birds Perched",I13,IF($G$4="Fireworks",J13,IF($G$4="Landscape",K13,IF($G$4="Macro",L13,IF($G$4="People",M13,IF($G$4="Sports",N13,IF($G$4="Travel",O13,IF($G$4="Waterdrops",P13,IF($G$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X13" s="38" t="n">
-        <x:f>IF($G$4="C1 Wildlife",D13,IF($G$4="C2 Birds in Flight",E13,IF($G$4="C3 Landscape",F13,IF($G$4="Default Settings",G13,IF($G$4="Androo",H13,IF($G$4="Birds in Flight",I13,IF($G$4="Birds Perched",J13,IF($G$4="Fireworks",K13,IF($G$4="Landscape",L13,IF($G$4="Macro",M13,IF($G$4="People",N13,IF($G$4="Sports",O13,IF($G$4="Travel",P13,IF($G$4="Waterdrops",Q13,IF($G$4="Wildlife",R13,"")))))))))))))))</x:f>
+      <x:c r="X13" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D13,IF($H$4="C2 Birds in Flight",E13,IF($H$4="C3 Landscape",F13,IF($H$4="Default Settings",G13,IF($H$4="Birds in Flight",H13,IF($H$4="Birds Perched",I13,IF($H$4="Fireworks",J13,IF($H$4="Landscape",K13,IF($H$4="Macro",L13,IF($H$4="People",M13,IF($H$4="Sports",N13,IF($H$4="Travel",O13,IF($H$4="Waterdrops",P13,IF($H$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>Adjust for background</x:v>
+      </x:c>
+      <x:c r="Y13" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D13,IF($I$4="C2 Birds in Flight",E13,IF($I$4="C3 Landscape",F13,IF($I$4="Default Settings",G13,IF($I$4="Birds in Flight",H13,IF($I$4="Birds Perched",I13,IF($I$4="Fireworks",J13,IF($I$4="Landscape",K13,IF($I$4="Macro",L13,IF($I$4="People",M13,IF($I$4="Sports",N13,IF($I$4="Travel",O13,IF($I$4="Waterdrops",P13,IF($I$4="Wildlife",Q13,""))))))))))))))</x:f>
+        <x:v>0 to +1/3</x:v>
+      </x:c>
+      <x:c r="Z13" s="38" t="n">
+        <x:f>IF($J$4="C1 Wildlife",D13,IF($J$4="C2 Birds in Flight",E13,IF($J$4="C3 Landscape",F13,IF($J$4="Default Settings",G13,IF($J$4="Birds in Flight",H13,IF($J$4="Birds Perched",I13,IF($J$4="Fireworks",J13,IF($J$4="Landscape",K13,IF($J$4="Macro",L13,IF($J$4="People",M13,IF($J$4="Sports",N13,IF($J$4="Travel",O13,IF($J$4="Waterdrops",P13,IF($J$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y13" s="38" t="n">
-        <x:f>IF($H$4="C1 Wildlife",D13,IF($H$4="C2 Birds in Flight",E13,IF($H$4="C3 Landscape",F13,IF($H$4="Default Settings",G13,IF($H$4="Androo",H13,IF($H$4="Birds in Flight",I13,IF($H$4="Birds Perched",J13,IF($H$4="Fireworks",K13,IF($H$4="Landscape",L13,IF($H$4="Macro",M13,IF($H$4="People",N13,IF($H$4="Sports",O13,IF($H$4="Travel",P13,IF($H$4="Waterdrops",Q13,IF($H$4="Wildlife",R13,"")))))))))))))))</x:f>
+      <x:c r="AA13" s="38" t="n">
+        <x:f>IF($K$4="C1 Wildlife",D13,IF($K$4="C2 Birds in Flight",E13,IF($K$4="C3 Landscape",F13,IF($K$4="Default Settings",G13,IF($K$4="Birds in Flight",H13,IF($K$4="Birds Perched",I13,IF($K$4="Fireworks",J13,IF($K$4="Landscape",K13,IF($K$4="Macro",L13,IF($K$4="People",M13,IF($K$4="Sports",N13,IF($K$4="Travel",O13,IF($K$4="Waterdrops",P13,IF($K$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Z13" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D13,IF($I$4="C2 Birds in Flight",E13,IF($I$4="C3 Landscape",F13,IF($I$4="Default Settings",G13,IF($I$4="Androo",H13,IF($I$4="Birds in Flight",I13,IF($I$4="Birds Perched",J13,IF($I$4="Fireworks",K13,IF($I$4="Landscape",L13,IF($I$4="Macro",M13,IF($I$4="People",N13,IF($I$4="Sports",O13,IF($I$4="Travel",P13,IF($I$4="Waterdrops",Q13,IF($I$4="Wildlife",R13,"")))))))))))))))</x:f>
-        <x:v>Adjust for background</x:v>
-      </x:c>
-      <x:c r="AA13" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D13,IF($J$4="C2 Birds in Flight",E13,IF($J$4="C3 Landscape",F13,IF($J$4="Default Settings",G13,IF($J$4="Androo",H13,IF($J$4="Birds in Flight",I13,IF($J$4="Birds Perched",J13,IF($J$4="Fireworks",K13,IF($J$4="Landscape",L13,IF($J$4="Macro",M13,IF($J$4="People",N13,IF($J$4="Sports",O13,IF($J$4="Travel",P13,IF($J$4="Waterdrops",Q13,IF($J$4="Wildlife",R13,"")))))))))))))))</x:f>
-        <x:v>0 to +1/3</x:v>
-      </x:c>
       <x:c r="AB13" s="38" t="n">
-        <x:f>IF($K$4="C1 Wildlife",D13,IF($K$4="C2 Birds in Flight",E13,IF($K$4="C3 Landscape",F13,IF($K$4="Default Settings",G13,IF($K$4="Androo",H13,IF($K$4="Birds in Flight",I13,IF($K$4="Birds Perched",J13,IF($K$4="Fireworks",K13,IF($K$4="Landscape",L13,IF($K$4="Macro",M13,IF($K$4="People",N13,IF($K$4="Sports",O13,IF($K$4="Travel",P13,IF($K$4="Waterdrops",Q13,IF($K$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D13,IF($L$4="C2 Birds in Flight",E13,IF($L$4="C3 Landscape",F13,IF($L$4="Default Settings",G13,IF($L$4="Birds in Flight",H13,IF($L$4="Birds Perched",I13,IF($L$4="Fireworks",J13,IF($L$4="Landscape",K13,IF($L$4="Macro",L13,IF($L$4="People",M13,IF($L$4="Sports",N13,IF($L$4="Travel",O13,IF($L$4="Waterdrops",P13,IF($L$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AC13" s="38" t="n">
-        <x:f>IF($L$4="C1 Wildlife",D13,IF($L$4="C2 Birds in Flight",E13,IF($L$4="C3 Landscape",F13,IF($L$4="Default Settings",G13,IF($L$4="Androo",H13,IF($L$4="Birds in Flight",I13,IF($L$4="Birds Perched",J13,IF($L$4="Fireworks",K13,IF($L$4="Landscape",L13,IF($L$4="Macro",M13,IF($L$4="People",N13,IF($L$4="Sports",O13,IF($L$4="Travel",P13,IF($L$4="Waterdrops",Q13,IF($L$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($M$4="C1 Wildlife",D13,IF($M$4="C2 Birds in Flight",E13,IF($M$4="C3 Landscape",F13,IF($M$4="Default Settings",G13,IF($M$4="Birds in Flight",H13,IF($M$4="Birds Perched",I13,IF($M$4="Fireworks",J13,IF($M$4="Landscape",K13,IF($M$4="Macro",L13,IF($M$4="People",M13,IF($M$4="Sports",N13,IF($M$4="Travel",O13,IF($M$4="Waterdrops",P13,IF($M$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AD13" s="38" t="n">
-        <x:f>IF($M$4="C1 Wildlife",D13,IF($M$4="C2 Birds in Flight",E13,IF($M$4="C3 Landscape",F13,IF($M$4="Default Settings",G13,IF($M$4="Androo",H13,IF($M$4="Birds in Flight",I13,IF($M$4="Birds Perched",J13,IF($M$4="Fireworks",K13,IF($M$4="Landscape",L13,IF($M$4="Macro",M13,IF($M$4="People",N13,IF($M$4="Sports",O13,IF($M$4="Travel",P13,IF($M$4="Waterdrops",Q13,IF($M$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($N$4="C1 Wildlife",D13,IF($N$4="C2 Birds in Flight",E13,IF($N$4="C3 Landscape",F13,IF($N$4="Default Settings",G13,IF($N$4="Birds in Flight",H13,IF($N$4="Birds Perched",I13,IF($N$4="Fireworks",J13,IF($N$4="Landscape",K13,IF($N$4="Macro",L13,IF($N$4="People",M13,IF($N$4="Sports",N13,IF($N$4="Travel",O13,IF($N$4="Waterdrops",P13,IF($N$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AE13" s="38" t="n">
-        <x:f>IF($N$4="C1 Wildlife",D13,IF($N$4="C2 Birds in Flight",E13,IF($N$4="C3 Landscape",F13,IF($N$4="Default Settings",G13,IF($N$4="Androo",H13,IF($N$4="Birds in Flight",I13,IF($N$4="Birds Perched",J13,IF($N$4="Fireworks",K13,IF($N$4="Landscape",L13,IF($N$4="Macro",M13,IF($N$4="People",N13,IF($N$4="Sports",O13,IF($N$4="Travel",P13,IF($N$4="Waterdrops",Q13,IF($N$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D13,IF($O$4="C2 Birds in Flight",E13,IF($O$4="C3 Landscape",F13,IF($O$4="Default Settings",G13,IF($O$4="Birds in Flight",H13,IF($O$4="Birds Perched",I13,IF($O$4="Fireworks",J13,IF($O$4="Landscape",K13,IF($O$4="Macro",L13,IF($O$4="People",M13,IF($O$4="Sports",N13,IF($O$4="Travel",O13,IF($O$4="Waterdrops",P13,IF($O$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AF13" s="38" t="n">
-        <x:f>IF($O$4="C1 Wildlife",D13,IF($O$4="C2 Birds in Flight",E13,IF($O$4="C3 Landscape",F13,IF($O$4="Default Settings",G13,IF($O$4="Androo",H13,IF($O$4="Birds in Flight",I13,IF($O$4="Birds Perched",J13,IF($O$4="Fireworks",K13,IF($O$4="Landscape",L13,IF($O$4="Macro",M13,IF($O$4="People",N13,IF($O$4="Sports",O13,IF($O$4="Travel",P13,IF($O$4="Waterdrops",Q13,IF($O$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D13,IF($P$4="C2 Birds in Flight",E13,IF($P$4="C3 Landscape",F13,IF($P$4="Default Settings",G13,IF($P$4="Birds in Flight",H13,IF($P$4="Birds Perched",I13,IF($P$4="Fireworks",J13,IF($P$4="Landscape",K13,IF($P$4="Macro",L13,IF($P$4="People",M13,IF($P$4="Sports",N13,IF($P$4="Travel",O13,IF($P$4="Waterdrops",P13,IF($P$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="AG13" s="38" t="n">
-        <x:f>IF($P$4="C1 Wildlife",D13,IF($P$4="C2 Birds in Flight",E13,IF($P$4="C3 Landscape",F13,IF($P$4="Default Settings",G13,IF($P$4="Androo",H13,IF($P$4="Birds in Flight",I13,IF($P$4="Birds Perched",J13,IF($P$4="Fireworks",K13,IF($P$4="Landscape",L13,IF($P$4="Macro",M13,IF($P$4="People",N13,IF($P$4="Sports",O13,IF($P$4="Travel",P13,IF($P$4="Waterdrops",Q13,IF($P$4="Wildlife",R13,"")))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH13" s="38" t="n">
-        <x:f>IF($Q$4="C1 Wildlife",D13,IF($Q$4="C2 Birds in Flight",E13,IF($Q$4="C3 Landscape",F13,IF($Q$4="Default Settings",G13,IF($Q$4="Androo",H13,IF($Q$4="Birds in Flight",I13,IF($Q$4="Birds Perched",J13,IF($Q$4="Fireworks",K13,IF($Q$4="Landscape",L13,IF($Q$4="Macro",M13,IF($Q$4="People",N13,IF($Q$4="Sports",O13,IF($Q$4="Travel",P13,IF($Q$4="Waterdrops",Q13,IF($Q$4="Wildlife",R13,"")))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AI13" s="38" t="n">
-        <x:f>IF($R$4="C1 Wildlife",D13,IF($R$4="C2 Birds in Flight",E13,IF($R$4="C3 Landscape",F13,IF($R$4="Default Settings",G13,IF($R$4="Androo",H13,IF($R$4="Birds in Flight",I13,IF($R$4="Birds Perched",J13,IF($R$4="Fireworks",K13,IF($R$4="Landscape",L13,IF($R$4="Macro",M13,IF($R$4="People",N13,IF($R$4="Sports",O13,IF($R$4="Travel",P13,IF($R$4="Waterdrops",Q13,IF($R$4="Wildlife",R13,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D13,IF($Q$4="C2 Birds in Flight",E13,IF($Q$4="C3 Landscape",F13,IF($Q$4="Default Settings",G13,IF($Q$4="Birds in Flight",H13,IF($Q$4="Birds Perched",I13,IF($Q$4="Fireworks",J13,IF($Q$4="Landscape",K13,IF($Q$4="Macro",L13,IF($Q$4="People",M13,IF($Q$4="Sports",N13,IF($Q$4="Travel",O13,IF($Q$4="Waterdrops",P13,IF($Q$4="Wildlife",Q13,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1871,22 +1794,22 @@
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="H14" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="I14" s="17" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="J14" s="17" t="str">
-        <x:v>Servo AF</x:v>
+        <x:v>Manual Focus</x:v>
       </x:c>
       <x:c r="K14" s="17" t="str">
-        <x:v>Manual Focus</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="L14" s="17" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="M14" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="N14" s="17" t="str">
         <x:v>Servo AF</x:v>
@@ -1895,78 +1818,71 @@
         <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="P14" s="17" t="str">
+        <x:v>Manual Focus</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="str">
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="Q14" s="17" t="str">
+      <x:c r="R14" s="20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="S14" s="20" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="T14" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D14,IF($D$4="C2 Birds in Flight",E14,IF($D$4="C3 Landscape",F14,IF($D$4="Default Settings",G14,IF($D$4="Birds in Flight",H14,IF($D$4="Birds Perched",I14,IF($D$4="Fireworks",J14,IF($D$4="Landscape",K14,IF($D$4="Macro",L14,IF($D$4="People",M14,IF($D$4="Sports",N14,IF($D$4="Travel",O14,IF($D$4="Waterdrops",P14,IF($D$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="U14" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D14,IF($E$4="C2 Birds in Flight",E14,IF($E$4="C3 Landscape",F14,IF($E$4="Default Settings",G14,IF($E$4="Birds in Flight",H14,IF($E$4="Birds Perched",I14,IF($E$4="Fireworks",J14,IF($E$4="Landscape",K14,IF($E$4="Macro",L14,IF($E$4="People",M14,IF($E$4="Sports",N14,IF($E$4="Travel",O14,IF($E$4="Waterdrops",P14,IF($E$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="V14" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D14,IF($F$4="C2 Birds in Flight",E14,IF($F$4="C3 Landscape",F14,IF($F$4="Default Settings",G14,IF($F$4="Birds in Flight",H14,IF($F$4="Birds Perched",I14,IF($F$4="Fireworks",J14,IF($F$4="Landscape",K14,IF($F$4="Macro",L14,IF($F$4="People",M14,IF($F$4="Sports",N14,IF($F$4="Travel",O14,IF($F$4="Waterdrops",P14,IF($F$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="W14" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D14,IF($G$4="C2 Birds in Flight",E14,IF($G$4="C3 Landscape",F14,IF($G$4="Default Settings",G14,IF($G$4="Birds in Flight",H14,IF($G$4="Birds Perched",I14,IF($G$4="Fireworks",J14,IF($G$4="Landscape",K14,IF($G$4="Macro",L14,IF($G$4="People",M14,IF($G$4="Sports",N14,IF($G$4="Travel",O14,IF($G$4="Waterdrops",P14,IF($G$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="X14" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D14,IF($H$4="C2 Birds in Flight",E14,IF($H$4="C3 Landscape",F14,IF($H$4="Default Settings",G14,IF($H$4="Birds in Flight",H14,IF($H$4="Birds Perched",I14,IF($H$4="Fireworks",J14,IF($H$4="Landscape",K14,IF($H$4="Macro",L14,IF($H$4="People",M14,IF($H$4="Sports",N14,IF($H$4="Travel",O14,IF($H$4="Waterdrops",P14,IF($H$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Y14" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D14,IF($I$4="C2 Birds in Flight",E14,IF($I$4="C3 Landscape",F14,IF($I$4="Default Settings",G14,IF($I$4="Birds in Flight",H14,IF($I$4="Birds Perched",I14,IF($I$4="Fireworks",J14,IF($I$4="Landscape",K14,IF($I$4="Macro",L14,IF($I$4="People",M14,IF($I$4="Sports",N14,IF($I$4="Travel",O14,IF($I$4="Waterdrops",P14,IF($I$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Z14" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D14,IF($J$4="C2 Birds in Flight",E14,IF($J$4="C3 Landscape",F14,IF($J$4="Default Settings",G14,IF($J$4="Birds in Flight",H14,IF($J$4="Birds Perched",I14,IF($J$4="Fireworks",J14,IF($J$4="Landscape",K14,IF($J$4="Macro",L14,IF($J$4="People",M14,IF($J$4="Sports",N14,IF($J$4="Travel",O14,IF($J$4="Waterdrops",P14,IF($J$4="Wildlife",Q14,""))))))))))))))</x:f>
         <x:v>Manual Focus</x:v>
       </x:c>
-      <x:c r="R14" s="17" t="str">
+      <x:c r="AA14" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D14,IF($K$4="C2 Birds in Flight",E14,IF($K$4="C3 Landscape",F14,IF($K$4="Default Settings",G14,IF($K$4="Birds in Flight",H14,IF($K$4="Birds Perched",I14,IF($K$4="Fireworks",J14,IF($K$4="Landscape",K14,IF($K$4="Macro",L14,IF($K$4="People",M14,IF($K$4="Sports",N14,IF($K$4="Travel",O14,IF($K$4="Waterdrops",P14,IF($K$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="AB14" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D14,IF($L$4="C2 Birds in Flight",E14,IF($L$4="C3 Landscape",F14,IF($L$4="Default Settings",G14,IF($L$4="Birds in Flight",H14,IF($L$4="Birds Perched",I14,IF($L$4="Fireworks",J14,IF($L$4="Landscape",K14,IF($L$4="Macro",L14,IF($L$4="People",M14,IF($L$4="Sports",N14,IF($L$4="Travel",O14,IF($L$4="Waterdrops",P14,IF($L$4="Wildlife",Q14,""))))))))))))))</x:f>
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="AC14" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D14,IF($M$4="C2 Birds in Flight",E14,IF($M$4="C3 Landscape",F14,IF($M$4="Default Settings",G14,IF($M$4="Birds in Flight",H14,IF($M$4="Birds Perched",I14,IF($M$4="Fireworks",J14,IF($M$4="Landscape",K14,IF($M$4="Macro",L14,IF($M$4="People",M14,IF($M$4="Sports",N14,IF($M$4="Travel",O14,IF($M$4="Waterdrops",P14,IF($M$4="Wildlife",Q14,""))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="S14" s="20" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T14" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="U14" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D14,IF($D$4="C2 Birds in Flight",E14,IF($D$4="C3 Landscape",F14,IF($D$4="Default Settings",G14,IF($D$4="Androo",H14,IF($D$4="Birds in Flight",I14,IF($D$4="Birds Perched",J14,IF($D$4="Fireworks",K14,IF($D$4="Landscape",L14,IF($D$4="Macro",M14,IF($D$4="People",N14,IF($D$4="Sports",O14,IF($D$4="Travel",P14,IF($D$4="Waterdrops",Q14,IF($D$4="Wildlife",R14,"")))))))))))))))</x:f>
+      <x:c r="AD14" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D14,IF($N$4="C2 Birds in Flight",E14,IF($N$4="C3 Landscape",F14,IF($N$4="Default Settings",G14,IF($N$4="Birds in Flight",H14,IF($N$4="Birds Perched",I14,IF($N$4="Fireworks",J14,IF($N$4="Landscape",K14,IF($N$4="Macro",L14,IF($N$4="People",M14,IF($N$4="Sports",N14,IF($N$4="Travel",O14,IF($N$4="Waterdrops",P14,IF($N$4="Wildlife",Q14,""))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="V14" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D14,IF($E$4="C2 Birds in Flight",E14,IF($E$4="C3 Landscape",F14,IF($E$4="Default Settings",G14,IF($E$4="Androo",H14,IF($E$4="Birds in Flight",I14,IF($E$4="Birds Perched",J14,IF($E$4="Fireworks",K14,IF($E$4="Landscape",L14,IF($E$4="Macro",M14,IF($E$4="People",N14,IF($E$4="Sports",O14,IF($E$4="Travel",P14,IF($E$4="Waterdrops",Q14,IF($E$4="Wildlife",R14,"")))))))))))))))</x:f>
+      <x:c r="AE14" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D14,IF($O$4="C2 Birds in Flight",E14,IF($O$4="C3 Landscape",F14,IF($O$4="Default Settings",G14,IF($O$4="Birds in Flight",H14,IF($O$4="Birds Perched",I14,IF($O$4="Fireworks",J14,IF($O$4="Landscape",K14,IF($O$4="Macro",L14,IF($O$4="People",M14,IF($O$4="Sports",N14,IF($O$4="Travel",O14,IF($O$4="Waterdrops",P14,IF($O$4="Wildlife",Q14,""))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="W14" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D14,IF($F$4="C2 Birds in Flight",E14,IF($F$4="C3 Landscape",F14,IF($F$4="Default Settings",G14,IF($F$4="Androo",H14,IF($F$4="Birds in Flight",I14,IF($F$4="Birds Perched",J14,IF($F$4="Fireworks",K14,IF($F$4="Landscape",L14,IF($F$4="Macro",M14,IF($F$4="People",N14,IF($F$4="Sports",O14,IF($F$4="Travel",P14,IF($F$4="Waterdrops",Q14,IF($F$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="X14" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D14,IF($G$4="C2 Birds in Flight",E14,IF($G$4="C3 Landscape",F14,IF($G$4="Default Settings",G14,IF($G$4="Androo",H14,IF($G$4="Birds in Flight",I14,IF($G$4="Birds Perched",J14,IF($G$4="Fireworks",K14,IF($G$4="Landscape",L14,IF($G$4="Macro",M14,IF($G$4="People",N14,IF($G$4="Sports",O14,IF($G$4="Travel",P14,IF($G$4="Waterdrops",Q14,IF($G$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="Y14" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D14,IF($H$4="C2 Birds in Flight",E14,IF($H$4="C3 Landscape",F14,IF($H$4="Default Settings",G14,IF($H$4="Androo",H14,IF($H$4="Birds in Flight",I14,IF($H$4="Birds Perched",J14,IF($H$4="Fireworks",K14,IF($H$4="Landscape",L14,IF($H$4="Macro",M14,IF($H$4="People",N14,IF($H$4="Sports",O14,IF($H$4="Travel",P14,IF($H$4="Waterdrops",Q14,IF($H$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="Z14" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D14,IF($I$4="C2 Birds in Flight",E14,IF($I$4="C3 Landscape",F14,IF($I$4="Default Settings",G14,IF($I$4="Androo",H14,IF($I$4="Birds in Flight",I14,IF($I$4="Birds Perched",J14,IF($I$4="Fireworks",K14,IF($I$4="Landscape",L14,IF($I$4="Macro",M14,IF($I$4="People",N14,IF($I$4="Sports",O14,IF($I$4="Travel",P14,IF($I$4="Waterdrops",Q14,IF($I$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AA14" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D14,IF($J$4="C2 Birds in Flight",E14,IF($J$4="C3 Landscape",F14,IF($J$4="Default Settings",G14,IF($J$4="Androo",H14,IF($J$4="Birds in Flight",I14,IF($J$4="Birds Perched",J14,IF($J$4="Fireworks",K14,IF($J$4="Landscape",L14,IF($J$4="Macro",M14,IF($J$4="People",N14,IF($J$4="Sports",O14,IF($J$4="Travel",P14,IF($J$4="Waterdrops",Q14,IF($J$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AB14" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D14,IF($K$4="C2 Birds in Flight",E14,IF($K$4="C3 Landscape",F14,IF($K$4="Default Settings",G14,IF($K$4="Androo",H14,IF($K$4="Birds in Flight",I14,IF($K$4="Birds Perched",J14,IF($K$4="Fireworks",K14,IF($K$4="Landscape",L14,IF($K$4="Macro",M14,IF($K$4="People",N14,IF($K$4="Sports",O14,IF($K$4="Travel",P14,IF($K$4="Waterdrops",Q14,IF($K$4="Wildlife",R14,"")))))))))))))))</x:f>
+      <x:c r="AF14" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D14,IF($P$4="C2 Birds in Flight",E14,IF($P$4="C3 Landscape",F14,IF($P$4="Default Settings",G14,IF($P$4="Birds in Flight",H14,IF($P$4="Birds Perched",I14,IF($P$4="Fireworks",J14,IF($P$4="Landscape",K14,IF($P$4="Macro",L14,IF($P$4="People",M14,IF($P$4="Sports",N14,IF($P$4="Travel",O14,IF($P$4="Waterdrops",P14,IF($P$4="Wildlife",Q14,""))))))))))))))</x:f>
         <x:v>Manual Focus</x:v>
       </x:c>
-      <x:c r="AC14" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D14,IF($L$4="C2 Birds in Flight",E14,IF($L$4="C3 Landscape",F14,IF($L$4="Default Settings",G14,IF($L$4="Androo",H14,IF($L$4="Birds in Flight",I14,IF($L$4="Birds Perched",J14,IF($L$4="Fireworks",K14,IF($L$4="Landscape",L14,IF($L$4="Macro",M14,IF($L$4="People",N14,IF($L$4="Sports",O14,IF($L$4="Travel",P14,IF($L$4="Waterdrops",Q14,IF($L$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="AD14" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D14,IF($M$4="C2 Birds in Flight",E14,IF($M$4="C3 Landscape",F14,IF($M$4="Default Settings",G14,IF($M$4="Androo",H14,IF($M$4="Birds in Flight",I14,IF($M$4="Birds Perched",J14,IF($M$4="Fireworks",K14,IF($M$4="Landscape",L14,IF($M$4="Macro",M14,IF($M$4="People",N14,IF($M$4="Sports",O14,IF($M$4="Travel",P14,IF($M$4="Waterdrops",Q14,IF($M$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="AE14" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D14,IF($N$4="C2 Birds in Flight",E14,IF($N$4="C3 Landscape",F14,IF($N$4="Default Settings",G14,IF($N$4="Androo",H14,IF($N$4="Birds in Flight",I14,IF($N$4="Birds Perched",J14,IF($N$4="Fireworks",K14,IF($N$4="Landscape",L14,IF($N$4="Macro",M14,IF($N$4="People",N14,IF($N$4="Sports",O14,IF($N$4="Travel",P14,IF($N$4="Waterdrops",Q14,IF($N$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AF14" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D14,IF($O$4="C2 Birds in Flight",E14,IF($O$4="C3 Landscape",F14,IF($O$4="Default Settings",G14,IF($O$4="Androo",H14,IF($O$4="Birds in Flight",I14,IF($O$4="Birds Perched",J14,IF($O$4="Fireworks",K14,IF($O$4="Landscape",L14,IF($O$4="Macro",M14,IF($O$4="People",N14,IF($O$4="Sports",O14,IF($O$4="Travel",P14,IF($O$4="Waterdrops",Q14,IF($O$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
       <x:c r="AG14" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D14,IF($P$4="C2 Birds in Flight",E14,IF($P$4="C3 Landscape",F14,IF($P$4="Default Settings",G14,IF($P$4="Androo",H14,IF($P$4="Birds in Flight",I14,IF($P$4="Birds Perched",J14,IF($P$4="Fireworks",K14,IF($P$4="Landscape",L14,IF($P$4="Macro",M14,IF($P$4="People",N14,IF($P$4="Sports",O14,IF($P$4="Travel",P14,IF($P$4="Waterdrops",Q14,IF($P$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AH14" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D14,IF($Q$4="C2 Birds in Flight",E14,IF($Q$4="C3 Landscape",F14,IF($Q$4="Default Settings",G14,IF($Q$4="Androo",H14,IF($Q$4="Birds in Flight",I14,IF($Q$4="Birds Perched",J14,IF($Q$4="Fireworks",K14,IF($Q$4="Landscape",L14,IF($Q$4="Macro",M14,IF($Q$4="People",N14,IF($Q$4="Sports",O14,IF($Q$4="Travel",P14,IF($Q$4="Waterdrops",Q14,IF($Q$4="Wildlife",R14,"")))))))))))))))</x:f>
-        <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="AI14" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D14,IF($R$4="C2 Birds in Flight",E14,IF($R$4="C3 Landscape",F14,IF($R$4="Default Settings",G14,IF($R$4="Androo",H14,IF($R$4="Birds in Flight",I14,IF($R$4="Birds Perched",J14,IF($R$4="Fireworks",K14,IF($R$4="Landscape",L14,IF($R$4="Macro",M14,IF($R$4="People",N14,IF($R$4="Sports",O14,IF($R$4="Travel",P14,IF($R$4="Waterdrops",Q14,IF($R$4="Wildlife",R14,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D14,IF($Q$4="C2 Birds in Flight",E14,IF($Q$4="C3 Landscape",F14,IF($Q$4="Default Settings",G14,IF($Q$4="Birds in Flight",H14,IF($Q$4="Birds Perched",I14,IF($Q$4="Fireworks",J14,IF($Q$4="Landscape",K14,IF($Q$4="Macro",L14,IF($Q$4="People",M14,IF($Q$4="Sports",N14,IF($Q$4="Travel",O14,IF($Q$4="Waterdrops",P14,IF($Q$4="Wildlife",Q14,""))))))))))))))</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
     </x:row>
@@ -1993,102 +1909,95 @@
         <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="I15" s="17" t="str">
+        <x:v>Case 1 (Custom)</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="str">
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="str">
+        <x:v>Case 1 (Custom)</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="P15" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q15" s="17" t="str">
+        <x:v>Case 1 (Custom)</x:v>
+      </x:c>
+      <x:c r="R15" s="20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="S15" s="20" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="T15" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Birds in Flight",H15,IF($D$4="Birds Perched",I15,IF($D$4="Fireworks",J15,IF($D$4="Landscape",K15,IF($D$4="Macro",L15,IF($D$4="People",M15,IF($D$4="Sports",N15,IF($D$4="Travel",O15,IF($D$4="Waterdrops",P15,IF($D$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Case 1 (Custom)</x:v>
+      </x:c>
+      <x:c r="U15" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Birds in Flight",H15,IF($E$4="Birds Perched",I15,IF($E$4="Fireworks",J15,IF($E$4="Landscape",K15,IF($E$4="Macro",L15,IF($E$4="People",M15,IF($E$4="Sports",N15,IF($E$4="Travel",O15,IF($E$4="Waterdrops",P15,IF($E$4="Wildlife",Q15,""))))))))))))))</x:f>
         <x:v>Case 4</x:v>
       </x:c>
-      <x:c r="J15" s="17" t="str">
+      <x:c r="V15" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Birds in Flight",H15,IF($F$4="Birds Perched",I15,IF($F$4="Fireworks",J15,IF($F$4="Landscape",K15,IF($F$4="Macro",L15,IF($F$4="People",M15,IF($F$4="Sports",N15,IF($F$4="Travel",O15,IF($F$4="Waterdrops",P15,IF($F$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W15" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Birds in Flight",H15,IF($G$4="Birds Perched",I15,IF($G$4="Fireworks",J15,IF($G$4="Landscape",K15,IF($G$4="Macro",L15,IF($G$4="People",M15,IF($G$4="Sports",N15,IF($G$4="Travel",O15,IF($G$4="Waterdrops",P15,IF($G$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Case A (Auto)</x:v>
+      </x:c>
+      <x:c r="X15" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Birds in Flight",H15,IF($H$4="Birds Perched",I15,IF($H$4="Fireworks",J15,IF($H$4="Landscape",K15,IF($H$4="Macro",L15,IF($H$4="People",M15,IF($H$4="Sports",N15,IF($H$4="Travel",O15,IF($H$4="Waterdrops",P15,IF($H$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Case 4</x:v>
+      </x:c>
+      <x:c r="Y15" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Birds in Flight",H15,IF($I$4="Birds Perched",I15,IF($I$4="Fireworks",J15,IF($I$4="Landscape",K15,IF($I$4="Macro",L15,IF($I$4="People",M15,IF($I$4="Sports",N15,IF($I$4="Travel",O15,IF($I$4="Waterdrops",P15,IF($I$4="Wildlife",Q15,""))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="N15" s="17" t="str">
+      <x:c r="Z15" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Birds in Flight",H15,IF($J$4="Birds Perched",I15,IF($J$4="Fireworks",J15,IF($J$4="Landscape",K15,IF($J$4="Macro",L15,IF($J$4="People",M15,IF($J$4="Sports",N15,IF($J$4="Travel",O15,IF($J$4="Waterdrops",P15,IF($J$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA15" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Birds in Flight",H15,IF($K$4="Birds Perched",I15,IF($K$4="Fireworks",J15,IF($K$4="Landscape",K15,IF($K$4="Macro",L15,IF($K$4="People",M15,IF($K$4="Sports",N15,IF($K$4="Travel",O15,IF($K$4="Waterdrops",P15,IF($K$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AB15" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Birds in Flight",H15,IF($L$4="Birds Perched",I15,IF($L$4="Fireworks",J15,IF($L$4="Landscape",K15,IF($L$4="Macro",L15,IF($L$4="People",M15,IF($L$4="Sports",N15,IF($L$4="Travel",O15,IF($L$4="Waterdrops",P15,IF($L$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC15" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Birds in Flight",H15,IF($M$4="Birds Perched",I15,IF($M$4="Fireworks",J15,IF($M$4="Landscape",K15,IF($M$4="Macro",L15,IF($M$4="People",M15,IF($M$4="Sports",N15,IF($M$4="Travel",O15,IF($M$4="Waterdrops",P15,IF($M$4="Wildlife",Q15,""))))))))))))))</x:f>
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="O15" s="17" t="str">
+      <x:c r="AD15" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Birds in Flight",H15,IF($N$4="Birds Perched",I15,IF($N$4="Fireworks",J15,IF($N$4="Landscape",K15,IF($N$4="Macro",L15,IF($N$4="People",M15,IF($N$4="Sports",N15,IF($N$4="Travel",O15,IF($N$4="Waterdrops",P15,IF($N$4="Wildlife",Q15,""))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="P15" s="17" t="str">
+      <x:c r="AE15" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Birds in Flight",H15,IF($O$4="Birds Perched",I15,IF($O$4="Fireworks",J15,IF($O$4="Landscape",K15,IF($O$4="Macro",L15,IF($O$4="People",M15,IF($O$4="Sports",N15,IF($O$4="Travel",O15,IF($O$4="Waterdrops",P15,IF($O$4="Wildlife",Q15,""))))))))))))))</x:f>
         <x:v>Case A (Auto)</x:v>
       </x:c>
-      <x:c r="Q15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R15" s="17" t="str">
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="S15" s="20" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T15" s="20" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="U15" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Androo",H15,IF($D$4="Birds in Flight",I15,IF($D$4="Birds Perched",J15,IF($D$4="Fireworks",K15,IF($D$4="Landscape",L15,IF($D$4="Macro",M15,IF($D$4="People",N15,IF($D$4="Sports",O15,IF($D$4="Travel",P15,IF($D$4="Waterdrops",Q15,IF($D$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="V15" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Androo",H15,IF($E$4="Birds in Flight",I15,IF($E$4="Birds Perched",J15,IF($E$4="Fireworks",K15,IF($E$4="Landscape",L15,IF($E$4="Macro",M15,IF($E$4="People",N15,IF($E$4="Sports",O15,IF($E$4="Travel",P15,IF($E$4="Waterdrops",Q15,IF($E$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case 4</x:v>
-      </x:c>
-      <x:c r="W15" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Androo",H15,IF($F$4="Birds in Flight",I15,IF($F$4="Birds Perched",J15,IF($F$4="Fireworks",K15,IF($F$4="Landscape",L15,IF($F$4="Macro",M15,IF($F$4="People",N15,IF($F$4="Sports",O15,IF($F$4="Travel",P15,IF($F$4="Waterdrops",Q15,IF($F$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="X15" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Androo",H15,IF($G$4="Birds in Flight",I15,IF($G$4="Birds Perched",J15,IF($G$4="Fireworks",K15,IF($G$4="Landscape",L15,IF($G$4="Macro",M15,IF($G$4="People",N15,IF($G$4="Sports",O15,IF($G$4="Travel",P15,IF($G$4="Waterdrops",Q15,IF($G$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
-      <x:c r="Y15" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Androo",H15,IF($H$4="Birds in Flight",I15,IF($H$4="Birds Perched",J15,IF($H$4="Fireworks",K15,IF($H$4="Landscape",L15,IF($H$4="Macro",M15,IF($H$4="People",N15,IF($H$4="Sports",O15,IF($H$4="Travel",P15,IF($H$4="Waterdrops",Q15,IF($H$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Z15" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Androo",H15,IF($I$4="Birds in Flight",I15,IF($I$4="Birds Perched",J15,IF($I$4="Fireworks",K15,IF($I$4="Landscape",L15,IF($I$4="Macro",M15,IF($I$4="People",N15,IF($I$4="Sports",O15,IF($I$4="Travel",P15,IF($I$4="Waterdrops",Q15,IF($I$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case 4</x:v>
-      </x:c>
-      <x:c r="AA15" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Androo",H15,IF($J$4="Birds in Flight",I15,IF($J$4="Birds Perched",J15,IF($J$4="Fireworks",K15,IF($J$4="Landscape",L15,IF($J$4="Macro",M15,IF($J$4="People",N15,IF($J$4="Sports",O15,IF($J$4="Travel",P15,IF($J$4="Waterdrops",Q15,IF($J$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="AB15" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Androo",H15,IF($K$4="Birds in Flight",I15,IF($K$4="Birds Perched",J15,IF($K$4="Fireworks",K15,IF($K$4="Landscape",L15,IF($K$4="Macro",M15,IF($K$4="People",N15,IF($K$4="Sports",O15,IF($K$4="Travel",P15,IF($K$4="Waterdrops",Q15,IF($K$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC15" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Androo",H15,IF($L$4="Birds in Flight",I15,IF($L$4="Birds Perched",J15,IF($L$4="Fireworks",K15,IF($L$4="Landscape",L15,IF($L$4="Macro",M15,IF($L$4="People",N15,IF($L$4="Sports",O15,IF($L$4="Travel",P15,IF($L$4="Waterdrops",Q15,IF($L$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AD15" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Androo",H15,IF($M$4="Birds in Flight",I15,IF($M$4="Birds Perched",J15,IF($M$4="Fireworks",K15,IF($M$4="Landscape",L15,IF($M$4="Macro",M15,IF($M$4="People",N15,IF($M$4="Sports",O15,IF($M$4="Travel",P15,IF($M$4="Waterdrops",Q15,IF($M$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AE15" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Androo",H15,IF($N$4="Birds in Flight",I15,IF($N$4="Birds Perched",J15,IF($N$4="Fireworks",K15,IF($N$4="Landscape",L15,IF($N$4="Macro",M15,IF($N$4="People",N15,IF($N$4="Sports",O15,IF($N$4="Travel",P15,IF($N$4="Waterdrops",Q15,IF($N$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
       <x:c r="AF15" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Androo",H15,IF($O$4="Birds in Flight",I15,IF($O$4="Birds Perched",J15,IF($O$4="Fireworks",K15,IF($O$4="Landscape",L15,IF($O$4="Macro",M15,IF($O$4="People",N15,IF($O$4="Sports",O15,IF($O$4="Travel",P15,IF($O$4="Waterdrops",Q15,IF($O$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
+        <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Birds in Flight",H15,IF($P$4="Birds Perched",I15,IF($P$4="Fireworks",J15,IF($P$4="Landscape",K15,IF($P$4="Macro",L15,IF($P$4="People",M15,IF($P$4="Sports",N15,IF($P$4="Travel",O15,IF($P$4="Waterdrops",P15,IF($P$4="Wildlife",Q15,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG15" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Androo",H15,IF($P$4="Birds in Flight",I15,IF($P$4="Birds Perched",J15,IF($P$4="Fireworks",K15,IF($P$4="Landscape",L15,IF($P$4="Macro",M15,IF($P$4="People",N15,IF($P$4="Sports",O15,IF($P$4="Travel",P15,IF($P$4="Waterdrops",Q15,IF($P$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
-      <x:c r="AH15" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Androo",H15,IF($Q$4="Birds in Flight",I15,IF($Q$4="Birds Perched",J15,IF($Q$4="Fireworks",K15,IF($Q$4="Landscape",L15,IF($Q$4="Macro",M15,IF($Q$4="People",N15,IF($Q$4="Sports",O15,IF($Q$4="Travel",P15,IF($Q$4="Waterdrops",Q15,IF($Q$4="Wildlife",R15,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI15" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D15,IF($R$4="C2 Birds in Flight",E15,IF($R$4="C3 Landscape",F15,IF($R$4="Default Settings",G15,IF($R$4="Androo",H15,IF($R$4="Birds in Flight",I15,IF($R$4="Birds Perched",J15,IF($R$4="Fireworks",K15,IF($R$4="Landscape",L15,IF($R$4="Macro",M15,IF($R$4="People",N15,IF($R$4="Sports",O15,IF($R$4="Travel",P15,IF($R$4="Waterdrops",Q15,IF($R$4="Wildlife",R15,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Birds in Flight",H15,IF($Q$4="Birds Perched",I15,IF($Q$4="Fireworks",J15,IF($Q$4="Landscape",K15,IF($Q$4="Macro",L15,IF($Q$4="People",M15,IF($Q$4="Sports",N15,IF($Q$4="Travel",O15,IF($Q$4="Waterdrops",P15,IF($Q$4="Wildlife",Q15,""))))))))))))))</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
     </x:row>
@@ -2114,103 +2023,96 @@
       <x:c r="G16" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
-      <x:c r="H16" s="17" t="str">
-        <x:v>Not Used</x:v>
+      <x:c r="H16" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L16" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P16" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q16" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="R16" s="20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S16" s="20" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="T16" s="38" t="n">
+        <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Birds in Flight",H16,IF($D$4="Birds Perched",I16,IF($D$4="Fireworks",J16,IF($D$4="Landscape",K16,IF($D$4="Macro",L16,IF($D$4="People",M16,IF($D$4="Sports",N16,IF($D$4="Travel",O16,IF($D$4="Waterdrops",P16,IF($D$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="U16" s="38" t="n">
+        <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Birds in Flight",H16,IF($E$4="Birds Perched",I16,IF($E$4="Fireworks",J16,IF($E$4="Landscape",K16,IF($E$4="Macro",L16,IF($E$4="People",M16,IF($E$4="Sports",N16,IF($E$4="Travel",O16,IF($E$4="Waterdrops",P16,IF($E$4="Wildlife",Q16,""))))))))))))))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J16" s="17" t="n">
+      <x:c r="V16" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Birds in Flight",H16,IF($F$4="Birds Perched",I16,IF($F$4="Fireworks",J16,IF($F$4="Landscape",K16,IF($F$4="Macro",L16,IF($F$4="People",M16,IF($F$4="Sports",N16,IF($F$4="Travel",O16,IF($F$4="Waterdrops",P16,IF($F$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W16" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Birds in Flight",H16,IF($G$4="Birds Perched",I16,IF($G$4="Fireworks",J16,IF($G$4="Landscape",K16,IF($G$4="Macro",L16,IF($G$4="People",M16,IF($G$4="Sports",N16,IF($G$4="Travel",O16,IF($G$4="Waterdrops",P16,IF($G$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X16" s="38" t="n">
+        <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Birds in Flight",H16,IF($H$4="Birds Perched",I16,IF($H$4="Fireworks",J16,IF($H$4="Landscape",K16,IF($H$4="Macro",L16,IF($H$4="People",M16,IF($H$4="Sports",N16,IF($H$4="Travel",O16,IF($H$4="Waterdrops",P16,IF($H$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y16" s="38" t="n">
+        <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Birds in Flight",H16,IF($I$4="Birds Perched",I16,IF($I$4="Fireworks",J16,IF($I$4="Landscape",K16,IF($I$4="Macro",L16,IF($I$4="People",M16,IF($I$4="Sports",N16,IF($I$4="Travel",O16,IF($I$4="Waterdrops",P16,IF($I$4="Wildlife",Q16,""))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="M16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="N16" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="O16" s="17" t="n">
+      <x:c r="Z16" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Birds in Flight",H16,IF($J$4="Birds Perched",I16,IF($J$4="Fireworks",J16,IF($J$4="Landscape",K16,IF($J$4="Macro",L16,IF($J$4="People",M16,IF($J$4="Sports",N16,IF($J$4="Travel",O16,IF($J$4="Waterdrops",P16,IF($J$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA16" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Birds in Flight",H16,IF($K$4="Birds Perched",I16,IF($K$4="Fireworks",J16,IF($K$4="Landscape",K16,IF($K$4="Macro",L16,IF($K$4="People",M16,IF($K$4="Sports",N16,IF($K$4="Travel",O16,IF($K$4="Waterdrops",P16,IF($K$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AB16" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Birds in Flight",H16,IF($L$4="Birds Perched",I16,IF($L$4="Fireworks",J16,IF($L$4="Landscape",K16,IF($L$4="Macro",L16,IF($L$4="People",M16,IF($L$4="Sports",N16,IF($L$4="Travel",O16,IF($L$4="Waterdrops",P16,IF($L$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC16" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Birds in Flight",H16,IF($M$4="Birds Perched",I16,IF($M$4="Fireworks",J16,IF($M$4="Landscape",K16,IF($M$4="Macro",L16,IF($M$4="People",M16,IF($M$4="Sports",N16,IF($M$4="Travel",O16,IF($M$4="Waterdrops",P16,IF($M$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AD16" s="38" t="n">
+        <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Birds in Flight",H16,IF($N$4="Birds Perched",I16,IF($N$4="Fireworks",J16,IF($N$4="Landscape",K16,IF($N$4="Macro",L16,IF($N$4="People",M16,IF($N$4="Sports",N16,IF($N$4="Travel",O16,IF($N$4="Waterdrops",P16,IF($N$4="Wildlife",Q16,""))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="P16" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Q16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R16" s="17" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="S16" s="20" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T16" s="20" t="n">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="U16" s="38" t="n">
-        <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Androo",H16,IF($D$4="Birds in Flight",I16,IF($D$4="Birds Perched",J16,IF($D$4="Fireworks",K16,IF($D$4="Landscape",L16,IF($D$4="Macro",M16,IF($D$4="People",N16,IF($D$4="Sports",O16,IF($D$4="Travel",P16,IF($D$4="Waterdrops",Q16,IF($D$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="V16" s="38" t="n">
-        <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Androo",H16,IF($E$4="Birds in Flight",I16,IF($E$4="Birds Perched",J16,IF($E$4="Fireworks",K16,IF($E$4="Landscape",L16,IF($E$4="Macro",M16,IF($E$4="People",N16,IF($E$4="Sports",O16,IF($E$4="Travel",P16,IF($E$4="Waterdrops",Q16,IF($E$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W16" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Androo",H16,IF($F$4="Birds in Flight",I16,IF($F$4="Birds Perched",J16,IF($F$4="Fireworks",K16,IF($F$4="Landscape",L16,IF($F$4="Macro",M16,IF($F$4="People",N16,IF($F$4="Sports",O16,IF($F$4="Travel",P16,IF($F$4="Waterdrops",Q16,IF($F$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="X16" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Androo",H16,IF($G$4="Birds in Flight",I16,IF($G$4="Birds Perched",J16,IF($G$4="Fireworks",K16,IF($G$4="Landscape",L16,IF($G$4="Macro",M16,IF($G$4="People",N16,IF($G$4="Sports",O16,IF($G$4="Travel",P16,IF($G$4="Waterdrops",Q16,IF($G$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Y16" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Androo",H16,IF($H$4="Birds in Flight",I16,IF($H$4="Birds Perched",J16,IF($H$4="Fireworks",K16,IF($H$4="Landscape",L16,IF($H$4="Macro",M16,IF($H$4="People",N16,IF($H$4="Sports",O16,IF($H$4="Travel",P16,IF($H$4="Waterdrops",Q16,IF($H$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Z16" s="38" t="n">
-        <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Androo",H16,IF($I$4="Birds in Flight",I16,IF($I$4="Birds Perched",J16,IF($I$4="Fireworks",K16,IF($I$4="Landscape",L16,IF($I$4="Macro",M16,IF($I$4="People",N16,IF($I$4="Sports",O16,IF($I$4="Travel",P16,IF($I$4="Waterdrops",Q16,IF($I$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AA16" s="38" t="n">
-        <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Androo",H16,IF($J$4="Birds in Flight",I16,IF($J$4="Birds Perched",J16,IF($J$4="Fireworks",K16,IF($J$4="Landscape",L16,IF($J$4="Macro",M16,IF($J$4="People",N16,IF($J$4="Sports",O16,IF($J$4="Travel",P16,IF($J$4="Waterdrops",Q16,IF($J$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="AB16" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Androo",H16,IF($K$4="Birds in Flight",I16,IF($K$4="Birds Perched",J16,IF($K$4="Fireworks",K16,IF($K$4="Landscape",L16,IF($K$4="Macro",M16,IF($K$4="People",N16,IF($K$4="Sports",O16,IF($K$4="Travel",P16,IF($K$4="Waterdrops",Q16,IF($K$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC16" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Androo",H16,IF($L$4="Birds in Flight",I16,IF($L$4="Birds Perched",J16,IF($L$4="Fireworks",K16,IF($L$4="Landscape",L16,IF($L$4="Macro",M16,IF($L$4="People",N16,IF($L$4="Sports",O16,IF($L$4="Travel",P16,IF($L$4="Waterdrops",Q16,IF($L$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AD16" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Androo",H16,IF($M$4="Birds in Flight",I16,IF($M$4="Birds Perched",J16,IF($M$4="Fireworks",K16,IF($M$4="Landscape",L16,IF($M$4="Macro",M16,IF($M$4="People",N16,IF($M$4="Sports",O16,IF($M$4="Travel",P16,IF($M$4="Waterdrops",Q16,IF($M$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AE16" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Androo",H16,IF($N$4="Birds in Flight",I16,IF($N$4="Birds Perched",J16,IF($N$4="Fireworks",K16,IF($N$4="Landscape",L16,IF($N$4="Macro",M16,IF($N$4="People",N16,IF($N$4="Sports",O16,IF($N$4="Travel",P16,IF($N$4="Waterdrops",Q16,IF($N$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AF16" s="38" t="n">
-        <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Androo",H16,IF($O$4="Birds in Flight",I16,IF($O$4="Birds Perched",J16,IF($O$4="Fireworks",K16,IF($O$4="Landscape",L16,IF($O$4="Macro",M16,IF($O$4="People",N16,IF($O$4="Sports",O16,IF($O$4="Travel",P16,IF($O$4="Waterdrops",Q16,IF($O$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="AG16" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Androo",H16,IF($P$4="Birds in Flight",I16,IF($P$4="Birds Perched",J16,IF($P$4="Fireworks",K16,IF($P$4="Landscape",L16,IF($P$4="Macro",M16,IF($P$4="People",N16,IF($P$4="Sports",O16,IF($P$4="Travel",P16,IF($P$4="Waterdrops",Q16,IF($P$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AH16" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Androo",H16,IF($Q$4="Birds in Flight",I16,IF($Q$4="Birds Perched",J16,IF($Q$4="Fireworks",K16,IF($Q$4="Landscape",L16,IF($Q$4="Macro",M16,IF($Q$4="People",N16,IF($Q$4="Sports",O16,IF($Q$4="Travel",P16,IF($Q$4="Waterdrops",Q16,IF($Q$4="Wildlife",R16,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI16" s="38" t="n">
-        <x:f>IF($R$4="C1 Wildlife",D16,IF($R$4="C2 Birds in Flight",E16,IF($R$4="C3 Landscape",F16,IF($R$4="Default Settings",G16,IF($R$4="Androo",H16,IF($R$4="Birds in Flight",I16,IF($R$4="Birds Perched",J16,IF($R$4="Fireworks",K16,IF($R$4="Landscape",L16,IF($R$4="Macro",M16,IF($R$4="People",N16,IF($R$4="Sports",O16,IF($R$4="Travel",P16,IF($R$4="Waterdrops",Q16,IF($R$4="Wildlife",R16,"")))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Birds in Flight",H16,IF($O$4="Birds Perched",I16,IF($O$4="Fireworks",J16,IF($O$4="Landscape",K16,IF($O$4="Macro",L16,IF($O$4="People",M16,IF($O$4="Sports",N16,IF($O$4="Travel",O16,IF($O$4="Waterdrops",P16,IF($O$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AF16" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Birds in Flight",H16,IF($P$4="Birds Perched",I16,IF($P$4="Fireworks",J16,IF($P$4="Landscape",K16,IF($P$4="Macro",L16,IF($P$4="People",M16,IF($P$4="Sports",N16,IF($P$4="Travel",O16,IF($P$4="Waterdrops",P16,IF($P$4="Wildlife",Q16,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AG16" s="38" t="n">
+        <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Birds in Flight",H16,IF($Q$4="Birds Perched",I16,IF($Q$4="Fireworks",J16,IF($Q$4="Landscape",K16,IF($Q$4="Macro",L16,IF($Q$4="People",M16,IF($Q$4="Sports",N16,IF($Q$4="Travel",O16,IF($Q$4="Waterdrops",P16,IF($Q$4="Wildlife",Q16,""))))))))))))))</x:f>
         <x:v>-1</x:v>
       </x:c>
     </x:row>
@@ -2237,102 +2139,95 @@
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
         <x:v>+1</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L17" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="N17" s="17" t="str">
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L17" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="M17" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="N17" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="O17" s="17" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="P17" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q17" s="17" t="str">
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="P17" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="Q17" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R17" s="17" t="str">
+      <x:c r="R17" s="20" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="S17" s="20" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="T17" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Birds in Flight",H17,IF($D$4="Birds Perched",I17,IF($D$4="Fireworks",J17,IF($D$4="Landscape",K17,IF($D$4="Macro",L17,IF($D$4="People",M17,IF($D$4="Sports",N17,IF($D$4="Travel",O17,IF($D$4="Waterdrops",P17,IF($D$4="Wildlife",Q17,""))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="T17" s="20" t="n">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="U17" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Androo",H17,IF($D$4="Birds in Flight",I17,IF($D$4="Birds Perched",J17,IF($D$4="Fireworks",K17,IF($D$4="Landscape",L17,IF($D$4="Macro",M17,IF($D$4="People",N17,IF($D$4="Sports",O17,IF($D$4="Travel",P17,IF($D$4="Waterdrops",Q17,IF($D$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Birds in Flight",H17,IF($E$4="Birds Perched",I17,IF($E$4="Fireworks",J17,IF($E$4="Landscape",K17,IF($E$4="Macro",L17,IF($E$4="People",M17,IF($E$4="Sports",N17,IF($E$4="Travel",O17,IF($E$4="Waterdrops",P17,IF($E$4="Wildlife",Q17,""))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Androo",H17,IF($E$4="Birds in Flight",I17,IF($E$4="Birds Perched",J17,IF($E$4="Fireworks",K17,IF($E$4="Landscape",L17,IF($E$4="Macro",M17,IF($E$4="People",N17,IF($E$4="Sports",O17,IF($E$4="Travel",P17,IF($E$4="Waterdrops",Q17,IF($E$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Birds in Flight",H17,IF($F$4="Birds Perched",I17,IF($F$4="Fireworks",J17,IF($F$4="Landscape",K17,IF($F$4="Macro",L17,IF($F$4="People",M17,IF($F$4="Sports",N17,IF($F$4="Travel",O17,IF($F$4="Waterdrops",P17,IF($F$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W17" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Birds in Flight",H17,IF($G$4="Birds Perched",I17,IF($G$4="Fireworks",J17,IF($G$4="Landscape",K17,IF($G$4="Macro",L17,IF($G$4="People",M17,IF($G$4="Sports",N17,IF($G$4="Travel",O17,IF($G$4="Waterdrops",P17,IF($G$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X17" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Birds in Flight",H17,IF($H$4="Birds Perched",I17,IF($H$4="Fireworks",J17,IF($H$4="Landscape",K17,IF($H$4="Macro",L17,IF($H$4="People",M17,IF($H$4="Sports",N17,IF($H$4="Travel",O17,IF($H$4="Waterdrops",P17,IF($H$4="Wildlife",Q17,""))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="W17" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Androo",H17,IF($F$4="Birds in Flight",I17,IF($F$4="Birds Perched",J17,IF($F$4="Fireworks",K17,IF($F$4="Landscape",L17,IF($F$4="Macro",M17,IF($F$4="People",N17,IF($F$4="Sports",O17,IF($F$4="Travel",P17,IF($F$4="Waterdrops",Q17,IF($F$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="X17" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Androo",H17,IF($G$4="Birds in Flight",I17,IF($G$4="Birds Perched",J17,IF($G$4="Fireworks",K17,IF($G$4="Landscape",L17,IF($G$4="Macro",M17,IF($G$4="People",N17,IF($G$4="Sports",O17,IF($G$4="Travel",P17,IF($G$4="Waterdrops",Q17,IF($G$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
       <x:c r="Y17" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Androo",H17,IF($H$4="Birds in Flight",I17,IF($H$4="Birds Perched",J17,IF($H$4="Fireworks",K17,IF($H$4="Landscape",L17,IF($H$4="Macro",M17,IF($H$4="People",N17,IF($H$4="Sports",O17,IF($H$4="Travel",P17,IF($H$4="Waterdrops",Q17,IF($H$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Birds in Flight",H17,IF($I$4="Birds Perched",I17,IF($I$4="Fireworks",J17,IF($I$4="Landscape",K17,IF($I$4="Macro",L17,IF($I$4="People",M17,IF($I$4="Sports",N17,IF($I$4="Travel",O17,IF($I$4="Waterdrops",P17,IF($I$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="Z17" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Androo",H17,IF($I$4="Birds in Flight",I17,IF($I$4="Birds Perched",J17,IF($I$4="Fireworks",K17,IF($I$4="Landscape",L17,IF($I$4="Macro",M17,IF($I$4="People",N17,IF($I$4="Sports",O17,IF($I$4="Travel",P17,IF($I$4="Waterdrops",Q17,IF($I$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Birds in Flight",H17,IF($J$4="Birds Perched",I17,IF($J$4="Fireworks",J17,IF($J$4="Landscape",K17,IF($J$4="Macro",L17,IF($J$4="People",M17,IF($J$4="Sports",N17,IF($J$4="Travel",O17,IF($J$4="Waterdrops",P17,IF($J$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA17" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Birds in Flight",H17,IF($K$4="Birds Perched",I17,IF($K$4="Fireworks",J17,IF($K$4="Landscape",K17,IF($K$4="Macro",L17,IF($K$4="People",M17,IF($K$4="Sports",N17,IF($K$4="Travel",O17,IF($K$4="Waterdrops",P17,IF($K$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AB17" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Birds in Flight",H17,IF($L$4="Birds Perched",I17,IF($L$4="Fireworks",J17,IF($L$4="Landscape",K17,IF($L$4="Macro",L17,IF($L$4="People",M17,IF($L$4="Sports",N17,IF($L$4="Travel",O17,IF($L$4="Waterdrops",P17,IF($L$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC17" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Birds in Flight",H17,IF($M$4="Birds Perched",I17,IF($M$4="Fireworks",J17,IF($M$4="Landscape",K17,IF($M$4="Macro",L17,IF($M$4="People",M17,IF($M$4="Sports",N17,IF($M$4="Travel",O17,IF($M$4="Waterdrops",P17,IF($M$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AD17" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Birds in Flight",H17,IF($N$4="Birds Perched",I17,IF($N$4="Fireworks",J17,IF($N$4="Landscape",K17,IF($N$4="Macro",L17,IF($N$4="People",M17,IF($N$4="Sports",N17,IF($N$4="Travel",O17,IF($N$4="Waterdrops",P17,IF($N$4="Wildlife",Q17,""))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="AA17" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Androo",H17,IF($J$4="Birds in Flight",I17,IF($J$4="Birds Perched",J17,IF($J$4="Fireworks",K17,IF($J$4="Landscape",L17,IF($J$4="Macro",M17,IF($J$4="People",N17,IF($J$4="Sports",O17,IF($J$4="Travel",P17,IF($J$4="Waterdrops",Q17,IF($J$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>+1</x:v>
-      </x:c>
-      <x:c r="AB17" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D17,IF($K$4="C2 Birds in Flight",E17,IF($K$4="C3 Landscape",F17,IF($K$4="Default Settings",G17,IF($K$4="Androo",H17,IF($K$4="Birds in Flight",I17,IF($K$4="Birds Perched",J17,IF($K$4="Fireworks",K17,IF($K$4="Landscape",L17,IF($K$4="Macro",M17,IF($K$4="People",N17,IF($K$4="Sports",O17,IF($K$4="Travel",P17,IF($K$4="Waterdrops",Q17,IF($K$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC17" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D17,IF($L$4="C2 Birds in Flight",E17,IF($L$4="C3 Landscape",F17,IF($L$4="Default Settings",G17,IF($L$4="Androo",H17,IF($L$4="Birds in Flight",I17,IF($L$4="Birds Perched",J17,IF($L$4="Fireworks",K17,IF($L$4="Landscape",L17,IF($L$4="Macro",M17,IF($L$4="People",N17,IF($L$4="Sports",O17,IF($L$4="Travel",P17,IF($L$4="Waterdrops",Q17,IF($L$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AD17" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Androo",H17,IF($M$4="Birds in Flight",I17,IF($M$4="Birds Perched",J17,IF($M$4="Fireworks",K17,IF($M$4="Landscape",L17,IF($M$4="Macro",M17,IF($M$4="People",N17,IF($M$4="Sports",O17,IF($M$4="Travel",P17,IF($M$4="Waterdrops",Q17,IF($M$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AE17" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Androo",H17,IF($N$4="Birds in Flight",I17,IF($N$4="Birds Perched",J17,IF($N$4="Fireworks",K17,IF($N$4="Landscape",L17,IF($N$4="Macro",M17,IF($N$4="People",N17,IF($N$4="Sports",O17,IF($N$4="Travel",P17,IF($N$4="Waterdrops",Q17,IF($N$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Birds in Flight",H17,IF($O$4="Birds Perched",I17,IF($O$4="Fireworks",J17,IF($O$4="Landscape",K17,IF($O$4="Macro",L17,IF($O$4="People",M17,IF($O$4="Sports",N17,IF($O$4="Travel",O17,IF($O$4="Waterdrops",P17,IF($O$4="Wildlife",Q17,""))))))))))))))</x:f>
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="AF17" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Androo",H17,IF($O$4="Birds in Flight",I17,IF($O$4="Birds Perched",J17,IF($O$4="Fireworks",K17,IF($O$4="Landscape",L17,IF($O$4="Macro",M17,IF($O$4="People",N17,IF($O$4="Sports",O17,IF($O$4="Travel",P17,IF($O$4="Waterdrops",Q17,IF($O$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Birds in Flight",H17,IF($P$4="Birds Perched",I17,IF($P$4="Fireworks",J17,IF($P$4="Landscape",K17,IF($P$4="Macro",L17,IF($P$4="People",M17,IF($P$4="Sports",N17,IF($P$4="Travel",O17,IF($P$4="Waterdrops",P17,IF($P$4="Wildlife",Q17,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG17" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Androo",H17,IF($P$4="Birds in Flight",I17,IF($P$4="Birds Perched",J17,IF($P$4="Fireworks",K17,IF($P$4="Landscape",L17,IF($P$4="Macro",M17,IF($P$4="People",N17,IF($P$4="Sports",O17,IF($P$4="Travel",P17,IF($P$4="Waterdrops",Q17,IF($P$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AH17" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Androo",H17,IF($Q$4="Birds in Flight",I17,IF($Q$4="Birds Perched",J17,IF($Q$4="Fireworks",K17,IF($Q$4="Landscape",L17,IF($Q$4="Macro",M17,IF($Q$4="People",N17,IF($Q$4="Sports",O17,IF($Q$4="Travel",P17,IF($Q$4="Waterdrops",Q17,IF($Q$4="Wildlife",R17,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI17" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D17,IF($R$4="C2 Birds in Flight",E17,IF($R$4="C3 Landscape",F17,IF($R$4="Default Settings",G17,IF($R$4="Androo",H17,IF($R$4="Birds in Flight",I17,IF($R$4="Birds Perched",J17,IF($R$4="Fireworks",K17,IF($R$4="Landscape",L17,IF($R$4="Macro",M17,IF($R$4="People",N17,IF($R$4="Sports",O17,IF($R$4="Travel",P17,IF($R$4="Waterdrops",Q17,IF($R$4="Wildlife",R17,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Birds in Flight",H17,IF($Q$4="Birds Perched",I17,IF($Q$4="Fireworks",J17,IF($Q$4="Landscape",K17,IF($Q$4="Macro",L17,IF($Q$4="People",M17,IF($Q$4="Sports",N17,IF($Q$4="Travel",O17,IF($Q$4="Waterdrops",P17,IF($Q$4="Wildlife",Q17,""))))))))))))))</x:f>
         <x:v>+1</x:v>
       </x:c>
     </x:row>
@@ -2365,96 +2260,89 @@
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L18" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="str">
         <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L18" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="M18" s="17" t="str">
-        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="N18" s="17" t="str">
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="O18" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="P18" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q18" s="17" t="str">
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="P18" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Q18" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R18" s="17" t="str">
+      <x:c r="R18" s="20" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="S18" s="20" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="T18" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Birds in Flight",H18,IF($D$4="Birds Perched",I18,IF($D$4="Fireworks",J18,IF($D$4="Landscape",K18,IF($D$4="Macro",L18,IF($D$4="People",M18,IF($D$4="Sports",N18,IF($D$4="Travel",O18,IF($D$4="Waterdrops",P18,IF($D$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="S18" s="20" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T18" s="20" t="n">
-        <x:v>138</x:v>
-      </x:c>
       <x:c r="U18" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Androo",H18,IF($D$4="Birds in Flight",I18,IF($D$4="Birds Perched",J18,IF($D$4="Fireworks",K18,IF($D$4="Landscape",L18,IF($D$4="Macro",M18,IF($D$4="People",N18,IF($D$4="Sports",O18,IF($D$4="Travel",P18,IF($D$4="Waterdrops",Q18,IF($D$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Birds in Flight",H18,IF($E$4="Birds Perched",I18,IF($E$4="Fireworks",J18,IF($E$4="Landscape",K18,IF($E$4="Macro",L18,IF($E$4="People",M18,IF($E$4="Sports",N18,IF($E$4="Travel",O18,IF($E$4="Waterdrops",P18,IF($E$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="V18" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Androo",H18,IF($E$4="Birds in Flight",I18,IF($E$4="Birds Perched",J18,IF($E$4="Fireworks",K18,IF($E$4="Landscape",L18,IF($E$4="Macro",M18,IF($E$4="People",N18,IF($E$4="Sports",O18,IF($E$4="Travel",P18,IF($E$4="Waterdrops",Q18,IF($E$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Birds in Flight",H18,IF($F$4="Birds Perched",I18,IF($F$4="Fireworks",J18,IF($F$4="Landscape",K18,IF($F$4="Macro",L18,IF($F$4="People",M18,IF($F$4="Sports",N18,IF($F$4="Travel",O18,IF($F$4="Waterdrops",P18,IF($F$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W18" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Birds in Flight",H18,IF($G$4="Birds Perched",I18,IF($G$4="Fireworks",J18,IF($G$4="Landscape",K18,IF($G$4="Macro",L18,IF($G$4="People",M18,IF($G$4="Sports",N18,IF($G$4="Travel",O18,IF($G$4="Waterdrops",P18,IF($G$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="W18" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Androo",H18,IF($F$4="Birds in Flight",I18,IF($F$4="Birds Perched",J18,IF($F$4="Fireworks",K18,IF($F$4="Landscape",L18,IF($F$4="Macro",M18,IF($F$4="People",N18,IF($F$4="Sports",O18,IF($F$4="Travel",P18,IF($F$4="Waterdrops",Q18,IF($F$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="X18" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Androo",H18,IF($G$4="Birds in Flight",I18,IF($G$4="Birds Perched",J18,IF($G$4="Fireworks",K18,IF($G$4="Landscape",L18,IF($G$4="Macro",M18,IF($G$4="People",N18,IF($G$4="Sports",O18,IF($G$4="Travel",P18,IF($G$4="Waterdrops",Q18,IF($G$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Birds in Flight",H18,IF($H$4="Birds Perched",I18,IF($H$4="Fireworks",J18,IF($H$4="Landscape",K18,IF($H$4="Macro",L18,IF($H$4="People",M18,IF($H$4="Sports",N18,IF($H$4="Travel",O18,IF($H$4="Waterdrops",P18,IF($H$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="Y18" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Androo",H18,IF($H$4="Birds in Flight",I18,IF($H$4="Birds Perched",J18,IF($H$4="Fireworks",K18,IF($H$4="Landscape",L18,IF($H$4="Macro",M18,IF($H$4="People",N18,IF($H$4="Sports",O18,IF($H$4="Travel",P18,IF($H$4="Waterdrops",Q18,IF($H$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Birds in Flight",H18,IF($I$4="Birds Perched",I18,IF($I$4="Fireworks",J18,IF($I$4="Landscape",K18,IF($I$4="Macro",L18,IF($I$4="People",M18,IF($I$4="Sports",N18,IF($I$4="Travel",O18,IF($I$4="Waterdrops",P18,IF($I$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
       <x:c r="Z18" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Androo",H18,IF($I$4="Birds in Flight",I18,IF($I$4="Birds Perched",J18,IF($I$4="Fireworks",K18,IF($I$4="Landscape",L18,IF($I$4="Macro",M18,IF($I$4="People",N18,IF($I$4="Sports",O18,IF($I$4="Travel",P18,IF($I$4="Waterdrops",Q18,IF($I$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Birds in Flight",H18,IF($J$4="Birds Perched",I18,IF($J$4="Fireworks",J18,IF($J$4="Landscape",K18,IF($J$4="Macro",L18,IF($J$4="People",M18,IF($J$4="Sports",N18,IF($J$4="Travel",O18,IF($J$4="Waterdrops",P18,IF($J$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA18" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Birds in Flight",H18,IF($K$4="Birds Perched",I18,IF($K$4="Fireworks",J18,IF($K$4="Landscape",K18,IF($K$4="Macro",L18,IF($K$4="People",M18,IF($K$4="Sports",N18,IF($K$4="Travel",O18,IF($K$4="Waterdrops",P18,IF($K$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AB18" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Birds in Flight",H18,IF($L$4="Birds Perched",I18,IF($L$4="Fireworks",J18,IF($L$4="Landscape",K18,IF($L$4="Macro",L18,IF($L$4="People",M18,IF($L$4="Sports",N18,IF($L$4="Travel",O18,IF($L$4="Waterdrops",P18,IF($L$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC18" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Birds in Flight",H18,IF($M$4="Birds Perched",I18,IF($M$4="Fireworks",J18,IF($M$4="Landscape",K18,IF($M$4="Macro",L18,IF($M$4="People",M18,IF($M$4="Sports",N18,IF($M$4="Travel",O18,IF($M$4="Waterdrops",P18,IF($M$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="AA18" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Androo",H18,IF($J$4="Birds in Flight",I18,IF($J$4="Birds Perched",J18,IF($J$4="Fireworks",K18,IF($J$4="Landscape",L18,IF($J$4="Macro",M18,IF($J$4="People",N18,IF($J$4="Sports",O18,IF($J$4="Travel",P18,IF($J$4="Waterdrops",Q18,IF($J$4="Wildlife",R18,"")))))))))))))))</x:f>
+      <x:c r="AD18" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Birds in Flight",H18,IF($N$4="Birds Perched",I18,IF($N$4="Fireworks",J18,IF($N$4="Landscape",K18,IF($N$4="Macro",L18,IF($N$4="People",M18,IF($N$4="Sports",N18,IF($N$4="Travel",O18,IF($N$4="Waterdrops",P18,IF($N$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="AB18" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D18,IF($K$4="C2 Birds in Flight",E18,IF($K$4="C3 Landscape",F18,IF($K$4="Default Settings",G18,IF($K$4="Androo",H18,IF($K$4="Birds in Flight",I18,IF($K$4="Birds Perched",J18,IF($K$4="Fireworks",K18,IF($K$4="Landscape",L18,IF($K$4="Macro",M18,IF($K$4="People",N18,IF($K$4="Sports",O18,IF($K$4="Travel",P18,IF($K$4="Waterdrops",Q18,IF($K$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC18" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D18,IF($L$4="C2 Birds in Flight",E18,IF($L$4="C3 Landscape",F18,IF($L$4="Default Settings",G18,IF($L$4="Androo",H18,IF($L$4="Birds in Flight",I18,IF($L$4="Birds Perched",J18,IF($L$4="Fireworks",K18,IF($L$4="Landscape",L18,IF($L$4="Macro",M18,IF($L$4="People",N18,IF($L$4="Sports",O18,IF($L$4="Travel",P18,IF($L$4="Waterdrops",Q18,IF($L$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AD18" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Androo",H18,IF($M$4="Birds in Flight",I18,IF($M$4="Birds Perched",J18,IF($M$4="Fireworks",K18,IF($M$4="Landscape",L18,IF($M$4="Macro",M18,IF($M$4="People",N18,IF($M$4="Sports",O18,IF($M$4="Travel",P18,IF($M$4="Waterdrops",Q18,IF($M$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="AE18" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Androo",H18,IF($N$4="Birds in Flight",I18,IF($N$4="Birds Perched",J18,IF($N$4="Fireworks",K18,IF($N$4="Landscape",L18,IF($N$4="Macro",M18,IF($N$4="People",N18,IF($N$4="Sports",O18,IF($N$4="Travel",P18,IF($N$4="Waterdrops",Q18,IF($N$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>On subject</x:v>
+        <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Birds in Flight",H18,IF($O$4="Birds Perched",I18,IF($O$4="Fireworks",J18,IF($O$4="Landscape",K18,IF($O$4="Macro",L18,IF($O$4="People",M18,IF($O$4="Sports",N18,IF($O$4="Travel",O18,IF($O$4="Waterdrops",P18,IF($O$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AF18" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Androo",H18,IF($O$4="Birds in Flight",I18,IF($O$4="Birds Perched",J18,IF($O$4="Fireworks",K18,IF($O$4="Landscape",L18,IF($O$4="Macro",M18,IF($O$4="People",N18,IF($O$4="Sports",O18,IF($O$4="Travel",P18,IF($O$4="Waterdrops",Q18,IF($O$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>On subject</x:v>
+        <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Birds in Flight",H18,IF($P$4="Birds Perched",I18,IF($P$4="Fireworks",J18,IF($P$4="Landscape",K18,IF($P$4="Macro",L18,IF($P$4="People",M18,IF($P$4="Sports",N18,IF($P$4="Travel",O18,IF($P$4="Waterdrops",P18,IF($P$4="Wildlife",Q18,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG18" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Androo",H18,IF($P$4="Birds in Flight",I18,IF($P$4="Birds Perched",J18,IF($P$4="Fireworks",K18,IF($P$4="Landscape",L18,IF($P$4="Macro",M18,IF($P$4="People",N18,IF($P$4="Sports",O18,IF($P$4="Travel",P18,IF($P$4="Waterdrops",Q18,IF($P$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AH18" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Androo",H18,IF($Q$4="Birds in Flight",I18,IF($Q$4="Birds Perched",J18,IF($Q$4="Fireworks",K18,IF($Q$4="Landscape",L18,IF($Q$4="Macro",M18,IF($Q$4="People",N18,IF($Q$4="Sports",O18,IF($Q$4="Travel",P18,IF($Q$4="Waterdrops",Q18,IF($Q$4="Wildlife",R18,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI18" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D18,IF($R$4="C2 Birds in Flight",E18,IF($R$4="C3 Landscape",F18,IF($R$4="Default Settings",G18,IF($R$4="Androo",H18,IF($R$4="Birds in Flight",I18,IF($R$4="Birds Perched",J18,IF($R$4="Fireworks",K18,IF($R$4="Landscape",L18,IF($R$4="Macro",M18,IF($R$4="People",N18,IF($R$4="Sports",O18,IF($R$4="Travel",P18,IF($R$4="Waterdrops",Q18,IF($R$4="Wildlife",R18,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Birds in Flight",H18,IF($Q$4="Birds Perched",I18,IF($Q$4="Fireworks",J18,IF($Q$4="Landscape",K18,IF($Q$4="Macro",L18,IF($Q$4="People",M18,IF($Q$4="Sports",N18,IF($Q$4="Travel",O18,IF($Q$4="Waterdrops",P18,IF($Q$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>On subject</x:v>
       </x:c>
     </x:row>
@@ -2487,96 +2375,89 @@
         <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="str">
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="L19" s="17" t="str">
+        <x:v>Spot AF</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="str">
         <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="K19" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L19" s="17" t="str">
-        <x:v>1-Point AF</x:v>
-      </x:c>
-      <x:c r="M19" s="17" t="str">
-        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="O19" s="17" t="str">
+        <x:v>1-Point AF</x:v>
+      </x:c>
+      <x:c r="P19" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q19" s="17" t="str">
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="P19" s="17" t="str">
+      <x:c r="R19" s="20" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="S19" s="20" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="T19" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Birds in Flight",H19,IF($D$4="Birds Perched",I19,IF($D$4="Fireworks",J19,IF($D$4="Landscape",K19,IF($D$4="Macro",L19,IF($D$4="People",M19,IF($D$4="Sports",N19,IF($D$4="Travel",O19,IF($D$4="Waterdrops",P19,IF($D$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="U19" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Birds in Flight",H19,IF($E$4="Birds Perched",I19,IF($E$4="Fireworks",J19,IF($E$4="Landscape",K19,IF($E$4="Macro",L19,IF($E$4="People",M19,IF($E$4="Sports",N19,IF($E$4="Travel",O19,IF($E$4="Waterdrops",P19,IF($E$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Face + Tracking</x:v>
+      </x:c>
+      <x:c r="V19" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Birds in Flight",H19,IF($F$4="Birds Perched",I19,IF($F$4="Fireworks",J19,IF($F$4="Landscape",K19,IF($F$4="Macro",L19,IF($F$4="People",M19,IF($F$4="Sports",N19,IF($F$4="Travel",O19,IF($F$4="Waterdrops",P19,IF($F$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="Q19" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R19" s="17" t="str">
+      <x:c r="W19" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Birds in Flight",H19,IF($G$4="Birds Perched",I19,IF($G$4="Fireworks",J19,IF($G$4="Landscape",K19,IF($G$4="Macro",L19,IF($G$4="People",M19,IF($G$4="Sports",N19,IF($G$4="Travel",O19,IF($G$4="Waterdrops",P19,IF($G$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="S19" s="20" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T19" s="20" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="U19" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Androo",H19,IF($D$4="Birds in Flight",I19,IF($D$4="Birds Perched",J19,IF($D$4="Fireworks",K19,IF($D$4="Landscape",L19,IF($D$4="Macro",M19,IF($D$4="People",N19,IF($D$4="Sports",O19,IF($D$4="Travel",P19,IF($D$4="Waterdrops",Q19,IF($D$4="Wildlife",R19,"")))))))))))))))</x:f>
+      <x:c r="X19" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Birds in Flight",H19,IF($H$4="Birds Perched",I19,IF($H$4="Fireworks",J19,IF($H$4="Landscape",K19,IF($H$4="Macro",L19,IF($H$4="People",M19,IF($H$4="Sports",N19,IF($H$4="Travel",O19,IF($H$4="Waterdrops",P19,IF($H$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="V19" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Androo",H19,IF($E$4="Birds in Flight",I19,IF($E$4="Birds Perched",J19,IF($E$4="Fireworks",K19,IF($E$4="Landscape",L19,IF($E$4="Macro",M19,IF($E$4="People",N19,IF($E$4="Sports",O19,IF($E$4="Travel",P19,IF($E$4="Waterdrops",Q19,IF($E$4="Wildlife",R19,"")))))))))))))))</x:f>
+      <x:c r="Y19" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Birds in Flight",H19,IF($I$4="Birds Perched",I19,IF($I$4="Fireworks",J19,IF($I$4="Landscape",K19,IF($I$4="Macro",L19,IF($I$4="People",M19,IF($I$4="Sports",N19,IF($I$4="Travel",O19,IF($I$4="Waterdrops",P19,IF($I$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="W19" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Androo",H19,IF($F$4="Birds in Flight",I19,IF($F$4="Birds Perched",J19,IF($F$4="Fireworks",K19,IF($F$4="Landscape",L19,IF($F$4="Macro",M19,IF($F$4="People",N19,IF($F$4="Sports",O19,IF($F$4="Travel",P19,IF($F$4="Waterdrops",Q19,IF($F$4="Wildlife",R19,"")))))))))))))))</x:f>
+      <x:c r="Z19" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Birds in Flight",H19,IF($J$4="Birds Perched",I19,IF($J$4="Fireworks",J19,IF($J$4="Landscape",K19,IF($J$4="Macro",L19,IF($J$4="People",M19,IF($J$4="Sports",N19,IF($J$4="Travel",O19,IF($J$4="Waterdrops",P19,IF($J$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA19" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Birds in Flight",H19,IF($K$4="Birds Perched",I19,IF($K$4="Fireworks",J19,IF($K$4="Landscape",K19,IF($K$4="Macro",L19,IF($K$4="People",M19,IF($K$4="Sports",N19,IF($K$4="Travel",O19,IF($K$4="Waterdrops",P19,IF($K$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="X19" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Androo",H19,IF($G$4="Birds in Flight",I19,IF($G$4="Birds Perched",J19,IF($G$4="Fireworks",K19,IF($G$4="Landscape",L19,IF($G$4="Macro",M19,IF($G$4="People",N19,IF($G$4="Sports",O19,IF($G$4="Travel",P19,IF($G$4="Waterdrops",Q19,IF($G$4="Wildlife",R19,"")))))))))))))))</x:f>
+      <x:c r="AB19" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Birds in Flight",H19,IF($L$4="Birds Perched",I19,IF($L$4="Fireworks",J19,IF($L$4="Landscape",K19,IF($L$4="Macro",L19,IF($L$4="People",M19,IF($L$4="Sports",N19,IF($L$4="Travel",O19,IF($L$4="Waterdrops",P19,IF($L$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Spot AF</x:v>
+      </x:c>
+      <x:c r="AC19" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Birds in Flight",H19,IF($M$4="Birds Perched",I19,IF($M$4="Fireworks",J19,IF($M$4="Landscape",K19,IF($M$4="Macro",L19,IF($M$4="People",M19,IF($M$4="Sports",N19,IF($M$4="Travel",O19,IF($M$4="Waterdrops",P19,IF($M$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="Y19" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Androo",H19,IF($H$4="Birds in Flight",I19,IF($H$4="Birds Perched",J19,IF($H$4="Fireworks",K19,IF($H$4="Landscape",L19,IF($H$4="Macro",M19,IF($H$4="People",N19,IF($H$4="Sports",O19,IF($H$4="Travel",P19,IF($H$4="Waterdrops",Q19,IF($H$4="Wildlife",R19,"")))))))))))))))</x:f>
+      <x:c r="AD19" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Birds in Flight",H19,IF($N$4="Birds Perched",I19,IF($N$4="Fireworks",J19,IF($N$4="Landscape",K19,IF($N$4="Macro",L19,IF($N$4="People",M19,IF($N$4="Sports",N19,IF($N$4="Travel",O19,IF($N$4="Waterdrops",P19,IF($N$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="Z19" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Androo",H19,IF($I$4="Birds in Flight",I19,IF($I$4="Birds Perched",J19,IF($I$4="Fireworks",K19,IF($I$4="Landscape",L19,IF($I$4="Macro",M19,IF($I$4="People",N19,IF($I$4="Sports",O19,IF($I$4="Travel",P19,IF($I$4="Waterdrops",Q19,IF($I$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="AA19" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Androo",H19,IF($J$4="Birds in Flight",I19,IF($J$4="Birds Perched",J19,IF($J$4="Fireworks",K19,IF($J$4="Landscape",L19,IF($J$4="Macro",M19,IF($J$4="People",N19,IF($J$4="Sports",O19,IF($J$4="Travel",P19,IF($J$4="Waterdrops",Q19,IF($J$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
-      <x:c r="AB19" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Androo",H19,IF($K$4="Birds in Flight",I19,IF($K$4="Birds Perched",J19,IF($K$4="Fireworks",K19,IF($K$4="Landscape",L19,IF($K$4="Macro",M19,IF($K$4="People",N19,IF($K$4="Sports",O19,IF($K$4="Travel",P19,IF($K$4="Waterdrops",Q19,IF($K$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC19" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Androo",H19,IF($L$4="Birds in Flight",I19,IF($L$4="Birds Perched",J19,IF($L$4="Fireworks",K19,IF($L$4="Landscape",L19,IF($L$4="Macro",M19,IF($L$4="People",N19,IF($L$4="Sports",O19,IF($L$4="Travel",P19,IF($L$4="Waterdrops",Q19,IF($L$4="Wildlife",R19,"")))))))))))))))</x:f>
+      <x:c r="AE19" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Birds in Flight",H19,IF($O$4="Birds Perched",I19,IF($O$4="Fireworks",J19,IF($O$4="Landscape",K19,IF($O$4="Macro",L19,IF($O$4="People",M19,IF($O$4="Sports",N19,IF($O$4="Travel",O19,IF($O$4="Waterdrops",P19,IF($O$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="AD19" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Androo",H19,IF($M$4="Birds in Flight",I19,IF($M$4="Birds Perched",J19,IF($M$4="Fireworks",K19,IF($M$4="Landscape",L19,IF($M$4="Macro",M19,IF($M$4="People",N19,IF($M$4="Sports",O19,IF($M$4="Travel",P19,IF($M$4="Waterdrops",Q19,IF($M$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Spot AF</x:v>
-      </x:c>
-      <x:c r="AE19" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Androo",H19,IF($N$4="Birds in Flight",I19,IF($N$4="Birds Perched",J19,IF($N$4="Fireworks",K19,IF($N$4="Landscape",L19,IF($N$4="Macro",M19,IF($N$4="People",N19,IF($N$4="Sports",O19,IF($N$4="Travel",P19,IF($N$4="Waterdrops",Q19,IF($N$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
-      </x:c>
       <x:c r="AF19" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Androo",H19,IF($O$4="Birds in Flight",I19,IF($O$4="Birds Perched",J19,IF($O$4="Fireworks",K19,IF($O$4="Landscape",L19,IF($O$4="Macro",M19,IF($O$4="People",N19,IF($O$4="Sports",O19,IF($O$4="Travel",P19,IF($O$4="Waterdrops",Q19,IF($O$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Birds in Flight",H19,IF($P$4="Birds Perched",I19,IF($P$4="Fireworks",J19,IF($P$4="Landscape",K19,IF($P$4="Macro",L19,IF($P$4="People",M19,IF($P$4="Sports",N19,IF($P$4="Travel",O19,IF($P$4="Waterdrops",P19,IF($P$4="Wildlife",Q19,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG19" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Androo",H19,IF($P$4="Birds in Flight",I19,IF($P$4="Birds Perched",J19,IF($P$4="Fireworks",K19,IF($P$4="Landscape",L19,IF($P$4="Macro",M19,IF($P$4="People",N19,IF($P$4="Sports",O19,IF($P$4="Travel",P19,IF($P$4="Waterdrops",Q19,IF($P$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
-      </x:c>
-      <x:c r="AH19" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Androo",H19,IF($Q$4="Birds in Flight",I19,IF($Q$4="Birds Perched",J19,IF($Q$4="Fireworks",K19,IF($Q$4="Landscape",L19,IF($Q$4="Macro",M19,IF($Q$4="People",N19,IF($Q$4="Sports",O19,IF($Q$4="Travel",P19,IF($Q$4="Waterdrops",Q19,IF($Q$4="Wildlife",R19,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI19" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D19,IF($R$4="C2 Birds in Flight",E19,IF($R$4="C3 Landscape",F19,IF($R$4="Default Settings",G19,IF($R$4="Androo",H19,IF($R$4="Birds in Flight",I19,IF($R$4="Birds Perched",J19,IF($R$4="Fireworks",K19,IF($R$4="Landscape",L19,IF($R$4="Macro",M19,IF($R$4="People",N19,IF($R$4="Sports",O19,IF($R$4="Travel",P19,IF($R$4="Waterdrops",Q19,IF($R$4="Wildlife",R19,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Birds in Flight",H19,IF($Q$4="Birds Perched",I19,IF($Q$4="Fireworks",J19,IF($Q$4="Landscape",K19,IF($Q$4="Macro",L19,IF($Q$4="People",M19,IF($Q$4="Sports",N19,IF($Q$4="Travel",O19,IF($Q$4="Waterdrops",P19,IF($Q$4="Wildlife",Q19,""))))))))))))))</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
@@ -2603,102 +2484,95 @@
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
-        <x:v>Vehicles</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
         <x:v>Animals</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="L20" s="17" t="str">
         <x:v>None</x:v>
       </x:c>
       <x:c r="M20" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="N20" s="17" t="str">
         <x:v>People</x:v>
       </x:c>
       <x:c r="O20" s="17" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="P20" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q20" s="17" t="str">
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="R20" s="20" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S20" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="T20" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Birds in Flight",H20,IF($D$4="Birds Perched",I20,IF($D$4="Fireworks",J20,IF($D$4="Landscape",K20,IF($D$4="Macro",L20,IF($D$4="People",M20,IF($D$4="Sports",N20,IF($D$4="Travel",O20,IF($D$4="Waterdrops",P20,IF($D$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="U20" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Birds in Flight",H20,IF($E$4="Birds Perched",I20,IF($E$4="Fireworks",J20,IF($E$4="Landscape",K20,IF($E$4="Macro",L20,IF($E$4="People",M20,IF($E$4="Sports",N20,IF($E$4="Travel",O20,IF($E$4="Waterdrops",P20,IF($E$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="V20" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Birds in Flight",H20,IF($F$4="Birds Perched",I20,IF($F$4="Fireworks",J20,IF($F$4="Landscape",K20,IF($F$4="Macro",L20,IF($F$4="People",M20,IF($F$4="Sports",N20,IF($F$4="Travel",O20,IF($F$4="Waterdrops",P20,IF($F$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="W20" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Birds in Flight",H20,IF($G$4="Birds Perched",I20,IF($G$4="Fireworks",J20,IF($G$4="Landscape",K20,IF($G$4="Macro",L20,IF($G$4="People",M20,IF($G$4="Sports",N20,IF($G$4="Travel",O20,IF($G$4="Waterdrops",P20,IF($G$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="X20" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Birds in Flight",H20,IF($H$4="Birds Perched",I20,IF($H$4="Fireworks",J20,IF($H$4="Landscape",K20,IF($H$4="Macro",L20,IF($H$4="People",M20,IF($H$4="Sports",N20,IF($H$4="Travel",O20,IF($H$4="Waterdrops",P20,IF($H$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="Y20" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Birds in Flight",H20,IF($I$4="Birds Perched",I20,IF($I$4="Fireworks",J20,IF($I$4="Landscape",K20,IF($I$4="Macro",L20,IF($I$4="People",M20,IF($I$4="Sports",N20,IF($I$4="Travel",O20,IF($I$4="Waterdrops",P20,IF($I$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Animals</x:v>
+      </x:c>
+      <x:c r="Z20" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Birds in Flight",H20,IF($J$4="Birds Perched",I20,IF($J$4="Fireworks",J20,IF($J$4="Landscape",K20,IF($J$4="Macro",L20,IF($J$4="People",M20,IF($J$4="Sports",N20,IF($J$4="Travel",O20,IF($J$4="Waterdrops",P20,IF($J$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA20" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Birds in Flight",H20,IF($K$4="Birds Perched",I20,IF($K$4="Fireworks",J20,IF($K$4="Landscape",K20,IF($K$4="Macro",L20,IF($K$4="People",M20,IF($K$4="Sports",N20,IF($K$4="Travel",O20,IF($K$4="Waterdrops",P20,IF($K$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AB20" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Birds in Flight",H20,IF($L$4="Birds Perched",I20,IF($L$4="Fireworks",J20,IF($L$4="Landscape",K20,IF($L$4="Macro",L20,IF($L$4="People",M20,IF($L$4="Sports",N20,IF($L$4="Travel",O20,IF($L$4="Waterdrops",P20,IF($L$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="AC20" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Birds in Flight",H20,IF($M$4="Birds Perched",I20,IF($M$4="Fireworks",J20,IF($M$4="Landscape",K20,IF($M$4="Macro",L20,IF($M$4="People",M20,IF($M$4="Sports",N20,IF($M$4="Travel",O20,IF($M$4="Waterdrops",P20,IF($M$4="Wildlife",Q20,""))))))))))))))</x:f>
         <x:v>People</x:v>
       </x:c>
-      <x:c r="P20" s="17" t="str">
+      <x:c r="AD20" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Birds in Flight",H20,IF($N$4="Birds Perched",I20,IF($N$4="Fireworks",J20,IF($N$4="Landscape",K20,IF($N$4="Macro",L20,IF($N$4="People",M20,IF($N$4="Sports",N20,IF($N$4="Travel",O20,IF($N$4="Waterdrops",P20,IF($N$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>People</x:v>
+      </x:c>
+      <x:c r="AE20" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Birds in Flight",H20,IF($O$4="Birds Perched",I20,IF($O$4="Fireworks",J20,IF($O$4="Landscape",K20,IF($O$4="Macro",L20,IF($O$4="People",M20,IF($O$4="Sports",N20,IF($O$4="Travel",O20,IF($O$4="Waterdrops",P20,IF($O$4="Wildlife",Q20,""))))))))))))))</x:f>
         <x:v>None</x:v>
       </x:c>
-      <x:c r="Q20" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R20" s="17" t="str">
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="S20" s="20" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T20" s="20" t="n">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="U20" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Androo",H20,IF($D$4="Birds in Flight",I20,IF($D$4="Birds Perched",J20,IF($D$4="Fireworks",K20,IF($D$4="Landscape",L20,IF($D$4="Macro",M20,IF($D$4="People",N20,IF($D$4="Sports",O20,IF($D$4="Travel",P20,IF($D$4="Waterdrops",Q20,IF($D$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="V20" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Androo",H20,IF($E$4="Birds in Flight",I20,IF($E$4="Birds Perched",J20,IF($E$4="Fireworks",K20,IF($E$4="Landscape",L20,IF($E$4="Macro",M20,IF($E$4="People",N20,IF($E$4="Sports",O20,IF($E$4="Travel",P20,IF($E$4="Waterdrops",Q20,IF($E$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="W20" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Androo",H20,IF($F$4="Birds in Flight",I20,IF($F$4="Birds Perched",J20,IF($F$4="Fireworks",K20,IF($F$4="Landscape",L20,IF($F$4="Macro",M20,IF($F$4="People",N20,IF($F$4="Sports",O20,IF($F$4="Travel",P20,IF($F$4="Waterdrops",Q20,IF($F$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="X20" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Androo",H20,IF($G$4="Birds in Flight",I20,IF($G$4="Birds Perched",J20,IF($G$4="Fireworks",K20,IF($G$4="Landscape",L20,IF($G$4="Macro",M20,IF($G$4="People",N20,IF($G$4="Sports",O20,IF($G$4="Travel",P20,IF($G$4="Waterdrops",Q20,IF($G$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="Y20" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Androo",H20,IF($H$4="Birds in Flight",I20,IF($H$4="Birds Perched",J20,IF($H$4="Fireworks",K20,IF($H$4="Landscape",L20,IF($H$4="Macro",M20,IF($H$4="People",N20,IF($H$4="Sports",O20,IF($H$4="Travel",P20,IF($H$4="Waterdrops",Q20,IF($H$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Vehicles</x:v>
-      </x:c>
-      <x:c r="Z20" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Androo",H20,IF($I$4="Birds in Flight",I20,IF($I$4="Birds Perched",J20,IF($I$4="Fireworks",K20,IF($I$4="Landscape",L20,IF($I$4="Macro",M20,IF($I$4="People",N20,IF($I$4="Sports",O20,IF($I$4="Travel",P20,IF($I$4="Waterdrops",Q20,IF($I$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="AA20" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Androo",H20,IF($J$4="Birds in Flight",I20,IF($J$4="Birds Perched",J20,IF($J$4="Fireworks",K20,IF($J$4="Landscape",L20,IF($J$4="Macro",M20,IF($J$4="People",N20,IF($J$4="Sports",O20,IF($J$4="Travel",P20,IF($J$4="Waterdrops",Q20,IF($J$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Animals</x:v>
-      </x:c>
-      <x:c r="AB20" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Androo",H20,IF($K$4="Birds in Flight",I20,IF($K$4="Birds Perched",J20,IF($K$4="Fireworks",K20,IF($K$4="Landscape",L20,IF($K$4="Macro",M20,IF($K$4="People",N20,IF($K$4="Sports",O20,IF($K$4="Travel",P20,IF($K$4="Waterdrops",Q20,IF($K$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC20" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Androo",H20,IF($L$4="Birds in Flight",I20,IF($L$4="Birds Perched",J20,IF($L$4="Fireworks",K20,IF($L$4="Landscape",L20,IF($L$4="Macro",M20,IF($L$4="People",N20,IF($L$4="Sports",O20,IF($L$4="Travel",P20,IF($L$4="Waterdrops",Q20,IF($L$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AD20" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Androo",H20,IF($M$4="Birds in Flight",I20,IF($M$4="Birds Perched",J20,IF($M$4="Fireworks",K20,IF($M$4="Landscape",L20,IF($M$4="Macro",M20,IF($M$4="People",N20,IF($M$4="Sports",O20,IF($M$4="Travel",P20,IF($M$4="Waterdrops",Q20,IF($M$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AE20" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Androo",H20,IF($N$4="Birds in Flight",I20,IF($N$4="Birds Perched",J20,IF($N$4="Fireworks",K20,IF($N$4="Landscape",L20,IF($N$4="Macro",M20,IF($N$4="People",N20,IF($N$4="Sports",O20,IF($N$4="Travel",P20,IF($N$4="Waterdrops",Q20,IF($N$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>People</x:v>
-      </x:c>
       <x:c r="AF20" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Androo",H20,IF($O$4="Birds in Flight",I20,IF($O$4="Birds Perched",J20,IF($O$4="Fireworks",K20,IF($O$4="Landscape",L20,IF($O$4="Macro",M20,IF($O$4="People",N20,IF($O$4="Sports",O20,IF($O$4="Travel",P20,IF($O$4="Waterdrops",Q20,IF($O$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Birds in Flight",H20,IF($P$4="Birds Perched",I20,IF($P$4="Fireworks",J20,IF($P$4="Landscape",K20,IF($P$4="Macro",L20,IF($P$4="People",M20,IF($P$4="Sports",N20,IF($P$4="Travel",O20,IF($P$4="Waterdrops",P20,IF($P$4="Wildlife",Q20,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG20" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Androo",H20,IF($P$4="Birds in Flight",I20,IF($P$4="Birds Perched",J20,IF($P$4="Fireworks",K20,IF($P$4="Landscape",L20,IF($P$4="Macro",M20,IF($P$4="People",N20,IF($P$4="Sports",O20,IF($P$4="Travel",P20,IF($P$4="Waterdrops",Q20,IF($P$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="AH20" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Androo",H20,IF($Q$4="Birds in Flight",I20,IF($Q$4="Birds Perched",J20,IF($Q$4="Fireworks",K20,IF($Q$4="Landscape",L20,IF($Q$4="Macro",M20,IF($Q$4="People",N20,IF($Q$4="Sports",O20,IF($Q$4="Travel",P20,IF($Q$4="Waterdrops",Q20,IF($Q$4="Wildlife",R20,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI20" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D20,IF($R$4="C2 Birds in Flight",E20,IF($R$4="C3 Landscape",F20,IF($R$4="Default Settings",G20,IF($R$4="Androo",H20,IF($R$4="Birds in Flight",I20,IF($R$4="Birds Perched",J20,IF($R$4="Fireworks",K20,IF($R$4="Landscape",L20,IF($R$4="Macro",M20,IF($R$4="People",N20,IF($R$4="Sports",O20,IF($R$4="Travel",P20,IF($R$4="Waterdrops",Q20,IF($R$4="Wildlife",R20,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Birds in Flight",H20,IF($Q$4="Birds Perched",I20,IF($Q$4="Fireworks",J20,IF($Q$4="Landscape",K20,IF($Q$4="Macro",L20,IF($Q$4="People",M20,IF($Q$4="Sports",N20,IF($Q$4="Travel",O20,IF($Q$4="Waterdrops",P20,IF($Q$4="Wildlife",Q20,""))))))))))))))</x:f>
         <x:v>Animals</x:v>
       </x:c>
     </x:row>
@@ -2725,102 +2599,95 @@
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="str">
         <x:v>Enable</x:v>
-      </x:c>
-      <x:c r="K21" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L21" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="M21" s="17" t="str">
-        <x:v>Disable</x:v>
       </x:c>
       <x:c r="N21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="O21" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P21" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q21" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="P21" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="Q21" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R21" s="17" t="str">
+      <x:c r="R21" s="20" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S21" s="20" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="T21" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Birds in Flight",H21,IF($D$4="Birds Perched",I21,IF($D$4="Fireworks",J21,IF($D$4="Landscape",K21,IF($D$4="Macro",L21,IF($D$4="People",M21,IF($D$4="Sports",N21,IF($D$4="Travel",O21,IF($D$4="Waterdrops",P21,IF($D$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="S21" s="20" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="T21" s="20" t="n">
-        <x:v>150</x:v>
-      </x:c>
       <x:c r="U21" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Androo",H21,IF($D$4="Birds in Flight",I21,IF($D$4="Birds Perched",J21,IF($D$4="Fireworks",K21,IF($D$4="Landscape",L21,IF($D$4="Macro",M21,IF($D$4="People",N21,IF($D$4="Sports",O21,IF($D$4="Travel",P21,IF($D$4="Waterdrops",Q21,IF($D$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Birds in Flight",H21,IF($E$4="Birds Perched",I21,IF($E$4="Fireworks",J21,IF($E$4="Landscape",K21,IF($E$4="Macro",L21,IF($E$4="People",M21,IF($E$4="Sports",N21,IF($E$4="Travel",O21,IF($E$4="Waterdrops",P21,IF($E$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="V21" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Androo",H21,IF($E$4="Birds in Flight",I21,IF($E$4="Birds Perched",J21,IF($E$4="Fireworks",K21,IF($E$4="Landscape",L21,IF($E$4="Macro",M21,IF($E$4="People",N21,IF($E$4="Sports",O21,IF($E$4="Travel",P21,IF($E$4="Waterdrops",Q21,IF($E$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Birds in Flight",H21,IF($F$4="Birds Perched",I21,IF($F$4="Fireworks",J21,IF($F$4="Landscape",K21,IF($F$4="Macro",L21,IF($F$4="People",M21,IF($F$4="Sports",N21,IF($F$4="Travel",O21,IF($F$4="Waterdrops",P21,IF($F$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W21" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Birds in Flight",H21,IF($G$4="Birds Perched",I21,IF($G$4="Fireworks",J21,IF($G$4="Landscape",K21,IF($G$4="Macro",L21,IF($G$4="People",M21,IF($G$4="Sports",N21,IF($G$4="Travel",O21,IF($G$4="Waterdrops",P21,IF($G$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="W21" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Androo",H21,IF($F$4="Birds in Flight",I21,IF($F$4="Birds Perched",J21,IF($F$4="Fireworks",K21,IF($F$4="Landscape",L21,IF($F$4="Macro",M21,IF($F$4="People",N21,IF($F$4="Sports",O21,IF($F$4="Travel",P21,IF($F$4="Waterdrops",Q21,IF($F$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="X21" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Androo",H21,IF($G$4="Birds in Flight",I21,IF($G$4="Birds Perched",J21,IF($G$4="Fireworks",K21,IF($G$4="Landscape",L21,IF($G$4="Macro",M21,IF($G$4="People",N21,IF($G$4="Sports",O21,IF($G$4="Travel",P21,IF($G$4="Waterdrops",Q21,IF($G$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Birds in Flight",H21,IF($H$4="Birds Perched",I21,IF($H$4="Fireworks",J21,IF($H$4="Landscape",K21,IF($H$4="Macro",L21,IF($H$4="People",M21,IF($H$4="Sports",N21,IF($H$4="Travel",O21,IF($H$4="Waterdrops",P21,IF($H$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="Y21" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Androo",H21,IF($H$4="Birds in Flight",I21,IF($H$4="Birds Perched",J21,IF($H$4="Fireworks",K21,IF($H$4="Landscape",L21,IF($H$4="Macro",M21,IF($H$4="People",N21,IF($H$4="Sports",O21,IF($H$4="Travel",P21,IF($H$4="Waterdrops",Q21,IF($H$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Birds in Flight",H21,IF($I$4="Birds Perched",I21,IF($I$4="Fireworks",J21,IF($I$4="Landscape",K21,IF($I$4="Macro",L21,IF($I$4="People",M21,IF($I$4="Sports",N21,IF($I$4="Travel",O21,IF($I$4="Waterdrops",P21,IF($I$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Z21" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Androo",H21,IF($I$4="Birds in Flight",I21,IF($I$4="Birds Perched",J21,IF($I$4="Fireworks",K21,IF($I$4="Landscape",L21,IF($I$4="Macro",M21,IF($I$4="People",N21,IF($I$4="Sports",O21,IF($I$4="Travel",P21,IF($I$4="Waterdrops",Q21,IF($I$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Birds in Flight",H21,IF($J$4="Birds Perched",I21,IF($J$4="Fireworks",J21,IF($J$4="Landscape",K21,IF($J$4="Macro",L21,IF($J$4="People",M21,IF($J$4="Sports",N21,IF($J$4="Travel",O21,IF($J$4="Waterdrops",P21,IF($J$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA21" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Birds in Flight",H21,IF($K$4="Birds Perched",I21,IF($K$4="Fireworks",J21,IF($K$4="Landscape",K21,IF($K$4="Macro",L21,IF($K$4="People",M21,IF($K$4="Sports",N21,IF($K$4="Travel",O21,IF($K$4="Waterdrops",P21,IF($K$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB21" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Birds in Flight",H21,IF($L$4="Birds Perched",I21,IF($L$4="Fireworks",J21,IF($L$4="Landscape",K21,IF($L$4="Macro",L21,IF($L$4="People",M21,IF($L$4="Sports",N21,IF($L$4="Travel",O21,IF($L$4="Waterdrops",P21,IF($L$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AC21" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Birds in Flight",H21,IF($M$4="Birds Perched",I21,IF($M$4="Fireworks",J21,IF($M$4="Landscape",K21,IF($M$4="Macro",L21,IF($M$4="People",M21,IF($M$4="Sports",N21,IF($M$4="Travel",O21,IF($M$4="Waterdrops",P21,IF($M$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="AA21" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Androo",H21,IF($J$4="Birds in Flight",I21,IF($J$4="Birds Perched",J21,IF($J$4="Fireworks",K21,IF($J$4="Landscape",L21,IF($J$4="Macro",M21,IF($J$4="People",N21,IF($J$4="Sports",O21,IF($J$4="Travel",P21,IF($J$4="Waterdrops",Q21,IF($J$4="Wildlife",R21,"")))))))))))))))</x:f>
+      <x:c r="AD21" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Birds in Flight",H21,IF($N$4="Birds Perched",I21,IF($N$4="Fireworks",J21,IF($N$4="Landscape",K21,IF($N$4="Macro",L21,IF($N$4="People",M21,IF($N$4="Sports",N21,IF($N$4="Travel",O21,IF($N$4="Waterdrops",P21,IF($N$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="AB21" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Androo",H21,IF($K$4="Birds in Flight",I21,IF($K$4="Birds Perched",J21,IF($K$4="Fireworks",K21,IF($K$4="Landscape",L21,IF($K$4="Macro",M21,IF($K$4="People",N21,IF($K$4="Sports",O21,IF($K$4="Travel",P21,IF($K$4="Waterdrops",Q21,IF($K$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC21" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Androo",H21,IF($L$4="Birds in Flight",I21,IF($L$4="Birds Perched",J21,IF($L$4="Fireworks",K21,IF($L$4="Landscape",L21,IF($L$4="Macro",M21,IF($L$4="People",N21,IF($L$4="Sports",O21,IF($L$4="Travel",P21,IF($L$4="Waterdrops",Q21,IF($L$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AD21" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Androo",H21,IF($M$4="Birds in Flight",I21,IF($M$4="Birds Perched",J21,IF($M$4="Fireworks",K21,IF($M$4="Landscape",L21,IF($M$4="Macro",M21,IF($M$4="People",N21,IF($M$4="Sports",O21,IF($M$4="Travel",P21,IF($M$4="Waterdrops",Q21,IF($M$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="AE21" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Androo",H21,IF($N$4="Birds in Flight",I21,IF($N$4="Birds Perched",J21,IF($N$4="Fireworks",K21,IF($N$4="Landscape",L21,IF($N$4="Macro",M21,IF($N$4="People",N21,IF($N$4="Sports",O21,IF($N$4="Travel",P21,IF($N$4="Waterdrops",Q21,IF($N$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Birds in Flight",H21,IF($O$4="Birds Perched",I21,IF($O$4="Fireworks",J21,IF($O$4="Landscape",K21,IF($O$4="Macro",L21,IF($O$4="People",M21,IF($O$4="Sports",N21,IF($O$4="Travel",O21,IF($O$4="Waterdrops",P21,IF($O$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AF21" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Androo",H21,IF($O$4="Birds in Flight",I21,IF($O$4="Birds Perched",J21,IF($O$4="Fireworks",K21,IF($O$4="Landscape",L21,IF($O$4="Macro",M21,IF($O$4="People",N21,IF($O$4="Sports",O21,IF($O$4="Travel",P21,IF($O$4="Waterdrops",Q21,IF($O$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Birds in Flight",H21,IF($P$4="Birds Perched",I21,IF($P$4="Fireworks",J21,IF($P$4="Landscape",K21,IF($P$4="Macro",L21,IF($P$4="People",M21,IF($P$4="Sports",N21,IF($P$4="Travel",O21,IF($P$4="Waterdrops",P21,IF($P$4="Wildlife",Q21,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG21" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Androo",H21,IF($P$4="Birds in Flight",I21,IF($P$4="Birds Perched",J21,IF($P$4="Fireworks",K21,IF($P$4="Landscape",L21,IF($P$4="Macro",M21,IF($P$4="People",N21,IF($P$4="Sports",O21,IF($P$4="Travel",P21,IF($P$4="Waterdrops",Q21,IF($P$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AH21" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Androo",H21,IF($Q$4="Birds in Flight",I21,IF($Q$4="Birds Perched",J21,IF($Q$4="Fireworks",K21,IF($Q$4="Landscape",L21,IF($Q$4="Macro",M21,IF($Q$4="People",N21,IF($Q$4="Sports",O21,IF($Q$4="Travel",P21,IF($Q$4="Waterdrops",Q21,IF($Q$4="Wildlife",R21,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI21" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D21,IF($R$4="C2 Birds in Flight",E21,IF($R$4="C3 Landscape",F21,IF($R$4="Default Settings",G21,IF($R$4="Androo",H21,IF($R$4="Birds in Flight",I21,IF($R$4="Birds Perched",J21,IF($R$4="Fireworks",K21,IF($R$4="Landscape",L21,IF($R$4="Macro",M21,IF($R$4="People",N21,IF($R$4="Sports",O21,IF($R$4="Travel",P21,IF($R$4="Waterdrops",Q21,IF($R$4="Wildlife",R21,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Birds in Flight",H21,IF($Q$4="Birds Perched",I21,IF($Q$4="Fireworks",J21,IF($Q$4="Landscape",K21,IF($Q$4="Macro",L21,IF($Q$4="People",M21,IF($Q$4="Sports",N21,IF($Q$4="Travel",O21,IF($Q$4="Waterdrops",P21,IF($Q$4="Wildlife",Q21,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
@@ -2847,13 +2714,13 @@
         <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="H22" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="J22" s="17" t="str">
         <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="I22" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
-      </x:c>
-      <x:c r="J22" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
         <x:v>Single Shot</x:v>
@@ -2862,87 +2729,80 @@
         <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="M22" s="17" t="str">
+        <x:v>Low Speed Continuous</x:v>
+      </x:c>
+      <x:c r="N22" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="O22" s="17" t="str">
         <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="N22" s="17" t="str">
-        <x:v>Low Speed Continuous</x:v>
-      </x:c>
-      <x:c r="O22" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
       </x:c>
       <x:c r="P22" s="17" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
       <x:c r="Q22" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="R22" s="20" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="S22" s="20" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="T22" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Birds in Flight",H22,IF($D$4="Birds Perched",I22,IF($D$4="Fireworks",J22,IF($D$4="Landscape",K22,IF($D$4="Macro",L22,IF($D$4="People",M22,IF($D$4="Sports",N22,IF($D$4="Travel",O22,IF($D$4="Waterdrops",P22,IF($D$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="U22" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Birds in Flight",H22,IF($E$4="Birds Perched",I22,IF($E$4="Fireworks",J22,IF($E$4="Landscape",K22,IF($E$4="Macro",L22,IF($E$4="People",M22,IF($E$4="Sports",N22,IF($E$4="Travel",O22,IF($E$4="Waterdrops",P22,IF($E$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="V22" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Birds in Flight",H22,IF($F$4="Birds Perched",I22,IF($F$4="Fireworks",J22,IF($F$4="Landscape",K22,IF($F$4="Macro",L22,IF($F$4="People",M22,IF($F$4="Sports",N22,IF($F$4="Travel",O22,IF($F$4="Waterdrops",P22,IF($F$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="R22" s="17" t="str">
+      <x:c r="W22" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Birds in Flight",H22,IF($G$4="Birds Perched",I22,IF($G$4="Fireworks",J22,IF($G$4="Landscape",K22,IF($G$4="Macro",L22,IF($G$4="People",M22,IF($G$4="Sports",N22,IF($G$4="Travel",O22,IF($G$4="Waterdrops",P22,IF($G$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="S22" s="20" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="T22" s="20" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="U22" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Androo",H22,IF($D$4="Birds in Flight",I22,IF($D$4="Birds Perched",J22,IF($D$4="Fireworks",K22,IF($D$4="Landscape",L22,IF($D$4="Macro",M22,IF($D$4="People",N22,IF($D$4="Sports",O22,IF($D$4="Travel",P22,IF($D$4="Waterdrops",Q22,IF($D$4="Wildlife",R22,"")))))))))))))))</x:f>
+      <x:c r="X22" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Birds in Flight",H22,IF($H$4="Birds Perched",I22,IF($H$4="Fireworks",J22,IF($H$4="Landscape",K22,IF($H$4="Macro",L22,IF($H$4="People",M22,IF($H$4="Sports",N22,IF($H$4="Travel",O22,IF($H$4="Waterdrops",P22,IF($H$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="Y22" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Birds in Flight",H22,IF($I$4="Birds Perched",I22,IF($I$4="Fireworks",J22,IF($I$4="Landscape",K22,IF($I$4="Macro",L22,IF($I$4="People",M22,IF($I$4="Sports",N22,IF($I$4="Travel",O22,IF($I$4="Waterdrops",P22,IF($I$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="V22" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Androo",H22,IF($E$4="Birds in Flight",I22,IF($E$4="Birds Perched",J22,IF($E$4="Fireworks",K22,IF($E$4="Landscape",L22,IF($E$4="Macro",M22,IF($E$4="People",N22,IF($E$4="Sports",O22,IF($E$4="Travel",P22,IF($E$4="Waterdrops",Q22,IF($E$4="Wildlife",R22,"")))))))))))))))</x:f>
+      <x:c r="Z22" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Birds in Flight",H22,IF($J$4="Birds Perched",I22,IF($J$4="Fireworks",J22,IF($J$4="Landscape",K22,IF($J$4="Macro",L22,IF($J$4="People",M22,IF($J$4="Sports",N22,IF($J$4="Travel",O22,IF($J$4="Waterdrops",P22,IF($J$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AA22" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Birds in Flight",H22,IF($K$4="Birds Perched",I22,IF($K$4="Fireworks",J22,IF($K$4="Landscape",K22,IF($K$4="Macro",L22,IF($K$4="People",M22,IF($K$4="Sports",N22,IF($K$4="Travel",O22,IF($K$4="Waterdrops",P22,IF($K$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AB22" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Birds in Flight",H22,IF($L$4="Birds Perched",I22,IF($L$4="Fireworks",J22,IF($L$4="Landscape",K22,IF($L$4="Macro",L22,IF($L$4="People",M22,IF($L$4="Sports",N22,IF($L$4="Travel",O22,IF($L$4="Waterdrops",P22,IF($L$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AC22" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Birds in Flight",H22,IF($M$4="Birds Perched",I22,IF($M$4="Fireworks",J22,IF($M$4="Landscape",K22,IF($M$4="Macro",L22,IF($M$4="People",M22,IF($M$4="Sports",N22,IF($M$4="Travel",O22,IF($M$4="Waterdrops",P22,IF($M$4="Wildlife",Q22,""))))))))))))))</x:f>
+        <x:v>Low Speed Continuous</x:v>
+      </x:c>
+      <x:c r="AD22" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Birds in Flight",H22,IF($N$4="Birds Perched",I22,IF($N$4="Fireworks",J22,IF($N$4="Landscape",K22,IF($N$4="Macro",L22,IF($N$4="People",M22,IF($N$4="Sports",N22,IF($N$4="Travel",O22,IF($N$4="Waterdrops",P22,IF($N$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="W22" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Androo",H22,IF($F$4="Birds in Flight",I22,IF($F$4="Birds Perched",J22,IF($F$4="Fireworks",K22,IF($F$4="Landscape",L22,IF($F$4="Macro",M22,IF($F$4="People",N22,IF($F$4="Sports",O22,IF($F$4="Travel",P22,IF($F$4="Waterdrops",Q22,IF($F$4="Wildlife",R22,"")))))))))))))))</x:f>
+      <x:c r="AE22" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Birds in Flight",H22,IF($O$4="Birds Perched",I22,IF($O$4="Fireworks",J22,IF($O$4="Landscape",K22,IF($O$4="Macro",L22,IF($O$4="People",M22,IF($O$4="Sports",N22,IF($O$4="Travel",O22,IF($O$4="Waterdrops",P22,IF($O$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="X22" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Androo",H22,IF($G$4="Birds in Flight",I22,IF($G$4="Birds Perched",J22,IF($G$4="Fireworks",K22,IF($G$4="Landscape",L22,IF($G$4="Macro",M22,IF($G$4="People",N22,IF($G$4="Sports",O22,IF($G$4="Travel",P22,IF($G$4="Waterdrops",Q22,IF($G$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
-      </x:c>
-      <x:c r="Y22" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Androo",H22,IF($H$4="Birds in Flight",I22,IF($H$4="Birds Perched",J22,IF($H$4="Fireworks",K22,IF($H$4="Landscape",L22,IF($H$4="Macro",M22,IF($H$4="People",N22,IF($H$4="Sports",O22,IF($H$4="Travel",P22,IF($H$4="Waterdrops",Q22,IF($H$4="Wildlife",R22,"")))))))))))))))</x:f>
+      <x:c r="AF22" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Birds in Flight",H22,IF($P$4="Birds Perched",I22,IF($P$4="Fireworks",J22,IF($P$4="Landscape",K22,IF($P$4="Macro",L22,IF($P$4="People",M22,IF($P$4="Sports",N22,IF($P$4="Travel",O22,IF($P$4="Waterdrops",P22,IF($P$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="Z22" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Androo",H22,IF($I$4="Birds in Flight",I22,IF($I$4="Birds Perched",J22,IF($I$4="Fireworks",K22,IF($I$4="Landscape",L22,IF($I$4="Macro",M22,IF($I$4="People",N22,IF($I$4="Sports",O22,IF($I$4="Travel",P22,IF($I$4="Waterdrops",Q22,IF($I$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
-      </x:c>
-      <x:c r="AA22" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Androo",H22,IF($J$4="Birds in Flight",I22,IF($J$4="Birds Perched",J22,IF($J$4="Fireworks",K22,IF($J$4="Landscape",L22,IF($J$4="Macro",M22,IF($J$4="People",N22,IF($J$4="Sports",O22,IF($J$4="Travel",P22,IF($J$4="Waterdrops",Q22,IF($J$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
-      </x:c>
-      <x:c r="AB22" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Androo",H22,IF($K$4="Birds in Flight",I22,IF($K$4="Birds Perched",J22,IF($K$4="Fireworks",K22,IF($K$4="Landscape",L22,IF($K$4="Macro",M22,IF($K$4="People",N22,IF($K$4="Sports",O22,IF($K$4="Travel",P22,IF($K$4="Waterdrops",Q22,IF($K$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="AC22" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Androo",H22,IF($L$4="Birds in Flight",I22,IF($L$4="Birds Perched",J22,IF($L$4="Fireworks",K22,IF($L$4="Landscape",L22,IF($L$4="Macro",M22,IF($L$4="People",N22,IF($L$4="Sports",O22,IF($L$4="Travel",P22,IF($L$4="Waterdrops",Q22,IF($L$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="AD22" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Androo",H22,IF($M$4="Birds in Flight",I22,IF($M$4="Birds Perched",J22,IF($M$4="Fireworks",K22,IF($M$4="Landscape",L22,IF($M$4="Macro",M22,IF($M$4="People",N22,IF($M$4="Sports",O22,IF($M$4="Travel",P22,IF($M$4="Waterdrops",Q22,IF($M$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="AE22" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Androo",H22,IF($N$4="Birds in Flight",I22,IF($N$4="Birds Perched",J22,IF($N$4="Fireworks",K22,IF($N$4="Landscape",L22,IF($N$4="Macro",M22,IF($N$4="People",N22,IF($N$4="Sports",O22,IF($N$4="Travel",P22,IF($N$4="Waterdrops",Q22,IF($N$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>Low Speed Continuous</x:v>
-      </x:c>
-      <x:c r="AF22" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Androo",H22,IF($O$4="Birds in Flight",I22,IF($O$4="Birds Perched",J22,IF($O$4="Fireworks",K22,IF($O$4="Landscape",L22,IF($O$4="Macro",M22,IF($O$4="People",N22,IF($O$4="Sports",O22,IF($O$4="Travel",P22,IF($O$4="Waterdrops",Q22,IF($O$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
-      </x:c>
       <x:c r="AG22" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Androo",H22,IF($P$4="Birds in Flight",I22,IF($P$4="Birds Perched",J22,IF($P$4="Fireworks",K22,IF($P$4="Landscape",L22,IF($P$4="Macro",M22,IF($P$4="People",N22,IF($P$4="Sports",O22,IF($P$4="Travel",P22,IF($P$4="Waterdrops",Q22,IF($P$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="AH22" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Androo",H22,IF($Q$4="Birds in Flight",I22,IF($Q$4="Birds Perched",J22,IF($Q$4="Fireworks",K22,IF($Q$4="Landscape",L22,IF($Q$4="Macro",M22,IF($Q$4="People",N22,IF($Q$4="Sports",O22,IF($Q$4="Travel",P22,IF($Q$4="Waterdrops",Q22,IF($Q$4="Wildlife",R22,"")))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
-      </x:c>
-      <x:c r="AI22" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D22,IF($R$4="C2 Birds in Flight",E22,IF($R$4="C3 Landscape",F22,IF($R$4="Default Settings",G22,IF($R$4="Androo",H22,IF($R$4="Birds in Flight",I22,IF($R$4="Birds Perched",J22,IF($R$4="Fireworks",K22,IF($R$4="Landscape",L22,IF($R$4="Macro",M22,IF($R$4="People",N22,IF($R$4="Sports",O22,IF($R$4="Travel",P22,IF($R$4="Waterdrops",Q22,IF($R$4="Wildlife",R22,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Birds in Flight",H22,IF($Q$4="Birds Perched",I22,IF($Q$4="Fireworks",J22,IF($Q$4="Landscape",K22,IF($Q$4="Macro",L22,IF($Q$4="People",M22,IF($Q$4="Sports",N22,IF($Q$4="Travel",O22,IF($Q$4="Waterdrops",P22,IF($Q$4="Wildlife",Q22,""))))))))))))))</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
     </x:row>
@@ -2972,99 +2832,92 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="J23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="N23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="O23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="P23" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q23" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="K23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="M23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="N23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="O23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="P23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Q23" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="R23" s="17" t="str">
+      <x:c r="R23" s="20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="S23" s="20" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="T23" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D23,IF($D$4="C2 Birds in Flight",E23,IF($D$4="C3 Landscape",F23,IF($D$4="Default Settings",G23,IF($D$4="Birds in Flight",H23,IF($D$4="Birds Perched",I23,IF($D$4="Fireworks",J23,IF($D$4="Landscape",K23,IF($D$4="Macro",L23,IF($D$4="People",M23,IF($D$4="Sports",N23,IF($D$4="Travel",O23,IF($D$4="Waterdrops",P23,IF($D$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="S23" s="20" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="T23" s="20" t="n">
-        <x:v>165</x:v>
-      </x:c>
       <x:c r="U23" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D23,IF($D$4="C2 Birds in Flight",E23,IF($D$4="C3 Landscape",F23,IF($D$4="Default Settings",G23,IF($D$4="Androo",H23,IF($D$4="Birds in Flight",I23,IF($D$4="Birds Perched",J23,IF($D$4="Fireworks",K23,IF($D$4="Landscape",L23,IF($D$4="Macro",M23,IF($D$4="People",N23,IF($D$4="Sports",O23,IF($D$4="Travel",P23,IF($D$4="Waterdrops",Q23,IF($D$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($E$4="C1 Wildlife",D23,IF($E$4="C2 Birds in Flight",E23,IF($E$4="C3 Landscape",F23,IF($E$4="Default Settings",G23,IF($E$4="Birds in Flight",H23,IF($E$4="Birds Perched",I23,IF($E$4="Fireworks",J23,IF($E$4="Landscape",K23,IF($E$4="Macro",L23,IF($E$4="People",M23,IF($E$4="Sports",N23,IF($E$4="Travel",O23,IF($E$4="Waterdrops",P23,IF($E$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="V23" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D23,IF($F$4="C2 Birds in Flight",E23,IF($F$4="C3 Landscape",F23,IF($F$4="Default Settings",G23,IF($F$4="Birds in Flight",H23,IF($F$4="Birds Perched",I23,IF($F$4="Fireworks",J23,IF($F$4="Landscape",K23,IF($F$4="Macro",L23,IF($F$4="People",M23,IF($F$4="Sports",N23,IF($F$4="Travel",O23,IF($F$4="Waterdrops",P23,IF($F$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W23" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D23,IF($G$4="C2 Birds in Flight",E23,IF($G$4="C3 Landscape",F23,IF($G$4="Default Settings",G23,IF($G$4="Birds in Flight",H23,IF($G$4="Birds Perched",I23,IF($G$4="Fireworks",J23,IF($G$4="Landscape",K23,IF($G$4="Macro",L23,IF($G$4="People",M23,IF($G$4="Sports",N23,IF($G$4="Travel",O23,IF($G$4="Waterdrops",P23,IF($G$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="V23" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D23,IF($E$4="C2 Birds in Flight",E23,IF($E$4="C3 Landscape",F23,IF($E$4="Default Settings",G23,IF($E$4="Androo",H23,IF($E$4="Birds in Flight",I23,IF($E$4="Birds Perched",J23,IF($E$4="Fireworks",K23,IF($E$4="Landscape",L23,IF($E$4="Macro",M23,IF($E$4="People",N23,IF($E$4="Sports",O23,IF($E$4="Travel",P23,IF($E$4="Waterdrops",Q23,IF($E$4="Wildlife",R23,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="W23" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D23,IF($F$4="C2 Birds in Flight",E23,IF($F$4="C3 Landscape",F23,IF($F$4="Default Settings",G23,IF($F$4="Androo",H23,IF($F$4="Birds in Flight",I23,IF($F$4="Birds Perched",J23,IF($F$4="Fireworks",K23,IF($F$4="Landscape",L23,IF($F$4="Macro",M23,IF($F$4="People",N23,IF($F$4="Sports",O23,IF($F$4="Travel",P23,IF($F$4="Waterdrops",Q23,IF($F$4="Wildlife",R23,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="X23" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D23,IF($G$4="C2 Birds in Flight",E23,IF($G$4="C3 Landscape",F23,IF($G$4="Default Settings",G23,IF($G$4="Androo",H23,IF($G$4="Birds in Flight",I23,IF($G$4="Birds Perched",J23,IF($G$4="Fireworks",K23,IF($G$4="Landscape",L23,IF($G$4="Macro",M23,IF($G$4="People",N23,IF($G$4="Sports",O23,IF($G$4="Travel",P23,IF($G$4="Waterdrops",Q23,IF($G$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($H$4="C1 Wildlife",D23,IF($H$4="C2 Birds in Flight",E23,IF($H$4="C3 Landscape",F23,IF($H$4="Default Settings",G23,IF($H$4="Birds in Flight",H23,IF($H$4="Birds Perched",I23,IF($H$4="Fireworks",J23,IF($H$4="Landscape",K23,IF($H$4="Macro",L23,IF($H$4="People",M23,IF($H$4="Sports",N23,IF($H$4="Travel",O23,IF($H$4="Waterdrops",P23,IF($H$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Y23" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D23,IF($I$4="C2 Birds in Flight",E23,IF($I$4="C3 Landscape",F23,IF($I$4="Default Settings",G23,IF($I$4="Birds in Flight",H23,IF($I$4="Birds Perched",I23,IF($I$4="Fireworks",J23,IF($I$4="Landscape",K23,IF($I$4="Macro",L23,IF($I$4="People",M23,IF($I$4="Sports",N23,IF($I$4="Travel",O23,IF($I$4="Waterdrops",P23,IF($I$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="Y23" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D23,IF($H$4="C2 Birds in Flight",E23,IF($H$4="C3 Landscape",F23,IF($H$4="Default Settings",G23,IF($H$4="Androo",H23,IF($H$4="Birds in Flight",I23,IF($H$4="Birds Perched",J23,IF($H$4="Fireworks",K23,IF($H$4="Landscape",L23,IF($H$4="Macro",M23,IF($H$4="People",N23,IF($H$4="Sports",O23,IF($H$4="Travel",P23,IF($H$4="Waterdrops",Q23,IF($H$4="Wildlife",R23,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
       <x:c r="Z23" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D23,IF($I$4="C2 Birds in Flight",E23,IF($I$4="C3 Landscape",F23,IF($I$4="Default Settings",G23,IF($I$4="Androo",H23,IF($I$4="Birds in Flight",I23,IF($I$4="Birds Perched",J23,IF($I$4="Fireworks",K23,IF($I$4="Landscape",L23,IF($I$4="Macro",M23,IF($I$4="People",N23,IF($I$4="Sports",O23,IF($I$4="Travel",P23,IF($I$4="Waterdrops",Q23,IF($I$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($J$4="C1 Wildlife",D23,IF($J$4="C2 Birds in Flight",E23,IF($J$4="C3 Landscape",F23,IF($J$4="Default Settings",G23,IF($J$4="Birds in Flight",H23,IF($J$4="Birds Perched",I23,IF($J$4="Fireworks",J23,IF($J$4="Landscape",K23,IF($J$4="Macro",L23,IF($J$4="People",M23,IF($J$4="Sports",N23,IF($J$4="Travel",O23,IF($J$4="Waterdrops",P23,IF($J$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AA23" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D23,IF($J$4="C2 Birds in Flight",E23,IF($J$4="C3 Landscape",F23,IF($J$4="Default Settings",G23,IF($J$4="Androo",H23,IF($J$4="Birds in Flight",I23,IF($J$4="Birds Perched",J23,IF($J$4="Fireworks",K23,IF($J$4="Landscape",L23,IF($J$4="Macro",M23,IF($J$4="People",N23,IF($J$4="Sports",O23,IF($J$4="Travel",P23,IF($J$4="Waterdrops",Q23,IF($J$4="Wildlife",R23,"")))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:f>IF($K$4="C1 Wildlife",D23,IF($K$4="C2 Birds in Flight",E23,IF($K$4="C3 Landscape",F23,IF($K$4="Default Settings",G23,IF($K$4="Birds in Flight",H23,IF($K$4="Birds Perched",I23,IF($K$4="Fireworks",J23,IF($K$4="Landscape",K23,IF($K$4="Macro",L23,IF($K$4="People",M23,IF($K$4="Sports",N23,IF($K$4="Travel",O23,IF($K$4="Waterdrops",P23,IF($K$4="Wildlife",Q23,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB23" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D23,IF($K$4="C2 Birds in Flight",E23,IF($K$4="C3 Landscape",F23,IF($K$4="Default Settings",G23,IF($K$4="Androo",H23,IF($K$4="Birds in Flight",I23,IF($K$4="Birds Perched",J23,IF($K$4="Fireworks",K23,IF($K$4="Landscape",L23,IF($K$4="Macro",M23,IF($K$4="People",N23,IF($K$4="Sports",O23,IF($K$4="Travel",P23,IF($K$4="Waterdrops",Q23,IF($K$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($L$4="C1 Wildlife",D23,IF($L$4="C2 Birds in Flight",E23,IF($L$4="C3 Landscape",F23,IF($L$4="Default Settings",G23,IF($L$4="Birds in Flight",H23,IF($L$4="Birds Perched",I23,IF($L$4="Fireworks",J23,IF($L$4="Landscape",K23,IF($L$4="Macro",L23,IF($L$4="People",M23,IF($L$4="Sports",N23,IF($L$4="Travel",O23,IF($L$4="Waterdrops",P23,IF($L$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC23" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D23,IF($L$4="C2 Birds in Flight",E23,IF($L$4="C3 Landscape",F23,IF($L$4="Default Settings",G23,IF($L$4="Androo",H23,IF($L$4="Birds in Flight",I23,IF($L$4="Birds Perched",J23,IF($L$4="Fireworks",K23,IF($L$4="Landscape",L23,IF($L$4="Macro",M23,IF($L$4="People",N23,IF($L$4="Sports",O23,IF($L$4="Travel",P23,IF($L$4="Waterdrops",Q23,IF($L$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($M$4="C1 Wildlife",D23,IF($M$4="C2 Birds in Flight",E23,IF($M$4="C3 Landscape",F23,IF($M$4="Default Settings",G23,IF($M$4="Birds in Flight",H23,IF($M$4="Birds Perched",I23,IF($M$4="Fireworks",J23,IF($M$4="Landscape",K23,IF($M$4="Macro",L23,IF($M$4="People",M23,IF($M$4="Sports",N23,IF($M$4="Travel",O23,IF($M$4="Waterdrops",P23,IF($M$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AD23" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D23,IF($M$4="C2 Birds in Flight",E23,IF($M$4="C3 Landscape",F23,IF($M$4="Default Settings",G23,IF($M$4="Androo",H23,IF($M$4="Birds in Flight",I23,IF($M$4="Birds Perched",J23,IF($M$4="Fireworks",K23,IF($M$4="Landscape",L23,IF($M$4="Macro",M23,IF($M$4="People",N23,IF($M$4="Sports",O23,IF($M$4="Travel",P23,IF($M$4="Waterdrops",Q23,IF($M$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($N$4="C1 Wildlife",D23,IF($N$4="C2 Birds in Flight",E23,IF($N$4="C3 Landscape",F23,IF($N$4="Default Settings",G23,IF($N$4="Birds in Flight",H23,IF($N$4="Birds Perched",I23,IF($N$4="Fireworks",J23,IF($N$4="Landscape",K23,IF($N$4="Macro",L23,IF($N$4="People",M23,IF($N$4="Sports",N23,IF($N$4="Travel",O23,IF($N$4="Waterdrops",P23,IF($N$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AE23" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D23,IF($N$4="C2 Birds in Flight",E23,IF($N$4="C3 Landscape",F23,IF($N$4="Default Settings",G23,IF($N$4="Androo",H23,IF($N$4="Birds in Flight",I23,IF($N$4="Birds Perched",J23,IF($N$4="Fireworks",K23,IF($N$4="Landscape",L23,IF($N$4="Macro",M23,IF($N$4="People",N23,IF($N$4="Sports",O23,IF($N$4="Travel",P23,IF($N$4="Waterdrops",Q23,IF($N$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D23,IF($O$4="C2 Birds in Flight",E23,IF($O$4="C3 Landscape",F23,IF($O$4="Default Settings",G23,IF($O$4="Birds in Flight",H23,IF($O$4="Birds Perched",I23,IF($O$4="Fireworks",J23,IF($O$4="Landscape",K23,IF($O$4="Macro",L23,IF($O$4="People",M23,IF($O$4="Sports",N23,IF($O$4="Travel",O23,IF($O$4="Waterdrops",P23,IF($O$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AF23" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D23,IF($O$4="C2 Birds in Flight",E23,IF($O$4="C3 Landscape",F23,IF($O$4="Default Settings",G23,IF($O$4="Androo",H23,IF($O$4="Birds in Flight",I23,IF($O$4="Birds Perched",J23,IF($O$4="Fireworks",K23,IF($O$4="Landscape",L23,IF($O$4="Macro",M23,IF($O$4="People",N23,IF($O$4="Sports",O23,IF($O$4="Travel",P23,IF($O$4="Waterdrops",Q23,IF($O$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D23,IF($P$4="C2 Birds in Flight",E23,IF($P$4="C3 Landscape",F23,IF($P$4="Default Settings",G23,IF($P$4="Birds in Flight",H23,IF($P$4="Birds Perched",I23,IF($P$4="Fireworks",J23,IF($P$4="Landscape",K23,IF($P$4="Macro",L23,IF($P$4="People",M23,IF($P$4="Sports",N23,IF($P$4="Travel",O23,IF($P$4="Waterdrops",P23,IF($P$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG23" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D23,IF($P$4="C2 Birds in Flight",E23,IF($P$4="C3 Landscape",F23,IF($P$4="Default Settings",G23,IF($P$4="Androo",H23,IF($P$4="Birds in Flight",I23,IF($P$4="Birds Perched",J23,IF($P$4="Fireworks",K23,IF($P$4="Landscape",L23,IF($P$4="Macro",M23,IF($P$4="People",N23,IF($P$4="Sports",O23,IF($P$4="Travel",P23,IF($P$4="Waterdrops",Q23,IF($P$4="Wildlife",R23,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AH23" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D23,IF($Q$4="C2 Birds in Flight",E23,IF($Q$4="C3 Landscape",F23,IF($Q$4="Default Settings",G23,IF($Q$4="Androo",H23,IF($Q$4="Birds in Flight",I23,IF($Q$4="Birds Perched",J23,IF($Q$4="Fireworks",K23,IF($Q$4="Landscape",L23,IF($Q$4="Macro",M23,IF($Q$4="People",N23,IF($Q$4="Sports",O23,IF($Q$4="Travel",P23,IF($Q$4="Waterdrops",Q23,IF($Q$4="Wildlife",R23,"")))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AI23" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D23,IF($R$4="C2 Birds in Flight",E23,IF($R$4="C3 Landscape",F23,IF($R$4="Default Settings",G23,IF($R$4="Androo",H23,IF($R$4="Birds in Flight",I23,IF($R$4="Birds Perched",J23,IF($R$4="Fireworks",K23,IF($R$4="Landscape",L23,IF($R$4="Macro",M23,IF($R$4="People",N23,IF($R$4="Sports",O23,IF($R$4="Travel",P23,IF($R$4="Waterdrops",Q23,IF($R$4="Wildlife",R23,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D23,IF($Q$4="C2 Birds in Flight",E23,IF($Q$4="C3 Landscape",F23,IF($Q$4="Default Settings",G23,IF($Q$4="Birds in Flight",H23,IF($Q$4="Birds Perched",I23,IF($Q$4="Fireworks",J23,IF($Q$4="Landscape",K23,IF($Q$4="Macro",L23,IF($Q$4="People",M23,IF($Q$4="Sports",N23,IF($Q$4="Travel",O23,IF($Q$4="Waterdrops",P23,IF($Q$4="Wildlife",Q23,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
     </x:row>
@@ -3091,16 +2944,16 @@
         <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="H24" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="I24" s="17" t="str">
-        <x:v>Mode 3</x:v>
-      </x:c>
       <x:c r="J24" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="str">
         <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="K24" s="17" t="str">
-        <x:v>Off</x:v>
       </x:c>
       <x:c r="L24" s="17" t="str">
         <x:v>Mode 1</x:v>
@@ -3109,84 +2962,77 @@
         <x:v>Mode 1</x:v>
       </x:c>
       <x:c r="N24" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="O24" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="O24" s="17" t="str">
+      <x:c r="P24" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q24" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="R24" s="20" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="S24" s="20" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="T24" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D24,IF($D$4="C2 Birds in Flight",E24,IF($D$4="C3 Landscape",F24,IF($D$4="Default Settings",G24,IF($D$4="Birds in Flight",H24,IF($D$4="Birds Perched",I24,IF($D$4="Fireworks",J24,IF($D$4="Landscape",K24,IF($D$4="Macro",L24,IF($D$4="People",M24,IF($D$4="Sports",N24,IF($D$4="Travel",O24,IF($D$4="Waterdrops",P24,IF($D$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U24" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D24,IF($E$4="C2 Birds in Flight",E24,IF($E$4="C3 Landscape",F24,IF($E$4="Default Settings",G24,IF($E$4="Birds in Flight",H24,IF($E$4="Birds Perched",I24,IF($E$4="Fireworks",J24,IF($E$4="Landscape",K24,IF($E$4="Macro",L24,IF($E$4="People",M24,IF($E$4="Sports",N24,IF($E$4="Travel",O24,IF($E$4="Waterdrops",P24,IF($E$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="P24" s="17" t="str">
+      <x:c r="V24" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D24,IF($F$4="C2 Birds in Flight",E24,IF($F$4="C3 Landscape",F24,IF($F$4="Default Settings",G24,IF($F$4="Birds in Flight",H24,IF($F$4="Birds Perched",I24,IF($F$4="Fireworks",J24,IF($F$4="Landscape",K24,IF($F$4="Macro",L24,IF($F$4="People",M24,IF($F$4="Sports",N24,IF($F$4="Travel",O24,IF($F$4="Waterdrops",P24,IF($F$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="Q24" s="17" t="str">
+      <x:c r="W24" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D24,IF($G$4="C2 Birds in Flight",E24,IF($G$4="C3 Landscape",F24,IF($G$4="Default Settings",G24,IF($G$4="Birds in Flight",H24,IF($G$4="Birds Perched",I24,IF($G$4="Fireworks",J24,IF($G$4="Landscape",K24,IF($G$4="Macro",L24,IF($G$4="People",M24,IF($G$4="Sports",N24,IF($G$4="Travel",O24,IF($G$4="Waterdrops",P24,IF($G$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="X24" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D24,IF($H$4="C2 Birds in Flight",E24,IF($H$4="C3 Landscape",F24,IF($H$4="Default Settings",G24,IF($H$4="Birds in Flight",H24,IF($H$4="Birds Perched",I24,IF($H$4="Fireworks",J24,IF($H$4="Landscape",K24,IF($H$4="Macro",L24,IF($H$4="People",M24,IF($H$4="Sports",N24,IF($H$4="Travel",O24,IF($H$4="Waterdrops",P24,IF($H$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="Y24" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D24,IF($I$4="C2 Birds in Flight",E24,IF($I$4="C3 Landscape",F24,IF($I$4="Default Settings",G24,IF($I$4="Birds in Flight",H24,IF($I$4="Birds Perched",I24,IF($I$4="Fireworks",J24,IF($I$4="Landscape",K24,IF($I$4="Macro",L24,IF($I$4="People",M24,IF($I$4="Sports",N24,IF($I$4="Travel",O24,IF($I$4="Waterdrops",P24,IF($I$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Z24" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D24,IF($J$4="C2 Birds in Flight",E24,IF($J$4="C3 Landscape",F24,IF($J$4="Default Settings",G24,IF($J$4="Birds in Flight",H24,IF($J$4="Birds Perched",I24,IF($J$4="Fireworks",J24,IF($J$4="Landscape",K24,IF($J$4="Macro",L24,IF($J$4="People",M24,IF($J$4="Sports",N24,IF($J$4="Travel",O24,IF($J$4="Waterdrops",P24,IF($J$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Off</x:v>
       </x:c>
-      <x:c r="R24" s="17" t="str">
+      <x:c r="AA24" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D24,IF($K$4="C2 Birds in Flight",E24,IF($K$4="C3 Landscape",F24,IF($K$4="Default Settings",G24,IF($K$4="Birds in Flight",H24,IF($K$4="Birds Perched",I24,IF($K$4="Fireworks",J24,IF($K$4="Landscape",K24,IF($K$4="Macro",L24,IF($K$4="People",M24,IF($K$4="Sports",N24,IF($K$4="Travel",O24,IF($K$4="Waterdrops",P24,IF($K$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="S24" s="20" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="T24" s="20" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="U24" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D24,IF($D$4="C2 Birds in Flight",E24,IF($D$4="C3 Landscape",F24,IF($D$4="Default Settings",G24,IF($D$4="Androo",H24,IF($D$4="Birds in Flight",I24,IF($D$4="Birds Perched",J24,IF($D$4="Fireworks",K24,IF($D$4="Landscape",L24,IF($D$4="Macro",M24,IF($D$4="People",N24,IF($D$4="Sports",O24,IF($D$4="Travel",P24,IF($D$4="Waterdrops",Q24,IF($D$4="Wildlife",R24,"")))))))))))))))</x:f>
+      <x:c r="AB24" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D24,IF($L$4="C2 Birds in Flight",E24,IF($L$4="C3 Landscape",F24,IF($L$4="Default Settings",G24,IF($L$4="Birds in Flight",H24,IF($L$4="Birds Perched",I24,IF($L$4="Fireworks",J24,IF($L$4="Landscape",K24,IF($L$4="Macro",L24,IF($L$4="People",M24,IF($L$4="Sports",N24,IF($L$4="Travel",O24,IF($L$4="Waterdrops",P24,IF($L$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="V24" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D24,IF($E$4="C2 Birds in Flight",E24,IF($E$4="C3 Landscape",F24,IF($E$4="Default Settings",G24,IF($E$4="Androo",H24,IF($E$4="Birds in Flight",I24,IF($E$4="Birds Perched",J24,IF($E$4="Fireworks",K24,IF($E$4="Landscape",L24,IF($E$4="Macro",M24,IF($E$4="People",N24,IF($E$4="Sports",O24,IF($E$4="Travel",P24,IF($E$4="Waterdrops",Q24,IF($E$4="Wildlife",R24,"")))))))))))))))</x:f>
+      <x:c r="AC24" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D24,IF($M$4="C2 Birds in Flight",E24,IF($M$4="C3 Landscape",F24,IF($M$4="Default Settings",G24,IF($M$4="Birds in Flight",H24,IF($M$4="Birds Perched",I24,IF($M$4="Fireworks",J24,IF($M$4="Landscape",K24,IF($M$4="Macro",L24,IF($M$4="People",M24,IF($M$4="Sports",N24,IF($M$4="Travel",O24,IF($M$4="Waterdrops",P24,IF($M$4="Wildlife",Q24,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AD24" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D24,IF($N$4="C2 Birds in Flight",E24,IF($N$4="C3 Landscape",F24,IF($N$4="Default Settings",G24,IF($N$4="Birds in Flight",H24,IF($N$4="Birds Perched",I24,IF($N$4="Fireworks",J24,IF($N$4="Landscape",K24,IF($N$4="Macro",L24,IF($N$4="People",M24,IF($N$4="Sports",N24,IF($N$4="Travel",O24,IF($N$4="Waterdrops",P24,IF($N$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="W24" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D24,IF($F$4="C2 Birds in Flight",E24,IF($F$4="C3 Landscape",F24,IF($F$4="Default Settings",G24,IF($F$4="Androo",H24,IF($F$4="Birds in Flight",I24,IF($F$4="Birds Perched",J24,IF($F$4="Fireworks",K24,IF($F$4="Landscape",L24,IF($F$4="Macro",M24,IF($F$4="People",N24,IF($F$4="Sports",O24,IF($F$4="Travel",P24,IF($F$4="Waterdrops",Q24,IF($F$4="Wildlife",R24,"")))))))))))))))</x:f>
+      <x:c r="AE24" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D24,IF($O$4="C2 Birds in Flight",E24,IF($O$4="C3 Landscape",F24,IF($O$4="Default Settings",G24,IF($O$4="Birds in Flight",H24,IF($O$4="Birds Perched",I24,IF($O$4="Fireworks",J24,IF($O$4="Landscape",K24,IF($O$4="Macro",L24,IF($O$4="People",M24,IF($O$4="Sports",N24,IF($O$4="Travel",O24,IF($O$4="Waterdrops",P24,IF($O$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="X24" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D24,IF($G$4="C2 Birds in Flight",E24,IF($G$4="C3 Landscape",F24,IF($G$4="Default Settings",G24,IF($G$4="Androo",H24,IF($G$4="Birds in Flight",I24,IF($G$4="Birds Perched",J24,IF($G$4="Fireworks",K24,IF($G$4="Landscape",L24,IF($G$4="Macro",M24,IF($G$4="People",N24,IF($G$4="Sports",O24,IF($G$4="Travel",P24,IF($G$4="Waterdrops",Q24,IF($G$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="Y24" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D24,IF($H$4="C2 Birds in Flight",E24,IF($H$4="C3 Landscape",F24,IF($H$4="Default Settings",G24,IF($H$4="Androo",H24,IF($H$4="Birds in Flight",I24,IF($H$4="Birds Perched",J24,IF($H$4="Fireworks",K24,IF($H$4="Landscape",L24,IF($H$4="Macro",M24,IF($H$4="People",N24,IF($H$4="Sports",O24,IF($H$4="Travel",P24,IF($H$4="Waterdrops",Q24,IF($H$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="Z24" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D24,IF($I$4="C2 Birds in Flight",E24,IF($I$4="C3 Landscape",F24,IF($I$4="Default Settings",G24,IF($I$4="Androo",H24,IF($I$4="Birds in Flight",I24,IF($I$4="Birds Perched",J24,IF($I$4="Fireworks",K24,IF($I$4="Landscape",L24,IF($I$4="Macro",M24,IF($I$4="People",N24,IF($I$4="Sports",O24,IF($I$4="Travel",P24,IF($I$4="Waterdrops",Q24,IF($I$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
-      </x:c>
-      <x:c r="AA24" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D24,IF($J$4="C2 Birds in Flight",E24,IF($J$4="C3 Landscape",F24,IF($J$4="Default Settings",G24,IF($J$4="Androo",H24,IF($J$4="Birds in Flight",I24,IF($J$4="Birds Perched",J24,IF($J$4="Fireworks",K24,IF($J$4="Landscape",L24,IF($J$4="Macro",M24,IF($J$4="People",N24,IF($J$4="Sports",O24,IF($J$4="Travel",P24,IF($J$4="Waterdrops",Q24,IF($J$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="AB24" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D24,IF($K$4="C2 Birds in Flight",E24,IF($K$4="C3 Landscape",F24,IF($K$4="Default Settings",G24,IF($K$4="Androo",H24,IF($K$4="Birds in Flight",I24,IF($K$4="Birds Perched",J24,IF($K$4="Fireworks",K24,IF($K$4="Landscape",L24,IF($K$4="Macro",M24,IF($K$4="People",N24,IF($K$4="Sports",O24,IF($K$4="Travel",P24,IF($K$4="Waterdrops",Q24,IF($K$4="Wildlife",R24,"")))))))))))))))</x:f>
+      <x:c r="AF24" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D24,IF($P$4="C2 Birds in Flight",E24,IF($P$4="C3 Landscape",F24,IF($P$4="Default Settings",G24,IF($P$4="Birds in Flight",H24,IF($P$4="Birds Perched",I24,IF($P$4="Fireworks",J24,IF($P$4="Landscape",K24,IF($P$4="Macro",L24,IF($P$4="People",M24,IF($P$4="Sports",N24,IF($P$4="Travel",O24,IF($P$4="Waterdrops",P24,IF($P$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Off</x:v>
       </x:c>
-      <x:c r="AC24" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D24,IF($L$4="C2 Birds in Flight",E24,IF($L$4="C3 Landscape",F24,IF($L$4="Default Settings",G24,IF($L$4="Androo",H24,IF($L$4="Birds in Flight",I24,IF($L$4="Birds Perched",J24,IF($L$4="Fireworks",K24,IF($L$4="Landscape",L24,IF($L$4="Macro",M24,IF($L$4="People",N24,IF($L$4="Sports",O24,IF($L$4="Travel",P24,IF($L$4="Waterdrops",Q24,IF($L$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="AD24" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D24,IF($M$4="C2 Birds in Flight",E24,IF($M$4="C3 Landscape",F24,IF($M$4="Default Settings",G24,IF($M$4="Androo",H24,IF($M$4="Birds in Flight",I24,IF($M$4="Birds Perched",J24,IF($M$4="Fireworks",K24,IF($M$4="Landscape",L24,IF($M$4="Macro",M24,IF($M$4="People",N24,IF($M$4="Sports",O24,IF($M$4="Travel",P24,IF($M$4="Waterdrops",Q24,IF($M$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="AE24" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D24,IF($N$4="C2 Birds in Flight",E24,IF($N$4="C3 Landscape",F24,IF($N$4="Default Settings",G24,IF($N$4="Androo",H24,IF($N$4="Birds in Flight",I24,IF($N$4="Birds Perched",J24,IF($N$4="Fireworks",K24,IF($N$4="Landscape",L24,IF($N$4="Macro",M24,IF($N$4="People",N24,IF($N$4="Sports",O24,IF($N$4="Travel",P24,IF($N$4="Waterdrops",Q24,IF($N$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="AF24" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D24,IF($O$4="C2 Birds in Flight",E24,IF($O$4="C3 Landscape",F24,IF($O$4="Default Settings",G24,IF($O$4="Androo",H24,IF($O$4="Birds in Flight",I24,IF($O$4="Birds Perched",J24,IF($O$4="Fireworks",K24,IF($O$4="Landscape",L24,IF($O$4="Macro",M24,IF($O$4="People",N24,IF($O$4="Sports",O24,IF($O$4="Travel",P24,IF($O$4="Waterdrops",Q24,IF($O$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
-      </x:c>
       <x:c r="AG24" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D24,IF($P$4="C2 Birds in Flight",E24,IF($P$4="C3 Landscape",F24,IF($P$4="Default Settings",G24,IF($P$4="Androo",H24,IF($P$4="Birds in Flight",I24,IF($P$4="Birds Perched",J24,IF($P$4="Fireworks",K24,IF($P$4="Landscape",L24,IF($P$4="Macro",M24,IF($P$4="People",N24,IF($P$4="Sports",O24,IF($P$4="Travel",P24,IF($P$4="Waterdrops",Q24,IF($P$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
-      </x:c>
-      <x:c r="AH24" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D24,IF($Q$4="C2 Birds in Flight",E24,IF($Q$4="C3 Landscape",F24,IF($Q$4="Default Settings",G24,IF($Q$4="Androo",H24,IF($Q$4="Birds in Flight",I24,IF($Q$4="Birds Perched",J24,IF($Q$4="Fireworks",K24,IF($Q$4="Landscape",L24,IF($Q$4="Macro",M24,IF($Q$4="People",N24,IF($Q$4="Sports",O24,IF($Q$4="Travel",P24,IF($Q$4="Waterdrops",Q24,IF($Q$4="Wildlife",R24,"")))))))))))))))</x:f>
-        <x:v>Off</x:v>
-      </x:c>
-      <x:c r="AI24" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D24,IF($R$4="C2 Birds in Flight",E24,IF($R$4="C3 Landscape",F24,IF($R$4="Default Settings",G24,IF($R$4="Androo",H24,IF($R$4="Birds in Flight",I24,IF($R$4="Birds Perched",J24,IF($R$4="Fireworks",K24,IF($R$4="Landscape",L24,IF($R$4="Macro",M24,IF($R$4="People",N24,IF($R$4="Sports",O24,IF($R$4="Travel",P24,IF($R$4="Waterdrops",Q24,IF($R$4="Wildlife",R24,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D24,IF($Q$4="C2 Birds in Flight",E24,IF($Q$4="C3 Landscape",F24,IF($Q$4="Default Settings",G24,IF($Q$4="Birds in Flight",H24,IF($Q$4="Birds Perched",I24,IF($Q$4="Fireworks",J24,IF($Q$4="Landscape",K24,IF($Q$4="Macro",L24,IF($Q$4="People",M24,IF($Q$4="Sports",N24,IF($Q$4="Travel",O24,IF($Q$4="Waterdrops",P24,IF($Q$4="Wildlife",Q24,""))))))))))))))</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
     </x:row>
@@ -3219,10 +3065,10 @@
         <x:v>On / On</x:v>
       </x:c>
       <x:c r="J25" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="str">
         <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="K25" s="17" t="str">
-        <x:v>Off / Off</x:v>
       </x:c>
       <x:c r="L25" s="17" t="str">
         <x:v>On / On</x:v>
@@ -3237,78 +3083,71 @@
         <x:v>On / On</x:v>
       </x:c>
       <x:c r="P25" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="Q25" s="17" t="str">
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="Q25" s="17" t="str">
+      <x:c r="R25" s="20" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="S25" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="T25" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D25,IF($D$4="C2 Birds in Flight",E25,IF($D$4="C3 Landscape",F25,IF($D$4="Default Settings",G25,IF($D$4="Birds in Flight",H25,IF($D$4="Birds Perched",I25,IF($D$4="Fireworks",J25,IF($D$4="Landscape",K25,IF($D$4="Macro",L25,IF($D$4="People",M25,IF($D$4="Sports",N25,IF($D$4="Travel",O25,IF($D$4="Waterdrops",P25,IF($D$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U25" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D25,IF($E$4="C2 Birds in Flight",E25,IF($E$4="C3 Landscape",F25,IF($E$4="Default Settings",G25,IF($E$4="Birds in Flight",H25,IF($E$4="Birds Perched",I25,IF($E$4="Fireworks",J25,IF($E$4="Landscape",K25,IF($E$4="Macro",L25,IF($E$4="People",M25,IF($E$4="Sports",N25,IF($E$4="Travel",O25,IF($E$4="Waterdrops",P25,IF($E$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V25" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D25,IF($F$4="C2 Birds in Flight",E25,IF($F$4="C3 Landscape",F25,IF($F$4="Default Settings",G25,IF($F$4="Birds in Flight",H25,IF($F$4="Birds Perched",I25,IF($F$4="Fireworks",J25,IF($F$4="Landscape",K25,IF($F$4="Macro",L25,IF($F$4="People",M25,IF($F$4="Sports",N25,IF($F$4="Travel",O25,IF($F$4="Waterdrops",P25,IF($F$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="W25" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D25,IF($G$4="C2 Birds in Flight",E25,IF($G$4="C3 Landscape",F25,IF($G$4="Default Settings",G25,IF($G$4="Birds in Flight",H25,IF($G$4="Birds Perched",I25,IF($G$4="Fireworks",J25,IF($G$4="Landscape",K25,IF($G$4="Macro",L25,IF($G$4="People",M25,IF($G$4="Sports",N25,IF($G$4="Travel",O25,IF($G$4="Waterdrops",P25,IF($G$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="X25" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D25,IF($H$4="C2 Birds in Flight",E25,IF($H$4="C3 Landscape",F25,IF($H$4="Default Settings",G25,IF($H$4="Birds in Flight",H25,IF($H$4="Birds Perched",I25,IF($H$4="Fireworks",J25,IF($H$4="Landscape",K25,IF($H$4="Macro",L25,IF($H$4="People",M25,IF($H$4="Sports",N25,IF($H$4="Travel",O25,IF($H$4="Waterdrops",P25,IF($H$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Y25" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D25,IF($I$4="C2 Birds in Flight",E25,IF($I$4="C3 Landscape",F25,IF($I$4="Default Settings",G25,IF($I$4="Birds in Flight",H25,IF($I$4="Birds Perched",I25,IF($I$4="Fireworks",J25,IF($I$4="Landscape",K25,IF($I$4="Macro",L25,IF($I$4="People",M25,IF($I$4="Sports",N25,IF($I$4="Travel",O25,IF($I$4="Waterdrops",P25,IF($I$4="Wildlife",Q25,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Z25" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D25,IF($J$4="C2 Birds in Flight",E25,IF($J$4="C3 Landscape",F25,IF($J$4="Default Settings",G25,IF($J$4="Birds in Flight",H25,IF($J$4="Birds Perched",I25,IF($J$4="Fireworks",J25,IF($J$4="Landscape",K25,IF($J$4="Macro",L25,IF($J$4="People",M25,IF($J$4="Sports",N25,IF($J$4="Travel",O25,IF($J$4="Waterdrops",P25,IF($J$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>Off / Off</x:v>
       </x:c>
-      <x:c r="R25" s="17" t="str">
+      <x:c r="AA25" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D25,IF($K$4="C2 Birds in Flight",E25,IF($K$4="C3 Landscape",F25,IF($K$4="Default Settings",G25,IF($K$4="Birds in Flight",H25,IF($K$4="Birds Perched",I25,IF($K$4="Fireworks",J25,IF($K$4="Landscape",K25,IF($K$4="Macro",L25,IF($K$4="People",M25,IF($K$4="Sports",N25,IF($K$4="Travel",O25,IF($K$4="Waterdrops",P25,IF($K$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="S25" s="20" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="T25" s="20" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="U25" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D25,IF($D$4="C2 Birds in Flight",E25,IF($D$4="C3 Landscape",F25,IF($D$4="Default Settings",G25,IF($D$4="Androo",H25,IF($D$4="Birds in Flight",I25,IF($D$4="Birds Perched",J25,IF($D$4="Fireworks",K25,IF($D$4="Landscape",L25,IF($D$4="Macro",M25,IF($D$4="People",N25,IF($D$4="Sports",O25,IF($D$4="Travel",P25,IF($D$4="Waterdrops",Q25,IF($D$4="Wildlife",R25,"")))))))))))))))</x:f>
+      <x:c r="AB25" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D25,IF($L$4="C2 Birds in Flight",E25,IF($L$4="C3 Landscape",F25,IF($L$4="Default Settings",G25,IF($L$4="Birds in Flight",H25,IF($L$4="Birds Perched",I25,IF($L$4="Fireworks",J25,IF($L$4="Landscape",K25,IF($L$4="Macro",L25,IF($L$4="People",M25,IF($L$4="Sports",N25,IF($L$4="Travel",O25,IF($L$4="Waterdrops",P25,IF($L$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="V25" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D25,IF($E$4="C2 Birds in Flight",E25,IF($E$4="C3 Landscape",F25,IF($E$4="Default Settings",G25,IF($E$4="Androo",H25,IF($E$4="Birds in Flight",I25,IF($E$4="Birds Perched",J25,IF($E$4="Fireworks",K25,IF($E$4="Landscape",L25,IF($E$4="Macro",M25,IF($E$4="People",N25,IF($E$4="Sports",O25,IF($E$4="Travel",P25,IF($E$4="Waterdrops",Q25,IF($E$4="Wildlife",R25,"")))))))))))))))</x:f>
+      <x:c r="AC25" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D25,IF($M$4="C2 Birds in Flight",E25,IF($M$4="C3 Landscape",F25,IF($M$4="Default Settings",G25,IF($M$4="Birds in Flight",H25,IF($M$4="Birds Perched",I25,IF($M$4="Fireworks",J25,IF($M$4="Landscape",K25,IF($M$4="Macro",L25,IF($M$4="People",M25,IF($M$4="Sports",N25,IF($M$4="Travel",O25,IF($M$4="Waterdrops",P25,IF($M$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="W25" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D25,IF($F$4="C2 Birds in Flight",E25,IF($F$4="C3 Landscape",F25,IF($F$4="Default Settings",G25,IF($F$4="Androo",H25,IF($F$4="Birds in Flight",I25,IF($F$4="Birds Perched",J25,IF($F$4="Fireworks",K25,IF($F$4="Landscape",L25,IF($F$4="Macro",M25,IF($F$4="People",N25,IF($F$4="Sports",O25,IF($F$4="Travel",P25,IF($F$4="Waterdrops",Q25,IF($F$4="Wildlife",R25,"")))))))))))))))</x:f>
+      <x:c r="AD25" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D25,IF($N$4="C2 Birds in Flight",E25,IF($N$4="C3 Landscape",F25,IF($N$4="Default Settings",G25,IF($N$4="Birds in Flight",H25,IF($N$4="Birds Perched",I25,IF($N$4="Fireworks",J25,IF($N$4="Landscape",K25,IF($N$4="Macro",L25,IF($N$4="People",M25,IF($N$4="Sports",N25,IF($N$4="Travel",O25,IF($N$4="Waterdrops",P25,IF($N$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="X25" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D25,IF($G$4="C2 Birds in Flight",E25,IF($G$4="C3 Landscape",F25,IF($G$4="Default Settings",G25,IF($G$4="Androo",H25,IF($G$4="Birds in Flight",I25,IF($G$4="Birds Perched",J25,IF($G$4="Fireworks",K25,IF($G$4="Landscape",L25,IF($G$4="Macro",M25,IF($G$4="People",N25,IF($G$4="Sports",O25,IF($G$4="Travel",P25,IF($G$4="Waterdrops",Q25,IF($G$4="Wildlife",R25,"")))))))))))))))</x:f>
+      <x:c r="AE25" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D25,IF($O$4="C2 Birds in Flight",E25,IF($O$4="C3 Landscape",F25,IF($O$4="Default Settings",G25,IF($O$4="Birds in Flight",H25,IF($O$4="Birds Perched",I25,IF($O$4="Fireworks",J25,IF($O$4="Landscape",K25,IF($O$4="Macro",L25,IF($O$4="People",M25,IF($O$4="Sports",N25,IF($O$4="Travel",O25,IF($O$4="Waterdrops",P25,IF($O$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="Y25" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D25,IF($H$4="C2 Birds in Flight",E25,IF($H$4="C3 Landscape",F25,IF($H$4="Default Settings",G25,IF($H$4="Androo",H25,IF($H$4="Birds in Flight",I25,IF($H$4="Birds Perched",J25,IF($H$4="Fireworks",K25,IF($H$4="Landscape",L25,IF($H$4="Macro",M25,IF($H$4="People",N25,IF($H$4="Sports",O25,IF($H$4="Travel",P25,IF($H$4="Waterdrops",Q25,IF($H$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="Z25" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D25,IF($I$4="C2 Birds in Flight",E25,IF($I$4="C3 Landscape",F25,IF($I$4="Default Settings",G25,IF($I$4="Androo",H25,IF($I$4="Birds in Flight",I25,IF($I$4="Birds Perched",J25,IF($I$4="Fireworks",K25,IF($I$4="Landscape",L25,IF($I$4="Macro",M25,IF($I$4="People",N25,IF($I$4="Sports",O25,IF($I$4="Travel",P25,IF($I$4="Waterdrops",Q25,IF($I$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="AA25" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D25,IF($J$4="C2 Birds in Flight",E25,IF($J$4="C3 Landscape",F25,IF($J$4="Default Settings",G25,IF($J$4="Androo",H25,IF($J$4="Birds in Flight",I25,IF($J$4="Birds Perched",J25,IF($J$4="Fireworks",K25,IF($J$4="Landscape",L25,IF($J$4="Macro",M25,IF($J$4="People",N25,IF($J$4="Sports",O25,IF($J$4="Travel",P25,IF($J$4="Waterdrops",Q25,IF($J$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="AB25" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D25,IF($K$4="C2 Birds in Flight",E25,IF($K$4="C3 Landscape",F25,IF($K$4="Default Settings",G25,IF($K$4="Androo",H25,IF($K$4="Birds in Flight",I25,IF($K$4="Birds Perched",J25,IF($K$4="Fireworks",K25,IF($K$4="Landscape",L25,IF($K$4="Macro",M25,IF($K$4="People",N25,IF($K$4="Sports",O25,IF($K$4="Travel",P25,IF($K$4="Waterdrops",Q25,IF($K$4="Wildlife",R25,"")))))))))))))))</x:f>
+      <x:c r="AF25" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D25,IF($P$4="C2 Birds in Flight",E25,IF($P$4="C3 Landscape",F25,IF($P$4="Default Settings",G25,IF($P$4="Birds in Flight",H25,IF($P$4="Birds Perched",I25,IF($P$4="Fireworks",J25,IF($P$4="Landscape",K25,IF($P$4="Macro",L25,IF($P$4="People",M25,IF($P$4="Sports",N25,IF($P$4="Travel",O25,IF($P$4="Waterdrops",P25,IF($P$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>Off / Off</x:v>
       </x:c>
-      <x:c r="AC25" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D25,IF($L$4="C2 Birds in Flight",E25,IF($L$4="C3 Landscape",F25,IF($L$4="Default Settings",G25,IF($L$4="Androo",H25,IF($L$4="Birds in Flight",I25,IF($L$4="Birds Perched",J25,IF($L$4="Fireworks",K25,IF($L$4="Landscape",L25,IF($L$4="Macro",M25,IF($L$4="People",N25,IF($L$4="Sports",O25,IF($L$4="Travel",P25,IF($L$4="Waterdrops",Q25,IF($L$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="AD25" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D25,IF($M$4="C2 Birds in Flight",E25,IF($M$4="C3 Landscape",F25,IF($M$4="Default Settings",G25,IF($M$4="Androo",H25,IF($M$4="Birds in Flight",I25,IF($M$4="Birds Perched",J25,IF($M$4="Fireworks",K25,IF($M$4="Landscape",L25,IF($M$4="Macro",M25,IF($M$4="People",N25,IF($M$4="Sports",O25,IF($M$4="Travel",P25,IF($M$4="Waterdrops",Q25,IF($M$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="AE25" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D25,IF($N$4="C2 Birds in Flight",E25,IF($N$4="C3 Landscape",F25,IF($N$4="Default Settings",G25,IF($N$4="Androo",H25,IF($N$4="Birds in Flight",I25,IF($N$4="Birds Perched",J25,IF($N$4="Fireworks",K25,IF($N$4="Landscape",L25,IF($N$4="Macro",M25,IF($N$4="People",N25,IF($N$4="Sports",O25,IF($N$4="Travel",P25,IF($N$4="Waterdrops",Q25,IF($N$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="AF25" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D25,IF($O$4="C2 Birds in Flight",E25,IF($O$4="C3 Landscape",F25,IF($O$4="Default Settings",G25,IF($O$4="Androo",H25,IF($O$4="Birds in Flight",I25,IF($O$4="Birds Perched",J25,IF($O$4="Fireworks",K25,IF($O$4="Landscape",L25,IF($O$4="Macro",M25,IF($O$4="People",N25,IF($O$4="Sports",O25,IF($O$4="Travel",P25,IF($O$4="Waterdrops",Q25,IF($O$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
       <x:c r="AG25" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D25,IF($P$4="C2 Birds in Flight",E25,IF($P$4="C3 Landscape",F25,IF($P$4="Default Settings",G25,IF($P$4="Androo",H25,IF($P$4="Birds in Flight",I25,IF($P$4="Birds Perched",J25,IF($P$4="Fireworks",K25,IF($P$4="Landscape",L25,IF($P$4="Macro",M25,IF($P$4="People",N25,IF($P$4="Sports",O25,IF($P$4="Travel",P25,IF($P$4="Waterdrops",Q25,IF($P$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>On / On</x:v>
-      </x:c>
-      <x:c r="AH25" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D25,IF($Q$4="C2 Birds in Flight",E25,IF($Q$4="C3 Landscape",F25,IF($Q$4="Default Settings",G25,IF($Q$4="Androo",H25,IF($Q$4="Birds in Flight",I25,IF($Q$4="Birds Perched",J25,IF($Q$4="Fireworks",K25,IF($Q$4="Landscape",L25,IF($Q$4="Macro",M25,IF($Q$4="People",N25,IF($Q$4="Sports",O25,IF($Q$4="Travel",P25,IF($Q$4="Waterdrops",Q25,IF($Q$4="Wildlife",R25,"")))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
-      </x:c>
-      <x:c r="AI25" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D25,IF($R$4="C2 Birds in Flight",E25,IF($R$4="C3 Landscape",F25,IF($R$4="Default Settings",G25,IF($R$4="Androo",H25,IF($R$4="Birds in Flight",I25,IF($R$4="Birds Perched",J25,IF($R$4="Fireworks",K25,IF($R$4="Landscape",L25,IF($R$4="Macro",M25,IF($R$4="People",N25,IF($R$4="Sports",O25,IF($R$4="Travel",P25,IF($R$4="Waterdrops",Q25,IF($R$4="Wildlife",R25,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D25,IF($Q$4="C2 Birds in Flight",E25,IF($Q$4="C3 Landscape",F25,IF($Q$4="Default Settings",G25,IF($Q$4="Birds in Flight",H25,IF($Q$4="Birds Perched",I25,IF($Q$4="Fireworks",J25,IF($Q$4="Landscape",K25,IF($Q$4="Macro",L25,IF($Q$4="People",M25,IF($Q$4="Sports",N25,IF($Q$4="Travel",O25,IF($Q$4="Waterdrops",P25,IF($Q$4="Wildlife",Q25,""))))))))))))))</x:f>
         <x:v>On / On</x:v>
       </x:c>
     </x:row>
@@ -3347,226 +3186,211 @@
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="L26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="M26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="N26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="O26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q26" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R26" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="S26" s="20" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="T26" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D26,IF($D$4="C2 Birds in Flight",E26,IF($D$4="C3 Landscape",F26,IF($D$4="Default Settings",G26,IF($D$4="Birds in Flight",H26,IF($D$4="Birds Perched",I26,IF($D$4="Fireworks",J26,IF($D$4="Landscape",K26,IF($D$4="Macro",L26,IF($D$4="People",M26,IF($D$4="Sports",N26,IF($D$4="Travel",O26,IF($D$4="Waterdrops",P26,IF($D$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U26" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D26,IF($E$4="C2 Birds in Flight",E26,IF($E$4="C3 Landscape",F26,IF($E$4="Default Settings",G26,IF($E$4="Birds in Flight",H26,IF($E$4="Birds Perched",I26,IF($E$4="Fireworks",J26,IF($E$4="Landscape",K26,IF($E$4="Macro",L26,IF($E$4="People",M26,IF($E$4="Sports",N26,IF($E$4="Travel",O26,IF($E$4="Waterdrops",P26,IF($E$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V26" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D26,IF($F$4="C2 Birds in Flight",E26,IF($F$4="C3 Landscape",F26,IF($F$4="Default Settings",G26,IF($F$4="Birds in Flight",H26,IF($F$4="Birds Perched",I26,IF($F$4="Fireworks",J26,IF($F$4="Landscape",K26,IF($F$4="Macro",L26,IF($F$4="People",M26,IF($F$4="Sports",N26,IF($F$4="Travel",O26,IF($F$4="Waterdrops",P26,IF($F$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W26" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D26,IF($G$4="C2 Birds in Flight",E26,IF($G$4="C3 Landscape",F26,IF($G$4="Default Settings",G26,IF($G$4="Birds in Flight",H26,IF($G$4="Birds Perched",I26,IF($G$4="Fireworks",J26,IF($G$4="Landscape",K26,IF($G$4="Macro",L26,IF($G$4="People",M26,IF($G$4="Sports",N26,IF($G$4="Travel",O26,IF($G$4="Waterdrops",P26,IF($G$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X26" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D26,IF($H$4="C2 Birds in Flight",E26,IF($H$4="C3 Landscape",F26,IF($H$4="Default Settings",G26,IF($H$4="Birds in Flight",H26,IF($H$4="Birds Perched",I26,IF($H$4="Fireworks",J26,IF($H$4="Landscape",K26,IF($H$4="Macro",L26,IF($H$4="People",M26,IF($H$4="Sports",N26,IF($H$4="Travel",O26,IF($H$4="Waterdrops",P26,IF($H$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Y26" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D26,IF($I$4="C2 Birds in Flight",E26,IF($I$4="C3 Landscape",F26,IF($I$4="Default Settings",G26,IF($I$4="Birds in Flight",H26,IF($I$4="Birds Perched",I26,IF($I$4="Fireworks",J26,IF($I$4="Landscape",K26,IF($I$4="Macro",L26,IF($I$4="People",M26,IF($I$4="Sports",N26,IF($I$4="Travel",O26,IF($I$4="Waterdrops",P26,IF($I$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z26" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D26,IF($J$4="C2 Birds in Flight",E26,IF($J$4="C3 Landscape",F26,IF($J$4="Default Settings",G26,IF($J$4="Birds in Flight",H26,IF($J$4="Birds Perched",I26,IF($J$4="Fireworks",J26,IF($J$4="Landscape",K26,IF($J$4="Macro",L26,IF($J$4="People",M26,IF($J$4="Sports",N26,IF($J$4="Travel",O26,IF($J$4="Waterdrops",P26,IF($J$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AA26" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D26,IF($K$4="C2 Birds in Flight",E26,IF($K$4="C3 Landscape",F26,IF($K$4="Default Settings",G26,IF($K$4="Birds in Flight",H26,IF($K$4="Birds Perched",I26,IF($K$4="Fireworks",J26,IF($K$4="Landscape",K26,IF($K$4="Macro",L26,IF($K$4="People",M26,IF($K$4="Sports",N26,IF($K$4="Travel",O26,IF($K$4="Waterdrops",P26,IF($K$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB26" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D26,IF($L$4="C2 Birds in Flight",E26,IF($L$4="C3 Landscape",F26,IF($L$4="Default Settings",G26,IF($L$4="Birds in Flight",H26,IF($L$4="Birds Perched",I26,IF($L$4="Fireworks",J26,IF($L$4="Landscape",K26,IF($L$4="Macro",L26,IF($L$4="People",M26,IF($L$4="Sports",N26,IF($L$4="Travel",O26,IF($L$4="Waterdrops",P26,IF($L$4="Wildlife",Q26,""))))))))))))))</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="N26" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="O26" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="P26" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="Q26" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="R26" s="17" t="str">
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="S26" s="20" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="T26" s="20" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="U26" s="38" t="str">
-        <x:f>IF($D$4="C1 Wildlife",D26,IF($D$4="C2 Birds in Flight",E26,IF($D$4="C3 Landscape",F26,IF($D$4="Default Settings",G26,IF($D$4="Androo",H26,IF($D$4="Birds in Flight",I26,IF($D$4="Birds Perched",J26,IF($D$4="Fireworks",K26,IF($D$4="Landscape",L26,IF($D$4="Macro",M26,IF($D$4="People",N26,IF($D$4="Sports",O26,IF($D$4="Travel",P26,IF($D$4="Waterdrops",Q26,IF($D$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="V26" s="38" t="str">
-        <x:f>IF($E$4="C1 Wildlife",D26,IF($E$4="C2 Birds in Flight",E26,IF($E$4="C3 Landscape",F26,IF($E$4="Default Settings",G26,IF($E$4="Androo",H26,IF($E$4="Birds in Flight",I26,IF($E$4="Birds Perched",J26,IF($E$4="Fireworks",K26,IF($E$4="Landscape",L26,IF($E$4="Macro",M26,IF($E$4="People",N26,IF($E$4="Sports",O26,IF($E$4="Travel",P26,IF($E$4="Waterdrops",Q26,IF($E$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="W26" s="38" t="str">
-        <x:f>IF($F$4="C1 Wildlife",D26,IF($F$4="C2 Birds in Flight",E26,IF($F$4="C3 Landscape",F26,IF($F$4="Default Settings",G26,IF($F$4="Androo",H26,IF($F$4="Birds in Flight",I26,IF($F$4="Birds Perched",J26,IF($F$4="Fireworks",K26,IF($F$4="Landscape",L26,IF($F$4="Macro",M26,IF($F$4="People",N26,IF($F$4="Sports",O26,IF($F$4="Travel",P26,IF($F$4="Waterdrops",Q26,IF($F$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="X26" s="38" t="str">
-        <x:f>IF($G$4="C1 Wildlife",D26,IF($G$4="C2 Birds in Flight",E26,IF($G$4="C3 Landscape",F26,IF($G$4="Default Settings",G26,IF($G$4="Androo",H26,IF($G$4="Birds in Flight",I26,IF($G$4="Birds Perched",J26,IF($G$4="Fireworks",K26,IF($G$4="Landscape",L26,IF($G$4="Macro",M26,IF($G$4="People",N26,IF($G$4="Sports",O26,IF($G$4="Travel",P26,IF($G$4="Waterdrops",Q26,IF($G$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="Y26" s="38" t="str">
-        <x:f>IF($H$4="C1 Wildlife",D26,IF($H$4="C2 Birds in Flight",E26,IF($H$4="C3 Landscape",F26,IF($H$4="Default Settings",G26,IF($H$4="Androo",H26,IF($H$4="Birds in Flight",I26,IF($H$4="Birds Perched",J26,IF($H$4="Fireworks",K26,IF($H$4="Landscape",L26,IF($H$4="Macro",M26,IF($H$4="People",N26,IF($H$4="Sports",O26,IF($H$4="Travel",P26,IF($H$4="Waterdrops",Q26,IF($H$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="Z26" s="38" t="str">
-        <x:f>IF($I$4="C1 Wildlife",D26,IF($I$4="C2 Birds in Flight",E26,IF($I$4="C3 Landscape",F26,IF($I$4="Default Settings",G26,IF($I$4="Androo",H26,IF($I$4="Birds in Flight",I26,IF($I$4="Birds Perched",J26,IF($I$4="Fireworks",K26,IF($I$4="Landscape",L26,IF($I$4="Macro",M26,IF($I$4="People",N26,IF($I$4="Sports",O26,IF($I$4="Travel",P26,IF($I$4="Waterdrops",Q26,IF($I$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AA26" s="38" t="str">
-        <x:f>IF($J$4="C1 Wildlife",D26,IF($J$4="C2 Birds in Flight",E26,IF($J$4="C3 Landscape",F26,IF($J$4="Default Settings",G26,IF($J$4="Androo",H26,IF($J$4="Birds in Flight",I26,IF($J$4="Birds Perched",J26,IF($J$4="Fireworks",K26,IF($J$4="Landscape",L26,IF($J$4="Macro",M26,IF($J$4="People",N26,IF($J$4="Sports",O26,IF($J$4="Travel",P26,IF($J$4="Waterdrops",Q26,IF($J$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AB26" s="38" t="str">
-        <x:f>IF($K$4="C1 Wildlife",D26,IF($K$4="C2 Birds in Flight",E26,IF($K$4="C3 Landscape",F26,IF($K$4="Default Settings",G26,IF($K$4="Androo",H26,IF($K$4="Birds in Flight",I26,IF($K$4="Birds Perched",J26,IF($K$4="Fireworks",K26,IF($K$4="Landscape",L26,IF($K$4="Macro",M26,IF($K$4="People",N26,IF($K$4="Sports",O26,IF($K$4="Travel",P26,IF($K$4="Waterdrops",Q26,IF($K$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
       <x:c r="AC26" s="38" t="str">
-        <x:f>IF($L$4="C1 Wildlife",D26,IF($L$4="C2 Birds in Flight",E26,IF($L$4="C3 Landscape",F26,IF($L$4="Default Settings",G26,IF($L$4="Androo",H26,IF($L$4="Birds in Flight",I26,IF($L$4="Birds Perched",J26,IF($L$4="Fireworks",K26,IF($L$4="Landscape",L26,IF($L$4="Macro",M26,IF($L$4="People",N26,IF($L$4="Sports",O26,IF($L$4="Travel",P26,IF($L$4="Waterdrops",Q26,IF($L$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:f>IF($M$4="C1 Wildlife",D26,IF($M$4="C2 Birds in Flight",E26,IF($M$4="C3 Landscape",F26,IF($M$4="Default Settings",G26,IF($M$4="Birds in Flight",H26,IF($M$4="Birds Perched",I26,IF($M$4="Fireworks",J26,IF($M$4="Landscape",K26,IF($M$4="Macro",L26,IF($M$4="People",M26,IF($M$4="Sports",N26,IF($M$4="Travel",O26,IF($M$4="Waterdrops",P26,IF($M$4="Wildlife",Q26,""))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AD26" s="38" t="str">
-        <x:f>IF($M$4="C1 Wildlife",D26,IF($M$4="C2 Birds in Flight",E26,IF($M$4="C3 Landscape",F26,IF($M$4="Default Settings",G26,IF($M$4="Androo",H26,IF($M$4="Birds in Flight",I26,IF($M$4="Birds Perched",J26,IF($M$4="Fireworks",K26,IF($M$4="Landscape",L26,IF($M$4="Macro",M26,IF($M$4="People",N26,IF($M$4="Sports",O26,IF($M$4="Travel",P26,IF($M$4="Waterdrops",Q26,IF($M$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:f>IF($N$4="C1 Wildlife",D26,IF($N$4="C2 Birds in Flight",E26,IF($N$4="C3 Landscape",F26,IF($N$4="Default Settings",G26,IF($N$4="Birds in Flight",H26,IF($N$4="Birds Perched",I26,IF($N$4="Fireworks",J26,IF($N$4="Landscape",K26,IF($N$4="Macro",L26,IF($N$4="People",M26,IF($N$4="Sports",N26,IF($N$4="Travel",O26,IF($N$4="Waterdrops",P26,IF($N$4="Wildlife",Q26,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AE26" s="38" t="str">
-        <x:f>IF($N$4="C1 Wildlife",D26,IF($N$4="C2 Birds in Flight",E26,IF($N$4="C3 Landscape",F26,IF($N$4="Default Settings",G26,IF($N$4="Androo",H26,IF($N$4="Birds in Flight",I26,IF($N$4="Birds Perched",J26,IF($N$4="Fireworks",K26,IF($N$4="Landscape",L26,IF($N$4="Macro",M26,IF($N$4="People",N26,IF($N$4="Sports",O26,IF($N$4="Travel",P26,IF($N$4="Waterdrops",Q26,IF($N$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:f>IF($O$4="C1 Wildlife",D26,IF($O$4="C2 Birds in Flight",E26,IF($O$4="C3 Landscape",F26,IF($O$4="Default Settings",G26,IF($O$4="Birds in Flight",H26,IF($O$4="Birds Perched",I26,IF($O$4="Fireworks",J26,IF($O$4="Landscape",K26,IF($O$4="Macro",L26,IF($O$4="People",M26,IF($O$4="Sports",N26,IF($O$4="Travel",O26,IF($O$4="Waterdrops",P26,IF($O$4="Wildlife",Q26,""))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AF26" s="38" t="str">
-        <x:f>IF($O$4="C1 Wildlife",D26,IF($O$4="C2 Birds in Flight",E26,IF($O$4="C3 Landscape",F26,IF($O$4="Default Settings",G26,IF($O$4="Androo",H26,IF($O$4="Birds in Flight",I26,IF($O$4="Birds Perched",J26,IF($O$4="Fireworks",K26,IF($O$4="Landscape",L26,IF($O$4="Macro",M26,IF($O$4="People",N26,IF($O$4="Sports",O26,IF($O$4="Travel",P26,IF($O$4="Waterdrops",Q26,IF($O$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:f>IF($P$4="C1 Wildlife",D26,IF($P$4="C2 Birds in Flight",E26,IF($P$4="C3 Landscape",F26,IF($P$4="Default Settings",G26,IF($P$4="Birds in Flight",H26,IF($P$4="Birds Perched",I26,IF($P$4="Fireworks",J26,IF($P$4="Landscape",K26,IF($P$4="Macro",L26,IF($P$4="People",M26,IF($P$4="Sports",N26,IF($P$4="Travel",O26,IF($P$4="Waterdrops",P26,IF($P$4="Wildlife",Q26,""))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="AG26" s="38" t="str">
-        <x:f>IF($P$4="C1 Wildlife",D26,IF($P$4="C2 Birds in Flight",E26,IF($P$4="C3 Landscape",F26,IF($P$4="Default Settings",G26,IF($P$4="Androo",H26,IF($P$4="Birds in Flight",I26,IF($P$4="Birds Perched",J26,IF($P$4="Fireworks",K26,IF($P$4="Landscape",L26,IF($P$4="Macro",M26,IF($P$4="People",N26,IF($P$4="Sports",O26,IF($P$4="Travel",P26,IF($P$4="Waterdrops",Q26,IF($P$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AH26" s="38" t="str">
-        <x:f>IF($Q$4="C1 Wildlife",D26,IF($Q$4="C2 Birds in Flight",E26,IF($Q$4="C3 Landscape",F26,IF($Q$4="Default Settings",G26,IF($Q$4="Androo",H26,IF($Q$4="Birds in Flight",I26,IF($Q$4="Birds Perched",J26,IF($Q$4="Fireworks",K26,IF($Q$4="Landscape",L26,IF($Q$4="Macro",M26,IF($Q$4="People",N26,IF($Q$4="Sports",O26,IF($Q$4="Travel",P26,IF($Q$4="Waterdrops",Q26,IF($Q$4="Wildlife",R26,"")))))))))))))))</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="AI26" s="38" t="str">
-        <x:f>IF($R$4="C1 Wildlife",D26,IF($R$4="C2 Birds in Flight",E26,IF($R$4="C3 Landscape",F26,IF($R$4="Default Settings",G26,IF($R$4="Androo",H26,IF($R$4="Birds in Flight",I26,IF($R$4="Birds Perched",J26,IF($R$4="Fireworks",K26,IF($R$4="Landscape",L26,IF($R$4="Macro",M26,IF($R$4="People",N26,IF($R$4="Sports",O26,IF($R$4="Travel",P26,IF($R$4="Waterdrops",Q26,IF($R$4="Wildlife",R26,"")))))))))))))))</x:f>
+        <x:f>IF($Q$4="C1 Wildlife",D26,IF($Q$4="C2 Birds in Flight",E26,IF($Q$4="C3 Landscape",F26,IF($Q$4="Default Settings",G26,IF($Q$4="Birds in Flight",H26,IF($Q$4="Birds Perched",I26,IF($Q$4="Fireworks",J26,IF($Q$4="Landscape",K26,IF($Q$4="Macro",L26,IF($Q$4="People",M26,IF($Q$4="Sports",N26,IF($Q$4="Travel",O26,IF($Q$4="Waterdrops",P26,IF($Q$4="Wildlife",Q26,""))))))))))))))</x:f>
         <x:v>Disable</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D26">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
-      <x:formula>$U7</x:formula>
+      <x:formula>$T7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="E7:E26">
     <x:cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
-      <x:formula>$V7</x:formula>
+      <x:formula>$U7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="F7:F26">
     <x:cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
-      <x:formula>$W7</x:formula>
+      <x:formula>$V7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="G7:G26">
     <x:cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
-      <x:formula>$X7</x:formula>
+      <x:formula>$W7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="H7:H26">
     <x:cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
-      <x:formula>$Y7</x:formula>
+      <x:formula>$X7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="I7:I26">
     <x:cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
-      <x:formula>$Z7</x:formula>
+      <x:formula>$Y7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="J7:J26">
     <x:cfRule type="cellIs" dxfId="6" priority="7" operator="notEqual">
-      <x:formula>$AA7</x:formula>
+      <x:formula>$Z7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="K7:K26">
     <x:cfRule type="cellIs" dxfId="7" priority="8" operator="notEqual">
-      <x:formula>$AB7</x:formula>
+      <x:formula>$AA7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="L7:L26">
     <x:cfRule type="cellIs" dxfId="8" priority="9" operator="notEqual">
-      <x:formula>$AC7</x:formula>
+      <x:formula>$AB7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="M7:M26">
     <x:cfRule type="cellIs" dxfId="9" priority="10" operator="notEqual">
-      <x:formula>$AD7</x:formula>
+      <x:formula>$AC7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="N7:N26">
     <x:cfRule type="cellIs" dxfId="10" priority="11" operator="notEqual">
-      <x:formula>$AE7</x:formula>
+      <x:formula>$AD7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="O7:O26">
     <x:cfRule type="cellIs" dxfId="11" priority="12" operator="notEqual">
-      <x:formula>$AF7</x:formula>
+      <x:formula>$AE7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="P7:P26">
     <x:cfRule type="cellIs" dxfId="12" priority="13" operator="notEqual">
-      <x:formula>$AG7</x:formula>
+      <x:formula>$AF7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:conditionalFormatting sqref="Q7:Q26">
     <x:cfRule type="cellIs" dxfId="13" priority="14" operator="notEqual">
-      <x:formula>$AH7</x:formula>
+      <x:formula>$AG7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="R7:R26">
-    <x:cfRule type="cellIs" dxfId="14" priority="15" operator="notEqual">
-      <x:formula>$AI7</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:R26">
-    <x:cfRule type="containsText" dxfId="15" priority="16" operator="containsText" text="Not Used"/>
-    <x:cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+  <x:conditionalFormatting sqref="D7:Q26">
+    <x:cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Not Used"/>
+    <x:cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <x:formula>"—"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="15">
+  <x:dataValidations count="14">
     <x:dataValidation type="list" sqref="D4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="H4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="I4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="K4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="L4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="M4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="N4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="O4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="P4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="Q4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="R4">
-      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Androo,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
+      <x:formula1>"C1 Wildlife,C2 Birds in Flight,C3 Landscape,Default Settings,Birds in Flight,Birds Perched,Fireworks,Landscape,Macro,People,Sports,Travel,Waterdrops,Wildlife"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R927c036383c9451f"/>
+  <x:drawing ns1:id="Rbe9a3ada33a24cdf"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R9fa21415ad914f34"/>
+    <x:tablePart ns1:id="R0f96c99050124d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3597,7 +3421,6 @@
     <x:col min="20" max="20" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="21" max="21" width="0.2199999988079071" hidden="1" customWidth="1"/>
     <x:col min="22" max="22" width="0.2199999988079071" hidden="1" customWidth="1"/>
-    <x:col min="23" max="23" width="0.2199999988079071" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -3607,9 +3430,9 @@
       <x:c r="B1" s="43"/>
       <x:c r="C1" s="43"/>
       <x:c r="D1" s="43"/>
+      <x:c r="T1" s="38"/>
       <x:c r="U1" s="38"/>
       <x:c r="V1" s="38"/>
-      <x:c r="W1" s="38"/>
     </x:row>
     <x:row r="2" hidden="0">
       <x:c r="A2" s="6" t="str">
@@ -3624,9 +3447,9 @@
       <x:c r="D2" s="6" t="str">
         <x:v>C3 Landscape</x:v>
       </x:c>
+      <x:c r="T2" s="38"/>
       <x:c r="U2" s="38"/>
       <x:c r="V2" s="38"/>
-      <x:c r="W2" s="38"/>
     </x:row>
     <x:row r="3" hidden="0">
       <x:c r="A3" s="15" t="str">
@@ -3641,15 +3464,15 @@
       <x:c r="D3" s="17" t="str">
         <x:v>Av</x:v>
       </x:c>
-      <x:c r="U3" s="38" t="str">
+      <x:c r="T3" s="38" t="str">
         <x:f>B3</x:f>
         <x:v>Fv</x:v>
       </x:c>
-      <x:c r="V3" s="38" t="str">
+      <x:c r="U3" s="38" t="str">
         <x:f>C3</x:f>
         <x:v>Tv</x:v>
       </x:c>
-      <x:c r="W3" s="38" t="str">
+      <x:c r="V3" s="38" t="str">
         <x:f>D3</x:f>
         <x:v>Av</x:v>
       </x:c>
@@ -3667,15 +3490,15 @@
       <x:c r="D4" s="17" t="str">
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="U4" s="38" t="str">
+      <x:c r="T4" s="38" t="str">
         <x:f>B4</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="V4" s="38" t="str">
+      <x:c r="U4" s="38" t="str">
         <x:f>C4</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
-      <x:c r="W4" s="38" t="str">
+      <x:c r="V4" s="38" t="str">
         <x:f>D4</x:f>
         <x:v>Evaluative</x:v>
       </x:c>
@@ -3693,15 +3516,15 @@
       <x:c r="D5" s="17" t="str">
         <x:v>Auto</x:v>
       </x:c>
+      <x:c r="T5" s="38" t="str">
+        <x:f>B5</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
       <x:c r="U5" s="38" t="str">
-        <x:f>B5</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="V5" s="38" t="str">
         <x:f>C5</x:f>
         <x:v>1/2500 sec.</x:v>
       </x:c>
-      <x:c r="W5" s="38" t="str">
+      <x:c r="V5" s="38" t="str">
         <x:f>D5</x:f>
         <x:v>Auto</x:v>
       </x:c>
@@ -3719,15 +3542,15 @@
       <x:c r="D6" s="17" t="str">
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="U6" s="38" t="str">
+      <x:c r="T6" s="38" t="str">
         <x:f>B6</x:f>
         <x:v>EFCS</x:v>
       </x:c>
-      <x:c r="V6" s="38" t="str">
+      <x:c r="U6" s="38" t="str">
         <x:f>C6</x:f>
         <x:v>Mechanical</x:v>
       </x:c>
-      <x:c r="W6" s="38" t="str">
+      <x:c r="V6" s="38" t="str">
         <x:f>D6</x:f>
         <x:v>EFCS</x:v>
       </x:c>
@@ -3745,15 +3568,15 @@
       <x:c r="D7" s="17" t="str">
         <x:v>f/9</x:v>
       </x:c>
+      <x:c r="T7" s="38" t="str">
+        <x:f>B7</x:f>
+        <x:v>Auto</x:v>
+      </x:c>
       <x:c r="U7" s="38" t="str">
-        <x:f>B7</x:f>
+        <x:f>C7</x:f>
         <x:v>Auto</x:v>
       </x:c>
       <x:c r="V7" s="38" t="str">
-        <x:f>C7</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="W7" s="38" t="str">
         <x:f>D7</x:f>
         <x:v>f/9</x:v>
       </x:c>
@@ -3771,15 +3594,15 @@
       <x:c r="D8" s="17" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="U8" s="38" t="str">
+      <x:c r="T8" s="38" t="str">
         <x:f>B8</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="V8" s="38" t="str">
+      <x:c r="U8" s="38" t="str">
         <x:f>C8</x:f>
         <x:v>Auto - 12800</x:v>
       </x:c>
-      <x:c r="W8" s="38" t="n">
+      <x:c r="V8" s="38" t="n">
         <x:f>D8</x:f>
         <x:v>100</x:v>
       </x:c>
@@ -3797,15 +3620,15 @@
       <x:c r="D9" s="17" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="U9" s="38" t="n">
+      <x:c r="T9" s="38" t="n">
         <x:f>B9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V9" s="38" t="str">
+      <x:c r="U9" s="38" t="str">
         <x:f>C9</x:f>
         <x:v>0 starting point</x:v>
       </x:c>
-      <x:c r="W9" s="38" t="n">
+      <x:c r="V9" s="38" t="n">
         <x:f>D9</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3823,15 +3646,15 @@
       <x:c r="D10" s="17" t="str">
         <x:v>One-Shot AF</x:v>
       </x:c>
-      <x:c r="U10" s="38" t="str">
+      <x:c r="T10" s="38" t="str">
         <x:f>B10</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="V10" s="38" t="str">
+      <x:c r="U10" s="38" t="str">
         <x:f>C10</x:f>
         <x:v>Servo AF</x:v>
       </x:c>
-      <x:c r="W10" s="38" t="str">
+      <x:c r="V10" s="38" t="str">
         <x:f>D10</x:f>
         <x:v>One-Shot AF</x:v>
       </x:c>
@@ -3849,15 +3672,15 @@
       <x:c r="D11" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="U11" s="38" t="str">
+      <x:c r="T11" s="38" t="str">
         <x:f>B11</x:f>
         <x:v>Case 1 (Custom)</x:v>
       </x:c>
-      <x:c r="V11" s="38" t="str">
+      <x:c r="U11" s="38" t="str">
         <x:f>C11</x:f>
         <x:v>Case 4</x:v>
       </x:c>
-      <x:c r="W11" s="38" t="str">
+      <x:c r="V11" s="38" t="str">
         <x:f>D11</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3875,15 +3698,15 @@
       <x:c r="D12" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="U12" s="38" t="n">
+      <x:c r="T12" s="38" t="n">
         <x:f>B12</x:f>
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="V12" s="38" t="n">
+      <x:c r="U12" s="38" t="n">
         <x:f>C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W12" s="38" t="str">
+      <x:c r="V12" s="38" t="str">
         <x:f>D12</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3901,15 +3724,15 @@
       <x:c r="D13" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="U13" s="38" t="str">
+      <x:c r="T13" s="38" t="str">
         <x:f>B13</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="V13" s="38" t="str">
+      <x:c r="U13" s="38" t="str">
         <x:f>C13</x:f>
         <x:v>+1</x:v>
       </x:c>
-      <x:c r="W13" s="38" t="str">
+      <x:c r="V13" s="38" t="str">
         <x:f>D13</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3927,15 +3750,15 @@
       <x:c r="D14" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="U14" s="38" t="str">
+      <x:c r="T14" s="38" t="str">
         <x:f>B14</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="V14" s="38" t="str">
+      <x:c r="U14" s="38" t="str">
         <x:f>C14</x:f>
         <x:v>On subject</x:v>
       </x:c>
-      <x:c r="W14" s="38" t="str">
+      <x:c r="V14" s="38" t="str">
         <x:f>D14</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -3953,15 +3776,15 @@
       <x:c r="D15" s="17" t="str">
         <x:v>1-Point AF</x:v>
       </x:c>
-      <x:c r="U15" s="38" t="str">
+      <x:c r="T15" s="38" t="str">
         <x:f>B15</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="V15" s="38" t="str">
+      <x:c r="U15" s="38" t="str">
         <x:f>C15</x:f>
         <x:v>Face + Tracking</x:v>
       </x:c>
-      <x:c r="W15" s="38" t="str">
+      <x:c r="V15" s="38" t="str">
         <x:f>D15</x:f>
         <x:v>1-Point AF</x:v>
       </x:c>
@@ -3979,15 +3802,15 @@
       <x:c r="D16" s="17" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="U16" s="38" t="str">
+      <x:c r="T16" s="38" t="str">
         <x:f>B16</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="V16" s="38" t="str">
+      <x:c r="U16" s="38" t="str">
         <x:f>C16</x:f>
         <x:v>Animals</x:v>
       </x:c>
-      <x:c r="W16" s="38" t="str">
+      <x:c r="V16" s="38" t="str">
         <x:f>D16</x:f>
         <x:v>None</x:v>
       </x:c>
@@ -4005,15 +3828,15 @@
       <x:c r="D17" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
-      <x:c r="U17" s="38" t="str">
+      <x:c r="T17" s="38" t="str">
         <x:f>B17</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="V17" s="38" t="str">
+      <x:c r="U17" s="38" t="str">
         <x:f>C17</x:f>
         <x:v>Enable</x:v>
       </x:c>
-      <x:c r="W17" s="38" t="str">
+      <x:c r="V17" s="38" t="str">
         <x:f>D17</x:f>
         <x:v>Disable</x:v>
       </x:c>
@@ -4031,15 +3854,15 @@
       <x:c r="D18" s="17" t="str">
         <x:v>Single Shot</x:v>
       </x:c>
-      <x:c r="U18" s="38" t="str">
+      <x:c r="T18" s="38" t="str">
         <x:f>B18</x:f>
         <x:v>High Speed Continuous</x:v>
       </x:c>
-      <x:c r="V18" s="38" t="str">
+      <x:c r="U18" s="38" t="str">
         <x:f>C18</x:f>
         <x:v>High Speed Continuous+</x:v>
       </x:c>
-      <x:c r="W18" s="38" t="str">
+      <x:c r="V18" s="38" t="str">
         <x:f>D18</x:f>
         <x:v>Single Shot</x:v>
       </x:c>
@@ -4057,15 +3880,15 @@
       <x:c r="D19" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="U19" s="38" t="str">
+      <x:c r="T19" s="38" t="str">
         <x:f>B19</x:f>
         <x:v>Enable</x:v>
       </x:c>
+      <x:c r="U19" s="38" t="str">
+        <x:f>C19</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
       <x:c r="V19" s="38" t="str">
-        <x:f>C19</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="W19" s="38" t="str">
         <x:f>D19</x:f>
         <x:v>Not Used</x:v>
       </x:c>
@@ -4083,15 +3906,15 @@
       <x:c r="D20" s="17" t="str">
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="U20" s="38" t="str">
+      <x:c r="T20" s="38" t="str">
         <x:f>B20</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
-      <x:c r="V20" s="38" t="str">
+      <x:c r="U20" s="38" t="str">
         <x:f>C20</x:f>
         <x:v>Mode 3</x:v>
       </x:c>
-      <x:c r="W20" s="38" t="str">
+      <x:c r="V20" s="38" t="str">
         <x:f>D20</x:f>
         <x:v>Mode 1</x:v>
       </x:c>
@@ -4109,15 +3932,15 @@
       <x:c r="D21" s="17" t="str">
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="U21" s="38" t="str">
+      <x:c r="T21" s="38" t="str">
         <x:f>B21</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="V21" s="38" t="str">
+      <x:c r="U21" s="38" t="str">
         <x:f>C21</x:f>
         <x:v>On / On</x:v>
       </x:c>
-      <x:c r="W21" s="38" t="str">
+      <x:c r="V21" s="38" t="str">
         <x:f>D21</x:f>
         <x:v>On / On</x:v>
       </x:c>
@@ -4135,15 +3958,15 @@
       <x:c r="D22" s="17" t="str">
         <x:v>Disable</x:v>
       </x:c>
+      <x:c r="T22" s="38" t="str">
+        <x:f>B22</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
       <x:c r="U22" s="38" t="str">
-        <x:f>B22</x:f>
+        <x:f>C22</x:f>
         <x:v>Disable</x:v>
       </x:c>
       <x:c r="V22" s="38" t="str">
-        <x:f>C22</x:f>
-        <x:v>Disable</x:v>
-      </x:c>
-      <x:c r="W22" s="38" t="str">
         <x:f>D22</x:f>
         <x:v>Disable</x:v>
       </x:c>
@@ -4153,23 +3976,23 @@
     <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="B3:B22">
-    <x:cfRule type="cellIs" dxfId="17" priority="1" operator="notEqual">
+    <x:cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
+      <x:formula>$T3</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="C3:C22">
+    <x:cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
       <x:formula>$U3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C3:C22">
-    <x:cfRule type="cellIs" dxfId="18" priority="2" operator="notEqual">
+  <x:conditionalFormatting sqref="D3:D22">
+    <x:cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
       <x:formula>$V3</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D3:D22">
-    <x:cfRule type="cellIs" dxfId="19" priority="3" operator="notEqual">
-      <x:formula>$W3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R0fb18e4be6514425"/>
+    <x:tablePart ns1:id="R81d79827fe37415a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R91b3e431b9e444b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R6d041c6ad3c0481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R6e7959ce39cb4984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R33154ee3a0f84735"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="646283c4-0ec3-4e01-8dc0-89e33c3f8925"/>
+        <xdr:cNvPr id="1" name="f9b08aec-61b1-45b3-b1ce-016221c86426"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc056bdc970214e17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7e402440ccc047da"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -849,16 +849,16 @@
         <x:v>Camera Defaults + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="H5" s="37" t="str">
-        <x:v>C2 Birds in Flight + AF Case</x:v>
+        <x:v>C2 Birds in Flight + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="I5" s="37" t="str">
-        <x:v>C1 Wildlife + AF Case</x:v>
+        <x:v>C1 Wildlife + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="J5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="K5" s="37" t="str">
-        <x:v>C3 Landscape</x:v>
+        <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="L5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
@@ -870,13 +870,13 @@
         <x:v>C2 Birds in Flight + SWITCH + AF Case</x:v>
       </x:c>
       <x:c r="O5" s="37" t="str">
-        <x:v>C3 Landscape</x:v>
+        <x:v>C3 Landscape + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="P5" s="37" t="str">
         <x:v>C3 Landscape + SWITCH</x:v>
       </x:c>
       <x:c r="Q5" s="37" t="str">
-        <x:v>C1 Wildlife + AF Case</x:v>
+        <x:v>C1 Wildlife + AF Case + SWITCH</x:v>
       </x:c>
       <x:c r="T5" s="38"/>
       <x:c r="U5" s="38"/>
@@ -3388,9 +3388,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rbe9a3ada33a24cdf"/>
+  <x:drawing ns1:id="R3d10a9c51937413e"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R0f96c99050124d18"/>
+    <x:tablePart ns1:id="Raf51ea05238a4793"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3992,7 +3992,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R81d79827fe37415a"/>
+    <x:tablePart ns1:id="Re9c032c28fd247e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R6e7959ce39cb4984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R33154ee3a0f84735"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Re8c9c34fc9344ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R9218f080977b4325"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="f9b08aec-61b1-45b3-b1ce-016221c86426"/>
+        <xdr:cNvPr id="1" name="e8c97b97-c8df-48f4-88c9-f9fb12814803"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7e402440ccc047da"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2714f49b16be4722"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3388,9 +3388,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R3d10a9c51937413e"/>
+  <x:drawing ns1:id="R158d399ee375412e"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Raf51ea05238a4793"/>
+    <x:tablePart ns1:id="R91972fff75fa46f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3992,7 +3992,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Re9c032c28fd247e8"/>
+    <x:tablePart ns1:id="Rbb0a4e13996e43a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Re8c9c34fc9344ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R9218f080977b4325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Re1db1ead78ab43e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R142c6c1c8fa1455c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="e8c97b97-c8df-48f4-88c9-f9fb12814803"/>
+        <xdr:cNvPr id="1" name="ebb6a567-5e25-4d25-b93e-b67911893025"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2714f49b16be4722"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re6a82793416b4b5e"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -453,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A6:S26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SubjectSettingsTable" displayName="SubjectSettingsTable" ref="A6:S46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:S46"/>
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="Menu Location"/>
     <x:tableColumn id="2" name="Best or Quick Access"/>
@@ -481,8 +481,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A2:D22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CxDefaultsTable" displayName="CxDefaultsTable" ref="A2:D42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A2:D42"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Setting"/>
     <x:tableColumn id="2" name="C1 Wildlife"/>
@@ -1658,491 +1658,491 @@
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="12" t="str">
-        <x:v>Direct control; Q is the alternative</x:v>
+        <x:v>Shooting 2 &gt; ISO speed settings</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>Rear dial / Fv exposure dials</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Exposure Comp</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>ISO Value</x:v>
+      </x:c>
+      <x:c r="D13" s="17" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="E13" s="17" t="str">
-        <x:v>0 starting point</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="F13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="H13" s="17" t="str">
-        <x:v>Adjust for background</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="I13" s="17" t="str">
-        <x:v>0 to +1/3</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="J13" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P13" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q13" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L13" s="17" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N13" s="17" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="P13" s="17" t="str">
+        <x:v>100-400</x:v>
+      </x:c>
+      <x:c r="Q13" s="17" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="R13" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="S13" s="20" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="T13" s="38" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="T13" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D13,IF($D$4="C2 Birds in Flight",E13,IF($D$4="C3 Landscape",F13,IF($D$4="Default Settings",G13,IF($D$4="Birds in Flight",H13,IF($D$4="Birds Perched",I13,IF($D$4="Fireworks",J13,IF($D$4="Landscape",K13,IF($D$4="Macro",L13,IF($D$4="People",M13,IF($D$4="Sports",N13,IF($D$4="Travel",O13,IF($D$4="Waterdrops",P13,IF($D$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="U13" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D13,IF($E$4="C2 Birds in Flight",E13,IF($E$4="C3 Landscape",F13,IF($E$4="Default Settings",G13,IF($E$4="Birds in Flight",H13,IF($E$4="Birds Perched",I13,IF($E$4="Fireworks",J13,IF($E$4="Landscape",K13,IF($E$4="Macro",L13,IF($E$4="People",M13,IF($E$4="Sports",N13,IF($E$4="Travel",O13,IF($E$4="Waterdrops",P13,IF($E$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0 starting point</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="V13" s="38" t="n">
         <x:f>IF($F$4="C1 Wildlife",D13,IF($F$4="C2 Birds in Flight",E13,IF($F$4="C3 Landscape",F13,IF($F$4="Default Settings",G13,IF($F$4="Birds in Flight",H13,IF($F$4="Birds Perched",I13,IF($F$4="Fireworks",J13,IF($F$4="Landscape",K13,IF($F$4="Macro",L13,IF($F$4="People",M13,IF($F$4="Sports",N13,IF($F$4="Travel",O13,IF($F$4="Waterdrops",P13,IF($F$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W13" s="38" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="W13" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D13,IF($G$4="C2 Birds in Flight",E13,IF($G$4="C3 Landscape",F13,IF($G$4="Default Settings",G13,IF($G$4="Birds in Flight",H13,IF($G$4="Birds Perched",I13,IF($G$4="Fireworks",J13,IF($G$4="Landscape",K13,IF($G$4="Macro",L13,IF($G$4="People",M13,IF($G$4="Sports",N13,IF($G$4="Travel",O13,IF($G$4="Waterdrops",P13,IF($G$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="X13" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D13,IF($H$4="C2 Birds in Flight",E13,IF($H$4="C3 Landscape",F13,IF($H$4="Default Settings",G13,IF($H$4="Birds in Flight",H13,IF($H$4="Birds Perched",I13,IF($H$4="Fireworks",J13,IF($H$4="Landscape",K13,IF($H$4="Macro",L13,IF($H$4="People",M13,IF($H$4="Sports",N13,IF($H$4="Travel",O13,IF($H$4="Waterdrops",P13,IF($H$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>Adjust for background</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="Y13" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D13,IF($I$4="C2 Birds in Flight",E13,IF($I$4="C3 Landscape",F13,IF($I$4="Default Settings",G13,IF($I$4="Birds in Flight",H13,IF($I$4="Birds Perched",I13,IF($I$4="Fireworks",J13,IF($I$4="Landscape",K13,IF($I$4="Macro",L13,IF($I$4="People",M13,IF($I$4="Sports",N13,IF($I$4="Travel",O13,IF($I$4="Waterdrops",P13,IF($I$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0 to +1/3</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="Z13" s="38" t="n">
         <x:f>IF($J$4="C1 Wildlife",D13,IF($J$4="C2 Birds in Flight",E13,IF($J$4="C3 Landscape",F13,IF($J$4="Default Settings",G13,IF($J$4="Birds in Flight",H13,IF($J$4="Birds Perched",I13,IF($J$4="Fireworks",J13,IF($J$4="Landscape",K13,IF($J$4="Macro",L13,IF($J$4="People",M13,IF($J$4="Sports",N13,IF($J$4="Travel",O13,IF($J$4="Waterdrops",P13,IF($J$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="AA13" s="38" t="n">
         <x:f>IF($K$4="C1 Wildlife",D13,IF($K$4="C2 Birds in Flight",E13,IF($K$4="C3 Landscape",F13,IF($K$4="Default Settings",G13,IF($K$4="Birds in Flight",H13,IF($K$4="Birds Perched",I13,IF($K$4="Fireworks",J13,IF($K$4="Landscape",K13,IF($K$4="Macro",L13,IF($K$4="People",M13,IF($K$4="Sports",N13,IF($K$4="Travel",O13,IF($K$4="Waterdrops",P13,IF($K$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB13" s="38" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="AB13" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D13,IF($L$4="C2 Birds in Flight",E13,IF($L$4="C3 Landscape",F13,IF($L$4="Default Settings",G13,IF($L$4="Birds in Flight",H13,IF($L$4="Birds Perched",I13,IF($L$4="Fireworks",J13,IF($L$4="Landscape",K13,IF($L$4="Macro",L13,IF($L$4="People",M13,IF($L$4="Sports",N13,IF($L$4="Travel",O13,IF($L$4="Waterdrops",P13,IF($L$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC13" s="38" t="n">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="AC13" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D13,IF($M$4="C2 Birds in Flight",E13,IF($M$4="C3 Landscape",F13,IF($M$4="Default Settings",G13,IF($M$4="Birds in Flight",H13,IF($M$4="Birds Perched",I13,IF($M$4="Fireworks",J13,IF($M$4="Landscape",K13,IF($M$4="Macro",L13,IF($M$4="People",M13,IF($M$4="Sports",N13,IF($M$4="Travel",O13,IF($M$4="Waterdrops",P13,IF($M$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD13" s="38" t="n">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="AD13" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D13,IF($N$4="C2 Birds in Flight",E13,IF($N$4="C3 Landscape",F13,IF($N$4="Default Settings",G13,IF($N$4="Birds in Flight",H13,IF($N$4="Birds Perched",I13,IF($N$4="Fireworks",J13,IF($N$4="Landscape",K13,IF($N$4="Macro",L13,IF($N$4="People",M13,IF($N$4="Sports",N13,IF($N$4="Travel",O13,IF($N$4="Waterdrops",P13,IF($N$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AE13" s="38" t="n">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="AE13" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D13,IF($O$4="C2 Birds in Flight",E13,IF($O$4="C3 Landscape",F13,IF($O$4="Default Settings",G13,IF($O$4="Birds in Flight",H13,IF($O$4="Birds Perched",I13,IF($O$4="Fireworks",J13,IF($O$4="Landscape",K13,IF($O$4="Macro",L13,IF($O$4="People",M13,IF($O$4="Sports",N13,IF($O$4="Travel",O13,IF($O$4="Waterdrops",P13,IF($O$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF13" s="38" t="n">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="AF13" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D13,IF($P$4="C2 Birds in Flight",E13,IF($P$4="C3 Landscape",F13,IF($P$4="Default Settings",G13,IF($P$4="Birds in Flight",H13,IF($P$4="Birds Perched",I13,IF($P$4="Fireworks",J13,IF($P$4="Landscape",K13,IF($P$4="Macro",L13,IF($P$4="People",M13,IF($P$4="Sports",N13,IF($P$4="Travel",O13,IF($P$4="Waterdrops",P13,IF($P$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG13" s="38" t="n">
+        <x:v>100-400</x:v>
+      </x:c>
+      <x:c r="AG13" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D13,IF($Q$4="C2 Birds in Flight",E13,IF($Q$4="C3 Landscape",F13,IF($Q$4="Default Settings",G13,IF($Q$4="Birds in Flight",H13,IF($Q$4="Birds Perched",I13,IF($Q$4="Fireworks",J13,IF($Q$4="Landscape",K13,IF($Q$4="Macro",L13,IF($Q$4="People",M13,IF($Q$4="Sports",N13,IF($Q$4="Travel",O13,IF($Q$4="Waterdrops",P13,IF($Q$4="Wildlife",Q13,""))))))))))))))</x:f>
-        <x:v>0</x:v>
+        <x:v>—</x:v>
       </x:c>
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="12" t="str">
-        <x:v>AF1 &gt; AF operation</x:v>
+        <x:v>Shooting 2 &gt; ISO speed settings &gt; Auto range</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>Full camera menu</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>AF Operation</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="H14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="I14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="str">
-        <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="L14" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="N14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="O14" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="P14" s="17" t="str">
-        <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="Q14" s="17" t="str">
-        <x:v>Servo AF</x:v>
+        <x:v>Auto ISO Max</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="H14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="K14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="L14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="N14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="P14" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="n">
+        <x:v>12800</x:v>
       </x:c>
       <x:c r="R14" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S14" s="20" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="T14" s="38" t="str">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="T14" s="38" t="n">
         <x:f>IF($D$4="C1 Wildlife",D14,IF($D$4="C2 Birds in Flight",E14,IF($D$4="C3 Landscape",F14,IF($D$4="Default Settings",G14,IF($D$4="Birds in Flight",H14,IF($D$4="Birds Perched",I14,IF($D$4="Fireworks",J14,IF($D$4="Landscape",K14,IF($D$4="Macro",L14,IF($D$4="People",M14,IF($D$4="Sports",N14,IF($D$4="Travel",O14,IF($D$4="Waterdrops",P14,IF($D$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="U14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="U14" s="38" t="n">
         <x:f>IF($E$4="C1 Wildlife",D14,IF($E$4="C2 Birds in Flight",E14,IF($E$4="C3 Landscape",F14,IF($E$4="Default Settings",G14,IF($E$4="Birds in Flight",H14,IF($E$4="Birds Perched",I14,IF($E$4="Fireworks",J14,IF($E$4="Landscape",K14,IF($E$4="Macro",L14,IF($E$4="People",M14,IF($E$4="Sports",N14,IF($E$4="Travel",O14,IF($E$4="Waterdrops",P14,IF($E$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="V14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="V14" s="38" t="n">
         <x:f>IF($F$4="C1 Wildlife",D14,IF($F$4="C2 Birds in Flight",E14,IF($F$4="C3 Landscape",F14,IF($F$4="Default Settings",G14,IF($F$4="Birds in Flight",H14,IF($F$4="Birds Perched",I14,IF($F$4="Fireworks",J14,IF($F$4="Landscape",K14,IF($F$4="Macro",L14,IF($F$4="People",M14,IF($F$4="Sports",N14,IF($F$4="Travel",O14,IF($F$4="Waterdrops",P14,IF($F$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="W14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="W14" s="38" t="n">
         <x:f>IF($G$4="C1 Wildlife",D14,IF($G$4="C2 Birds in Flight",E14,IF($G$4="C3 Landscape",F14,IF($G$4="Default Settings",G14,IF($G$4="Birds in Flight",H14,IF($G$4="Birds Perched",I14,IF($G$4="Fireworks",J14,IF($G$4="Landscape",K14,IF($G$4="Macro",L14,IF($G$4="People",M14,IF($G$4="Sports",N14,IF($G$4="Travel",O14,IF($G$4="Waterdrops",P14,IF($G$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="X14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="X14" s="38" t="n">
         <x:f>IF($H$4="C1 Wildlife",D14,IF($H$4="C2 Birds in Flight",E14,IF($H$4="C3 Landscape",F14,IF($H$4="Default Settings",G14,IF($H$4="Birds in Flight",H14,IF($H$4="Birds Perched",I14,IF($H$4="Fireworks",J14,IF($H$4="Landscape",K14,IF($H$4="Macro",L14,IF($H$4="People",M14,IF($H$4="Sports",N14,IF($H$4="Travel",O14,IF($H$4="Waterdrops",P14,IF($H$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="Y14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="Y14" s="38" t="n">
         <x:f>IF($I$4="C1 Wildlife",D14,IF($I$4="C2 Birds in Flight",E14,IF($I$4="C3 Landscape",F14,IF($I$4="Default Settings",G14,IF($I$4="Birds in Flight",H14,IF($I$4="Birds Perched",I14,IF($I$4="Fireworks",J14,IF($I$4="Landscape",K14,IF($I$4="Macro",L14,IF($I$4="People",M14,IF($I$4="Sports",N14,IF($I$4="Travel",O14,IF($I$4="Waterdrops",P14,IF($I$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="Z14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="Z14" s="38" t="n">
         <x:f>IF($J$4="C1 Wildlife",D14,IF($J$4="C2 Birds in Flight",E14,IF($J$4="C3 Landscape",F14,IF($J$4="Default Settings",G14,IF($J$4="Birds in Flight",H14,IF($J$4="Birds Perched",I14,IF($J$4="Fireworks",J14,IF($J$4="Landscape",K14,IF($J$4="Macro",L14,IF($J$4="People",M14,IF($J$4="Sports",N14,IF($J$4="Travel",O14,IF($J$4="Waterdrops",P14,IF($J$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="AA14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AA14" s="38" t="n">
         <x:f>IF($K$4="C1 Wildlife",D14,IF($K$4="C2 Birds in Flight",E14,IF($K$4="C3 Landscape",F14,IF($K$4="Default Settings",G14,IF($K$4="Birds in Flight",H14,IF($K$4="Birds Perched",I14,IF($K$4="Fireworks",J14,IF($K$4="Landscape",K14,IF($K$4="Macro",L14,IF($K$4="People",M14,IF($K$4="Sports",N14,IF($K$4="Travel",O14,IF($K$4="Waterdrops",P14,IF($K$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="AB14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AB14" s="38" t="n">
         <x:f>IF($L$4="C1 Wildlife",D14,IF($L$4="C2 Birds in Flight",E14,IF($L$4="C3 Landscape",F14,IF($L$4="Default Settings",G14,IF($L$4="Birds in Flight",H14,IF($L$4="Birds Perched",I14,IF($L$4="Fireworks",J14,IF($L$4="Landscape",K14,IF($L$4="Macro",L14,IF($L$4="People",M14,IF($L$4="Sports",N14,IF($L$4="Travel",O14,IF($L$4="Waterdrops",P14,IF($L$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="AC14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AC14" s="38" t="n">
         <x:f>IF($M$4="C1 Wildlife",D14,IF($M$4="C2 Birds in Flight",E14,IF($M$4="C3 Landscape",F14,IF($M$4="Default Settings",G14,IF($M$4="Birds in Flight",H14,IF($M$4="Birds Perched",I14,IF($M$4="Fireworks",J14,IF($M$4="Landscape",K14,IF($M$4="Macro",L14,IF($M$4="People",M14,IF($M$4="Sports",N14,IF($M$4="Travel",O14,IF($M$4="Waterdrops",P14,IF($M$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AD14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AD14" s="38" t="n">
         <x:f>IF($N$4="C1 Wildlife",D14,IF($N$4="C2 Birds in Flight",E14,IF($N$4="C3 Landscape",F14,IF($N$4="Default Settings",G14,IF($N$4="Birds in Flight",H14,IF($N$4="Birds Perched",I14,IF($N$4="Fireworks",J14,IF($N$4="Landscape",K14,IF($N$4="Macro",L14,IF($N$4="People",M14,IF($N$4="Sports",N14,IF($N$4="Travel",O14,IF($N$4="Waterdrops",P14,IF($N$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AE14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AE14" s="38" t="n">
         <x:f>IF($O$4="C1 Wildlife",D14,IF($O$4="C2 Birds in Flight",E14,IF($O$4="C3 Landscape",F14,IF($O$4="Default Settings",G14,IF($O$4="Birds in Flight",H14,IF($O$4="Birds Perched",I14,IF($O$4="Fireworks",J14,IF($O$4="Landscape",K14,IF($O$4="Macro",L14,IF($O$4="People",M14,IF($O$4="Sports",N14,IF($O$4="Travel",O14,IF($O$4="Waterdrops",P14,IF($O$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="AF14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AF14" s="38" t="n">
         <x:f>IF($P$4="C1 Wildlife",D14,IF($P$4="C2 Birds in Flight",E14,IF($P$4="C3 Landscape",F14,IF($P$4="Default Settings",G14,IF($P$4="Birds in Flight",H14,IF($P$4="Birds Perched",I14,IF($P$4="Fireworks",J14,IF($P$4="Landscape",K14,IF($P$4="Macro",L14,IF($P$4="People",M14,IF($P$4="Sports",N14,IF($P$4="Travel",O14,IF($P$4="Waterdrops",P14,IF($P$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Manual Focus</x:v>
-      </x:c>
-      <x:c r="AG14" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="AG14" s="38" t="n">
         <x:f>IF($Q$4="C1 Wildlife",D14,IF($Q$4="C2 Birds in Flight",E14,IF($Q$4="C3 Landscape",F14,IF($Q$4="Default Settings",G14,IF($Q$4="Birds in Flight",H14,IF($Q$4="Birds Perched",I14,IF($Q$4="Fireworks",J14,IF($Q$4="Landscape",K14,IF($Q$4="Macro",L14,IF($Q$4="People",M14,IF($Q$4="Sports",N14,IF($Q$4="Travel",O14,IF($Q$4="Waterdrops",P14,IF($Q$4="Wildlife",Q14,""))))))))))))))</x:f>
-        <x:v>Servo AF</x:v>
+        <x:v>12800</x:v>
       </x:c>
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="12" t="str">
-        <x:v>My Menu &gt; AF Case &gt; Servo AF; AF3 &gt; Servo AF characteristics</x:v>
+        <x:v>Direct control; Q is the alternative</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
+        <x:v>Rear dial / Fv exposure dials</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>Servo AF Case</x:v>
-      </x:c>
-      <x:c r="D15" s="17" t="str">
-        <x:v>Case 1 (Custom)</x:v>
+        <x:v>Exposure Comp</x:v>
+      </x:c>
+      <x:c r="D15" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="17" t="str">
-        <x:v>Case 4</x:v>
-      </x:c>
-      <x:c r="F15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="17" t="str">
-        <x:v>Case 4</x:v>
+        <x:v>Adjust for background</x:v>
       </x:c>
       <x:c r="I15" s="17" t="str">
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="J15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="K15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="L15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="M15" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
-      <x:c r="N15" s="17" t="str">
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="O15" s="17" t="str">
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
-      <x:c r="P15" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Q15" s="17" t="str">
-        <x:v>Case 1 (Custom)</x:v>
+        <x:v>0 to +1/3</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R15" s="20" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="S15" s="20" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="T15" s="38" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="T15" s="38" t="n">
         <x:f>IF($D$4="C1 Wildlife",D15,IF($D$4="C2 Birds in Flight",E15,IF($D$4="C3 Landscape",F15,IF($D$4="Default Settings",G15,IF($D$4="Birds in Flight",H15,IF($D$4="Birds Perched",I15,IF($D$4="Fireworks",J15,IF($D$4="Landscape",K15,IF($D$4="Macro",L15,IF($D$4="People",M15,IF($D$4="Sports",N15,IF($D$4="Travel",O15,IF($D$4="Waterdrops",P15,IF($D$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U15" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D15,IF($E$4="C2 Birds in Flight",E15,IF($E$4="C3 Landscape",F15,IF($E$4="Default Settings",G15,IF($E$4="Birds in Flight",H15,IF($E$4="Birds Perched",I15,IF($E$4="Fireworks",J15,IF($E$4="Landscape",K15,IF($E$4="Macro",L15,IF($E$4="People",M15,IF($E$4="Sports",N15,IF($E$4="Travel",O15,IF($E$4="Waterdrops",P15,IF($E$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 4</x:v>
-      </x:c>
-      <x:c r="V15" s="38" t="str">
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="V15" s="38" t="n">
         <x:f>IF($F$4="C1 Wildlife",D15,IF($F$4="C2 Birds in Flight",E15,IF($F$4="C3 Landscape",F15,IF($F$4="Default Settings",G15,IF($F$4="Birds in Flight",H15,IF($F$4="Birds Perched",I15,IF($F$4="Fireworks",J15,IF($F$4="Landscape",K15,IF($F$4="Macro",L15,IF($F$4="People",M15,IF($F$4="Sports",N15,IF($F$4="Travel",O15,IF($F$4="Waterdrops",P15,IF($F$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="W15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W15" s="38" t="n">
         <x:f>IF($G$4="C1 Wildlife",D15,IF($G$4="C2 Birds in Flight",E15,IF($G$4="C3 Landscape",F15,IF($G$4="Default Settings",G15,IF($G$4="Birds in Flight",H15,IF($G$4="Birds Perched",I15,IF($G$4="Fireworks",J15,IF($G$4="Landscape",K15,IF($G$4="Macro",L15,IF($G$4="People",M15,IF($G$4="Sports",N15,IF($G$4="Travel",O15,IF($G$4="Waterdrops",P15,IF($G$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X15" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D15,IF($H$4="C2 Birds in Flight",E15,IF($H$4="C3 Landscape",F15,IF($H$4="Default Settings",G15,IF($H$4="Birds in Flight",H15,IF($H$4="Birds Perched",I15,IF($H$4="Fireworks",J15,IF($H$4="Landscape",K15,IF($H$4="Macro",L15,IF($H$4="People",M15,IF($H$4="Sports",N15,IF($H$4="Travel",O15,IF($H$4="Waterdrops",P15,IF($H$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 4</x:v>
+        <x:v>Adjust for background</x:v>
       </x:c>
       <x:c r="Y15" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D15,IF($I$4="C2 Birds in Flight",E15,IF($I$4="C3 Landscape",F15,IF($I$4="Default Settings",G15,IF($I$4="Birds in Flight",H15,IF($I$4="Birds Perched",I15,IF($I$4="Fireworks",J15,IF($I$4="Landscape",K15,IF($I$4="Macro",L15,IF($I$4="People",M15,IF($I$4="Sports",N15,IF($I$4="Travel",O15,IF($I$4="Waterdrops",P15,IF($I$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="Z15" s="38" t="str">
+        <x:v>0 to +1/3</x:v>
+      </x:c>
+      <x:c r="Z15" s="38" t="n">
         <x:f>IF($J$4="C1 Wildlife",D15,IF($J$4="C2 Birds in Flight",E15,IF($J$4="C3 Landscape",F15,IF($J$4="Default Settings",G15,IF($J$4="Birds in Flight",H15,IF($J$4="Birds Perched",I15,IF($J$4="Fireworks",J15,IF($J$4="Landscape",K15,IF($J$4="Macro",L15,IF($J$4="People",M15,IF($J$4="Sports",N15,IF($J$4="Travel",O15,IF($J$4="Waterdrops",P15,IF($J$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AA15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA15" s="38" t="n">
         <x:f>IF($K$4="C1 Wildlife",D15,IF($K$4="C2 Birds in Flight",E15,IF($K$4="C3 Landscape",F15,IF($K$4="Default Settings",G15,IF($K$4="Birds in Flight",H15,IF($K$4="Birds Perched",I15,IF($K$4="Fireworks",J15,IF($K$4="Landscape",K15,IF($K$4="Macro",L15,IF($K$4="People",M15,IF($K$4="Sports",N15,IF($K$4="Travel",O15,IF($K$4="Waterdrops",P15,IF($K$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AB15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB15" s="38" t="n">
         <x:f>IF($L$4="C1 Wildlife",D15,IF($L$4="C2 Birds in Flight",E15,IF($L$4="C3 Landscape",F15,IF($L$4="Default Settings",G15,IF($L$4="Birds in Flight",H15,IF($L$4="Birds Perched",I15,IF($L$4="Fireworks",J15,IF($L$4="Landscape",K15,IF($L$4="Macro",L15,IF($L$4="People",M15,IF($L$4="Sports",N15,IF($L$4="Travel",O15,IF($L$4="Waterdrops",P15,IF($L$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AC15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AC15" s="38" t="n">
         <x:f>IF($M$4="C1 Wildlife",D15,IF($M$4="C2 Birds in Flight",E15,IF($M$4="C3 Landscape",F15,IF($M$4="Default Settings",G15,IF($M$4="Birds in Flight",H15,IF($M$4="Birds Perched",I15,IF($M$4="Fireworks",J15,IF($M$4="Landscape",K15,IF($M$4="Macro",L15,IF($M$4="People",M15,IF($M$4="Sports",N15,IF($M$4="Travel",O15,IF($M$4="Waterdrops",P15,IF($M$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
-      <x:c r="AD15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD15" s="38" t="n">
         <x:f>IF($N$4="C1 Wildlife",D15,IF($N$4="C2 Birds in Flight",E15,IF($N$4="C3 Landscape",F15,IF($N$4="Default Settings",G15,IF($N$4="Birds in Flight",H15,IF($N$4="Birds Perched",I15,IF($N$4="Fireworks",J15,IF($N$4="Landscape",K15,IF($N$4="Macro",L15,IF($N$4="People",M15,IF($N$4="Sports",N15,IF($N$4="Travel",O15,IF($N$4="Waterdrops",P15,IF($N$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
-      </x:c>
-      <x:c r="AE15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AE15" s="38" t="n">
         <x:f>IF($O$4="C1 Wildlife",D15,IF($O$4="C2 Birds in Flight",E15,IF($O$4="C3 Landscape",F15,IF($O$4="Default Settings",G15,IF($O$4="Birds in Flight",H15,IF($O$4="Birds Perched",I15,IF($O$4="Fireworks",J15,IF($O$4="Landscape",K15,IF($O$4="Macro",L15,IF($O$4="People",M15,IF($O$4="Sports",N15,IF($O$4="Travel",O15,IF($O$4="Waterdrops",P15,IF($O$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case A (Auto)</x:v>
-      </x:c>
-      <x:c r="AF15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF15" s="38" t="n">
         <x:f>IF($P$4="C1 Wildlife",D15,IF($P$4="C2 Birds in Flight",E15,IF($P$4="C3 Landscape",F15,IF($P$4="Default Settings",G15,IF($P$4="Birds in Flight",H15,IF($P$4="Birds Perched",I15,IF($P$4="Fireworks",J15,IF($P$4="Landscape",K15,IF($P$4="Macro",L15,IF($P$4="People",M15,IF($P$4="Sports",N15,IF($P$4="Travel",O15,IF($P$4="Waterdrops",P15,IF($P$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AG15" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AG15" s="38" t="n">
         <x:f>IF($Q$4="C1 Wildlife",D15,IF($Q$4="C2 Birds in Flight",E15,IF($Q$4="C3 Landscape",F15,IF($Q$4="Default Settings",G15,IF($Q$4="Birds in Flight",H15,IF($Q$4="Birds Perched",I15,IF($Q$4="Fireworks",J15,IF($Q$4="Landscape",K15,IF($Q$4="Macro",L15,IF($Q$4="People",M15,IF($Q$4="Sports",N15,IF($Q$4="Travel",O15,IF($Q$4="Waterdrops",P15,IF($Q$4="Wildlife",Q15,""))))))))))))))</x:f>
-        <x:v>Case 1 (Custom)</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="12" t="str">
-        <x:v>My Menu &gt; AF Case &gt; Tracking Sensitivity; AF3 &gt; Servo AF characteristics</x:v>
+        <x:v>AF1 &gt; AF operation</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
+        <x:v>Q screen</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Tracking Sensitivity</x:v>
-      </x:c>
-      <x:c r="D16" s="17" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="E16" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>AF Operation</x:v>
+      </x:c>
+      <x:c r="D16" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="str">
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="F16" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="G16" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="H16" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="17" t="n">
-        <x:v>-1</x:v>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="H16" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="J16" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Manual Focus</x:v>
       </x:c>
       <x:c r="K16" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="L16" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="M16" s="17" t="str">
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="N16" s="17" t="n">
-        <x:v>-1</x:v>
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="N16" s="17" t="str">
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="O16" s="17" t="str">
-        <x:v>Auto</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="P16" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="Q16" s="17" t="n">
-        <x:v>-1</x:v>
+        <x:v>Manual Focus</x:v>
+      </x:c>
+      <x:c r="Q16" s="17" t="str">
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="R16" s="20" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="S16" s="20" t="n">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="T16" s="38" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="T16" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D16,IF($D$4="C2 Birds in Flight",E16,IF($D$4="C3 Landscape",F16,IF($D$4="Default Settings",G16,IF($D$4="Birds in Flight",H16,IF($D$4="Birds Perched",I16,IF($D$4="Fireworks",J16,IF($D$4="Landscape",K16,IF($D$4="Macro",L16,IF($D$4="People",M16,IF($D$4="Sports",N16,IF($D$4="Travel",O16,IF($D$4="Waterdrops",P16,IF($D$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="U16" s="38" t="n">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="U16" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D16,IF($E$4="C2 Birds in Flight",E16,IF($E$4="C3 Landscape",F16,IF($E$4="Default Settings",G16,IF($E$4="Birds in Flight",H16,IF($E$4="Birds Perched",I16,IF($E$4="Fireworks",J16,IF($E$4="Landscape",K16,IF($E$4="Macro",L16,IF($E$4="People",M16,IF($E$4="Sports",N16,IF($E$4="Travel",O16,IF($E$4="Waterdrops",P16,IF($E$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>0</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="V16" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D16,IF($F$4="C2 Birds in Flight",E16,IF($F$4="C3 Landscape",F16,IF($F$4="Default Settings",G16,IF($F$4="Birds in Flight",H16,IF($F$4="Birds Perched",I16,IF($F$4="Fireworks",J16,IF($F$4="Landscape",K16,IF($F$4="Macro",L16,IF($F$4="People",M16,IF($F$4="Sports",N16,IF($F$4="Travel",O16,IF($F$4="Waterdrops",P16,IF($F$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="W16" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D16,IF($G$4="C2 Birds in Flight",E16,IF($G$4="C3 Landscape",F16,IF($G$4="Default Settings",G16,IF($G$4="Birds in Flight",H16,IF($G$4="Birds Perched",I16,IF($G$4="Fireworks",J16,IF($G$4="Landscape",K16,IF($G$4="Macro",L16,IF($G$4="People",M16,IF($G$4="Sports",N16,IF($G$4="Travel",O16,IF($G$4="Waterdrops",P16,IF($G$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="X16" s="38" t="n">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="X16" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D16,IF($H$4="C2 Birds in Flight",E16,IF($H$4="C3 Landscape",F16,IF($H$4="Default Settings",G16,IF($H$4="Birds in Flight",H16,IF($H$4="Birds Perched",I16,IF($H$4="Fireworks",J16,IF($H$4="Landscape",K16,IF($H$4="Macro",L16,IF($H$4="People",M16,IF($H$4="Sports",N16,IF($H$4="Travel",O16,IF($H$4="Waterdrops",P16,IF($H$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y16" s="38" t="n">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="Y16" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D16,IF($I$4="C2 Birds in Flight",E16,IF($I$4="C3 Landscape",F16,IF($I$4="Default Settings",G16,IF($I$4="Birds in Flight",H16,IF($I$4="Birds Perched",I16,IF($I$4="Fireworks",J16,IF($I$4="Landscape",K16,IF($I$4="Macro",L16,IF($I$4="People",M16,IF($I$4="Sports",N16,IF($I$4="Travel",O16,IF($I$4="Waterdrops",P16,IF($I$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>-1</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="Z16" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D16,IF($J$4="C2 Birds in Flight",E16,IF($J$4="C3 Landscape",F16,IF($J$4="Default Settings",G16,IF($J$4="Birds in Flight",H16,IF($J$4="Birds Perched",I16,IF($J$4="Fireworks",J16,IF($J$4="Landscape",K16,IF($J$4="Macro",L16,IF($J$4="People",M16,IF($J$4="Sports",N16,IF($J$4="Travel",O16,IF($J$4="Waterdrops",P16,IF($J$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Manual Focus</x:v>
       </x:c>
       <x:c r="AA16" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D16,IF($K$4="C2 Birds in Flight",E16,IF($K$4="C3 Landscape",F16,IF($K$4="Default Settings",G16,IF($K$4="Birds in Flight",H16,IF($K$4="Birds Perched",I16,IF($K$4="Fireworks",J16,IF($K$4="Landscape",K16,IF($K$4="Macro",L16,IF($K$4="People",M16,IF($K$4="Sports",N16,IF($K$4="Travel",O16,IF($K$4="Waterdrops",P16,IF($K$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="AB16" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D16,IF($L$4="C2 Birds in Flight",E16,IF($L$4="C3 Landscape",F16,IF($L$4="Default Settings",G16,IF($L$4="Birds in Flight",H16,IF($L$4="Birds Perched",I16,IF($L$4="Fireworks",J16,IF($L$4="Landscape",K16,IF($L$4="Macro",L16,IF($L$4="People",M16,IF($L$4="Sports",N16,IF($L$4="Travel",O16,IF($L$4="Waterdrops",P16,IF($L$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
       <x:c r="AC16" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D16,IF($M$4="C2 Birds in Flight",E16,IF($M$4="C3 Landscape",F16,IF($M$4="Default Settings",G16,IF($M$4="Birds in Flight",H16,IF($M$4="Birds Perched",I16,IF($M$4="Fireworks",J16,IF($M$4="Landscape",K16,IF($M$4="Macro",L16,IF($M$4="People",M16,IF($M$4="Sports",N16,IF($M$4="Travel",O16,IF($M$4="Waterdrops",P16,IF($M$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
-      </x:c>
-      <x:c r="AD16" s="38" t="n">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="AD16" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D16,IF($N$4="C2 Birds in Flight",E16,IF($N$4="C3 Landscape",F16,IF($N$4="Default Settings",G16,IF($N$4="Birds in Flight",H16,IF($N$4="Birds Perched",I16,IF($N$4="Fireworks",J16,IF($N$4="Landscape",K16,IF($N$4="Macro",L16,IF($N$4="People",M16,IF($N$4="Sports",N16,IF($N$4="Travel",O16,IF($N$4="Waterdrops",P16,IF($N$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>-1</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="AE16" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D16,IF($O$4="C2 Birds in Flight",E16,IF($O$4="C3 Landscape",F16,IF($O$4="Default Settings",G16,IF($O$4="Birds in Flight",H16,IF($O$4="Birds Perched",I16,IF($O$4="Fireworks",J16,IF($O$4="Landscape",K16,IF($O$4="Macro",L16,IF($O$4="People",M16,IF($O$4="Sports",N16,IF($O$4="Travel",O16,IF($O$4="Waterdrops",P16,IF($O$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="AF16" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D16,IF($P$4="C2 Birds in Flight",E16,IF($P$4="C3 Landscape",F16,IF($P$4="Default Settings",G16,IF($P$4="Birds in Flight",H16,IF($P$4="Birds Perched",I16,IF($P$4="Fireworks",J16,IF($P$4="Landscape",K16,IF($P$4="Macro",L16,IF($P$4="People",M16,IF($P$4="Sports",N16,IF($P$4="Travel",O16,IF($P$4="Waterdrops",P16,IF($P$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="AG16" s="38" t="n">
+        <x:v>Manual Focus</x:v>
+      </x:c>
+      <x:c r="AG16" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D16,IF($Q$4="C2 Birds in Flight",E16,IF($Q$4="C3 Landscape",F16,IF($Q$4="Default Settings",G16,IF($Q$4="Birds in Flight",H16,IF($Q$4="Birds Perched",I16,IF($Q$4="Fireworks",J16,IF($Q$4="Landscape",K16,IF($Q$4="Macro",L16,IF($Q$4="People",M16,IF($Q$4="Sports",N16,IF($Q$4="Travel",O16,IF($Q$4="Waterdrops",P16,IF($Q$4="Wildlife",Q16,""))))))))))))))</x:f>
-        <x:v>-1</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="12" t="str">
-        <x:v>My Menu &gt; AF Case &gt; Accel./Decel. tracking; AF3 &gt; Servo AF characteristics</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Servo AF; AF3 &gt; Servo AF characteristics</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
         <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Accel./Decel. Tracking</x:v>
+        <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="E17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="F17" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G17" s="17" t="str">
-        <x:v>Auto</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="H17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="I17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="J17" s="17" t="str">
         <x:v>Not Used</x:v>
@@ -2154,33 +2154,33 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M17" s="17" t="str">
-        <x:v>Auto</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="N17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="O17" s="17" t="str">
-        <x:v>Auto</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="P17" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q17" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="R17" s="20" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="S17" s="20" t="n">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="T17" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D17,IF($D$4="C2 Birds in Flight",E17,IF($D$4="C3 Landscape",F17,IF($D$4="Default Settings",G17,IF($D$4="Birds in Flight",H17,IF($D$4="Birds Perched",I17,IF($D$4="Fireworks",J17,IF($D$4="Landscape",K17,IF($D$4="Macro",L17,IF($D$4="People",M17,IF($D$4="Sports",N17,IF($D$4="Travel",O17,IF($D$4="Waterdrops",P17,IF($D$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="U17" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D17,IF($E$4="C2 Birds in Flight",E17,IF($E$4="C3 Landscape",F17,IF($E$4="Default Settings",G17,IF($E$4="Birds in Flight",H17,IF($E$4="Birds Perched",I17,IF($E$4="Fireworks",J17,IF($E$4="Landscape",K17,IF($E$4="Macro",L17,IF($E$4="People",M17,IF($E$4="Sports",N17,IF($E$4="Travel",O17,IF($E$4="Waterdrops",P17,IF($E$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D17,IF($F$4="C2 Birds in Flight",E17,IF($F$4="C3 Landscape",F17,IF($F$4="Default Settings",G17,IF($F$4="Birds in Flight",H17,IF($F$4="Birds Perched",I17,IF($F$4="Fireworks",J17,IF($F$4="Landscape",K17,IF($F$4="Macro",L17,IF($F$4="People",M17,IF($F$4="Sports",N17,IF($F$4="Travel",O17,IF($F$4="Waterdrops",P17,IF($F$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2188,15 +2188,15 @@
       </x:c>
       <x:c r="W17" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D17,IF($G$4="C2 Birds in Flight",E17,IF($G$4="C3 Landscape",F17,IF($G$4="Default Settings",G17,IF($G$4="Birds in Flight",H17,IF($G$4="Birds Perched",I17,IF($G$4="Fireworks",J17,IF($G$4="Landscape",K17,IF($G$4="Macro",L17,IF($G$4="People",M17,IF($G$4="Sports",N17,IF($G$4="Travel",O17,IF($G$4="Waterdrops",P17,IF($G$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="X17" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D17,IF($H$4="C2 Birds in Flight",E17,IF($H$4="C3 Landscape",F17,IF($H$4="Default Settings",G17,IF($H$4="Birds in Flight",H17,IF($H$4="Birds Perched",I17,IF($H$4="Fireworks",J17,IF($H$4="Landscape",K17,IF($H$4="Macro",L17,IF($H$4="People",M17,IF($H$4="Sports",N17,IF($H$4="Travel",O17,IF($H$4="Waterdrops",P17,IF($H$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="Y17" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D17,IF($I$4="C2 Birds in Flight",E17,IF($I$4="C3 Landscape",F17,IF($I$4="Default Settings",G17,IF($I$4="Birds in Flight",H17,IF($I$4="Birds Perched",I17,IF($I$4="Fireworks",J17,IF($I$4="Landscape",K17,IF($I$4="Macro",L17,IF($I$4="People",M17,IF($I$4="Sports",N17,IF($I$4="Travel",O17,IF($I$4="Waterdrops",P17,IF($I$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="Z17" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D17,IF($J$4="C2 Birds in Flight",E17,IF($J$4="C3 Landscape",F17,IF($J$4="Default Settings",G17,IF($J$4="Birds in Flight",H17,IF($J$4="Birds Perched",I17,IF($J$4="Fireworks",J17,IF($J$4="Landscape",K17,IF($J$4="Macro",L17,IF($J$4="People",M17,IF($J$4="Sports",N17,IF($J$4="Travel",O17,IF($J$4="Waterdrops",P17,IF($J$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2212,15 +2212,15 @@
       </x:c>
       <x:c r="AC17" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D17,IF($M$4="C2 Birds in Flight",E17,IF($M$4="C3 Landscape",F17,IF($M$4="Default Settings",G17,IF($M$4="Birds in Flight",H17,IF($M$4="Birds Perched",I17,IF($M$4="Fireworks",J17,IF($M$4="Landscape",K17,IF($M$4="Macro",L17,IF($M$4="People",M17,IF($M$4="Sports",N17,IF($M$4="Travel",O17,IF($M$4="Waterdrops",P17,IF($M$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="AD17" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D17,IF($N$4="C2 Birds in Flight",E17,IF($N$4="C3 Landscape",F17,IF($N$4="Default Settings",G17,IF($N$4="Birds in Flight",H17,IF($N$4="Birds Perched",I17,IF($N$4="Fireworks",J17,IF($N$4="Landscape",K17,IF($N$4="Macro",L17,IF($N$4="People",M17,IF($N$4="Sports",N17,IF($N$4="Travel",O17,IF($N$4="Waterdrops",P17,IF($N$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="AE17" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D17,IF($O$4="C2 Birds in Flight",E17,IF($O$4="C3 Landscape",F17,IF($O$4="Default Settings",G17,IF($O$4="Birds in Flight",H17,IF($O$4="Birds Perched",I17,IF($O$4="Fireworks",J17,IF($O$4="Landscape",K17,IF($O$4="Macro",L17,IF($O$4="People",M17,IF($O$4="Sports",N17,IF($O$4="Travel",O17,IF($O$4="Waterdrops",P17,IF($O$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>Auto</x:v>
+        <x:v>Case A (Auto)</x:v>
       </x:c>
       <x:c r="AF17" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D17,IF($P$4="C2 Birds in Flight",E17,IF($P$4="C3 Landscape",F17,IF($P$4="Default Settings",G17,IF($P$4="Birds in Flight",H17,IF($P$4="Birds Perched",I17,IF($P$4="Fireworks",J17,IF($P$4="Landscape",K17,IF($P$4="Macro",L17,IF($P$4="People",M17,IF($P$4="Sports",N17,IF($P$4="Travel",O17,IF($P$4="Waterdrops",P17,IF($P$4="Wildlife",Q17,""))))))))))))))</x:f>
@@ -2228,36 +2228,36 @@
       </x:c>
       <x:c r="AG17" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D17,IF($Q$4="C2 Birds in Flight",E17,IF($Q$4="C3 Landscape",F17,IF($Q$4="Default Settings",G17,IF($Q$4="Birds in Flight",H17,IF($Q$4="Birds Perched",I17,IF($Q$4="Fireworks",J17,IF($Q$4="Landscape",K17,IF($Q$4="Macro",L17,IF($Q$4="People",M17,IF($Q$4="Sports",N17,IF($Q$4="Travel",O17,IF($Q$4="Waterdrops",P17,IF($Q$4="Wildlife",Q17,""))))))))))))))</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="12" t="str">
-        <x:v>My Menu &gt; AF Case &gt; Switching tracked subjects; AF4 &gt; Switching tracked subjects</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Tracking Sensitivity; AF3 &gt; Servo AF characteristics</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
         <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
-        <x:v>Switching Tracked Subjects</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="str">
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="str">
-        <x:v>On subject</x:v>
+        <x:v>Tracking Sensitivity</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G18" s="17" t="str">
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="H18" s="17" t="str">
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="I18" s="17" t="str">
-        <x:v>On subject</x:v>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="H18" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="J18" s="17" t="str">
         <x:v>Not Used</x:v>
@@ -2269,33 +2269,33 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M18" s="17" t="str">
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="N18" s="17" t="str">
-        <x:v>On subject</x:v>
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="N18" s="17" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="O18" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="P18" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="Q18" s="17" t="str">
-        <x:v>On subject</x:v>
+      <x:c r="Q18" s="17" t="n">
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="R18" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="S18" s="20" t="n">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="T18" s="38" t="str">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="T18" s="38" t="n">
         <x:f>IF($D$4="C1 Wildlife",D18,IF($D$4="C2 Birds in Flight",E18,IF($D$4="C3 Landscape",F18,IF($D$4="Default Settings",G18,IF($D$4="Birds in Flight",H18,IF($D$4="Birds Perched",I18,IF($D$4="Fireworks",J18,IF($D$4="Landscape",K18,IF($D$4="Macro",L18,IF($D$4="People",M18,IF($D$4="Sports",N18,IF($D$4="Travel",O18,IF($D$4="Waterdrops",P18,IF($D$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="U18" s="38" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="U18" s="38" t="n">
         <x:f>IF($E$4="C1 Wildlife",D18,IF($E$4="C2 Birds in Flight",E18,IF($E$4="C3 Landscape",F18,IF($E$4="Default Settings",G18,IF($E$4="Birds in Flight",H18,IF($E$4="Birds Perched",I18,IF($E$4="Fireworks",J18,IF($E$4="Landscape",K18,IF($E$4="Macro",L18,IF($E$4="People",M18,IF($E$4="Sports",N18,IF($E$4="Travel",O18,IF($E$4="Waterdrops",P18,IF($E$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V18" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D18,IF($F$4="C2 Birds in Flight",E18,IF($F$4="C3 Landscape",F18,IF($F$4="Default Settings",G18,IF($F$4="Birds in Flight",H18,IF($F$4="Birds Perched",I18,IF($F$4="Fireworks",J18,IF($F$4="Landscape",K18,IF($F$4="Macro",L18,IF($F$4="People",M18,IF($F$4="Sports",N18,IF($F$4="Travel",O18,IF($F$4="Waterdrops",P18,IF($F$4="Wildlife",Q18,""))))))))))))))</x:f>
@@ -2303,15 +2303,15 @@
       </x:c>
       <x:c r="W18" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D18,IF($G$4="C2 Birds in Flight",E18,IF($G$4="C3 Landscape",F18,IF($G$4="Default Settings",G18,IF($G$4="Birds in Flight",H18,IF($G$4="Birds Perched",I18,IF($G$4="Fireworks",J18,IF($G$4="Landscape",K18,IF($G$4="Macro",L18,IF($G$4="People",M18,IF($G$4="Sports",N18,IF($G$4="Travel",O18,IF($G$4="Waterdrops",P18,IF($G$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="X18" s="38" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="X18" s="38" t="n">
         <x:f>IF($H$4="C1 Wildlife",D18,IF($H$4="C2 Birds in Flight",E18,IF($H$4="C3 Landscape",F18,IF($H$4="Default Settings",G18,IF($H$4="Birds in Flight",H18,IF($H$4="Birds Perched",I18,IF($H$4="Fireworks",J18,IF($H$4="Landscape",K18,IF($H$4="Macro",L18,IF($H$4="People",M18,IF($H$4="Sports",N18,IF($H$4="Travel",O18,IF($H$4="Waterdrops",P18,IF($H$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="Y18" s="38" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y18" s="38" t="n">
         <x:f>IF($I$4="C1 Wildlife",D18,IF($I$4="C2 Birds in Flight",E18,IF($I$4="C3 Landscape",F18,IF($I$4="Default Settings",G18,IF($I$4="Birds in Flight",H18,IF($I$4="Birds Perched",I18,IF($I$4="Fireworks",J18,IF($I$4="Landscape",K18,IF($I$4="Macro",L18,IF($I$4="People",M18,IF($I$4="Sports",N18,IF($I$4="Travel",O18,IF($I$4="Waterdrops",P18,IF($I$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="Z18" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D18,IF($J$4="C2 Birds in Flight",E18,IF($J$4="C3 Landscape",F18,IF($J$4="Default Settings",G18,IF($J$4="Birds in Flight",H18,IF($J$4="Birds Perched",I18,IF($J$4="Fireworks",J18,IF($J$4="Landscape",K18,IF($J$4="Macro",L18,IF($J$4="People",M18,IF($J$4="Sports",N18,IF($J$4="Travel",O18,IF($J$4="Waterdrops",P18,IF($J$4="Wildlife",Q18,""))))))))))))))</x:f>
@@ -2327,106 +2327,106 @@
       </x:c>
       <x:c r="AC18" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D18,IF($M$4="C2 Birds in Flight",E18,IF($M$4="C3 Landscape",F18,IF($M$4="Default Settings",G18,IF($M$4="Birds in Flight",H18,IF($M$4="Birds Perched",I18,IF($M$4="Fireworks",J18,IF($M$4="Landscape",K18,IF($M$4="Macro",L18,IF($M$4="People",M18,IF($M$4="Sports",N18,IF($M$4="Travel",O18,IF($M$4="Waterdrops",P18,IF($M$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="AD18" s="38" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+      <x:c r="AD18" s="38" t="n">
         <x:f>IF($N$4="C1 Wildlife",D18,IF($N$4="C2 Birds in Flight",E18,IF($N$4="C3 Landscape",F18,IF($N$4="Default Settings",G18,IF($N$4="Birds in Flight",H18,IF($N$4="Birds Perched",I18,IF($N$4="Fireworks",J18,IF($N$4="Landscape",K18,IF($N$4="Macro",L18,IF($N$4="People",M18,IF($N$4="Sports",N18,IF($N$4="Travel",O18,IF($N$4="Waterdrops",P18,IF($N$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="AE18" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D18,IF($O$4="C2 Birds in Flight",E18,IF($O$4="C3 Landscape",F18,IF($O$4="Default Settings",G18,IF($O$4="Birds in Flight",H18,IF($O$4="Birds Perched",I18,IF($O$4="Fireworks",J18,IF($O$4="Landscape",K18,IF($O$4="Macro",L18,IF($O$4="People",M18,IF($O$4="Sports",N18,IF($O$4="Travel",O18,IF($O$4="Waterdrops",P18,IF($O$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="AF18" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D18,IF($P$4="C2 Birds in Flight",E18,IF($P$4="C3 Landscape",F18,IF($P$4="Default Settings",G18,IF($P$4="Birds in Flight",H18,IF($P$4="Birds Perched",I18,IF($P$4="Fireworks",J18,IF($P$4="Landscape",K18,IF($P$4="Macro",L18,IF($P$4="People",M18,IF($P$4="Sports",N18,IF($P$4="Travel",O18,IF($P$4="Waterdrops",P18,IF($P$4="Wildlife",Q18,""))))))))))))))</x:f>
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="AG18" s="38" t="str">
+      <x:c r="AG18" s="38" t="n">
         <x:f>IF($Q$4="C1 Wildlife",D18,IF($Q$4="C2 Birds in Flight",E18,IF($Q$4="C3 Landscape",F18,IF($Q$4="Default Settings",G18,IF($Q$4="Birds in Flight",H18,IF($Q$4="Birds Perched",I18,IF($Q$4="Fireworks",J18,IF($Q$4="Landscape",K18,IF($Q$4="Macro",L18,IF($Q$4="People",M18,IF($Q$4="Sports",N18,IF($Q$4="Travel",O18,IF($Q$4="Waterdrops",P18,IF($Q$4="Wildlife",Q18,""))))))))))))))</x:f>
-        <x:v>On subject</x:v>
+        <x:v>-1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="12" t="str">
-        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Accel./Decel. tracking; AF3 &gt; Servo AF characteristics</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>AF Point Selection button + Main Dial</x:v>
+        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="E19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="F19" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="H19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="I19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="J19" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K19" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L19" s="17" t="str">
-        <x:v>Spot AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="N19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="O19" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="P19" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q19" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="R19" s="20" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="S19" s="20" t="n">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="T19" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D19,IF($D$4="C2 Birds in Flight",E19,IF($D$4="C3 Landscape",F19,IF($D$4="Default Settings",G19,IF($D$4="Birds in Flight",H19,IF($D$4="Birds Perched",I19,IF($D$4="Fireworks",J19,IF($D$4="Landscape",K19,IF($D$4="Macro",L19,IF($D$4="People",M19,IF($D$4="Sports",N19,IF($D$4="Travel",O19,IF($D$4="Waterdrops",P19,IF($D$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="U19" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D19,IF($E$4="C2 Birds in Flight",E19,IF($E$4="C3 Landscape",F19,IF($E$4="Default Settings",G19,IF($E$4="Birds in Flight",H19,IF($E$4="Birds Perched",I19,IF($E$4="Fireworks",J19,IF($E$4="Landscape",K19,IF($E$4="Macro",L19,IF($E$4="People",M19,IF($E$4="Sports",N19,IF($E$4="Travel",O19,IF($E$4="Waterdrops",P19,IF($E$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="V19" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D19,IF($F$4="C2 Birds in Flight",E19,IF($F$4="C3 Landscape",F19,IF($F$4="Default Settings",G19,IF($F$4="Birds in Flight",H19,IF($F$4="Birds Perched",I19,IF($F$4="Fireworks",J19,IF($F$4="Landscape",K19,IF($F$4="Macro",L19,IF($F$4="People",M19,IF($F$4="Sports",N19,IF($F$4="Travel",O19,IF($F$4="Waterdrops",P19,IF($F$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W19" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D19,IF($G$4="C2 Birds in Flight",E19,IF($G$4="C3 Landscape",F19,IF($G$4="Default Settings",G19,IF($G$4="Birds in Flight",H19,IF($G$4="Birds Perched",I19,IF($G$4="Fireworks",J19,IF($G$4="Landscape",K19,IF($G$4="Macro",L19,IF($G$4="People",M19,IF($G$4="Sports",N19,IF($G$4="Travel",O19,IF($G$4="Waterdrops",P19,IF($G$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="X19" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D19,IF($H$4="C2 Birds in Flight",E19,IF($H$4="C3 Landscape",F19,IF($H$4="Default Settings",G19,IF($H$4="Birds in Flight",H19,IF($H$4="Birds Perched",I19,IF($H$4="Fireworks",J19,IF($H$4="Landscape",K19,IF($H$4="Macro",L19,IF($H$4="People",M19,IF($H$4="Sports",N19,IF($H$4="Travel",O19,IF($H$4="Waterdrops",P19,IF($H$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="Y19" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D19,IF($I$4="C2 Birds in Flight",E19,IF($I$4="C3 Landscape",F19,IF($I$4="Default Settings",G19,IF($I$4="Birds in Flight",H19,IF($I$4="Birds Perched",I19,IF($I$4="Fireworks",J19,IF($I$4="Landscape",K19,IF($I$4="Macro",L19,IF($I$4="People",M19,IF($I$4="Sports",N19,IF($I$4="Travel",O19,IF($I$4="Waterdrops",P19,IF($I$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="Z19" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D19,IF($J$4="C2 Birds in Flight",E19,IF($J$4="C3 Landscape",F19,IF($J$4="Default Settings",G19,IF($J$4="Birds in Flight",H19,IF($J$4="Birds Perched",I19,IF($J$4="Fireworks",J19,IF($J$4="Landscape",K19,IF($J$4="Macro",L19,IF($J$4="People",M19,IF($J$4="Sports",N19,IF($J$4="Travel",O19,IF($J$4="Waterdrops",P19,IF($J$4="Wildlife",Q19,""))))))))))))))</x:f>
@@ -2434,23 +2434,23 @@
       </x:c>
       <x:c r="AA19" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D19,IF($K$4="C2 Birds in Flight",E19,IF($K$4="C3 Landscape",F19,IF($K$4="Default Settings",G19,IF($K$4="Birds in Flight",H19,IF($K$4="Birds Perched",I19,IF($K$4="Fireworks",J19,IF($K$4="Landscape",K19,IF($K$4="Macro",L19,IF($K$4="People",M19,IF($K$4="Sports",N19,IF($K$4="Travel",O19,IF($K$4="Waterdrops",P19,IF($K$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB19" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D19,IF($L$4="C2 Birds in Flight",E19,IF($L$4="C3 Landscape",F19,IF($L$4="Default Settings",G19,IF($L$4="Birds in Flight",H19,IF($L$4="Birds Perched",I19,IF($L$4="Fireworks",J19,IF($L$4="Landscape",K19,IF($L$4="Macro",L19,IF($L$4="People",M19,IF($L$4="Sports",N19,IF($L$4="Travel",O19,IF($L$4="Waterdrops",P19,IF($L$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Spot AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC19" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D19,IF($M$4="C2 Birds in Flight",E19,IF($M$4="C3 Landscape",F19,IF($M$4="Default Settings",G19,IF($M$4="Birds in Flight",H19,IF($M$4="Birds Perched",I19,IF($M$4="Fireworks",J19,IF($M$4="Landscape",K19,IF($M$4="Macro",L19,IF($M$4="People",M19,IF($M$4="Sports",N19,IF($M$4="Travel",O19,IF($M$4="Waterdrops",P19,IF($M$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="AD19" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D19,IF($N$4="C2 Birds in Flight",E19,IF($N$4="C3 Landscape",F19,IF($N$4="Default Settings",G19,IF($N$4="Birds in Flight",H19,IF($N$4="Birds Perched",I19,IF($N$4="Fireworks",J19,IF($N$4="Landscape",K19,IF($N$4="Macro",L19,IF($N$4="People",M19,IF($N$4="Sports",N19,IF($N$4="Travel",O19,IF($N$4="Waterdrops",P19,IF($N$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="AE19" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D19,IF($O$4="C2 Birds in Flight",E19,IF($O$4="C3 Landscape",F19,IF($O$4="Default Settings",G19,IF($O$4="Birds in Flight",H19,IF($O$4="Birds Perched",I19,IF($O$4="Fireworks",J19,IF($O$4="Landscape",K19,IF($O$4="Macro",L19,IF($O$4="People",M19,IF($O$4="Sports",N19,IF($O$4="Travel",O19,IF($O$4="Waterdrops",P19,IF($O$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Auto</x:v>
       </x:c>
       <x:c r="AF19" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D19,IF($P$4="C2 Birds in Flight",E19,IF($P$4="C3 Landscape",F19,IF($P$4="Default Settings",G19,IF($P$4="Birds in Flight",H19,IF($P$4="Birds Perched",I19,IF($P$4="Fireworks",J19,IF($P$4="Landscape",K19,IF($P$4="Macro",L19,IF($P$4="People",M19,IF($P$4="Sports",N19,IF($P$4="Travel",O19,IF($P$4="Waterdrops",P19,IF($P$4="Wildlife",Q19,""))))))))))))))</x:f>
@@ -2458,90 +2458,90 @@
       </x:c>
       <x:c r="AG19" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D19,IF($Q$4="C2 Birds in Flight",E19,IF($Q$4="C3 Landscape",F19,IF($Q$4="Default Settings",G19,IF($Q$4="Birds in Flight",H19,IF($Q$4="Birds Perched",I19,IF($Q$4="Fireworks",J19,IF($Q$4="Landscape",K19,IF($Q$4="Macro",L19,IF($Q$4="People",M19,IF($Q$4="Sports",N19,IF($Q$4="Travel",O19,IF($Q$4="Waterdrops",P19,IF($Q$4="Wildlife",Q19,""))))))))))))))</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="12" t="str">
-        <x:v>AF1 &gt; Subject to detect</x:v>
+        <x:v>My Menu &gt; AF Case &gt; Switching tracked subjects; AF4 &gt; Switching tracked subjects</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>MM-SWITCH</x:v>
+        <x:v>MM-AF Case; C1-C3 registered profile</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="E20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="F20" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="G20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="H20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="I20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="J20" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K20" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="L20" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="M20" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="N20" s="17" t="str">
-        <x:v>People</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="O20" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="P20" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q20" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="R20" s="20" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="S20" s="20" t="n">
-        <x:v>220</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="T20" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D20,IF($D$4="C2 Birds in Flight",E20,IF($D$4="C3 Landscape",F20,IF($D$4="Default Settings",G20,IF($D$4="Birds in Flight",H20,IF($D$4="Birds Perched",I20,IF($D$4="Fireworks",J20,IF($D$4="Landscape",K20,IF($D$4="Macro",L20,IF($D$4="People",M20,IF($D$4="Sports",N20,IF($D$4="Travel",O20,IF($D$4="Waterdrops",P20,IF($D$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="U20" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D20,IF($E$4="C2 Birds in Flight",E20,IF($E$4="C3 Landscape",F20,IF($E$4="Default Settings",G20,IF($E$4="Birds in Flight",H20,IF($E$4="Birds Perched",I20,IF($E$4="Fireworks",J20,IF($E$4="Landscape",K20,IF($E$4="Macro",L20,IF($E$4="People",M20,IF($E$4="Sports",N20,IF($E$4="Travel",O20,IF($E$4="Waterdrops",P20,IF($E$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="V20" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D20,IF($F$4="C2 Birds in Flight",E20,IF($F$4="C3 Landscape",F20,IF($F$4="Default Settings",G20,IF($F$4="Birds in Flight",H20,IF($F$4="Birds Perched",I20,IF($F$4="Fireworks",J20,IF($F$4="Landscape",K20,IF($F$4="Macro",L20,IF($F$4="People",M20,IF($F$4="Sports",N20,IF($F$4="Travel",O20,IF($F$4="Waterdrops",P20,IF($F$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="W20" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D20,IF($G$4="C2 Birds in Flight",E20,IF($G$4="C3 Landscape",F20,IF($G$4="Default Settings",G20,IF($G$4="Birds in Flight",H20,IF($G$4="Birds Perched",I20,IF($G$4="Fireworks",J20,IF($G$4="Landscape",K20,IF($G$4="Macro",L20,IF($G$4="People",M20,IF($G$4="Sports",N20,IF($G$4="Travel",O20,IF($G$4="Waterdrops",P20,IF($G$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="X20" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D20,IF($H$4="C2 Birds in Flight",E20,IF($H$4="C3 Landscape",F20,IF($H$4="Default Settings",G20,IF($H$4="Birds in Flight",H20,IF($H$4="Birds Perched",I20,IF($H$4="Fireworks",J20,IF($H$4="Landscape",K20,IF($H$4="Macro",L20,IF($H$4="People",M20,IF($H$4="Sports",N20,IF($H$4="Travel",O20,IF($H$4="Waterdrops",P20,IF($H$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="Y20" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D20,IF($I$4="C2 Birds in Flight",E20,IF($I$4="C3 Landscape",F20,IF($I$4="Default Settings",G20,IF($I$4="Birds in Flight",H20,IF($I$4="Birds Perched",I20,IF($I$4="Fireworks",J20,IF($I$4="Landscape",K20,IF($I$4="Macro",L20,IF($I$4="People",M20,IF($I$4="Sports",N20,IF($I$4="Travel",O20,IF($I$4="Waterdrops",P20,IF($I$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="Z20" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D20,IF($J$4="C2 Birds in Flight",E20,IF($J$4="C3 Landscape",F20,IF($J$4="Default Settings",G20,IF($J$4="Birds in Flight",H20,IF($J$4="Birds Perched",I20,IF($J$4="Fireworks",J20,IF($J$4="Landscape",K20,IF($J$4="Macro",L20,IF($J$4="People",M20,IF($J$4="Sports",N20,IF($J$4="Travel",O20,IF($J$4="Waterdrops",P20,IF($J$4="Wildlife",Q20,""))))))))))))))</x:f>
@@ -2549,23 +2549,23 @@
       </x:c>
       <x:c r="AA20" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D20,IF($K$4="C2 Birds in Flight",E20,IF($K$4="C3 Landscape",F20,IF($K$4="Default Settings",G20,IF($K$4="Birds in Flight",H20,IF($K$4="Birds Perched",I20,IF($K$4="Fireworks",J20,IF($K$4="Landscape",K20,IF($K$4="Macro",L20,IF($K$4="People",M20,IF($K$4="Sports",N20,IF($K$4="Travel",O20,IF($K$4="Waterdrops",P20,IF($K$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AB20" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D20,IF($L$4="C2 Birds in Flight",E20,IF($L$4="C3 Landscape",F20,IF($L$4="Default Settings",G20,IF($L$4="Birds in Flight",H20,IF($L$4="Birds Perched",I20,IF($L$4="Fireworks",J20,IF($L$4="Landscape",K20,IF($L$4="Macro",L20,IF($L$4="People",M20,IF($L$4="Sports",N20,IF($L$4="Travel",O20,IF($L$4="Waterdrops",P20,IF($L$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AC20" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D20,IF($M$4="C2 Birds in Flight",E20,IF($M$4="C3 Landscape",F20,IF($M$4="Default Settings",G20,IF($M$4="Birds in Flight",H20,IF($M$4="Birds Perched",I20,IF($M$4="Fireworks",J20,IF($M$4="Landscape",K20,IF($M$4="Macro",L20,IF($M$4="People",M20,IF($M$4="Sports",N20,IF($M$4="Travel",O20,IF($M$4="Waterdrops",P20,IF($M$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="AD20" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D20,IF($N$4="C2 Birds in Flight",E20,IF($N$4="C3 Landscape",F20,IF($N$4="Default Settings",G20,IF($N$4="Birds in Flight",H20,IF($N$4="Birds Perched",I20,IF($N$4="Fireworks",J20,IF($N$4="Landscape",K20,IF($N$4="Macro",L20,IF($N$4="People",M20,IF($N$4="Sports",N20,IF($N$4="Travel",O20,IF($N$4="Waterdrops",P20,IF($N$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>People</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="AE20" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D20,IF($O$4="C2 Birds in Flight",E20,IF($O$4="C3 Landscape",F20,IF($O$4="Default Settings",G20,IF($O$4="Birds in Flight",H20,IF($O$4="Birds Perched",I20,IF($O$4="Fireworks",J20,IF($O$4="Landscape",K20,IF($O$4="Macro",L20,IF($O$4="People",M20,IF($O$4="Sports",N20,IF($O$4="Travel",O20,IF($O$4="Waterdrops",P20,IF($O$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AF20" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D20,IF($P$4="C2 Birds in Flight",E20,IF($P$4="C3 Landscape",F20,IF($P$4="Default Settings",G20,IF($P$4="Birds in Flight",H20,IF($P$4="Birds Perched",I20,IF($P$4="Fireworks",J20,IF($P$4="Landscape",K20,IF($P$4="Macro",L20,IF($P$4="People",M20,IF($P$4="Sports",N20,IF($P$4="Travel",O20,IF($P$4="Waterdrops",P20,IF($P$4="Wildlife",Q20,""))))))))))))))</x:f>
@@ -2573,90 +2573,90 @@
       </x:c>
       <x:c r="AG20" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D20,IF($Q$4="C2 Birds in Flight",E20,IF($Q$4="C3 Landscape",F20,IF($Q$4="Default Settings",G20,IF($Q$4="Birds in Flight",H20,IF($Q$4="Birds Perched",I20,IF($Q$4="Fireworks",J20,IF($Q$4="Landscape",K20,IF($Q$4="Macro",L20,IF($Q$4="People",M20,IF($Q$4="Sports",N20,IF($Q$4="Travel",O20,IF($Q$4="Waterdrops",P20,IF($Q$4="Wildlife",Q20,""))))))))))))))</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="12" t="str">
-        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
+        <x:v>AF1 &gt; AF method; Q is the alternative</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>SET button</x:v>
+        <x:v>AF Point Selection button + Main Dial</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="E21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="F21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="G21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="H21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="I21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="J21" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="L21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="M21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="N21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="O21" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="P21" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q21" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="R21" s="20" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="S21" s="20" t="n">
-        <x:v>150</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="T21" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D21,IF($D$4="C2 Birds in Flight",E21,IF($D$4="C3 Landscape",F21,IF($D$4="Default Settings",G21,IF($D$4="Birds in Flight",H21,IF($D$4="Birds Perched",I21,IF($D$4="Fireworks",J21,IF($D$4="Landscape",K21,IF($D$4="Macro",L21,IF($D$4="People",M21,IF($D$4="Sports",N21,IF($D$4="Travel",O21,IF($D$4="Waterdrops",P21,IF($D$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="U21" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D21,IF($E$4="C2 Birds in Flight",E21,IF($E$4="C3 Landscape",F21,IF($E$4="Default Settings",G21,IF($E$4="Birds in Flight",H21,IF($E$4="Birds Perched",I21,IF($E$4="Fireworks",J21,IF($E$4="Landscape",K21,IF($E$4="Macro",L21,IF($E$4="People",M21,IF($E$4="Sports",N21,IF($E$4="Travel",O21,IF($E$4="Waterdrops",P21,IF($E$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="V21" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D21,IF($F$4="C2 Birds in Flight",E21,IF($F$4="C3 Landscape",F21,IF($F$4="Default Settings",G21,IF($F$4="Birds in Flight",H21,IF($F$4="Birds Perched",I21,IF($F$4="Fireworks",J21,IF($F$4="Landscape",K21,IF($F$4="Macro",L21,IF($F$4="People",M21,IF($F$4="Sports",N21,IF($F$4="Travel",O21,IF($F$4="Waterdrops",P21,IF($F$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="W21" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D21,IF($G$4="C2 Birds in Flight",E21,IF($G$4="C3 Landscape",F21,IF($G$4="Default Settings",G21,IF($G$4="Birds in Flight",H21,IF($G$4="Birds Perched",I21,IF($G$4="Fireworks",J21,IF($G$4="Landscape",K21,IF($G$4="Macro",L21,IF($G$4="People",M21,IF($G$4="Sports",N21,IF($G$4="Travel",O21,IF($G$4="Waterdrops",P21,IF($G$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="X21" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D21,IF($H$4="C2 Birds in Flight",E21,IF($H$4="C3 Landscape",F21,IF($H$4="Default Settings",G21,IF($H$4="Birds in Flight",H21,IF($H$4="Birds Perched",I21,IF($H$4="Fireworks",J21,IF($H$4="Landscape",K21,IF($H$4="Macro",L21,IF($H$4="People",M21,IF($H$4="Sports",N21,IF($H$4="Travel",O21,IF($H$4="Waterdrops",P21,IF($H$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Y21" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D21,IF($I$4="C2 Birds in Flight",E21,IF($I$4="C3 Landscape",F21,IF($I$4="Default Settings",G21,IF($I$4="Birds in Flight",H21,IF($I$4="Birds Perched",I21,IF($I$4="Fireworks",J21,IF($I$4="Landscape",K21,IF($I$4="Macro",L21,IF($I$4="People",M21,IF($I$4="Sports",N21,IF($I$4="Travel",O21,IF($I$4="Waterdrops",P21,IF($I$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="Z21" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D21,IF($J$4="C2 Birds in Flight",E21,IF($J$4="C3 Landscape",F21,IF($J$4="Default Settings",G21,IF($J$4="Birds in Flight",H21,IF($J$4="Birds Perched",I21,IF($J$4="Fireworks",J21,IF($J$4="Landscape",K21,IF($J$4="Macro",L21,IF($J$4="People",M21,IF($J$4="Sports",N21,IF($J$4="Travel",O21,IF($J$4="Waterdrops",P21,IF($J$4="Wildlife",Q21,""))))))))))))))</x:f>
@@ -2664,23 +2664,23 @@
       </x:c>
       <x:c r="AA21" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D21,IF($K$4="C2 Birds in Flight",E21,IF($K$4="C3 Landscape",F21,IF($K$4="Default Settings",G21,IF($K$4="Birds in Flight",H21,IF($K$4="Birds Perched",I21,IF($K$4="Fireworks",J21,IF($K$4="Landscape",K21,IF($K$4="Macro",L21,IF($K$4="People",M21,IF($K$4="Sports",N21,IF($K$4="Travel",O21,IF($K$4="Waterdrops",P21,IF($K$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="AB21" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D21,IF($L$4="C2 Birds in Flight",E21,IF($L$4="C3 Landscape",F21,IF($L$4="Default Settings",G21,IF($L$4="Birds in Flight",H21,IF($L$4="Birds Perched",I21,IF($L$4="Fireworks",J21,IF($L$4="Landscape",K21,IF($L$4="Macro",L21,IF($L$4="People",M21,IF($L$4="Sports",N21,IF($L$4="Travel",O21,IF($L$4="Waterdrops",P21,IF($L$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Spot AF</x:v>
       </x:c>
       <x:c r="AC21" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D21,IF($M$4="C2 Birds in Flight",E21,IF($M$4="C3 Landscape",F21,IF($M$4="Default Settings",G21,IF($M$4="Birds in Flight",H21,IF($M$4="Birds Perched",I21,IF($M$4="Fireworks",J21,IF($M$4="Landscape",K21,IF($M$4="Macro",L21,IF($M$4="People",M21,IF($M$4="Sports",N21,IF($M$4="Travel",O21,IF($M$4="Waterdrops",P21,IF($M$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="AD21" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D21,IF($N$4="C2 Birds in Flight",E21,IF($N$4="C3 Landscape",F21,IF($N$4="Default Settings",G21,IF($N$4="Birds in Flight",H21,IF($N$4="Birds Perched",I21,IF($N$4="Fireworks",J21,IF($N$4="Landscape",K21,IF($N$4="Macro",L21,IF($N$4="People",M21,IF($N$4="Sports",N21,IF($N$4="Travel",O21,IF($N$4="Waterdrops",P21,IF($N$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="AE21" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D21,IF($O$4="C2 Birds in Flight",E21,IF($O$4="C3 Landscape",F21,IF($O$4="Default Settings",G21,IF($O$4="Birds in Flight",H21,IF($O$4="Birds Perched",I21,IF($O$4="Fireworks",J21,IF($O$4="Landscape",K21,IF($O$4="Macro",L21,IF($O$4="People",M21,IF($O$4="Sports",N21,IF($O$4="Travel",O21,IF($O$4="Waterdrops",P21,IF($O$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="AF21" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D21,IF($P$4="C2 Birds in Flight",E21,IF($P$4="C3 Landscape",F21,IF($P$4="Default Settings",G21,IF($P$4="Birds in Flight",H21,IF($P$4="Birds Perched",I21,IF($P$4="Fireworks",J21,IF($P$4="Landscape",K21,IF($P$4="Macro",L21,IF($P$4="People",M21,IF($P$4="Sports",N21,IF($P$4="Travel",O21,IF($P$4="Waterdrops",P21,IF($P$4="Wildlife",Q21,""))))))))))))))</x:f>
@@ -2688,148 +2688,148 @@
       </x:c>
       <x:c r="AG21" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D21,IF($Q$4="C2 Birds in Flight",E21,IF($Q$4="C3 Landscape",F21,IF($Q$4="Default Settings",G21,IF($Q$4="Birds in Flight",H21,IF($Q$4="Birds Perched",I21,IF($Q$4="Fireworks",J21,IF($Q$4="Landscape",K21,IF($Q$4="Macro",L21,IF($Q$4="People",M21,IF($Q$4="Sports",N21,IF($Q$4="Travel",O21,IF($Q$4="Waterdrops",P21,IF($Q$4="Wildlife",Q21,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
     </x:row>
     <x:row r="22" hidden="0">
       <x:c r="A22" s="12" t="str">
-        <x:v>Shooting menu &gt; Drive mode</x:v>
+        <x:v>AF1 &gt; Subject to detect</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Q screen</x:v>
+        <x:v>MM-SWITCH</x:v>
       </x:c>
       <x:c r="C22" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="D22" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="E22" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="F22" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="G22" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="H22" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="I22" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="J22" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K22" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="L22" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="M22" s="17" t="str">
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="N22" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="O22" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="P22" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="Q22" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="R22" s="20" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="S22" s="20" t="n">
-        <x:v>160</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="T22" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D22,IF($D$4="C2 Birds in Flight",E22,IF($D$4="C3 Landscape",F22,IF($D$4="Default Settings",G22,IF($D$4="Birds in Flight",H22,IF($D$4="Birds Perched",I22,IF($D$4="Fireworks",J22,IF($D$4="Landscape",K22,IF($D$4="Macro",L22,IF($D$4="People",M22,IF($D$4="Sports",N22,IF($D$4="Travel",O22,IF($D$4="Waterdrops",P22,IF($D$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="U22" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D22,IF($E$4="C2 Birds in Flight",E22,IF($E$4="C3 Landscape",F22,IF($E$4="Default Settings",G22,IF($E$4="Birds in Flight",H22,IF($E$4="Birds Perched",I22,IF($E$4="Fireworks",J22,IF($E$4="Landscape",K22,IF($E$4="Macro",L22,IF($E$4="People",M22,IF($E$4="Sports",N22,IF($E$4="Travel",O22,IF($E$4="Waterdrops",P22,IF($E$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="V22" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D22,IF($F$4="C2 Birds in Flight",E22,IF($F$4="C3 Landscape",F22,IF($F$4="Default Settings",G22,IF($F$4="Birds in Flight",H22,IF($F$4="Birds Perched",I22,IF($F$4="Fireworks",J22,IF($F$4="Landscape",K22,IF($F$4="Macro",L22,IF($F$4="People",M22,IF($F$4="Sports",N22,IF($F$4="Travel",O22,IF($F$4="Waterdrops",P22,IF($F$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="W22" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D22,IF($G$4="C2 Birds in Flight",E22,IF($G$4="C3 Landscape",F22,IF($G$4="Default Settings",G22,IF($G$4="Birds in Flight",H22,IF($G$4="Birds Perched",I22,IF($G$4="Fireworks",J22,IF($G$4="Landscape",K22,IF($G$4="Macro",L22,IF($G$4="People",M22,IF($G$4="Sports",N22,IF($G$4="Travel",O22,IF($G$4="Waterdrops",P22,IF($G$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="X22" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D22,IF($H$4="C2 Birds in Flight",E22,IF($H$4="C3 Landscape",F22,IF($H$4="Default Settings",G22,IF($H$4="Birds in Flight",H22,IF($H$4="Birds Perched",I22,IF($H$4="Fireworks",J22,IF($H$4="Landscape",K22,IF($H$4="Macro",L22,IF($H$4="People",M22,IF($H$4="Sports",N22,IF($H$4="Travel",O22,IF($H$4="Waterdrops",P22,IF($H$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Y22" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D22,IF($I$4="C2 Birds in Flight",E22,IF($I$4="C3 Landscape",F22,IF($I$4="Default Settings",G22,IF($I$4="Birds in Flight",H22,IF($I$4="Birds Perched",I22,IF($I$4="Fireworks",J22,IF($I$4="Landscape",K22,IF($I$4="Macro",L22,IF($I$4="People",M22,IF($I$4="Sports",N22,IF($I$4="Travel",O22,IF($I$4="Waterdrops",P22,IF($I$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="Z22" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D22,IF($J$4="C2 Birds in Flight",E22,IF($J$4="C3 Landscape",F22,IF($J$4="Default Settings",G22,IF($J$4="Birds in Flight",H22,IF($J$4="Birds Perched",I22,IF($J$4="Fireworks",J22,IF($J$4="Landscape",K22,IF($J$4="Macro",L22,IF($J$4="People",M22,IF($J$4="Sports",N22,IF($J$4="Travel",O22,IF($J$4="Waterdrops",P22,IF($J$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AA22" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D22,IF($K$4="C2 Birds in Flight",E22,IF($K$4="C3 Landscape",F22,IF($K$4="Default Settings",G22,IF($K$4="Birds in Flight",H22,IF($K$4="Birds Perched",I22,IF($K$4="Fireworks",J22,IF($K$4="Landscape",K22,IF($K$4="Macro",L22,IF($K$4="People",M22,IF($K$4="Sports",N22,IF($K$4="Travel",O22,IF($K$4="Waterdrops",P22,IF($K$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AB22" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D22,IF($L$4="C2 Birds in Flight",E22,IF($L$4="C3 Landscape",F22,IF($L$4="Default Settings",G22,IF($L$4="Birds in Flight",H22,IF($L$4="Birds Perched",I22,IF($L$4="Fireworks",J22,IF($L$4="Landscape",K22,IF($L$4="Macro",L22,IF($L$4="People",M22,IF($L$4="Sports",N22,IF($L$4="Travel",O22,IF($L$4="Waterdrops",P22,IF($L$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AC22" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D22,IF($M$4="C2 Birds in Flight",E22,IF($M$4="C3 Landscape",F22,IF($M$4="Default Settings",G22,IF($M$4="Birds in Flight",H22,IF($M$4="Birds Perched",I22,IF($M$4="Fireworks",J22,IF($M$4="Landscape",K22,IF($M$4="Macro",L22,IF($M$4="People",M22,IF($M$4="Sports",N22,IF($M$4="Travel",O22,IF($M$4="Waterdrops",P22,IF($M$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Low Speed Continuous</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="AD22" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D22,IF($N$4="C2 Birds in Flight",E22,IF($N$4="C3 Landscape",F22,IF($N$4="Default Settings",G22,IF($N$4="Birds in Flight",H22,IF($N$4="Birds Perched",I22,IF($N$4="Fireworks",J22,IF($N$4="Landscape",K22,IF($N$4="Macro",L22,IF($N$4="People",M22,IF($N$4="Sports",N22,IF($N$4="Travel",O22,IF($N$4="Waterdrops",P22,IF($N$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>People</x:v>
       </x:c>
       <x:c r="AE22" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D22,IF($O$4="C2 Birds in Flight",E22,IF($O$4="C3 Landscape",F22,IF($O$4="Default Settings",G22,IF($O$4="Birds in Flight",H22,IF($O$4="Birds Perched",I22,IF($O$4="Fireworks",J22,IF($O$4="Landscape",K22,IF($O$4="Macro",L22,IF($O$4="People",M22,IF($O$4="Sports",N22,IF($O$4="Travel",O22,IF($O$4="Waterdrops",P22,IF($O$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="AF22" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D22,IF($P$4="C2 Birds in Flight",E22,IF($P$4="C3 Landscape",F22,IF($P$4="Default Settings",G22,IF($P$4="Birds in Flight",H22,IF($P$4="Birds Perched",I22,IF($P$4="Fireworks",J22,IF($P$4="Landscape",K22,IF($P$4="Macro",L22,IF($P$4="People",M22,IF($P$4="Sports",N22,IF($P$4="Travel",O22,IF($P$4="Waterdrops",P22,IF($P$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="AG22" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D22,IF($Q$4="C2 Birds in Flight",E22,IF($Q$4="C3 Landscape",F22,IF($Q$4="Default Settings",G22,IF($Q$4="Birds in Flight",H22,IF($Q$4="Birds Perched",I22,IF($Q$4="Fireworks",J22,IF($Q$4="Landscape",K22,IF($Q$4="Macro",L22,IF($Q$4="People",M22,IF($Q$4="Sports",N22,IF($Q$4="Travel",O22,IF($Q$4="Waterdrops",P22,IF($Q$4="Wildlife",Q22,""))))))))))))))</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
     </x:row>
     <x:row r="23" hidden="0">
       <x:c r="A23" s="12" t="str">
-        <x:v>Shooting 7 &gt; High speed display</x:v>
+        <x:v>AF1 &gt; Eye detection; shortcut works with a compatible AF method</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>Set once; C1-C3 registered profile</x:v>
+        <x:v>SET button</x:v>
       </x:c>
       <x:c r="C23" s="15" t="str">
-        <x:v>High Speed Display</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="D23" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="E23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="F23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="G23" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="H23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="I23" s="17" t="str">
         <x:v>Enable</x:v>
@@ -2838,19 +2838,19 @@
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="K23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="L23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="M23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="N23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="O23" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="P23" s="17" t="str">
         <x:v>Not Used</x:v>
@@ -2862,7 +2862,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="S23" s="20" t="n">
-        <x:v>165</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="T23" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D23,IF($D$4="C2 Birds in Flight",E23,IF($D$4="C3 Landscape",F23,IF($D$4="Default Settings",G23,IF($D$4="Birds in Flight",H23,IF($D$4="Birds Perched",I23,IF($D$4="Fireworks",J23,IF($D$4="Landscape",K23,IF($D$4="Macro",L23,IF($D$4="People",M23,IF($D$4="Sports",N23,IF($D$4="Travel",O23,IF($D$4="Waterdrops",P23,IF($D$4="Wildlife",Q23,""))))))))))))))</x:f>
@@ -2870,11 +2870,11 @@
       </x:c>
       <x:c r="U23" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D23,IF($E$4="C2 Birds in Flight",E23,IF($E$4="C3 Landscape",F23,IF($E$4="Default Settings",G23,IF($E$4="Birds in Flight",H23,IF($E$4="Birds Perched",I23,IF($E$4="Fireworks",J23,IF($E$4="Landscape",K23,IF($E$4="Macro",L23,IF($E$4="People",M23,IF($E$4="Sports",N23,IF($E$4="Travel",O23,IF($E$4="Waterdrops",P23,IF($E$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V23" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D23,IF($F$4="C2 Birds in Flight",E23,IF($F$4="C3 Landscape",F23,IF($F$4="Default Settings",G23,IF($F$4="Birds in Flight",H23,IF($F$4="Birds Perched",I23,IF($F$4="Fireworks",J23,IF($F$4="Landscape",K23,IF($F$4="Macro",L23,IF($F$4="People",M23,IF($F$4="Sports",N23,IF($F$4="Travel",O23,IF($F$4="Waterdrops",P23,IF($F$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="W23" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D23,IF($G$4="C2 Birds in Flight",E23,IF($G$4="C3 Landscape",F23,IF($G$4="Default Settings",G23,IF($G$4="Birds in Flight",H23,IF($G$4="Birds Perched",I23,IF($G$4="Fireworks",J23,IF($G$4="Landscape",K23,IF($G$4="Macro",L23,IF($G$4="People",M23,IF($G$4="Sports",N23,IF($G$4="Travel",O23,IF($G$4="Waterdrops",P23,IF($G$4="Wildlife",Q23,""))))))))))))))</x:f>
@@ -2882,7 +2882,7 @@
       </x:c>
       <x:c r="X23" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D23,IF($H$4="C2 Birds in Flight",E23,IF($H$4="C3 Landscape",F23,IF($H$4="Default Settings",G23,IF($H$4="Birds in Flight",H23,IF($H$4="Birds Perched",I23,IF($H$4="Fireworks",J23,IF($H$4="Landscape",K23,IF($H$4="Macro",L23,IF($H$4="People",M23,IF($H$4="Sports",N23,IF($H$4="Travel",O23,IF($H$4="Waterdrops",P23,IF($H$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Y23" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D23,IF($I$4="C2 Birds in Flight",E23,IF($I$4="C3 Landscape",F23,IF($I$4="Default Settings",G23,IF($I$4="Birds in Flight",H23,IF($I$4="Birds Perched",I23,IF($I$4="Fireworks",J23,IF($I$4="Landscape",K23,IF($I$4="Macro",L23,IF($I$4="People",M23,IF($I$4="Sports",N23,IF($I$4="Travel",O23,IF($I$4="Waterdrops",P23,IF($I$4="Wildlife",Q23,""))))))))))))))</x:f>
@@ -2894,23 +2894,23 @@
       </x:c>
       <x:c r="AA23" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D23,IF($K$4="C2 Birds in Flight",E23,IF($K$4="C3 Landscape",F23,IF($K$4="Default Settings",G23,IF($K$4="Birds in Flight",H23,IF($K$4="Birds Perched",I23,IF($K$4="Fireworks",J23,IF($K$4="Landscape",K23,IF($K$4="Macro",L23,IF($K$4="People",M23,IF($K$4="Sports",N23,IF($K$4="Travel",O23,IF($K$4="Waterdrops",P23,IF($K$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AB23" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D23,IF($L$4="C2 Birds in Flight",E23,IF($L$4="C3 Landscape",F23,IF($L$4="Default Settings",G23,IF($L$4="Birds in Flight",H23,IF($L$4="Birds Perched",I23,IF($L$4="Fireworks",J23,IF($L$4="Landscape",K23,IF($L$4="Macro",L23,IF($L$4="People",M23,IF($L$4="Sports",N23,IF($L$4="Travel",O23,IF($L$4="Waterdrops",P23,IF($L$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AC23" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D23,IF($M$4="C2 Birds in Flight",E23,IF($M$4="C3 Landscape",F23,IF($M$4="Default Settings",G23,IF($M$4="Birds in Flight",H23,IF($M$4="Birds Perched",I23,IF($M$4="Fireworks",J23,IF($M$4="Landscape",K23,IF($M$4="Macro",L23,IF($M$4="People",M23,IF($M$4="Sports",N23,IF($M$4="Travel",O23,IF($M$4="Waterdrops",P23,IF($M$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AD23" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D23,IF($N$4="C2 Birds in Flight",E23,IF($N$4="C3 Landscape",F23,IF($N$4="Default Settings",G23,IF($N$4="Birds in Flight",H23,IF($N$4="Birds Perched",I23,IF($N$4="Fireworks",J23,IF($N$4="Landscape",K23,IF($N$4="Macro",L23,IF($N$4="People",M23,IF($N$4="Sports",N23,IF($N$4="Travel",O23,IF($N$4="Waterdrops",P23,IF($N$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AE23" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D23,IF($O$4="C2 Birds in Flight",E23,IF($O$4="C3 Landscape",F23,IF($O$4="Default Settings",G23,IF($O$4="Birds in Flight",H23,IF($O$4="Birds Perched",I23,IF($O$4="Fireworks",J23,IF($O$4="Landscape",K23,IF($O$4="Macro",L23,IF($O$4="People",M23,IF($O$4="Sports",N23,IF($O$4="Travel",O23,IF($O$4="Waterdrops",P23,IF($O$4="Wildlife",Q23,""))))))))))))))</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="AF23" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D23,IF($P$4="C2 Birds in Flight",E23,IF($P$4="C3 Landscape",F23,IF($P$4="Default Settings",G23,IF($P$4="Birds in Flight",H23,IF($P$4="Birds Perched",I23,IF($P$4="Fireworks",J23,IF($P$4="Landscape",K23,IF($P$4="Macro",L23,IF($P$4="People",M23,IF($P$4="Sports",N23,IF($P$4="Travel",O23,IF($P$4="Waterdrops",P23,IF($P$4="Wildlife",Q23,""))))))))))))))</x:f>
@@ -2923,421 +2923,2721 @@
     </x:row>
     <x:row r="24" hidden="0">
       <x:c r="A24" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
+        <x:v>AF1 &gt; Touch &amp; drag AF settings &gt; Touch &amp; drag AF</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
+        <x:v>Set once</x:v>
       </x:c>
       <x:c r="C24" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Touch &amp; Drag AF</x:v>
       </x:c>
       <x:c r="D24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="E24" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="F24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="G24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="H24" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="I24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="J24" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="K24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="L24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="M24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="N24" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="O24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="P24" s="17" t="str">
-        <x:v>Off</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Q24" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="R24" s="20" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="S24" s="20" t="n">
-        <x:v>230</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="T24" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D24,IF($D$4="C2 Birds in Flight",E24,IF($D$4="C3 Landscape",F24,IF($D$4="Default Settings",G24,IF($D$4="Birds in Flight",H24,IF($D$4="Birds Perched",I24,IF($D$4="Fireworks",J24,IF($D$4="Landscape",K24,IF($D$4="Macro",L24,IF($D$4="People",M24,IF($D$4="Sports",N24,IF($D$4="Travel",O24,IF($D$4="Waterdrops",P24,IF($D$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="U24" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D24,IF($E$4="C2 Birds in Flight",E24,IF($E$4="C3 Landscape",F24,IF($E$4="Default Settings",G24,IF($E$4="Birds in Flight",H24,IF($E$4="Birds Perched",I24,IF($E$4="Fireworks",J24,IF($E$4="Landscape",K24,IF($E$4="Macro",L24,IF($E$4="People",M24,IF($E$4="Sports",N24,IF($E$4="Travel",O24,IF($E$4="Waterdrops",P24,IF($E$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V24" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D24,IF($F$4="C2 Birds in Flight",E24,IF($F$4="C3 Landscape",F24,IF($F$4="Default Settings",G24,IF($F$4="Birds in Flight",H24,IF($F$4="Birds Perched",I24,IF($F$4="Fireworks",J24,IF($F$4="Landscape",K24,IF($F$4="Macro",L24,IF($F$4="People",M24,IF($F$4="Sports",N24,IF($F$4="Travel",O24,IF($F$4="Waterdrops",P24,IF($F$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="W24" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D24,IF($G$4="C2 Birds in Flight",E24,IF($G$4="C3 Landscape",F24,IF($G$4="Default Settings",G24,IF($G$4="Birds in Flight",H24,IF($G$4="Birds Perched",I24,IF($G$4="Fireworks",J24,IF($G$4="Landscape",K24,IF($G$4="Macro",L24,IF($G$4="People",M24,IF($G$4="Sports",N24,IF($G$4="Travel",O24,IF($G$4="Waterdrops",P24,IF($G$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="X24" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D24,IF($H$4="C2 Birds in Flight",E24,IF($H$4="C3 Landscape",F24,IF($H$4="Default Settings",G24,IF($H$4="Birds in Flight",H24,IF($H$4="Birds Perched",I24,IF($H$4="Fireworks",J24,IF($H$4="Landscape",K24,IF($H$4="Macro",L24,IF($H$4="People",M24,IF($H$4="Sports",N24,IF($H$4="Travel",O24,IF($H$4="Waterdrops",P24,IF($H$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Y24" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D24,IF($I$4="C2 Birds in Flight",E24,IF($I$4="C3 Landscape",F24,IF($I$4="Default Settings",G24,IF($I$4="Birds in Flight",H24,IF($I$4="Birds Perched",I24,IF($I$4="Fireworks",J24,IF($I$4="Landscape",K24,IF($I$4="Macro",L24,IF($I$4="People",M24,IF($I$4="Sports",N24,IF($I$4="Travel",O24,IF($I$4="Waterdrops",P24,IF($I$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="Z24" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D24,IF($J$4="C2 Birds in Flight",E24,IF($J$4="C3 Landscape",F24,IF($J$4="Default Settings",G24,IF($J$4="Birds in Flight",H24,IF($J$4="Birds Perched",I24,IF($J$4="Fireworks",J24,IF($J$4="Landscape",K24,IF($J$4="Macro",L24,IF($J$4="People",M24,IF($J$4="Sports",N24,IF($J$4="Travel",O24,IF($J$4="Waterdrops",P24,IF($J$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Off</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AA24" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D24,IF($K$4="C2 Birds in Flight",E24,IF($K$4="C3 Landscape",F24,IF($K$4="Default Settings",G24,IF($K$4="Birds in Flight",H24,IF($K$4="Birds Perched",I24,IF($K$4="Fireworks",J24,IF($K$4="Landscape",K24,IF($K$4="Macro",L24,IF($K$4="People",M24,IF($K$4="Sports",N24,IF($K$4="Travel",O24,IF($K$4="Waterdrops",P24,IF($K$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AB24" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D24,IF($L$4="C2 Birds in Flight",E24,IF($L$4="C3 Landscape",F24,IF($L$4="Default Settings",G24,IF($L$4="Birds in Flight",H24,IF($L$4="Birds Perched",I24,IF($L$4="Fireworks",J24,IF($L$4="Landscape",K24,IF($L$4="Macro",L24,IF($L$4="People",M24,IF($L$4="Sports",N24,IF($L$4="Travel",O24,IF($L$4="Waterdrops",P24,IF($L$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AC24" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D24,IF($M$4="C2 Birds in Flight",E24,IF($M$4="C3 Landscape",F24,IF($M$4="Default Settings",G24,IF($M$4="Birds in Flight",H24,IF($M$4="Birds Perched",I24,IF($M$4="Fireworks",J24,IF($M$4="Landscape",K24,IF($M$4="Macro",L24,IF($M$4="People",M24,IF($M$4="Sports",N24,IF($M$4="Travel",O24,IF($M$4="Waterdrops",P24,IF($M$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AD24" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D24,IF($N$4="C2 Birds in Flight",E24,IF($N$4="C3 Landscape",F24,IF($N$4="Default Settings",G24,IF($N$4="Birds in Flight",H24,IF($N$4="Birds Perched",I24,IF($N$4="Fireworks",J24,IF($N$4="Landscape",K24,IF($N$4="Macro",L24,IF($N$4="People",M24,IF($N$4="Sports",N24,IF($N$4="Travel",O24,IF($N$4="Waterdrops",P24,IF($N$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AE24" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D24,IF($O$4="C2 Birds in Flight",E24,IF($O$4="C3 Landscape",F24,IF($O$4="Default Settings",G24,IF($O$4="Birds in Flight",H24,IF($O$4="Birds Perched",I24,IF($O$4="Fireworks",J24,IF($O$4="Landscape",K24,IF($O$4="Macro",L24,IF($O$4="People",M24,IF($O$4="Sports",N24,IF($O$4="Travel",O24,IF($O$4="Waterdrops",P24,IF($O$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AF24" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D24,IF($P$4="C2 Birds in Flight",E24,IF($P$4="C3 Landscape",F24,IF($P$4="Default Settings",G24,IF($P$4="Birds in Flight",H24,IF($P$4="Birds Perched",I24,IF($P$4="Fireworks",J24,IF($P$4="Landscape",K24,IF($P$4="Macro",L24,IF($P$4="People",M24,IF($P$4="Sports",N24,IF($P$4="Travel",O24,IF($P$4="Waterdrops",P24,IF($P$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Off</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="AG24" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D24,IF($Q$4="C2 Birds in Flight",E24,IF($Q$4="C3 Landscape",F24,IF($Q$4="Default Settings",G24,IF($Q$4="Birds in Flight",H24,IF($Q$4="Birds Perched",I24,IF($Q$4="Fireworks",J24,IF($Q$4="Landscape",K24,IF($Q$4="Macro",L24,IF($Q$4="People",M24,IF($Q$4="Sports",N24,IF($Q$4="Travel",O24,IF($Q$4="Waterdrops",P24,IF($Q$4="Wildlife",Q24,""))))))))))))))</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="25" hidden="0">
       <x:c r="A25" s="12" t="str">
-        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+        <x:v>AF1 &gt; Touch &amp; drag AF settings &gt; Positioning method</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>Lens IS switch; camera IS menu when available</x:v>
+        <x:v>Set once</x:v>
       </x:c>
       <x:c r="C25" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Positioning method</x:v>
       </x:c>
       <x:c r="D25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="E25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="F25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="G25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="H25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="I25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="J25" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="K25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="L25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="M25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="N25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="O25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="P25" s="17" t="str">
-        <x:v>Off / Off</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="Q25" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="R25" s="20" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="S25" s="20" t="n">
-        <x:v>40</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="T25" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D25,IF($D$4="C2 Birds in Flight",E25,IF($D$4="C3 Landscape",F25,IF($D$4="Default Settings",G25,IF($D$4="Birds in Flight",H25,IF($D$4="Birds Perched",I25,IF($D$4="Fireworks",J25,IF($D$4="Landscape",K25,IF($D$4="Macro",L25,IF($D$4="People",M25,IF($D$4="Sports",N25,IF($D$4="Travel",O25,IF($D$4="Waterdrops",P25,IF($D$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="U25" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D25,IF($E$4="C2 Birds in Flight",E25,IF($E$4="C3 Landscape",F25,IF($E$4="Default Settings",G25,IF($E$4="Birds in Flight",H25,IF($E$4="Birds Perched",I25,IF($E$4="Fireworks",J25,IF($E$4="Landscape",K25,IF($E$4="Macro",L25,IF($E$4="People",M25,IF($E$4="Sports",N25,IF($E$4="Travel",O25,IF($E$4="Waterdrops",P25,IF($E$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="V25" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D25,IF($F$4="C2 Birds in Flight",E25,IF($F$4="C3 Landscape",F25,IF($F$4="Default Settings",G25,IF($F$4="Birds in Flight",H25,IF($F$4="Birds Perched",I25,IF($F$4="Fireworks",J25,IF($F$4="Landscape",K25,IF($F$4="Macro",L25,IF($F$4="People",M25,IF($F$4="Sports",N25,IF($F$4="Travel",O25,IF($F$4="Waterdrops",P25,IF($F$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="W25" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D25,IF($G$4="C2 Birds in Flight",E25,IF($G$4="C3 Landscape",F25,IF($G$4="Default Settings",G25,IF($G$4="Birds in Flight",H25,IF($G$4="Birds Perched",I25,IF($G$4="Fireworks",J25,IF($G$4="Landscape",K25,IF($G$4="Macro",L25,IF($G$4="People",M25,IF($G$4="Sports",N25,IF($G$4="Travel",O25,IF($G$4="Waterdrops",P25,IF($G$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="X25" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D25,IF($H$4="C2 Birds in Flight",E25,IF($H$4="C3 Landscape",F25,IF($H$4="Default Settings",G25,IF($H$4="Birds in Flight",H25,IF($H$4="Birds Perched",I25,IF($H$4="Fireworks",J25,IF($H$4="Landscape",K25,IF($H$4="Macro",L25,IF($H$4="People",M25,IF($H$4="Sports",N25,IF($H$4="Travel",O25,IF($H$4="Waterdrops",P25,IF($H$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="Y25" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D25,IF($I$4="C2 Birds in Flight",E25,IF($I$4="C3 Landscape",F25,IF($I$4="Default Settings",G25,IF($I$4="Birds in Flight",H25,IF($I$4="Birds Perched",I25,IF($I$4="Fireworks",J25,IF($I$4="Landscape",K25,IF($I$4="Macro",L25,IF($I$4="People",M25,IF($I$4="Sports",N25,IF($I$4="Travel",O25,IF($I$4="Waterdrops",P25,IF($I$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="Z25" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D25,IF($J$4="C2 Birds in Flight",E25,IF($J$4="C3 Landscape",F25,IF($J$4="Default Settings",G25,IF($J$4="Birds in Flight",H25,IF($J$4="Birds Perched",I25,IF($J$4="Fireworks",J25,IF($J$4="Landscape",K25,IF($J$4="Macro",L25,IF($J$4="People",M25,IF($J$4="Sports",N25,IF($J$4="Travel",O25,IF($J$4="Waterdrops",P25,IF($J$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AA25" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D25,IF($K$4="C2 Birds in Flight",E25,IF($K$4="C3 Landscape",F25,IF($K$4="Default Settings",G25,IF($K$4="Birds in Flight",H25,IF($K$4="Birds Perched",I25,IF($K$4="Fireworks",J25,IF($K$4="Landscape",K25,IF($K$4="Macro",L25,IF($K$4="People",M25,IF($K$4="Sports",N25,IF($K$4="Travel",O25,IF($K$4="Waterdrops",P25,IF($K$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AB25" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D25,IF($L$4="C2 Birds in Flight",E25,IF($L$4="C3 Landscape",F25,IF($L$4="Default Settings",G25,IF($L$4="Birds in Flight",H25,IF($L$4="Birds Perched",I25,IF($L$4="Fireworks",J25,IF($L$4="Landscape",K25,IF($L$4="Macro",L25,IF($L$4="People",M25,IF($L$4="Sports",N25,IF($L$4="Travel",O25,IF($L$4="Waterdrops",P25,IF($L$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AC25" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D25,IF($M$4="C2 Birds in Flight",E25,IF($M$4="C3 Landscape",F25,IF($M$4="Default Settings",G25,IF($M$4="Birds in Flight",H25,IF($M$4="Birds Perched",I25,IF($M$4="Fireworks",J25,IF($M$4="Landscape",K25,IF($M$4="Macro",L25,IF($M$4="People",M25,IF($M$4="Sports",N25,IF($M$4="Travel",O25,IF($M$4="Waterdrops",P25,IF($M$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AD25" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D25,IF($N$4="C2 Birds in Flight",E25,IF($N$4="C3 Landscape",F25,IF($N$4="Default Settings",G25,IF($N$4="Birds in Flight",H25,IF($N$4="Birds Perched",I25,IF($N$4="Fireworks",J25,IF($N$4="Landscape",K25,IF($N$4="Macro",L25,IF($N$4="People",M25,IF($N$4="Sports",N25,IF($N$4="Travel",O25,IF($N$4="Waterdrops",P25,IF($N$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AE25" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D25,IF($O$4="C2 Birds in Flight",E25,IF($O$4="C3 Landscape",F25,IF($O$4="Default Settings",G25,IF($O$4="Birds in Flight",H25,IF($O$4="Birds Perched",I25,IF($O$4="Fireworks",J25,IF($O$4="Landscape",K25,IF($O$4="Macro",L25,IF($O$4="People",M25,IF($O$4="Sports",N25,IF($O$4="Travel",O25,IF($O$4="Waterdrops",P25,IF($O$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AF25" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D25,IF($P$4="C2 Birds in Flight",E25,IF($P$4="C3 Landscape",F25,IF($P$4="Default Settings",G25,IF($P$4="Birds in Flight",H25,IF($P$4="Birds Perched",I25,IF($P$4="Fireworks",J25,IF($P$4="Landscape",K25,IF($P$4="Macro",L25,IF($P$4="People",M25,IF($P$4="Sports",N25,IF($P$4="Travel",O25,IF($P$4="Waterdrops",P25,IF($P$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>Off / Off</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="AG25" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D25,IF($Q$4="C2 Birds in Flight",E25,IF($Q$4="C3 Landscape",F25,IF($Q$4="Default Settings",G25,IF($Q$4="Birds in Flight",H25,IF($Q$4="Birds Perched",I25,IF($Q$4="Fireworks",J25,IF($Q$4="Landscape",K25,IF($Q$4="Macro",L25,IF($Q$4="People",M25,IF($Q$4="Sports",N25,IF($Q$4="Travel",O25,IF($Q$4="Waterdrops",P25,IF($Q$4="Wildlife",Q25,""))))))))))))))</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
     </x:row>
     <x:row r="26" hidden="0">
       <x:c r="A26" s="12" t="str">
-        <x:v>Shooting 5 &gt; Focus bracketing</x:v>
+        <x:v>AF1 &gt; Touch &amp; drag AF settings &gt; Active touch area</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>MM-SWITCH; MM-FOCUS*</x:v>
+        <x:v>Set once</x:v>
       </x:c>
       <x:c r="C26" s="15" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>Active touch area</x:v>
       </x:c>
       <x:c r="D26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="E26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="F26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="G26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="H26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="I26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="J26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="K26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="L26" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="M26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="N26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="O26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="P26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="Q26" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="R26" s="20" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="S26" s="20" t="n">
-        <x:v>240</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="T26" s="38" t="str">
         <x:f>IF($D$4="C1 Wildlife",D26,IF($D$4="C2 Birds in Flight",E26,IF($D$4="C3 Landscape",F26,IF($D$4="Default Settings",G26,IF($D$4="Birds in Flight",H26,IF($D$4="Birds Perched",I26,IF($D$4="Fireworks",J26,IF($D$4="Landscape",K26,IF($D$4="Macro",L26,IF($D$4="People",M26,IF($D$4="Sports",N26,IF($D$4="Travel",O26,IF($D$4="Waterdrops",P26,IF($D$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="U26" s="38" t="str">
         <x:f>IF($E$4="C1 Wildlife",D26,IF($E$4="C2 Birds in Flight",E26,IF($E$4="C3 Landscape",F26,IF($E$4="Default Settings",G26,IF($E$4="Birds in Flight",H26,IF($E$4="Birds Perched",I26,IF($E$4="Fireworks",J26,IF($E$4="Landscape",K26,IF($E$4="Macro",L26,IF($E$4="People",M26,IF($E$4="Sports",N26,IF($E$4="Travel",O26,IF($E$4="Waterdrops",P26,IF($E$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="V26" s="38" t="str">
         <x:f>IF($F$4="C1 Wildlife",D26,IF($F$4="C2 Birds in Flight",E26,IF($F$4="C3 Landscape",F26,IF($F$4="Default Settings",G26,IF($F$4="Birds in Flight",H26,IF($F$4="Birds Perched",I26,IF($F$4="Fireworks",J26,IF($F$4="Landscape",K26,IF($F$4="Macro",L26,IF($F$4="People",M26,IF($F$4="Sports",N26,IF($F$4="Travel",O26,IF($F$4="Waterdrops",P26,IF($F$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="W26" s="38" t="str">
         <x:f>IF($G$4="C1 Wildlife",D26,IF($G$4="C2 Birds in Flight",E26,IF($G$4="C3 Landscape",F26,IF($G$4="Default Settings",G26,IF($G$4="Birds in Flight",H26,IF($G$4="Birds Perched",I26,IF($G$4="Fireworks",J26,IF($G$4="Landscape",K26,IF($G$4="Macro",L26,IF($G$4="People",M26,IF($G$4="Sports",N26,IF($G$4="Travel",O26,IF($G$4="Waterdrops",P26,IF($G$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="X26" s="38" t="str">
         <x:f>IF($H$4="C1 Wildlife",D26,IF($H$4="C2 Birds in Flight",E26,IF($H$4="C3 Landscape",F26,IF($H$4="Default Settings",G26,IF($H$4="Birds in Flight",H26,IF($H$4="Birds Perched",I26,IF($H$4="Fireworks",J26,IF($H$4="Landscape",K26,IF($H$4="Macro",L26,IF($H$4="People",M26,IF($H$4="Sports",N26,IF($H$4="Travel",O26,IF($H$4="Waterdrops",P26,IF($H$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="Y26" s="38" t="str">
         <x:f>IF($I$4="C1 Wildlife",D26,IF($I$4="C2 Birds in Flight",E26,IF($I$4="C3 Landscape",F26,IF($I$4="Default Settings",G26,IF($I$4="Birds in Flight",H26,IF($I$4="Birds Perched",I26,IF($I$4="Fireworks",J26,IF($I$4="Landscape",K26,IF($I$4="Macro",L26,IF($I$4="People",M26,IF($I$4="Sports",N26,IF($I$4="Travel",O26,IF($I$4="Waterdrops",P26,IF($I$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="Z26" s="38" t="str">
         <x:f>IF($J$4="C1 Wildlife",D26,IF($J$4="C2 Birds in Flight",E26,IF($J$4="C3 Landscape",F26,IF($J$4="Default Settings",G26,IF($J$4="Birds in Flight",H26,IF($J$4="Birds Perched",I26,IF($J$4="Fireworks",J26,IF($J$4="Landscape",K26,IF($J$4="Macro",L26,IF($J$4="People",M26,IF($J$4="Sports",N26,IF($J$4="Travel",O26,IF($J$4="Waterdrops",P26,IF($J$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AA26" s="38" t="str">
         <x:f>IF($K$4="C1 Wildlife",D26,IF($K$4="C2 Birds in Flight",E26,IF($K$4="C3 Landscape",F26,IF($K$4="Default Settings",G26,IF($K$4="Birds in Flight",H26,IF($K$4="Birds Perched",I26,IF($K$4="Fireworks",J26,IF($K$4="Landscape",K26,IF($K$4="Macro",L26,IF($K$4="People",M26,IF($K$4="Sports",N26,IF($K$4="Travel",O26,IF($K$4="Waterdrops",P26,IF($K$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AB26" s="38" t="str">
         <x:f>IF($L$4="C1 Wildlife",D26,IF($L$4="C2 Birds in Flight",E26,IF($L$4="C3 Landscape",F26,IF($L$4="Default Settings",G26,IF($L$4="Birds in Flight",H26,IF($L$4="Birds Perched",I26,IF($L$4="Fireworks",J26,IF($L$4="Landscape",K26,IF($L$4="Macro",L26,IF($L$4="People",M26,IF($L$4="Sports",N26,IF($L$4="Travel",O26,IF($L$4="Waterdrops",P26,IF($L$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AC26" s="38" t="str">
         <x:f>IF($M$4="C1 Wildlife",D26,IF($M$4="C2 Birds in Flight",E26,IF($M$4="C3 Landscape",F26,IF($M$4="Default Settings",G26,IF($M$4="Birds in Flight",H26,IF($M$4="Birds Perched",I26,IF($M$4="Fireworks",J26,IF($M$4="Landscape",K26,IF($M$4="Macro",L26,IF($M$4="People",M26,IF($M$4="Sports",N26,IF($M$4="Travel",O26,IF($M$4="Waterdrops",P26,IF($M$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AD26" s="38" t="str">
         <x:f>IF($N$4="C1 Wildlife",D26,IF($N$4="C2 Birds in Flight",E26,IF($N$4="C3 Landscape",F26,IF($N$4="Default Settings",G26,IF($N$4="Birds in Flight",H26,IF($N$4="Birds Perched",I26,IF($N$4="Fireworks",J26,IF($N$4="Landscape",K26,IF($N$4="Macro",L26,IF($N$4="People",M26,IF($N$4="Sports",N26,IF($N$4="Travel",O26,IF($N$4="Waterdrops",P26,IF($N$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AE26" s="38" t="str">
         <x:f>IF($O$4="C1 Wildlife",D26,IF($O$4="C2 Birds in Flight",E26,IF($O$4="C3 Landscape",F26,IF($O$4="Default Settings",G26,IF($O$4="Birds in Flight",H26,IF($O$4="Birds Perched",I26,IF($O$4="Fireworks",J26,IF($O$4="Landscape",K26,IF($O$4="Macro",L26,IF($O$4="People",M26,IF($O$4="Sports",N26,IF($O$4="Travel",O26,IF($O$4="Waterdrops",P26,IF($O$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AF26" s="38" t="str">
         <x:f>IF($P$4="C1 Wildlife",D26,IF($P$4="C2 Birds in Flight",E26,IF($P$4="C3 Landscape",F26,IF($P$4="Default Settings",G26,IF($P$4="Birds in Flight",H26,IF($P$4="Birds Perched",I26,IF($P$4="Fireworks",J26,IF($P$4="Landscape",K26,IF($P$4="Macro",L26,IF($P$4="People",M26,IF($P$4="Sports",N26,IF($P$4="Travel",O26,IF($P$4="Waterdrops",P26,IF($P$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="AG26" s="38" t="str">
         <x:f>IF($Q$4="C1 Wildlife",D26,IF($Q$4="C2 Birds in Flight",E26,IF($Q$4="C3 Landscape",F26,IF($Q$4="Default Settings",G26,IF($Q$4="Birds in Flight",H26,IF($Q$4="Birds Perched",I26,IF($Q$4="Fireworks",J26,IF($Q$4="Landscape",K26,IF($Q$4="Macro",L26,IF($Q$4="People",M26,IF($Q$4="Sports",N26,IF($Q$4="Travel",O26,IF($Q$4="Waterdrops",P26,IF($Q$4="Wildlife",Q26,""))))))))))))))</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" hidden="0">
+      <x:c r="A27" s="12" t="str">
+        <x:v>Shooting menu &gt; Drive mode</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>Q screen</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="str">
+        <x:v>Drive</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="H27" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="I27" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="L27" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="M27" s="17" t="str">
+        <x:v>Low Speed Continuous</x:v>
+      </x:c>
+      <x:c r="N27" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="O27" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="P27" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="Q27" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="R27" s="20" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="S27" s="20" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="T27" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D27,IF($D$4="C2 Birds in Flight",E27,IF($D$4="C3 Landscape",F27,IF($D$4="Default Settings",G27,IF($D$4="Birds in Flight",H27,IF($D$4="Birds Perched",I27,IF($D$4="Fireworks",J27,IF($D$4="Landscape",K27,IF($D$4="Macro",L27,IF($D$4="People",M27,IF($D$4="Sports",N27,IF($D$4="Travel",O27,IF($D$4="Waterdrops",P27,IF($D$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="U27" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D27,IF($E$4="C2 Birds in Flight",E27,IF($E$4="C3 Landscape",F27,IF($E$4="Default Settings",G27,IF($E$4="Birds in Flight",H27,IF($E$4="Birds Perched",I27,IF($E$4="Fireworks",J27,IF($E$4="Landscape",K27,IF($E$4="Macro",L27,IF($E$4="People",M27,IF($E$4="Sports",N27,IF($E$4="Travel",O27,IF($E$4="Waterdrops",P27,IF($E$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="V27" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D27,IF($F$4="C2 Birds in Flight",E27,IF($F$4="C3 Landscape",F27,IF($F$4="Default Settings",G27,IF($F$4="Birds in Flight",H27,IF($F$4="Birds Perched",I27,IF($F$4="Fireworks",J27,IF($F$4="Landscape",K27,IF($F$4="Macro",L27,IF($F$4="People",M27,IF($F$4="Sports",N27,IF($F$4="Travel",O27,IF($F$4="Waterdrops",P27,IF($F$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="W27" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D27,IF($G$4="C2 Birds in Flight",E27,IF($G$4="C3 Landscape",F27,IF($G$4="Default Settings",G27,IF($G$4="Birds in Flight",H27,IF($G$4="Birds Perched",I27,IF($G$4="Fireworks",J27,IF($G$4="Landscape",K27,IF($G$4="Macro",L27,IF($G$4="People",M27,IF($G$4="Sports",N27,IF($G$4="Travel",O27,IF($G$4="Waterdrops",P27,IF($G$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="X27" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D27,IF($H$4="C2 Birds in Flight",E27,IF($H$4="C3 Landscape",F27,IF($H$4="Default Settings",G27,IF($H$4="Birds in Flight",H27,IF($H$4="Birds Perched",I27,IF($H$4="Fireworks",J27,IF($H$4="Landscape",K27,IF($H$4="Macro",L27,IF($H$4="People",M27,IF($H$4="Sports",N27,IF($H$4="Travel",O27,IF($H$4="Waterdrops",P27,IF($H$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="Y27" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D27,IF($I$4="C2 Birds in Flight",E27,IF($I$4="C3 Landscape",F27,IF($I$4="Default Settings",G27,IF($I$4="Birds in Flight",H27,IF($I$4="Birds Perched",I27,IF($I$4="Fireworks",J27,IF($I$4="Landscape",K27,IF($I$4="Macro",L27,IF($I$4="People",M27,IF($I$4="Sports",N27,IF($I$4="Travel",O27,IF($I$4="Waterdrops",P27,IF($I$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="Z27" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D27,IF($J$4="C2 Birds in Flight",E27,IF($J$4="C3 Landscape",F27,IF($J$4="Default Settings",G27,IF($J$4="Birds in Flight",H27,IF($J$4="Birds Perched",I27,IF($J$4="Fireworks",J27,IF($J$4="Landscape",K27,IF($J$4="Macro",L27,IF($J$4="People",M27,IF($J$4="Sports",N27,IF($J$4="Travel",O27,IF($J$4="Waterdrops",P27,IF($J$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AA27" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D27,IF($K$4="C2 Birds in Flight",E27,IF($K$4="C3 Landscape",F27,IF($K$4="Default Settings",G27,IF($K$4="Birds in Flight",H27,IF($K$4="Birds Perched",I27,IF($K$4="Fireworks",J27,IF($K$4="Landscape",K27,IF($K$4="Macro",L27,IF($K$4="People",M27,IF($K$4="Sports",N27,IF($K$4="Travel",O27,IF($K$4="Waterdrops",P27,IF($K$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AB27" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D27,IF($L$4="C2 Birds in Flight",E27,IF($L$4="C3 Landscape",F27,IF($L$4="Default Settings",G27,IF($L$4="Birds in Flight",H27,IF($L$4="Birds Perched",I27,IF($L$4="Fireworks",J27,IF($L$4="Landscape",K27,IF($L$4="Macro",L27,IF($L$4="People",M27,IF($L$4="Sports",N27,IF($L$4="Travel",O27,IF($L$4="Waterdrops",P27,IF($L$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AC27" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D27,IF($M$4="C2 Birds in Flight",E27,IF($M$4="C3 Landscape",F27,IF($M$4="Default Settings",G27,IF($M$4="Birds in Flight",H27,IF($M$4="Birds Perched",I27,IF($M$4="Fireworks",J27,IF($M$4="Landscape",K27,IF($M$4="Macro",L27,IF($M$4="People",M27,IF($M$4="Sports",N27,IF($M$4="Travel",O27,IF($M$4="Waterdrops",P27,IF($M$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Low Speed Continuous</x:v>
+      </x:c>
+      <x:c r="AD27" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D27,IF($N$4="C2 Birds in Flight",E27,IF($N$4="C3 Landscape",F27,IF($N$4="Default Settings",G27,IF($N$4="Birds in Flight",H27,IF($N$4="Birds Perched",I27,IF($N$4="Fireworks",J27,IF($N$4="Landscape",K27,IF($N$4="Macro",L27,IF($N$4="People",M27,IF($N$4="Sports",N27,IF($N$4="Travel",O27,IF($N$4="Waterdrops",P27,IF($N$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="AE27" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D27,IF($O$4="C2 Birds in Flight",E27,IF($O$4="C3 Landscape",F27,IF($O$4="Default Settings",G27,IF($O$4="Birds in Flight",H27,IF($O$4="Birds Perched",I27,IF($O$4="Fireworks",J27,IF($O$4="Landscape",K27,IF($O$4="Macro",L27,IF($O$4="People",M27,IF($O$4="Sports",N27,IF($O$4="Travel",O27,IF($O$4="Waterdrops",P27,IF($O$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AF27" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D27,IF($P$4="C2 Birds in Flight",E27,IF($P$4="C3 Landscape",F27,IF($P$4="Default Settings",G27,IF($P$4="Birds in Flight",H27,IF($P$4="Birds Perched",I27,IF($P$4="Fireworks",J27,IF($P$4="Landscape",K27,IF($P$4="Macro",L27,IF($P$4="People",M27,IF($P$4="Sports",N27,IF($P$4="Travel",O27,IF($P$4="Waterdrops",P27,IF($P$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="AG27" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D27,IF($Q$4="C2 Birds in Flight",E27,IF($Q$4="C3 Landscape",F27,IF($Q$4="Default Settings",G27,IF($Q$4="Birds in Flight",H27,IF($Q$4="Birds Perched",I27,IF($Q$4="Fireworks",J27,IF($Q$4="Landscape",K27,IF($Q$4="Macro",L27,IF($Q$4="People",M27,IF($Q$4="Sports",N27,IF($Q$4="Travel",O27,IF($Q$4="Waterdrops",P27,IF($Q$4="Wildlife",Q27,""))))))))))))))</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" hidden="0">
+      <x:c r="A28" s="12" t="str">
+        <x:v>Shooting 7 &gt; High speed display</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>Set once; C1-C3 registered profile</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="str">
+        <x:v>High Speed Display</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="H28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="I28" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="L28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="M28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="N28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="O28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="P28" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Q28" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="R28" s="20" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="S28" s="20" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="T28" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D28,IF($D$4="C2 Birds in Flight",E28,IF($D$4="C3 Landscape",F28,IF($D$4="Default Settings",G28,IF($D$4="Birds in Flight",H28,IF($D$4="Birds Perched",I28,IF($D$4="Fireworks",J28,IF($D$4="Landscape",K28,IF($D$4="Macro",L28,IF($D$4="People",M28,IF($D$4="Sports",N28,IF($D$4="Travel",O28,IF($D$4="Waterdrops",P28,IF($D$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="U28" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D28,IF($E$4="C2 Birds in Flight",E28,IF($E$4="C3 Landscape",F28,IF($E$4="Default Settings",G28,IF($E$4="Birds in Flight",H28,IF($E$4="Birds Perched",I28,IF($E$4="Fireworks",J28,IF($E$4="Landscape",K28,IF($E$4="Macro",L28,IF($E$4="People",M28,IF($E$4="Sports",N28,IF($E$4="Travel",O28,IF($E$4="Waterdrops",P28,IF($E$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="V28" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D28,IF($F$4="C2 Birds in Flight",E28,IF($F$4="C3 Landscape",F28,IF($F$4="Default Settings",G28,IF($F$4="Birds in Flight",H28,IF($F$4="Birds Perched",I28,IF($F$4="Fireworks",J28,IF($F$4="Landscape",K28,IF($F$4="Macro",L28,IF($F$4="People",M28,IF($F$4="Sports",N28,IF($F$4="Travel",O28,IF($F$4="Waterdrops",P28,IF($F$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="W28" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D28,IF($G$4="C2 Birds in Flight",E28,IF($G$4="C3 Landscape",F28,IF($G$4="Default Settings",G28,IF($G$4="Birds in Flight",H28,IF($G$4="Birds Perched",I28,IF($G$4="Fireworks",J28,IF($G$4="Landscape",K28,IF($G$4="Macro",L28,IF($G$4="People",M28,IF($G$4="Sports",N28,IF($G$4="Travel",O28,IF($G$4="Waterdrops",P28,IF($G$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="X28" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D28,IF($H$4="C2 Birds in Flight",E28,IF($H$4="C3 Landscape",F28,IF($H$4="Default Settings",G28,IF($H$4="Birds in Flight",H28,IF($H$4="Birds Perched",I28,IF($H$4="Fireworks",J28,IF($H$4="Landscape",K28,IF($H$4="Macro",L28,IF($H$4="People",M28,IF($H$4="Sports",N28,IF($H$4="Travel",O28,IF($H$4="Waterdrops",P28,IF($H$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="Y28" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D28,IF($I$4="C2 Birds in Flight",E28,IF($I$4="C3 Landscape",F28,IF($I$4="Default Settings",G28,IF($I$4="Birds in Flight",H28,IF($I$4="Birds Perched",I28,IF($I$4="Fireworks",J28,IF($I$4="Landscape",K28,IF($I$4="Macro",L28,IF($I$4="People",M28,IF($I$4="Sports",N28,IF($I$4="Travel",O28,IF($I$4="Waterdrops",P28,IF($I$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="Z28" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D28,IF($J$4="C2 Birds in Flight",E28,IF($J$4="C3 Landscape",F28,IF($J$4="Default Settings",G28,IF($J$4="Birds in Flight",H28,IF($J$4="Birds Perched",I28,IF($J$4="Fireworks",J28,IF($J$4="Landscape",K28,IF($J$4="Macro",L28,IF($J$4="People",M28,IF($J$4="Sports",N28,IF($J$4="Travel",O28,IF($J$4="Waterdrops",P28,IF($J$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AA28" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D28,IF($K$4="C2 Birds in Flight",E28,IF($K$4="C3 Landscape",F28,IF($K$4="Default Settings",G28,IF($K$4="Birds in Flight",H28,IF($K$4="Birds Perched",I28,IF($K$4="Fireworks",J28,IF($K$4="Landscape",K28,IF($K$4="Macro",L28,IF($K$4="People",M28,IF($K$4="Sports",N28,IF($K$4="Travel",O28,IF($K$4="Waterdrops",P28,IF($K$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AB28" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D28,IF($L$4="C2 Birds in Flight",E28,IF($L$4="C3 Landscape",F28,IF($L$4="Default Settings",G28,IF($L$4="Birds in Flight",H28,IF($L$4="Birds Perched",I28,IF($L$4="Fireworks",J28,IF($L$4="Landscape",K28,IF($L$4="Macro",L28,IF($L$4="People",M28,IF($L$4="Sports",N28,IF($L$4="Travel",O28,IF($L$4="Waterdrops",P28,IF($L$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AC28" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D28,IF($M$4="C2 Birds in Flight",E28,IF($M$4="C3 Landscape",F28,IF($M$4="Default Settings",G28,IF($M$4="Birds in Flight",H28,IF($M$4="Birds Perched",I28,IF($M$4="Fireworks",J28,IF($M$4="Landscape",K28,IF($M$4="Macro",L28,IF($M$4="People",M28,IF($M$4="Sports",N28,IF($M$4="Travel",O28,IF($M$4="Waterdrops",P28,IF($M$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AD28" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D28,IF($N$4="C2 Birds in Flight",E28,IF($N$4="C3 Landscape",F28,IF($N$4="Default Settings",G28,IF($N$4="Birds in Flight",H28,IF($N$4="Birds Perched",I28,IF($N$4="Fireworks",J28,IF($N$4="Landscape",K28,IF($N$4="Macro",L28,IF($N$4="People",M28,IF($N$4="Sports",N28,IF($N$4="Travel",O28,IF($N$4="Waterdrops",P28,IF($N$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AE28" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D28,IF($O$4="C2 Birds in Flight",E28,IF($O$4="C3 Landscape",F28,IF($O$4="Default Settings",G28,IF($O$4="Birds in Flight",H28,IF($O$4="Birds Perched",I28,IF($O$4="Fireworks",J28,IF($O$4="Landscape",K28,IF($O$4="Macro",L28,IF($O$4="People",M28,IF($O$4="Sports",N28,IF($O$4="Travel",O28,IF($O$4="Waterdrops",P28,IF($O$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AF28" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D28,IF($P$4="C2 Birds in Flight",E28,IF($P$4="C3 Landscape",F28,IF($P$4="Default Settings",G28,IF($P$4="Birds in Flight",H28,IF($P$4="Birds Perched",I28,IF($P$4="Fireworks",J28,IF($P$4="Landscape",K28,IF($P$4="Macro",L28,IF($P$4="People",M28,IF($P$4="Sports",N28,IF($P$4="Travel",O28,IF($P$4="Waterdrops",P28,IF($P$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="AG28" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D28,IF($Q$4="C2 Birds in Flight",E28,IF($Q$4="C3 Landscape",F28,IF($Q$4="Default Settings",G28,IF($Q$4="Birds in Flight",H28,IF($Q$4="Birds Perched",I28,IF($Q$4="Fireworks",J28,IF($Q$4="Landscape",K28,IF($Q$4="Macro",L28,IF($Q$4="People",M28,IF($Q$4="Sports",N28,IF($Q$4="Travel",O28,IF($Q$4="Waterdrops",P28,IF($Q$4="Wildlife",Q28,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" hidden="0">
+      <x:c r="A29" s="12" t="str">
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; page varies by equipment</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>MM-SWITCH; MM-FOCUS*/MM-LONG*</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="str">
+        <x:v>Image Stabilization</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="H29" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="I29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="L29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="M29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="N29" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="O29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="P29" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q29" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="R29" s="20" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S29" s="20" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="T29" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D29,IF($D$4="C2 Birds in Flight",E29,IF($D$4="C3 Landscape",F29,IF($D$4="Default Settings",G29,IF($D$4="Birds in Flight",H29,IF($D$4="Birds Perched",I29,IF($D$4="Fireworks",J29,IF($D$4="Landscape",K29,IF($D$4="Macro",L29,IF($D$4="People",M29,IF($D$4="Sports",N29,IF($D$4="Travel",O29,IF($D$4="Waterdrops",P29,IF($D$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U29" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D29,IF($E$4="C2 Birds in Flight",E29,IF($E$4="C3 Landscape",F29,IF($E$4="Default Settings",G29,IF($E$4="Birds in Flight",H29,IF($E$4="Birds Perched",I29,IF($E$4="Fireworks",J29,IF($E$4="Landscape",K29,IF($E$4="Macro",L29,IF($E$4="People",M29,IF($E$4="Sports",N29,IF($E$4="Travel",O29,IF($E$4="Waterdrops",P29,IF($E$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="V29" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D29,IF($F$4="C2 Birds in Flight",E29,IF($F$4="C3 Landscape",F29,IF($F$4="Default Settings",G29,IF($F$4="Birds in Flight",H29,IF($F$4="Birds Perched",I29,IF($F$4="Fireworks",J29,IF($F$4="Landscape",K29,IF($F$4="Macro",L29,IF($F$4="People",M29,IF($F$4="Sports",N29,IF($F$4="Travel",O29,IF($F$4="Waterdrops",P29,IF($F$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="W29" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D29,IF($G$4="C2 Birds in Flight",E29,IF($G$4="C3 Landscape",F29,IF($G$4="Default Settings",G29,IF($G$4="Birds in Flight",H29,IF($G$4="Birds Perched",I29,IF($G$4="Fireworks",J29,IF($G$4="Landscape",K29,IF($G$4="Macro",L29,IF($G$4="People",M29,IF($G$4="Sports",N29,IF($G$4="Travel",O29,IF($G$4="Waterdrops",P29,IF($G$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="X29" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D29,IF($H$4="C2 Birds in Flight",E29,IF($H$4="C3 Landscape",F29,IF($H$4="Default Settings",G29,IF($H$4="Birds in Flight",H29,IF($H$4="Birds Perched",I29,IF($H$4="Fireworks",J29,IF($H$4="Landscape",K29,IF($H$4="Macro",L29,IF($H$4="People",M29,IF($H$4="Sports",N29,IF($H$4="Travel",O29,IF($H$4="Waterdrops",P29,IF($H$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="Y29" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D29,IF($I$4="C2 Birds in Flight",E29,IF($I$4="C3 Landscape",F29,IF($I$4="Default Settings",G29,IF($I$4="Birds in Flight",H29,IF($I$4="Birds Perched",I29,IF($I$4="Fireworks",J29,IF($I$4="Landscape",K29,IF($I$4="Macro",L29,IF($I$4="People",M29,IF($I$4="Sports",N29,IF($I$4="Travel",O29,IF($I$4="Waterdrops",P29,IF($I$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="Z29" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D29,IF($J$4="C2 Birds in Flight",E29,IF($J$4="C3 Landscape",F29,IF($J$4="Default Settings",G29,IF($J$4="Birds in Flight",H29,IF($J$4="Birds Perched",I29,IF($J$4="Fireworks",J29,IF($J$4="Landscape",K29,IF($J$4="Macro",L29,IF($J$4="People",M29,IF($J$4="Sports",N29,IF($J$4="Travel",O29,IF($J$4="Waterdrops",P29,IF($J$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA29" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D29,IF($K$4="C2 Birds in Flight",E29,IF($K$4="C3 Landscape",F29,IF($K$4="Default Settings",G29,IF($K$4="Birds in Flight",H29,IF($K$4="Birds Perched",I29,IF($K$4="Fireworks",J29,IF($K$4="Landscape",K29,IF($K$4="Macro",L29,IF($K$4="People",M29,IF($K$4="Sports",N29,IF($K$4="Travel",O29,IF($K$4="Waterdrops",P29,IF($K$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AB29" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D29,IF($L$4="C2 Birds in Flight",E29,IF($L$4="C3 Landscape",F29,IF($L$4="Default Settings",G29,IF($L$4="Birds in Flight",H29,IF($L$4="Birds Perched",I29,IF($L$4="Fireworks",J29,IF($L$4="Landscape",K29,IF($L$4="Macro",L29,IF($L$4="People",M29,IF($L$4="Sports",N29,IF($L$4="Travel",O29,IF($L$4="Waterdrops",P29,IF($L$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AC29" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D29,IF($M$4="C2 Birds in Flight",E29,IF($M$4="C3 Landscape",F29,IF($M$4="Default Settings",G29,IF($M$4="Birds in Flight",H29,IF($M$4="Birds Perched",I29,IF($M$4="Fireworks",J29,IF($M$4="Landscape",K29,IF($M$4="Macro",L29,IF($M$4="People",M29,IF($M$4="Sports",N29,IF($M$4="Travel",O29,IF($M$4="Waterdrops",P29,IF($M$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AD29" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D29,IF($N$4="C2 Birds in Flight",E29,IF($N$4="C3 Landscape",F29,IF($N$4="Default Settings",G29,IF($N$4="Birds in Flight",H29,IF($N$4="Birds Perched",I29,IF($N$4="Fireworks",J29,IF($N$4="Landscape",K29,IF($N$4="Macro",L29,IF($N$4="People",M29,IF($N$4="Sports",N29,IF($N$4="Travel",O29,IF($N$4="Waterdrops",P29,IF($N$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="AE29" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D29,IF($O$4="C2 Birds in Flight",E29,IF($O$4="C3 Landscape",F29,IF($O$4="Default Settings",G29,IF($O$4="Birds in Flight",H29,IF($O$4="Birds Perched",I29,IF($O$4="Fireworks",J29,IF($O$4="Landscape",K29,IF($O$4="Macro",L29,IF($O$4="People",M29,IF($O$4="Sports",N29,IF($O$4="Travel",O29,IF($O$4="Waterdrops",P29,IF($O$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="AF29" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D29,IF($P$4="C2 Birds in Flight",E29,IF($P$4="C3 Landscape",F29,IF($P$4="Default Settings",G29,IF($P$4="Birds in Flight",H29,IF($P$4="Birds Perched",I29,IF($P$4="Fireworks",J29,IF($P$4="Landscape",K29,IF($P$4="Macro",L29,IF($P$4="People",M29,IF($P$4="Sports",N29,IF($P$4="Travel",O29,IF($P$4="Waterdrops",P29,IF($P$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG29" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D29,IF($Q$4="C2 Birds in Flight",E29,IF($Q$4="C3 Landscape",F29,IF($Q$4="Default Settings",G29,IF($Q$4="Birds in Flight",H29,IF($Q$4="Birds Perched",I29,IF($Q$4="Fireworks",J29,IF($Q$4="Landscape",K29,IF($Q$4="Macro",L29,IF($Q$4="People",M29,IF($Q$4="Sports",N29,IF($Q$4="Travel",O29,IF($Q$4="Waterdrops",P29,IF($Q$4="Wildlife",Q29,""))))))))))))))</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" hidden="0">
+      <x:c r="A30" s="12" t="str">
+        <x:v>Shooting menu &gt; IS (Image Stabilizer) mode; lens mode switch when fitted</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>Lens IS switch; camera IS menu when available</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="str">
+        <x:v>IBIS / Lens IS</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="H30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="I30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="L30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="M30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="N30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="O30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="P30" s="17" t="str">
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="Q30" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="R30" s="20" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="S30" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="T30" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D30,IF($D$4="C2 Birds in Flight",E30,IF($D$4="C3 Landscape",F30,IF($D$4="Default Settings",G30,IF($D$4="Birds in Flight",H30,IF($D$4="Birds Perched",I30,IF($D$4="Fireworks",J30,IF($D$4="Landscape",K30,IF($D$4="Macro",L30,IF($D$4="People",M30,IF($D$4="Sports",N30,IF($D$4="Travel",O30,IF($D$4="Waterdrops",P30,IF($D$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U30" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D30,IF($E$4="C2 Birds in Flight",E30,IF($E$4="C3 Landscape",F30,IF($E$4="Default Settings",G30,IF($E$4="Birds in Flight",H30,IF($E$4="Birds Perched",I30,IF($E$4="Fireworks",J30,IF($E$4="Landscape",K30,IF($E$4="Macro",L30,IF($E$4="People",M30,IF($E$4="Sports",N30,IF($E$4="Travel",O30,IF($E$4="Waterdrops",P30,IF($E$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V30" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D30,IF($F$4="C2 Birds in Flight",E30,IF($F$4="C3 Landscape",F30,IF($F$4="Default Settings",G30,IF($F$4="Birds in Flight",H30,IF($F$4="Birds Perched",I30,IF($F$4="Fireworks",J30,IF($F$4="Landscape",K30,IF($F$4="Macro",L30,IF($F$4="People",M30,IF($F$4="Sports",N30,IF($F$4="Travel",O30,IF($F$4="Waterdrops",P30,IF($F$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="W30" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D30,IF($G$4="C2 Birds in Flight",E30,IF($G$4="C3 Landscape",F30,IF($G$4="Default Settings",G30,IF($G$4="Birds in Flight",H30,IF($G$4="Birds Perched",I30,IF($G$4="Fireworks",J30,IF($G$4="Landscape",K30,IF($G$4="Macro",L30,IF($G$4="People",M30,IF($G$4="Sports",N30,IF($G$4="Travel",O30,IF($G$4="Waterdrops",P30,IF($G$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="X30" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D30,IF($H$4="C2 Birds in Flight",E30,IF($H$4="C3 Landscape",F30,IF($H$4="Default Settings",G30,IF($H$4="Birds in Flight",H30,IF($H$4="Birds Perched",I30,IF($H$4="Fireworks",J30,IF($H$4="Landscape",K30,IF($H$4="Macro",L30,IF($H$4="People",M30,IF($H$4="Sports",N30,IF($H$4="Travel",O30,IF($H$4="Waterdrops",P30,IF($H$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Y30" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D30,IF($I$4="C2 Birds in Flight",E30,IF($I$4="C3 Landscape",F30,IF($I$4="Default Settings",G30,IF($I$4="Birds in Flight",H30,IF($I$4="Birds Perched",I30,IF($I$4="Fireworks",J30,IF($I$4="Landscape",K30,IF($I$4="Macro",L30,IF($I$4="People",M30,IF($I$4="Sports",N30,IF($I$4="Travel",O30,IF($I$4="Waterdrops",P30,IF($I$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="Z30" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D30,IF($J$4="C2 Birds in Flight",E30,IF($J$4="C3 Landscape",F30,IF($J$4="Default Settings",G30,IF($J$4="Birds in Flight",H30,IF($J$4="Birds Perched",I30,IF($J$4="Fireworks",J30,IF($J$4="Landscape",K30,IF($J$4="Macro",L30,IF($J$4="People",M30,IF($J$4="Sports",N30,IF($J$4="Travel",O30,IF($J$4="Waterdrops",P30,IF($J$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="AA30" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D30,IF($K$4="C2 Birds in Flight",E30,IF($K$4="C3 Landscape",F30,IF($K$4="Default Settings",G30,IF($K$4="Birds in Flight",H30,IF($K$4="Birds Perched",I30,IF($K$4="Fireworks",J30,IF($K$4="Landscape",K30,IF($K$4="Macro",L30,IF($K$4="People",M30,IF($K$4="Sports",N30,IF($K$4="Travel",O30,IF($K$4="Waterdrops",P30,IF($K$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AB30" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D30,IF($L$4="C2 Birds in Flight",E30,IF($L$4="C3 Landscape",F30,IF($L$4="Default Settings",G30,IF($L$4="Birds in Flight",H30,IF($L$4="Birds Perched",I30,IF($L$4="Fireworks",J30,IF($L$4="Landscape",K30,IF($L$4="Macro",L30,IF($L$4="People",M30,IF($L$4="Sports",N30,IF($L$4="Travel",O30,IF($L$4="Waterdrops",P30,IF($L$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AC30" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D30,IF($M$4="C2 Birds in Flight",E30,IF($M$4="C3 Landscape",F30,IF($M$4="Default Settings",G30,IF($M$4="Birds in Flight",H30,IF($M$4="Birds Perched",I30,IF($M$4="Fireworks",J30,IF($M$4="Landscape",K30,IF($M$4="Macro",L30,IF($M$4="People",M30,IF($M$4="Sports",N30,IF($M$4="Travel",O30,IF($M$4="Waterdrops",P30,IF($M$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AD30" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D30,IF($N$4="C2 Birds in Flight",E30,IF($N$4="C3 Landscape",F30,IF($N$4="Default Settings",G30,IF($N$4="Birds in Flight",H30,IF($N$4="Birds Perched",I30,IF($N$4="Fireworks",J30,IF($N$4="Landscape",K30,IF($N$4="Macro",L30,IF($N$4="People",M30,IF($N$4="Sports",N30,IF($N$4="Travel",O30,IF($N$4="Waterdrops",P30,IF($N$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AE30" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D30,IF($O$4="C2 Birds in Flight",E30,IF($O$4="C3 Landscape",F30,IF($O$4="Default Settings",G30,IF($O$4="Birds in Flight",H30,IF($O$4="Birds Perched",I30,IF($O$4="Fireworks",J30,IF($O$4="Landscape",K30,IF($O$4="Macro",L30,IF($O$4="People",M30,IF($O$4="Sports",N30,IF($O$4="Travel",O30,IF($O$4="Waterdrops",P30,IF($O$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="AF30" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D30,IF($P$4="C2 Birds in Flight",E30,IF($P$4="C3 Landscape",F30,IF($P$4="Default Settings",G30,IF($P$4="Birds in Flight",H30,IF($P$4="Birds Perched",I30,IF($P$4="Fireworks",J30,IF($P$4="Landscape",K30,IF($P$4="Macro",L30,IF($P$4="People",M30,IF($P$4="Sports",N30,IF($P$4="Travel",O30,IF($P$4="Waterdrops",P30,IF($P$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>Off / Off</x:v>
+      </x:c>
+      <x:c r="AG30" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D30,IF($Q$4="C2 Birds in Flight",E30,IF($Q$4="C3 Landscape",F30,IF($Q$4="Default Settings",G30,IF($Q$4="Birds in Flight",H30,IF($Q$4="Birds Perched",I30,IF($Q$4="Fireworks",J30,IF($Q$4="Landscape",K30,IF($Q$4="Macro",L30,IF($Q$4="People",M30,IF($Q$4="Sports",N30,IF($Q$4="Travel",O30,IF($Q$4="Waterdrops",P30,IF($Q$4="Wildlife",Q30,""))))))))))))))</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" hidden="0">
+      <x:c r="A31" s="12" t="str">
+        <x:v>Shooting 7 &gt; IS (Image Stabilizer) mode; physical lens control when fitted</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>Lens IS switch</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="str">
+        <x:v>Lens IS</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="H31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="I31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="J31" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="L31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="M31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="N31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="O31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="P31" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q31" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="R31" s="20" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S31" s="20" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T31" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D31,IF($D$4="C2 Birds in Flight",E31,IF($D$4="C3 Landscape",F31,IF($D$4="Default Settings",G31,IF($D$4="Birds in Flight",H31,IF($D$4="Birds Perched",I31,IF($D$4="Fireworks",J31,IF($D$4="Landscape",K31,IF($D$4="Macro",L31,IF($D$4="People",M31,IF($D$4="Sports",N31,IF($D$4="Travel",O31,IF($D$4="Waterdrops",P31,IF($D$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="U31" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D31,IF($E$4="C2 Birds in Flight",E31,IF($E$4="C3 Landscape",F31,IF($E$4="Default Settings",G31,IF($E$4="Birds in Flight",H31,IF($E$4="Birds Perched",I31,IF($E$4="Fireworks",J31,IF($E$4="Landscape",K31,IF($E$4="Macro",L31,IF($E$4="People",M31,IF($E$4="Sports",N31,IF($E$4="Travel",O31,IF($E$4="Waterdrops",P31,IF($E$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="V31" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D31,IF($F$4="C2 Birds in Flight",E31,IF($F$4="C3 Landscape",F31,IF($F$4="Default Settings",G31,IF($F$4="Birds in Flight",H31,IF($F$4="Birds Perched",I31,IF($F$4="Fireworks",J31,IF($F$4="Landscape",K31,IF($F$4="Macro",L31,IF($F$4="People",M31,IF($F$4="Sports",N31,IF($F$4="Travel",O31,IF($F$4="Waterdrops",P31,IF($F$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="W31" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D31,IF($G$4="C2 Birds in Flight",E31,IF($G$4="C3 Landscape",F31,IF($G$4="Default Settings",G31,IF($G$4="Birds in Flight",H31,IF($G$4="Birds Perched",I31,IF($G$4="Fireworks",J31,IF($G$4="Landscape",K31,IF($G$4="Macro",L31,IF($G$4="People",M31,IF($G$4="Sports",N31,IF($G$4="Travel",O31,IF($G$4="Waterdrops",P31,IF($G$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="X31" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D31,IF($H$4="C2 Birds in Flight",E31,IF($H$4="C3 Landscape",F31,IF($H$4="Default Settings",G31,IF($H$4="Birds in Flight",H31,IF($H$4="Birds Perched",I31,IF($H$4="Fireworks",J31,IF($H$4="Landscape",K31,IF($H$4="Macro",L31,IF($H$4="People",M31,IF($H$4="Sports",N31,IF($H$4="Travel",O31,IF($H$4="Waterdrops",P31,IF($H$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Y31" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D31,IF($I$4="C2 Birds in Flight",E31,IF($I$4="C3 Landscape",F31,IF($I$4="Default Settings",G31,IF($I$4="Birds in Flight",H31,IF($I$4="Birds Perched",I31,IF($I$4="Fireworks",J31,IF($I$4="Landscape",K31,IF($I$4="Macro",L31,IF($I$4="People",M31,IF($I$4="Sports",N31,IF($I$4="Travel",O31,IF($I$4="Waterdrops",P31,IF($I$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="Z31" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D31,IF($J$4="C2 Birds in Flight",E31,IF($J$4="C3 Landscape",F31,IF($J$4="Default Settings",G31,IF($J$4="Birds in Flight",H31,IF($J$4="Birds Perched",I31,IF($J$4="Fireworks",J31,IF($J$4="Landscape",K31,IF($J$4="Macro",L31,IF($J$4="People",M31,IF($J$4="Sports",N31,IF($J$4="Travel",O31,IF($J$4="Waterdrops",P31,IF($J$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA31" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D31,IF($K$4="C2 Birds in Flight",E31,IF($K$4="C3 Landscape",F31,IF($K$4="Default Settings",G31,IF($K$4="Birds in Flight",H31,IF($K$4="Birds Perched",I31,IF($K$4="Fireworks",J31,IF($K$4="Landscape",K31,IF($K$4="Macro",L31,IF($K$4="People",M31,IF($K$4="Sports",N31,IF($K$4="Travel",O31,IF($K$4="Waterdrops",P31,IF($K$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="AB31" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D31,IF($L$4="C2 Birds in Flight",E31,IF($L$4="C3 Landscape",F31,IF($L$4="Default Settings",G31,IF($L$4="Birds in Flight",H31,IF($L$4="Birds Perched",I31,IF($L$4="Fireworks",J31,IF($L$4="Landscape",K31,IF($L$4="Macro",L31,IF($L$4="People",M31,IF($L$4="Sports",N31,IF($L$4="Travel",O31,IF($L$4="Waterdrops",P31,IF($L$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="AC31" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D31,IF($M$4="C2 Birds in Flight",E31,IF($M$4="C3 Landscape",F31,IF($M$4="Default Settings",G31,IF($M$4="Birds in Flight",H31,IF($M$4="Birds Perched",I31,IF($M$4="Fireworks",J31,IF($M$4="Landscape",K31,IF($M$4="Macro",L31,IF($M$4="People",M31,IF($M$4="Sports",N31,IF($M$4="Travel",O31,IF($M$4="Waterdrops",P31,IF($M$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="AD31" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D31,IF($N$4="C2 Birds in Flight",E31,IF($N$4="C3 Landscape",F31,IF($N$4="Default Settings",G31,IF($N$4="Birds in Flight",H31,IF($N$4="Birds Perched",I31,IF($N$4="Fireworks",J31,IF($N$4="Landscape",K31,IF($N$4="Macro",L31,IF($N$4="People",M31,IF($N$4="Sports",N31,IF($N$4="Travel",O31,IF($N$4="Waterdrops",P31,IF($N$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="AE31" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D31,IF($O$4="C2 Birds in Flight",E31,IF($O$4="C3 Landscape",F31,IF($O$4="Default Settings",G31,IF($O$4="Birds in Flight",H31,IF($O$4="Birds Perched",I31,IF($O$4="Fireworks",J31,IF($O$4="Landscape",K31,IF($O$4="Macro",L31,IF($O$4="People",M31,IF($O$4="Sports",N31,IF($O$4="Travel",O31,IF($O$4="Waterdrops",P31,IF($O$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="AF31" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D31,IF($P$4="C2 Birds in Flight",E31,IF($P$4="C3 Landscape",F31,IF($P$4="Default Settings",G31,IF($P$4="Birds in Flight",H31,IF($P$4="Birds Perched",I31,IF($P$4="Fireworks",J31,IF($P$4="Landscape",K31,IF($P$4="Macro",L31,IF($P$4="People",M31,IF($P$4="Sports",N31,IF($P$4="Travel",O31,IF($P$4="Waterdrops",P31,IF($P$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG31" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D31,IF($Q$4="C2 Birds in Flight",E31,IF($Q$4="C3 Landscape",F31,IF($Q$4="Default Settings",G31,IF($Q$4="Birds in Flight",H31,IF($Q$4="Birds Perched",I31,IF($Q$4="Fireworks",J31,IF($Q$4="Landscape",K31,IF($Q$4="Macro",L31,IF($Q$4="People",M31,IF($Q$4="Sports",N31,IF($Q$4="Travel",O31,IF($Q$4="Waterdrops",P31,IF($Q$4="Wildlife",Q31,""))))))))))))))</x:f>
+        <x:v>On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" hidden="0">
+      <x:c r="A32" s="12" t="str">
+        <x:v>Shooting 5 &gt; Focus bracketing</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>MM-SWITCH; MM-FOCUS*</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="H32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="I32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="K32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L32" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="M32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="N32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="O32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q32" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R32" s="20" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S32" s="20" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="T32" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D32,IF($D$4="C2 Birds in Flight",E32,IF($D$4="C3 Landscape",F32,IF($D$4="Default Settings",G32,IF($D$4="Birds in Flight",H32,IF($D$4="Birds Perched",I32,IF($D$4="Fireworks",J32,IF($D$4="Landscape",K32,IF($D$4="Macro",L32,IF($D$4="People",M32,IF($D$4="Sports",N32,IF($D$4="Travel",O32,IF($D$4="Waterdrops",P32,IF($D$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U32" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D32,IF($E$4="C2 Birds in Flight",E32,IF($E$4="C3 Landscape",F32,IF($E$4="Default Settings",G32,IF($E$4="Birds in Flight",H32,IF($E$4="Birds Perched",I32,IF($E$4="Fireworks",J32,IF($E$4="Landscape",K32,IF($E$4="Macro",L32,IF($E$4="People",M32,IF($E$4="Sports",N32,IF($E$4="Travel",O32,IF($E$4="Waterdrops",P32,IF($E$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V32" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D32,IF($F$4="C2 Birds in Flight",E32,IF($F$4="C3 Landscape",F32,IF($F$4="Default Settings",G32,IF($F$4="Birds in Flight",H32,IF($F$4="Birds Perched",I32,IF($F$4="Fireworks",J32,IF($F$4="Landscape",K32,IF($F$4="Macro",L32,IF($F$4="People",M32,IF($F$4="Sports",N32,IF($F$4="Travel",O32,IF($F$4="Waterdrops",P32,IF($F$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W32" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D32,IF($G$4="C2 Birds in Flight",E32,IF($G$4="C3 Landscape",F32,IF($G$4="Default Settings",G32,IF($G$4="Birds in Flight",H32,IF($G$4="Birds Perched",I32,IF($G$4="Fireworks",J32,IF($G$4="Landscape",K32,IF($G$4="Macro",L32,IF($G$4="People",M32,IF($G$4="Sports",N32,IF($G$4="Travel",O32,IF($G$4="Waterdrops",P32,IF($G$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X32" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D32,IF($H$4="C2 Birds in Flight",E32,IF($H$4="C3 Landscape",F32,IF($H$4="Default Settings",G32,IF($H$4="Birds in Flight",H32,IF($H$4="Birds Perched",I32,IF($H$4="Fireworks",J32,IF($H$4="Landscape",K32,IF($H$4="Macro",L32,IF($H$4="People",M32,IF($H$4="Sports",N32,IF($H$4="Travel",O32,IF($H$4="Waterdrops",P32,IF($H$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Y32" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D32,IF($I$4="C2 Birds in Flight",E32,IF($I$4="C3 Landscape",F32,IF($I$4="Default Settings",G32,IF($I$4="Birds in Flight",H32,IF($I$4="Birds Perched",I32,IF($I$4="Fireworks",J32,IF($I$4="Landscape",K32,IF($I$4="Macro",L32,IF($I$4="People",M32,IF($I$4="Sports",N32,IF($I$4="Travel",O32,IF($I$4="Waterdrops",P32,IF($I$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z32" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D32,IF($J$4="C2 Birds in Flight",E32,IF($J$4="C3 Landscape",F32,IF($J$4="Default Settings",G32,IF($J$4="Birds in Flight",H32,IF($J$4="Birds Perched",I32,IF($J$4="Fireworks",J32,IF($J$4="Landscape",K32,IF($J$4="Macro",L32,IF($J$4="People",M32,IF($J$4="Sports",N32,IF($J$4="Travel",O32,IF($J$4="Waterdrops",P32,IF($J$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AA32" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D32,IF($K$4="C2 Birds in Flight",E32,IF($K$4="C3 Landscape",F32,IF($K$4="Default Settings",G32,IF($K$4="Birds in Flight",H32,IF($K$4="Birds Perched",I32,IF($K$4="Fireworks",J32,IF($K$4="Landscape",K32,IF($K$4="Macro",L32,IF($K$4="People",M32,IF($K$4="Sports",N32,IF($K$4="Travel",O32,IF($K$4="Waterdrops",P32,IF($K$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB32" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D32,IF($L$4="C2 Birds in Flight",E32,IF($L$4="C3 Landscape",F32,IF($L$4="Default Settings",G32,IF($L$4="Birds in Flight",H32,IF($L$4="Birds Perched",I32,IF($L$4="Fireworks",J32,IF($L$4="Landscape",K32,IF($L$4="Macro",L32,IF($L$4="People",M32,IF($L$4="Sports",N32,IF($L$4="Travel",O32,IF($L$4="Waterdrops",P32,IF($L$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="AC32" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D32,IF($M$4="C2 Birds in Flight",E32,IF($M$4="C3 Landscape",F32,IF($M$4="Default Settings",G32,IF($M$4="Birds in Flight",H32,IF($M$4="Birds Perched",I32,IF($M$4="Fireworks",J32,IF($M$4="Landscape",K32,IF($M$4="Macro",L32,IF($M$4="People",M32,IF($M$4="Sports",N32,IF($M$4="Travel",O32,IF($M$4="Waterdrops",P32,IF($M$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD32" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D32,IF($N$4="C2 Birds in Flight",E32,IF($N$4="C3 Landscape",F32,IF($N$4="Default Settings",G32,IF($N$4="Birds in Flight",H32,IF($N$4="Birds Perched",I32,IF($N$4="Fireworks",J32,IF($N$4="Landscape",K32,IF($N$4="Macro",L32,IF($N$4="People",M32,IF($N$4="Sports",N32,IF($N$4="Travel",O32,IF($N$4="Waterdrops",P32,IF($N$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AE32" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D32,IF($O$4="C2 Birds in Flight",E32,IF($O$4="C3 Landscape",F32,IF($O$4="Default Settings",G32,IF($O$4="Birds in Flight",H32,IF($O$4="Birds Perched",I32,IF($O$4="Fireworks",J32,IF($O$4="Landscape",K32,IF($O$4="Macro",L32,IF($O$4="People",M32,IF($O$4="Sports",N32,IF($O$4="Travel",O32,IF($O$4="Waterdrops",P32,IF($O$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AF32" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D32,IF($P$4="C2 Birds in Flight",E32,IF($P$4="C3 Landscape",F32,IF($P$4="Default Settings",G32,IF($P$4="Birds in Flight",H32,IF($P$4="Birds Perched",I32,IF($P$4="Fireworks",J32,IF($P$4="Landscape",K32,IF($P$4="Macro",L32,IF($P$4="People",M32,IF($P$4="Sports",N32,IF($P$4="Travel",O32,IF($P$4="Waterdrops",P32,IF($P$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AG32" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D32,IF($Q$4="C2 Birds in Flight",E32,IF($Q$4="C3 Landscape",F32,IF($Q$4="Default Settings",G32,IF($Q$4="Birds in Flight",H32,IF($Q$4="Birds Perched",I32,IF($Q$4="Fireworks",J32,IF($Q$4="Landscape",K32,IF($Q$4="Macro",L32,IF($Q$4="People",M32,IF($Q$4="Sports",N32,IF($Q$4="Travel",O32,IF($Q$4="Waterdrops",P32,IF($Q$4="Wildlife",Q32,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" hidden="0">
+      <x:c r="A33" s="12" t="str">
+        <x:v>Shooting 4 &gt; Long exp. noise reduction</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>Full camera menu</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="str">
+        <x:v>Long Exposure NR</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="H33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="I33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="J33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="M33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="N33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="O33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="P33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q33" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="R33" s="20" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S33" s="20" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="T33" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D33,IF($D$4="C2 Birds in Flight",E33,IF($D$4="C3 Landscape",F33,IF($D$4="Default Settings",G33,IF($D$4="Birds in Flight",H33,IF($D$4="Birds Perched",I33,IF($D$4="Fireworks",J33,IF($D$4="Landscape",K33,IF($D$4="Macro",L33,IF($D$4="People",M33,IF($D$4="Sports",N33,IF($D$4="Travel",O33,IF($D$4="Waterdrops",P33,IF($D$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U33" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D33,IF($E$4="C2 Birds in Flight",E33,IF($E$4="C3 Landscape",F33,IF($E$4="Default Settings",G33,IF($E$4="Birds in Flight",H33,IF($E$4="Birds Perched",I33,IF($E$4="Fireworks",J33,IF($E$4="Landscape",K33,IF($E$4="Macro",L33,IF($E$4="People",M33,IF($E$4="Sports",N33,IF($E$4="Travel",O33,IF($E$4="Waterdrops",P33,IF($E$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V33" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D33,IF($F$4="C2 Birds in Flight",E33,IF($F$4="C3 Landscape",F33,IF($F$4="Default Settings",G33,IF($F$4="Birds in Flight",H33,IF($F$4="Birds Perched",I33,IF($F$4="Fireworks",J33,IF($F$4="Landscape",K33,IF($F$4="Macro",L33,IF($F$4="People",M33,IF($F$4="Sports",N33,IF($F$4="Travel",O33,IF($F$4="Waterdrops",P33,IF($F$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="W33" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D33,IF($G$4="C2 Birds in Flight",E33,IF($G$4="C3 Landscape",F33,IF($G$4="Default Settings",G33,IF($G$4="Birds in Flight",H33,IF($G$4="Birds Perched",I33,IF($G$4="Fireworks",J33,IF($G$4="Landscape",K33,IF($G$4="Macro",L33,IF($G$4="People",M33,IF($G$4="Sports",N33,IF($G$4="Travel",O33,IF($G$4="Waterdrops",P33,IF($G$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="X33" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D33,IF($H$4="C2 Birds in Flight",E33,IF($H$4="C3 Landscape",F33,IF($H$4="Default Settings",G33,IF($H$4="Birds in Flight",H33,IF($H$4="Birds Perched",I33,IF($H$4="Fireworks",J33,IF($H$4="Landscape",K33,IF($H$4="Macro",L33,IF($H$4="People",M33,IF($H$4="Sports",N33,IF($H$4="Travel",O33,IF($H$4="Waterdrops",P33,IF($H$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Y33" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D33,IF($I$4="C2 Birds in Flight",E33,IF($I$4="C3 Landscape",F33,IF($I$4="Default Settings",G33,IF($I$4="Birds in Flight",H33,IF($I$4="Birds Perched",I33,IF($I$4="Fireworks",J33,IF($I$4="Landscape",K33,IF($I$4="Macro",L33,IF($I$4="People",M33,IF($I$4="Sports",N33,IF($I$4="Travel",O33,IF($I$4="Waterdrops",P33,IF($I$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Z33" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D33,IF($J$4="C2 Birds in Flight",E33,IF($J$4="C3 Landscape",F33,IF($J$4="Default Settings",G33,IF($J$4="Birds in Flight",H33,IF($J$4="Birds Perched",I33,IF($J$4="Fireworks",J33,IF($J$4="Landscape",K33,IF($J$4="Macro",L33,IF($J$4="People",M33,IF($J$4="Sports",N33,IF($J$4="Travel",O33,IF($J$4="Waterdrops",P33,IF($J$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA33" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D33,IF($K$4="C2 Birds in Flight",E33,IF($K$4="C3 Landscape",F33,IF($K$4="Default Settings",G33,IF($K$4="Birds in Flight",H33,IF($K$4="Birds Perched",I33,IF($K$4="Fireworks",J33,IF($K$4="Landscape",K33,IF($K$4="Macro",L33,IF($K$4="People",M33,IF($K$4="Sports",N33,IF($K$4="Travel",O33,IF($K$4="Waterdrops",P33,IF($K$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AB33" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D33,IF($L$4="C2 Birds in Flight",E33,IF($L$4="C3 Landscape",F33,IF($L$4="Default Settings",G33,IF($L$4="Birds in Flight",H33,IF($L$4="Birds Perched",I33,IF($L$4="Fireworks",J33,IF($L$4="Landscape",K33,IF($L$4="Macro",L33,IF($L$4="People",M33,IF($L$4="Sports",N33,IF($L$4="Travel",O33,IF($L$4="Waterdrops",P33,IF($L$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AC33" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D33,IF($M$4="C2 Birds in Flight",E33,IF($M$4="C3 Landscape",F33,IF($M$4="Default Settings",G33,IF($M$4="Birds in Flight",H33,IF($M$4="Birds Perched",I33,IF($M$4="Fireworks",J33,IF($M$4="Landscape",K33,IF($M$4="Macro",L33,IF($M$4="People",M33,IF($M$4="Sports",N33,IF($M$4="Travel",O33,IF($M$4="Waterdrops",P33,IF($M$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AD33" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D33,IF($N$4="C2 Birds in Flight",E33,IF($N$4="C3 Landscape",F33,IF($N$4="Default Settings",G33,IF($N$4="Birds in Flight",H33,IF($N$4="Birds Perched",I33,IF($N$4="Fireworks",J33,IF($N$4="Landscape",K33,IF($N$4="Macro",L33,IF($N$4="People",M33,IF($N$4="Sports",N33,IF($N$4="Travel",O33,IF($N$4="Waterdrops",P33,IF($N$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AE33" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D33,IF($O$4="C2 Birds in Flight",E33,IF($O$4="C3 Landscape",F33,IF($O$4="Default Settings",G33,IF($O$4="Birds in Flight",H33,IF($O$4="Birds Perched",I33,IF($O$4="Fireworks",J33,IF($O$4="Landscape",K33,IF($O$4="Macro",L33,IF($O$4="People",M33,IF($O$4="Sports",N33,IF($O$4="Travel",O33,IF($O$4="Waterdrops",P33,IF($O$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AF33" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D33,IF($P$4="C2 Birds in Flight",E33,IF($P$4="C3 Landscape",F33,IF($P$4="Default Settings",G33,IF($P$4="Birds in Flight",H33,IF($P$4="Birds Perched",I33,IF($P$4="Fireworks",J33,IF($P$4="Landscape",K33,IF($P$4="Macro",L33,IF($P$4="People",M33,IF($P$4="Sports",N33,IF($P$4="Travel",O33,IF($P$4="Waterdrops",P33,IF($P$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG33" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D33,IF($Q$4="C2 Birds in Flight",E33,IF($Q$4="C3 Landscape",F33,IF($Q$4="Default Settings",G33,IF($Q$4="Birds in Flight",H33,IF($Q$4="Birds Perched",I33,IF($Q$4="Fireworks",J33,IF($Q$4="Landscape",K33,IF($Q$4="Macro",L33,IF($Q$4="People",M33,IF($Q$4="Sports",N33,IF($Q$4="Travel",O33,IF($Q$4="Waterdrops",P33,IF($Q$4="Wildlife",Q33,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" hidden="0">
+      <x:c r="A34" s="12" t="str">
+        <x:v>Shooting 7 &gt; Shooting info. disp. &gt; Screen info. settings</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>Set once</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="str">
+        <x:v>Screen Info</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="E34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="H34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="I34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="J34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="K34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="L34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="M34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="N34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="O34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="P34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="Q34" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="R34" s="20" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="S34" s="20" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="T34" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D34,IF($D$4="C2 Birds in Flight",E34,IF($D$4="C3 Landscape",F34,IF($D$4="Default Settings",G34,IF($D$4="Birds in Flight",H34,IF($D$4="Birds Perched",I34,IF($D$4="Fireworks",J34,IF($D$4="Landscape",K34,IF($D$4="Macro",L34,IF($D$4="People",M34,IF($D$4="Sports",N34,IF($D$4="Travel",O34,IF($D$4="Waterdrops",P34,IF($D$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="U34" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D34,IF($E$4="C2 Birds in Flight",E34,IF($E$4="C3 Landscape",F34,IF($E$4="Default Settings",G34,IF($E$4="Birds in Flight",H34,IF($E$4="Birds Perched",I34,IF($E$4="Fireworks",J34,IF($E$4="Landscape",K34,IF($E$4="Macro",L34,IF($E$4="People",M34,IF($E$4="Sports",N34,IF($E$4="Travel",O34,IF($E$4="Waterdrops",P34,IF($E$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="V34" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D34,IF($F$4="C2 Birds in Flight",E34,IF($F$4="C3 Landscape",F34,IF($F$4="Default Settings",G34,IF($F$4="Birds in Flight",H34,IF($F$4="Birds Perched",I34,IF($F$4="Fireworks",J34,IF($F$4="Landscape",K34,IF($F$4="Macro",L34,IF($F$4="People",M34,IF($F$4="Sports",N34,IF($F$4="Travel",O34,IF($F$4="Waterdrops",P34,IF($F$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="W34" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D34,IF($G$4="C2 Birds in Flight",E34,IF($G$4="C3 Landscape",F34,IF($G$4="Default Settings",G34,IF($G$4="Birds in Flight",H34,IF($G$4="Birds Perched",I34,IF($G$4="Fireworks",J34,IF($G$4="Landscape",K34,IF($G$4="Macro",L34,IF($G$4="People",M34,IF($G$4="Sports",N34,IF($G$4="Travel",O34,IF($G$4="Waterdrops",P34,IF($G$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="X34" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D34,IF($H$4="C2 Birds in Flight",E34,IF($H$4="C3 Landscape",F34,IF($H$4="Default Settings",G34,IF($H$4="Birds in Flight",H34,IF($H$4="Birds Perched",I34,IF($H$4="Fireworks",J34,IF($H$4="Landscape",K34,IF($H$4="Macro",L34,IF($H$4="People",M34,IF($H$4="Sports",N34,IF($H$4="Travel",O34,IF($H$4="Waterdrops",P34,IF($H$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="Y34" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D34,IF($I$4="C2 Birds in Flight",E34,IF($I$4="C3 Landscape",F34,IF($I$4="Default Settings",G34,IF($I$4="Birds in Flight",H34,IF($I$4="Birds Perched",I34,IF($I$4="Fireworks",J34,IF($I$4="Landscape",K34,IF($I$4="Macro",L34,IF($I$4="People",M34,IF($I$4="Sports",N34,IF($I$4="Travel",O34,IF($I$4="Waterdrops",P34,IF($I$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="Z34" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D34,IF($J$4="C2 Birds in Flight",E34,IF($J$4="C3 Landscape",F34,IF($J$4="Default Settings",G34,IF($J$4="Birds in Flight",H34,IF($J$4="Birds Perched",I34,IF($J$4="Fireworks",J34,IF($J$4="Landscape",K34,IF($J$4="Macro",L34,IF($J$4="People",M34,IF($J$4="Sports",N34,IF($J$4="Travel",O34,IF($J$4="Waterdrops",P34,IF($J$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AA34" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D34,IF($K$4="C2 Birds in Flight",E34,IF($K$4="C3 Landscape",F34,IF($K$4="Default Settings",G34,IF($K$4="Birds in Flight",H34,IF($K$4="Birds Perched",I34,IF($K$4="Fireworks",J34,IF($K$4="Landscape",K34,IF($K$4="Macro",L34,IF($K$4="People",M34,IF($K$4="Sports",N34,IF($K$4="Travel",O34,IF($K$4="Waterdrops",P34,IF($K$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AB34" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D34,IF($L$4="C2 Birds in Flight",E34,IF($L$4="C3 Landscape",F34,IF($L$4="Default Settings",G34,IF($L$4="Birds in Flight",H34,IF($L$4="Birds Perched",I34,IF($L$4="Fireworks",J34,IF($L$4="Landscape",K34,IF($L$4="Macro",L34,IF($L$4="People",M34,IF($L$4="Sports",N34,IF($L$4="Travel",O34,IF($L$4="Waterdrops",P34,IF($L$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AC34" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D34,IF($M$4="C2 Birds in Flight",E34,IF($M$4="C3 Landscape",F34,IF($M$4="Default Settings",G34,IF($M$4="Birds in Flight",H34,IF($M$4="Birds Perched",I34,IF($M$4="Fireworks",J34,IF($M$4="Landscape",K34,IF($M$4="Macro",L34,IF($M$4="People",M34,IF($M$4="Sports",N34,IF($M$4="Travel",O34,IF($M$4="Waterdrops",P34,IF($M$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AD34" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D34,IF($N$4="C2 Birds in Flight",E34,IF($N$4="C3 Landscape",F34,IF($N$4="Default Settings",G34,IF($N$4="Birds in Flight",H34,IF($N$4="Birds Perched",I34,IF($N$4="Fireworks",J34,IF($N$4="Landscape",K34,IF($N$4="Macro",L34,IF($N$4="People",M34,IF($N$4="Sports",N34,IF($N$4="Travel",O34,IF($N$4="Waterdrops",P34,IF($N$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AE34" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D34,IF($O$4="C2 Birds in Flight",E34,IF($O$4="C3 Landscape",F34,IF($O$4="Default Settings",G34,IF($O$4="Birds in Flight",H34,IF($O$4="Birds Perched",I34,IF($O$4="Fireworks",J34,IF($O$4="Landscape",K34,IF($O$4="Macro",L34,IF($O$4="People",M34,IF($O$4="Sports",N34,IF($O$4="Travel",O34,IF($O$4="Waterdrops",P34,IF($O$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AF34" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D34,IF($P$4="C2 Birds in Flight",E34,IF($P$4="C3 Landscape",F34,IF($P$4="Default Settings",G34,IF($P$4="Birds in Flight",H34,IF($P$4="Birds Perched",I34,IF($P$4="Fireworks",J34,IF($P$4="Landscape",K34,IF($P$4="Macro",L34,IF($P$4="People",M34,IF($P$4="Sports",N34,IF($P$4="Travel",O34,IF($P$4="Waterdrops",P34,IF($P$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="AG34" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D34,IF($Q$4="C2 Birds in Flight",E34,IF($Q$4="C3 Landscape",F34,IF($Q$4="Default Settings",G34,IF($Q$4="Birds in Flight",H34,IF($Q$4="Birds Perched",I34,IF($Q$4="Fireworks",J34,IF($Q$4="Landscape",K34,IF($Q$4="Macro",L34,IF($Q$4="People",M34,IF($Q$4="Sports",N34,IF($Q$4="Travel",O34,IF($Q$4="Waterdrops",P34,IF($Q$4="Wildlife",Q34,""))))))))))))))</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" hidden="0">
+      <x:c r="A35" s="12" t="str">
+        <x:v>Shooting 7 &gt; Shooting info. disp. &gt; Histogram disp</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>Set once</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="str">
+        <x:v>Histogram</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="H35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="I35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="J35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="K35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="L35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="M35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="N35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="O35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="P35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="Q35" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="R35" s="20" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S35" s="20" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="T35" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D35,IF($D$4="C2 Birds in Flight",E35,IF($D$4="C3 Landscape",F35,IF($D$4="Default Settings",G35,IF($D$4="Birds in Flight",H35,IF($D$4="Birds Perched",I35,IF($D$4="Fireworks",J35,IF($D$4="Landscape",K35,IF($D$4="Macro",L35,IF($D$4="People",M35,IF($D$4="Sports",N35,IF($D$4="Travel",O35,IF($D$4="Waterdrops",P35,IF($D$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="U35" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D35,IF($E$4="C2 Birds in Flight",E35,IF($E$4="C3 Landscape",F35,IF($E$4="Default Settings",G35,IF($E$4="Birds in Flight",H35,IF($E$4="Birds Perched",I35,IF($E$4="Fireworks",J35,IF($E$4="Landscape",K35,IF($E$4="Macro",L35,IF($E$4="People",M35,IF($E$4="Sports",N35,IF($E$4="Travel",O35,IF($E$4="Waterdrops",P35,IF($E$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="V35" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D35,IF($F$4="C2 Birds in Flight",E35,IF($F$4="C3 Landscape",F35,IF($F$4="Default Settings",G35,IF($F$4="Birds in Flight",H35,IF($F$4="Birds Perched",I35,IF($F$4="Fireworks",J35,IF($F$4="Landscape",K35,IF($F$4="Macro",L35,IF($F$4="People",M35,IF($F$4="Sports",N35,IF($F$4="Travel",O35,IF($F$4="Waterdrops",P35,IF($F$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="W35" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D35,IF($G$4="C2 Birds in Flight",E35,IF($G$4="C3 Landscape",F35,IF($G$4="Default Settings",G35,IF($G$4="Birds in Flight",H35,IF($G$4="Birds Perched",I35,IF($G$4="Fireworks",J35,IF($G$4="Landscape",K35,IF($G$4="Macro",L35,IF($G$4="People",M35,IF($G$4="Sports",N35,IF($G$4="Travel",O35,IF($G$4="Waterdrops",P35,IF($G$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="X35" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D35,IF($H$4="C2 Birds in Flight",E35,IF($H$4="C3 Landscape",F35,IF($H$4="Default Settings",G35,IF($H$4="Birds in Flight",H35,IF($H$4="Birds Perched",I35,IF($H$4="Fireworks",J35,IF($H$4="Landscape",K35,IF($H$4="Macro",L35,IF($H$4="People",M35,IF($H$4="Sports",N35,IF($H$4="Travel",O35,IF($H$4="Waterdrops",P35,IF($H$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="Y35" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D35,IF($I$4="C2 Birds in Flight",E35,IF($I$4="C3 Landscape",F35,IF($I$4="Default Settings",G35,IF($I$4="Birds in Flight",H35,IF($I$4="Birds Perched",I35,IF($I$4="Fireworks",J35,IF($I$4="Landscape",K35,IF($I$4="Macro",L35,IF($I$4="People",M35,IF($I$4="Sports",N35,IF($I$4="Travel",O35,IF($I$4="Waterdrops",P35,IF($I$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="Z35" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D35,IF($J$4="C2 Birds in Flight",E35,IF($J$4="C3 Landscape",F35,IF($J$4="Default Settings",G35,IF($J$4="Birds in Flight",H35,IF($J$4="Birds Perched",I35,IF($J$4="Fireworks",J35,IF($J$4="Landscape",K35,IF($J$4="Macro",L35,IF($J$4="People",M35,IF($J$4="Sports",N35,IF($J$4="Travel",O35,IF($J$4="Waterdrops",P35,IF($J$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AA35" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D35,IF($K$4="C2 Birds in Flight",E35,IF($K$4="C3 Landscape",F35,IF($K$4="Default Settings",G35,IF($K$4="Birds in Flight",H35,IF($K$4="Birds Perched",I35,IF($K$4="Fireworks",J35,IF($K$4="Landscape",K35,IF($K$4="Macro",L35,IF($K$4="People",M35,IF($K$4="Sports",N35,IF($K$4="Travel",O35,IF($K$4="Waterdrops",P35,IF($K$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AB35" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D35,IF($L$4="C2 Birds in Flight",E35,IF($L$4="C3 Landscape",F35,IF($L$4="Default Settings",G35,IF($L$4="Birds in Flight",H35,IF($L$4="Birds Perched",I35,IF($L$4="Fireworks",J35,IF($L$4="Landscape",K35,IF($L$4="Macro",L35,IF($L$4="People",M35,IF($L$4="Sports",N35,IF($L$4="Travel",O35,IF($L$4="Waterdrops",P35,IF($L$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AC35" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D35,IF($M$4="C2 Birds in Flight",E35,IF($M$4="C3 Landscape",F35,IF($M$4="Default Settings",G35,IF($M$4="Birds in Flight",H35,IF($M$4="Birds Perched",I35,IF($M$4="Fireworks",J35,IF($M$4="Landscape",K35,IF($M$4="Macro",L35,IF($M$4="People",M35,IF($M$4="Sports",N35,IF($M$4="Travel",O35,IF($M$4="Waterdrops",P35,IF($M$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AD35" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D35,IF($N$4="C2 Birds in Flight",E35,IF($N$4="C3 Landscape",F35,IF($N$4="Default Settings",G35,IF($N$4="Birds in Flight",H35,IF($N$4="Birds Perched",I35,IF($N$4="Fireworks",J35,IF($N$4="Landscape",K35,IF($N$4="Macro",L35,IF($N$4="People",M35,IF($N$4="Sports",N35,IF($N$4="Travel",O35,IF($N$4="Waterdrops",P35,IF($N$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AE35" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D35,IF($O$4="C2 Birds in Flight",E35,IF($O$4="C3 Landscape",F35,IF($O$4="Default Settings",G35,IF($O$4="Birds in Flight",H35,IF($O$4="Birds Perched",I35,IF($O$4="Fireworks",J35,IF($O$4="Landscape",K35,IF($O$4="Macro",L35,IF($O$4="People",M35,IF($O$4="Sports",N35,IF($O$4="Travel",O35,IF($O$4="Waterdrops",P35,IF($O$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AF35" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D35,IF($P$4="C2 Birds in Flight",E35,IF($P$4="C3 Landscape",F35,IF($P$4="Default Settings",G35,IF($P$4="Birds in Flight",H35,IF($P$4="Birds Perched",I35,IF($P$4="Fireworks",J35,IF($P$4="Landscape",K35,IF($P$4="Macro",L35,IF($P$4="People",M35,IF($P$4="Sports",N35,IF($P$4="Travel",O35,IF($P$4="Waterdrops",P35,IF($P$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="AG35" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D35,IF($Q$4="C2 Birds in Flight",E35,IF($Q$4="C3 Landscape",F35,IF($Q$4="Default Settings",G35,IF($Q$4="Birds in Flight",H35,IF($Q$4="Birds Perched",I35,IF($Q$4="Fireworks",J35,IF($Q$4="Landscape",K35,IF($Q$4="Macro",L35,IF($Q$4="People",M35,IF($Q$4="Sports",N35,IF($Q$4="Travel",O35,IF($Q$4="Waterdrops",P35,IF($Q$4="Wildlife",Q35,""))))))))))))))</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" hidden="0">
+      <x:c r="A36" s="12" t="str">
+        <x:v>Playback 5 &gt; Highlight alert</x:v>
+      </x:c>
+      <x:c r="B36" s="14" t="str">
+        <x:v>Set once</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="str">
+        <x:v>Highlight Alert</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="H36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="I36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="J36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="K36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="L36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="M36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="N36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="O36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="P36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="Q36" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="R36" s="20" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S36" s="20" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="T36" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D36,IF($D$4="C2 Birds in Flight",E36,IF($D$4="C3 Landscape",F36,IF($D$4="Default Settings",G36,IF($D$4="Birds in Flight",H36,IF($D$4="Birds Perched",I36,IF($D$4="Fireworks",J36,IF($D$4="Landscape",K36,IF($D$4="Macro",L36,IF($D$4="People",M36,IF($D$4="Sports",N36,IF($D$4="Travel",O36,IF($D$4="Waterdrops",P36,IF($D$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="U36" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D36,IF($E$4="C2 Birds in Flight",E36,IF($E$4="C3 Landscape",F36,IF($E$4="Default Settings",G36,IF($E$4="Birds in Flight",H36,IF($E$4="Birds Perched",I36,IF($E$4="Fireworks",J36,IF($E$4="Landscape",K36,IF($E$4="Macro",L36,IF($E$4="People",M36,IF($E$4="Sports",N36,IF($E$4="Travel",O36,IF($E$4="Waterdrops",P36,IF($E$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="V36" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D36,IF($F$4="C2 Birds in Flight",E36,IF($F$4="C3 Landscape",F36,IF($F$4="Default Settings",G36,IF($F$4="Birds in Flight",H36,IF($F$4="Birds Perched",I36,IF($F$4="Fireworks",J36,IF($F$4="Landscape",K36,IF($F$4="Macro",L36,IF($F$4="People",M36,IF($F$4="Sports",N36,IF($F$4="Travel",O36,IF($F$4="Waterdrops",P36,IF($F$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="W36" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D36,IF($G$4="C2 Birds in Flight",E36,IF($G$4="C3 Landscape",F36,IF($G$4="Default Settings",G36,IF($G$4="Birds in Flight",H36,IF($G$4="Birds Perched",I36,IF($G$4="Fireworks",J36,IF($G$4="Landscape",K36,IF($G$4="Macro",L36,IF($G$4="People",M36,IF($G$4="Sports",N36,IF($G$4="Travel",O36,IF($G$4="Waterdrops",P36,IF($G$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="X36" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D36,IF($H$4="C2 Birds in Flight",E36,IF($H$4="C3 Landscape",F36,IF($H$4="Default Settings",G36,IF($H$4="Birds in Flight",H36,IF($H$4="Birds Perched",I36,IF($H$4="Fireworks",J36,IF($H$4="Landscape",K36,IF($H$4="Macro",L36,IF($H$4="People",M36,IF($H$4="Sports",N36,IF($H$4="Travel",O36,IF($H$4="Waterdrops",P36,IF($H$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="Y36" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D36,IF($I$4="C2 Birds in Flight",E36,IF($I$4="C3 Landscape",F36,IF($I$4="Default Settings",G36,IF($I$4="Birds in Flight",H36,IF($I$4="Birds Perched",I36,IF($I$4="Fireworks",J36,IF($I$4="Landscape",K36,IF($I$4="Macro",L36,IF($I$4="People",M36,IF($I$4="Sports",N36,IF($I$4="Travel",O36,IF($I$4="Waterdrops",P36,IF($I$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="Z36" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D36,IF($J$4="C2 Birds in Flight",E36,IF($J$4="C3 Landscape",F36,IF($J$4="Default Settings",G36,IF($J$4="Birds in Flight",H36,IF($J$4="Birds Perched",I36,IF($J$4="Fireworks",J36,IF($J$4="Landscape",K36,IF($J$4="Macro",L36,IF($J$4="People",M36,IF($J$4="Sports",N36,IF($J$4="Travel",O36,IF($J$4="Waterdrops",P36,IF($J$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AA36" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D36,IF($K$4="C2 Birds in Flight",E36,IF($K$4="C3 Landscape",F36,IF($K$4="Default Settings",G36,IF($K$4="Birds in Flight",H36,IF($K$4="Birds Perched",I36,IF($K$4="Fireworks",J36,IF($K$4="Landscape",K36,IF($K$4="Macro",L36,IF($K$4="People",M36,IF($K$4="Sports",N36,IF($K$4="Travel",O36,IF($K$4="Waterdrops",P36,IF($K$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AB36" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D36,IF($L$4="C2 Birds in Flight",E36,IF($L$4="C3 Landscape",F36,IF($L$4="Default Settings",G36,IF($L$4="Birds in Flight",H36,IF($L$4="Birds Perched",I36,IF($L$4="Fireworks",J36,IF($L$4="Landscape",K36,IF($L$4="Macro",L36,IF($L$4="People",M36,IF($L$4="Sports",N36,IF($L$4="Travel",O36,IF($L$4="Waterdrops",P36,IF($L$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AC36" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D36,IF($M$4="C2 Birds in Flight",E36,IF($M$4="C3 Landscape",F36,IF($M$4="Default Settings",G36,IF($M$4="Birds in Flight",H36,IF($M$4="Birds Perched",I36,IF($M$4="Fireworks",J36,IF($M$4="Landscape",K36,IF($M$4="Macro",L36,IF($M$4="People",M36,IF($M$4="Sports",N36,IF($M$4="Travel",O36,IF($M$4="Waterdrops",P36,IF($M$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AD36" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D36,IF($N$4="C2 Birds in Flight",E36,IF($N$4="C3 Landscape",F36,IF($N$4="Default Settings",G36,IF($N$4="Birds in Flight",H36,IF($N$4="Birds Perched",I36,IF($N$4="Fireworks",J36,IF($N$4="Landscape",K36,IF($N$4="Macro",L36,IF($N$4="People",M36,IF($N$4="Sports",N36,IF($N$4="Travel",O36,IF($N$4="Waterdrops",P36,IF($N$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AE36" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D36,IF($O$4="C2 Birds in Flight",E36,IF($O$4="C3 Landscape",F36,IF($O$4="Default Settings",G36,IF($O$4="Birds in Flight",H36,IF($O$4="Birds Perched",I36,IF($O$4="Fireworks",J36,IF($O$4="Landscape",K36,IF($O$4="Macro",L36,IF($O$4="People",M36,IF($O$4="Sports",N36,IF($O$4="Travel",O36,IF($O$4="Waterdrops",P36,IF($O$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AF36" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D36,IF($P$4="C2 Birds in Flight",E36,IF($P$4="C3 Landscape",F36,IF($P$4="Default Settings",G36,IF($P$4="Birds in Flight",H36,IF($P$4="Birds Perched",I36,IF($P$4="Fireworks",J36,IF($P$4="Landscape",K36,IF($P$4="Macro",L36,IF($P$4="People",M36,IF($P$4="Sports",N36,IF($P$4="Travel",O36,IF($P$4="Waterdrops",P36,IF($P$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="AG36" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D36,IF($Q$4="C2 Birds in Flight",E36,IF($Q$4="C3 Landscape",F36,IF($Q$4="Default Settings",G36,IF($Q$4="Birds in Flight",H36,IF($Q$4="Birds Perched",I36,IF($Q$4="Fireworks",J36,IF($Q$4="Landscape",K36,IF($Q$4="Macro",L36,IF($Q$4="People",M36,IF($Q$4="Sports",N36,IF($Q$4="Travel",O36,IF($Q$4="Waterdrops",P36,IF($Q$4="Wildlife",Q36,""))))))))))))))</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" hidden="0">
+      <x:c r="A37" s="12" t="str">
+        <x:v>Shooting 1 &gt; Image quality</x:v>
+      </x:c>
+      <x:c r="B37" s="14" t="str">
+        <x:v>Q screen</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="str">
+        <x:v>Image Quality</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="H37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="I37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="J37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="K37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="L37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="M37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="N37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="O37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="P37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="Q37" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="R37" s="20" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S37" s="20" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="T37" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D37,IF($D$4="C2 Birds in Flight",E37,IF($D$4="C3 Landscape",F37,IF($D$4="Default Settings",G37,IF($D$4="Birds in Flight",H37,IF($D$4="Birds Perched",I37,IF($D$4="Fireworks",J37,IF($D$4="Landscape",K37,IF($D$4="Macro",L37,IF($D$4="People",M37,IF($D$4="Sports",N37,IF($D$4="Travel",O37,IF($D$4="Waterdrops",P37,IF($D$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="U37" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D37,IF($E$4="C2 Birds in Flight",E37,IF($E$4="C3 Landscape",F37,IF($E$4="Default Settings",G37,IF($E$4="Birds in Flight",H37,IF($E$4="Birds Perched",I37,IF($E$4="Fireworks",J37,IF($E$4="Landscape",K37,IF($E$4="Macro",L37,IF($E$4="People",M37,IF($E$4="Sports",N37,IF($E$4="Travel",O37,IF($E$4="Waterdrops",P37,IF($E$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="V37" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D37,IF($F$4="C2 Birds in Flight",E37,IF($F$4="C3 Landscape",F37,IF($F$4="Default Settings",G37,IF($F$4="Birds in Flight",H37,IF($F$4="Birds Perched",I37,IF($F$4="Fireworks",J37,IF($F$4="Landscape",K37,IF($F$4="Macro",L37,IF($F$4="People",M37,IF($F$4="Sports",N37,IF($F$4="Travel",O37,IF($F$4="Waterdrops",P37,IF($F$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="W37" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D37,IF($G$4="C2 Birds in Flight",E37,IF($G$4="C3 Landscape",F37,IF($G$4="Default Settings",G37,IF($G$4="Birds in Flight",H37,IF($G$4="Birds Perched",I37,IF($G$4="Fireworks",J37,IF($G$4="Landscape",K37,IF($G$4="Macro",L37,IF($G$4="People",M37,IF($G$4="Sports",N37,IF($G$4="Travel",O37,IF($G$4="Waterdrops",P37,IF($G$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="X37" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D37,IF($H$4="C2 Birds in Flight",E37,IF($H$4="C3 Landscape",F37,IF($H$4="Default Settings",G37,IF($H$4="Birds in Flight",H37,IF($H$4="Birds Perched",I37,IF($H$4="Fireworks",J37,IF($H$4="Landscape",K37,IF($H$4="Macro",L37,IF($H$4="People",M37,IF($H$4="Sports",N37,IF($H$4="Travel",O37,IF($H$4="Waterdrops",P37,IF($H$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="Y37" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D37,IF($I$4="C2 Birds in Flight",E37,IF($I$4="C3 Landscape",F37,IF($I$4="Default Settings",G37,IF($I$4="Birds in Flight",H37,IF($I$4="Birds Perched",I37,IF($I$4="Fireworks",J37,IF($I$4="Landscape",K37,IF($I$4="Macro",L37,IF($I$4="People",M37,IF($I$4="Sports",N37,IF($I$4="Travel",O37,IF($I$4="Waterdrops",P37,IF($I$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="Z37" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D37,IF($J$4="C2 Birds in Flight",E37,IF($J$4="C3 Landscape",F37,IF($J$4="Default Settings",G37,IF($J$4="Birds in Flight",H37,IF($J$4="Birds Perched",I37,IF($J$4="Fireworks",J37,IF($J$4="Landscape",K37,IF($J$4="Macro",L37,IF($J$4="People",M37,IF($J$4="Sports",N37,IF($J$4="Travel",O37,IF($J$4="Waterdrops",P37,IF($J$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AA37" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D37,IF($K$4="C2 Birds in Flight",E37,IF($K$4="C3 Landscape",F37,IF($K$4="Default Settings",G37,IF($K$4="Birds in Flight",H37,IF($K$4="Birds Perched",I37,IF($K$4="Fireworks",J37,IF($K$4="Landscape",K37,IF($K$4="Macro",L37,IF($K$4="People",M37,IF($K$4="Sports",N37,IF($K$4="Travel",O37,IF($K$4="Waterdrops",P37,IF($K$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AB37" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D37,IF($L$4="C2 Birds in Flight",E37,IF($L$4="C3 Landscape",F37,IF($L$4="Default Settings",G37,IF($L$4="Birds in Flight",H37,IF($L$4="Birds Perched",I37,IF($L$4="Fireworks",J37,IF($L$4="Landscape",K37,IF($L$4="Macro",L37,IF($L$4="People",M37,IF($L$4="Sports",N37,IF($L$4="Travel",O37,IF($L$4="Waterdrops",P37,IF($L$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AC37" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D37,IF($M$4="C2 Birds in Flight",E37,IF($M$4="C3 Landscape",F37,IF($M$4="Default Settings",G37,IF($M$4="Birds in Flight",H37,IF($M$4="Birds Perched",I37,IF($M$4="Fireworks",J37,IF($M$4="Landscape",K37,IF($M$4="Macro",L37,IF($M$4="People",M37,IF($M$4="Sports",N37,IF($M$4="Travel",O37,IF($M$4="Waterdrops",P37,IF($M$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AD37" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D37,IF($N$4="C2 Birds in Flight",E37,IF($N$4="C3 Landscape",F37,IF($N$4="Default Settings",G37,IF($N$4="Birds in Flight",H37,IF($N$4="Birds Perched",I37,IF($N$4="Fireworks",J37,IF($N$4="Landscape",K37,IF($N$4="Macro",L37,IF($N$4="People",M37,IF($N$4="Sports",N37,IF($N$4="Travel",O37,IF($N$4="Waterdrops",P37,IF($N$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AE37" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D37,IF($O$4="C2 Birds in Flight",E37,IF($O$4="C3 Landscape",F37,IF($O$4="Default Settings",G37,IF($O$4="Birds in Flight",H37,IF($O$4="Birds Perched",I37,IF($O$4="Fireworks",J37,IF($O$4="Landscape",K37,IF($O$4="Macro",L37,IF($O$4="People",M37,IF($O$4="Sports",N37,IF($O$4="Travel",O37,IF($O$4="Waterdrops",P37,IF($O$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AF37" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D37,IF($P$4="C2 Birds in Flight",E37,IF($P$4="C3 Landscape",F37,IF($P$4="Default Settings",G37,IF($P$4="Birds in Flight",H37,IF($P$4="Birds Perched",I37,IF($P$4="Fireworks",J37,IF($P$4="Landscape",K37,IF($P$4="Macro",L37,IF($P$4="People",M37,IF($P$4="Sports",N37,IF($P$4="Travel",O37,IF($P$4="Waterdrops",P37,IF($P$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="AG37" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D37,IF($Q$4="C2 Birds in Flight",E37,IF($Q$4="C3 Landscape",F37,IF($Q$4="Default Settings",G37,IF($Q$4="Birds in Flight",H37,IF($Q$4="Birds Perched",I37,IF($Q$4="Fireworks",J37,IF($Q$4="Landscape",K37,IF($Q$4="Macro",L37,IF($Q$4="People",M37,IF($Q$4="Sports",N37,IF($Q$4="Travel",O37,IF($Q$4="Waterdrops",P37,IF($Q$4="Wildlife",Q37,""))))))))))))))</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" hidden="0">
+      <x:c r="A38" s="12" t="str">
+        <x:v>Shooting 1 &gt; Cropping/aspect ratio</x:v>
+      </x:c>
+      <x:c r="B38" s="14" t="str">
+        <x:v>MM-SWITCH</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="str">
+        <x:v>Crop / Aspect</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="H38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="I38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="J38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="K38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="L38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="M38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="N38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="O38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="P38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="Q38" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="R38" s="20" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S38" s="20" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="T38" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D38,IF($D$4="C2 Birds in Flight",E38,IF($D$4="C3 Landscape",F38,IF($D$4="Default Settings",G38,IF($D$4="Birds in Flight",H38,IF($D$4="Birds Perched",I38,IF($D$4="Fireworks",J38,IF($D$4="Landscape",K38,IF($D$4="Macro",L38,IF($D$4="People",M38,IF($D$4="Sports",N38,IF($D$4="Travel",O38,IF($D$4="Waterdrops",P38,IF($D$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="U38" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D38,IF($E$4="C2 Birds in Flight",E38,IF($E$4="C3 Landscape",F38,IF($E$4="Default Settings",G38,IF($E$4="Birds in Flight",H38,IF($E$4="Birds Perched",I38,IF($E$4="Fireworks",J38,IF($E$4="Landscape",K38,IF($E$4="Macro",L38,IF($E$4="People",M38,IF($E$4="Sports",N38,IF($E$4="Travel",O38,IF($E$4="Waterdrops",P38,IF($E$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="V38" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D38,IF($F$4="C2 Birds in Flight",E38,IF($F$4="C3 Landscape",F38,IF($F$4="Default Settings",G38,IF($F$4="Birds in Flight",H38,IF($F$4="Birds Perched",I38,IF($F$4="Fireworks",J38,IF($F$4="Landscape",K38,IF($F$4="Macro",L38,IF($F$4="People",M38,IF($F$4="Sports",N38,IF($F$4="Travel",O38,IF($F$4="Waterdrops",P38,IF($F$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="W38" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D38,IF($G$4="C2 Birds in Flight",E38,IF($G$4="C3 Landscape",F38,IF($G$4="Default Settings",G38,IF($G$4="Birds in Flight",H38,IF($G$4="Birds Perched",I38,IF($G$4="Fireworks",J38,IF($G$4="Landscape",K38,IF($G$4="Macro",L38,IF($G$4="People",M38,IF($G$4="Sports",N38,IF($G$4="Travel",O38,IF($G$4="Waterdrops",P38,IF($G$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="X38" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D38,IF($H$4="C2 Birds in Flight",E38,IF($H$4="C3 Landscape",F38,IF($H$4="Default Settings",G38,IF($H$4="Birds in Flight",H38,IF($H$4="Birds Perched",I38,IF($H$4="Fireworks",J38,IF($H$4="Landscape",K38,IF($H$4="Macro",L38,IF($H$4="People",M38,IF($H$4="Sports",N38,IF($H$4="Travel",O38,IF($H$4="Waterdrops",P38,IF($H$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="Y38" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D38,IF($I$4="C2 Birds in Flight",E38,IF($I$4="C3 Landscape",F38,IF($I$4="Default Settings",G38,IF($I$4="Birds in Flight",H38,IF($I$4="Birds Perched",I38,IF($I$4="Fireworks",J38,IF($I$4="Landscape",K38,IF($I$4="Macro",L38,IF($I$4="People",M38,IF($I$4="Sports",N38,IF($I$4="Travel",O38,IF($I$4="Waterdrops",P38,IF($I$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="Z38" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D38,IF($J$4="C2 Birds in Flight",E38,IF($J$4="C3 Landscape",F38,IF($J$4="Default Settings",G38,IF($J$4="Birds in Flight",H38,IF($J$4="Birds Perched",I38,IF($J$4="Fireworks",J38,IF($J$4="Landscape",K38,IF($J$4="Macro",L38,IF($J$4="People",M38,IF($J$4="Sports",N38,IF($J$4="Travel",O38,IF($J$4="Waterdrops",P38,IF($J$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AA38" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D38,IF($K$4="C2 Birds in Flight",E38,IF($K$4="C3 Landscape",F38,IF($K$4="Default Settings",G38,IF($K$4="Birds in Flight",H38,IF($K$4="Birds Perched",I38,IF($K$4="Fireworks",J38,IF($K$4="Landscape",K38,IF($K$4="Macro",L38,IF($K$4="People",M38,IF($K$4="Sports",N38,IF($K$4="Travel",O38,IF($K$4="Waterdrops",P38,IF($K$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AB38" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D38,IF($L$4="C2 Birds in Flight",E38,IF($L$4="C3 Landscape",F38,IF($L$4="Default Settings",G38,IF($L$4="Birds in Flight",H38,IF($L$4="Birds Perched",I38,IF($L$4="Fireworks",J38,IF($L$4="Landscape",K38,IF($L$4="Macro",L38,IF($L$4="People",M38,IF($L$4="Sports",N38,IF($L$4="Travel",O38,IF($L$4="Waterdrops",P38,IF($L$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AC38" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D38,IF($M$4="C2 Birds in Flight",E38,IF($M$4="C3 Landscape",F38,IF($M$4="Default Settings",G38,IF($M$4="Birds in Flight",H38,IF($M$4="Birds Perched",I38,IF($M$4="Fireworks",J38,IF($M$4="Landscape",K38,IF($M$4="Macro",L38,IF($M$4="People",M38,IF($M$4="Sports",N38,IF($M$4="Travel",O38,IF($M$4="Waterdrops",P38,IF($M$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AD38" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D38,IF($N$4="C2 Birds in Flight",E38,IF($N$4="C3 Landscape",F38,IF($N$4="Default Settings",G38,IF($N$4="Birds in Flight",H38,IF($N$4="Birds Perched",I38,IF($N$4="Fireworks",J38,IF($N$4="Landscape",K38,IF($N$4="Macro",L38,IF($N$4="People",M38,IF($N$4="Sports",N38,IF($N$4="Travel",O38,IF($N$4="Waterdrops",P38,IF($N$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AE38" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D38,IF($O$4="C2 Birds in Flight",E38,IF($O$4="C3 Landscape",F38,IF($O$4="Default Settings",G38,IF($O$4="Birds in Flight",H38,IF($O$4="Birds Perched",I38,IF($O$4="Fireworks",J38,IF($O$4="Landscape",K38,IF($O$4="Macro",L38,IF($O$4="People",M38,IF($O$4="Sports",N38,IF($O$4="Travel",O38,IF($O$4="Waterdrops",P38,IF($O$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AF38" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D38,IF($P$4="C2 Birds in Flight",E38,IF($P$4="C3 Landscape",F38,IF($P$4="Default Settings",G38,IF($P$4="Birds in Flight",H38,IF($P$4="Birds Perched",I38,IF($P$4="Fireworks",J38,IF($P$4="Landscape",K38,IF($P$4="Macro",L38,IF($P$4="People",M38,IF($P$4="Sports",N38,IF($P$4="Travel",O38,IF($P$4="Waterdrops",P38,IF($P$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="AG38" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D38,IF($Q$4="C2 Birds in Flight",E38,IF($Q$4="C3 Landscape",F38,IF($Q$4="Default Settings",G38,IF($Q$4="Birds in Flight",H38,IF($Q$4="Birds Perched",I38,IF($Q$4="Fireworks",J38,IF($Q$4="Landscape",K38,IF($Q$4="Macro",L38,IF($Q$4="People",M38,IF($Q$4="Sports",N38,IF($Q$4="Travel",O38,IF($Q$4="Waterdrops",P38,IF($Q$4="Wildlife",Q38,""))))))))))))))</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" hidden="0">
+      <x:c r="A39" s="12" t="str">
+        <x:v>Shooting 3 &gt; White balance</x:v>
+      </x:c>
+      <x:c r="B39" s="14" t="str">
+        <x:v>Q screen</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="str">
+        <x:v>White Balance</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="H39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="I39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="J39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="K39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="L39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="M39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="N39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="O39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="P39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="Q39" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="R39" s="20" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S39" s="20" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="T39" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D39,IF($D$4="C2 Birds in Flight",E39,IF($D$4="C3 Landscape",F39,IF($D$4="Default Settings",G39,IF($D$4="Birds in Flight",H39,IF($D$4="Birds Perched",I39,IF($D$4="Fireworks",J39,IF($D$4="Landscape",K39,IF($D$4="Macro",L39,IF($D$4="People",M39,IF($D$4="Sports",N39,IF($D$4="Travel",O39,IF($D$4="Waterdrops",P39,IF($D$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="U39" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D39,IF($E$4="C2 Birds in Flight",E39,IF($E$4="C3 Landscape",F39,IF($E$4="Default Settings",G39,IF($E$4="Birds in Flight",H39,IF($E$4="Birds Perched",I39,IF($E$4="Fireworks",J39,IF($E$4="Landscape",K39,IF($E$4="Macro",L39,IF($E$4="People",M39,IF($E$4="Sports",N39,IF($E$4="Travel",O39,IF($E$4="Waterdrops",P39,IF($E$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="V39" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D39,IF($F$4="C2 Birds in Flight",E39,IF($F$4="C3 Landscape",F39,IF($F$4="Default Settings",G39,IF($F$4="Birds in Flight",H39,IF($F$4="Birds Perched",I39,IF($F$4="Fireworks",J39,IF($F$4="Landscape",K39,IF($F$4="Macro",L39,IF($F$4="People",M39,IF($F$4="Sports",N39,IF($F$4="Travel",O39,IF($F$4="Waterdrops",P39,IF($F$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="W39" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D39,IF($G$4="C2 Birds in Flight",E39,IF($G$4="C3 Landscape",F39,IF($G$4="Default Settings",G39,IF($G$4="Birds in Flight",H39,IF($G$4="Birds Perched",I39,IF($G$4="Fireworks",J39,IF($G$4="Landscape",K39,IF($G$4="Macro",L39,IF($G$4="People",M39,IF($G$4="Sports",N39,IF($G$4="Travel",O39,IF($G$4="Waterdrops",P39,IF($G$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="X39" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D39,IF($H$4="C2 Birds in Flight",E39,IF($H$4="C3 Landscape",F39,IF($H$4="Default Settings",G39,IF($H$4="Birds in Flight",H39,IF($H$4="Birds Perched",I39,IF($H$4="Fireworks",J39,IF($H$4="Landscape",K39,IF($H$4="Macro",L39,IF($H$4="People",M39,IF($H$4="Sports",N39,IF($H$4="Travel",O39,IF($H$4="Waterdrops",P39,IF($H$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="Y39" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D39,IF($I$4="C2 Birds in Flight",E39,IF($I$4="C3 Landscape",F39,IF($I$4="Default Settings",G39,IF($I$4="Birds in Flight",H39,IF($I$4="Birds Perched",I39,IF($I$4="Fireworks",J39,IF($I$4="Landscape",K39,IF($I$4="Macro",L39,IF($I$4="People",M39,IF($I$4="Sports",N39,IF($I$4="Travel",O39,IF($I$4="Waterdrops",P39,IF($I$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="Z39" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D39,IF($J$4="C2 Birds in Flight",E39,IF($J$4="C3 Landscape",F39,IF($J$4="Default Settings",G39,IF($J$4="Birds in Flight",H39,IF($J$4="Birds Perched",I39,IF($J$4="Fireworks",J39,IF($J$4="Landscape",K39,IF($J$4="Macro",L39,IF($J$4="People",M39,IF($J$4="Sports",N39,IF($J$4="Travel",O39,IF($J$4="Waterdrops",P39,IF($J$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AA39" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D39,IF($K$4="C2 Birds in Flight",E39,IF($K$4="C3 Landscape",F39,IF($K$4="Default Settings",G39,IF($K$4="Birds in Flight",H39,IF($K$4="Birds Perched",I39,IF($K$4="Fireworks",J39,IF($K$4="Landscape",K39,IF($K$4="Macro",L39,IF($K$4="People",M39,IF($K$4="Sports",N39,IF($K$4="Travel",O39,IF($K$4="Waterdrops",P39,IF($K$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AB39" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D39,IF($L$4="C2 Birds in Flight",E39,IF($L$4="C3 Landscape",F39,IF($L$4="Default Settings",G39,IF($L$4="Birds in Flight",H39,IF($L$4="Birds Perched",I39,IF($L$4="Fireworks",J39,IF($L$4="Landscape",K39,IF($L$4="Macro",L39,IF($L$4="People",M39,IF($L$4="Sports",N39,IF($L$4="Travel",O39,IF($L$4="Waterdrops",P39,IF($L$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AC39" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D39,IF($M$4="C2 Birds in Flight",E39,IF($M$4="C3 Landscape",F39,IF($M$4="Default Settings",G39,IF($M$4="Birds in Flight",H39,IF($M$4="Birds Perched",I39,IF($M$4="Fireworks",J39,IF($M$4="Landscape",K39,IF($M$4="Macro",L39,IF($M$4="People",M39,IF($M$4="Sports",N39,IF($M$4="Travel",O39,IF($M$4="Waterdrops",P39,IF($M$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AD39" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D39,IF($N$4="C2 Birds in Flight",E39,IF($N$4="C3 Landscape",F39,IF($N$4="Default Settings",G39,IF($N$4="Birds in Flight",H39,IF($N$4="Birds Perched",I39,IF($N$4="Fireworks",J39,IF($N$4="Landscape",K39,IF($N$4="Macro",L39,IF($N$4="People",M39,IF($N$4="Sports",N39,IF($N$4="Travel",O39,IF($N$4="Waterdrops",P39,IF($N$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AE39" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D39,IF($O$4="C2 Birds in Flight",E39,IF($O$4="C3 Landscape",F39,IF($O$4="Default Settings",G39,IF($O$4="Birds in Flight",H39,IF($O$4="Birds Perched",I39,IF($O$4="Fireworks",J39,IF($O$4="Landscape",K39,IF($O$4="Macro",L39,IF($O$4="People",M39,IF($O$4="Sports",N39,IF($O$4="Travel",O39,IF($O$4="Waterdrops",P39,IF($O$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AF39" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D39,IF($P$4="C2 Birds in Flight",E39,IF($P$4="C3 Landscape",F39,IF($P$4="Default Settings",G39,IF($P$4="Birds in Flight",H39,IF($P$4="Birds Perched",I39,IF($P$4="Fireworks",J39,IF($P$4="Landscape",K39,IF($P$4="Macro",L39,IF($P$4="People",M39,IF($P$4="Sports",N39,IF($P$4="Travel",O39,IF($P$4="Waterdrops",P39,IF($P$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="AG39" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D39,IF($Q$4="C2 Birds in Flight",E39,IF($Q$4="C3 Landscape",F39,IF($Q$4="Default Settings",G39,IF($Q$4="Birds in Flight",H39,IF($Q$4="Birds Perched",I39,IF($Q$4="Fireworks",J39,IF($Q$4="Landscape",K39,IF($Q$4="Macro",L39,IF($Q$4="People",M39,IF($Q$4="Sports",N39,IF($Q$4="Travel",O39,IF($Q$4="Waterdrops",P39,IF($Q$4="Wildlife",Q39,""))))))))))))))</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" hidden="0">
+      <x:c r="A40" s="12" t="str">
+        <x:v>Shooting 3 &gt; Picture Style</x:v>
+      </x:c>
+      <x:c r="B40" s="14" t="str">
+        <x:v>Q screen</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="str">
+        <x:v>Picture Style</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="H40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="I40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="J40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="K40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="L40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="M40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="N40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="O40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="P40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="Q40" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="R40" s="20" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S40" s="20" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="T40" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D40,IF($D$4="C2 Birds in Flight",E40,IF($D$4="C3 Landscape",F40,IF($D$4="Default Settings",G40,IF($D$4="Birds in Flight",H40,IF($D$4="Birds Perched",I40,IF($D$4="Fireworks",J40,IF($D$4="Landscape",K40,IF($D$4="Macro",L40,IF($D$4="People",M40,IF($D$4="Sports",N40,IF($D$4="Travel",O40,IF($D$4="Waterdrops",P40,IF($D$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="U40" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D40,IF($E$4="C2 Birds in Flight",E40,IF($E$4="C3 Landscape",F40,IF($E$4="Default Settings",G40,IF($E$4="Birds in Flight",H40,IF($E$4="Birds Perched",I40,IF($E$4="Fireworks",J40,IF($E$4="Landscape",K40,IF($E$4="Macro",L40,IF($E$4="People",M40,IF($E$4="Sports",N40,IF($E$4="Travel",O40,IF($E$4="Waterdrops",P40,IF($E$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="V40" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D40,IF($F$4="C2 Birds in Flight",E40,IF($F$4="C3 Landscape",F40,IF($F$4="Default Settings",G40,IF($F$4="Birds in Flight",H40,IF($F$4="Birds Perched",I40,IF($F$4="Fireworks",J40,IF($F$4="Landscape",K40,IF($F$4="Macro",L40,IF($F$4="People",M40,IF($F$4="Sports",N40,IF($F$4="Travel",O40,IF($F$4="Waterdrops",P40,IF($F$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="W40" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D40,IF($G$4="C2 Birds in Flight",E40,IF($G$4="C3 Landscape",F40,IF($G$4="Default Settings",G40,IF($G$4="Birds in Flight",H40,IF($G$4="Birds Perched",I40,IF($G$4="Fireworks",J40,IF($G$4="Landscape",K40,IF($G$4="Macro",L40,IF($G$4="People",M40,IF($G$4="Sports",N40,IF($G$4="Travel",O40,IF($G$4="Waterdrops",P40,IF($G$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="X40" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D40,IF($H$4="C2 Birds in Flight",E40,IF($H$4="C3 Landscape",F40,IF($H$4="Default Settings",G40,IF($H$4="Birds in Flight",H40,IF($H$4="Birds Perched",I40,IF($H$4="Fireworks",J40,IF($H$4="Landscape",K40,IF($H$4="Macro",L40,IF($H$4="People",M40,IF($H$4="Sports",N40,IF($H$4="Travel",O40,IF($H$4="Waterdrops",P40,IF($H$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="Y40" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D40,IF($I$4="C2 Birds in Flight",E40,IF($I$4="C3 Landscape",F40,IF($I$4="Default Settings",G40,IF($I$4="Birds in Flight",H40,IF($I$4="Birds Perched",I40,IF($I$4="Fireworks",J40,IF($I$4="Landscape",K40,IF($I$4="Macro",L40,IF($I$4="People",M40,IF($I$4="Sports",N40,IF($I$4="Travel",O40,IF($I$4="Waterdrops",P40,IF($I$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="Z40" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D40,IF($J$4="C2 Birds in Flight",E40,IF($J$4="C3 Landscape",F40,IF($J$4="Default Settings",G40,IF($J$4="Birds in Flight",H40,IF($J$4="Birds Perched",I40,IF($J$4="Fireworks",J40,IF($J$4="Landscape",K40,IF($J$4="Macro",L40,IF($J$4="People",M40,IF($J$4="Sports",N40,IF($J$4="Travel",O40,IF($J$4="Waterdrops",P40,IF($J$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AA40" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D40,IF($K$4="C2 Birds in Flight",E40,IF($K$4="C3 Landscape",F40,IF($K$4="Default Settings",G40,IF($K$4="Birds in Flight",H40,IF($K$4="Birds Perched",I40,IF($K$4="Fireworks",J40,IF($K$4="Landscape",K40,IF($K$4="Macro",L40,IF($K$4="People",M40,IF($K$4="Sports",N40,IF($K$4="Travel",O40,IF($K$4="Waterdrops",P40,IF($K$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AB40" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D40,IF($L$4="C2 Birds in Flight",E40,IF($L$4="C3 Landscape",F40,IF($L$4="Default Settings",G40,IF($L$4="Birds in Flight",H40,IF($L$4="Birds Perched",I40,IF($L$4="Fireworks",J40,IF($L$4="Landscape",K40,IF($L$4="Macro",L40,IF($L$4="People",M40,IF($L$4="Sports",N40,IF($L$4="Travel",O40,IF($L$4="Waterdrops",P40,IF($L$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AC40" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D40,IF($M$4="C2 Birds in Flight",E40,IF($M$4="C3 Landscape",F40,IF($M$4="Default Settings",G40,IF($M$4="Birds in Flight",H40,IF($M$4="Birds Perched",I40,IF($M$4="Fireworks",J40,IF($M$4="Landscape",K40,IF($M$4="Macro",L40,IF($M$4="People",M40,IF($M$4="Sports",N40,IF($M$4="Travel",O40,IF($M$4="Waterdrops",P40,IF($M$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AD40" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D40,IF($N$4="C2 Birds in Flight",E40,IF($N$4="C3 Landscape",F40,IF($N$4="Default Settings",G40,IF($N$4="Birds in Flight",H40,IF($N$4="Birds Perched",I40,IF($N$4="Fireworks",J40,IF($N$4="Landscape",K40,IF($N$4="Macro",L40,IF($N$4="People",M40,IF($N$4="Sports",N40,IF($N$4="Travel",O40,IF($N$4="Waterdrops",P40,IF($N$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AE40" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D40,IF($O$4="C2 Birds in Flight",E40,IF($O$4="C3 Landscape",F40,IF($O$4="Default Settings",G40,IF($O$4="Birds in Flight",H40,IF($O$4="Birds Perched",I40,IF($O$4="Fireworks",J40,IF($O$4="Landscape",K40,IF($O$4="Macro",L40,IF($O$4="People",M40,IF($O$4="Sports",N40,IF($O$4="Travel",O40,IF($O$4="Waterdrops",P40,IF($O$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AF40" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D40,IF($P$4="C2 Birds in Flight",E40,IF($P$4="C3 Landscape",F40,IF($P$4="Default Settings",G40,IF($P$4="Birds in Flight",H40,IF($P$4="Birds Perched",I40,IF($P$4="Fireworks",J40,IF($P$4="Landscape",K40,IF($P$4="Macro",L40,IF($P$4="People",M40,IF($P$4="Sports",N40,IF($P$4="Travel",O40,IF($P$4="Waterdrops",P40,IF($P$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="AG40" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D40,IF($Q$4="C2 Birds in Flight",E40,IF($Q$4="C3 Landscape",F40,IF($Q$4="Default Settings",G40,IF($Q$4="Birds in Flight",H40,IF($Q$4="Birds Perched",I40,IF($Q$4="Fireworks",J40,IF($Q$4="Landscape",K40,IF($Q$4="Macro",L40,IF($Q$4="People",M40,IF($Q$4="Sports",N40,IF($Q$4="Travel",O40,IF($Q$4="Waterdrops",P40,IF($Q$4="Wildlife",Q40,""))))))))))))))</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" hidden="0">
+      <x:c r="A41" s="12" t="str">
+        <x:v>Shooting 2 &gt; Highlight tone priority</x:v>
+      </x:c>
+      <x:c r="B41" s="14" t="str">
+        <x:v>Full camera menu</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="str">
+        <x:v>Highlight Tone Priority</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="E41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="H41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="I41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="J41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="M41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="N41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="O41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="P41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="R41" s="20" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S41" s="20" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="T41" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D41,IF($D$4="C2 Birds in Flight",E41,IF($D$4="C3 Landscape",F41,IF($D$4="Default Settings",G41,IF($D$4="Birds in Flight",H41,IF($D$4="Birds Perched",I41,IF($D$4="Fireworks",J41,IF($D$4="Landscape",K41,IF($D$4="Macro",L41,IF($D$4="People",M41,IF($D$4="Sports",N41,IF($D$4="Travel",O41,IF($D$4="Waterdrops",P41,IF($D$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U41" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D41,IF($E$4="C2 Birds in Flight",E41,IF($E$4="C3 Landscape",F41,IF($E$4="Default Settings",G41,IF($E$4="Birds in Flight",H41,IF($E$4="Birds Perched",I41,IF($E$4="Fireworks",J41,IF($E$4="Landscape",K41,IF($E$4="Macro",L41,IF($E$4="People",M41,IF($E$4="Sports",N41,IF($E$4="Travel",O41,IF($E$4="Waterdrops",P41,IF($E$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V41" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D41,IF($F$4="C2 Birds in Flight",E41,IF($F$4="C3 Landscape",F41,IF($F$4="Default Settings",G41,IF($F$4="Birds in Flight",H41,IF($F$4="Birds Perched",I41,IF($F$4="Fireworks",J41,IF($F$4="Landscape",K41,IF($F$4="Macro",L41,IF($F$4="People",M41,IF($F$4="Sports",N41,IF($F$4="Travel",O41,IF($F$4="Waterdrops",P41,IF($F$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="W41" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D41,IF($G$4="C2 Birds in Flight",E41,IF($G$4="C3 Landscape",F41,IF($G$4="Default Settings",G41,IF($G$4="Birds in Flight",H41,IF($G$4="Birds Perched",I41,IF($G$4="Fireworks",J41,IF($G$4="Landscape",K41,IF($G$4="Macro",L41,IF($G$4="People",M41,IF($G$4="Sports",N41,IF($G$4="Travel",O41,IF($G$4="Waterdrops",P41,IF($G$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="X41" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D41,IF($H$4="C2 Birds in Flight",E41,IF($H$4="C3 Landscape",F41,IF($H$4="Default Settings",G41,IF($H$4="Birds in Flight",H41,IF($H$4="Birds Perched",I41,IF($H$4="Fireworks",J41,IF($H$4="Landscape",K41,IF($H$4="Macro",L41,IF($H$4="People",M41,IF($H$4="Sports",N41,IF($H$4="Travel",O41,IF($H$4="Waterdrops",P41,IF($H$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Y41" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D41,IF($I$4="C2 Birds in Flight",E41,IF($I$4="C3 Landscape",F41,IF($I$4="Default Settings",G41,IF($I$4="Birds in Flight",H41,IF($I$4="Birds Perched",I41,IF($I$4="Fireworks",J41,IF($I$4="Landscape",K41,IF($I$4="Macro",L41,IF($I$4="People",M41,IF($I$4="Sports",N41,IF($I$4="Travel",O41,IF($I$4="Waterdrops",P41,IF($I$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Z41" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D41,IF($J$4="C2 Birds in Flight",E41,IF($J$4="C3 Landscape",F41,IF($J$4="Default Settings",G41,IF($J$4="Birds in Flight",H41,IF($J$4="Birds Perched",I41,IF($J$4="Fireworks",J41,IF($J$4="Landscape",K41,IF($J$4="Macro",L41,IF($J$4="People",M41,IF($J$4="Sports",N41,IF($J$4="Travel",O41,IF($J$4="Waterdrops",P41,IF($J$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA41" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D41,IF($K$4="C2 Birds in Flight",E41,IF($K$4="C3 Landscape",F41,IF($K$4="Default Settings",G41,IF($K$4="Birds in Flight",H41,IF($K$4="Birds Perched",I41,IF($K$4="Fireworks",J41,IF($K$4="Landscape",K41,IF($K$4="Macro",L41,IF($K$4="People",M41,IF($K$4="Sports",N41,IF($K$4="Travel",O41,IF($K$4="Waterdrops",P41,IF($K$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AB41" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D41,IF($L$4="C2 Birds in Flight",E41,IF($L$4="C3 Landscape",F41,IF($L$4="Default Settings",G41,IF($L$4="Birds in Flight",H41,IF($L$4="Birds Perched",I41,IF($L$4="Fireworks",J41,IF($L$4="Landscape",K41,IF($L$4="Macro",L41,IF($L$4="People",M41,IF($L$4="Sports",N41,IF($L$4="Travel",O41,IF($L$4="Waterdrops",P41,IF($L$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AC41" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D41,IF($M$4="C2 Birds in Flight",E41,IF($M$4="C3 Landscape",F41,IF($M$4="Default Settings",G41,IF($M$4="Birds in Flight",H41,IF($M$4="Birds Perched",I41,IF($M$4="Fireworks",J41,IF($M$4="Landscape",K41,IF($M$4="Macro",L41,IF($M$4="People",M41,IF($M$4="Sports",N41,IF($M$4="Travel",O41,IF($M$4="Waterdrops",P41,IF($M$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AD41" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D41,IF($N$4="C2 Birds in Flight",E41,IF($N$4="C3 Landscape",F41,IF($N$4="Default Settings",G41,IF($N$4="Birds in Flight",H41,IF($N$4="Birds Perched",I41,IF($N$4="Fireworks",J41,IF($N$4="Landscape",K41,IF($N$4="Macro",L41,IF($N$4="People",M41,IF($N$4="Sports",N41,IF($N$4="Travel",O41,IF($N$4="Waterdrops",P41,IF($N$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AE41" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D41,IF($O$4="C2 Birds in Flight",E41,IF($O$4="C3 Landscape",F41,IF($O$4="Default Settings",G41,IF($O$4="Birds in Flight",H41,IF($O$4="Birds Perched",I41,IF($O$4="Fireworks",J41,IF($O$4="Landscape",K41,IF($O$4="Macro",L41,IF($O$4="People",M41,IF($O$4="Sports",N41,IF($O$4="Travel",O41,IF($O$4="Waterdrops",P41,IF($O$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AF41" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D41,IF($P$4="C2 Birds in Flight",E41,IF($P$4="C3 Landscape",F41,IF($P$4="Default Settings",G41,IF($P$4="Birds in Flight",H41,IF($P$4="Birds Perched",I41,IF($P$4="Fireworks",J41,IF($P$4="Landscape",K41,IF($P$4="Macro",L41,IF($P$4="People",M41,IF($P$4="Sports",N41,IF($P$4="Travel",O41,IF($P$4="Waterdrops",P41,IF($P$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG41" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D41,IF($Q$4="C2 Birds in Flight",E41,IF($Q$4="C3 Landscape",F41,IF($Q$4="Default Settings",G41,IF($Q$4="Birds in Flight",H41,IF($Q$4="Birds Perched",I41,IF($Q$4="Fireworks",J41,IF($Q$4="Landscape",K41,IF($Q$4="Macro",L41,IF($Q$4="People",M41,IF($Q$4="Sports",N41,IF($Q$4="Travel",O41,IF($Q$4="Waterdrops",P41,IF($Q$4="Wildlife",Q41,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" hidden="0">
+      <x:c r="A42" s="12" t="str">
+        <x:v>Shooting 4 &gt; High ISO speed NR</x:v>
+      </x:c>
+      <x:c r="B42" s="14" t="str">
+        <x:v>Full camera menu</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="str">
+        <x:v>High ISO NR</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="E42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="H42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="I42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="J42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="M42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="N42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="O42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="P42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="R42" s="20" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="S42" s="20" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="T42" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D42,IF($D$4="C2 Birds in Flight",E42,IF($D$4="C3 Landscape",F42,IF($D$4="Default Settings",G42,IF($D$4="Birds in Flight",H42,IF($D$4="Birds Perched",I42,IF($D$4="Fireworks",J42,IF($D$4="Landscape",K42,IF($D$4="Macro",L42,IF($D$4="People",M42,IF($D$4="Sports",N42,IF($D$4="Travel",O42,IF($D$4="Waterdrops",P42,IF($D$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U42" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D42,IF($E$4="C2 Birds in Flight",E42,IF($E$4="C3 Landscape",F42,IF($E$4="Default Settings",G42,IF($E$4="Birds in Flight",H42,IF($E$4="Birds Perched",I42,IF($E$4="Fireworks",J42,IF($E$4="Landscape",K42,IF($E$4="Macro",L42,IF($E$4="People",M42,IF($E$4="Sports",N42,IF($E$4="Travel",O42,IF($E$4="Waterdrops",P42,IF($E$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V42" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D42,IF($F$4="C2 Birds in Flight",E42,IF($F$4="C3 Landscape",F42,IF($F$4="Default Settings",G42,IF($F$4="Birds in Flight",H42,IF($F$4="Birds Perched",I42,IF($F$4="Fireworks",J42,IF($F$4="Landscape",K42,IF($F$4="Macro",L42,IF($F$4="People",M42,IF($F$4="Sports",N42,IF($F$4="Travel",O42,IF($F$4="Waterdrops",P42,IF($F$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="W42" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D42,IF($G$4="C2 Birds in Flight",E42,IF($G$4="C3 Landscape",F42,IF($G$4="Default Settings",G42,IF($G$4="Birds in Flight",H42,IF($G$4="Birds Perched",I42,IF($G$4="Fireworks",J42,IF($G$4="Landscape",K42,IF($G$4="Macro",L42,IF($G$4="People",M42,IF($G$4="Sports",N42,IF($G$4="Travel",O42,IF($G$4="Waterdrops",P42,IF($G$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="X42" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D42,IF($H$4="C2 Birds in Flight",E42,IF($H$4="C3 Landscape",F42,IF($H$4="Default Settings",G42,IF($H$4="Birds in Flight",H42,IF($H$4="Birds Perched",I42,IF($H$4="Fireworks",J42,IF($H$4="Landscape",K42,IF($H$4="Macro",L42,IF($H$4="People",M42,IF($H$4="Sports",N42,IF($H$4="Travel",O42,IF($H$4="Waterdrops",P42,IF($H$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Y42" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D42,IF($I$4="C2 Birds in Flight",E42,IF($I$4="C3 Landscape",F42,IF($I$4="Default Settings",G42,IF($I$4="Birds in Flight",H42,IF($I$4="Birds Perched",I42,IF($I$4="Fireworks",J42,IF($I$4="Landscape",K42,IF($I$4="Macro",L42,IF($I$4="People",M42,IF($I$4="Sports",N42,IF($I$4="Travel",O42,IF($I$4="Waterdrops",P42,IF($I$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Z42" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D42,IF($J$4="C2 Birds in Flight",E42,IF($J$4="C3 Landscape",F42,IF($J$4="Default Settings",G42,IF($J$4="Birds in Flight",H42,IF($J$4="Birds Perched",I42,IF($J$4="Fireworks",J42,IF($J$4="Landscape",K42,IF($J$4="Macro",L42,IF($J$4="People",M42,IF($J$4="Sports",N42,IF($J$4="Travel",O42,IF($J$4="Waterdrops",P42,IF($J$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA42" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D42,IF($K$4="C2 Birds in Flight",E42,IF($K$4="C3 Landscape",F42,IF($K$4="Default Settings",G42,IF($K$4="Birds in Flight",H42,IF($K$4="Birds Perched",I42,IF($K$4="Fireworks",J42,IF($K$4="Landscape",K42,IF($K$4="Macro",L42,IF($K$4="People",M42,IF($K$4="Sports",N42,IF($K$4="Travel",O42,IF($K$4="Waterdrops",P42,IF($K$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AB42" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D42,IF($L$4="C2 Birds in Flight",E42,IF($L$4="C3 Landscape",F42,IF($L$4="Default Settings",G42,IF($L$4="Birds in Flight",H42,IF($L$4="Birds Perched",I42,IF($L$4="Fireworks",J42,IF($L$4="Landscape",K42,IF($L$4="Macro",L42,IF($L$4="People",M42,IF($L$4="Sports",N42,IF($L$4="Travel",O42,IF($L$4="Waterdrops",P42,IF($L$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AC42" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D42,IF($M$4="C2 Birds in Flight",E42,IF($M$4="C3 Landscape",F42,IF($M$4="Default Settings",G42,IF($M$4="Birds in Flight",H42,IF($M$4="Birds Perched",I42,IF($M$4="Fireworks",J42,IF($M$4="Landscape",K42,IF($M$4="Macro",L42,IF($M$4="People",M42,IF($M$4="Sports",N42,IF($M$4="Travel",O42,IF($M$4="Waterdrops",P42,IF($M$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AD42" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D42,IF($N$4="C2 Birds in Flight",E42,IF($N$4="C3 Landscape",F42,IF($N$4="Default Settings",G42,IF($N$4="Birds in Flight",H42,IF($N$4="Birds Perched",I42,IF($N$4="Fireworks",J42,IF($N$4="Landscape",K42,IF($N$4="Macro",L42,IF($N$4="People",M42,IF($N$4="Sports",N42,IF($N$4="Travel",O42,IF($N$4="Waterdrops",P42,IF($N$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AE42" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D42,IF($O$4="C2 Birds in Flight",E42,IF($O$4="C3 Landscape",F42,IF($O$4="Default Settings",G42,IF($O$4="Birds in Flight",H42,IF($O$4="Birds Perched",I42,IF($O$4="Fireworks",J42,IF($O$4="Landscape",K42,IF($O$4="Macro",L42,IF($O$4="People",M42,IF($O$4="Sports",N42,IF($O$4="Travel",O42,IF($O$4="Waterdrops",P42,IF($O$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AF42" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D42,IF($P$4="C2 Birds in Flight",E42,IF($P$4="C3 Landscape",F42,IF($P$4="Default Settings",G42,IF($P$4="Birds in Flight",H42,IF($P$4="Birds Perched",I42,IF($P$4="Fireworks",J42,IF($P$4="Landscape",K42,IF($P$4="Macro",L42,IF($P$4="People",M42,IF($P$4="Sports",N42,IF($P$4="Travel",O42,IF($P$4="Waterdrops",P42,IF($P$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG42" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D42,IF($Q$4="C2 Birds in Flight",E42,IF($Q$4="C3 Landscape",F42,IF($Q$4="Default Settings",G42,IF($Q$4="Birds in Flight",H42,IF($Q$4="Birds Perched",I42,IF($Q$4="Fireworks",J42,IF($Q$4="Landscape",K42,IF($Q$4="Macro",L42,IF($Q$4="People",M42,IF($Q$4="Sports",N42,IF($Q$4="Travel",O42,IF($Q$4="Waterdrops",P42,IF($Q$4="Wildlife",Q42,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" hidden="0">
+      <x:c r="A43" s="12" t="str">
+        <x:v>Set-up 5 &gt; Custom shooting mode (C1-C3) &gt; Auto update set.</x:v>
+      </x:c>
+      <x:c r="B43" s="14" t="str">
+        <x:v>Set once</x:v>
+      </x:c>
+      <x:c r="C43" s="15" t="str">
+        <x:v>C1-C3 Auto Update</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="E43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="H43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="I43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="J43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="K43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="L43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="M43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="N43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="O43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="P43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Q43" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="R43" s="20" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S43" s="20" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="T43" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D43,IF($D$4="C2 Birds in Flight",E43,IF($D$4="C3 Landscape",F43,IF($D$4="Default Settings",G43,IF($D$4="Birds in Flight",H43,IF($D$4="Birds Perched",I43,IF($D$4="Fireworks",J43,IF($D$4="Landscape",K43,IF($D$4="Macro",L43,IF($D$4="People",M43,IF($D$4="Sports",N43,IF($D$4="Travel",O43,IF($D$4="Waterdrops",P43,IF($D$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U43" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D43,IF($E$4="C2 Birds in Flight",E43,IF($E$4="C3 Landscape",F43,IF($E$4="Default Settings",G43,IF($E$4="Birds in Flight",H43,IF($E$4="Birds Perched",I43,IF($E$4="Fireworks",J43,IF($E$4="Landscape",K43,IF($E$4="Macro",L43,IF($E$4="People",M43,IF($E$4="Sports",N43,IF($E$4="Travel",O43,IF($E$4="Waterdrops",P43,IF($E$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V43" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D43,IF($F$4="C2 Birds in Flight",E43,IF($F$4="C3 Landscape",F43,IF($F$4="Default Settings",G43,IF($F$4="Birds in Flight",H43,IF($F$4="Birds Perched",I43,IF($F$4="Fireworks",J43,IF($F$4="Landscape",K43,IF($F$4="Macro",L43,IF($F$4="People",M43,IF($F$4="Sports",N43,IF($F$4="Travel",O43,IF($F$4="Waterdrops",P43,IF($F$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="W43" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D43,IF($G$4="C2 Birds in Flight",E43,IF($G$4="C3 Landscape",F43,IF($G$4="Default Settings",G43,IF($G$4="Birds in Flight",H43,IF($G$4="Birds Perched",I43,IF($G$4="Fireworks",J43,IF($G$4="Landscape",K43,IF($G$4="Macro",L43,IF($G$4="People",M43,IF($G$4="Sports",N43,IF($G$4="Travel",O43,IF($G$4="Waterdrops",P43,IF($G$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="X43" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D43,IF($H$4="C2 Birds in Flight",E43,IF($H$4="C3 Landscape",F43,IF($H$4="Default Settings",G43,IF($H$4="Birds in Flight",H43,IF($H$4="Birds Perched",I43,IF($H$4="Fireworks",J43,IF($H$4="Landscape",K43,IF($H$4="Macro",L43,IF($H$4="People",M43,IF($H$4="Sports",N43,IF($H$4="Travel",O43,IF($H$4="Waterdrops",P43,IF($H$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Y43" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D43,IF($I$4="C2 Birds in Flight",E43,IF($I$4="C3 Landscape",F43,IF($I$4="Default Settings",G43,IF($I$4="Birds in Flight",H43,IF($I$4="Birds Perched",I43,IF($I$4="Fireworks",J43,IF($I$4="Landscape",K43,IF($I$4="Macro",L43,IF($I$4="People",M43,IF($I$4="Sports",N43,IF($I$4="Travel",O43,IF($I$4="Waterdrops",P43,IF($I$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="Z43" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D43,IF($J$4="C2 Birds in Flight",E43,IF($J$4="C3 Landscape",F43,IF($J$4="Default Settings",G43,IF($J$4="Birds in Flight",H43,IF($J$4="Birds Perched",I43,IF($J$4="Fireworks",J43,IF($J$4="Landscape",K43,IF($J$4="Macro",L43,IF($J$4="People",M43,IF($J$4="Sports",N43,IF($J$4="Travel",O43,IF($J$4="Waterdrops",P43,IF($J$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AA43" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D43,IF($K$4="C2 Birds in Flight",E43,IF($K$4="C3 Landscape",F43,IF($K$4="Default Settings",G43,IF($K$4="Birds in Flight",H43,IF($K$4="Birds Perched",I43,IF($K$4="Fireworks",J43,IF($K$4="Landscape",K43,IF($K$4="Macro",L43,IF($K$4="People",M43,IF($K$4="Sports",N43,IF($K$4="Travel",O43,IF($K$4="Waterdrops",P43,IF($K$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AB43" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D43,IF($L$4="C2 Birds in Flight",E43,IF($L$4="C3 Landscape",F43,IF($L$4="Default Settings",G43,IF($L$4="Birds in Flight",H43,IF($L$4="Birds Perched",I43,IF($L$4="Fireworks",J43,IF($L$4="Landscape",K43,IF($L$4="Macro",L43,IF($L$4="People",M43,IF($L$4="Sports",N43,IF($L$4="Travel",O43,IF($L$4="Waterdrops",P43,IF($L$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AC43" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D43,IF($M$4="C2 Birds in Flight",E43,IF($M$4="C3 Landscape",F43,IF($M$4="Default Settings",G43,IF($M$4="Birds in Flight",H43,IF($M$4="Birds Perched",I43,IF($M$4="Fireworks",J43,IF($M$4="Landscape",K43,IF($M$4="Macro",L43,IF($M$4="People",M43,IF($M$4="Sports",N43,IF($M$4="Travel",O43,IF($M$4="Waterdrops",P43,IF($M$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AD43" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D43,IF($N$4="C2 Birds in Flight",E43,IF($N$4="C3 Landscape",F43,IF($N$4="Default Settings",G43,IF($N$4="Birds in Flight",H43,IF($N$4="Birds Perched",I43,IF($N$4="Fireworks",J43,IF($N$4="Landscape",K43,IF($N$4="Macro",L43,IF($N$4="People",M43,IF($N$4="Sports",N43,IF($N$4="Travel",O43,IF($N$4="Waterdrops",P43,IF($N$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AE43" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D43,IF($O$4="C2 Birds in Flight",E43,IF($O$4="C3 Landscape",F43,IF($O$4="Default Settings",G43,IF($O$4="Birds in Flight",H43,IF($O$4="Birds Perched",I43,IF($O$4="Fireworks",J43,IF($O$4="Landscape",K43,IF($O$4="Macro",L43,IF($O$4="People",M43,IF($O$4="Sports",N43,IF($O$4="Travel",O43,IF($O$4="Waterdrops",P43,IF($O$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AF43" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D43,IF($P$4="C2 Birds in Flight",E43,IF($P$4="C3 Landscape",F43,IF($P$4="Default Settings",G43,IF($P$4="Birds in Flight",H43,IF($P$4="Birds Perched",I43,IF($P$4="Fireworks",J43,IF($P$4="Landscape",K43,IF($P$4="Macro",L43,IF($P$4="People",M43,IF($P$4="Sports",N43,IF($P$4="Travel",O43,IF($P$4="Waterdrops",P43,IF($P$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="AG43" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D43,IF($Q$4="C2 Birds in Flight",E43,IF($Q$4="C3 Landscape",F43,IF($Q$4="Default Settings",G43,IF($Q$4="Birds in Flight",H43,IF($Q$4="Birds Perched",I43,IF($Q$4="Fireworks",J43,IF($Q$4="Landscape",K43,IF($Q$4="Macro",L43,IF($Q$4="People",M43,IF($Q$4="Sports",N43,IF($Q$4="Travel",O43,IF($Q$4="Waterdrops",P43,IF($Q$4="Wildlife",Q43,""))))))))))))))</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" hidden="0">
+      <x:c r="A44" s="12" t="str">
+        <x:v>AF5 &gt; Electronic full-time MF</x:v>
+      </x:c>
+      <x:c r="B44" s="14" t="str">
+        <x:v>Set once</x:v>
+      </x:c>
+      <x:c r="C44" s="15" t="str">
+        <x:v>Electronic Full-time MF</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="E44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="G44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="H44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="I44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="J44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="M44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="N44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="O44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="P44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q44" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="R44" s="20" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S44" s="20" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="T44" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D44,IF($D$4="C2 Birds in Flight",E44,IF($D$4="C3 Landscape",F44,IF($D$4="Default Settings",G44,IF($D$4="Birds in Flight",H44,IF($D$4="Birds Perched",I44,IF($D$4="Fireworks",J44,IF($D$4="Landscape",K44,IF($D$4="Macro",L44,IF($D$4="People",M44,IF($D$4="Sports",N44,IF($D$4="Travel",O44,IF($D$4="Waterdrops",P44,IF($D$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U44" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D44,IF($E$4="C2 Birds in Flight",E44,IF($E$4="C3 Landscape",F44,IF($E$4="Default Settings",G44,IF($E$4="Birds in Flight",H44,IF($E$4="Birds Perched",I44,IF($E$4="Fireworks",J44,IF($E$4="Landscape",K44,IF($E$4="Macro",L44,IF($E$4="People",M44,IF($E$4="Sports",N44,IF($E$4="Travel",O44,IF($E$4="Waterdrops",P44,IF($E$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V44" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D44,IF($F$4="C2 Birds in Flight",E44,IF($F$4="C3 Landscape",F44,IF($F$4="Default Settings",G44,IF($F$4="Birds in Flight",H44,IF($F$4="Birds Perched",I44,IF($F$4="Fireworks",J44,IF($F$4="Landscape",K44,IF($F$4="Macro",L44,IF($F$4="People",M44,IF($F$4="Sports",N44,IF($F$4="Travel",O44,IF($F$4="Waterdrops",P44,IF($F$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="W44" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D44,IF($G$4="C2 Birds in Flight",E44,IF($G$4="C3 Landscape",F44,IF($G$4="Default Settings",G44,IF($G$4="Birds in Flight",H44,IF($G$4="Birds Perched",I44,IF($G$4="Fireworks",J44,IF($G$4="Landscape",K44,IF($G$4="Macro",L44,IF($G$4="People",M44,IF($G$4="Sports",N44,IF($G$4="Travel",O44,IF($G$4="Waterdrops",P44,IF($G$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="X44" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D44,IF($H$4="C2 Birds in Flight",E44,IF($H$4="C3 Landscape",F44,IF($H$4="Default Settings",G44,IF($H$4="Birds in Flight",H44,IF($H$4="Birds Perched",I44,IF($H$4="Fireworks",J44,IF($H$4="Landscape",K44,IF($H$4="Macro",L44,IF($H$4="People",M44,IF($H$4="Sports",N44,IF($H$4="Travel",O44,IF($H$4="Waterdrops",P44,IF($H$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Y44" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D44,IF($I$4="C2 Birds in Flight",E44,IF($I$4="C3 Landscape",F44,IF($I$4="Default Settings",G44,IF($I$4="Birds in Flight",H44,IF($I$4="Birds Perched",I44,IF($I$4="Fireworks",J44,IF($I$4="Landscape",K44,IF($I$4="Macro",L44,IF($I$4="People",M44,IF($I$4="Sports",N44,IF($I$4="Travel",O44,IF($I$4="Waterdrops",P44,IF($I$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Z44" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D44,IF($J$4="C2 Birds in Flight",E44,IF($J$4="C3 Landscape",F44,IF($J$4="Default Settings",G44,IF($J$4="Birds in Flight",H44,IF($J$4="Birds Perched",I44,IF($J$4="Fireworks",J44,IF($J$4="Landscape",K44,IF($J$4="Macro",L44,IF($J$4="People",M44,IF($J$4="Sports",N44,IF($J$4="Travel",O44,IF($J$4="Waterdrops",P44,IF($J$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA44" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D44,IF($K$4="C2 Birds in Flight",E44,IF($K$4="C3 Landscape",F44,IF($K$4="Default Settings",G44,IF($K$4="Birds in Flight",H44,IF($K$4="Birds Perched",I44,IF($K$4="Fireworks",J44,IF($K$4="Landscape",K44,IF($K$4="Macro",L44,IF($K$4="People",M44,IF($K$4="Sports",N44,IF($K$4="Travel",O44,IF($K$4="Waterdrops",P44,IF($K$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AB44" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D44,IF($L$4="C2 Birds in Flight",E44,IF($L$4="C3 Landscape",F44,IF($L$4="Default Settings",G44,IF($L$4="Birds in Flight",H44,IF($L$4="Birds Perched",I44,IF($L$4="Fireworks",J44,IF($L$4="Landscape",K44,IF($L$4="Macro",L44,IF($L$4="People",M44,IF($L$4="Sports",N44,IF($L$4="Travel",O44,IF($L$4="Waterdrops",P44,IF($L$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AC44" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D44,IF($M$4="C2 Birds in Flight",E44,IF($M$4="C3 Landscape",F44,IF($M$4="Default Settings",G44,IF($M$4="Birds in Flight",H44,IF($M$4="Birds Perched",I44,IF($M$4="Fireworks",J44,IF($M$4="Landscape",K44,IF($M$4="Macro",L44,IF($M$4="People",M44,IF($M$4="Sports",N44,IF($M$4="Travel",O44,IF($M$4="Waterdrops",P44,IF($M$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AD44" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D44,IF($N$4="C2 Birds in Flight",E44,IF($N$4="C3 Landscape",F44,IF($N$4="Default Settings",G44,IF($N$4="Birds in Flight",H44,IF($N$4="Birds Perched",I44,IF($N$4="Fireworks",J44,IF($N$4="Landscape",K44,IF($N$4="Macro",L44,IF($N$4="People",M44,IF($N$4="Sports",N44,IF($N$4="Travel",O44,IF($N$4="Waterdrops",P44,IF($N$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AE44" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D44,IF($O$4="C2 Birds in Flight",E44,IF($O$4="C3 Landscape",F44,IF($O$4="Default Settings",G44,IF($O$4="Birds in Flight",H44,IF($O$4="Birds Perched",I44,IF($O$4="Fireworks",J44,IF($O$4="Landscape",K44,IF($O$4="Macro",L44,IF($O$4="People",M44,IF($O$4="Sports",N44,IF($O$4="Travel",O44,IF($O$4="Waterdrops",P44,IF($O$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AF44" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D44,IF($P$4="C2 Birds in Flight",E44,IF($P$4="C3 Landscape",F44,IF($P$4="Default Settings",G44,IF($P$4="Birds in Flight",H44,IF($P$4="Birds Perched",I44,IF($P$4="Fireworks",J44,IF($P$4="Landscape",K44,IF($P$4="Macro",L44,IF($P$4="People",M44,IF($P$4="Sports",N44,IF($P$4="Travel",O44,IF($P$4="Waterdrops",P44,IF($P$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG44" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D44,IF($Q$4="C2 Birds in Flight",E44,IF($Q$4="C3 Landscape",F44,IF($Q$4="Default Settings",G44,IF($Q$4="Birds in Flight",H44,IF($Q$4="Birds Perched",I44,IF($Q$4="Fireworks",J44,IF($Q$4="Landscape",K44,IF($Q$4="Macro",L44,IF($Q$4="People",M44,IF($Q$4="Sports",N44,IF($Q$4="Travel",O44,IF($Q$4="Waterdrops",P44,IF($Q$4="Wildlife",Q44,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" hidden="0">
+      <x:c r="A45" s="12" t="str">
+        <x:v>Shooting 5 &gt; IBIS High resolution shot</x:v>
+      </x:c>
+      <x:c r="B45" s="14" t="str">
+        <x:v>Full camera menu</x:v>
+      </x:c>
+      <x:c r="C45" s="15" t="str">
+        <x:v>IBIS High Res Shot</x:v>
+      </x:c>
+      <x:c r="D45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="E45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="G45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="H45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="I45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="J45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="M45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="N45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="O45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="P45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q45" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="R45" s="20" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S45" s="20" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="T45" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D45,IF($D$4="C2 Birds in Flight",E45,IF($D$4="C3 Landscape",F45,IF($D$4="Default Settings",G45,IF($D$4="Birds in Flight",H45,IF($D$4="Birds Perched",I45,IF($D$4="Fireworks",J45,IF($D$4="Landscape",K45,IF($D$4="Macro",L45,IF($D$4="People",M45,IF($D$4="Sports",N45,IF($D$4="Travel",O45,IF($D$4="Waterdrops",P45,IF($D$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U45" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D45,IF($E$4="C2 Birds in Flight",E45,IF($E$4="C3 Landscape",F45,IF($E$4="Default Settings",G45,IF($E$4="Birds in Flight",H45,IF($E$4="Birds Perched",I45,IF($E$4="Fireworks",J45,IF($E$4="Landscape",K45,IF($E$4="Macro",L45,IF($E$4="People",M45,IF($E$4="Sports",N45,IF($E$4="Travel",O45,IF($E$4="Waterdrops",P45,IF($E$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V45" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D45,IF($F$4="C2 Birds in Flight",E45,IF($F$4="C3 Landscape",F45,IF($F$4="Default Settings",G45,IF($F$4="Birds in Flight",H45,IF($F$4="Birds Perched",I45,IF($F$4="Fireworks",J45,IF($F$4="Landscape",K45,IF($F$4="Macro",L45,IF($F$4="People",M45,IF($F$4="Sports",N45,IF($F$4="Travel",O45,IF($F$4="Waterdrops",P45,IF($F$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="W45" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D45,IF($G$4="C2 Birds in Flight",E45,IF($G$4="C3 Landscape",F45,IF($G$4="Default Settings",G45,IF($G$4="Birds in Flight",H45,IF($G$4="Birds Perched",I45,IF($G$4="Fireworks",J45,IF($G$4="Landscape",K45,IF($G$4="Macro",L45,IF($G$4="People",M45,IF($G$4="Sports",N45,IF($G$4="Travel",O45,IF($G$4="Waterdrops",P45,IF($G$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="X45" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D45,IF($H$4="C2 Birds in Flight",E45,IF($H$4="C3 Landscape",F45,IF($H$4="Default Settings",G45,IF($H$4="Birds in Flight",H45,IF($H$4="Birds Perched",I45,IF($H$4="Fireworks",J45,IF($H$4="Landscape",K45,IF($H$4="Macro",L45,IF($H$4="People",M45,IF($H$4="Sports",N45,IF($H$4="Travel",O45,IF($H$4="Waterdrops",P45,IF($H$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Y45" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D45,IF($I$4="C2 Birds in Flight",E45,IF($I$4="C3 Landscape",F45,IF($I$4="Default Settings",G45,IF($I$4="Birds in Flight",H45,IF($I$4="Birds Perched",I45,IF($I$4="Fireworks",J45,IF($I$4="Landscape",K45,IF($I$4="Macro",L45,IF($I$4="People",M45,IF($I$4="Sports",N45,IF($I$4="Travel",O45,IF($I$4="Waterdrops",P45,IF($I$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Z45" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D45,IF($J$4="C2 Birds in Flight",E45,IF($J$4="C3 Landscape",F45,IF($J$4="Default Settings",G45,IF($J$4="Birds in Flight",H45,IF($J$4="Birds Perched",I45,IF($J$4="Fireworks",J45,IF($J$4="Landscape",K45,IF($J$4="Macro",L45,IF($J$4="People",M45,IF($J$4="Sports",N45,IF($J$4="Travel",O45,IF($J$4="Waterdrops",P45,IF($J$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA45" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D45,IF($K$4="C2 Birds in Flight",E45,IF($K$4="C3 Landscape",F45,IF($K$4="Default Settings",G45,IF($K$4="Birds in Flight",H45,IF($K$4="Birds Perched",I45,IF($K$4="Fireworks",J45,IF($K$4="Landscape",K45,IF($K$4="Macro",L45,IF($K$4="People",M45,IF($K$4="Sports",N45,IF($K$4="Travel",O45,IF($K$4="Waterdrops",P45,IF($K$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AB45" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D45,IF($L$4="C2 Birds in Flight",E45,IF($L$4="C3 Landscape",F45,IF($L$4="Default Settings",G45,IF($L$4="Birds in Flight",H45,IF($L$4="Birds Perched",I45,IF($L$4="Fireworks",J45,IF($L$4="Landscape",K45,IF($L$4="Macro",L45,IF($L$4="People",M45,IF($L$4="Sports",N45,IF($L$4="Travel",O45,IF($L$4="Waterdrops",P45,IF($L$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AC45" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D45,IF($M$4="C2 Birds in Flight",E45,IF($M$4="C3 Landscape",F45,IF($M$4="Default Settings",G45,IF($M$4="Birds in Flight",H45,IF($M$4="Birds Perched",I45,IF($M$4="Fireworks",J45,IF($M$4="Landscape",K45,IF($M$4="Macro",L45,IF($M$4="People",M45,IF($M$4="Sports",N45,IF($M$4="Travel",O45,IF($M$4="Waterdrops",P45,IF($M$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AD45" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D45,IF($N$4="C2 Birds in Flight",E45,IF($N$4="C3 Landscape",F45,IF($N$4="Default Settings",G45,IF($N$4="Birds in Flight",H45,IF($N$4="Birds Perched",I45,IF($N$4="Fireworks",J45,IF($N$4="Landscape",K45,IF($N$4="Macro",L45,IF($N$4="People",M45,IF($N$4="Sports",N45,IF($N$4="Travel",O45,IF($N$4="Waterdrops",P45,IF($N$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AE45" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D45,IF($O$4="C2 Birds in Flight",E45,IF($O$4="C3 Landscape",F45,IF($O$4="Default Settings",G45,IF($O$4="Birds in Flight",H45,IF($O$4="Birds Perched",I45,IF($O$4="Fireworks",J45,IF($O$4="Landscape",K45,IF($O$4="Macro",L45,IF($O$4="People",M45,IF($O$4="Sports",N45,IF($O$4="Travel",O45,IF($O$4="Waterdrops",P45,IF($O$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AF45" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D45,IF($P$4="C2 Birds in Flight",E45,IF($P$4="C3 Landscape",F45,IF($P$4="Default Settings",G45,IF($P$4="Birds in Flight",H45,IF($P$4="Birds Perched",I45,IF($P$4="Fireworks",J45,IF($P$4="Landscape",K45,IF($P$4="Macro",L45,IF($P$4="People",M45,IF($P$4="Sports",N45,IF($P$4="Travel",O45,IF($P$4="Waterdrops",P45,IF($P$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG45" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D45,IF($Q$4="C2 Birds in Flight",E45,IF($Q$4="C3 Landscape",F45,IF($Q$4="Default Settings",G45,IF($Q$4="Birds in Flight",H45,IF($Q$4="Birds Perched",I45,IF($Q$4="Fireworks",J45,IF($Q$4="Landscape",K45,IF($Q$4="Macro",L45,IF($Q$4="People",M45,IF($Q$4="Sports",N45,IF($Q$4="Travel",O45,IF($Q$4="Waterdrops",P45,IF($Q$4="Wildlife",Q45,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" hidden="0">
+      <x:c r="A46" s="12" t="str">
+        <x:v>AF1 &gt; Continuous AF</x:v>
+      </x:c>
+      <x:c r="B46" s="14" t="str">
+        <x:v>Set once</x:v>
+      </x:c>
+      <x:c r="C46" s="15" t="str">
+        <x:v>Continuous AF</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="E46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="F46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="G46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="H46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="I46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="J46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="K46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="L46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="M46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="N46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="O46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="P46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Q46" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="R46" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S46" s="20" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="T46" s="38" t="str">
+        <x:f>IF($D$4="C1 Wildlife",D46,IF($D$4="C2 Birds in Flight",E46,IF($D$4="C3 Landscape",F46,IF($D$4="Default Settings",G46,IF($D$4="Birds in Flight",H46,IF($D$4="Birds Perched",I46,IF($D$4="Fireworks",J46,IF($D$4="Landscape",K46,IF($D$4="Macro",L46,IF($D$4="People",M46,IF($D$4="Sports",N46,IF($D$4="Travel",O46,IF($D$4="Waterdrops",P46,IF($D$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U46" s="38" t="str">
+        <x:f>IF($E$4="C1 Wildlife",D46,IF($E$4="C2 Birds in Flight",E46,IF($E$4="C3 Landscape",F46,IF($E$4="Default Settings",G46,IF($E$4="Birds in Flight",H46,IF($E$4="Birds Perched",I46,IF($E$4="Fireworks",J46,IF($E$4="Landscape",K46,IF($E$4="Macro",L46,IF($E$4="People",M46,IF($E$4="Sports",N46,IF($E$4="Travel",O46,IF($E$4="Waterdrops",P46,IF($E$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V46" s="38" t="str">
+        <x:f>IF($F$4="C1 Wildlife",D46,IF($F$4="C2 Birds in Flight",E46,IF($F$4="C3 Landscape",F46,IF($F$4="Default Settings",G46,IF($F$4="Birds in Flight",H46,IF($F$4="Birds Perched",I46,IF($F$4="Fireworks",J46,IF($F$4="Landscape",K46,IF($F$4="Macro",L46,IF($F$4="People",M46,IF($F$4="Sports",N46,IF($F$4="Travel",O46,IF($F$4="Waterdrops",P46,IF($F$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="W46" s="38" t="str">
+        <x:f>IF($G$4="C1 Wildlife",D46,IF($G$4="C2 Birds in Flight",E46,IF($G$4="C3 Landscape",F46,IF($G$4="Default Settings",G46,IF($G$4="Birds in Flight",H46,IF($G$4="Birds Perched",I46,IF($G$4="Fireworks",J46,IF($G$4="Landscape",K46,IF($G$4="Macro",L46,IF($G$4="People",M46,IF($G$4="Sports",N46,IF($G$4="Travel",O46,IF($G$4="Waterdrops",P46,IF($G$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="X46" s="38" t="str">
+        <x:f>IF($H$4="C1 Wildlife",D46,IF($H$4="C2 Birds in Flight",E46,IF($H$4="C3 Landscape",F46,IF($H$4="Default Settings",G46,IF($H$4="Birds in Flight",H46,IF($H$4="Birds Perched",I46,IF($H$4="Fireworks",J46,IF($H$4="Landscape",K46,IF($H$4="Macro",L46,IF($H$4="People",M46,IF($H$4="Sports",N46,IF($H$4="Travel",O46,IF($H$4="Waterdrops",P46,IF($H$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Y46" s="38" t="str">
+        <x:f>IF($I$4="C1 Wildlife",D46,IF($I$4="C2 Birds in Flight",E46,IF($I$4="C3 Landscape",F46,IF($I$4="Default Settings",G46,IF($I$4="Birds in Flight",H46,IF($I$4="Birds Perched",I46,IF($I$4="Fireworks",J46,IF($I$4="Landscape",K46,IF($I$4="Macro",L46,IF($I$4="People",M46,IF($I$4="Sports",N46,IF($I$4="Travel",O46,IF($I$4="Waterdrops",P46,IF($I$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="Z46" s="38" t="str">
+        <x:f>IF($J$4="C1 Wildlife",D46,IF($J$4="C2 Birds in Flight",E46,IF($J$4="C3 Landscape",F46,IF($J$4="Default Settings",G46,IF($J$4="Birds in Flight",H46,IF($J$4="Birds Perched",I46,IF($J$4="Fireworks",J46,IF($J$4="Landscape",K46,IF($J$4="Macro",L46,IF($J$4="People",M46,IF($J$4="Sports",N46,IF($J$4="Travel",O46,IF($J$4="Waterdrops",P46,IF($J$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AA46" s="38" t="str">
+        <x:f>IF($K$4="C1 Wildlife",D46,IF($K$4="C2 Birds in Flight",E46,IF($K$4="C3 Landscape",F46,IF($K$4="Default Settings",G46,IF($K$4="Birds in Flight",H46,IF($K$4="Birds Perched",I46,IF($K$4="Fireworks",J46,IF($K$4="Landscape",K46,IF($K$4="Macro",L46,IF($K$4="People",M46,IF($K$4="Sports",N46,IF($K$4="Travel",O46,IF($K$4="Waterdrops",P46,IF($K$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AB46" s="38" t="str">
+        <x:f>IF($L$4="C1 Wildlife",D46,IF($L$4="C2 Birds in Flight",E46,IF($L$4="C3 Landscape",F46,IF($L$4="Default Settings",G46,IF($L$4="Birds in Flight",H46,IF($L$4="Birds Perched",I46,IF($L$4="Fireworks",J46,IF($L$4="Landscape",K46,IF($L$4="Macro",L46,IF($L$4="People",M46,IF($L$4="Sports",N46,IF($L$4="Travel",O46,IF($L$4="Waterdrops",P46,IF($L$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AC46" s="38" t="str">
+        <x:f>IF($M$4="C1 Wildlife",D46,IF($M$4="C2 Birds in Flight",E46,IF($M$4="C3 Landscape",F46,IF($M$4="Default Settings",G46,IF($M$4="Birds in Flight",H46,IF($M$4="Birds Perched",I46,IF($M$4="Fireworks",J46,IF($M$4="Landscape",K46,IF($M$4="Macro",L46,IF($M$4="People",M46,IF($M$4="Sports",N46,IF($M$4="Travel",O46,IF($M$4="Waterdrops",P46,IF($M$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AD46" s="38" t="str">
+        <x:f>IF($N$4="C1 Wildlife",D46,IF($N$4="C2 Birds in Flight",E46,IF($N$4="C3 Landscape",F46,IF($N$4="Default Settings",G46,IF($N$4="Birds in Flight",H46,IF($N$4="Birds Perched",I46,IF($N$4="Fireworks",J46,IF($N$4="Landscape",K46,IF($N$4="Macro",L46,IF($N$4="People",M46,IF($N$4="Sports",N46,IF($N$4="Travel",O46,IF($N$4="Waterdrops",P46,IF($N$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AE46" s="38" t="str">
+        <x:f>IF($O$4="C1 Wildlife",D46,IF($O$4="C2 Birds in Flight",E46,IF($O$4="C3 Landscape",F46,IF($O$4="Default Settings",G46,IF($O$4="Birds in Flight",H46,IF($O$4="Birds Perched",I46,IF($O$4="Fireworks",J46,IF($O$4="Landscape",K46,IF($O$4="Macro",L46,IF($O$4="People",M46,IF($O$4="Sports",N46,IF($O$4="Travel",O46,IF($O$4="Waterdrops",P46,IF($O$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AF46" s="38" t="str">
+        <x:f>IF($P$4="C1 Wildlife",D46,IF($P$4="C2 Birds in Flight",E46,IF($P$4="C3 Landscape",F46,IF($P$4="Default Settings",G46,IF($P$4="Birds in Flight",H46,IF($P$4="Birds Perched",I46,IF($P$4="Fireworks",J46,IF($P$4="Landscape",K46,IF($P$4="Macro",L46,IF($P$4="People",M46,IF($P$4="Sports",N46,IF($P$4="Travel",O46,IF($P$4="Waterdrops",P46,IF($P$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="AG46" s="38" t="str">
+        <x:f>IF($Q$4="C1 Wildlife",D46,IF($Q$4="C2 Birds in Flight",E46,IF($Q$4="C3 Landscape",F46,IF($Q$4="Default Settings",G46,IF($Q$4="Birds in Flight",H46,IF($Q$4="Birds Perched",I46,IF($Q$4="Fireworks",J46,IF($Q$4="Landscape",K46,IF($Q$4="Macro",L46,IF($Q$4="People",M46,IF($Q$4="Sports",N46,IF($Q$4="Travel",O46,IF($Q$4="Waterdrops",P46,IF($Q$4="Wildlife",Q46,""))))))))))))))</x:f>
+        <x:v>Off</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D7:D26">
+  <x:conditionalFormatting sqref="D7:D46">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <x:formula>$T7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E7:E26">
+  <x:conditionalFormatting sqref="E7:E46">
     <x:cfRule type="cellIs" dxfId="1" priority="2" operator="notEqual">
       <x:formula>$U7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="F7:F26">
+  <x:conditionalFormatting sqref="F7:F46">
     <x:cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
       <x:formula>$V7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G7:G26">
+  <x:conditionalFormatting sqref="G7:G46">
     <x:cfRule type="cellIs" dxfId="3" priority="4" operator="notEqual">
       <x:formula>$W7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="H7:H26">
+  <x:conditionalFormatting sqref="H7:H46">
     <x:cfRule type="cellIs" dxfId="4" priority="5" operator="notEqual">
       <x:formula>$X7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="I7:I26">
+  <x:conditionalFormatting sqref="I7:I46">
     <x:cfRule type="cellIs" dxfId="5" priority="6" operator="notEqual">
       <x:formula>$Y7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J7:J26">
+  <x:conditionalFormatting sqref="J7:J46">
     <x:cfRule type="cellIs" dxfId="6" priority="7" operator="notEqual">
       <x:formula>$Z7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="K7:K26">
+  <x:conditionalFormatting sqref="K7:K46">
     <x:cfRule type="cellIs" dxfId="7" priority="8" operator="notEqual">
       <x:formula>$AA7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="L7:L26">
+  <x:conditionalFormatting sqref="L7:L46">
     <x:cfRule type="cellIs" dxfId="8" priority="9" operator="notEqual">
       <x:formula>$AB7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="M7:M26">
+  <x:conditionalFormatting sqref="M7:M46">
     <x:cfRule type="cellIs" dxfId="9" priority="10" operator="notEqual">
       <x:formula>$AC7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="N7:N26">
+  <x:conditionalFormatting sqref="N7:N46">
     <x:cfRule type="cellIs" dxfId="10" priority="11" operator="notEqual">
       <x:formula>$AD7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O7:O26">
+  <x:conditionalFormatting sqref="O7:O46">
     <x:cfRule type="cellIs" dxfId="11" priority="12" operator="notEqual">
       <x:formula>$AE7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="P7:P26">
+  <x:conditionalFormatting sqref="P7:P46">
     <x:cfRule type="cellIs" dxfId="12" priority="13" operator="notEqual">
       <x:formula>$AF7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="Q7:Q26">
+  <x:conditionalFormatting sqref="Q7:Q46">
     <x:cfRule type="cellIs" dxfId="13" priority="14" operator="notEqual">
       <x:formula>$AG7</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:Q26">
+  <x:conditionalFormatting sqref="D7:Q46">
     <x:cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Not Used"/>
     <x:cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
       <x:formula>"—"</x:formula>
@@ -3388,9 +5688,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R158d399ee375412e"/>
+  <x:drawing ns1:id="R3ad92f4855234330"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R91972fff75fa46f1"/>
+    <x:tablePart ns1:id="R2f45b775b8bc43cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3609,128 +5909,128 @@
     </x:row>
     <x:row r="9" hidden="0">
       <x:c r="A9" s="15" t="str">
-        <x:v>Exposure Comp</x:v>
-      </x:c>
-      <x:c r="B9" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>ISO Value</x:v>
+      </x:c>
+      <x:c r="B9" s="17" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="C9" s="17" t="str">
-        <x:v>0 starting point</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="D9" s="17" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T9" s="38" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="T9" s="38" t="str">
         <x:f>B9</x:f>
-        <x:v>0</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="U9" s="38" t="str">
         <x:f>C9</x:f>
-        <x:v>0 starting point</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="V9" s="38" t="n">
         <x:f>D9</x:f>
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="10" hidden="0">
       <x:c r="A10" s="15" t="str">
-        <x:v>AF Operation</x:v>
-      </x:c>
-      <x:c r="B10" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="C10" s="17" t="str">
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="D10" s="17" t="str">
-        <x:v>One-Shot AF</x:v>
-      </x:c>
-      <x:c r="T10" s="38" t="str">
+        <x:v>Auto ISO Max</x:v>
+      </x:c>
+      <x:c r="B10" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="D10" s="17" t="n">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="T10" s="38" t="n">
         <x:f>B10</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="U10" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="U10" s="38" t="n">
         <x:f>C10</x:f>
-        <x:v>Servo AF</x:v>
-      </x:c>
-      <x:c r="V10" s="38" t="str">
+        <x:v>12800</x:v>
+      </x:c>
+      <x:c r="V10" s="38" t="n">
         <x:f>D10</x:f>
-        <x:v>One-Shot AF</x:v>
+        <x:v>12800</x:v>
       </x:c>
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11" s="15" t="str">
-        <x:v>Servo AF Case</x:v>
-      </x:c>
-      <x:c r="B11" s="17" t="str">
-        <x:v>Case 1 (Custom)</x:v>
+        <x:v>Exposure Comp</x:v>
+      </x:c>
+      <x:c r="B11" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
-        <x:v>Case 4</x:v>
-      </x:c>
-      <x:c r="D11" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="T11" s="38" t="str">
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="D11" s="17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T11" s="38" t="n">
         <x:f>B11</x:f>
-        <x:v>Case 1 (Custom)</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U11" s="38" t="str">
         <x:f>C11</x:f>
-        <x:v>Case 4</x:v>
-      </x:c>
-      <x:c r="V11" s="38" t="str">
+        <x:v>0 starting point</x:v>
+      </x:c>
+      <x:c r="V11" s="38" t="n">
         <x:f>D11</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12" s="15" t="str">
-        <x:v>Tracking Sensitivity</x:v>
-      </x:c>
-      <x:c r="B12" s="17" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="n">
-        <x:v>0</x:v>
+        <x:v>AF Operation</x:v>
+      </x:c>
+      <x:c r="B12" s="17" t="str">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="str">
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="D12" s="17" t="str">
-        <x:v>Not Used</x:v>
-      </x:c>
-      <x:c r="T12" s="38" t="n">
+        <x:v>One-Shot AF</x:v>
+      </x:c>
+      <x:c r="T12" s="38" t="str">
         <x:f>B12</x:f>
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="U12" s="38" t="n">
+        <x:v>Servo AF</x:v>
+      </x:c>
+      <x:c r="U12" s="38" t="str">
         <x:f>C12</x:f>
-        <x:v>0</x:v>
+        <x:v>Servo AF</x:v>
       </x:c>
       <x:c r="V12" s="38" t="str">
         <x:f>D12</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>One-Shot AF</x:v>
       </x:c>
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13" s="15" t="str">
-        <x:v>Accel./Decel. Tracking</x:v>
+        <x:v>Servo AF Case</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>+1</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="D13" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
       <x:c r="T13" s="38" t="str">
         <x:f>B13</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 1 (Custom)</x:v>
       </x:c>
       <x:c r="U13" s="38" t="str">
         <x:f>C13</x:f>
-        <x:v>+1</x:v>
+        <x:v>Case 4</x:v>
       </x:c>
       <x:c r="V13" s="38" t="str">
         <x:f>D13</x:f>
@@ -3739,24 +6039,24 @@
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14" s="15" t="str">
-        <x:v>Switching Tracked Subjects</x:v>
-      </x:c>
-      <x:c r="B14" s="17" t="str">
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="str">
-        <x:v>On subject</x:v>
+        <x:v>Tracking Sensitivity</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>Not Used</x:v>
       </x:c>
-      <x:c r="T14" s="38" t="str">
+      <x:c r="T14" s="38" t="n">
         <x:f>B14</x:f>
-        <x:v>On subject</x:v>
-      </x:c>
-      <x:c r="U14" s="38" t="str">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="U14" s="38" t="n">
         <x:f>C14</x:f>
-        <x:v>On subject</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V14" s="38" t="str">
         <x:f>D14</x:f>
@@ -3765,120 +6065,120 @@
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15" s="15" t="str">
-        <x:v>AF Method</x:v>
+        <x:v>Accel./Decel. Tracking</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="C15" s="17" t="str">
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="D15" s="17" t="str">
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="T15" s="38" t="str">
         <x:f>B15</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="U15" s="38" t="str">
         <x:f>C15</x:f>
-        <x:v>Face + Tracking</x:v>
+        <x:v>+1</x:v>
       </x:c>
       <x:c r="V15" s="38" t="str">
         <x:f>D15</x:f>
-        <x:v>1-Point AF</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
     </x:row>
     <x:row r="16" hidden="0">
       <x:c r="A16" s="15" t="str">
-        <x:v>Subject Detection</x:v>
+        <x:v>Switching Tracked Subjects</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="C16" s="17" t="str">
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
       <x:c r="T16" s="38" t="str">
         <x:f>B16</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="U16" s="38" t="str">
         <x:f>C16</x:f>
-        <x:v>Animals</x:v>
+        <x:v>On subject</x:v>
       </x:c>
       <x:c r="V16" s="38" t="str">
         <x:f>D16</x:f>
-        <x:v>None</x:v>
+        <x:v>Not Used</x:v>
       </x:c>
     </x:row>
     <x:row r="17" hidden="0">
       <x:c r="A17" s="15" t="str">
-        <x:v>Eye Detection</x:v>
+        <x:v>AF Method</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="D17" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
       <x:c r="T17" s="38" t="str">
         <x:f>B17</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="U17" s="38" t="str">
         <x:f>C17</x:f>
-        <x:v>Enable</x:v>
+        <x:v>Face + Tracking</x:v>
       </x:c>
       <x:c r="V17" s="38" t="str">
         <x:f>D17</x:f>
-        <x:v>Disable</x:v>
+        <x:v>1-Point AF</x:v>
       </x:c>
     </x:row>
     <x:row r="18" hidden="0">
       <x:c r="A18" s="15" t="str">
-        <x:v>Drive</x:v>
+        <x:v>Subject Detection</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="C18" s="17" t="str">
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="D18" s="17" t="str">
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="T18" s="38" t="str">
         <x:f>B18</x:f>
-        <x:v>High Speed Continuous</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="U18" s="38" t="str">
         <x:f>C18</x:f>
-        <x:v>High Speed Continuous+</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="V18" s="38" t="str">
         <x:f>D18</x:f>
-        <x:v>Single Shot</x:v>
+        <x:v>None</x:v>
       </x:c>
     </x:row>
     <x:row r="19" hidden="0">
       <x:c r="A19" s="15" t="str">
-        <x:v>High Speed Display</x:v>
+        <x:v>Eye Detection</x:v>
       </x:c>
       <x:c r="B19" s="17" t="str">
         <x:v>Enable</x:v>
       </x:c>
       <x:c r="C19" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D19" s="17" t="str">
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
       <x:c r="T19" s="38" t="str">
         <x:f>B19</x:f>
@@ -3886,113 +6186,633 @@
       </x:c>
       <x:c r="U19" s="38" t="str">
         <x:f>C19</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V19" s="38" t="str">
         <x:f>D19</x:f>
-        <x:v>Not Used</x:v>
+        <x:v>Disable</x:v>
       </x:c>
     </x:row>
     <x:row r="20" hidden="0">
       <x:c r="A20" s="15" t="str">
-        <x:v>Image Stabilization</x:v>
+        <x:v>Touch &amp; Drag AF</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="D20" s="17" t="str">
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="T20" s="38" t="str">
         <x:f>B20</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="U20" s="38" t="str">
         <x:f>C20</x:f>
-        <x:v>Mode 3</x:v>
+        <x:v>Enable</x:v>
       </x:c>
       <x:c r="V20" s="38" t="str">
         <x:f>D20</x:f>
-        <x:v>Mode 1</x:v>
+        <x:v>Enable</x:v>
       </x:c>
     </x:row>
     <x:row r="21" hidden="0">
       <x:c r="A21" s="15" t="str">
-        <x:v>IBIS / Lens IS</x:v>
+        <x:v>Positioning method</x:v>
       </x:c>
       <x:c r="B21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="C21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="D21" s="17" t="str">
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="T21" s="38" t="str">
         <x:f>B21</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="U21" s="38" t="str">
         <x:f>C21</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
       <x:c r="V21" s="38" t="str">
         <x:f>D21</x:f>
-        <x:v>On / On</x:v>
+        <x:v>Relative</x:v>
       </x:c>
     </x:row>
     <x:row r="22" hidden="0">
       <x:c r="A22" s="15" t="str">
-        <x:v>Focus Bracketing</x:v>
+        <x:v>Active touch area</x:v>
       </x:c>
       <x:c r="B22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="D22" s="17" t="str">
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="T22" s="38" t="str">
         <x:f>B22</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="U22" s="38" t="str">
         <x:f>C22</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
       </x:c>
       <x:c r="V22" s="38" t="str">
         <x:f>D22</x:f>
-        <x:v>Disable</x:v>
+        <x:v>Right</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" hidden="0">
+      <x:c r="A23" s="15" t="str">
+        <x:v>Drive</x:v>
+      </x:c>
+      <x:c r="B23" s="17" t="str">
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="str">
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="D23" s="17" t="str">
+        <x:v>Single Shot</x:v>
+      </x:c>
+      <x:c r="T23" s="38" t="str">
+        <x:f>B23</x:f>
+        <x:v>High Speed Continuous</x:v>
+      </x:c>
+      <x:c r="U23" s="38" t="str">
+        <x:f>C23</x:f>
+        <x:v>High Speed Continuous+</x:v>
+      </x:c>
+      <x:c r="V23" s="38" t="str">
+        <x:f>D23</x:f>
+        <x:v>Single Shot</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" hidden="0">
+      <x:c r="A24" s="15" t="str">
+        <x:v>High Speed Display</x:v>
+      </x:c>
+      <x:c r="B24" s="17" t="str">
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="D24" s="17" t="str">
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="T24" s="38" t="str">
+        <x:f>B24</x:f>
+        <x:v>Enable</x:v>
+      </x:c>
+      <x:c r="U24" s="38" t="str">
+        <x:f>C24</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+      <x:c r="V24" s="38" t="str">
+        <x:f>D24</x:f>
+        <x:v>Not Used</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" hidden="0">
+      <x:c r="A25" s="15" t="str">
+        <x:v>Image Stabilization</x:v>
+      </x:c>
+      <x:c r="B25" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="str">
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="D25" s="17" t="str">
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="T25" s="38" t="str">
+        <x:f>B25</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+      <x:c r="U25" s="38" t="str">
+        <x:f>C25</x:f>
+        <x:v>Mode 3</x:v>
+      </x:c>
+      <x:c r="V25" s="38" t="str">
+        <x:f>D25</x:f>
+        <x:v>Mode 1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" hidden="0">
+      <x:c r="A26" s="15" t="str">
+        <x:v>IBIS / Lens IS</x:v>
+      </x:c>
+      <x:c r="B26" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="D26" s="17" t="str">
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="T26" s="38" t="str">
+        <x:f>B26</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="U26" s="38" t="str">
+        <x:f>C26</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+      <x:c r="V26" s="38" t="str">
+        <x:f>D26</x:f>
+        <x:v>On / On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" hidden="0">
+      <x:c r="A27" s="15" t="str">
+        <x:v>Lens IS</x:v>
+      </x:c>
+      <x:c r="B27" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="D27" s="17" t="str">
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="T27" s="38" t="str">
+        <x:f>B27</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="U27" s="38" t="str">
+        <x:f>C27</x:f>
+        <x:v>On</x:v>
+      </x:c>
+      <x:c r="V27" s="38" t="str">
+        <x:f>D27</x:f>
+        <x:v>On</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" hidden="0">
+      <x:c r="A28" s="15" t="str">
+        <x:v>Focus Bracketing</x:v>
+      </x:c>
+      <x:c r="B28" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="D28" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="T28" s="38" t="str">
+        <x:f>B28</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U28" s="38" t="str">
+        <x:f>C28</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V28" s="38" t="str">
+        <x:f>D28</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" hidden="0">
+      <x:c r="A29" s="15" t="str">
+        <x:v>Long Exposure NR</x:v>
+      </x:c>
+      <x:c r="B29" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D29" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="T29" s="38" t="str">
+        <x:f>B29</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U29" s="38" t="str">
+        <x:f>C29</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V29" s="38" t="str">
+        <x:f>D29</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" hidden="0">
+      <x:c r="A30" s="15" t="str">
+        <x:v>Screen Info</x:v>
+      </x:c>
+      <x:c r="B30" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="D30" s="17" t="str">
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="T30" s="38" t="str">
+        <x:f>B30</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="U30" s="38" t="str">
+        <x:f>C30</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+      <x:c r="V30" s="38" t="str">
+        <x:f>D30</x:f>
+        <x:v>Modes 1–5 enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" hidden="0">
+      <x:c r="A31" s="15" t="str">
+        <x:v>Histogram</x:v>
+      </x:c>
+      <x:c r="B31" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="str">
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="T31" s="38" t="str">
+        <x:f>B31</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="U31" s="38" t="str">
+        <x:f>C31</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+      <x:c r="V31" s="38" t="str">
+        <x:f>D31</x:f>
+        <x:v>RGB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" hidden="0">
+      <x:c r="A32" s="15" t="str">
+        <x:v>Highlight Alert</x:v>
+      </x:c>
+      <x:c r="B32" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="T32" s="38" t="str">
+        <x:f>B32</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="U32" s="38" t="str">
+        <x:f>C32</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="V32" s="38" t="str">
+        <x:f>D32</x:f>
+        <x:v>Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" hidden="0">
+      <x:c r="A33" s="15" t="str">
+        <x:v>Image Quality</x:v>
+      </x:c>
+      <x:c r="B33" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="str">
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="T33" s="38" t="str">
+        <x:f>B33</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="U33" s="38" t="str">
+        <x:f>C33</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+      <x:c r="V33" s="38" t="str">
+        <x:f>D33</x:f>
+        <x:v>cRAW</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" hidden="0">
+      <x:c r="A34" s="15" t="str">
+        <x:v>Crop / Aspect</x:v>
+      </x:c>
+      <x:c r="B34" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="str">
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="T34" s="38" t="str">
+        <x:f>B34</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="U34" s="38" t="str">
+        <x:f>C34</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+      <x:c r="V34" s="38" t="str">
+        <x:f>D34</x:f>
+        <x:v>Full-frame</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" hidden="0">
+      <x:c r="A35" s="15" t="str">
+        <x:v>White Balance</x:v>
+      </x:c>
+      <x:c r="B35" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="str">
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="T35" s="38" t="str">
+        <x:f>B35</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="U35" s="38" t="str">
+        <x:f>C35</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+      <x:c r="V35" s="38" t="str">
+        <x:f>D35</x:f>
+        <x:v>AWB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" hidden="0">
+      <x:c r="A36" s="15" t="str">
+        <x:v>Picture Style</x:v>
+      </x:c>
+      <x:c r="B36" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="T36" s="38" t="str">
+        <x:f>B36</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="U36" s="38" t="str">
+        <x:f>C36</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="V36" s="38" t="str">
+        <x:f>D36</x:f>
+        <x:v>Neutral</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" hidden="0">
+      <x:c r="A37" s="15" t="str">
+        <x:v>Highlight Tone Priority</x:v>
+      </x:c>
+      <x:c r="B37" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="T37" s="38" t="str">
+        <x:f>B37</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U37" s="38" t="str">
+        <x:f>C37</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V37" s="38" t="str">
+        <x:f>D37</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" hidden="0">
+      <x:c r="A38" s="15" t="str">
+        <x:v>High ISO NR</x:v>
+      </x:c>
+      <x:c r="B38" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="T38" s="38" t="str">
+        <x:f>B38</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U38" s="38" t="str">
+        <x:f>C38</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V38" s="38" t="str">
+        <x:f>D38</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" hidden="0">
+      <x:c r="A39" s="15" t="str">
+        <x:v>C1-C3 Auto Update</x:v>
+      </x:c>
+      <x:c r="B39" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="str">
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="T39" s="38" t="str">
+        <x:f>B39</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="U39" s="38" t="str">
+        <x:f>C39</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+      <x:c r="V39" s="38" t="str">
+        <x:f>D39</x:f>
+        <x:v>Disable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" hidden="0">
+      <x:c r="A40" s="15" t="str">
+        <x:v>Electronic Full-time MF</x:v>
+      </x:c>
+      <x:c r="B40" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="T40" s="38" t="str">
+        <x:f>B40</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U40" s="38" t="str">
+        <x:f>C40</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V40" s="38" t="str">
+        <x:f>D40</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" hidden="0">
+      <x:c r="A41" s="15" t="str">
+        <x:v>IBIS High Res Shot</x:v>
+      </x:c>
+      <x:c r="B41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="T41" s="38" t="str">
+        <x:f>B41</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U41" s="38" t="str">
+        <x:f>C41</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V41" s="38" t="str">
+        <x:f>D41</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" hidden="0">
+      <x:c r="A42" s="15" t="str">
+        <x:v>Continuous AF</x:v>
+      </x:c>
+      <x:c r="B42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="T42" s="38" t="str">
+        <x:f>B42</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="U42" s="38" t="str">
+        <x:f>C42</x:f>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="V42" s="38" t="str">
+        <x:f>D42</x:f>
+        <x:v>Off</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="B3:B22">
+  <x:conditionalFormatting sqref="B3:B42">
     <x:cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
       <x:formula>$T3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="C3:C22">
+  <x:conditionalFormatting sqref="C3:C42">
     <x:cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
       <x:formula>$U3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D3:D22">
+  <x:conditionalFormatting sqref="D3:D42">
     <x:cfRule type="cellIs" dxfId="18" priority="3" operator="notEqual">
       <x:formula>$V3</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rbb0a4e13996e43a9"/>
+    <x:tablePart ns1:id="Rf2514e0a8141408a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="Re1db1ead78ab43e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R142c6c1c8fa1455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R1605a80ff87a4e7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R300ecaccc8284d70"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="ebb6a567-5e25-4d25-b93e-b67911893025"/>
+        <xdr:cNvPr id="1" name="ef97ad79-dcc8-4f8a-bf02-5ad11eddf51a"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re6a82793416b4b5e"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf3c48f2783404676"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5688,9 +5688,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R3ad92f4855234330"/>
+  <x:drawing ns1:id="R3ce5f156e4b54536"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2f45b775b8bc43cc"/>
+    <x:tablePart ns1:id="R2edb6d31fea54b68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6812,7 +6812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rf2514e0a8141408a"/>
+    <x:tablePart ns1:id="Rc8c04f183a464052"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R1605a80ff87a4e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R300ecaccc8284d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R2b71e983934b43cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R4c859fbab7294416"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="ef97ad79-dcc8-4f8a-bf02-5ad11eddf51a"/>
+        <xdr:cNvPr id="1" name="4e3c650b-177e-4591-96fd-6ce5c8637f71"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf3c48f2783404676"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd08045b2bc8648ef"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5688,9 +5688,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R3ce5f156e4b54536"/>
+  <x:drawing ns1:id="R667ec60e70704171"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R2edb6d31fea54b68"/>
+    <x:tablePart ns1:id="R6f4ec5d0f86f4607"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5725,7 +5725,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="43" t="str">
-        <x:v>Approved registration targets pending physical verification. Ordinary copy/paste back to the matching C1–C3 column restores both the target values and compatible comparison highlighting.</x:v>
+        <x:v>Session-3 camera-body targets; lens Mode 1/3 remains pending. Edited targets require physical re-verification. Ordinary copy/paste back to the matching C1–C3 column restores both the target values and compatible comparison highlighting.</x:v>
       </x:c>
       <x:c r="B1" s="43"/>
       <x:c r="C1" s="43"/>
@@ -6812,7 +6812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rc8c04f183a464052"/>
+    <x:tablePart ns1:id="R5430a6c1abbb482d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R2b71e983934b43cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R4c859fbab7294416"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R4a02eb6137ad4a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R7acf3d80f6c34912"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="4e3c650b-177e-4591-96fd-6ce5c8637f71"/>
+        <xdr:cNvPr id="1" name="5bb49d56-76b8-44d2-8c16-e921227b674f"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rd08045b2bc8648ef"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R385622037a8d4e94"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5688,9 +5688,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R667ec60e70704171"/>
+  <x:drawing ns1:id="Rd29f6c7ef03b4597"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R6f4ec5d0f86f4607"/>
+    <x:tablePart ns1:id="Raf616c98a43942cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6812,7 +6812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R5430a6c1abbb482d"/>
+    <x:tablePart ns1:id="Rdbfd415a2e4d4840"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R4a02eb6137ad4a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R7acf3d80f6c34912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R9615eda7ce6e44e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R92a92fee229d4f81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="5bb49d56-76b8-44d2-8c16-e921227b674f"/>
+        <xdr:cNvPr id="1" name="927dbb08-e6ac-4484-b4fe-1937c1351bd1"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R385622037a8d4e94"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re34fbd3c99f2416c"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5688,9 +5688,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="Rd29f6c7ef03b4597"/>
+  <x:drawing ns1:id="R1723229fa62d426d"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Raf616c98a43942cd"/>
+    <x:tablePart ns1:id="R89cd764354044205"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6812,7 +6812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rdbfd415a2e4d4840"/>
+    <x:tablePart ns1:id="Rcfa9b9e74ad34633"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/downloads/Subject Settings Matrix.xlsx
+++ b/docs/downloads/Subject Settings Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R9615eda7ce6e44e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R92a92fee229d4f81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subject Settings Matrix" sheetId="1" r:id="R4a02eb6137ad4a3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C1-C3 Defaults" sheetId="2" r:id="R7acf3d80f6c34912"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,13 +432,13 @@
     <xdr:ext cx="24765000" cy="1200150"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="927dbb08-e6ac-4484-b4fe-1937c1351bd1"/>
+        <xdr:cNvPr id="1" name="5bb49d56-76b8-44d2-8c16-e921227b674f"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re34fbd3c99f2416c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R385622037a8d4e94"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5688,9 +5688,9 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing ns1:id="R1723229fa62d426d"/>
+  <x:drawing ns1:id="Rd29f6c7ef03b4597"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="R89cd764354044205"/>
+    <x:tablePart ns1:id="Raf616c98a43942cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6812,7 +6812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart ns1:id="Rcfa9b9e74ad34633"/>
+    <x:tablePart ns1:id="Rdbfd415a2e4d4840"/>
   </x:tableParts>
 </x:worksheet>
 </file>